--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kasus Uji" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prasyarat" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tombol Makro (opsional)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$244</definedName>
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,18 +73,9 @@
     <font>
       <b val="1"/>
       <color rgb="004F46E5"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="10.5"/>
-    </font>
-    <font>
-      <name val="Menlo"/>
-      <sz val="9.5"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="006E728C"/>
       <sz val="10.5"/>
     </font>
     <font>
@@ -104,11 +95,6 @@
     <font>
       <i val="1"/>
       <color rgb="00B91C1C"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="004F46E5"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -199,11 +185,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -215,9 +201,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -267,12 +253,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10326,8 +10307,8 @@
     <col width="16" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
     <col width="34" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
@@ -10339,20 +10320,20 @@
       </c>
       <c r="C1" s="24" t="inlineStr">
         <is>
-          <t>Isi satu baris per temuan. Simpan tangkapan layarnya di folder defect-capture, lalu tulis nama berkasnya di kolom Capture.</t>
+          <t>Isi satu baris per temuan. Unggah tangkapan layarnya ke folder Drive, lalu tempel tautan berkasnya di kolom Link Capture.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="25">
-        <f>HYPERLINK("defect-capture", "📎  BUKA FOLDER CAPTURE")</f>
+        <f>HYPERLINK("https://drive.google.com/drive/folders/1MonfUjlqV0aABrLDleDZhugd3pULLIOf?usp=sharing", "BUKA FOLDER CAPTURE")</f>
         <v/>
       </c>
       <c r="B2" s="26" t="n"/>
       <c r="C2" s="27" t="n"/>
       <c r="D2" s="28" t="inlineStr">
         <is>
-          <t>Seret tangkapan layarnya ke folder itu, beri nama sesuai ID temuan (DF-001.jpg), lalu tulis namanya di kolom Capture.</t>
+          <t>Unggah ke folder itu, beri nama sesuai ID temuan (DF-001.jpg), lalu Salin Tautan berkasnya dan tempel di kolom Link Capture.</t>
         </is>
       </c>
     </row>
@@ -10454,12 +10435,12 @@
       </c>
       <c r="T4" s="12" t="inlineStr">
         <is>
-          <t>Capture</t>
+          <t>Link Capture</t>
         </is>
       </c>
       <c r="U4" s="12" t="inlineStr">
         <is>
-          <t>Buka Capture</t>
+          <t>Buka</t>
         </is>
       </c>
       <c r="V4" s="12" t="inlineStr">
@@ -10490,7 +10471,7 @@
       <c r="S5" s="13" t="n"/>
       <c r="T5" s="13" t="n"/>
       <c r="U5" s="29">
-        <f>IF(T5="","",HYPERLINK("defect-capture/"&amp;T5,"Buka"))</f>
+        <f>IF(T5="","",HYPERLINK(T5,"Buka"))</f>
         <v/>
       </c>
       <c r="V5" s="13" t="n"/>
@@ -10517,7 +10498,7 @@
       <c r="S6" s="16" t="n"/>
       <c r="T6" s="16" t="n"/>
       <c r="U6" s="30">
-        <f>IF(T6="","",HYPERLINK("defect-capture/"&amp;T6,"Buka"))</f>
+        <f>IF(T6="","",HYPERLINK(T6,"Buka"))</f>
         <v/>
       </c>
       <c r="V6" s="16" t="n"/>
@@ -10544,7 +10525,7 @@
       <c r="S7" s="13" t="n"/>
       <c r="T7" s="13" t="n"/>
       <c r="U7" s="29">
-        <f>IF(T7="","",HYPERLINK("defect-capture/"&amp;T7,"Buka"))</f>
+        <f>IF(T7="","",HYPERLINK(T7,"Buka"))</f>
         <v/>
       </c>
       <c r="V7" s="13" t="n"/>
@@ -10571,7 +10552,7 @@
       <c r="S8" s="16" t="n"/>
       <c r="T8" s="16" t="n"/>
       <c r="U8" s="30">
-        <f>IF(T8="","",HYPERLINK("defect-capture/"&amp;T8,"Buka"))</f>
+        <f>IF(T8="","",HYPERLINK(T8,"Buka"))</f>
         <v/>
       </c>
       <c r="V8" s="16" t="n"/>
@@ -10598,7 +10579,7 @@
       <c r="S9" s="13" t="n"/>
       <c r="T9" s="13" t="n"/>
       <c r="U9" s="29">
-        <f>IF(T9="","",HYPERLINK("defect-capture/"&amp;T9,"Buka"))</f>
+        <f>IF(T9="","",HYPERLINK(T9,"Buka"))</f>
         <v/>
       </c>
       <c r="V9" s="13" t="n"/>
@@ -10625,7 +10606,7 @@
       <c r="S10" s="16" t="n"/>
       <c r="T10" s="16" t="n"/>
       <c r="U10" s="30">
-        <f>IF(T10="","",HYPERLINK("defect-capture/"&amp;T10,"Buka"))</f>
+        <f>IF(T10="","",HYPERLINK(T10,"Buka"))</f>
         <v/>
       </c>
       <c r="V10" s="16" t="n"/>
@@ -10652,7 +10633,7 @@
       <c r="S11" s="13" t="n"/>
       <c r="T11" s="13" t="n"/>
       <c r="U11" s="29">
-        <f>IF(T11="","",HYPERLINK("defect-capture/"&amp;T11,"Buka"))</f>
+        <f>IF(T11="","",HYPERLINK(T11,"Buka"))</f>
         <v/>
       </c>
       <c r="V11" s="13" t="n"/>
@@ -10679,7 +10660,7 @@
       <c r="S12" s="16" t="n"/>
       <c r="T12" s="16" t="n"/>
       <c r="U12" s="30">
-        <f>IF(T12="","",HYPERLINK("defect-capture/"&amp;T12,"Buka"))</f>
+        <f>IF(T12="","",HYPERLINK(T12,"Buka"))</f>
         <v/>
       </c>
       <c r="V12" s="16" t="n"/>
@@ -10706,7 +10687,7 @@
       <c r="S13" s="13" t="n"/>
       <c r="T13" s="13" t="n"/>
       <c r="U13" s="29">
-        <f>IF(T13="","",HYPERLINK("defect-capture/"&amp;T13,"Buka"))</f>
+        <f>IF(T13="","",HYPERLINK(T13,"Buka"))</f>
         <v/>
       </c>
       <c r="V13" s="13" t="n"/>
@@ -10733,7 +10714,7 @@
       <c r="S14" s="16" t="n"/>
       <c r="T14" s="16" t="n"/>
       <c r="U14" s="30">
-        <f>IF(T14="","",HYPERLINK("defect-capture/"&amp;T14,"Buka"))</f>
+        <f>IF(T14="","",HYPERLINK(T14,"Buka"))</f>
         <v/>
       </c>
       <c r="V14" s="16" t="n"/>
@@ -10760,7 +10741,7 @@
       <c r="S15" s="13" t="n"/>
       <c r="T15" s="13" t="n"/>
       <c r="U15" s="29">
-        <f>IF(T15="","",HYPERLINK("defect-capture/"&amp;T15,"Buka"))</f>
+        <f>IF(T15="","",HYPERLINK(T15,"Buka"))</f>
         <v/>
       </c>
       <c r="V15" s="13" t="n"/>
@@ -10787,7 +10768,7 @@
       <c r="S16" s="16" t="n"/>
       <c r="T16" s="16" t="n"/>
       <c r="U16" s="30">
-        <f>IF(T16="","",HYPERLINK("defect-capture/"&amp;T16,"Buka"))</f>
+        <f>IF(T16="","",HYPERLINK(T16,"Buka"))</f>
         <v/>
       </c>
       <c r="V16" s="16" t="n"/>
@@ -10814,7 +10795,7 @@
       <c r="S17" s="13" t="n"/>
       <c r="T17" s="13" t="n"/>
       <c r="U17" s="29">
-        <f>IF(T17="","",HYPERLINK("defect-capture/"&amp;T17,"Buka"))</f>
+        <f>IF(T17="","",HYPERLINK(T17,"Buka"))</f>
         <v/>
       </c>
       <c r="V17" s="13" t="n"/>
@@ -10841,7 +10822,7 @@
       <c r="S18" s="16" t="n"/>
       <c r="T18" s="16" t="n"/>
       <c r="U18" s="30">
-        <f>IF(T18="","",HYPERLINK("defect-capture/"&amp;T18,"Buka"))</f>
+        <f>IF(T18="","",HYPERLINK(T18,"Buka"))</f>
         <v/>
       </c>
       <c r="V18" s="16" t="n"/>
@@ -10868,7 +10849,7 @@
       <c r="S19" s="13" t="n"/>
       <c r="T19" s="13" t="n"/>
       <c r="U19" s="29">
-        <f>IF(T19="","",HYPERLINK("defect-capture/"&amp;T19,"Buka"))</f>
+        <f>IF(T19="","",HYPERLINK(T19,"Buka"))</f>
         <v/>
       </c>
       <c r="V19" s="13" t="n"/>
@@ -10895,7 +10876,7 @@
       <c r="S20" s="16" t="n"/>
       <c r="T20" s="16" t="n"/>
       <c r="U20" s="30">
-        <f>IF(T20="","",HYPERLINK("defect-capture/"&amp;T20,"Buka"))</f>
+        <f>IF(T20="","",HYPERLINK(T20,"Buka"))</f>
         <v/>
       </c>
       <c r="V20" s="16" t="n"/>
@@ -10922,7 +10903,7 @@
       <c r="S21" s="13" t="n"/>
       <c r="T21" s="13" t="n"/>
       <c r="U21" s="29">
-        <f>IF(T21="","",HYPERLINK("defect-capture/"&amp;T21,"Buka"))</f>
+        <f>IF(T21="","",HYPERLINK(T21,"Buka"))</f>
         <v/>
       </c>
       <c r="V21" s="13" t="n"/>
@@ -10949,7 +10930,7 @@
       <c r="S22" s="16" t="n"/>
       <c r="T22" s="16" t="n"/>
       <c r="U22" s="30">
-        <f>IF(T22="","",HYPERLINK("defect-capture/"&amp;T22,"Buka"))</f>
+        <f>IF(T22="","",HYPERLINK(T22,"Buka"))</f>
         <v/>
       </c>
       <c r="V22" s="16" t="n"/>
@@ -10976,7 +10957,7 @@
       <c r="S23" s="13" t="n"/>
       <c r="T23" s="13" t="n"/>
       <c r="U23" s="29">
-        <f>IF(T23="","",HYPERLINK("defect-capture/"&amp;T23,"Buka"))</f>
+        <f>IF(T23="","",HYPERLINK(T23,"Buka"))</f>
         <v/>
       </c>
       <c r="V23" s="13" t="n"/>
@@ -11003,7 +10984,7 @@
       <c r="S24" s="16" t="n"/>
       <c r="T24" s="16" t="n"/>
       <c r="U24" s="30">
-        <f>IF(T24="","",HYPERLINK("defect-capture/"&amp;T24,"Buka"))</f>
+        <f>IF(T24="","",HYPERLINK(T24,"Buka"))</f>
         <v/>
       </c>
       <c r="V24" s="16" t="n"/>
@@ -11030,7 +11011,7 @@
       <c r="S25" s="13" t="n"/>
       <c r="T25" s="13" t="n"/>
       <c r="U25" s="29">
-        <f>IF(T25="","",HYPERLINK("defect-capture/"&amp;T25,"Buka"))</f>
+        <f>IF(T25="","",HYPERLINK(T25,"Buka"))</f>
         <v/>
       </c>
       <c r="V25" s="13" t="n"/>
@@ -11057,7 +11038,7 @@
       <c r="S26" s="16" t="n"/>
       <c r="T26" s="16" t="n"/>
       <c r="U26" s="30">
-        <f>IF(T26="","",HYPERLINK("defect-capture/"&amp;T26,"Buka"))</f>
+        <f>IF(T26="","",HYPERLINK(T26,"Buka"))</f>
         <v/>
       </c>
       <c r="V26" s="16" t="n"/>
@@ -11084,7 +11065,7 @@
       <c r="S27" s="13" t="n"/>
       <c r="T27" s="13" t="n"/>
       <c r="U27" s="29">
-        <f>IF(T27="","",HYPERLINK("defect-capture/"&amp;T27,"Buka"))</f>
+        <f>IF(T27="","",HYPERLINK(T27,"Buka"))</f>
         <v/>
       </c>
       <c r="V27" s="13" t="n"/>
@@ -11111,7 +11092,7 @@
       <c r="S28" s="16" t="n"/>
       <c r="T28" s="16" t="n"/>
       <c r="U28" s="30">
-        <f>IF(T28="","",HYPERLINK("defect-capture/"&amp;T28,"Buka"))</f>
+        <f>IF(T28="","",HYPERLINK(T28,"Buka"))</f>
         <v/>
       </c>
       <c r="V28" s="16" t="n"/>
@@ -11138,7 +11119,7 @@
       <c r="S29" s="13" t="n"/>
       <c r="T29" s="13" t="n"/>
       <c r="U29" s="29">
-        <f>IF(T29="","",HYPERLINK("defect-capture/"&amp;T29,"Buka"))</f>
+        <f>IF(T29="","",HYPERLINK(T29,"Buka"))</f>
         <v/>
       </c>
       <c r="V29" s="13" t="n"/>
@@ -11165,7 +11146,7 @@
       <c r="S30" s="16" t="n"/>
       <c r="T30" s="16" t="n"/>
       <c r="U30" s="30">
-        <f>IF(T30="","",HYPERLINK("defect-capture/"&amp;T30,"Buka"))</f>
+        <f>IF(T30="","",HYPERLINK(T30,"Buka"))</f>
         <v/>
       </c>
       <c r="V30" s="16" t="n"/>
@@ -11192,7 +11173,7 @@
       <c r="S31" s="13" t="n"/>
       <c r="T31" s="13" t="n"/>
       <c r="U31" s="29">
-        <f>IF(T31="","",HYPERLINK("defect-capture/"&amp;T31,"Buka"))</f>
+        <f>IF(T31="","",HYPERLINK(T31,"Buka"))</f>
         <v/>
       </c>
       <c r="V31" s="13" t="n"/>
@@ -11219,7 +11200,7 @@
       <c r="S32" s="16" t="n"/>
       <c r="T32" s="16" t="n"/>
       <c r="U32" s="30">
-        <f>IF(T32="","",HYPERLINK("defect-capture/"&amp;T32,"Buka"))</f>
+        <f>IF(T32="","",HYPERLINK(T32,"Buka"))</f>
         <v/>
       </c>
       <c r="V32" s="16" t="n"/>
@@ -11246,7 +11227,7 @@
       <c r="S33" s="13" t="n"/>
       <c r="T33" s="13" t="n"/>
       <c r="U33" s="29">
-        <f>IF(T33="","",HYPERLINK("defect-capture/"&amp;T33,"Buka"))</f>
+        <f>IF(T33="","",HYPERLINK(T33,"Buka"))</f>
         <v/>
       </c>
       <c r="V33" s="13" t="n"/>
@@ -11273,7 +11254,7 @@
       <c r="S34" s="16" t="n"/>
       <c r="T34" s="16" t="n"/>
       <c r="U34" s="30">
-        <f>IF(T34="","",HYPERLINK("defect-capture/"&amp;T34,"Buka"))</f>
+        <f>IF(T34="","",HYPERLINK(T34,"Buka"))</f>
         <v/>
       </c>
       <c r="V34" s="16" t="n"/>
@@ -11300,7 +11281,7 @@
       <c r="S35" s="13" t="n"/>
       <c r="T35" s="13" t="n"/>
       <c r="U35" s="29">
-        <f>IF(T35="","",HYPERLINK("defect-capture/"&amp;T35,"Buka"))</f>
+        <f>IF(T35="","",HYPERLINK(T35,"Buka"))</f>
         <v/>
       </c>
       <c r="V35" s="13" t="n"/>
@@ -11327,7 +11308,7 @@
       <c r="S36" s="16" t="n"/>
       <c r="T36" s="16" t="n"/>
       <c r="U36" s="30">
-        <f>IF(T36="","",HYPERLINK("defect-capture/"&amp;T36,"Buka"))</f>
+        <f>IF(T36="","",HYPERLINK(T36,"Buka"))</f>
         <v/>
       </c>
       <c r="V36" s="16" t="n"/>
@@ -11354,7 +11335,7 @@
       <c r="S37" s="13" t="n"/>
       <c r="T37" s="13" t="n"/>
       <c r="U37" s="29">
-        <f>IF(T37="","",HYPERLINK("defect-capture/"&amp;T37,"Buka"))</f>
+        <f>IF(T37="","",HYPERLINK(T37,"Buka"))</f>
         <v/>
       </c>
       <c r="V37" s="13" t="n"/>
@@ -11381,7 +11362,7 @@
       <c r="S38" s="16" t="n"/>
       <c r="T38" s="16" t="n"/>
       <c r="U38" s="30">
-        <f>IF(T38="","",HYPERLINK("defect-capture/"&amp;T38,"Buka"))</f>
+        <f>IF(T38="","",HYPERLINK(T38,"Buka"))</f>
         <v/>
       </c>
       <c r="V38" s="16" t="n"/>
@@ -11408,7 +11389,7 @@
       <c r="S39" s="13" t="n"/>
       <c r="T39" s="13" t="n"/>
       <c r="U39" s="29">
-        <f>IF(T39="","",HYPERLINK("defect-capture/"&amp;T39,"Buka"))</f>
+        <f>IF(T39="","",HYPERLINK(T39,"Buka"))</f>
         <v/>
       </c>
       <c r="V39" s="13" t="n"/>
@@ -11435,7 +11416,7 @@
       <c r="S40" s="16" t="n"/>
       <c r="T40" s="16" t="n"/>
       <c r="U40" s="30">
-        <f>IF(T40="","",HYPERLINK("defect-capture/"&amp;T40,"Buka"))</f>
+        <f>IF(T40="","",HYPERLINK(T40,"Buka"))</f>
         <v/>
       </c>
       <c r="V40" s="16" t="n"/>
@@ -11462,7 +11443,7 @@
       <c r="S41" s="13" t="n"/>
       <c r="T41" s="13" t="n"/>
       <c r="U41" s="29">
-        <f>IF(T41="","",HYPERLINK("defect-capture/"&amp;T41,"Buka"))</f>
+        <f>IF(T41="","",HYPERLINK(T41,"Buka"))</f>
         <v/>
       </c>
       <c r="V41" s="13" t="n"/>
@@ -11489,7 +11470,7 @@
       <c r="S42" s="16" t="n"/>
       <c r="T42" s="16" t="n"/>
       <c r="U42" s="30">
-        <f>IF(T42="","",HYPERLINK("defect-capture/"&amp;T42,"Buka"))</f>
+        <f>IF(T42="","",HYPERLINK(T42,"Buka"))</f>
         <v/>
       </c>
       <c r="V42" s="16" t="n"/>
@@ -11516,7 +11497,7 @@
       <c r="S43" s="13" t="n"/>
       <c r="T43" s="13" t="n"/>
       <c r="U43" s="29">
-        <f>IF(T43="","",HYPERLINK("defect-capture/"&amp;T43,"Buka"))</f>
+        <f>IF(T43="","",HYPERLINK(T43,"Buka"))</f>
         <v/>
       </c>
       <c r="V43" s="13" t="n"/>
@@ -11543,7 +11524,7 @@
       <c r="S44" s="16" t="n"/>
       <c r="T44" s="16" t="n"/>
       <c r="U44" s="30">
-        <f>IF(T44="","",HYPERLINK("defect-capture/"&amp;T44,"Buka"))</f>
+        <f>IF(T44="","",HYPERLINK(T44,"Buka"))</f>
         <v/>
       </c>
       <c r="V44" s="16" t="n"/>
@@ -11570,7 +11551,7 @@
       <c r="S45" s="13" t="n"/>
       <c r="T45" s="13" t="n"/>
       <c r="U45" s="29">
-        <f>IF(T45="","",HYPERLINK("defect-capture/"&amp;T45,"Buka"))</f>
+        <f>IF(T45="","",HYPERLINK(T45,"Buka"))</f>
         <v/>
       </c>
       <c r="V45" s="13" t="n"/>
@@ -11597,7 +11578,7 @@
       <c r="S46" s="16" t="n"/>
       <c r="T46" s="16" t="n"/>
       <c r="U46" s="30">
-        <f>IF(T46="","",HYPERLINK("defect-capture/"&amp;T46,"Buka"))</f>
+        <f>IF(T46="","",HYPERLINK(T46,"Buka"))</f>
         <v/>
       </c>
       <c r="V46" s="16" t="n"/>
@@ -11624,7 +11605,7 @@
       <c r="S47" s="13" t="n"/>
       <c r="T47" s="13" t="n"/>
       <c r="U47" s="29">
-        <f>IF(T47="","",HYPERLINK("defect-capture/"&amp;T47,"Buka"))</f>
+        <f>IF(T47="","",HYPERLINK(T47,"Buka"))</f>
         <v/>
       </c>
       <c r="V47" s="13" t="n"/>
@@ -11651,7 +11632,7 @@
       <c r="S48" s="16" t="n"/>
       <c r="T48" s="16" t="n"/>
       <c r="U48" s="30">
-        <f>IF(T48="","",HYPERLINK("defect-capture/"&amp;T48,"Buka"))</f>
+        <f>IF(T48="","",HYPERLINK(T48,"Buka"))</f>
         <v/>
       </c>
       <c r="V48" s="16" t="n"/>
@@ -11678,7 +11659,7 @@
       <c r="S49" s="13" t="n"/>
       <c r="T49" s="13" t="n"/>
       <c r="U49" s="29">
-        <f>IF(T49="","",HYPERLINK("defect-capture/"&amp;T49,"Buka"))</f>
+        <f>IF(T49="","",HYPERLINK(T49,"Buka"))</f>
         <v/>
       </c>
       <c r="V49" s="13" t="n"/>
@@ -11705,7 +11686,7 @@
       <c r="S50" s="16" t="n"/>
       <c r="T50" s="16" t="n"/>
       <c r="U50" s="30">
-        <f>IF(T50="","",HYPERLINK("defect-capture/"&amp;T50,"Buka"))</f>
+        <f>IF(T50="","",HYPERLINK(T50,"Buka"))</f>
         <v/>
       </c>
       <c r="V50" s="16" t="n"/>
@@ -11732,7 +11713,7 @@
       <c r="S51" s="13" t="n"/>
       <c r="T51" s="13" t="n"/>
       <c r="U51" s="29">
-        <f>IF(T51="","",HYPERLINK("defect-capture/"&amp;T51,"Buka"))</f>
+        <f>IF(T51="","",HYPERLINK(T51,"Buka"))</f>
         <v/>
       </c>
       <c r="V51" s="13" t="n"/>
@@ -11759,7 +11740,7 @@
       <c r="S52" s="16" t="n"/>
       <c r="T52" s="16" t="n"/>
       <c r="U52" s="30">
-        <f>IF(T52="","",HYPERLINK("defect-capture/"&amp;T52,"Buka"))</f>
+        <f>IF(T52="","",HYPERLINK(T52,"Buka"))</f>
         <v/>
       </c>
       <c r="V52" s="16" t="n"/>
@@ -11786,7 +11767,7 @@
       <c r="S53" s="13" t="n"/>
       <c r="T53" s="13" t="n"/>
       <c r="U53" s="29">
-        <f>IF(T53="","",HYPERLINK("defect-capture/"&amp;T53,"Buka"))</f>
+        <f>IF(T53="","",HYPERLINK(T53,"Buka"))</f>
         <v/>
       </c>
       <c r="V53" s="13" t="n"/>
@@ -11813,7 +11794,7 @@
       <c r="S54" s="16" t="n"/>
       <c r="T54" s="16" t="n"/>
       <c r="U54" s="30">
-        <f>IF(T54="","",HYPERLINK("defect-capture/"&amp;T54,"Buka"))</f>
+        <f>IF(T54="","",HYPERLINK(T54,"Buka"))</f>
         <v/>
       </c>
       <c r="V54" s="16" t="n"/>
@@ -11840,7 +11821,7 @@
       <c r="S55" s="13" t="n"/>
       <c r="T55" s="13" t="n"/>
       <c r="U55" s="29">
-        <f>IF(T55="","",HYPERLINK("defect-capture/"&amp;T55,"Buka"))</f>
+        <f>IF(T55="","",HYPERLINK(T55,"Buka"))</f>
         <v/>
       </c>
       <c r="V55" s="13" t="n"/>
@@ -11867,7 +11848,7 @@
       <c r="S56" s="16" t="n"/>
       <c r="T56" s="16" t="n"/>
       <c r="U56" s="30">
-        <f>IF(T56="","",HYPERLINK("defect-capture/"&amp;T56,"Buka"))</f>
+        <f>IF(T56="","",HYPERLINK(T56,"Buka"))</f>
         <v/>
       </c>
       <c r="V56" s="16" t="n"/>
@@ -11894,7 +11875,7 @@
       <c r="S57" s="13" t="n"/>
       <c r="T57" s="13" t="n"/>
       <c r="U57" s="29">
-        <f>IF(T57="","",HYPERLINK("defect-capture/"&amp;T57,"Buka"))</f>
+        <f>IF(T57="","",HYPERLINK(T57,"Buka"))</f>
         <v/>
       </c>
       <c r="V57" s="13" t="n"/>
@@ -11921,7 +11902,7 @@
       <c r="S58" s="16" t="n"/>
       <c r="T58" s="16" t="n"/>
       <c r="U58" s="30">
-        <f>IF(T58="","",HYPERLINK("defect-capture/"&amp;T58,"Buka"))</f>
+        <f>IF(T58="","",HYPERLINK(T58,"Buka"))</f>
         <v/>
       </c>
       <c r="V58" s="16" t="n"/>
@@ -11948,7 +11929,7 @@
       <c r="S59" s="13" t="n"/>
       <c r="T59" s="13" t="n"/>
       <c r="U59" s="29">
-        <f>IF(T59="","",HYPERLINK("defect-capture/"&amp;T59,"Buka"))</f>
+        <f>IF(T59="","",HYPERLINK(T59,"Buka"))</f>
         <v/>
       </c>
       <c r="V59" s="13" t="n"/>
@@ -11975,7 +11956,7 @@
       <c r="S60" s="16" t="n"/>
       <c r="T60" s="16" t="n"/>
       <c r="U60" s="30">
-        <f>IF(T60="","",HYPERLINK("defect-capture/"&amp;T60,"Buka"))</f>
+        <f>IF(T60="","",HYPERLINK(T60,"Buka"))</f>
         <v/>
       </c>
       <c r="V60" s="16" t="n"/>
@@ -12002,7 +11983,7 @@
       <c r="S61" s="13" t="n"/>
       <c r="T61" s="13" t="n"/>
       <c r="U61" s="29">
-        <f>IF(T61="","",HYPERLINK("defect-capture/"&amp;T61,"Buka"))</f>
+        <f>IF(T61="","",HYPERLINK(T61,"Buka"))</f>
         <v/>
       </c>
       <c r="V61" s="13" t="n"/>
@@ -12029,7 +12010,7 @@
       <c r="S62" s="16" t="n"/>
       <c r="T62" s="16" t="n"/>
       <c r="U62" s="30">
-        <f>IF(T62="","",HYPERLINK("defect-capture/"&amp;T62,"Buka"))</f>
+        <f>IF(T62="","",HYPERLINK(T62,"Buka"))</f>
         <v/>
       </c>
       <c r="V62" s="16" t="n"/>
@@ -12056,7 +12037,7 @@
       <c r="S63" s="13" t="n"/>
       <c r="T63" s="13" t="n"/>
       <c r="U63" s="29">
-        <f>IF(T63="","",HYPERLINK("defect-capture/"&amp;T63,"Buka"))</f>
+        <f>IF(T63="","",HYPERLINK(T63,"Buka"))</f>
         <v/>
       </c>
       <c r="V63" s="13" t="n"/>
@@ -12083,7 +12064,7 @@
       <c r="S64" s="16" t="n"/>
       <c r="T64" s="16" t="n"/>
       <c r="U64" s="30">
-        <f>IF(T64="","",HYPERLINK("defect-capture/"&amp;T64,"Buka"))</f>
+        <f>IF(T64="","",HYPERLINK(T64,"Buka"))</f>
         <v/>
       </c>
       <c r="V64" s="16" t="n"/>
@@ -12308,281 +12289,125 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B46"/>
+  <dimension ref="B1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="108" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="31" t="inlineStr">
-        <is>
-          <t>Tombol unggah capture — kalau memakai Excel desktop</t>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Melampirkan tangkapan layar temuan</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="32" t="inlineStr"/>
+      <c r="B2" s="31" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="B3" s="32" t="inlineStr">
-        <is>
-          <t>Tombol ungu di lembar Defect membuka folder capture, lalu gambarnya diseret ke sana. Itu bekerja di Excel, LibreOffice, maupun Numbers, dan tidak butuh izin apa pun.</t>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>1.  Ambil tangkapan layar di HP saat temuannya terlihat.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="32" t="inlineStr"/>
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>2.  Klik tombol BUKA FOLDER CAPTURE di lembar Defect — folder Drive-nya terbuka di peramban.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="32" t="inlineStr">
-        <is>
-          <t>Kalau ingin tombol yang benar-benar membuka jendela pilih berkas lalu menyalin gambarnya sendiri, itu butuh makro — dan makro hanya hidup di berkas .xlsm. Sekali pasang:</t>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>3.  Unggah gambarnya ke sana, beri nama sesuai ID temuan: DF-001.jpg. Kalau butuh lebih dari satu, tambahkan keterangan: DF-001-sebelum.jpg, DF-001-sesudah.jpg.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="32" t="inlineStr"/>
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>4.  Klik kanan berkasnya di Drive - Bagikan - Salin tautan.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="32" t="inlineStr">
-        <is>
-          <t>1.  Simpan berkas ini sebagai .xlsm  (File - Save As - Excel Macro-Enabled Workbook)</t>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>5.  Tempel tautannya di kolom Link Capture pada baris temuan itu. Kolom Buka di sebelahnya berubah sendiri jadi tautan yang bisa diklik.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="32" t="inlineStr">
-        <is>
-          <t>2.  Alt+F11, atau Tools - Macro - Visual Basic Editor di Mac</t>
-        </is>
-      </c>
+      <c r="B8" s="31" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="32" t="inlineStr">
-        <is>
-          <t>3.  Insert - Module, tempel kode di bawah</t>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Pastikan aksesnya "Siapa saja yang memiliki link"</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>4.  Kembali ke lembar Defect, Developer - Insert - Button, tautkan ke UnggahCapture</t>
-        </is>
-      </c>
+      <c r="B10" s="31" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="B11" s="32" t="inlineStr"/>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Tautan yang hanya bisa dibuka pemiliknya sama saja dengan tidak dilampirkan: yang membaca laporan ini nanti bukan orang yang mengunggahnya, dan dia akan berhenti di halaman minta izin.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="inlineStr">
-        <is>
-          <t>KODE VBA</t>
-        </is>
-      </c>
+      <c r="B12" s="31" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="B13" s="32" t="inlineStr"/>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Kenapa gambarnya tidak ditempel langsung ke Excel</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="B14" s="33" t="inlineStr">
-        <is>
-          <t>Sub UnggahCapture()</t>
-        </is>
-      </c>
+      <c r="B14" s="31" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Dim asal As Variant, tujuan As String, folder As String</t>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Satu tangkapan layar HP berukuran 300-800 KB. Tiga puluh temuan sudah cukup membuat berkas ini terlalu berat untuk dikirim lewat chat mana pun — dan berkas yang tidak bisa dikirim tidak dipakai siapa-siapa.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Dim baris As Long, idTemuan As String, ext As String</t>
-        </is>
-      </c>
+      <c r="B16" s="31" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="B17" s="33" t="inlineStr"/>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Kenapa tombolnya berupa tautan, bukan makro</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="B18" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    baris = ActiveCell.Row</t>
-        </is>
-      </c>
+      <c r="B18" s="31" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="B19" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    If baris &lt; 5 Then</t>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>Tombol yang menjalankan perintah di Excel butuh makro, dan makro tidak bisa mengunggah ke Google Drive tanpa kredensial API yang harus dititipkan di dalam berkasnya — kredensial di dalam berkas yang dikirim ke banyak orang sama saja dengan diumumkan.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        MsgBox "Klik dulu baris temuannya."</t>
-        </is>
-      </c>
+      <c r="B20" s="31" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="B21" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Exit Sub</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    End If</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="33" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    idTemuan = Trim(Cells(baris, 1).Value)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    If idTemuan = "" Then</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        MsgBox "Isi dulu ID temuannya di kolom A."</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Exit Sub</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    End If</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="33" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    asal = Application.GetOpenFilename( _</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        "Gambar (*.jpg;*.jpeg;*.png),*.jpg;*.jpeg;*.png", , _</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        "Pilih tangkapan layar untuk " &amp; idTemuan)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    If asal = False Then Exit Sub</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="33" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    folder = ThisWorkbook.Path &amp; Application.PathSeparator &amp; "defect-capture"</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    If Dir(folder, vbDirectory) = "" Then MkDir folder</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="33" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ext = Mid(asal, InStrRev(asal, "."))</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    tujuan = folder &amp; Application.PathSeparator &amp; idTemuan &amp; ext</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="33" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="B41" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    FileCopy CStr(asal), tujuan</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Cells(baris, 20).Value = idTemuan &amp; ext</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    MsgBox "Tersimpan: " &amp; idTemuan &amp; ext</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="33" t="inlineStr">
-        <is>
-          <t>End Sub</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="34" t="inlineStr">
-        <is>
-          <t>Angka 20 di baris Cells(baris, 20) adalah kolom Capture. Kalau urutan kolom di lembar Defect diubah, angka itu harus ikut diubah — makronya tidak akan mengeluh, ia hanya menulis ke kolom yang salah.</t>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>Selain itu makro hanya hidup di berkas .xlsm: mati di Google Sheets, mati di Numbers, dan ditolak sebagian penyetelan keamanan kantor. Tautan bekerja di semuanya, dan satu klik membuka folder tempat unggahannya memang dilakukan.</t>
         </is>
       </c>
     </row>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$244</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$270</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C244,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C270,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P1",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P1",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P1",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P1",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P1",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P1",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P1",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P1",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C244,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C270,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P2",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P2",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P2",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P2",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P2",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P2",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P2",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P2",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C244,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C270,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P3",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P3",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P3",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P3",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P3",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P3",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C244,"P3",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C270,"P3",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pelanggan",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pelanggan",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pelanggan",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pelanggan",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pelanggan",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pelanggan",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pelanggan",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pelanggan",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Kasir",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kasir",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Kasir",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kasir",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Kasir",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kasir",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Kasir",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kasir",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pending Payment",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pending Payment",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pending Payment",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pending Payment",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pending Payment",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pending Payment",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pending Payment",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pending Payment",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Dapur",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Dapur",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Dapur",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Dapur",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Dapur",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Dapur",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Dapur",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Dapur",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Keuangan",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Keuangan",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Keuangan",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Keuangan",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Keuangan",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Keuangan",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Keuangan",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Keuangan",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Setor Saldo Cash",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Setor Saldo Cash",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Setor Saldo Cash",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Setor Saldo Cash",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Setor Saldo Cash",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Setor Saldo Cash",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Setor Saldo Cash",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Setor Saldo Cash",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"QR Meja",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"QR Meja",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"QR Meja",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"QR Meja",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"QR Meja",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"QR Meja",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"QR Meja",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"QR Meja",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Diskon",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Diskon",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Diskon",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Diskon",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Diskon",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Diskon",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Diskon",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Diskon",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembayaran QRIS",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembayaran QRIS",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembayaran QRIS",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembayaran QRIS",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembayaran QRIS",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembayaran QRIS",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembayaran QRIS",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembayaran QRIS",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Tampilan",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Tampilan",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Tampilan",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Tampilan",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Tampilan",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Tampilan",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Tampilan",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Tampilan",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Super Admin",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Super Admin",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Super Admin",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Super Admin",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Super Admin",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Super Admin",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Super Admin",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Super Admin",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembaruan Aplikasi",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembaruan Aplikasi",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembaruan Aplikasi",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembaruan Aplikasi",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembaruan Aplikasi",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembaruan Aplikasi",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Pembaruan Aplikasi",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembaruan Aplikasi",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1351,27 +1351,27 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1382,27 +1382,27 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1413,27 +1413,27 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Uji Ujung-ke-Ujung</t>
+          <t>Regresi — bug yang pernah terjadi</t>
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A244,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G244,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G270,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G244,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G270,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G244,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G270,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A244,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G244,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G270,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1441,214 +1441,245 @@
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>Uji Ujung-ke-Ujung</t>
+        </is>
+      </c>
+      <c r="B31" s="5">
+        <f>COUNTIF('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung")</f>
+        <v/>
+      </c>
+      <c r="C31" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <v/>
+      </c>
+      <c r="D31" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <v/>
+      </c>
+      <c r="E31" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <v/>
+      </c>
+      <c r="F31" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <v/>
+      </c>
+      <c r="G31" s="5">
+        <f>B31-SUM(C31:F31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>Rilis ditahan selama masih ada P1 yang Gagal.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="10" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Temuan</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Jumlah</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>Dikonfirmasi</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
         <is>
           <t>Sedang diperbaiki</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr">
+      <c r="F36" s="3" t="inlineStr">
         <is>
           <t>Menunggu retest</t>
         </is>
       </c>
-      <c r="G35" s="3" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>Ditutup</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Blocker</t>
-        </is>
-      </c>
-      <c r="B36" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Blocker")</f>
-        <v/>
-      </c>
-      <c r="C36" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Baru")</f>
-        <v/>
-      </c>
-      <c r="D36" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Dikonfirmasi")</f>
-        <v/>
-      </c>
-      <c r="E36" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Sedang diperbaiki")</f>
-        <v/>
-      </c>
-      <c r="F36" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Menunggu retest")</f>
-        <v/>
-      </c>
-      <c r="G36" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Ditutup")</f>
-        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="B37" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Major")</f>
+        <f>COUNTIF(Defect!M5:M64,"Blocker")</f>
         <v/>
       </c>
       <c r="C37" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Baru")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
       <c r="D37" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Dikonfirmasi")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
       <c r="E37" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
       <c r="F37" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Menunggu retest")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
       <c r="G37" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Ditutup")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="B38" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Minor")</f>
+        <f>COUNTIF(Defect!M5:M64,"Major")</f>
         <v/>
       </c>
       <c r="C38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Baru")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
       <c r="D38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Dikonfirmasi")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
       <c r="E38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
       <c r="F38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Menunggu retest")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
       <c r="G38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Ditutup")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="B39" s="5">
+        <f>COUNTIF(Defect!M5:M64,"Minor")</f>
+        <v/>
+      </c>
+      <c r="C39" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Baru")</f>
+        <v/>
+      </c>
+      <c r="D39" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Dikonfirmasi")</f>
+        <v/>
+      </c>
+      <c r="E39" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <v/>
+      </c>
+      <c r="F39" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Menunggu retest")</f>
+        <v/>
+      </c>
+      <c r="G39" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Ditutup")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="B39" s="5">
+      <c r="B40" s="5">
         <f>COUNTIF(Defect!M5:M64,"Trivial")</f>
         <v/>
       </c>
-      <c r="C39" s="5">
+      <c r="C40" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
-      <c r="D39" s="5">
+      <c r="D40" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
-      <c r="E39" s="5">
+      <c r="E40" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
-      <c r="F39" s="5">
+      <c r="F40" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
-      <c r="G39" s="5">
+      <c r="G40" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B40" s="7">
-        <f>SUM(B36:B39)</f>
-        <v/>
-      </c>
-      <c r="C40" s="7">
-        <f>SUM(C36:C39)</f>
-        <v/>
-      </c>
-      <c r="D40" s="7">
-        <f>SUM(D36:D39)</f>
-        <v/>
-      </c>
-      <c r="E40" s="7">
-        <f>SUM(E36:E39)</f>
-        <v/>
-      </c>
-      <c r="F40" s="7">
-        <f>SUM(F36:F39)</f>
-        <v/>
-      </c>
-      <c r="G40" s="7">
-        <f>SUM(G36:G39)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
+      <c r="B41" s="7">
+        <f>SUM(B37:B40)</f>
+        <v/>
+      </c>
+      <c r="C41" s="7">
+        <f>SUM(C37:C40)</f>
+        <v/>
+      </c>
+      <c r="D41" s="7">
+        <f>SUM(D37:D40)</f>
+        <v/>
+      </c>
+      <c r="E41" s="7">
+        <f>SUM(E37:E40)</f>
+        <v/>
+      </c>
+      <c r="F41" s="7">
+        <f>SUM(F37:F40)</f>
+        <v/>
+      </c>
+      <c r="G41" s="7">
+        <f>SUM(G37:G40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>Blocker yang belum Ditutup menahan rilis.</t>
         </is>
@@ -1665,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I244"/>
+  <dimension ref="A1:I270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8799,32 +8830,32 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B204" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
-        </is>
-      </c>
-      <c r="C204" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-01</t>
+        </is>
+      </c>
+      <c r="C204" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Super Admin → Billing Resto → atur harga dan tanggal untuk sebuah resto</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Tersimpan; kartu restonya menampilkan harga, tanggal, dan tenggangnya</t>
         </is>
       </c>
       <c r="F204" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-BL-01, F-BL-02</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr"/>
@@ -8834,32 +8865,32 @@
     <row r="205">
       <c r="A205" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B205" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
-        </is>
-      </c>
-      <c r="C205" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-02</t>
+        </is>
+      </c>
+      <c r="C205" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D205" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Buat resto baru, buka Billing Resto</t>
         </is>
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Sudah punya barisnya sendiri, berstatus Gratis</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-BL-06</t>
         </is>
       </c>
       <c r="G205" s="16" t="inlineStr"/>
@@ -8869,12 +8900,12 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B206" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-BL-03</t>
         </is>
       </c>
       <c r="C206" s="15" t="inlineStr">
@@ -8884,17 +8915,17 @@
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Setel harga Rp 0, lewatkan tanggal jatuh tempo jauh</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Tidak pernah terbit tagihan, tidak pernah terkunci</t>
         </is>
       </c>
       <c r="F206" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-BL-04</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr"/>
@@ -8904,12 +8935,12 @@
     <row r="207">
       <c r="A207" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B207" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
+          <t>TC-BL-04</t>
         </is>
       </c>
       <c r="C207" s="18" t="inlineStr">
@@ -8919,17 +8950,17 @@
       </c>
       <c r="D207" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Matikan saklar langganan pada resto berbayar yang menunggak</t>
         </is>
       </c>
       <c r="E207" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Tidak terkunci</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-BL-05</t>
         </is>
       </c>
       <c r="G207" s="16" t="inlineStr"/>
@@ -8939,32 +8970,32 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B208" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
-        </is>
-      </c>
-      <c r="C208" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-05</t>
+        </is>
+      </c>
+      <c r="C208" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Coba pilih tanggal tagihan 29, 30, atau 31</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Tidak tersedia di pilihan — hanya 1 sampai 28</t>
         </is>
       </c>
       <c r="F208" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-BL-02</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr"/>
@@ -8974,32 +9005,32 @@
     <row r="209">
       <c r="A209" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B209" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
-        </is>
-      </c>
-      <c r="C209" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-06</t>
+        </is>
+      </c>
+      <c r="C209" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D209" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Ketuk Terbitkan tagihan sekarang dua kali beruntun</t>
         </is>
       </c>
       <c r="E209" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tagihan tetap satu untuk periode itu</t>
         </is>
       </c>
       <c r="F209" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-BL-08</t>
         </is>
       </c>
       <c r="G209" s="16" t="inlineStr"/>
@@ -9009,12 +9040,12 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B210" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-BL-07</t>
         </is>
       </c>
       <c r="C210" s="15" t="inlineStr">
@@ -9024,17 +9055,17 @@
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Setel jatuh tempo 3 hari lagi, buka aplikasi sebagai Kasir</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Pita pengingat tampil di atas layar; isi layarnya tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F210" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-BL-09</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr"/>
@@ -9044,32 +9075,32 @@
     <row r="211">
       <c r="A211" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B211" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
-        </is>
-      </c>
-      <c r="C211" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-08</t>
+        </is>
+      </c>
+      <c r="C211" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D211" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Setel jatuh tempo 4 hari lagi</t>
         </is>
       </c>
       <c r="E211" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Pita belum tampil</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-BL-09</t>
         </is>
       </c>
       <c r="G211" s="16" t="inlineStr"/>
@@ -9079,12 +9110,12 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B212" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-BL-09</t>
         </is>
       </c>
       <c r="C212" s="15" t="inlineStr">
@@ -9094,17 +9125,17 @@
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Lewati jatuh tempo, masih dalam tenggang</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Pita berubah merah; aplikasi belum terkunci</t>
         </is>
       </c>
       <c r="F212" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>F-BL-03, F-BL-10</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr"/>
@@ -9114,12 +9145,12 @@
     <row r="213">
       <c r="A213" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B213" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-BL-10</t>
         </is>
       </c>
       <c r="C213" s="18" t="inlineStr">
@@ -9129,17 +9160,17 @@
       </c>
       <c r="D213" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Lewati tenggang, tagihan belum dibayar</t>
         </is>
       </c>
       <c r="E213" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Seluruh layar diganti halaman Aplikasi Terkunci Sementara</t>
         </is>
       </c>
       <c r="F213" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>F-BL-15</t>
         </is>
       </c>
       <c r="G213" s="16" t="inlineStr"/>
@@ -9149,32 +9180,32 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B214" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
-        </is>
-      </c>
-      <c r="C214" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-11</t>
+        </is>
+      </c>
+      <c r="C214" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Pada keadaan terkunci, coba buat pesanan lewat API langsung</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Ditolak database — bukan hanya layarnya yang menutup</t>
         </is>
       </c>
       <c r="F214" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>F-BL-18, TSD §7.3</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr"/>
@@ -9184,32 +9215,32 @@
     <row r="215">
       <c r="A215" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B215" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C215" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-12</t>
+        </is>
+      </c>
+      <c r="C215" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D215" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Pada keadaan terkunci, ketuk Lihat &amp; Bayar Tagihan</t>
         </is>
       </c>
       <c r="E215" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Layar tagihan terbuka dan bisa dipakai</t>
         </is>
       </c>
       <c r="F215" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>F-BL-16</t>
         </is>
       </c>
       <c r="G215" s="16" t="inlineStr"/>
@@ -9219,32 +9250,32 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B216" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C216" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-13</t>
+        </is>
+      </c>
+      <c r="C216" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Pada keadaan terkunci, ketuk Keluar</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Berhasil keluar akun</t>
         </is>
       </c>
       <c r="F216" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>F-BL-16</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr"/>
@@ -9254,12 +9285,12 @@
     <row r="217">
       <c r="A217" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B217" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-BL-14</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">
@@ -9269,17 +9300,17 @@
       </c>
       <c r="D217" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Unggah bukti bayar dari layar Tagihan</t>
         </is>
       </c>
       <c r="E217" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
         </is>
       </c>
       <c r="F217" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>F-BL-11, F-BL-12</t>
         </is>
       </c>
       <c r="G217" s="16" t="inlineStr"/>
@@ -9289,12 +9320,12 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B218" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
+          <t>TC-BL-15</t>
         </is>
       </c>
       <c r="C218" s="15" t="inlineStr">
@@ -9304,17 +9335,17 @@
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Coba kirim bukti tanpa melampirkan foto</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Tombol Kirim mati</t>
         </is>
       </c>
       <c r="F218" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr"/>
@@ -9324,12 +9355,12 @@
     <row r="219">
       <c r="A219" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B219" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-BL-16</t>
         </is>
       </c>
       <c r="C219" s="18" t="inlineStr">
@@ -9339,17 +9370,17 @@
       </c>
       <c r="D219" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Super Admin → tab Tagihan → Terima</t>
         </is>
       </c>
       <c r="E219" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
         </is>
       </c>
       <c r="F219" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G219" s="16" t="inlineStr"/>
@@ -9359,32 +9390,32 @@
     <row r="220">
       <c r="A220" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B220" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C220" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-17</t>
+        </is>
+      </c>
+      <c r="C220" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Super Admin → Tolak tanpa mengisi alasan</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
         </is>
       </c>
       <c r="F220" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>F-BL-14</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr"/>
@@ -9394,32 +9425,32 @@
     <row r="221">
       <c r="A221" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B221" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C221" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-18</t>
+        </is>
+      </c>
+      <c r="C221" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D221" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
         </is>
       </c>
       <c r="E221" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
         </is>
       </c>
       <c r="F221" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>F-BL-14, F-BL-15</t>
         </is>
       </c>
       <c r="G221" s="16" t="inlineStr"/>
@@ -9429,32 +9460,32 @@
     <row r="222">
       <c r="A222" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B222" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C222" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-19</t>
+        </is>
+      </c>
+      <c r="C222" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Login sebagai Super Admin saat ada resto terkunci</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Tidak terkunci sama sekali</t>
         </is>
       </c>
       <c r="F222" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>F-BL-17</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr"/>
@@ -9464,12 +9495,12 @@
     <row r="223">
       <c r="A223" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B223" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
+          <t>TC-BL-20</t>
         </is>
       </c>
       <c r="C223" s="18" t="inlineStr">
@@ -9479,17 +9510,17 @@
       </c>
       <c r="D223" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Sebagai resto terkunci, coba ubah harga produk</t>
         </is>
       </c>
       <c r="E223" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Ditolak — katalog ikut dibekukan</t>
         </is>
       </c>
       <c r="F223" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>F-BL-18</t>
         </is>
       </c>
       <c r="G223" s="16" t="inlineStr"/>
@@ -9499,12 +9530,12 @@
     <row r="224">
       <c r="A224" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B224" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
+          <t>TC-BL-21</t>
         </is>
       </c>
       <c r="C224" s="15" t="inlineStr">
@@ -9514,17 +9545,17 @@
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Resto B tidak terpengaruh</t>
         </is>
       </c>
       <c r="F224" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>F-BL-15, A-10</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr"/>
@@ -9534,12 +9565,12 @@
     <row r="225">
       <c r="A225" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B225" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
+          <t>TC-BL-22</t>
         </is>
       </c>
       <c r="C225" s="18" t="inlineStr">
@@ -9549,17 +9580,17 @@
       </c>
       <c r="D225" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
         </is>
       </c>
       <c r="E225" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F225" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G225" s="16" t="inlineStr"/>
@@ -9569,12 +9600,12 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B226" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
+          <t>TC-BL-23</t>
         </is>
       </c>
       <c r="C226" s="15" t="inlineStr">
@@ -9584,17 +9615,17 @@
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F226" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>F-BL-13, TSD §7.3</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr"/>
@@ -9604,32 +9635,32 @@
     <row r="227">
       <c r="A227" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B227" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
-        </is>
-      </c>
-      <c r="C227" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-24</t>
+        </is>
+      </c>
+      <c r="C227" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D227" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
         </is>
       </c>
       <c r="E227" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Tidak terkunci karena gagal memeriksa</t>
         </is>
       </c>
       <c r="F227" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G227" s="16" t="inlineStr"/>
@@ -9639,32 +9670,32 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B228" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
-        </is>
-      </c>
-      <c r="C228" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-25</t>
+        </is>
+      </c>
+      <c r="C228" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Owner → Tagihan Langganan</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Terbuka, memuat paket dan riwayat tagihan</t>
         </is>
       </c>
       <c r="F228" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr"/>
@@ -9674,32 +9705,32 @@
     <row r="229">
       <c r="A229" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B229" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C229" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-01</t>
+        </is>
+      </c>
+      <c r="C229" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D229" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E229" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G229" s="16" t="inlineStr"/>
@@ -9709,32 +9740,32 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B230" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C230" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-02</t>
+        </is>
+      </c>
+      <c r="C230" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F230" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr"/>
@@ -9744,32 +9775,32 @@
     <row r="231">
       <c r="A231" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B231" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
-        </is>
-      </c>
-      <c r="C231" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-03</t>
+        </is>
+      </c>
+      <c r="C231" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D231" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E231" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F231" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G231" s="16" t="inlineStr"/>
@@ -9779,32 +9810,32 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B232" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
-        </is>
-      </c>
-      <c r="C232" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-04</t>
+        </is>
+      </c>
+      <c r="C232" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F232" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr"/>
@@ -9814,32 +9845,32 @@
     <row r="233">
       <c r="A233" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B233" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
-        </is>
-      </c>
-      <c r="C233" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-05</t>
+        </is>
+      </c>
+      <c r="C233" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D233" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E233" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F233" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G233" s="16" t="inlineStr"/>
@@ -9849,32 +9880,32 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B234" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
-        </is>
-      </c>
-      <c r="C234" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-06</t>
+        </is>
+      </c>
+      <c r="C234" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F234" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr"/>
@@ -9884,12 +9915,12 @@
     <row r="235">
       <c r="A235" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B235" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
+          <t>TC-TS-07</t>
         </is>
       </c>
       <c r="C235" s="18" t="inlineStr">
@@ -9899,17 +9930,17 @@
       </c>
       <c r="D235" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E235" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F235" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G235" s="16" t="inlineStr"/>
@@ -9919,32 +9950,32 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B236" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
-        </is>
-      </c>
-      <c r="C236" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C236" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F236" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr"/>
@@ -9954,25 +9985,944 @@
     <row r="237">
       <c r="A237" s="16" t="inlineStr">
         <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B237" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C237" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D237" s="16" t="inlineStr">
+        <is>
+          <t>Buat resto baru dari Super Admin</t>
+        </is>
+      </c>
+      <c r="E237" s="16" t="inlineStr">
+        <is>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+        </is>
+      </c>
+      <c r="F237" s="16" t="inlineStr">
+        <is>
+          <t>A-19, TSD §6.2</t>
+        </is>
+      </c>
+      <c r="G237" s="16" t="inlineStr"/>
+      <c r="H237" s="16" t="inlineStr"/>
+      <c r="I237" s="16" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B238" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C238" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D238" s="13" t="inlineStr">
+        <is>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+        </is>
+      </c>
+      <c r="E238" s="13" t="inlineStr">
+        <is>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+        </is>
+      </c>
+      <c r="F238" s="13" t="inlineStr">
+        <is>
+          <t>TSD §6.2</t>
+        </is>
+      </c>
+      <c r="G238" s="13" t="inlineStr"/>
+      <c r="H238" s="13" t="inlineStr"/>
+      <c r="I238" s="13" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B239" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-11</t>
+        </is>
+      </c>
+      <c r="C239" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D239" s="16" t="inlineStr">
+        <is>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+        </is>
+      </c>
+      <c r="E239" s="16" t="inlineStr">
+        <is>
+          <t>Baris masuk, lalu sent_at terisi</t>
+        </is>
+      </c>
+      <c r="F239" s="16" t="inlineStr">
+        <is>
+          <t>TSD §8</t>
+        </is>
+      </c>
+      <c r="G239" s="16" t="inlineStr"/>
+      <c r="H239" s="16" t="inlineStr"/>
+      <c r="I239" s="16" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B240" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C240" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D240" s="13" t="inlineStr">
+        <is>
+          <t>Matikan sambungan, pakai aplikasi</t>
+        </is>
+      </c>
+      <c r="E240" s="13" t="inlineStr">
+        <is>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+        </is>
+      </c>
+      <c r="F240" s="13" t="inlineStr">
+        <is>
+          <t>TSD §10, FSD §5.6</t>
+        </is>
+      </c>
+      <c r="G240" s="13" t="inlineStr"/>
+      <c r="H240" s="13" t="inlineStr"/>
+      <c r="I240" s="13" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B241" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-13</t>
+        </is>
+      </c>
+      <c r="C241" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D241" s="16" t="inlineStr">
+        <is>
+          <t>Sambungkan lagi</t>
+        </is>
+      </c>
+      <c r="E241" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
+        </is>
+      </c>
+      <c r="F241" s="16" t="inlineStr">
+        <is>
+          <t>TSD §10</t>
+        </is>
+      </c>
+      <c r="G241" s="16" t="inlineStr"/>
+      <c r="H241" s="16" t="inlineStr"/>
+      <c r="I241" s="16" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B242" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-14</t>
+        </is>
+      </c>
+      <c r="C242" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D242" s="13" t="inlineStr">
+        <is>
+          <t>Coba bayar QRIS saat luring</t>
+        </is>
+      </c>
+      <c r="E242" s="13" t="inlineStr">
+        <is>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+        </is>
+      </c>
+      <c r="F242" s="13" t="inlineStr">
+        <is>
+          <t>FSD §5.6</t>
+        </is>
+      </c>
+      <c r="G242" s="13" t="inlineStr"/>
+      <c r="H242" s="13" t="inlineStr"/>
+      <c r="I242" s="13" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B243" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C243" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D243" s="16" t="inlineStr">
+        <is>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+        </is>
+      </c>
+      <c r="E243" s="16" t="inlineStr">
+        <is>
+          <t>Nominal yang dipakai tetap dari basis data</t>
+        </is>
+      </c>
+      <c r="F243" s="16" t="inlineStr">
+        <is>
+          <t>TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G243" s="16" t="inlineStr"/>
+      <c r="H243" s="16" t="inlineStr"/>
+      <c r="I243" s="16" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B244" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-16</t>
+        </is>
+      </c>
+      <c r="C244" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D244" s="13" t="inlineStr">
+        <is>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+        </is>
+      </c>
+      <c r="E244" s="13" t="inlineStr">
+        <is>
+          <t>Ditolak</t>
+        </is>
+      </c>
+      <c r="F244" s="13" t="inlineStr">
+        <is>
+          <t>F-PG-02, TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G244" s="13" t="inlineStr"/>
+      <c r="H244" s="13" t="inlineStr"/>
+      <c r="I244" s="13" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B245" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C245" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D245" s="16" t="inlineStr">
+        <is>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+        </is>
+      </c>
+      <c r="E245" s="16" t="inlineStr">
+        <is>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+        </is>
+      </c>
+      <c r="F245" s="16" t="inlineStr">
+        <is>
+          <t>TSD §1.2</t>
+        </is>
+      </c>
+      <c r="G245" s="16" t="inlineStr"/>
+      <c r="H245" s="16" t="inlineStr"/>
+      <c r="I245" s="16" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B246" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C246" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D246" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+        </is>
+      </c>
+      <c r="E246" s="13" t="inlineStr">
+        <is>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+        </is>
+      </c>
+      <c r="F246" s="13" t="inlineStr">
+        <is>
+          <t>TSD §6.5</t>
+        </is>
+      </c>
+      <c r="G246" s="13" t="inlineStr"/>
+      <c r="H246" s="13" t="inlineStr"/>
+      <c r="I246" s="13" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B247" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C247" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D247" s="16" t="inlineStr">
+        <is>
+          <t>Hapus resto uji</t>
+        </is>
+      </c>
+      <c r="E247" s="16" t="inlineStr">
+        <is>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+        </is>
+      </c>
+      <c r="F247" s="16" t="inlineStr">
+        <is>
+          <t>TSD §4.0</t>
+        </is>
+      </c>
+      <c r="G247" s="16" t="inlineStr"/>
+      <c r="H247" s="16" t="inlineStr"/>
+      <c r="I247" s="16" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B248" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C248" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D248" s="13" t="inlineStr">
+        <is>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+        </is>
+      </c>
+      <c r="E248" s="13" t="inlineStr">
+        <is>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+        </is>
+      </c>
+      <c r="F248" s="13" t="inlineStr">
+        <is>
+          <t>F-KS-09</t>
+        </is>
+      </c>
+      <c r="G248" s="13" t="inlineStr"/>
+      <c r="H248" s="13" t="inlineStr"/>
+      <c r="I248" s="13" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B249" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C249" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D249" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="E249" s="16" t="inlineStr">
+        <is>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="F249" s="16" t="inlineStr">
+        <is>
+          <t>F-PP-09, A-13</t>
+        </is>
+      </c>
+      <c r="G249" s="16" t="inlineStr"/>
+      <c r="H249" s="16" t="inlineStr"/>
+      <c r="I249" s="16" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B250" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C250" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D250" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+        </is>
+      </c>
+      <c r="E250" s="13" t="inlineStr">
+        <is>
+          <t>Tidak muncul sama sekali</t>
+        </is>
+      </c>
+      <c r="F250" s="13" t="inlineStr">
+        <is>
+          <t>A-17</t>
+        </is>
+      </c>
+      <c r="G250" s="13" t="inlineStr"/>
+      <c r="H250" s="13" t="inlineStr"/>
+      <c r="I250" s="13" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B251" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C251" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D251" s="16" t="inlineStr">
+        <is>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+        </is>
+      </c>
+      <c r="E251" s="16" t="inlineStr">
+        <is>
+          <t>Nominalnya sama dengan yang diajukan</t>
+        </is>
+      </c>
+      <c r="F251" s="16" t="inlineStr">
+        <is>
+          <t>F-FN-03</t>
+        </is>
+      </c>
+      <c r="G251" s="16" t="inlineStr"/>
+      <c r="H251" s="16" t="inlineStr"/>
+      <c r="I251" s="16" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B252" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C252" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D252" s="13" t="inlineStr">
+        <is>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+        </is>
+      </c>
+      <c r="E252" s="13" t="inlineStr">
+        <is>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
+        </is>
+      </c>
+      <c r="F252" s="13" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="G252" s="13" t="inlineStr"/>
+      <c r="H252" s="13" t="inlineStr"/>
+      <c r="I252" s="13" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B253" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C253" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D253" s="16" t="inlineStr">
+        <is>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+        </is>
+      </c>
+      <c r="E253" s="16" t="inlineStr">
+        <is>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+        </is>
+      </c>
+      <c r="F253" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-10, F-DS-12</t>
+        </is>
+      </c>
+      <c r="G253" s="16" t="inlineStr"/>
+      <c r="H253" s="16" t="inlineStr"/>
+      <c r="I253" s="16" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B254" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C254" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D254" s="13" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E254" s="13" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F254" s="13" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G254" s="13" t="inlineStr"/>
+      <c r="H254" s="13" t="inlineStr"/>
+      <c r="I254" s="13" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B255" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C255" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D255" s="16" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E255" s="16" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F255" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G255" s="16" t="inlineStr"/>
+      <c r="H255" s="16" t="inlineStr"/>
+      <c r="I255" s="16" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B256" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C256" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D256" s="13" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E256" s="13" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F256" s="13" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G256" s="13" t="inlineStr"/>
+      <c r="H256" s="13" t="inlineStr"/>
+      <c r="I256" s="13" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B257" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C257" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D257" s="16" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E257" s="16" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F257" s="16" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G257" s="16" t="inlineStr"/>
+      <c r="H257" s="16" t="inlineStr"/>
+      <c r="I257" s="16" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B258" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C258" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D258" s="13" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E258" s="13" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F258" s="13" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G258" s="13" t="inlineStr"/>
+      <c r="H258" s="13" t="inlineStr"/>
+      <c r="I258" s="13" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B259" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C259" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D259" s="16" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E259" s="16" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F259" s="16" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G259" s="16" t="inlineStr"/>
+      <c r="H259" s="16" t="inlineStr"/>
+      <c r="I259" s="16" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B260" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C260" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D260" s="13" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E260" s="13" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F260" s="13" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G260" s="13" t="inlineStr"/>
+      <c r="H260" s="13" t="inlineStr"/>
+      <c r="I260" s="13" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B261" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C261" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D261" s="16" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E261" s="16" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F261" s="16" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G261" s="16" t="inlineStr"/>
+      <c r="H261" s="16" t="inlineStr"/>
+      <c r="I261" s="16" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="13" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B237" s="17" t="inlineStr">
+      <c r="B262" s="14" t="inlineStr">
+        <is>
+          <t>E2E-09</t>
+        </is>
+      </c>
+      <c r="C262" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D262" s="13" t="inlineStr">
+        <is>
+          <t>Satu siklus langganan penuh</t>
+        </is>
+      </c>
+      <c r="E262" s="13" t="inlineStr">
+        <is>
+          <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
+2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
+3. Buka aplikasi sebagai Kasir → pita pengingat tampil, layar tetap bisa dipakai
+4. Majukan tanggal melewati jatuh tempo + 1 hari → buka lagi → terkunci
+5. Coba buat pesanan lewat API langsung → ditolak database
+6. Ketuk Lihat &amp; Bayar Tagihan → unggah bukti → status Menunggu Verifikasi
+7. Buka aplikasi lagi → tidak lagi terkunci
+8. Super Admin → Tolak berikut alasan → resto terkunci lagi, alasannya terbaca
+9. Unggah bukti baru → Super Admin → Terima → status Lunas
+10. Buka aplikasi → terbuka, pita hilang</t>
+        </is>
+      </c>
+      <c r="F262" s="13" t="inlineStr">
+        <is>
+          <t>F-BL-07 … F-BL-18, TSD §7.3</t>
+        </is>
+      </c>
+      <c r="G262" s="13" t="inlineStr"/>
+      <c r="H262" s="13" t="inlineStr"/>
+      <c r="I262" s="13" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="16" t="inlineStr">
+        <is>
+          <t>Uji Ujung-ke-Ujung</t>
+        </is>
+      </c>
+      <c r="B263" s="17" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C237" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D237" s="16" t="inlineStr">
+      <c r="C263" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D263" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E237" s="16" t="inlineStr">
+      <c r="E263" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -9984,37 +10934,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F237" s="16" t="inlineStr">
+      <c r="F263" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G237" s="16" t="inlineStr"/>
-      <c r="H237" s="16" t="inlineStr"/>
-      <c r="I237" s="16" t="inlineStr"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="13" t="inlineStr">
+      <c r="G263" s="16" t="inlineStr"/>
+      <c r="H263" s="16" t="inlineStr"/>
+      <c r="I263" s="16" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B238" s="14" t="inlineStr">
+      <c r="B264" s="14" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C238" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D238" s="13" t="inlineStr">
+      <c r="C264" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D264" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E238" s="13" t="inlineStr">
+      <c r="E264" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -10026,74 +10976,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F238" s="13" t="inlineStr">
+      <c r="F264" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G238" s="13" t="inlineStr"/>
-      <c r="H238" s="13" t="inlineStr"/>
-      <c r="I238" s="13" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="16" t="inlineStr">
+      <c r="G264" s="13" t="inlineStr"/>
+      <c r="H264" s="13" t="inlineStr"/>
+      <c r="I264" s="13" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B239" s="17" t="inlineStr">
+      <c r="B265" s="17" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C239" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D239" s="16" t="inlineStr">
+      <c r="C265" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D265" s="16" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E239" s="16" t="inlineStr">
+      <c r="E265" s="16" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F239" s="16" t="inlineStr">
+      <c r="F265" s="16" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G239" s="16" t="inlineStr"/>
-      <c r="H239" s="16" t="inlineStr"/>
-      <c r="I239" s="16" t="inlineStr"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="13" t="inlineStr">
+      <c r="G265" s="16" t="inlineStr"/>
+      <c r="H265" s="16" t="inlineStr"/>
+      <c r="I265" s="16" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B240" s="14" t="inlineStr">
+      <c r="B266" s="14" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C240" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D240" s="13" t="inlineStr">
+      <c r="C266" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D266" s="13" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E240" s="13" t="inlineStr">
+      <c r="E266" s="13" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -10104,73 +11054,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F240" s="13" t="inlineStr">
+      <c r="F266" s="13" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G240" s="13" t="inlineStr"/>
-      <c r="H240" s="13" t="inlineStr"/>
-      <c r="I240" s="13" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="16" t="inlineStr">
+      <c r="G266" s="13" t="inlineStr"/>
+      <c r="H266" s="13" t="inlineStr"/>
+      <c r="I266" s="13" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B241" s="17" t="inlineStr">
+      <c r="B267" s="17" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C241" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D241" s="16" t="inlineStr">
+      <c r="C267" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D267" s="16" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E241" s="16" t="inlineStr">
+      <c r="E267" s="16" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F241" s="16" t="inlineStr">
+      <c r="F267" s="16" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G241" s="16" t="inlineStr"/>
-      <c r="H241" s="16" t="inlineStr"/>
-      <c r="I241" s="16" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="13" t="inlineStr">
+      <c r="G267" s="16" t="inlineStr"/>
+      <c r="H267" s="16" t="inlineStr"/>
+      <c r="I267" s="16" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B242" s="14" t="inlineStr">
+      <c r="B268" s="14" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C242" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D242" s="13" t="inlineStr">
+      <c r="C268" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D268" s="13" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E242" s="13" t="inlineStr">
+      <c r="E268" s="13" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -10181,37 +11131,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F242" s="13" t="inlineStr">
+      <c r="F268" s="13" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G242" s="13" t="inlineStr"/>
-      <c r="H242" s="13" t="inlineStr"/>
-      <c r="I242" s="13" t="inlineStr"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="16" t="inlineStr">
+      <c r="G268" s="13" t="inlineStr"/>
+      <c r="H268" s="13" t="inlineStr"/>
+      <c r="I268" s="13" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B243" s="17" t="inlineStr">
+      <c r="B269" s="17" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C243" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D243" s="16" t="inlineStr">
+      <c r="C269" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D269" s="16" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E243" s="16" t="inlineStr">
+      <c r="E269" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -10221,37 +11171,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F243" s="16" t="inlineStr">
+      <c r="F269" s="16" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G243" s="16" t="inlineStr"/>
-      <c r="H243" s="16" t="inlineStr"/>
-      <c r="I243" s="16" t="inlineStr"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="13" t="inlineStr">
+      <c r="G269" s="16" t="inlineStr"/>
+      <c r="H269" s="16" t="inlineStr"/>
+      <c r="I269" s="16" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B244" s="14" t="inlineStr">
+      <c r="B270" s="14" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C244" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D244" s="13" t="inlineStr">
+      <c r="C270" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D270" s="13" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E244" s="13" t="inlineStr">
+      <c r="E270" s="13" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -10259,19 +11209,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F244" s="13" t="inlineStr">
+      <c r="F270" s="13" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G244" s="13" t="inlineStr"/>
-      <c r="H244" s="13" t="inlineStr"/>
-      <c r="I244" s="13" t="inlineStr"/>
+      <c r="G270" s="13" t="inlineStr"/>
+      <c r="H270" s="13" t="inlineStr"/>
+      <c r="I270" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I244"/>
+  <autoFilter ref="A1:I270"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G244" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G270" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$270</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$278</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C270,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C278,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P1",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P1",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P1",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P1",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P1",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P1",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P1",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P1",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C270,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C278,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P2",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P2",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P2",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P2",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P2",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P2",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P2",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P2",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C270,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C278,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P3",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P3",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P3",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P3",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P3",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P3",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C270,"P3",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C278,"P3",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pelanggan",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pelanggan",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pelanggan",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pelanggan",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pelanggan",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pelanggan",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pelanggan",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pelanggan",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kasir",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Kasir",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kasir",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Kasir",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kasir",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Kasir",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kasir",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Kasir",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pending Payment",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pending Payment",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pending Payment",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pending Payment",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pending Payment",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pending Payment",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pending Payment",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pending Payment",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Dapur",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Dapur",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Dapur",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Dapur",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Dapur",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Dapur",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Dapur",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Dapur",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Keuangan",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Keuangan",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Keuangan",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Keuangan",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Keuangan",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Keuangan",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Keuangan",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Keuangan",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Setor Saldo Cash",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Setor Saldo Cash",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Setor Saldo Cash",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Setor Saldo Cash",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Setor Saldo Cash",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Setor Saldo Cash",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Setor Saldo Cash",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Setor Saldo Cash",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"QR Meja",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"QR Meja",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"QR Meja",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"QR Meja",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"QR Meja",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"QR Meja",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"QR Meja",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"QR Meja",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Diskon",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Diskon",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Diskon",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Diskon",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Diskon",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Diskon",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Diskon",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Diskon",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembayaran QRIS",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembayaran QRIS",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembayaran QRIS",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembayaran QRIS",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembayaran QRIS",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembayaran QRIS",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembayaran QRIS",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembayaran QRIS",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Tampilan",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Tampilan",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Tampilan",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Tampilan",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Tampilan",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Tampilan",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Tampilan",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Tampilan",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Super Admin",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Super Admin",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Super Admin",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Super Admin",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Super Admin",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Super Admin",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Super Admin",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Super Admin",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembaruan Aplikasi",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembaruan Aplikasi",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembaruan Aplikasi",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembaruan Aplikasi",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembaruan Aplikasi",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembaruan Aplikasi",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Pembaruan Aplikasi",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Pembaruan Aplikasi",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A278,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G270,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G278,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G270,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G278,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G270,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G278,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A270,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G270,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A278,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G278,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1696,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I270"/>
+  <dimension ref="A1:I278"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9300,17 +9300,17 @@
       </c>
       <c r="D217" s="16" t="inlineStr">
         <is>
-          <t>Unggah bukti bayar dari layar Tagihan</t>
+          <t>Ketuk Buat Virtual Account → pilih BCA</t>
         </is>
       </c>
       <c r="E217" s="16" t="inlineStr">
         <is>
-          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
+          <t>Nomor VA tampil berikut nominal dan masa berlakunya</t>
         </is>
       </c>
       <c r="F217" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11, F-BL-12</t>
+          <t>F-BL-11, F-BL-19</t>
         </is>
       </c>
       <c r="G217" s="16" t="inlineStr"/>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="B218" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-15</t>
+          <t>TC-BL-14b</t>
         </is>
       </c>
       <c r="C218" s="15" t="inlineStr">
@@ -9335,17 +9335,17 @@
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>Coba kirim bukti tanpa melampirkan foto</t>
+          <t>Tutup layar, buka lagi, ketuk lagi</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Tombol Kirim mati</t>
+          <t>Nomor VA sama, tidak diterbitkan yang baru</t>
         </is>
       </c>
       <c r="F218" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-23</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr"/>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="B219" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-16</t>
+          <t>TC-BL-14c</t>
         </is>
       </c>
       <c r="C219" s="18" t="inlineStr">
@@ -9370,17 +9370,17 @@
       </c>
       <c r="D219" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → tab Tagihan → Terima</t>
+          <t>Transfer tepat sesuai nominal ke VA itu</t>
         </is>
       </c>
       <c r="E219" s="16" t="inlineStr">
         <is>
-          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
+          <t>Tagihan lunas sendiri dalam hitungan detik; kunci terbuka tanpa mengirim bukti</t>
         </is>
       </c>
       <c r="F219" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G219" s="16" t="inlineStr"/>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="B220" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-17</t>
+          <t>TC-BL-14d</t>
         </is>
       </c>
       <c r="C220" s="15" t="inlineStr">
@@ -9405,17 +9405,17 @@
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Tolak tanpa mengisi alasan</t>
+          <t>Transfer kurang dari nominal</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
+          <t>Tidak melunasi; tagihan tetap terbuka</t>
         </is>
       </c>
       <c r="F220" s="13" t="inlineStr">
         <is>
-          <t>F-BL-14</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr"/>
@@ -9430,27 +9430,27 @@
       </c>
       <c r="B221" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-18</t>
-        </is>
-      </c>
-      <c r="C221" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14e</t>
+        </is>
+      </c>
+      <c r="C221" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D221" s="16" t="inlineStr">
         <is>
-          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
+          <t>Ketuk Ganti Bank → pilih BNI</t>
         </is>
       </c>
       <c r="E221" s="16" t="inlineStr">
         <is>
-          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
+          <t>Nomor VA baru untuk bank itu</t>
         </is>
       </c>
       <c r="F221" s="16" t="inlineStr">
         <is>
-          <t>F-BL-14, F-BL-15</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G221" s="16" t="inlineStr"/>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="B222" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-19</t>
+          <t>TC-BL-14f</t>
         </is>
       </c>
       <c r="C222" s="15" t="inlineStr">
@@ -9475,17 +9475,17 @@
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Super Admin saat ada resto terkunci</t>
+          <t>Periksa rekening tujuan dana VA di Dashboard Xendit</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Tidak terkunci sama sekali</t>
+          <t>Masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
       <c r="F222" s="13" t="inlineStr">
         <is>
-          <t>F-BL-17</t>
+          <t>F-BL-11, TSD §7.3</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr"/>
@@ -9500,7 +9500,7 @@
       </c>
       <c r="B223" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-20</t>
+          <t>TC-BL-14g</t>
         </is>
       </c>
       <c r="C223" s="18" t="inlineStr">
@@ -9510,17 +9510,17 @@
       </c>
       <c r="D223" s="16" t="inlineStr">
         <is>
-          <t>Sebagai resto terkunci, coba ubah harga produk</t>
+          <t>Kirim callback palsu ke xendit-billing-webhook tanpa token</t>
         </is>
       </c>
       <c r="E223" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — katalog ikut dibekukan</t>
+          <t>Ditolak 401; tagihan tidak berubah</t>
         </is>
       </c>
       <c r="F223" s="16" t="inlineStr">
         <is>
-          <t>F-BL-18</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G223" s="16" t="inlineStr"/>
@@ -9535,27 +9535,27 @@
       </c>
       <c r="B224" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-21</t>
-        </is>
-      </c>
-      <c r="C224" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14h</t>
+        </is>
+      </c>
+      <c r="C224" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
+          <t>Xendit mengirim callback yang sama dua kali</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Resto B tidak terpengaruh</t>
+          <t>Tagihan tetap lunas sekali; catatan pelunasnya tidak berubah</t>
         </is>
       </c>
       <c r="F224" s="13" t="inlineStr">
         <is>
-          <t>F-BL-15, A-10</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr"/>
@@ -9570,27 +9570,27 @@
       </c>
       <c r="B225" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-22</t>
-        </is>
-      </c>
-      <c r="C225" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14i</t>
+        </is>
+      </c>
+      <c r="C225" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D225" s="16" t="inlineStr">
         <is>
-          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
+          <t>Unggah bukti transfer manual lewat jalur cadangan</t>
         </is>
       </c>
       <c r="E225" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — hanya Super Admin</t>
+          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
         </is>
       </c>
       <c r="F225" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-24, F-BL-12</t>
         </is>
       </c>
       <c r="G225" s="16" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="B226" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-23</t>
+          <t>TC-BL-15</t>
         </is>
       </c>
       <c r="C226" s="15" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
+          <t>Coba kirim bukti tanpa melampirkan foto</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tombol Kirim mati</t>
         </is>
       </c>
       <c r="F226" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13, TSD §7.3</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr"/>
@@ -9640,27 +9640,27 @@
       </c>
       <c r="B227" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-24</t>
-        </is>
-      </c>
-      <c r="C227" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-16</t>
+        </is>
+      </c>
+      <c r="C227" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D227" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
+          <t>Super Admin → tab Tagihan → Terima</t>
         </is>
       </c>
       <c r="E227" s="16" t="inlineStr">
         <is>
-          <t>Tidak terkunci karena gagal memeriksa</t>
+          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
         </is>
       </c>
       <c r="F227" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G227" s="16" t="inlineStr"/>
@@ -9675,27 +9675,27 @@
       </c>
       <c r="B228" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-25</t>
-        </is>
-      </c>
-      <c r="C228" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-17</t>
+        </is>
+      </c>
+      <c r="C228" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>Owner → Tagihan Langganan</t>
+          <t>Super Admin → Tolak tanpa mengisi alasan</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Terbuka, memuat paket dan riwayat tagihan</t>
+          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
         </is>
       </c>
       <c r="F228" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-14</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr"/>
@@ -9705,12 +9705,12 @@
     <row r="229">
       <c r="A229" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B229" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-BL-18</t>
         </is>
       </c>
       <c r="C229" s="18" t="inlineStr">
@@ -9720,17 +9720,17 @@
       </c>
       <c r="D229" s="16" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
         </is>
       </c>
       <c r="E229" s="16" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-BL-14, F-BL-15</t>
         </is>
       </c>
       <c r="G229" s="16" t="inlineStr"/>
@@ -9740,12 +9740,12 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B230" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-BL-19</t>
         </is>
       </c>
       <c r="C230" s="15" t="inlineStr">
@@ -9755,17 +9755,17 @@
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Login sebagai Super Admin saat ada resto terkunci</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Tidak terkunci sama sekali</t>
         </is>
       </c>
       <c r="F230" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-BL-17</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr"/>
@@ -9775,12 +9775,12 @@
     <row r="231">
       <c r="A231" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B231" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-BL-20</t>
         </is>
       </c>
       <c r="C231" s="18" t="inlineStr">
@@ -9790,17 +9790,17 @@
       </c>
       <c r="D231" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Sebagai resto terkunci, coba ubah harga produk</t>
         </is>
       </c>
       <c r="E231" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Ditolak — katalog ikut dibekukan</t>
         </is>
       </c>
       <c r="F231" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-BL-18</t>
         </is>
       </c>
       <c r="G231" s="16" t="inlineStr"/>
@@ -9810,12 +9810,12 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B232" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
+          <t>TC-BL-21</t>
         </is>
       </c>
       <c r="C232" s="15" t="inlineStr">
@@ -9825,17 +9825,17 @@
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Resto B tidak terpengaruh</t>
         </is>
       </c>
       <c r="F232" s="13" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-BL-15, A-10</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr"/>
@@ -9845,12 +9845,12 @@
     <row r="233">
       <c r="A233" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B233" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-BL-22</t>
         </is>
       </c>
       <c r="C233" s="18" t="inlineStr">
@@ -9860,17 +9860,17 @@
       </c>
       <c r="D233" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
         </is>
       </c>
       <c r="E233" s="16" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F233" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G233" s="16" t="inlineStr"/>
@@ -9880,12 +9880,12 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B234" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-BL-23</t>
         </is>
       </c>
       <c r="C234" s="15" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="F234" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-BL-13, TSD §7.3</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr"/>
@@ -9915,32 +9915,32 @@
     <row r="235">
       <c r="A235" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B235" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
-        </is>
-      </c>
-      <c r="C235" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-24</t>
+        </is>
+      </c>
+      <c r="C235" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D235" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
         </is>
       </c>
       <c r="E235" s="16" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Tidak terkunci karena gagal memeriksa</t>
         </is>
       </c>
       <c r="F235" s="16" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G235" s="16" t="inlineStr"/>
@@ -9950,32 +9950,32 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B236" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
-        </is>
-      </c>
-      <c r="C236" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-25</t>
+        </is>
+      </c>
+      <c r="C236" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Owner → Tagihan Langganan</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Terbuka, memuat paket dan riwayat tagihan</t>
         </is>
       </c>
       <c r="F236" s="13" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr"/>
@@ -9990,7 +9990,7 @@
       </c>
       <c r="B237" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-TS-01</t>
         </is>
       </c>
       <c r="C237" s="18" t="inlineStr">
@@ -10000,17 +10000,17 @@
       </c>
       <c r="D237" s="16" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E237" s="16" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F237" s="16" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G237" s="16" t="inlineStr"/>
@@ -10025,7 +10025,7 @@
       </c>
       <c r="B238" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-TS-02</t>
         </is>
       </c>
       <c r="C238" s="15" t="inlineStr">
@@ -10035,17 +10035,17 @@
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F238" s="13" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr"/>
@@ -10060,27 +10060,27 @@
       </c>
       <c r="B239" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
-        </is>
-      </c>
-      <c r="C239" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-03</t>
+        </is>
+      </c>
+      <c r="C239" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D239" s="16" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E239" s="16" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F239" s="16" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G239" s="16" t="inlineStr"/>
@@ -10095,27 +10095,27 @@
       </c>
       <c r="B240" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C240" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-04</t>
+        </is>
+      </c>
+      <c r="C240" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F240" s="13" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr"/>
@@ -10130,27 +10130,27 @@
       </c>
       <c r="B241" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C241" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-05</t>
+        </is>
+      </c>
+      <c r="C241" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D241" s="16" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E241" s="16" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G241" s="16" t="inlineStr"/>
@@ -10165,7 +10165,7 @@
       </c>
       <c r="B242" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C242" s="15" t="inlineStr">
@@ -10175,17 +10175,17 @@
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F242" s="13" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr"/>
@@ -10200,7 +10200,7 @@
       </c>
       <c r="B243" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
+          <t>TC-TS-07</t>
         </is>
       </c>
       <c r="C243" s="18" t="inlineStr">
@@ -10210,17 +10210,17 @@
       </c>
       <c r="D243" s="16" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E243" s="16" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F243" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G243" s="16" t="inlineStr"/>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="B244" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-TS-08</t>
         </is>
       </c>
       <c r="C244" s="15" t="inlineStr">
@@ -10245,17 +10245,17 @@
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F244" s="13" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr"/>
@@ -10270,27 +10270,27 @@
       </c>
       <c r="B245" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C245" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C245" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D245" s="16" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E245" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F245" s="16" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G245" s="16" t="inlineStr"/>
@@ -10305,27 +10305,27 @@
       </c>
       <c r="B246" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C246" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C246" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F246" s="13" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr"/>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="B247" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
+          <t>TC-TS-11</t>
         </is>
       </c>
       <c r="C247" s="20" t="inlineStr">
@@ -10350,17 +10350,17 @@
       </c>
       <c r="D247" s="16" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E247" s="16" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G247" s="16" t="inlineStr"/>
@@ -10370,32 +10370,32 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B248" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
-        </is>
-      </c>
-      <c r="C248" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C248" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F248" s="13" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr"/>
@@ -10405,32 +10405,32 @@
     <row r="249">
       <c r="A249" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B249" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
-        </is>
-      </c>
-      <c r="C249" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-13</t>
+        </is>
+      </c>
+      <c r="C249" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D249" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E249" s="16" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F249" s="16" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G249" s="16" t="inlineStr"/>
@@ -10440,12 +10440,12 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B250" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
+          <t>TC-TS-14</t>
         </is>
       </c>
       <c r="C250" s="15" t="inlineStr">
@@ -10455,17 +10455,17 @@
       </c>
       <c r="D250" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F250" s="13" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr"/>
@@ -10475,12 +10475,12 @@
     <row r="251">
       <c r="A251" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B251" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
+          <t>TC-TS-15</t>
         </is>
       </c>
       <c r="C251" s="18" t="inlineStr">
@@ -10490,17 +10490,17 @@
       </c>
       <c r="D251" s="16" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E251" s="16" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F251" s="16" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G251" s="16" t="inlineStr"/>
@@ -10510,12 +10510,12 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B252" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-TS-16</t>
         </is>
       </c>
       <c r="C252" s="15" t="inlineStr">
@@ -10525,17 +10525,17 @@
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F252" s="13" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>F-PG-02, TSD §7.1</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr"/>
@@ -10545,32 +10545,32 @@
     <row r="253">
       <c r="A253" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B253" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
-        </is>
-      </c>
-      <c r="C253" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C253" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D253" s="16" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
         </is>
       </c>
       <c r="E253" s="16" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
         </is>
       </c>
       <c r="F253" s="16" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>TSD §1.2</t>
         </is>
       </c>
       <c r="G253" s="16" t="inlineStr"/>
@@ -10580,12 +10580,12 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B254" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
+          <t>TC-TS-18</t>
         </is>
       </c>
       <c r="C254" s="19" t="inlineStr">
@@ -10595,17 +10595,17 @@
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
         </is>
       </c>
       <c r="F254" s="13" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>TSD §6.5</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr"/>
@@ -10615,12 +10615,12 @@
     <row r="255">
       <c r="A255" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B255" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
+          <t>TC-TS-19</t>
         </is>
       </c>
       <c r="C255" s="20" t="inlineStr">
@@ -10630,17 +10630,17 @@
       </c>
       <c r="D255" s="16" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Hapus resto uji</t>
         </is>
       </c>
       <c r="E255" s="16" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
         </is>
       </c>
       <c r="F255" s="16" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>TSD §4.0</t>
         </is>
       </c>
       <c r="G255" s="16" t="inlineStr"/>
@@ -10655,27 +10655,27 @@
       </c>
       <c r="B256" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
-        </is>
-      </c>
-      <c r="C256" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C256" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
         </is>
       </c>
       <c r="F256" s="13" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>F-KS-09</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr"/>
@@ -10690,27 +10690,27 @@
       </c>
       <c r="B257" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
-        </is>
-      </c>
-      <c r="C257" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C257" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D257" s="16" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
         </is>
       </c>
       <c r="E257" s="16" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
         </is>
       </c>
       <c r="F257" s="16" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-PP-09, A-13</t>
         </is>
       </c>
       <c r="G257" s="16" t="inlineStr"/>
@@ -10725,27 +10725,27 @@
       </c>
       <c r="B258" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
-        </is>
-      </c>
-      <c r="C258" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C258" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Tidak muncul sama sekali</t>
         </is>
       </c>
       <c r="F258" s="13" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr"/>
@@ -10760,27 +10760,27 @@
       </c>
       <c r="B259" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
-        </is>
-      </c>
-      <c r="C259" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C259" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D259" s="16" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
         </is>
       </c>
       <c r="E259" s="16" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Nominalnya sama dengan yang diajukan</t>
         </is>
       </c>
       <c r="F259" s="16" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>F-FN-03</t>
         </is>
       </c>
       <c r="G259" s="16" t="inlineStr"/>
@@ -10795,7 +10795,7 @@
       </c>
       <c r="B260" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
+          <t>TC-RG-05</t>
         </is>
       </c>
       <c r="C260" s="15" t="inlineStr">
@@ -10805,17 +10805,17 @@
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
         </is>
       </c>
       <c r="F260" s="13" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr"/>
@@ -10830,27 +10830,27 @@
       </c>
       <c r="B261" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
-        </is>
-      </c>
-      <c r="C261" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C261" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D261" s="16" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
         </is>
       </c>
       <c r="E261" s="16" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
         </is>
       </c>
       <c r="F261" s="16" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>F-DS-10, F-DS-12</t>
         </is>
       </c>
       <c r="G261" s="16" t="inlineStr"/>
@@ -10860,69 +10860,349 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B262" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C262" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D262" s="13" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E262" s="13" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F262" s="13" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G262" s="13" t="inlineStr"/>
+      <c r="H262" s="13" t="inlineStr"/>
+      <c r="I262" s="13" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B263" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C263" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D263" s="16" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E263" s="16" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F263" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G263" s="16" t="inlineStr"/>
+      <c r="H263" s="16" t="inlineStr"/>
+      <c r="I263" s="16" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B264" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C264" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D264" s="13" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E264" s="13" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F264" s="13" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G264" s="13" t="inlineStr"/>
+      <c r="H264" s="13" t="inlineStr"/>
+      <c r="I264" s="13" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B265" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C265" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D265" s="16" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E265" s="16" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F265" s="16" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G265" s="16" t="inlineStr"/>
+      <c r="H265" s="16" t="inlineStr"/>
+      <c r="I265" s="16" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B266" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C266" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D266" s="13" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E266" s="13" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F266" s="13" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G266" s="13" t="inlineStr"/>
+      <c r="H266" s="13" t="inlineStr"/>
+      <c r="I266" s="13" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B267" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C267" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D267" s="16" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E267" s="16" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F267" s="16" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G267" s="16" t="inlineStr"/>
+      <c r="H267" s="16" t="inlineStr"/>
+      <c r="I267" s="16" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B268" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C268" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D268" s="13" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E268" s="13" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F268" s="13" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G268" s="13" t="inlineStr"/>
+      <c r="H268" s="13" t="inlineStr"/>
+      <c r="I268" s="13" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B269" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C269" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D269" s="16" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E269" s="16" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F269" s="16" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G269" s="16" t="inlineStr"/>
+      <c r="H269" s="16" t="inlineStr"/>
+      <c r="I269" s="16" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="13" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B262" s="14" t="inlineStr">
+      <c r="B270" s="14" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C262" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D262" s="13" t="inlineStr">
+      <c r="C270" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D270" s="13" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E262" s="13" t="inlineStr">
+      <c r="E270" s="13" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
 3. Buka aplikasi sebagai Kasir → pita pengingat tampil, layar tetap bisa dipakai
 4. Majukan tanggal melewati jatuh tempo + 1 hari → buka lagi → terkunci
 5. Coba buat pesanan lewat API langsung → ditolak database
-6. Ketuk Lihat &amp; Bayar Tagihan → unggah bukti → status Menunggu Verifikasi
-7. Buka aplikasi lagi → tidak lagi terkunci
-8. Super Admin → Tolak berikut alasan → resto terkunci lagi, alasannya terbaca
-9. Unggah bukti baru → Super Admin → Terima → status Lunas
-10. Buka aplikasi → terbuka, pita hilang</t>
-        </is>
-      </c>
-      <c r="F262" s="13" t="inlineStr">
+6. Ketuk Lihat &amp; Bayar Tagihan → Buat Virtual Account → pilih bank
+7. Transfer tepat sesuai nominal ke nomor VA itu
+8. Tanpa menyentuh aplikasi lagi → status jadi Lunas sendiri
+9. Buka aplikasi → tidak lagi terkunci, pita hilang
+10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
+        </is>
+      </c>
+      <c r="F270" s="13" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G262" s="13" t="inlineStr"/>
-      <c r="H262" s="13" t="inlineStr"/>
-      <c r="I262" s="13" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="16" t="inlineStr">
+      <c r="G270" s="13" t="inlineStr"/>
+      <c r="H270" s="13" t="inlineStr"/>
+      <c r="I270" s="13" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B263" s="17" t="inlineStr">
+      <c r="B271" s="17" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C263" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D263" s="16" t="inlineStr">
+      <c r="C271" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D271" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E263" s="16" t="inlineStr">
+      <c r="E271" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -10934,37 +11214,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F263" s="16" t="inlineStr">
+      <c r="F271" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G263" s="16" t="inlineStr"/>
-      <c r="H263" s="16" t="inlineStr"/>
-      <c r="I263" s="16" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="13" t="inlineStr">
+      <c r="G271" s="16" t="inlineStr"/>
+      <c r="H271" s="16" t="inlineStr"/>
+      <c r="I271" s="16" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B264" s="14" t="inlineStr">
+      <c r="B272" s="14" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C264" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D264" s="13" t="inlineStr">
+      <c r="C272" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D272" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E264" s="13" t="inlineStr">
+      <c r="E272" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -10976,74 +11256,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F264" s="13" t="inlineStr">
+      <c r="F272" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G264" s="13" t="inlineStr"/>
-      <c r="H264" s="13" t="inlineStr"/>
-      <c r="I264" s="13" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="16" t="inlineStr">
+      <c r="G272" s="13" t="inlineStr"/>
+      <c r="H272" s="13" t="inlineStr"/>
+      <c r="I272" s="13" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B265" s="17" t="inlineStr">
+      <c r="B273" s="17" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C265" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D265" s="16" t="inlineStr">
+      <c r="C273" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D273" s="16" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E265" s="16" t="inlineStr">
+      <c r="E273" s="16" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F265" s="16" t="inlineStr">
+      <c r="F273" s="16" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G265" s="16" t="inlineStr"/>
-      <c r="H265" s="16" t="inlineStr"/>
-      <c r="I265" s="16" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" s="13" t="inlineStr">
+      <c r="G273" s="16" t="inlineStr"/>
+      <c r="H273" s="16" t="inlineStr"/>
+      <c r="I273" s="16" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B266" s="14" t="inlineStr">
+      <c r="B274" s="14" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C266" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D266" s="13" t="inlineStr">
+      <c r="C274" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D274" s="13" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E266" s="13" t="inlineStr">
+      <c r="E274" s="13" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -11054,73 +11334,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F266" s="13" t="inlineStr">
+      <c r="F274" s="13" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G266" s="13" t="inlineStr"/>
-      <c r="H266" s="13" t="inlineStr"/>
-      <c r="I266" s="13" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="16" t="inlineStr">
+      <c r="G274" s="13" t="inlineStr"/>
+      <c r="H274" s="13" t="inlineStr"/>
+      <c r="I274" s="13" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B267" s="17" t="inlineStr">
+      <c r="B275" s="17" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C267" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D267" s="16" t="inlineStr">
+      <c r="C275" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D275" s="16" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E267" s="16" t="inlineStr">
+      <c r="E275" s="16" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F267" s="16" t="inlineStr">
+      <c r="F275" s="16" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G267" s="16" t="inlineStr"/>
-      <c r="H267" s="16" t="inlineStr"/>
-      <c r="I267" s="16" t="inlineStr"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="13" t="inlineStr">
+      <c r="G275" s="16" t="inlineStr"/>
+      <c r="H275" s="16" t="inlineStr"/>
+      <c r="I275" s="16" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B268" s="14" t="inlineStr">
+      <c r="B276" s="14" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C268" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D268" s="13" t="inlineStr">
+      <c r="C276" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D276" s="13" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E268" s="13" t="inlineStr">
+      <c r="E276" s="13" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -11131,37 +11411,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F268" s="13" t="inlineStr">
+      <c r="F276" s="13" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G268" s="13" t="inlineStr"/>
-      <c r="H268" s="13" t="inlineStr"/>
-      <c r="I268" s="13" t="inlineStr"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="16" t="inlineStr">
+      <c r="G276" s="13" t="inlineStr"/>
+      <c r="H276" s="13" t="inlineStr"/>
+      <c r="I276" s="13" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B269" s="17" t="inlineStr">
+      <c r="B277" s="17" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C269" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D269" s="16" t="inlineStr">
+      <c r="C277" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D277" s="16" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E269" s="16" t="inlineStr">
+      <c r="E277" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -11171,37 +11451,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F269" s="16" t="inlineStr">
+      <c r="F277" s="16" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G269" s="16" t="inlineStr"/>
-      <c r="H269" s="16" t="inlineStr"/>
-      <c r="I269" s="16" t="inlineStr"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="13" t="inlineStr">
+      <c r="G277" s="16" t="inlineStr"/>
+      <c r="H277" s="16" t="inlineStr"/>
+      <c r="I277" s="16" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B270" s="14" t="inlineStr">
+      <c r="B278" s="14" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C270" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D270" s="13" t="inlineStr">
+      <c r="C278" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D278" s="13" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E270" s="13" t="inlineStr">
+      <c r="E278" s="13" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -11209,19 +11489,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F270" s="13" t="inlineStr">
+      <c r="F278" s="13" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G270" s="13" t="inlineStr"/>
-      <c r="H270" s="13" t="inlineStr"/>
-      <c r="I270" s="13" t="inlineStr"/>
+      <c r="G278" s="13" t="inlineStr"/>
+      <c r="H278" s="13" t="inlineStr"/>
+      <c r="I278" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I270"/>
+  <autoFilter ref="A1:I278"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G270" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G278" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$308</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C297,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C308,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P1",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P1",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P1",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P1",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P1",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P1",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P1",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P1",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C297,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C308,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P2",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P2",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P2",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P2",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P2",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P2",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P2",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P2",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C297,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C308,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P3",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P3",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P3",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P3",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P3",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P3",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C297,"P3",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C308,"P3",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pelanggan",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pelanggan",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pelanggan",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pelanggan",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pelanggan",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pelanggan",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pelanggan",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pelanggan",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Kasir",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kasir",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Kasir",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kasir",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Kasir",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kasir",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Kasir",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kasir",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pending Payment",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pending Payment",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pending Payment",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pending Payment",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pending Payment",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pending Payment",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pending Payment",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pending Payment",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Dapur",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Dapur",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Dapur",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Dapur",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Dapur",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Dapur",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Dapur",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Dapur",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Keuangan",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Keuangan",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Keuangan",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Keuangan",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Keuangan",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Keuangan",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Keuangan",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Keuangan",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Setor Saldo Cash",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Setor Saldo Cash",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Setor Saldo Cash",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Setor Saldo Cash",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Setor Saldo Cash",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Setor Saldo Cash",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Setor Saldo Cash",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Setor Saldo Cash",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"QR Meja",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"QR Meja",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"QR Meja",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"QR Meja",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"QR Meja",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"QR Meja",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"QR Meja",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"QR Meja",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Diskon",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Diskon",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Diskon",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Diskon",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Diskon",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Diskon",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Diskon",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Diskon",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembayaran QRIS",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembayaran QRIS",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembayaran QRIS",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembayaran QRIS",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembayaran QRIS",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembayaran QRIS",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembayaran QRIS",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembayaran QRIS",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Tampilan",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Tampilan",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Tampilan",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Tampilan",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Tampilan",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Tampilan",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Tampilan",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Tampilan",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Super Admin",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Super Admin",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Super Admin",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Super Admin",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Super Admin",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Super Admin",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Super Admin",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Super Admin",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembaruan Aplikasi",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembaruan Aplikasi",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembaruan Aplikasi",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembaruan Aplikasi",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembaruan Aplikasi",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembaruan Aplikasi",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Pembaruan Aplikasi",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembaruan Aplikasi",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A297,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G297,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G308,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G297,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G308,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G297,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G308,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A297,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G297,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G308,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1727,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I297"/>
+  <dimension ref="A1:I308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8546,32 +8546,32 @@
     <row r="195">
       <c r="A195" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B195" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-01</t>
-        </is>
-      </c>
-      <c r="C195" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-07</t>
+        </is>
+      </c>
+      <c r="C195" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D195" s="16" t="inlineStr">
         <is>
-          <t>Buka pengumuman versi → Unduh Versi Terbaru</t>
+          <t>List Resto → hapus sebuah resto</t>
         </is>
       </c>
       <c r="E195" s="16" t="inlineStr">
         <is>
-          <t>Unduhan mulai di dalam aplikasi, tidak membuka peramban</t>
+          <t>Hilang dari daftar; datanya tidak dibuang</t>
         </is>
       </c>
       <c r="F195" s="16" t="inlineStr">
         <is>
-          <t>F-UP-01, F-UP-02</t>
+          <t>F-SA-07</t>
         </is>
       </c>
       <c r="G195" s="16" t="inlineStr"/>
@@ -8581,32 +8581,32 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B196" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-02</t>
-        </is>
-      </c>
-      <c r="C196" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-08</t>
+        </is>
+      </c>
+      <c r="C196" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>Perhatikan bar notifikasi HP</t>
+          <t>Buka Pilih Resto sebagai pelanggan</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Kemajuannya tampil berikut persennya</t>
+          <t>Resto terhapus tidak muncul</t>
         </is>
       </c>
       <c r="F196" s="13" t="inlineStr">
         <is>
-          <t>F-UP-03</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr"/>
@@ -8616,32 +8616,32 @@
     <row r="197">
       <c r="A197" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B197" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-03</t>
-        </is>
-      </c>
-      <c r="C197" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-09</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D197" s="16" t="inlineStr">
         <is>
-          <t>Kunci HP saat unduhan berjalan, tunggu, buka lagi</t>
+          <t>Pindai QR meja resto yang sudah dihapus, coba pesan</t>
         </is>
       </c>
       <c r="E197" s="16" t="inlineStr">
         <is>
-          <t>Unduhannya lanjut, tidak mengulang dari nol</t>
+          <t>Ditolak database, bukan hanya disembunyikan layarnya</t>
         </is>
       </c>
       <c r="F197" s="16" t="inlineStr">
         <is>
-          <t>F-UP-04</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G197" s="16" t="inlineStr"/>
@@ -8651,32 +8651,32 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B198" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-04</t>
-        </is>
-      </c>
-      <c r="C198" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-10</t>
+        </is>
+      </c>
+      <c r="C198" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>Tekan tombol unduh lagi saat unduhan berjalan</t>
+          <t>Coba ubah harga produk resto terhapus</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Muncul pilihan Batalkan atau Lanjutkan</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F198" s="13" t="inlineStr">
         <is>
-          <t>F-UP-05, F-IN-18</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr"/>
@@ -8686,32 +8686,32 @@
     <row r="199">
       <c r="A199" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B199" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-05</t>
-        </is>
-      </c>
-      <c r="C199" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-11</t>
+        </is>
+      </c>
+      <c r="C199" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D199" s="16" t="inlineStr">
         <is>
-          <t>Pilih Batalkan</t>
+          <t>Terbitkan tagihan setelah resto dihapus</t>
         </is>
       </c>
       <c r="E199" s="16" t="inlineStr">
         <is>
-          <t>Unduhan berhenti; tidak ditampilkan sebagai galat</t>
+          <t>Tidak ada tagihan baru untuk resto itu</t>
         </is>
       </c>
       <c r="F199" s="16" t="inlineStr">
         <is>
-          <t>F-IN-19</t>
+          <t>F-SA-11</t>
         </is>
       </c>
       <c r="G199" s="16" t="inlineStr"/>
@@ -8721,32 +8721,32 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B200" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-06</t>
-        </is>
-      </c>
-      <c r="C200" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-12</t>
+        </is>
+      </c>
+      <c r="C200" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>Biarkan unduhan selesai</t>
+          <t>Periksa tagihan lama resto terhapus</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Notifikasi "ketuk untuk memasang"; pemasang Android terbuka</t>
+          <t>Masih ada dan bisa ditelusuri</t>
         </is>
       </c>
       <c r="F200" s="13" t="inlineStr">
         <is>
-          <t>F-UP-06, F-IN-17</t>
+          <t>F-SA-11</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr"/>
@@ -8756,12 +8756,12 @@
     <row r="201">
       <c r="A201" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B201" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-07</t>
+          <t>TC-SA-13</t>
         </is>
       </c>
       <c r="C201" s="20" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="D201" s="16" t="inlineStr">
         <is>
-          <t>Matikan data seluler di tengah unduhan</t>
+          <t>Nyalakan saklar Tampilkan yang dihapus</t>
         </is>
       </c>
       <c r="E201" s="16" t="inlineStr">
         <is>
-          <t>Pesannya menyebut masalah koneksi, satu kalimat, tanpa isi galat mentah</t>
+          <t>Resto terhapus muncul, hanya dengan tombol Kembalikan</t>
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr">
         <is>
-          <t>F-UP-07, F-IN-19</t>
+          <t>F-SA-09</t>
         </is>
       </c>
       <c r="G201" s="16" t="inlineStr"/>
@@ -8791,32 +8791,32 @@
     <row r="202">
       <c r="A202" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B202" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-08</t>
-        </is>
-      </c>
-      <c r="C202" s="21" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-SA-14</t>
+        </is>
+      </c>
+      <c r="C202" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>Penuhi penyimpanan HP, lalu unduh</t>
+          <t>Ketuk Kembalikan</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Pesannya menyebut penyimpanan penuh — dibedakan dari masalah koneksi</t>
+          <t>Kembali ke daftar, tapi belum aktif — harus dinyalakan sendiri</t>
         </is>
       </c>
       <c r="F202" s="13" t="inlineStr">
         <is>
-          <t>F-UP-07</t>
+          <t>F-SA-08</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr"/>
@@ -8826,32 +8826,32 @@
     <row r="203">
       <c r="A203" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B203" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-09</t>
-        </is>
-      </c>
-      <c r="C203" s="22" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-SA-15</t>
+        </is>
+      </c>
+      <c r="C203" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D203" s="16" t="inlineStr">
         <is>
-          <t>Pakai jalur cadangan lewat peramban</t>
+          <t>Coba hapus penyewa platform (KaataGo)</t>
         </is>
       </c>
       <c r="E203" s="16" t="inlineStr">
         <is>
-          <t>Berkasnya terunduh</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
         <is>
-          <t>F-IN-06</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G203" s="16" t="inlineStr"/>
@@ -8861,32 +8861,32 @@
     <row r="204">
       <c r="A204" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B204" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-01</t>
-        </is>
-      </c>
-      <c r="C204" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-16</t>
+        </is>
+      </c>
+      <c r="C204" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Billing Resto → atur harga dan tanggal untuk sebuah resto</t>
+          <t>Coba set_resto_deleted sebagai Owner resto</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Tersimpan; kartu restonya menampilkan harga, tanggal, dan tenggangnya</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F204" s="13" t="inlineStr">
         <is>
-          <t>F-BL-01, F-BL-02</t>
+          <t>F-SA-07</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr"/>
@@ -8896,12 +8896,12 @@
     <row r="205">
       <c r="A205" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B205" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-02</t>
+          <t>TC-SA-17</t>
         </is>
       </c>
       <c r="C205" s="20" t="inlineStr">
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D205" s="16" t="inlineStr">
         <is>
-          <t>Buat resto baru, buka Billing Resto</t>
+          <t>Periksa baris resto terhapus di database</t>
         </is>
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>Sudah punya barisnya sendiri, berstatus Gratis</t>
+          <t>deleted_by dan deleted_at terisi</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
         <is>
-          <t>F-BL-06</t>
+          <t>F-SA-12</t>
         </is>
       </c>
       <c r="G205" s="16" t="inlineStr"/>
@@ -8931,32 +8931,32 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B206" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-03</t>
-        </is>
-      </c>
-      <c r="C206" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-01</t>
+        </is>
+      </c>
+      <c r="C206" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>Setel harga Rp 0, lewatkan tanggal jatuh tempo jauh</t>
+          <t>Buka pengumuman versi → Unduh Versi Terbaru</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Tidak pernah terbit tagihan, tidak pernah terkunci</t>
+          <t>Unduhan mulai di dalam aplikasi, tidak membuka peramban</t>
         </is>
       </c>
       <c r="F206" s="13" t="inlineStr">
         <is>
-          <t>F-BL-04</t>
+          <t>F-UP-01, F-UP-02</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr"/>
@@ -8966,32 +8966,32 @@
     <row r="207">
       <c r="A207" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B207" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-04</t>
-        </is>
-      </c>
-      <c r="C207" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-02</t>
+        </is>
+      </c>
+      <c r="C207" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D207" s="16" t="inlineStr">
         <is>
-          <t>Matikan saklar langganan pada resto berbayar yang menunggak</t>
+          <t>Perhatikan bar notifikasi HP</t>
         </is>
       </c>
       <c r="E207" s="16" t="inlineStr">
         <is>
-          <t>Tidak terkunci</t>
+          <t>Kemajuannya tampil berikut persennya</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
         <is>
-          <t>F-BL-05</t>
+          <t>F-UP-03</t>
         </is>
       </c>
       <c r="G207" s="16" t="inlineStr"/>
@@ -9001,12 +9001,12 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B208" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-05</t>
+          <t>TC-UP-03</t>
         </is>
       </c>
       <c r="C208" s="19" t="inlineStr">
@@ -9016,17 +9016,17 @@
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>Coba pilih tanggal tagihan 29, 30, atau 31</t>
+          <t>Kunci HP saat unduhan berjalan, tunggu, buka lagi</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Tidak tersedia di pilihan — hanya 1 sampai 28</t>
+          <t>Unduhannya lanjut, tidak mengulang dari nol</t>
         </is>
       </c>
       <c r="F208" s="13" t="inlineStr">
         <is>
-          <t>F-BL-02</t>
+          <t>F-UP-04</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr"/>
@@ -9036,12 +9036,12 @@
     <row r="209">
       <c r="A209" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B209" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-06</t>
+          <t>TC-UP-04</t>
         </is>
       </c>
       <c r="C209" s="20" t="inlineStr">
@@ -9051,17 +9051,17 @@
       </c>
       <c r="D209" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Terbitkan tagihan sekarang dua kali beruntun</t>
+          <t>Tekan tombol unduh lagi saat unduhan berjalan</t>
         </is>
       </c>
       <c r="E209" s="16" t="inlineStr">
         <is>
-          <t>Tagihan tetap satu untuk periode itu</t>
+          <t>Muncul pilihan Batalkan atau Lanjutkan</t>
         </is>
       </c>
       <c r="F209" s="16" t="inlineStr">
         <is>
-          <t>F-BL-08</t>
+          <t>F-UP-05, F-IN-18</t>
         </is>
       </c>
       <c r="G209" s="16" t="inlineStr"/>
@@ -9071,32 +9071,32 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B210" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-07</t>
-        </is>
-      </c>
-      <c r="C210" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-05</t>
+        </is>
+      </c>
+      <c r="C210" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>Setel jatuh tempo 3 hari lagi, buka aplikasi sebagai Kasir</t>
+          <t>Pilih Batalkan</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Pita pengingat tampil di atas layar; isi layarnya tetap bisa dipakai</t>
+          <t>Unduhan berhenti; tidak ditampilkan sebagai galat</t>
         </is>
       </c>
       <c r="F210" s="13" t="inlineStr">
         <is>
-          <t>F-BL-09</t>
+          <t>F-IN-19</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr"/>
@@ -9106,12 +9106,12 @@
     <row r="211">
       <c r="A211" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B211" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-08</t>
+          <t>TC-UP-06</t>
         </is>
       </c>
       <c r="C211" s="20" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="D211" s="16" t="inlineStr">
         <is>
-          <t>Setel jatuh tempo 4 hari lagi</t>
+          <t>Biarkan unduhan selesai</t>
         </is>
       </c>
       <c r="E211" s="16" t="inlineStr">
         <is>
-          <t>Pita belum tampil</t>
+          <t>Notifikasi "ketuk untuk memasang"; pemasang Android terbuka</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>F-BL-09</t>
+          <t>F-UP-06, F-IN-17</t>
         </is>
       </c>
       <c r="G211" s="16" t="inlineStr"/>
@@ -9141,32 +9141,32 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B212" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-09</t>
-        </is>
-      </c>
-      <c r="C212" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-07</t>
+        </is>
+      </c>
+      <c r="C212" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>Lewati jatuh tempo, masih dalam tenggang</t>
+          <t>Matikan data seluler di tengah unduhan</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Pita berubah merah; aplikasi belum terkunci</t>
+          <t>Pesannya menyebut masalah koneksi, satu kalimat, tanpa isi galat mentah</t>
         </is>
       </c>
       <c r="F212" s="13" t="inlineStr">
         <is>
-          <t>F-BL-03, F-BL-10</t>
+          <t>F-UP-07, F-IN-19</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr"/>
@@ -9176,32 +9176,32 @@
     <row r="213">
       <c r="A213" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B213" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-10</t>
-        </is>
-      </c>
-      <c r="C213" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-08</t>
+        </is>
+      </c>
+      <c r="C213" s="22" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D213" s="16" t="inlineStr">
         <is>
-          <t>Lewati tenggang, tagihan belum dibayar</t>
+          <t>Penuhi penyimpanan HP, lalu unduh</t>
         </is>
       </c>
       <c r="E213" s="16" t="inlineStr">
         <is>
-          <t>Seluruh layar diganti halaman Aplikasi Terkunci Sementara</t>
+          <t>Pesannya menyebut penyimpanan penuh — dibedakan dari masalah koneksi</t>
         </is>
       </c>
       <c r="F213" s="16" t="inlineStr">
         <is>
-          <t>F-BL-15</t>
+          <t>F-UP-07</t>
         </is>
       </c>
       <c r="G213" s="16" t="inlineStr"/>
@@ -9211,32 +9211,32 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B214" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-11</t>
-        </is>
-      </c>
-      <c r="C214" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-09</t>
+        </is>
+      </c>
+      <c r="C214" s="21" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, coba buat pesanan lewat API langsung</t>
+          <t>Pakai jalur cadangan lewat peramban</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Ditolak database — bukan hanya layarnya yang menutup</t>
+          <t>Berkasnya terunduh</t>
         </is>
       </c>
       <c r="F214" s="13" t="inlineStr">
         <is>
-          <t>F-BL-18, TSD §7.3</t>
+          <t>F-IN-06</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr"/>
@@ -9251,27 +9251,27 @@
       </c>
       <c r="B215" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-12</t>
-        </is>
-      </c>
-      <c r="C215" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-01</t>
+        </is>
+      </c>
+      <c r="C215" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D215" s="16" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, ketuk Lihat &amp; Bayar Tagihan</t>
+          <t>Super Admin → Billing Resto → atur harga dan tanggal untuk sebuah resto</t>
         </is>
       </c>
       <c r="E215" s="16" t="inlineStr">
         <is>
-          <t>Layar tagihan terbuka dan bisa dipakai</t>
+          <t>Tersimpan; kartu restonya menampilkan harga, tanggal, dan tenggangnya</t>
         </is>
       </c>
       <c r="F215" s="16" t="inlineStr">
         <is>
-          <t>F-BL-16</t>
+          <t>F-BL-01, F-BL-02</t>
         </is>
       </c>
       <c r="G215" s="16" t="inlineStr"/>
@@ -9286,27 +9286,27 @@
       </c>
       <c r="B216" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-13</t>
-        </is>
-      </c>
-      <c r="C216" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-02</t>
+        </is>
+      </c>
+      <c r="C216" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, ketuk Keluar</t>
+          <t>Buat resto baru, buka Billing Resto</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Berhasil keluar akun</t>
+          <t>Sudah punya barisnya sendiri, berstatus Gratis</t>
         </is>
       </c>
       <c r="F216" s="13" t="inlineStr">
         <is>
-          <t>F-BL-16</t>
+          <t>F-BL-06</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr"/>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="B217" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14</t>
+          <t>TC-BL-03</t>
         </is>
       </c>
       <c r="C217" s="18" t="inlineStr">
@@ -9331,17 +9331,17 @@
       </c>
       <c r="D217" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Buat Virtual Account → pilih BCA</t>
+          <t>Setel harga Rp 0, lewatkan tanggal jatuh tempo jauh</t>
         </is>
       </c>
       <c r="E217" s="16" t="inlineStr">
         <is>
-          <t>Nomor VA tampil berikut nominal dan masa berlakunya</t>
+          <t>Tidak pernah terbit tagihan, tidak pernah terkunci</t>
         </is>
       </c>
       <c r="F217" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11, F-BL-19</t>
+          <t>F-BL-04</t>
         </is>
       </c>
       <c r="G217" s="16" t="inlineStr"/>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="B218" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14b</t>
+          <t>TC-BL-04</t>
         </is>
       </c>
       <c r="C218" s="15" t="inlineStr">
@@ -9366,17 +9366,17 @@
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>Tutup layar, buka lagi, ketuk lagi</t>
+          <t>Matikan saklar langganan pada resto berbayar yang menunggak</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Nomor VA sama, tidak diterbitkan yang baru</t>
+          <t>Tidak terkunci</t>
         </is>
       </c>
       <c r="F218" s="13" t="inlineStr">
         <is>
-          <t>F-BL-23</t>
+          <t>F-BL-05</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr"/>
@@ -9391,27 +9391,27 @@
       </c>
       <c r="B219" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14c</t>
-        </is>
-      </c>
-      <c r="C219" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-05</t>
+        </is>
+      </c>
+      <c r="C219" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D219" s="16" t="inlineStr">
         <is>
-          <t>Transfer tepat sesuai nominal ke VA itu</t>
+          <t>Coba pilih tanggal tagihan 29, 30, atau 31</t>
         </is>
       </c>
       <c r="E219" s="16" t="inlineStr">
         <is>
-          <t>Tagihan lunas sendiri dalam hitungan detik; kunci terbuka tanpa mengirim bukti</t>
+          <t>Tidak tersedia di pilihan — hanya 1 sampai 28</t>
         </is>
       </c>
       <c r="F219" s="16" t="inlineStr">
         <is>
-          <t>F-BL-22</t>
+          <t>F-BL-02</t>
         </is>
       </c>
       <c r="G219" s="16" t="inlineStr"/>
@@ -9426,27 +9426,27 @@
       </c>
       <c r="B220" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14d</t>
-        </is>
-      </c>
-      <c r="C220" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-06</t>
+        </is>
+      </c>
+      <c r="C220" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>Transfer kurang dari nominal</t>
+          <t>Ketuk Terbitkan tagihan sekarang dua kali beruntun</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Tidak melunasi; tagihan tetap terbuka</t>
+          <t>Tagihan tetap satu untuk periode itu</t>
         </is>
       </c>
       <c r="F220" s="13" t="inlineStr">
         <is>
-          <t>F-BL-20</t>
+          <t>F-BL-08</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr"/>
@@ -9461,27 +9461,27 @@
       </c>
       <c r="B221" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14e</t>
-        </is>
-      </c>
-      <c r="C221" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-07</t>
+        </is>
+      </c>
+      <c r="C221" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D221" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Ganti Bank → pilih BNI</t>
+          <t>Setel jatuh tempo 3 hari lagi, buka aplikasi sebagai Kasir</t>
         </is>
       </c>
       <c r="E221" s="16" t="inlineStr">
         <is>
-          <t>Nomor VA baru untuk bank itu</t>
+          <t>Pita pengingat tampil di atas layar; isi layarnya tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F221" s="16" t="inlineStr">
         <is>
-          <t>F-BL-19</t>
+          <t>F-BL-09</t>
         </is>
       </c>
       <c r="G221" s="16" t="inlineStr"/>
@@ -9496,27 +9496,27 @@
       </c>
       <c r="B222" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14f</t>
-        </is>
-      </c>
-      <c r="C222" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-08</t>
+        </is>
+      </c>
+      <c r="C222" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>Periksa rekening tujuan dana VA di Dashboard Xendit</t>
+          <t>Setel jatuh tempo 4 hari lagi</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Masuk ke akun KaataGo, bukan sub-akun resto</t>
+          <t>Pita belum tampil</t>
         </is>
       </c>
       <c r="F222" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11, TSD §7.3</t>
+          <t>F-BL-09</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr"/>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B223" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14g</t>
+          <t>TC-BL-09</t>
         </is>
       </c>
       <c r="C223" s="18" t="inlineStr">
@@ -9541,17 +9541,17 @@
       </c>
       <c r="D223" s="16" t="inlineStr">
         <is>
-          <t>Kirim callback palsu ke xendit-billing-webhook tanpa token</t>
+          <t>Lewati jatuh tempo, masih dalam tenggang</t>
         </is>
       </c>
       <c r="E223" s="16" t="inlineStr">
         <is>
-          <t>Ditolak 401; tagihan tidak berubah</t>
+          <t>Pita berubah merah; aplikasi belum terkunci</t>
         </is>
       </c>
       <c r="F223" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-03, F-BL-10</t>
         </is>
       </c>
       <c r="G223" s="16" t="inlineStr"/>
@@ -9566,27 +9566,27 @@
       </c>
       <c r="B224" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14h</t>
-        </is>
-      </c>
-      <c r="C224" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-10</t>
+        </is>
+      </c>
+      <c r="C224" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>Xendit mengirim callback yang sama dua kali</t>
+          <t>Lewati tenggang, tagihan belum dibayar</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Tagihan tetap lunas sekali; catatan pelunasnya tidak berubah</t>
+          <t>Seluruh layar diganti halaman Aplikasi Terkunci Sementara</t>
         </is>
       </c>
       <c r="F224" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-15</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr"/>
@@ -9601,27 +9601,27 @@
       </c>
       <c r="B225" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14i</t>
-        </is>
-      </c>
-      <c r="C225" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-11</t>
+        </is>
+      </c>
+      <c r="C225" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D225" s="16" t="inlineStr">
         <is>
-          <t>Unggah bukti transfer manual lewat jalur cadangan</t>
+          <t>Pada keadaan terkunci, coba buat pesanan lewat API langsung</t>
         </is>
       </c>
       <c r="E225" s="16" t="inlineStr">
         <is>
-          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
+          <t>Ditolak database — bukan hanya layarnya yang menutup</t>
         </is>
       </c>
       <c r="F225" s="16" t="inlineStr">
         <is>
-          <t>F-BL-24, F-BL-12</t>
+          <t>F-BL-18, TSD §7.3</t>
         </is>
       </c>
       <c r="G225" s="16" t="inlineStr"/>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="B226" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-15</t>
+          <t>TC-BL-12</t>
         </is>
       </c>
       <c r="C226" s="15" t="inlineStr">
@@ -9646,17 +9646,17 @@
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>Coba kirim bukti tanpa melampirkan foto</t>
+          <t>Pada keadaan terkunci, ketuk Lihat &amp; Bayar Tagihan</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Tombol Kirim mati</t>
+          <t>Layar tagihan terbuka dan bisa dipakai</t>
         </is>
       </c>
       <c r="F226" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-16</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr"/>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B227" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-16</t>
+          <t>TC-BL-13</t>
         </is>
       </c>
       <c r="C227" s="18" t="inlineStr">
@@ -9681,17 +9681,17 @@
       </c>
       <c r="D227" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → tab Tagihan → Terima</t>
+          <t>Pada keadaan terkunci, ketuk Keluar</t>
         </is>
       </c>
       <c r="E227" s="16" t="inlineStr">
         <is>
-          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
+          <t>Berhasil keluar akun</t>
         </is>
       </c>
       <c r="F227" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-16</t>
         </is>
       </c>
       <c r="G227" s="16" t="inlineStr"/>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="B228" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-17</t>
+          <t>TC-BL-14</t>
         </is>
       </c>
       <c r="C228" s="15" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Tolak tanpa mengisi alasan</t>
+          <t>Ketuk Buat Virtual Account → pilih BCA</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
+          <t>Nomor VA tampil berikut nominal dan masa berlakunya</t>
         </is>
       </c>
       <c r="F228" s="13" t="inlineStr">
         <is>
-          <t>F-BL-14</t>
+          <t>F-BL-11, F-BL-19</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr"/>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="B229" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-18</t>
+          <t>TC-BL-14b</t>
         </is>
       </c>
       <c r="C229" s="18" t="inlineStr">
@@ -9751,17 +9751,17 @@
       </c>
       <c r="D229" s="16" t="inlineStr">
         <is>
-          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
+          <t>Tutup layar, buka lagi, ketuk lagi</t>
         </is>
       </c>
       <c r="E229" s="16" t="inlineStr">
         <is>
-          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
+          <t>Nomor VA sama, tidak diterbitkan yang baru</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
         <is>
-          <t>F-BL-14, F-BL-15</t>
+          <t>F-BL-23</t>
         </is>
       </c>
       <c r="G229" s="16" t="inlineStr"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="B230" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-19</t>
+          <t>TC-BL-14c</t>
         </is>
       </c>
       <c r="C230" s="15" t="inlineStr">
@@ -9786,17 +9786,17 @@
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Super Admin saat ada resto terkunci</t>
+          <t>Transfer tepat sesuai nominal ke VA itu</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Tidak terkunci sama sekali</t>
+          <t>Tagihan lunas sendiri dalam hitungan detik; kunci terbuka tanpa mengirim bukti</t>
         </is>
       </c>
       <c r="F230" s="13" t="inlineStr">
         <is>
-          <t>F-BL-17</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr"/>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B231" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-20</t>
+          <t>TC-BL-14d</t>
         </is>
       </c>
       <c r="C231" s="18" t="inlineStr">
@@ -9821,17 +9821,17 @@
       </c>
       <c r="D231" s="16" t="inlineStr">
         <is>
-          <t>Sebagai resto terkunci, coba ubah harga produk</t>
+          <t>Transfer kurang dari nominal</t>
         </is>
       </c>
       <c r="E231" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — katalog ikut dibekukan</t>
+          <t>Tidak melunasi; tagihan tetap terbuka</t>
         </is>
       </c>
       <c r="F231" s="16" t="inlineStr">
         <is>
-          <t>F-BL-18</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G231" s="16" t="inlineStr"/>
@@ -9846,27 +9846,27 @@
       </c>
       <c r="B232" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-21</t>
-        </is>
-      </c>
-      <c r="C232" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14e</t>
+        </is>
+      </c>
+      <c r="C232" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
+          <t>Ketuk Ganti Bank → pilih BNI</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Resto B tidak terpengaruh</t>
+          <t>Nomor VA baru untuk bank itu</t>
         </is>
       </c>
       <c r="F232" s="13" t="inlineStr">
         <is>
-          <t>F-BL-15, A-10</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="B233" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-22</t>
+          <t>TC-BL-14f</t>
         </is>
       </c>
       <c r="C233" s="18" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D233" s="16" t="inlineStr">
         <is>
-          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
+          <t>Periksa rekening tujuan dana VA di Dashboard Xendit</t>
         </is>
       </c>
       <c r="E233" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — hanya Super Admin</t>
+          <t>Masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
       <c r="F233" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-11, TSD §7.3</t>
         </is>
       </c>
       <c r="G233" s="16" t="inlineStr"/>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B234" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-23</t>
+          <t>TC-BL-14g</t>
         </is>
       </c>
       <c r="C234" s="15" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
+          <t>Kirim callback palsu ke xendit-billing-webhook tanpa token</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Ditolak 401; tagihan tidak berubah</t>
         </is>
       </c>
       <c r="F234" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13, TSD §7.3</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr"/>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="B235" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-24</t>
+          <t>TC-BL-14h</t>
         </is>
       </c>
       <c r="C235" s="20" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="D235" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
+          <t>Xendit mengirim callback yang sama dua kali</t>
         </is>
       </c>
       <c r="E235" s="16" t="inlineStr">
         <is>
-          <t>Tidak terkunci karena gagal memeriksa</t>
+          <t>Tagihan tetap lunas sekali; catatan pelunasnya tidak berubah</t>
         </is>
       </c>
       <c r="F235" s="16" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="B236" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-25</t>
+          <t>TC-BL-14i</t>
         </is>
       </c>
       <c r="C236" s="19" t="inlineStr">
@@ -9996,17 +9996,17 @@
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>Owner → Tagihan Langganan</t>
+          <t>Unggah bukti transfer manual lewat jalur cadangan</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Terbuka, memuat paket dan riwayat tagihan</t>
+          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
         </is>
       </c>
       <c r="F236" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-24, F-BL-12</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr"/>
@@ -10016,12 +10016,12 @@
     <row r="237">
       <c r="A237" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B237" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-01</t>
+          <t>TC-BL-15</t>
         </is>
       </c>
       <c r="C237" s="18" t="inlineStr">
@@ -10031,17 +10031,17 @@
       </c>
       <c r="D237" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Riwayat Langganan</t>
+          <t>Coba kirim bukti tanpa melampirkan foto</t>
         </is>
       </c>
       <c r="E237" s="16" t="inlineStr">
         <is>
-          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
+          <t>Tombol Kirim mati</t>
         </is>
       </c>
       <c r="F237" s="16" t="inlineStr">
         <is>
-          <t>F-PF-01</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G237" s="16" t="inlineStr"/>
@@ -10051,32 +10051,32 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B238" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-02</t>
-        </is>
-      </c>
-      <c r="C238" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-16</t>
+        </is>
+      </c>
+      <c r="C238" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>Periksa penanda jalur pelunasan tiap baris</t>
+          <t>Super Admin → tab Tagihan → Terima</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
+          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
         </is>
       </c>
       <c r="F238" s="13" t="inlineStr">
         <is>
-          <t>F-PF-02</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr"/>
@@ -10086,12 +10086,12 @@
     <row r="239">
       <c r="A239" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B239" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-03</t>
+          <t>TC-BL-17</t>
         </is>
       </c>
       <c r="C239" s="18" t="inlineStr">
@@ -10101,17 +10101,17 @@
       </c>
       <c r="D239" s="16" t="inlineStr">
         <is>
-          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
+          <t>Super Admin → Tolak tanpa mengisi alasan</t>
         </is>
       </c>
       <c r="E239" s="16" t="inlineStr">
         <is>
-          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
+          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
         </is>
       </c>
       <c r="F239" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03, F-PF-05</t>
+          <t>F-BL-14</t>
         </is>
       </c>
       <c r="G239" s="16" t="inlineStr"/>
@@ -10121,12 +10121,12 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B240" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-04</t>
+          <t>TC-BL-18</t>
         </is>
       </c>
       <c r="C240" s="15" t="inlineStr">
@@ -10136,17 +10136,17 @@
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>Simpan diskon tanpa memilih resto</t>
+          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
+          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
         </is>
       </c>
       <c r="F240" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-BL-14, F-BL-15</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr"/>
@@ -10156,32 +10156,32 @@
     <row r="241">
       <c r="A241" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B241" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-05</t>
-        </is>
-      </c>
-      <c r="C241" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-19</t>
+        </is>
+      </c>
+      <c r="C241" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D241" s="16" t="inlineStr">
         <is>
-          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
+          <t>Login sebagai Super Admin saat ada resto terkunci</t>
         </is>
       </c>
       <c r="E241" s="16" t="inlineStr">
         <is>
-          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
+          <t>Tidak terkunci sama sekali</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-BL-17</t>
         </is>
       </c>
       <c r="G241" s="16" t="inlineStr"/>
@@ -10191,32 +10191,32 @@
     <row r="242">
       <c r="A242" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B242" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-06</t>
-        </is>
-      </c>
-      <c r="C242" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-20</t>
+        </is>
+      </c>
+      <c r="C242" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
+          <t>Sebagai resto terkunci, coba ubah harga produk</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
+          <t>Ditolak — katalog ikut dibekukan</t>
         </is>
       </c>
       <c r="F242" s="13" t="inlineStr">
         <is>
-          <t>F-PF-04</t>
+          <t>F-BL-18</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr"/>
@@ -10226,12 +10226,12 @@
     <row r="243">
       <c r="A243" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B243" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-07</t>
+          <t>TC-BL-21</t>
         </is>
       </c>
       <c r="C243" s="18" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="D243" s="16" t="inlineStr">
         <is>
-          <t>Hapus diskon setelah tagihan terbit</t>
+          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
         </is>
       </c>
       <c r="E243" s="16" t="inlineStr">
         <is>
-          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
+          <t>Resto B tidak terpengaruh</t>
         </is>
       </c>
       <c r="F243" s="16" t="inlineStr">
         <is>
-          <t>F-PF-05</t>
+          <t>F-BL-15, A-10</t>
         </is>
       </c>
       <c r="G243" s="16" t="inlineStr"/>
@@ -10261,12 +10261,12 @@
     <row r="244">
       <c r="A244" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B244" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-08</t>
+          <t>TC-BL-22</t>
         </is>
       </c>
       <c r="C244" s="15" t="inlineStr">
@@ -10276,17 +10276,17 @@
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
+          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Dua baris: pendapatan kredit, diskon debit</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F244" s="13" t="inlineStr">
         <is>
-          <t>F-PF-06, F-PF-07</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr"/>
@@ -10296,12 +10296,12 @@
     <row r="245">
       <c r="A245" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B245" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-09</t>
+          <t>TC-BL-23</t>
         </is>
       </c>
       <c r="C245" s="18" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="D245" s="16" t="inlineStr">
         <is>
-          <t>Tagihan ditolak lalu diterima lagi</t>
+          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
         </is>
       </c>
       <c r="E245" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F245" s="16" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-BL-13, TSD §7.3</t>
         </is>
       </c>
       <c r="G245" s="16" t="inlineStr"/>
@@ -10331,32 +10331,32 @@
     <row r="246">
       <c r="A246" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B246" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-10</t>
-        </is>
-      </c>
-      <c r="C246" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-24</t>
+        </is>
+      </c>
+      <c r="C246" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL resto yang membayar</t>
+          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada baris pendapatan langganan di sana</t>
+          <t>Tidak terkunci karena gagal memeriksa</t>
         </is>
       </c>
       <c r="F246" s="13" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr"/>
@@ -10366,12 +10366,12 @@
     <row r="247">
       <c r="A247" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B247" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-11</t>
+          <t>TC-BL-25</t>
         </is>
       </c>
       <c r="C247" s="20" t="inlineStr">
@@ -10381,17 +10381,17 @@
       </c>
       <c r="D247" s="16" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account KaataGo</t>
+          <t>Owner → Tagihan Langganan</t>
         </is>
       </c>
       <c r="E247" s="16" t="inlineStr">
         <is>
-          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
+          <t>Terbuka, memuat paket dan riwayat tagihan</t>
         </is>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
-          <t>F-PF-08</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G247" s="16" t="inlineStr"/>
@@ -10406,27 +10406,27 @@
       </c>
       <c r="B248" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-12</t>
-        </is>
-      </c>
-      <c r="C248" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-01</t>
+        </is>
+      </c>
+      <c r="C248" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
+          <t>Super Admin → Finance → Riwayat Langganan</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Bekerja sama seperti di resto</t>
+          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
         </is>
       </c>
       <c r="F248" s="13" t="inlineStr">
         <is>
-          <t>F-PF-09</t>
+          <t>F-PF-01</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr"/>
@@ -10441,27 +10441,27 @@
       </c>
       <c r="B249" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-13</t>
-        </is>
-      </c>
-      <c r="C249" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-02</t>
+        </is>
+      </c>
+      <c r="C249" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D249" s="16" t="inlineStr">
         <is>
-          <t>Telusuri menu Finance KaataGo</t>
+          <t>Periksa penanda jalur pelunasan tiap baris</t>
         </is>
       </c>
       <c r="E249" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada Setor Saldo Cash</t>
+          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
         </is>
       </c>
       <c r="F249" s="16" t="inlineStr">
         <is>
-          <t>F-PF-10</t>
+          <t>F-PF-02</t>
         </is>
       </c>
       <c r="G249" s="16" t="inlineStr"/>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="B250" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-14</t>
+          <t>TC-PF-03</t>
         </is>
       </c>
       <c r="C250" s="15" t="inlineStr">
@@ -10486,17 +10486,17 @@
       </c>
       <c r="D250" s="13" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL Semua Resto</t>
+          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
+          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
         </is>
       </c>
       <c r="F250" s="13" t="inlineStr">
         <is>
-          <t>F-PF-11</t>
+          <t>F-PF-03, F-PF-05</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr"/>
@@ -10511,7 +10511,7 @@
       </c>
       <c r="B251" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-15</t>
+          <t>TC-PF-04</t>
         </is>
       </c>
       <c r="C251" s="18" t="inlineStr">
@@ -10521,17 +10521,17 @@
       </c>
       <c r="D251" s="16" t="inlineStr">
         <is>
-          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
+          <t>Simpan diskon tanpa memilih resto</t>
         </is>
       </c>
       <c r="E251" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun — hanya bisa dilihat</t>
+          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
         </is>
       </c>
       <c r="F251" s="16" t="inlineStr">
         <is>
-          <t>F-PF-12</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G251" s="16" t="inlineStr"/>
@@ -10546,27 +10546,27 @@
       </c>
       <c r="B252" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-16</t>
-        </is>
-      </c>
-      <c r="C252" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-05</t>
+        </is>
+      </c>
+      <c r="C252" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
+          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
         </is>
       </c>
       <c r="F252" s="13" t="inlineStr">
         <is>
-          <t>F-PF-12, TSD §7.4</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr"/>
@@ -10581,27 +10581,27 @@
       </c>
       <c r="B253" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-17</t>
-        </is>
-      </c>
-      <c r="C253" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-06</t>
+        </is>
+      </c>
+      <c r="C253" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D253" s="16" t="inlineStr">
         <is>
-          <t>Buka Pilih Resto sebagai pelanggan</t>
+          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
         </is>
       </c>
       <c r="E253" s="16" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul di daftar mana pun</t>
+          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
         </is>
       </c>
       <c r="F253" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-04</t>
         </is>
       </c>
       <c r="G253" s="16" t="inlineStr"/>
@@ -10616,7 +10616,7 @@
       </c>
       <c r="B254" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-18</t>
+          <t>TC-PF-07</t>
         </is>
       </c>
       <c r="C254" s="15" t="inlineStr">
@@ -10626,17 +10626,17 @@
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
+          <t>Hapus diskon setelah tagihan terbit</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
+          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
         </is>
       </c>
       <c r="F254" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-05</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr"/>
@@ -10651,27 +10651,27 @@
       </c>
       <c r="B255" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-19</t>
-        </is>
-      </c>
-      <c r="C255" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-08</t>
+        </is>
+      </c>
+      <c r="C255" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D255" s="16" t="inlineStr">
         <is>
-          <t>Buka Diskon Langganan sebagai Owner resto</t>
+          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E255" s="16" t="inlineStr">
         <is>
-          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
+          <t>Dua baris: pendapatan kredit, diskon debit</t>
         </is>
       </c>
       <c r="F255" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-PF-06, F-PF-07</t>
         </is>
       </c>
       <c r="G255" s="16" t="inlineStr"/>
@@ -10681,12 +10681,12 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B256" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-PF-09</t>
         </is>
       </c>
       <c r="C256" s="15" t="inlineStr">
@@ -10696,17 +10696,17 @@
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Tagihan ditolak lalu diterima lagi</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
         </is>
       </c>
       <c r="F256" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr"/>
@@ -10716,12 +10716,12 @@
     <row r="257">
       <c r="A257" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B257" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-PF-10</t>
         </is>
       </c>
       <c r="C257" s="18" t="inlineStr">
@@ -10731,17 +10731,17 @@
       </c>
       <c r="D257" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Buka Jurnal GL resto yang membayar</t>
         </is>
       </c>
       <c r="E257" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Tidak ada baris pendapatan langganan di sana</t>
         </is>
       </c>
       <c r="F257" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G257" s="16" t="inlineStr"/>
@@ -10751,32 +10751,32 @@
     <row r="258">
       <c r="A258" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B258" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
-        </is>
-      </c>
-      <c r="C258" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-11</t>
+        </is>
+      </c>
+      <c r="C258" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F258" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr"/>
@@ -10786,32 +10786,32 @@
     <row r="259">
       <c r="A259" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B259" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
-        </is>
-      </c>
-      <c r="C259" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-12</t>
+        </is>
+      </c>
+      <c r="C259" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D259" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
         </is>
       </c>
       <c r="E259" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Bekerja sama seperti di resto</t>
         </is>
       </c>
       <c r="F259" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-PF-09</t>
         </is>
       </c>
       <c r="G259" s="16" t="inlineStr"/>
@@ -10821,12 +10821,12 @@
     <row r="260">
       <c r="A260" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B260" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-PF-13</t>
         </is>
       </c>
       <c r="C260" s="15" t="inlineStr">
@@ -10836,17 +10836,17 @@
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Telusuri menu Finance KaataGo</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Tidak ada Setor Saldo Cash</t>
         </is>
       </c>
       <c r="F260" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-PF-10</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr"/>
@@ -10856,12 +10856,12 @@
     <row r="261">
       <c r="A261" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B261" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-PF-14</t>
         </is>
       </c>
       <c r="C261" s="18" t="inlineStr">
@@ -10871,17 +10871,17 @@
       </c>
       <c r="D261" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Buka Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E261" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
         </is>
       </c>
       <c r="F261" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-PF-11</t>
         </is>
       </c>
       <c r="G261" s="16" t="inlineStr"/>
@@ -10891,12 +10891,12 @@
     <row r="262">
       <c r="A262" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B262" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-PF-15</t>
         </is>
       </c>
       <c r="C262" s="15" t="inlineStr">
@@ -10906,17 +10906,17 @@
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Tidak ada satu pun — hanya bisa dilihat</t>
         </is>
       </c>
       <c r="F262" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-PF-12</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr"/>
@@ -10926,12 +10926,12 @@
     <row r="263">
       <c r="A263" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B263" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
+          <t>TC-PF-16</t>
         </is>
       </c>
       <c r="C263" s="18" t="inlineStr">
@@ -10941,17 +10941,17 @@
       </c>
       <c r="D263" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
         </is>
       </c>
       <c r="E263" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F263" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-PF-12, TSD §7.4</t>
         </is>
       </c>
       <c r="G263" s="16" t="inlineStr"/>
@@ -10961,12 +10961,12 @@
     <row r="264">
       <c r="A264" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B264" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-PF-17</t>
         </is>
       </c>
       <c r="C264" s="15" t="inlineStr">
@@ -10976,17 +10976,17 @@
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Buka Pilih Resto sebagai pelanggan</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>KaataGo tidak muncul di daftar mana pun</t>
         </is>
       </c>
       <c r="F264" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr"/>
@@ -10996,12 +10996,12 @@
     <row r="265">
       <c r="A265" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B265" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-PF-18</t>
         </is>
       </c>
       <c r="C265" s="18" t="inlineStr">
@@ -11011,17 +11011,17 @@
       </c>
       <c r="D265" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
         </is>
       </c>
       <c r="E265" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
         </is>
       </c>
       <c r="F265" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G265" s="16" t="inlineStr"/>
@@ -11031,12 +11031,12 @@
     <row r="266">
       <c r="A266" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B266" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
+          <t>TC-PF-19</t>
         </is>
       </c>
       <c r="C266" s="19" t="inlineStr">
@@ -11046,17 +11046,17 @@
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Buka Diskon Langganan sebagai Owner resto</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
         </is>
       </c>
       <c r="F266" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr"/>
@@ -11071,27 +11071,27 @@
       </c>
       <c r="B267" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C267" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-01</t>
+        </is>
+      </c>
+      <c r="C267" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D267" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E267" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F267" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G267" s="16" t="inlineStr"/>
@@ -11106,27 +11106,27 @@
       </c>
       <c r="B268" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C268" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-02</t>
+        </is>
+      </c>
+      <c r="C268" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F268" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr"/>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="B269" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-TS-03</t>
         </is>
       </c>
       <c r="C269" s="18" t="inlineStr">
@@ -11151,17 +11151,17 @@
       </c>
       <c r="D269" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E269" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F269" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G269" s="16" t="inlineStr"/>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B270" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
+          <t>TC-TS-04</t>
         </is>
       </c>
       <c r="C270" s="15" t="inlineStr">
@@ -11186,17 +11186,17 @@
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F270" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr"/>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B271" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-TS-05</t>
         </is>
       </c>
       <c r="C271" s="18" t="inlineStr">
@@ -11221,17 +11221,17 @@
       </c>
       <c r="D271" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E271" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F271" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G271" s="16" t="inlineStr"/>
@@ -11246,27 +11246,27 @@
       </c>
       <c r="B272" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C272" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-06</t>
+        </is>
+      </c>
+      <c r="C272" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F272" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr"/>
@@ -11281,27 +11281,27 @@
       </c>
       <c r="B273" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C273" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-07</t>
+        </is>
+      </c>
+      <c r="C273" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E273" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F273" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G273" s="16" t="inlineStr"/>
@@ -11316,27 +11316,27 @@
       </c>
       <c r="B274" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C274" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C274" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr"/>
@@ -11346,12 +11346,12 @@
     <row r="275">
       <c r="A275" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B275" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
+          <t>TC-TS-09</t>
         </is>
       </c>
       <c r="C275" s="18" t="inlineStr">
@@ -11361,17 +11361,17 @@
       </c>
       <c r="D275" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E275" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F275" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G275" s="16" t="inlineStr"/>
@@ -11381,12 +11381,12 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B276" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
+          <t>TC-TS-10</t>
         </is>
       </c>
       <c r="C276" s="15" t="inlineStr">
@@ -11396,17 +11396,17 @@
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr"/>
@@ -11416,32 +11416,32 @@
     <row r="277">
       <c r="A277" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B277" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
-        </is>
-      </c>
-      <c r="C277" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-11</t>
+        </is>
+      </c>
+      <c r="C277" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D277" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E277" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F277" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G277" s="16" t="inlineStr"/>
@@ -11451,32 +11451,32 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B278" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
-        </is>
-      </c>
-      <c r="C278" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C278" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr"/>
@@ -11486,32 +11486,32 @@
     <row r="279">
       <c r="A279" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B279" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
-        </is>
-      </c>
-      <c r="C279" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-13</t>
+        </is>
+      </c>
+      <c r="C279" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E279" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F279" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G279" s="16" t="inlineStr"/>
@@ -11521,12 +11521,12 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B280" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-TS-14</t>
         </is>
       </c>
       <c r="C280" s="15" t="inlineStr">
@@ -11536,17 +11536,17 @@
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr"/>
@@ -11556,32 +11556,32 @@
     <row r="281">
       <c r="A281" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B281" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C281" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C281" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D281" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E281" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F281" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G281" s="16" t="inlineStr"/>
@@ -11591,32 +11591,32 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B282" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C282" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-16</t>
+        </is>
+      </c>
+      <c r="C282" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>F-PG-02, TSD §7.1</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr"/>
@@ -11626,12 +11626,12 @@
     <row r="283">
       <c r="A283" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B283" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
+          <t>TC-TS-17</t>
         </is>
       </c>
       <c r="C283" s="20" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="D283" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
         </is>
       </c>
       <c r="E283" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
         </is>
       </c>
       <c r="F283" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>TSD §1.2</t>
         </is>
       </c>
       <c r="G283" s="16" t="inlineStr"/>
@@ -11661,12 +11661,12 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B284" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
+          <t>TC-TS-18</t>
         </is>
       </c>
       <c r="C284" s="19" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
         </is>
       </c>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>TSD §6.5</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr"/>
@@ -11696,12 +11696,12 @@
     <row r="285">
       <c r="A285" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B285" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
+          <t>TC-TS-19</t>
         </is>
       </c>
       <c r="C285" s="20" t="inlineStr">
@@ -11711,17 +11711,17 @@
       </c>
       <c r="D285" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Hapus resto uji</t>
         </is>
       </c>
       <c r="E285" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
         </is>
       </c>
       <c r="F285" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>TSD §4.0</t>
         </is>
       </c>
       <c r="G285" s="16" t="inlineStr"/>
@@ -11736,27 +11736,27 @@
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
-        </is>
-      </c>
-      <c r="C286" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C286" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
         </is>
       </c>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>F-KS-09</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B287" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
+          <t>TC-RG-02</t>
         </is>
       </c>
       <c r="C287" s="18" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="D287" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
         </is>
       </c>
       <c r="E287" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
         </is>
       </c>
       <c r="F287" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-PP-09, A-13</t>
         </is>
       </c>
       <c r="G287" s="16" t="inlineStr"/>
@@ -11806,27 +11806,27 @@
       </c>
       <c r="B288" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
-        </is>
-      </c>
-      <c r="C288" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C288" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Tidak muncul sama sekali</t>
         </is>
       </c>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr"/>
@@ -11836,25 +11836,410 @@
     <row r="289">
       <c r="A289" s="16" t="inlineStr">
         <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B289" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C289" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D289" s="16" t="inlineStr">
+        <is>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+        </is>
+      </c>
+      <c r="E289" s="16" t="inlineStr">
+        <is>
+          <t>Nominalnya sama dengan yang diajukan</t>
+        </is>
+      </c>
+      <c r="F289" s="16" t="inlineStr">
+        <is>
+          <t>F-FN-03</t>
+        </is>
+      </c>
+      <c r="G289" s="16" t="inlineStr"/>
+      <c r="H289" s="16" t="inlineStr"/>
+      <c r="I289" s="16" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B290" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C290" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D290" s="13" t="inlineStr">
+        <is>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+        </is>
+      </c>
+      <c r="E290" s="13" t="inlineStr">
+        <is>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
+        </is>
+      </c>
+      <c r="F290" s="13" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="G290" s="13" t="inlineStr"/>
+      <c r="H290" s="13" t="inlineStr"/>
+      <c r="I290" s="13" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B291" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C291" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D291" s="16" t="inlineStr">
+        <is>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+        </is>
+      </c>
+      <c r="E291" s="16" t="inlineStr">
+        <is>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+        </is>
+      </c>
+      <c r="F291" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-10, F-DS-12</t>
+        </is>
+      </c>
+      <c r="G291" s="16" t="inlineStr"/>
+      <c r="H291" s="16" t="inlineStr"/>
+      <c r="I291" s="16" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B292" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C292" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D292" s="13" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E292" s="13" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F292" s="13" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G292" s="13" t="inlineStr"/>
+      <c r="H292" s="13" t="inlineStr"/>
+      <c r="I292" s="13" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B293" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C293" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D293" s="16" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E293" s="16" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F293" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G293" s="16" t="inlineStr"/>
+      <c r="H293" s="16" t="inlineStr"/>
+      <c r="I293" s="16" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B294" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C294" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D294" s="13" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E294" s="13" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F294" s="13" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G294" s="13" t="inlineStr"/>
+      <c r="H294" s="13" t="inlineStr"/>
+      <c r="I294" s="13" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B295" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C295" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D295" s="16" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E295" s="16" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F295" s="16" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G295" s="16" t="inlineStr"/>
+      <c r="H295" s="16" t="inlineStr"/>
+      <c r="I295" s="16" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B296" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C296" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D296" s="13" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E296" s="13" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F296" s="13" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G296" s="13" t="inlineStr"/>
+      <c r="H296" s="13" t="inlineStr"/>
+      <c r="I296" s="13" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B297" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C297" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D297" s="16" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E297" s="16" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F297" s="16" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G297" s="16" t="inlineStr"/>
+      <c r="H297" s="16" t="inlineStr"/>
+      <c r="I297" s="16" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B298" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C298" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D298" s="13" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E298" s="13" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F298" s="13" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G298" s="13" t="inlineStr"/>
+      <c r="H298" s="13" t="inlineStr"/>
+      <c r="I298" s="13" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B299" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C299" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D299" s="16" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E299" s="16" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F299" s="16" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G299" s="16" t="inlineStr"/>
+      <c r="H299" s="16" t="inlineStr"/>
+      <c r="I299" s="16" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="13" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B289" s="17" t="inlineStr">
+      <c r="B300" s="14" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C289" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D289" s="16" t="inlineStr">
+      <c r="C300" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D300" s="13" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E289" s="16" t="inlineStr">
+      <c r="E300" s="13" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -11868,37 +12253,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F289" s="16" t="inlineStr">
+      <c r="F300" s="13" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G289" s="16" t="inlineStr"/>
-      <c r="H289" s="16" t="inlineStr"/>
-      <c r="I289" s="16" t="inlineStr"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="13" t="inlineStr">
+      <c r="G300" s="13" t="inlineStr"/>
+      <c r="H300" s="13" t="inlineStr"/>
+      <c r="I300" s="13" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B290" s="14" t="inlineStr">
+      <c r="B301" s="17" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C290" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D290" s="13" t="inlineStr">
+      <c r="C301" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D301" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E290" s="13" t="inlineStr">
+      <c r="E301" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -11910,37 +12295,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F290" s="13" t="inlineStr">
+      <c r="F301" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G290" s="13" t="inlineStr"/>
-      <c r="H290" s="13" t="inlineStr"/>
-      <c r="I290" s="13" t="inlineStr"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="16" t="inlineStr">
+      <c r="G301" s="16" t="inlineStr"/>
+      <c r="H301" s="16" t="inlineStr"/>
+      <c r="I301" s="16" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B291" s="17" t="inlineStr">
+      <c r="B302" s="14" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C291" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D291" s="16" t="inlineStr">
+      <c r="C302" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D302" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E291" s="16" t="inlineStr">
+      <c r="E302" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -11952,74 +12337,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F291" s="16" t="inlineStr">
+      <c r="F302" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G291" s="16" t="inlineStr"/>
-      <c r="H291" s="16" t="inlineStr"/>
-      <c r="I291" s="16" t="inlineStr"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="13" t="inlineStr">
+      <c r="G302" s="13" t="inlineStr"/>
+      <c r="H302" s="13" t="inlineStr"/>
+      <c r="I302" s="13" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B292" s="14" t="inlineStr">
+      <c r="B303" s="17" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C292" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D292" s="13" t="inlineStr">
+      <c r="C303" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D303" s="16" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E292" s="13" t="inlineStr">
+      <c r="E303" s="16" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F292" s="13" t="inlineStr">
+      <c r="F303" s="16" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G292" s="13" t="inlineStr"/>
-      <c r="H292" s="13" t="inlineStr"/>
-      <c r="I292" s="13" t="inlineStr"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="16" t="inlineStr">
+      <c r="G303" s="16" t="inlineStr"/>
+      <c r="H303" s="16" t="inlineStr"/>
+      <c r="I303" s="16" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B293" s="17" t="inlineStr">
+      <c r="B304" s="14" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C293" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D293" s="16" t="inlineStr">
+      <c r="C304" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D304" s="13" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E293" s="16" t="inlineStr">
+      <c r="E304" s="13" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -12030,73 +12415,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F293" s="16" t="inlineStr">
+      <c r="F304" s="13" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G293" s="16" t="inlineStr"/>
-      <c r="H293" s="16" t="inlineStr"/>
-      <c r="I293" s="16" t="inlineStr"/>
-    </row>
-    <row r="294">
-      <c r="A294" s="13" t="inlineStr">
+      <c r="G304" s="13" t="inlineStr"/>
+      <c r="H304" s="13" t="inlineStr"/>
+      <c r="I304" s="13" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B294" s="14" t="inlineStr">
+      <c r="B305" s="17" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C294" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D294" s="13" t="inlineStr">
+      <c r="C305" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D305" s="16" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E294" s="13" t="inlineStr">
+      <c r="E305" s="16" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F294" s="13" t="inlineStr">
+      <c r="F305" s="16" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G294" s="13" t="inlineStr"/>
-      <c r="H294" s="13" t="inlineStr"/>
-      <c r="I294" s="13" t="inlineStr"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="16" t="inlineStr">
+      <c r="G305" s="16" t="inlineStr"/>
+      <c r="H305" s="16" t="inlineStr"/>
+      <c r="I305" s="16" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B295" s="17" t="inlineStr">
+      <c r="B306" s="14" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C295" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D295" s="16" t="inlineStr">
+      <c r="C306" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D306" s="13" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E295" s="16" t="inlineStr">
+      <c r="E306" s="13" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -12107,37 +12492,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F295" s="16" t="inlineStr">
+      <c r="F306" s="13" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G295" s="16" t="inlineStr"/>
-      <c r="H295" s="16" t="inlineStr"/>
-      <c r="I295" s="16" t="inlineStr"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="13" t="inlineStr">
+      <c r="G306" s="13" t="inlineStr"/>
+      <c r="H306" s="13" t="inlineStr"/>
+      <c r="I306" s="13" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B296" s="14" t="inlineStr">
+      <c r="B307" s="17" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C296" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D296" s="13" t="inlineStr">
+      <c r="C307" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D307" s="16" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E296" s="13" t="inlineStr">
+      <c r="E307" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -12147,37 +12532,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F296" s="13" t="inlineStr">
+      <c r="F307" s="16" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G296" s="13" t="inlineStr"/>
-      <c r="H296" s="13" t="inlineStr"/>
-      <c r="I296" s="13" t="inlineStr"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="16" t="inlineStr">
+      <c r="G307" s="16" t="inlineStr"/>
+      <c r="H307" s="16" t="inlineStr"/>
+      <c r="I307" s="16" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B297" s="17" t="inlineStr">
+      <c r="B308" s="14" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C297" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D297" s="16" t="inlineStr">
+      <c r="C308" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D308" s="13" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E297" s="16" t="inlineStr">
+      <c r="E308" s="13" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -12185,19 +12570,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F297" s="16" t="inlineStr">
+      <c r="F308" s="13" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G297" s="16" t="inlineStr"/>
-      <c r="H297" s="16" t="inlineStr"/>
-      <c r="I297" s="16" t="inlineStr"/>
+      <c r="G308" s="13" t="inlineStr"/>
+      <c r="H308" s="13" t="inlineStr"/>
+      <c r="I308" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I297"/>
+  <autoFilter ref="A1:I308"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G297" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G308" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$324</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C308,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C324,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P1",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P1",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P1",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P1",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P1",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P1",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P1",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P1",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C308,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C324,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P2",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P2",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P2",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P2",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P2",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P2",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P2",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P2",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C308,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C324,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P3",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P3",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P3",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P3",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P3",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P3",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C308,"P3",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C324,"P3",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pelanggan",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pelanggan",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pelanggan",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pelanggan",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pelanggan",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pelanggan",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pelanggan",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pelanggan",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kasir",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kasir",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kasir",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kasir",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kasir",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kasir",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kasir",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kasir",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pending Payment",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pending Payment",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pending Payment",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pending Payment",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pending Payment",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pending Payment",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pending Payment",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pending Payment",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Dapur",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Dapur",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Dapur",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Dapur",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Dapur",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Dapur",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Dapur",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Dapur",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Keuangan",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Keuangan",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Keuangan",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Keuangan",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Keuangan",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Keuangan",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Keuangan",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Keuangan",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Setor Saldo Cash",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Setor Saldo Cash",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Setor Saldo Cash",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Setor Saldo Cash",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Setor Saldo Cash",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Setor Saldo Cash",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Setor Saldo Cash",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Setor Saldo Cash",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"QR Meja",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"QR Meja",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"QR Meja",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"QR Meja",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"QR Meja",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"QR Meja",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"QR Meja",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"QR Meja",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Diskon",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Diskon",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Diskon",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Diskon",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Diskon",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Diskon",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Diskon",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Diskon",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembayaran QRIS",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembayaran QRIS",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembayaran QRIS",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembayaran QRIS",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembayaran QRIS",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembayaran QRIS",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembayaran QRIS",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembayaran QRIS",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Tampilan",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Tampilan",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Tampilan",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Tampilan",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Tampilan",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Tampilan",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Tampilan",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Tampilan",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Super Admin",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Super Admin",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Super Admin",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Super Admin",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Super Admin",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Super Admin",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Super Admin",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Super Admin",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembaruan Aplikasi",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembaruan Aplikasi",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembaruan Aplikasi",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembaruan Aplikasi",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembaruan Aplikasi",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembaruan Aplikasi",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Pembaruan Aplikasi",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembaruan Aplikasi",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G308,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G324,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G308,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G324,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G308,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G324,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A308,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G308,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G324,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1727,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I308"/>
+  <dimension ref="A1:I324"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10021,27 +10021,27 @@
       </c>
       <c r="B237" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-15</t>
-        </is>
-      </c>
-      <c r="C237" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-26</t>
+        </is>
+      </c>
+      <c r="C237" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D237" s="16" t="inlineStr">
         <is>
-          <t>Coba kirim bukti tanpa melampirkan foto</t>
+          <t>Dengan kunci uji Xendit, buka tagihan ber-VA</t>
         </is>
       </c>
       <c r="E237" s="16" t="inlineStr">
         <is>
-          <t>Tombol Kirim mati</t>
+          <t>Tombol Simulasikan Pembayaran muncul</t>
         </is>
       </c>
       <c r="F237" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G237" s="16" t="inlineStr"/>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="B238" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-16</t>
+          <t>TC-BL-27</t>
         </is>
       </c>
       <c r="C238" s="15" t="inlineStr">
@@ -10066,17 +10066,17 @@
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → tab Tagihan → Terima</t>
+          <t>Ketuk Simulasikan Pembayaran</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
+          <t>Tagihan jadi Lunas sendiri lewat webhook; kunci resto terbuka</t>
         </is>
       </c>
       <c r="F238" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr"/>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="B239" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-17</t>
+          <t>TC-BL-28</t>
         </is>
       </c>
       <c r="C239" s="18" t="inlineStr">
@@ -10101,17 +10101,17 @@
       </c>
       <c r="D239" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Tolak tanpa mengisi alasan</t>
+          <t>Pasang kunci produksi Xendit, buka layar yang sama</t>
         </is>
       </c>
       <c r="E239" s="16" t="inlineStr">
         <is>
-          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
+          <t>Tombol simulasi hilang sendiri</t>
         </is>
       </c>
       <c r="F239" s="16" t="inlineStr">
         <is>
-          <t>F-BL-14</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G239" s="16" t="inlineStr"/>
@@ -10126,7 +10126,7 @@
       </c>
       <c r="B240" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-18</t>
+          <t>TC-BL-29</t>
         </is>
       </c>
       <c r="C240" s="15" t="inlineStr">
@@ -10136,17 +10136,17 @@
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
+          <t>Buat diskon langganan setelah tagihan terbit → ketuk segarkan di Super Admin</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
+          <t>Nominal tagihan turun; nomor VA lama dibuang</t>
         </is>
       </c>
       <c r="F240" s="13" t="inlineStr">
         <is>
-          <t>F-BL-14, F-BL-15</t>
+          <t>F-BL-05</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr"/>
@@ -10161,7 +10161,7 @@
       </c>
       <c r="B241" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-19</t>
+          <t>TC-BL-30</t>
         </is>
       </c>
       <c r="C241" s="18" t="inlineStr">
@@ -10171,17 +10171,17 @@
       </c>
       <c r="D241" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Super Admin saat ada resto terkunci</t>
+          <t>Buat VA baru setelah nominalnya berubah</t>
         </is>
       </c>
       <c r="E241" s="16" t="inlineStr">
         <is>
-          <t>Tidak terkunci sama sekali</t>
+          <t>Nominalnya sesuai yang sudah dipotong</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>F-BL-17</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G241" s="16" t="inlineStr"/>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="B242" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-20</t>
+          <t>TC-BL-15</t>
         </is>
       </c>
       <c r="C242" s="15" t="inlineStr">
@@ -10206,17 +10206,17 @@
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>Sebagai resto terkunci, coba ubah harga produk</t>
+          <t>Coba kirim bukti tanpa melampirkan foto</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — katalog ikut dibekukan</t>
+          <t>Tombol Kirim mati</t>
         </is>
       </c>
       <c r="F242" s="13" t="inlineStr">
         <is>
-          <t>F-BL-18</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="B243" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-21</t>
+          <t>TC-BL-16</t>
         </is>
       </c>
       <c r="C243" s="18" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="D243" s="16" t="inlineStr">
         <is>
-          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
+          <t>Super Admin → tab Tagihan → Terima</t>
         </is>
       </c>
       <c r="E243" s="16" t="inlineStr">
         <is>
-          <t>Resto B tidak terpengaruh</t>
+          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
         </is>
       </c>
       <c r="F243" s="16" t="inlineStr">
         <is>
-          <t>F-BL-15, A-10</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G243" s="16" t="inlineStr"/>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="B244" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-22</t>
+          <t>TC-BL-17</t>
         </is>
       </c>
       <c r="C244" s="15" t="inlineStr">
@@ -10276,17 +10276,17 @@
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
+          <t>Super Admin → Tolak tanpa mengisi alasan</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — hanya Super Admin</t>
+          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
         </is>
       </c>
       <c r="F244" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-14</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr"/>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="B245" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-23</t>
+          <t>TC-BL-18</t>
         </is>
       </c>
       <c r="C245" s="18" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="D245" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
+          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
         </is>
       </c>
       <c r="E245" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
         </is>
       </c>
       <c r="F245" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13, TSD §7.3</t>
+          <t>F-BL-14, F-BL-15</t>
         </is>
       </c>
       <c r="G245" s="16" t="inlineStr"/>
@@ -10336,27 +10336,27 @@
       </c>
       <c r="B246" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-24</t>
-        </is>
-      </c>
-      <c r="C246" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-19</t>
+        </is>
+      </c>
+      <c r="C246" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
+          <t>Login sebagai Super Admin saat ada resto terkunci</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Tidak terkunci karena gagal memeriksa</t>
+          <t>Tidak terkunci sama sekali</t>
         </is>
       </c>
       <c r="F246" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-17</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr"/>
@@ -10371,27 +10371,27 @@
       </c>
       <c r="B247" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-25</t>
-        </is>
-      </c>
-      <c r="C247" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-20</t>
+        </is>
+      </c>
+      <c r="C247" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D247" s="16" t="inlineStr">
         <is>
-          <t>Owner → Tagihan Langganan</t>
+          <t>Sebagai resto terkunci, coba ubah harga produk</t>
         </is>
       </c>
       <c r="E247" s="16" t="inlineStr">
         <is>
-          <t>Terbuka, memuat paket dan riwayat tagihan</t>
+          <t>Ditolak — katalog ikut dibekukan</t>
         </is>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-18</t>
         </is>
       </c>
       <c r="G247" s="16" t="inlineStr"/>
@@ -10401,12 +10401,12 @@
     <row r="248">
       <c r="A248" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B248" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-01</t>
+          <t>TC-BL-21</t>
         </is>
       </c>
       <c r="C248" s="15" t="inlineStr">
@@ -10416,17 +10416,17 @@
       </c>
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Riwayat Langganan</t>
+          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
+          <t>Resto B tidak terpengaruh</t>
         </is>
       </c>
       <c r="F248" s="13" t="inlineStr">
         <is>
-          <t>F-PF-01</t>
+          <t>F-BL-15, A-10</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr"/>
@@ -10436,32 +10436,32 @@
     <row r="249">
       <c r="A249" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B249" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-02</t>
-        </is>
-      </c>
-      <c r="C249" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-22</t>
+        </is>
+      </c>
+      <c r="C249" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D249" s="16" t="inlineStr">
         <is>
-          <t>Periksa penanda jalur pelunasan tiap baris</t>
+          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
         </is>
       </c>
       <c r="E249" s="16" t="inlineStr">
         <is>
-          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F249" s="16" t="inlineStr">
         <is>
-          <t>F-PF-02</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G249" s="16" t="inlineStr"/>
@@ -10471,12 +10471,12 @@
     <row r="250">
       <c r="A250" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B250" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-03</t>
+          <t>TC-BL-23</t>
         </is>
       </c>
       <c r="C250" s="15" t="inlineStr">
@@ -10486,17 +10486,17 @@
       </c>
       <c r="D250" s="13" t="inlineStr">
         <is>
-          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
+          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F250" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03, F-PF-05</t>
+          <t>F-BL-13, TSD §7.3</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr"/>
@@ -10506,32 +10506,32 @@
     <row r="251">
       <c r="A251" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B251" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-04</t>
-        </is>
-      </c>
-      <c r="C251" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-24</t>
+        </is>
+      </c>
+      <c r="C251" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D251" s="16" t="inlineStr">
         <is>
-          <t>Simpan diskon tanpa memilih resto</t>
+          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
         </is>
       </c>
       <c r="E251" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
+          <t>Tidak terkunci karena gagal memeriksa</t>
         </is>
       </c>
       <c r="F251" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G251" s="16" t="inlineStr"/>
@@ -10541,12 +10541,12 @@
     <row r="252">
       <c r="A252" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B252" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-05</t>
+          <t>TC-BL-25</t>
         </is>
       </c>
       <c r="C252" s="19" t="inlineStr">
@@ -10556,17 +10556,17 @@
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
+          <t>Owner → Tagihan Langganan</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
+          <t>Terbuka, memuat paket dan riwayat tagihan</t>
         </is>
       </c>
       <c r="F252" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr"/>
@@ -10581,27 +10581,27 @@
       </c>
       <c r="B253" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-06</t>
-        </is>
-      </c>
-      <c r="C253" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-01</t>
+        </is>
+      </c>
+      <c r="C253" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D253" s="16" t="inlineStr">
         <is>
-          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
+          <t>Super Admin → Finance → Riwayat Langganan</t>
         </is>
       </c>
       <c r="E253" s="16" t="inlineStr">
         <is>
-          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
+          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
         </is>
       </c>
       <c r="F253" s="16" t="inlineStr">
         <is>
-          <t>F-PF-04</t>
+          <t>F-PF-01</t>
         </is>
       </c>
       <c r="G253" s="16" t="inlineStr"/>
@@ -10616,27 +10616,27 @@
       </c>
       <c r="B254" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-07</t>
-        </is>
-      </c>
-      <c r="C254" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-02</t>
+        </is>
+      </c>
+      <c r="C254" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>Hapus diskon setelah tagihan terbit</t>
+          <t>Periksa penanda jalur pelunasan tiap baris</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
+          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
         </is>
       </c>
       <c r="F254" s="13" t="inlineStr">
         <is>
-          <t>F-PF-05</t>
+          <t>F-PF-02</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr"/>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="B255" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-08</t>
+          <t>TC-PF-03</t>
         </is>
       </c>
       <c r="C255" s="18" t="inlineStr">
@@ -10661,17 +10661,17 @@
       </c>
       <c r="D255" s="16" t="inlineStr">
         <is>
-          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
+          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
         </is>
       </c>
       <c r="E255" s="16" t="inlineStr">
         <is>
-          <t>Dua baris: pendapatan kredit, diskon debit</t>
+          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
         </is>
       </c>
       <c r="F255" s="16" t="inlineStr">
         <is>
-          <t>F-PF-06, F-PF-07</t>
+          <t>F-PF-03, F-PF-05</t>
         </is>
       </c>
       <c r="G255" s="16" t="inlineStr"/>
@@ -10686,7 +10686,7 @@
       </c>
       <c r="B256" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-09</t>
+          <t>TC-PF-04</t>
         </is>
       </c>
       <c r="C256" s="15" t="inlineStr">
@@ -10696,17 +10696,17 @@
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>Tagihan ditolak lalu diterima lagi</t>
+          <t>Simpan diskon tanpa memilih resto</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
+          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
         </is>
       </c>
       <c r="F256" s="13" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr"/>
@@ -10721,27 +10721,27 @@
       </c>
       <c r="B257" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-10</t>
-        </is>
-      </c>
-      <c r="C257" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-05</t>
+        </is>
+      </c>
+      <c r="C257" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D257" s="16" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL resto yang membayar</t>
+          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
         </is>
       </c>
       <c r="E257" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada baris pendapatan langganan di sana</t>
+          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
         </is>
       </c>
       <c r="F257" s="16" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G257" s="16" t="inlineStr"/>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B258" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-11</t>
+          <t>TC-PF-06</t>
         </is>
       </c>
       <c r="C258" s="19" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account KaataGo</t>
+          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
+          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
         </is>
       </c>
       <c r="F258" s="13" t="inlineStr">
         <is>
-          <t>F-PF-08</t>
+          <t>F-PF-04</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr"/>
@@ -10791,27 +10791,27 @@
       </c>
       <c r="B259" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-12</t>
-        </is>
-      </c>
-      <c r="C259" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-07</t>
+        </is>
+      </c>
+      <c r="C259" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D259" s="16" t="inlineStr">
         <is>
-          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
+          <t>Hapus diskon setelah tagihan terbit</t>
         </is>
       </c>
       <c r="E259" s="16" t="inlineStr">
         <is>
-          <t>Bekerja sama seperti di resto</t>
+          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
         </is>
       </c>
       <c r="F259" s="16" t="inlineStr">
         <is>
-          <t>F-PF-09</t>
+          <t>F-PF-05</t>
         </is>
       </c>
       <c r="G259" s="16" t="inlineStr"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="B260" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-13</t>
+          <t>TC-PF-08</t>
         </is>
       </c>
       <c r="C260" s="15" t="inlineStr">
@@ -10836,17 +10836,17 @@
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>Telusuri menu Finance KaataGo</t>
+          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada Setor Saldo Cash</t>
+          <t>Dua baris: pendapatan kredit, diskon debit</t>
         </is>
       </c>
       <c r="F260" s="13" t="inlineStr">
         <is>
-          <t>F-PF-10</t>
+          <t>F-PF-06, F-PF-07</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr"/>
@@ -10861,7 +10861,7 @@
       </c>
       <c r="B261" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-14</t>
+          <t>TC-PF-09</t>
         </is>
       </c>
       <c r="C261" s="18" t="inlineStr">
@@ -10871,17 +10871,17 @@
       </c>
       <c r="D261" s="16" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL Semua Resto</t>
+          <t>Tagihan ditolak lalu diterima lagi</t>
         </is>
       </c>
       <c r="E261" s="16" t="inlineStr">
         <is>
-          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
+          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
         </is>
       </c>
       <c r="F261" s="16" t="inlineStr">
         <is>
-          <t>F-PF-11</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G261" s="16" t="inlineStr"/>
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B262" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-15</t>
+          <t>TC-PF-10</t>
         </is>
       </c>
       <c r="C262" s="15" t="inlineStr">
@@ -10906,17 +10906,17 @@
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
+          <t>Buka Jurnal GL resto yang membayar</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun — hanya bisa dilihat</t>
+          <t>Tidak ada baris pendapatan langganan di sana</t>
         </is>
       </c>
       <c r="F262" s="13" t="inlineStr">
         <is>
-          <t>F-PF-12</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr"/>
@@ -10931,27 +10931,27 @@
       </c>
       <c r="B263" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-16</t>
-        </is>
-      </c>
-      <c r="C263" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-11</t>
+        </is>
+      </c>
+      <c r="C263" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D263" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E263" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F263" s="16" t="inlineStr">
         <is>
-          <t>F-PF-12, TSD §7.4</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G263" s="16" t="inlineStr"/>
@@ -10966,27 +10966,27 @@
       </c>
       <c r="B264" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-17</t>
-        </is>
-      </c>
-      <c r="C264" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-12</t>
+        </is>
+      </c>
+      <c r="C264" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>Buka Pilih Resto sebagai pelanggan</t>
+          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul di daftar mana pun</t>
+          <t>Bekerja sama seperti di resto</t>
         </is>
       </c>
       <c r="F264" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-09</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B265" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-18</t>
+          <t>TC-PF-13</t>
         </is>
       </c>
       <c r="C265" s="18" t="inlineStr">
@@ -11011,17 +11011,17 @@
       </c>
       <c r="D265" s="16" t="inlineStr">
         <is>
-          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
+          <t>Telusuri menu Finance KaataGo</t>
         </is>
       </c>
       <c r="E265" s="16" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
+          <t>Tidak ada Setor Saldo Cash</t>
         </is>
       </c>
       <c r="F265" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-10</t>
         </is>
       </c>
       <c r="G265" s="16" t="inlineStr"/>
@@ -11036,27 +11036,27 @@
       </c>
       <c r="B266" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-19</t>
-        </is>
-      </c>
-      <c r="C266" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-14</t>
+        </is>
+      </c>
+      <c r="C266" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>Buka Diskon Langganan sebagai Owner resto</t>
+          <t>Buka Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
+          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
         </is>
       </c>
       <c r="F266" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-PF-11</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr"/>
@@ -11066,12 +11066,12 @@
     <row r="267">
       <c r="A267" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B267" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-PF-15</t>
         </is>
       </c>
       <c r="C267" s="18" t="inlineStr">
@@ -11081,17 +11081,17 @@
       </c>
       <c r="D267" s="16" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E267" s="16" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Tidak ada satu pun — hanya bisa dilihat</t>
         </is>
       </c>
       <c r="F267" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-12</t>
         </is>
       </c>
       <c r="G267" s="16" t="inlineStr"/>
@@ -11101,12 +11101,12 @@
     <row r="268">
       <c r="A268" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B268" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-PF-16</t>
         </is>
       </c>
       <c r="C268" s="15" t="inlineStr">
@@ -11116,17 +11116,17 @@
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F268" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-12, TSD §7.4</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr"/>
@@ -11136,12 +11136,12 @@
     <row r="269">
       <c r="A269" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B269" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-PF-17</t>
         </is>
       </c>
       <c r="C269" s="18" t="inlineStr">
@@ -11151,17 +11151,17 @@
       </c>
       <c r="D269" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Buka Pilih Resto sebagai pelanggan</t>
         </is>
       </c>
       <c r="E269" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>KaataGo tidak muncul di daftar mana pun</t>
         </is>
       </c>
       <c r="F269" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G269" s="16" t="inlineStr"/>
@@ -11171,12 +11171,12 @@
     <row r="270">
       <c r="A270" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B270" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
+          <t>TC-PF-18</t>
         </is>
       </c>
       <c r="C270" s="15" t="inlineStr">
@@ -11186,17 +11186,17 @@
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
         </is>
       </c>
       <c r="F270" s="13" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr"/>
@@ -11206,32 +11206,32 @@
     <row r="271">
       <c r="A271" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B271" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
-        </is>
-      </c>
-      <c r="C271" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-19</t>
+        </is>
+      </c>
+      <c r="C271" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D271" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Buka Diskon Langganan sebagai Owner resto</t>
         </is>
       </c>
       <c r="E271" s="16" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
         </is>
       </c>
       <c r="F271" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G271" s="16" t="inlineStr"/>
@@ -11241,12 +11241,12 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B272" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-PF-20</t>
         </is>
       </c>
       <c r="C272" s="15" t="inlineStr">
@@ -11256,17 +11256,17 @@
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Bandingkan total debit/kredit Jurnal Semua Resto dengan Jurnal GL resto itu (saring ke resto yang sama)</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Angkanya sama persis</t>
         </is>
       </c>
       <c r="F272" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-PF-14</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr"/>
@@ -11276,12 +11276,12 @@
     <row r="273">
       <c r="A273" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B273" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-PF-21</t>
         </is>
       </c>
       <c r="C273" s="18" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Batalkan sebuah pengeluaran, lihat kedua layar jurnal</t>
         </is>
       </c>
       <c r="E273" s="16" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Total tidak naik; keterangan "N pembatalan tidak dihitung" muncul</t>
         </is>
       </c>
       <c r="F273" s="16" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-PF-14</t>
         </is>
       </c>
       <c r="G273" s="16" t="inlineStr"/>
@@ -11311,32 +11311,32 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B274" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
-        </is>
-      </c>
-      <c r="C274" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-22</t>
+        </is>
+      </c>
+      <c r="C274" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Cari baris pembatalan di daftar</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Tetap tampil, bertanda PEMBATALAN</t>
         </is>
       </c>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-PF-15</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr"/>
@@ -11346,12 +11346,12 @@
     <row r="275">
       <c r="A275" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B275" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-PF-23</t>
         </is>
       </c>
       <c r="C275" s="18" t="inlineStr">
@@ -11361,17 +11361,17 @@
       </c>
       <c r="D275" s="16" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Saring ke sebuah resto, lalu pilih Semua resto lagi</t>
         </is>
       </c>
       <c r="E275" s="16" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Kembali menampilkan seluruh resto — bukan tetap tersaring</t>
         </is>
       </c>
       <c r="F275" s="16" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G275" s="16" t="inlineStr"/>
@@ -11381,12 +11381,12 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B276" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-PF-24</t>
         </is>
       </c>
       <c r="C276" s="15" t="inlineStr">
@@ -11396,17 +11396,17 @@
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Saring ke resto A, lalu saring lagi ke resto B yang punya jurnal</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Isinya berganti ke jurnal resto B</t>
         </is>
       </c>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr"/>
@@ -11416,12 +11416,12 @@
     <row r="277">
       <c r="A277" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B277" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
+          <t>TC-PF-25</t>
         </is>
       </c>
       <c r="C277" s="20" t="inlineStr">
@@ -11431,17 +11431,17 @@
       </c>
       <c r="D277" s="16" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Perhatikan pita di atas layar sesudah menyaring</t>
         </is>
       </c>
       <c r="E277" s="16" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Nama restonya tertulis, dengan tombol × untuk melepasnya</t>
         </is>
       </c>
       <c r="F277" s="16" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G277" s="16" t="inlineStr"/>
@@ -11451,12 +11451,12 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B278" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
+          <t>TC-PF-26</t>
         </is>
       </c>
       <c r="C278" s="19" t="inlineStr">
@@ -11466,17 +11466,17 @@
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Buka daftar saringan</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Resto yang belum punya jurnal ditandai "Belum ada jurnal"</t>
         </is>
       </c>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>F-PF-17</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr"/>
@@ -11486,12 +11486,12 @@
     <row r="279">
       <c r="A279" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B279" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
+          <t>TC-PF-27</t>
         </is>
       </c>
       <c r="C279" s="20" t="inlineStr">
@@ -11501,17 +11501,17 @@
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Perhatikan pengelompokan</t>
         </is>
       </c>
       <c r="E279" s="16" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Per tanggal, bisa dilipat; tanggal terbaru terbuka, sisanya tertutup</t>
         </is>
       </c>
       <c r="F279" s="16" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>F-PF-18</t>
         </is>
       </c>
       <c r="G279" s="16" t="inlineStr"/>
@@ -11521,12 +11521,12 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B280" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-PF-28</t>
         </is>
       </c>
       <c r="C280" s="15" t="inlineStr">
@@ -11536,17 +11536,17 @@
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Buka Mapping GL Account resto mana pun</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>GL Diskon punya bagiannya dan nomornya sudah terisi</t>
         </is>
       </c>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>F-PF-19, F-DS-09</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr"/>
@@ -11556,32 +11556,32 @@
     <row r="281">
       <c r="A281" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B281" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
-        </is>
-      </c>
-      <c r="C281" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-29</t>
+        </is>
+      </c>
+      <c r="C281" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D281" s="16" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E281" s="16" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Ada bagian GL Langganan; penghitung akun tidak pernah menyisakan yang mustahil terisi</t>
         </is>
       </c>
       <c r="F281" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>F-PF-19</t>
         </is>
       </c>
       <c r="G281" s="16" t="inlineStr"/>
@@ -11591,12 +11591,12 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B282" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-PF-30</t>
         </is>
       </c>
       <c r="C282" s="15" t="inlineStr">
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Pesan menu berpromo, bayar, buka Jurnal GL</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Baris GL Diskon menyebut nama promonya</t>
         </is>
       </c>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>F-PF-20, F-DS-13</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr"/>
@@ -11631,27 +11631,27 @@
       </c>
       <c r="B283" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C283" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-01</t>
+        </is>
+      </c>
+      <c r="C283" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D283" s="16" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E283" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F283" s="16" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G283" s="16" t="inlineStr"/>
@@ -11666,27 +11666,27 @@
       </c>
       <c r="B284" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C284" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-02</t>
+        </is>
+      </c>
+      <c r="C284" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr"/>
@@ -11701,27 +11701,27 @@
       </c>
       <c r="B285" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C285" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-03</t>
+        </is>
+      </c>
+      <c r="C285" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D285" s="16" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E285" s="16" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F285" s="16" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G285" s="16" t="inlineStr"/>
@@ -11731,12 +11731,12 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
+          <t>TC-TS-04</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
@@ -11746,17 +11746,17 @@
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr"/>
@@ -11766,12 +11766,12 @@
     <row r="287">
       <c r="A287" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B287" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
+          <t>TC-TS-05</t>
         </is>
       </c>
       <c r="C287" s="18" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="D287" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E287" s="16" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F287" s="16" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G287" s="16" t="inlineStr"/>
@@ -11801,12 +11801,12 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B288" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C288" s="15" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr"/>
@@ -11836,12 +11836,12 @@
     <row r="289">
       <c r="A289" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B289" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
+          <t>TC-TS-07</t>
         </is>
       </c>
       <c r="C289" s="18" t="inlineStr">
@@ -11851,17 +11851,17 @@
       </c>
       <c r="D289" s="16" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E289" s="16" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F289" s="16" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G289" s="16" t="inlineStr"/>
@@ -11871,12 +11871,12 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B290" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-TS-08</t>
         </is>
       </c>
       <c r="C290" s="15" t="inlineStr">
@@ -11886,17 +11886,17 @@
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr"/>
@@ -11906,12 +11906,12 @@
     <row r="291">
       <c r="A291" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B291" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-TS-09</t>
         </is>
       </c>
       <c r="C291" s="18" t="inlineStr">
@@ -11921,17 +11921,17 @@
       </c>
       <c r="D291" s="16" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E291" s="16" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F291" s="16" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G291" s="16" t="inlineStr"/>
@@ -11941,32 +11941,32 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B292" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C292" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C292" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr"/>
@@ -11976,12 +11976,12 @@
     <row r="293">
       <c r="A293" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B293" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
+          <t>TC-TS-11</t>
         </is>
       </c>
       <c r="C293" s="20" t="inlineStr">
@@ -11991,17 +11991,17 @@
       </c>
       <c r="D293" s="16" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E293" s="16" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F293" s="16" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G293" s="16" t="inlineStr"/>
@@ -12011,12 +12011,12 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B294" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
+          <t>TC-TS-12</t>
         </is>
       </c>
       <c r="C294" s="19" t="inlineStr">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr"/>
@@ -12046,12 +12046,12 @@
     <row r="295">
       <c r="A295" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B295" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
+          <t>TC-TS-13</t>
         </is>
       </c>
       <c r="C295" s="20" t="inlineStr">
@@ -12061,17 +12061,17 @@
       </c>
       <c r="D295" s="16" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E295" s="16" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F295" s="16" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G295" s="16" t="inlineStr"/>
@@ -12081,32 +12081,32 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B296" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
-        </is>
-      </c>
-      <c r="C296" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-14</t>
+        </is>
+      </c>
+      <c r="C296" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr"/>
@@ -12116,32 +12116,32 @@
     <row r="297">
       <c r="A297" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B297" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
-        </is>
-      </c>
-      <c r="C297" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C297" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D297" s="16" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E297" s="16" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F297" s="16" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G297" s="16" t="inlineStr"/>
@@ -12151,12 +12151,12 @@
     <row r="298">
       <c r="A298" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B298" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
+          <t>TC-TS-16</t>
         </is>
       </c>
       <c r="C298" s="15" t="inlineStr">
@@ -12166,17 +12166,17 @@
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
         </is>
       </c>
       <c r="E298" s="13" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-PG-02, TSD §7.1</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr"/>
@@ -12186,12 +12186,12 @@
     <row r="299">
       <c r="A299" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B299" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
+          <t>TC-TS-17</t>
         </is>
       </c>
       <c r="C299" s="20" t="inlineStr">
@@ -12201,17 +12201,17 @@
       </c>
       <c r="D299" s="16" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
         </is>
       </c>
       <c r="E299" s="16" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
         </is>
       </c>
       <c r="F299" s="16" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>TSD §1.2</t>
         </is>
       </c>
       <c r="G299" s="16" t="inlineStr"/>
@@ -12221,25 +12221,585 @@
     <row r="300">
       <c r="A300" s="13" t="inlineStr">
         <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B300" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C300" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D300" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+        </is>
+      </c>
+      <c r="E300" s="13" t="inlineStr">
+        <is>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+        </is>
+      </c>
+      <c r="F300" s="13" t="inlineStr">
+        <is>
+          <t>TSD §6.5</t>
+        </is>
+      </c>
+      <c r="G300" s="13" t="inlineStr"/>
+      <c r="H300" s="13" t="inlineStr"/>
+      <c r="I300" s="13" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B301" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C301" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D301" s="16" t="inlineStr">
+        <is>
+          <t>Hapus resto uji</t>
+        </is>
+      </c>
+      <c r="E301" s="16" t="inlineStr">
+        <is>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+        </is>
+      </c>
+      <c r="F301" s="16" t="inlineStr">
+        <is>
+          <t>TSD §4.0</t>
+        </is>
+      </c>
+      <c r="G301" s="16" t="inlineStr"/>
+      <c r="H301" s="16" t="inlineStr"/>
+      <c r="I301" s="16" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B302" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C302" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D302" s="13" t="inlineStr">
+        <is>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+        </is>
+      </c>
+      <c r="E302" s="13" t="inlineStr">
+        <is>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+        </is>
+      </c>
+      <c r="F302" s="13" t="inlineStr">
+        <is>
+          <t>F-KS-09</t>
+        </is>
+      </c>
+      <c r="G302" s="13" t="inlineStr"/>
+      <c r="H302" s="13" t="inlineStr"/>
+      <c r="I302" s="13" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B303" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C303" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D303" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="E303" s="16" t="inlineStr">
+        <is>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="F303" s="16" t="inlineStr">
+        <is>
+          <t>F-PP-09, A-13</t>
+        </is>
+      </c>
+      <c r="G303" s="16" t="inlineStr"/>
+      <c r="H303" s="16" t="inlineStr"/>
+      <c r="I303" s="16" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B304" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C304" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D304" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+        </is>
+      </c>
+      <c r="E304" s="13" t="inlineStr">
+        <is>
+          <t>Tidak muncul sama sekali</t>
+        </is>
+      </c>
+      <c r="F304" s="13" t="inlineStr">
+        <is>
+          <t>A-17</t>
+        </is>
+      </c>
+      <c r="G304" s="13" t="inlineStr"/>
+      <c r="H304" s="13" t="inlineStr"/>
+      <c r="I304" s="13" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B305" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C305" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D305" s="16" t="inlineStr">
+        <is>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+        </is>
+      </c>
+      <c r="E305" s="16" t="inlineStr">
+        <is>
+          <t>Nominalnya sama dengan yang diajukan</t>
+        </is>
+      </c>
+      <c r="F305" s="16" t="inlineStr">
+        <is>
+          <t>F-FN-03</t>
+        </is>
+      </c>
+      <c r="G305" s="16" t="inlineStr"/>
+      <c r="H305" s="16" t="inlineStr"/>
+      <c r="I305" s="16" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B306" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C306" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D306" s="13" t="inlineStr">
+        <is>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+        </is>
+      </c>
+      <c r="E306" s="13" t="inlineStr">
+        <is>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
+        </is>
+      </c>
+      <c r="F306" s="13" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="G306" s="13" t="inlineStr"/>
+      <c r="H306" s="13" t="inlineStr"/>
+      <c r="I306" s="13" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B307" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C307" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D307" s="16" t="inlineStr">
+        <is>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+        </is>
+      </c>
+      <c r="E307" s="16" t="inlineStr">
+        <is>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+        </is>
+      </c>
+      <c r="F307" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-10, F-DS-12</t>
+        </is>
+      </c>
+      <c r="G307" s="16" t="inlineStr"/>
+      <c r="H307" s="16" t="inlineStr"/>
+      <c r="I307" s="16" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B308" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C308" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D308" s="13" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E308" s="13" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F308" s="13" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G308" s="13" t="inlineStr"/>
+      <c r="H308" s="13" t="inlineStr"/>
+      <c r="I308" s="13" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B309" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C309" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D309" s="16" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E309" s="16" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F309" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G309" s="16" t="inlineStr"/>
+      <c r="H309" s="16" t="inlineStr"/>
+      <c r="I309" s="16" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B310" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C310" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D310" s="13" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E310" s="13" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F310" s="13" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G310" s="13" t="inlineStr"/>
+      <c r="H310" s="13" t="inlineStr"/>
+      <c r="I310" s="13" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B311" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C311" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D311" s="16" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E311" s="16" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F311" s="16" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G311" s="16" t="inlineStr"/>
+      <c r="H311" s="16" t="inlineStr"/>
+      <c r="I311" s="16" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B312" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C312" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D312" s="13" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E312" s="13" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F312" s="13" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G312" s="13" t="inlineStr"/>
+      <c r="H312" s="13" t="inlineStr"/>
+      <c r="I312" s="13" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B313" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C313" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D313" s="16" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E313" s="16" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F313" s="16" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G313" s="16" t="inlineStr"/>
+      <c r="H313" s="16" t="inlineStr"/>
+      <c r="I313" s="16" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B314" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C314" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D314" s="13" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E314" s="13" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F314" s="13" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G314" s="13" t="inlineStr"/>
+      <c r="H314" s="13" t="inlineStr"/>
+      <c r="I314" s="13" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B315" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C315" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D315" s="16" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E315" s="16" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F315" s="16" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G315" s="16" t="inlineStr"/>
+      <c r="H315" s="16" t="inlineStr"/>
+      <c r="I315" s="16" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="13" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B300" s="14" t="inlineStr">
+      <c r="B316" s="14" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C300" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D300" s="13" t="inlineStr">
+      <c r="C316" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D316" s="13" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E300" s="13" t="inlineStr">
+      <c r="E316" s="13" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -12253,37 +12813,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F300" s="13" t="inlineStr">
+      <c r="F316" s="13" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G300" s="13" t="inlineStr"/>
-      <c r="H300" s="13" t="inlineStr"/>
-      <c r="I300" s="13" t="inlineStr"/>
-    </row>
-    <row r="301">
-      <c r="A301" s="16" t="inlineStr">
+      <c r="G316" s="13" t="inlineStr"/>
+      <c r="H316" s="13" t="inlineStr"/>
+      <c r="I316" s="13" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B301" s="17" t="inlineStr">
+      <c r="B317" s="17" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C301" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D301" s="16" t="inlineStr">
+      <c r="C317" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D317" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E301" s="16" t="inlineStr">
+      <c r="E317" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -12295,37 +12855,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F301" s="16" t="inlineStr">
+      <c r="F317" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G301" s="16" t="inlineStr"/>
-      <c r="H301" s="16" t="inlineStr"/>
-      <c r="I301" s="16" t="inlineStr"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="13" t="inlineStr">
+      <c r="G317" s="16" t="inlineStr"/>
+      <c r="H317" s="16" t="inlineStr"/>
+      <c r="I317" s="16" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B302" s="14" t="inlineStr">
+      <c r="B318" s="14" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C302" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D302" s="13" t="inlineStr">
+      <c r="C318" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D318" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E302" s="13" t="inlineStr">
+      <c r="E318" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -12337,74 +12897,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F302" s="13" t="inlineStr">
+      <c r="F318" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G302" s="13" t="inlineStr"/>
-      <c r="H302" s="13" t="inlineStr"/>
-      <c r="I302" s="13" t="inlineStr"/>
-    </row>
-    <row r="303">
-      <c r="A303" s="16" t="inlineStr">
+      <c r="G318" s="13" t="inlineStr"/>
+      <c r="H318" s="13" t="inlineStr"/>
+      <c r="I318" s="13" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B303" s="17" t="inlineStr">
+      <c r="B319" s="17" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C303" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D303" s="16" t="inlineStr">
+      <c r="C319" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D319" s="16" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E303" s="16" t="inlineStr">
+      <c r="E319" s="16" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F303" s="16" t="inlineStr">
+      <c r="F319" s="16" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G303" s="16" t="inlineStr"/>
-      <c r="H303" s="16" t="inlineStr"/>
-      <c r="I303" s="16" t="inlineStr"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="13" t="inlineStr">
+      <c r="G319" s="16" t="inlineStr"/>
+      <c r="H319" s="16" t="inlineStr"/>
+      <c r="I319" s="16" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B304" s="14" t="inlineStr">
+      <c r="B320" s="14" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C304" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D304" s="13" t="inlineStr">
+      <c r="C320" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D320" s="13" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E304" s="13" t="inlineStr">
+      <c r="E320" s="13" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -12415,73 +12975,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F304" s="13" t="inlineStr">
+      <c r="F320" s="13" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G304" s="13" t="inlineStr"/>
-      <c r="H304" s="13" t="inlineStr"/>
-      <c r="I304" s="13" t="inlineStr"/>
-    </row>
-    <row r="305">
-      <c r="A305" s="16" t="inlineStr">
+      <c r="G320" s="13" t="inlineStr"/>
+      <c r="H320" s="13" t="inlineStr"/>
+      <c r="I320" s="13" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B305" s="17" t="inlineStr">
+      <c r="B321" s="17" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C305" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D305" s="16" t="inlineStr">
+      <c r="C321" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D321" s="16" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E305" s="16" t="inlineStr">
+      <c r="E321" s="16" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F305" s="16" t="inlineStr">
+      <c r="F321" s="16" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G305" s="16" t="inlineStr"/>
-      <c r="H305" s="16" t="inlineStr"/>
-      <c r="I305" s="16" t="inlineStr"/>
-    </row>
-    <row r="306">
-      <c r="A306" s="13" t="inlineStr">
+      <c r="G321" s="16" t="inlineStr"/>
+      <c r="H321" s="16" t="inlineStr"/>
+      <c r="I321" s="16" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B306" s="14" t="inlineStr">
+      <c r="B322" s="14" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C306" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D306" s="13" t="inlineStr">
+      <c r="C322" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D322" s="13" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E306" s="13" t="inlineStr">
+      <c r="E322" s="13" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -12492,37 +13052,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F306" s="13" t="inlineStr">
+      <c r="F322" s="13" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G306" s="13" t="inlineStr"/>
-      <c r="H306" s="13" t="inlineStr"/>
-      <c r="I306" s="13" t="inlineStr"/>
-    </row>
-    <row r="307">
-      <c r="A307" s="16" t="inlineStr">
+      <c r="G322" s="13" t="inlineStr"/>
+      <c r="H322" s="13" t="inlineStr"/>
+      <c r="I322" s="13" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B307" s="17" t="inlineStr">
+      <c r="B323" s="17" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C307" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D307" s="16" t="inlineStr">
+      <c r="C323" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E307" s="16" t="inlineStr">
+      <c r="E323" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -12532,37 +13092,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F307" s="16" t="inlineStr">
+      <c r="F323" s="16" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G307" s="16" t="inlineStr"/>
-      <c r="H307" s="16" t="inlineStr"/>
-      <c r="I307" s="16" t="inlineStr"/>
-    </row>
-    <row r="308">
-      <c r="A308" s="13" t="inlineStr">
+      <c r="G323" s="16" t="inlineStr"/>
+      <c r="H323" s="16" t="inlineStr"/>
+      <c r="I323" s="16" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B308" s="14" t="inlineStr">
+      <c r="B324" s="14" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C308" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D308" s="13" t="inlineStr">
+      <c r="C324" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D324" s="13" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E308" s="13" t="inlineStr">
+      <c r="E324" s="13" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -12570,19 +13130,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F308" s="13" t="inlineStr">
+      <c r="F324" s="13" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G308" s="13" t="inlineStr"/>
-      <c r="H308" s="13" t="inlineStr"/>
-      <c r="I308" s="13" t="inlineStr"/>
+      <c r="G324" s="13" t="inlineStr"/>
+      <c r="H324" s="13" t="inlineStr"/>
+      <c r="I324" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I308"/>
+  <autoFilter ref="A1:I324"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G308" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G324" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$324</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$328</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C324,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C328,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P1",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P1",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P1",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P1",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P1",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P1",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P1",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P1",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C324,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C328,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P2",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P2",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P2",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P2",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P2",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P2",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P2",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P2",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C324,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C328,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P3",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P3",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P3",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P3",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P3",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P3",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C324,"P3",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C328,"P3",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pelanggan",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pelanggan",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pelanggan",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pelanggan",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pelanggan",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pelanggan",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pelanggan",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pelanggan",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kasir",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kasir",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kasir",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kasir",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kasir",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kasir",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kasir",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kasir",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pending Payment",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pending Payment",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pending Payment",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pending Payment",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pending Payment",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pending Payment",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pending Payment",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pending Payment",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Dapur",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Dapur",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Dapur",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Dapur",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Dapur",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Dapur",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Dapur",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Dapur",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Keuangan",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Keuangan",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Keuangan",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Keuangan",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Keuangan",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Keuangan",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Keuangan",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Keuangan",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Setor Saldo Cash",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Setor Saldo Cash",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Setor Saldo Cash",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Setor Saldo Cash",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Setor Saldo Cash",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Setor Saldo Cash",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Setor Saldo Cash",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Setor Saldo Cash",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"QR Meja",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"QR Meja",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"QR Meja",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"QR Meja",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"QR Meja",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"QR Meja",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"QR Meja",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"QR Meja",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Diskon",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Diskon",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Diskon",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Diskon",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Diskon",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Diskon",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Diskon",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Diskon",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembayaran QRIS",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembayaran QRIS",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembayaran QRIS",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembayaran QRIS",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembayaran QRIS",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembayaran QRIS",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembayaran QRIS",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembayaran QRIS",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Tampilan",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Tampilan",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Tampilan",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Tampilan",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Tampilan",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Tampilan",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Tampilan",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Tampilan",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Super Admin",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Super Admin",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Super Admin",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Super Admin",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Super Admin",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Super Admin",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Super Admin",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Super Admin",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembaruan Aplikasi",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembaruan Aplikasi",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembaruan Aplikasi",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembaruan Aplikasi",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembaruan Aplikasi",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembaruan Aplikasi",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Pembaruan Aplikasi",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembaruan Aplikasi",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G324,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G328,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G324,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G328,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G324,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G328,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A324,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G324,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G328,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1727,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I324"/>
+  <dimension ref="A1:I328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11626,12 +11626,12 @@
     <row r="283">
       <c r="A283" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B283" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-PF-31</t>
         </is>
       </c>
       <c r="C283" s="18" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="D283" s="16" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Buka Jurnal GL Semua Resto sesudah ada tagihan langganan lunas</t>
         </is>
       </c>
       <c r="E283" s="16" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Baris pendapatan langganan tidak muncul di sana</t>
         </is>
       </c>
       <c r="F283" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-21</t>
         </is>
       </c>
       <c r="G283" s="16" t="inlineStr"/>
@@ -11661,12 +11661,12 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B284" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-PF-32</t>
         </is>
       </c>
       <c r="C284" s="15" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Buka daftar saringan resto</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>KaataGo tidak ada di daftarnya</t>
         </is>
       </c>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-21</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr"/>
@@ -11696,12 +11696,12 @@
     <row r="285">
       <c r="A285" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B285" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-PF-33</t>
         </is>
       </c>
       <c r="C285" s="18" t="inlineStr">
@@ -11711,17 +11711,17 @@
       </c>
       <c r="D285" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E285" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Pendapatan langganan ada di sana, dan Saldo Total tidak nol</t>
         </is>
       </c>
       <c r="F285" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G285" s="16" t="inlineStr"/>
@@ -11731,32 +11731,32 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
-        </is>
-      </c>
-      <c r="C286" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-34</t>
+        </is>
+      </c>
+      <c r="C286" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Periksa nomor akun di Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Golongan 11xxxxx, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B287" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-TS-01</t>
         </is>
       </c>
       <c r="C287" s="18" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="D287" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E287" s="16" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F287" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G287" s="16" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B288" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-TS-02</t>
         </is>
       </c>
       <c r="C288" s="15" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr"/>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="B289" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-TS-03</t>
         </is>
       </c>
       <c r="C289" s="18" t="inlineStr">
@@ -11851,17 +11851,17 @@
       </c>
       <c r="D289" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E289" s="16" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F289" s="16" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G289" s="16" t="inlineStr"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="B290" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
+          <t>TC-TS-04</t>
         </is>
       </c>
       <c r="C290" s="15" t="inlineStr">
@@ -11886,17 +11886,17 @@
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr"/>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="B291" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-TS-05</t>
         </is>
       </c>
       <c r="C291" s="18" t="inlineStr">
@@ -11921,17 +11921,17 @@
       </c>
       <c r="D291" s="16" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E291" s="16" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F291" s="16" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G291" s="16" t="inlineStr"/>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="B292" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C292" s="15" t="inlineStr">
@@ -11956,17 +11956,17 @@
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr"/>
@@ -11981,27 +11981,27 @@
       </c>
       <c r="B293" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
-        </is>
-      </c>
-      <c r="C293" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-07</t>
+        </is>
+      </c>
+      <c r="C293" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D293" s="16" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E293" s="16" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F293" s="16" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G293" s="16" t="inlineStr"/>
@@ -12016,27 +12016,27 @@
       </c>
       <c r="B294" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C294" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C294" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr"/>
@@ -12051,27 +12051,27 @@
       </c>
       <c r="B295" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C295" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C295" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D295" s="16" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E295" s="16" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F295" s="16" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G295" s="16" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="B296" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-TS-10</t>
         </is>
       </c>
       <c r="C296" s="15" t="inlineStr">
@@ -12096,17 +12096,17 @@
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr"/>
@@ -12121,27 +12121,27 @@
       </c>
       <c r="B297" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
-        </is>
-      </c>
-      <c r="C297" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-11</t>
+        </is>
+      </c>
+      <c r="C297" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D297" s="16" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E297" s="16" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F297" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G297" s="16" t="inlineStr"/>
@@ -12156,27 +12156,27 @@
       </c>
       <c r="B298" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
-        </is>
-      </c>
-      <c r="C298" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C298" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E298" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr"/>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B299" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
+          <t>TC-TS-13</t>
         </is>
       </c>
       <c r="C299" s="20" t="inlineStr">
@@ -12201,17 +12201,17 @@
       </c>
       <c r="D299" s="16" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E299" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F299" s="16" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G299" s="16" t="inlineStr"/>
@@ -12226,27 +12226,27 @@
       </c>
       <c r="B300" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C300" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-14</t>
+        </is>
+      </c>
+      <c r="C300" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E300" s="13" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F300" s="13" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G300" s="13" t="inlineStr"/>
@@ -12261,27 +12261,27 @@
       </c>
       <c r="B301" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C301" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C301" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D301" s="16" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E301" s="16" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F301" s="16" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G301" s="16" t="inlineStr"/>
@@ -12291,12 +12291,12 @@
     <row r="302">
       <c r="A302" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B302" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
+          <t>TC-TS-16</t>
         </is>
       </c>
       <c r="C302" s="15" t="inlineStr">
@@ -12306,17 +12306,17 @@
       </c>
       <c r="D302" s="13" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
         </is>
       </c>
       <c r="E302" s="13" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F302" s="13" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>F-PG-02, TSD §7.1</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr"/>
@@ -12326,32 +12326,32 @@
     <row r="303">
       <c r="A303" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B303" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
-        </is>
-      </c>
-      <c r="C303" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C303" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D303" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
         </is>
       </c>
       <c r="E303" s="16" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
         </is>
       </c>
       <c r="F303" s="16" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §1.2</t>
         </is>
       </c>
       <c r="G303" s="16" t="inlineStr"/>
@@ -12361,32 +12361,32 @@
     <row r="304">
       <c r="A304" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B304" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
-        </is>
-      </c>
-      <c r="C304" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C304" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
         </is>
       </c>
       <c r="E304" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
         </is>
       </c>
       <c r="F304" s="13" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>TSD §6.5</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr"/>
@@ -12396,32 +12396,32 @@
     <row r="305">
       <c r="A305" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B305" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
-        </is>
-      </c>
-      <c r="C305" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C305" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D305" s="16" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Hapus resto uji</t>
         </is>
       </c>
       <c r="E305" s="16" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
         </is>
       </c>
       <c r="F305" s="16" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>TSD §4.0</t>
         </is>
       </c>
       <c r="G305" s="16" t="inlineStr"/>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="B306" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-RG-01</t>
         </is>
       </c>
       <c r="C306" s="15" t="inlineStr">
@@ -12446,17 +12446,17 @@
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
         </is>
       </c>
       <c r="E306" s="13" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
         </is>
       </c>
       <c r="F306" s="13" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>F-KS-09</t>
         </is>
       </c>
       <c r="G306" s="13" t="inlineStr"/>
@@ -12471,7 +12471,7 @@
       </c>
       <c r="B307" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-RG-02</t>
         </is>
       </c>
       <c r="C307" s="18" t="inlineStr">
@@ -12481,17 +12481,17 @@
       </c>
       <c r="D307" s="16" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
         </is>
       </c>
       <c r="E307" s="16" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
         </is>
       </c>
       <c r="F307" s="16" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>F-PP-09, A-13</t>
         </is>
       </c>
       <c r="G307" s="16" t="inlineStr"/>
@@ -12506,27 +12506,27 @@
       </c>
       <c r="B308" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C308" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C308" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
         </is>
       </c>
       <c r="E308" s="13" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Tidak muncul sama sekali</t>
         </is>
       </c>
       <c r="F308" s="13" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="G308" s="13" t="inlineStr"/>
@@ -12541,27 +12541,27 @@
       </c>
       <c r="B309" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C309" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C309" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D309" s="16" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
         </is>
       </c>
       <c r="E309" s="16" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Nominalnya sama dengan yang diajukan</t>
         </is>
       </c>
       <c r="F309" s="16" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>F-FN-03</t>
         </is>
       </c>
       <c r="G309" s="16" t="inlineStr"/>
@@ -12576,27 +12576,27 @@
       </c>
       <c r="B310" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
-        </is>
-      </c>
-      <c r="C310" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C310" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
         </is>
       </c>
       <c r="E310" s="13" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
         </is>
       </c>
       <c r="F310" s="13" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="G310" s="13" t="inlineStr"/>
@@ -12611,27 +12611,27 @@
       </c>
       <c r="B311" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
-        </is>
-      </c>
-      <c r="C311" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C311" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D311" s="16" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
         </is>
       </c>
       <c r="E311" s="16" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
         </is>
       </c>
       <c r="F311" s="16" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-DS-10, F-DS-12</t>
         </is>
       </c>
       <c r="G311" s="16" t="inlineStr"/>
@@ -12646,7 +12646,7 @@
       </c>
       <c r="B312" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
+          <t>TC-RG-07</t>
         </is>
       </c>
       <c r="C312" s="19" t="inlineStr">
@@ -12656,17 +12656,17 @@
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
         </is>
       </c>
       <c r="E312" s="13" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
         </is>
       </c>
       <c r="F312" s="13" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>F-IN-15</t>
         </is>
       </c>
       <c r="G312" s="13" t="inlineStr"/>
@@ -12681,7 +12681,7 @@
       </c>
       <c r="B313" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
+          <t>TC-RG-08</t>
         </is>
       </c>
       <c r="C313" s="20" t="inlineStr">
@@ -12691,17 +12691,17 @@
       </c>
       <c r="D313" s="16" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
         </is>
       </c>
       <c r="E313" s="16" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Daftar menu termuat</t>
         </is>
       </c>
       <c r="F313" s="16" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>F-DS-01</t>
         </is>
       </c>
       <c r="G313" s="16" t="inlineStr"/>
@@ -12716,27 +12716,27 @@
       </c>
       <c r="B314" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
-        </is>
-      </c>
-      <c r="C314" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C314" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
         </is>
       </c>
       <c r="E314" s="13" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Detail jurnal terbuka</t>
         </is>
       </c>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-KS-13</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr"/>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="B315" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
+          <t>TC-RG-10</t>
         </is>
       </c>
       <c r="C315" s="20" t="inlineStr">
@@ -12761,17 +12761,17 @@
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
         </is>
       </c>
       <c r="E315" s="16" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Seluruh layar berganti bersih</t>
         </is>
       </c>
       <c r="F315" s="16" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>A-18</t>
         </is>
       </c>
       <c r="G315" s="16" t="inlineStr"/>
@@ -12781,25 +12781,165 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B316" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C316" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D316" s="13" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E316" s="13" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F316" s="13" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G316" s="13" t="inlineStr"/>
+      <c r="H316" s="13" t="inlineStr"/>
+      <c r="I316" s="13" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B317" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C317" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D317" s="16" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E317" s="16" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F317" s="16" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G317" s="16" t="inlineStr"/>
+      <c r="H317" s="16" t="inlineStr"/>
+      <c r="I317" s="16" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B318" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C318" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D318" s="13" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E318" s="13" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F318" s="13" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G318" s="13" t="inlineStr"/>
+      <c r="H318" s="13" t="inlineStr"/>
+      <c r="I318" s="13" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B319" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C319" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D319" s="16" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E319" s="16" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F319" s="16" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G319" s="16" t="inlineStr"/>
+      <c r="H319" s="16" t="inlineStr"/>
+      <c r="I319" s="16" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="13" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B316" s="14" t="inlineStr">
+      <c r="B320" s="14" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C316" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D316" s="13" t="inlineStr">
+      <c r="C320" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D320" s="13" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E316" s="13" t="inlineStr">
+      <c r="E320" s="13" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -12813,37 +12953,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F316" s="13" t="inlineStr">
+      <c r="F320" s="13" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G316" s="13" t="inlineStr"/>
-      <c r="H316" s="13" t="inlineStr"/>
-      <c r="I316" s="13" t="inlineStr"/>
-    </row>
-    <row r="317">
-      <c r="A317" s="16" t="inlineStr">
+      <c r="G320" s="13" t="inlineStr"/>
+      <c r="H320" s="13" t="inlineStr"/>
+      <c r="I320" s="13" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B317" s="17" t="inlineStr">
+      <c r="B321" s="17" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C317" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D317" s="16" t="inlineStr">
+      <c r="C321" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D321" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E317" s="16" t="inlineStr">
+      <c r="E321" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -12855,37 +12995,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F317" s="16" t="inlineStr">
+      <c r="F321" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G317" s="16" t="inlineStr"/>
-      <c r="H317" s="16" t="inlineStr"/>
-      <c r="I317" s="16" t="inlineStr"/>
-    </row>
-    <row r="318">
-      <c r="A318" s="13" t="inlineStr">
+      <c r="G321" s="16" t="inlineStr"/>
+      <c r="H321" s="16" t="inlineStr"/>
+      <c r="I321" s="16" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B318" s="14" t="inlineStr">
+      <c r="B322" s="14" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C318" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D318" s="13" t="inlineStr">
+      <c r="C322" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D322" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E318" s="13" t="inlineStr">
+      <c r="E322" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -12897,74 +13037,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F318" s="13" t="inlineStr">
+      <c r="F322" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G318" s="13" t="inlineStr"/>
-      <c r="H318" s="13" t="inlineStr"/>
-      <c r="I318" s="13" t="inlineStr"/>
-    </row>
-    <row r="319">
-      <c r="A319" s="16" t="inlineStr">
+      <c r="G322" s="13" t="inlineStr"/>
+      <c r="H322" s="13" t="inlineStr"/>
+      <c r="I322" s="13" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B319" s="17" t="inlineStr">
+      <c r="B323" s="17" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C319" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D319" s="16" t="inlineStr">
+      <c r="C323" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E319" s="16" t="inlineStr">
+      <c r="E323" s="16" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F319" s="16" t="inlineStr">
+      <c r="F323" s="16" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G319" s="16" t="inlineStr"/>
-      <c r="H319" s="16" t="inlineStr"/>
-      <c r="I319" s="16" t="inlineStr"/>
-    </row>
-    <row r="320">
-      <c r="A320" s="13" t="inlineStr">
+      <c r="G323" s="16" t="inlineStr"/>
+      <c r="H323" s="16" t="inlineStr"/>
+      <c r="I323" s="16" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B320" s="14" t="inlineStr">
+      <c r="B324" s="14" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C320" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D320" s="13" t="inlineStr">
+      <c r="C324" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D324" s="13" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E320" s="13" t="inlineStr">
+      <c r="E324" s="13" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -12975,73 +13115,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F320" s="13" t="inlineStr">
+      <c r="F324" s="13" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G320" s="13" t="inlineStr"/>
-      <c r="H320" s="13" t="inlineStr"/>
-      <c r="I320" s="13" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="16" t="inlineStr">
+      <c r="G324" s="13" t="inlineStr"/>
+      <c r="H324" s="13" t="inlineStr"/>
+      <c r="I324" s="13" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B321" s="17" t="inlineStr">
+      <c r="B325" s="17" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C321" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D321" s="16" t="inlineStr">
+      <c r="C325" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E321" s="16" t="inlineStr">
+      <c r="E325" s="16" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F321" s="16" t="inlineStr">
+      <c r="F325" s="16" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G321" s="16" t="inlineStr"/>
-      <c r="H321" s="16" t="inlineStr"/>
-      <c r="I321" s="16" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="13" t="inlineStr">
+      <c r="G325" s="16" t="inlineStr"/>
+      <c r="H325" s="16" t="inlineStr"/>
+      <c r="I325" s="16" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B322" s="14" t="inlineStr">
+      <c r="B326" s="14" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C322" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D322" s="13" t="inlineStr">
+      <c r="C326" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D326" s="13" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E322" s="13" t="inlineStr">
+      <c r="E326" s="13" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -13052,37 +13192,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F322" s="13" t="inlineStr">
+      <c r="F326" s="13" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G322" s="13" t="inlineStr"/>
-      <c r="H322" s="13" t="inlineStr"/>
-      <c r="I322" s="13" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" s="16" t="inlineStr">
+      <c r="G326" s="13" t="inlineStr"/>
+      <c r="H326" s="13" t="inlineStr"/>
+      <c r="I326" s="13" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B323" s="17" t="inlineStr">
+      <c r="B327" s="17" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C323" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D323" s="16" t="inlineStr">
+      <c r="C327" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D327" s="16" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E323" s="16" t="inlineStr">
+      <c r="E327" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -13092,37 +13232,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F323" s="16" t="inlineStr">
+      <c r="F327" s="16" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G323" s="16" t="inlineStr"/>
-      <c r="H323" s="16" t="inlineStr"/>
-      <c r="I323" s="16" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="13" t="inlineStr">
+      <c r="G327" s="16" t="inlineStr"/>
+      <c r="H327" s="16" t="inlineStr"/>
+      <c r="I327" s="16" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B324" s="14" t="inlineStr">
+      <c r="B328" s="14" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C324" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D324" s="13" t="inlineStr">
+      <c r="C328" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D328" s="13" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E324" s="13" t="inlineStr">
+      <c r="E328" s="13" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -13130,19 +13270,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F324" s="13" t="inlineStr">
+      <c r="F328" s="13" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G324" s="13" t="inlineStr"/>
-      <c r="H324" s="13" t="inlineStr"/>
-      <c r="I324" s="13" t="inlineStr"/>
+      <c r="G328" s="13" t="inlineStr"/>
+      <c r="H328" s="13" t="inlineStr"/>
+      <c r="I328" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I324"/>
+  <autoFilter ref="A1:I328"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G324" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G328" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$328</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$332</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C328,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C332,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P1",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P1",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P1",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P1",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P1",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P1",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P1",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P1",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C328,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C332,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P2",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P2",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P2",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P2",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P2",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P2",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P2",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P2",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C328,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C332,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P3",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P3",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P3",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P3",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P3",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P3",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C328,"P3",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C332,"P3",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pelanggan",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pelanggan",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pelanggan",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pelanggan",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pelanggan",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pelanggan",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pelanggan",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pelanggan",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kasir",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Kasir",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kasir",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Kasir",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kasir",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Kasir",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kasir",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Kasir",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pending Payment",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pending Payment",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pending Payment",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pending Payment",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pending Payment",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pending Payment",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pending Payment",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pending Payment",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Dapur",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Dapur",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Dapur",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Dapur",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Dapur",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Dapur",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Dapur",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Dapur",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Keuangan",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Keuangan",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Keuangan",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Keuangan",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Keuangan",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Keuangan",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Keuangan",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Keuangan",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Setor Saldo Cash",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Setor Saldo Cash",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Setor Saldo Cash",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Setor Saldo Cash",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Setor Saldo Cash",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Setor Saldo Cash",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Setor Saldo Cash",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Setor Saldo Cash",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"QR Meja",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"QR Meja",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"QR Meja",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"QR Meja",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"QR Meja",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"QR Meja",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"QR Meja",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"QR Meja",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Diskon",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Diskon",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Diskon",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Diskon",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Diskon",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Diskon",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Diskon",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Diskon",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembayaran QRIS",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembayaran QRIS",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembayaran QRIS",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembayaran QRIS",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembayaran QRIS",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembayaran QRIS",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembayaran QRIS",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembayaran QRIS",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Tampilan",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Tampilan",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Tampilan",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Tampilan",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Tampilan",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Tampilan",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Tampilan",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Tampilan",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Super Admin",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Super Admin",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Super Admin",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Super Admin",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Super Admin",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Super Admin",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Super Admin",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Super Admin",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembaruan Aplikasi",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembaruan Aplikasi",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembaruan Aplikasi",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembaruan Aplikasi",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembaruan Aplikasi",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembaruan Aplikasi",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Pembaruan Aplikasi",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Pembaruan Aplikasi",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A332,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G328,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G332,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G328,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G332,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G328,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G332,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A328,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G328,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A332,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G332,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1727,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I328"/>
+  <dimension ref="A1:I332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8336,12 +8336,12 @@
     <row r="189">
       <c r="A189" s="16" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B189" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-01</t>
+          <t>TC-TM-09</t>
         </is>
       </c>
       <c r="C189" s="20" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="D189" s="16" t="inlineStr">
         <is>
-          <t>Buka List Resto</t>
+          <t>Buka menu utama Kasir, Admin, Finance, Super Admin, Owner</t>
         </is>
       </c>
       <c r="E189" s="16" t="inlineStr">
         <is>
-          <t>Seluruh resto terdaftar tampil</t>
+          <t>Menunya berkelompok berikut judul tiap kelompok</t>
         </is>
       </c>
       <c r="F189" s="16" t="inlineStr">
         <is>
-          <t>F-SA-01</t>
+          <t>F-TM-05</t>
         </is>
       </c>
       <c r="G189" s="16" t="inlineStr"/>
@@ -8371,12 +8371,12 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B190" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-02</t>
+          <t>TC-TM-10</t>
         </is>
       </c>
       <c r="C190" s="19" t="inlineStr">
@@ -8386,17 +8386,17 @@
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>Kelola karyawan lintas resto, ubah perannya</t>
+          <t>Hitung menu di tiap peran, bandingkan dengan sebelum dikelompokkan</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Perubahan berlaku; karyawan itu melihat menu sesuai peran barunya</t>
+          <t>Tidak ada satu pun yang hilang</t>
         </is>
       </c>
       <c r="F190" s="13" t="inlineStr">
         <is>
-          <t>F-SA-02</t>
+          <t>F-TM-05</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr"/>
@@ -8406,32 +8406,32 @@
     <row r="191">
       <c r="A191" s="16" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B191" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-03</t>
-        </is>
-      </c>
-      <c r="C191" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TM-11</t>
+        </is>
+      </c>
+      <c r="C191" s="22" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D191" s="16" t="inlineStr">
         <is>
-          <t>Kirim pengumuman versi aplikasi</t>
+          <t>Buka di layar lebar / tablet</t>
         </is>
       </c>
       <c r="E191" s="16" t="inlineStr">
         <is>
-          <t>Sampai ke seluruh pengguna, di semua resto</t>
+          <t>Judul kelompok selebar layar, bukan terjepit selebar satu kartu</t>
         </is>
       </c>
       <c r="F191" s="16" t="inlineStr">
         <is>
-          <t>F-SA-03, F-IN-07</t>
+          <t>F-TM-06</t>
         </is>
       </c>
       <c r="G191" s="16" t="inlineStr"/>
@@ -8441,32 +8441,32 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B192" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-04</t>
-        </is>
-      </c>
-      <c r="C192" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TM-12</t>
+        </is>
+      </c>
+      <c r="C192" s="21" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
-          <t>Buka layar Kirim Pengumuman sebagai Admin resto</t>
+          <t>Periksa nama kelompok lintas peran</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Pilihan kategori Update Aplikasi tidak tersedia</t>
+          <t>"Keuangan" di Admin dan di Owner terbaca sama</t>
         </is>
       </c>
       <c r="F192" s="13" t="inlineStr">
         <is>
-          <t>F-SA-03, F-IN-08</t>
+          <t>F-TM-05</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr"/>
@@ -8481,7 +8481,7 @@
       </c>
       <c r="B193" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-05</t>
+          <t>TC-SA-01</t>
         </is>
       </c>
       <c r="C193" s="20" t="inlineStr">
@@ -8491,17 +8491,17 @@
       </c>
       <c r="D193" s="16" t="inlineStr">
         <is>
-          <t>Kirim pengumuman umum ke seluruh resto</t>
+          <t>Buka List Resto</t>
         </is>
       </c>
       <c r="E193" s="16" t="inlineStr">
         <is>
-          <t>Muncul di kotak masuk semua resto</t>
+          <t>Seluruh resto terdaftar tampil</t>
         </is>
       </c>
       <c r="F193" s="16" t="inlineStr">
         <is>
-          <t>F-SA-04</t>
+          <t>F-SA-01</t>
         </is>
       </c>
       <c r="G193" s="16" t="inlineStr"/>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="B194" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-06</t>
+          <t>TC-SA-02</t>
         </is>
       </c>
       <c r="C194" s="19" t="inlineStr">
@@ -8526,17 +8526,17 @@
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>Telusuri menu Super Admin</t>
+          <t>Kelola karyawan lintas resto, ubah perannya</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar kasir, dapur, maupun keuangan resto</t>
+          <t>Perubahan berlaku; karyawan itu melihat menu sesuai peran barunya</t>
         </is>
       </c>
       <c r="F194" s="13" t="inlineStr">
         <is>
-          <t>F-SA-06</t>
+          <t>F-SA-02</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr"/>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="B195" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-07</t>
+          <t>TC-SA-03</t>
         </is>
       </c>
       <c r="C195" s="18" t="inlineStr">
@@ -8561,17 +8561,17 @@
       </c>
       <c r="D195" s="16" t="inlineStr">
         <is>
-          <t>List Resto → hapus sebuah resto</t>
+          <t>Kirim pengumuman versi aplikasi</t>
         </is>
       </c>
       <c r="E195" s="16" t="inlineStr">
         <is>
-          <t>Hilang dari daftar; datanya tidak dibuang</t>
+          <t>Sampai ke seluruh pengguna, di semua resto</t>
         </is>
       </c>
       <c r="F195" s="16" t="inlineStr">
         <is>
-          <t>F-SA-07</t>
+          <t>F-SA-03, F-IN-07</t>
         </is>
       </c>
       <c r="G195" s="16" t="inlineStr"/>
@@ -8586,7 +8586,7 @@
       </c>
       <c r="B196" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-08</t>
+          <t>TC-SA-04</t>
         </is>
       </c>
       <c r="C196" s="15" t="inlineStr">
@@ -8596,17 +8596,17 @@
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>Buka Pilih Resto sebagai pelanggan</t>
+          <t>Buka layar Kirim Pengumuman sebagai Admin resto</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Resto terhapus tidak muncul</t>
+          <t>Pilihan kategori Update Aplikasi tidak tersedia</t>
         </is>
       </c>
       <c r="F196" s="13" t="inlineStr">
         <is>
-          <t>F-SA-10</t>
+          <t>F-SA-03, F-IN-08</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr"/>
@@ -8621,27 +8621,27 @@
       </c>
       <c r="B197" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-09</t>
-        </is>
-      </c>
-      <c r="C197" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-SA-05</t>
+        </is>
+      </c>
+      <c r="C197" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D197" s="16" t="inlineStr">
         <is>
-          <t>Pindai QR meja resto yang sudah dihapus, coba pesan</t>
+          <t>Kirim pengumuman umum ke seluruh resto</t>
         </is>
       </c>
       <c r="E197" s="16" t="inlineStr">
         <is>
-          <t>Ditolak database, bukan hanya disembunyikan layarnya</t>
+          <t>Muncul di kotak masuk semua resto</t>
         </is>
       </c>
       <c r="F197" s="16" t="inlineStr">
         <is>
-          <t>F-SA-10</t>
+          <t>F-SA-04</t>
         </is>
       </c>
       <c r="G197" s="16" t="inlineStr"/>
@@ -8656,27 +8656,27 @@
       </c>
       <c r="B198" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-10</t>
-        </is>
-      </c>
-      <c r="C198" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-SA-06</t>
+        </is>
+      </c>
+      <c r="C198" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>Coba ubah harga produk resto terhapus</t>
+          <t>Telusuri menu Super Admin</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tidak ada layar kasir, dapur, maupun keuangan resto</t>
         </is>
       </c>
       <c r="F198" s="13" t="inlineStr">
         <is>
-          <t>F-SA-10</t>
+          <t>F-SA-06</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr"/>
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B199" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-11</t>
+          <t>TC-SA-07</t>
         </is>
       </c>
       <c r="C199" s="18" t="inlineStr">
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D199" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan tagihan setelah resto dihapus</t>
+          <t>List Resto → hapus sebuah resto</t>
         </is>
       </c>
       <c r="E199" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada tagihan baru untuk resto itu</t>
+          <t>Hilang dari daftar; datanya tidak dibuang</t>
         </is>
       </c>
       <c r="F199" s="16" t="inlineStr">
         <is>
-          <t>F-SA-11</t>
+          <t>F-SA-07</t>
         </is>
       </c>
       <c r="G199" s="16" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="B200" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-12</t>
+          <t>TC-SA-08</t>
         </is>
       </c>
       <c r="C200" s="15" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>Periksa tagihan lama resto terhapus</t>
+          <t>Buka Pilih Resto sebagai pelanggan</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Masih ada dan bisa ditelusuri</t>
+          <t>Resto terhapus tidak muncul</t>
         </is>
       </c>
       <c r="F200" s="13" t="inlineStr">
         <is>
-          <t>F-SA-11</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr"/>
@@ -8761,27 +8761,27 @@
       </c>
       <c r="B201" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-13</t>
-        </is>
-      </c>
-      <c r="C201" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-09</t>
+        </is>
+      </c>
+      <c r="C201" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D201" s="16" t="inlineStr">
         <is>
-          <t>Nyalakan saklar Tampilkan yang dihapus</t>
+          <t>Pindai QR meja resto yang sudah dihapus, coba pesan</t>
         </is>
       </c>
       <c r="E201" s="16" t="inlineStr">
         <is>
-          <t>Resto terhapus muncul, hanya dengan tombol Kembalikan</t>
+          <t>Ditolak database, bukan hanya disembunyikan layarnya</t>
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr">
         <is>
-          <t>F-SA-09</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G201" s="16" t="inlineStr"/>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="B202" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-14</t>
+          <t>TC-SA-10</t>
         </is>
       </c>
       <c r="C202" s="15" t="inlineStr">
@@ -8806,17 +8806,17 @@
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Kembalikan</t>
+          <t>Coba ubah harga produk resto terhapus</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Kembali ke daftar, tapi belum aktif — harus dinyalakan sendiri</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F202" s="13" t="inlineStr">
         <is>
-          <t>F-SA-08</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr"/>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="B203" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-15</t>
+          <t>TC-SA-11</t>
         </is>
       </c>
       <c r="C203" s="18" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="D203" s="16" t="inlineStr">
         <is>
-          <t>Coba hapus penyewa platform (KaataGo)</t>
+          <t>Terbitkan tagihan setelah resto dihapus</t>
         </is>
       </c>
       <c r="E203" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tidak ada tagihan baru untuk resto itu</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-SA-11</t>
         </is>
       </c>
       <c r="G203" s="16" t="inlineStr"/>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="B204" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-16</t>
+          <t>TC-SA-12</t>
         </is>
       </c>
       <c r="C204" s="15" t="inlineStr">
@@ -8876,17 +8876,17 @@
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>Coba set_resto_deleted sebagai Owner resto</t>
+          <t>Periksa tagihan lama resto terhapus</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — hanya Super Admin</t>
+          <t>Masih ada dan bisa ditelusuri</t>
         </is>
       </c>
       <c r="F204" s="13" t="inlineStr">
         <is>
-          <t>F-SA-07</t>
+          <t>F-SA-11</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr"/>
@@ -8901,7 +8901,7 @@
       </c>
       <c r="B205" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-17</t>
+          <t>TC-SA-13</t>
         </is>
       </c>
       <c r="C205" s="20" t="inlineStr">
@@ -8911,17 +8911,17 @@
       </c>
       <c r="D205" s="16" t="inlineStr">
         <is>
-          <t>Periksa baris resto terhapus di database</t>
+          <t>Nyalakan saklar Tampilkan yang dihapus</t>
         </is>
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>deleted_by dan deleted_at terisi</t>
+          <t>Resto terhapus muncul, hanya dengan tombol Kembalikan</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
         <is>
-          <t>F-SA-12</t>
+          <t>F-SA-09</t>
         </is>
       </c>
       <c r="G205" s="16" t="inlineStr"/>
@@ -8931,32 +8931,32 @@
     <row r="206">
       <c r="A206" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B206" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-01</t>
-        </is>
-      </c>
-      <c r="C206" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-14</t>
+        </is>
+      </c>
+      <c r="C206" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>Buka pengumuman versi → Unduh Versi Terbaru</t>
+          <t>Ketuk Kembalikan</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Unduhan mulai di dalam aplikasi, tidak membuka peramban</t>
+          <t>Kembali ke daftar, tapi belum aktif — harus dinyalakan sendiri</t>
         </is>
       </c>
       <c r="F206" s="13" t="inlineStr">
         <is>
-          <t>F-UP-01, F-UP-02</t>
+          <t>F-SA-08</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr"/>
@@ -8966,32 +8966,32 @@
     <row r="207">
       <c r="A207" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B207" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-02</t>
-        </is>
-      </c>
-      <c r="C207" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-15</t>
+        </is>
+      </c>
+      <c r="C207" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D207" s="16" t="inlineStr">
         <is>
-          <t>Perhatikan bar notifikasi HP</t>
+          <t>Coba hapus penyewa platform (KaataGo)</t>
         </is>
       </c>
       <c r="E207" s="16" t="inlineStr">
         <is>
-          <t>Kemajuannya tampil berikut persennya</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
         <is>
-          <t>F-UP-03</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G207" s="16" t="inlineStr"/>
@@ -9001,32 +9001,32 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B208" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-03</t>
-        </is>
-      </c>
-      <c r="C208" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-16</t>
+        </is>
+      </c>
+      <c r="C208" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>Kunci HP saat unduhan berjalan, tunggu, buka lagi</t>
+          <t>Coba set_resto_deleted sebagai Owner resto</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Unduhannya lanjut, tidak mengulang dari nol</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F208" s="13" t="inlineStr">
         <is>
-          <t>F-UP-04</t>
+          <t>F-SA-07</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr"/>
@@ -9036,12 +9036,12 @@
     <row r="209">
       <c r="A209" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B209" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-04</t>
+          <t>TC-SA-17</t>
         </is>
       </c>
       <c r="C209" s="20" t="inlineStr">
@@ -9051,17 +9051,17 @@
       </c>
       <c r="D209" s="16" t="inlineStr">
         <is>
-          <t>Tekan tombol unduh lagi saat unduhan berjalan</t>
+          <t>Periksa baris resto terhapus di database</t>
         </is>
       </c>
       <c r="E209" s="16" t="inlineStr">
         <is>
-          <t>Muncul pilihan Batalkan atau Lanjutkan</t>
+          <t>deleted_by dan deleted_at terisi</t>
         </is>
       </c>
       <c r="F209" s="16" t="inlineStr">
         <is>
-          <t>F-UP-05, F-IN-18</t>
+          <t>F-SA-12</t>
         </is>
       </c>
       <c r="G209" s="16" t="inlineStr"/>
@@ -9076,7 +9076,7 @@
       </c>
       <c r="B210" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-05</t>
+          <t>TC-UP-01</t>
         </is>
       </c>
       <c r="C210" s="19" t="inlineStr">
@@ -9086,17 +9086,17 @@
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>Pilih Batalkan</t>
+          <t>Buka pengumuman versi → Unduh Versi Terbaru</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Unduhan berhenti; tidak ditampilkan sebagai galat</t>
+          <t>Unduhan mulai di dalam aplikasi, tidak membuka peramban</t>
         </is>
       </c>
       <c r="F210" s="13" t="inlineStr">
         <is>
-          <t>F-IN-19</t>
+          <t>F-UP-01, F-UP-02</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr"/>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="B211" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-06</t>
+          <t>TC-UP-02</t>
         </is>
       </c>
       <c r="C211" s="20" t="inlineStr">
@@ -9121,17 +9121,17 @@
       </c>
       <c r="D211" s="16" t="inlineStr">
         <is>
-          <t>Biarkan unduhan selesai</t>
+          <t>Perhatikan bar notifikasi HP</t>
         </is>
       </c>
       <c r="E211" s="16" t="inlineStr">
         <is>
-          <t>Notifikasi "ketuk untuk memasang"; pemasang Android terbuka</t>
+          <t>Kemajuannya tampil berikut persennya</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>F-UP-06, F-IN-17</t>
+          <t>F-UP-03</t>
         </is>
       </c>
       <c r="G211" s="16" t="inlineStr"/>
@@ -9146,7 +9146,7 @@
       </c>
       <c r="B212" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-07</t>
+          <t>TC-UP-03</t>
         </is>
       </c>
       <c r="C212" s="19" t="inlineStr">
@@ -9156,17 +9156,17 @@
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>Matikan data seluler di tengah unduhan</t>
+          <t>Kunci HP saat unduhan berjalan, tunggu, buka lagi</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Pesannya menyebut masalah koneksi, satu kalimat, tanpa isi galat mentah</t>
+          <t>Unduhannya lanjut, tidak mengulang dari nol</t>
         </is>
       </c>
       <c r="F212" s="13" t="inlineStr">
         <is>
-          <t>F-UP-07, F-IN-19</t>
+          <t>F-UP-04</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr"/>
@@ -9181,27 +9181,27 @@
       </c>
       <c r="B213" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-08</t>
-        </is>
-      </c>
-      <c r="C213" s="22" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-UP-04</t>
+        </is>
+      </c>
+      <c r="C213" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D213" s="16" t="inlineStr">
         <is>
-          <t>Penuhi penyimpanan HP, lalu unduh</t>
+          <t>Tekan tombol unduh lagi saat unduhan berjalan</t>
         </is>
       </c>
       <c r="E213" s="16" t="inlineStr">
         <is>
-          <t>Pesannya menyebut penyimpanan penuh — dibedakan dari masalah koneksi</t>
+          <t>Muncul pilihan Batalkan atau Lanjutkan</t>
         </is>
       </c>
       <c r="F213" s="16" t="inlineStr">
         <is>
-          <t>F-UP-07</t>
+          <t>F-UP-05, F-IN-18</t>
         </is>
       </c>
       <c r="G213" s="16" t="inlineStr"/>
@@ -9216,27 +9216,27 @@
       </c>
       <c r="B214" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-09</t>
-        </is>
-      </c>
-      <c r="C214" s="21" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-UP-05</t>
+        </is>
+      </c>
+      <c r="C214" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>Pakai jalur cadangan lewat peramban</t>
+          <t>Pilih Batalkan</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Berkasnya terunduh</t>
+          <t>Unduhan berhenti; tidak ditampilkan sebagai galat</t>
         </is>
       </c>
       <c r="F214" s="13" t="inlineStr">
         <is>
-          <t>F-IN-06</t>
+          <t>F-IN-19</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr"/>
@@ -9246,12 +9246,12 @@
     <row r="215">
       <c r="A215" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B215" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-01</t>
+          <t>TC-UP-06</t>
         </is>
       </c>
       <c r="C215" s="20" t="inlineStr">
@@ -9261,17 +9261,17 @@
       </c>
       <c r="D215" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Billing Resto → atur harga dan tanggal untuk sebuah resto</t>
+          <t>Biarkan unduhan selesai</t>
         </is>
       </c>
       <c r="E215" s="16" t="inlineStr">
         <is>
-          <t>Tersimpan; kartu restonya menampilkan harga, tanggal, dan tenggangnya</t>
+          <t>Notifikasi "ketuk untuk memasang"; pemasang Android terbuka</t>
         </is>
       </c>
       <c r="F215" s="16" t="inlineStr">
         <is>
-          <t>F-BL-01, F-BL-02</t>
+          <t>F-UP-06, F-IN-17</t>
         </is>
       </c>
       <c r="G215" s="16" t="inlineStr"/>
@@ -9281,12 +9281,12 @@
     <row r="216">
       <c r="A216" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B216" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-02</t>
+          <t>TC-UP-07</t>
         </is>
       </c>
       <c r="C216" s="19" t="inlineStr">
@@ -9296,17 +9296,17 @@
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru, buka Billing Resto</t>
+          <t>Matikan data seluler di tengah unduhan</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Sudah punya barisnya sendiri, berstatus Gratis</t>
+          <t>Pesannya menyebut masalah koneksi, satu kalimat, tanpa isi galat mentah</t>
         </is>
       </c>
       <c r="F216" s="13" t="inlineStr">
         <is>
-          <t>F-BL-06</t>
+          <t>F-UP-07, F-IN-19</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr"/>
@@ -9316,32 +9316,32 @@
     <row r="217">
       <c r="A217" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B217" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-03</t>
-        </is>
-      </c>
-      <c r="C217" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-08</t>
+        </is>
+      </c>
+      <c r="C217" s="22" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D217" s="16" t="inlineStr">
         <is>
-          <t>Setel harga Rp 0, lewatkan tanggal jatuh tempo jauh</t>
+          <t>Penuhi penyimpanan HP, lalu unduh</t>
         </is>
       </c>
       <c r="E217" s="16" t="inlineStr">
         <is>
-          <t>Tidak pernah terbit tagihan, tidak pernah terkunci</t>
+          <t>Pesannya menyebut penyimpanan penuh — dibedakan dari masalah koneksi</t>
         </is>
       </c>
       <c r="F217" s="16" t="inlineStr">
         <is>
-          <t>F-BL-04</t>
+          <t>F-UP-07</t>
         </is>
       </c>
       <c r="G217" s="16" t="inlineStr"/>
@@ -9351,32 +9351,32 @@
     <row r="218">
       <c r="A218" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B218" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-04</t>
-        </is>
-      </c>
-      <c r="C218" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-09</t>
+        </is>
+      </c>
+      <c r="C218" s="21" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>Matikan saklar langganan pada resto berbayar yang menunggak</t>
+          <t>Pakai jalur cadangan lewat peramban</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Tidak terkunci</t>
+          <t>Berkasnya terunduh</t>
         </is>
       </c>
       <c r="F218" s="13" t="inlineStr">
         <is>
-          <t>F-BL-05</t>
+          <t>F-IN-06</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="B219" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-05</t>
+          <t>TC-BL-01</t>
         </is>
       </c>
       <c r="C219" s="20" t="inlineStr">
@@ -9401,17 +9401,17 @@
       </c>
       <c r="D219" s="16" t="inlineStr">
         <is>
-          <t>Coba pilih tanggal tagihan 29, 30, atau 31</t>
+          <t>Super Admin → Billing Resto → atur harga dan tanggal untuk sebuah resto</t>
         </is>
       </c>
       <c r="E219" s="16" t="inlineStr">
         <is>
-          <t>Tidak tersedia di pilihan — hanya 1 sampai 28</t>
+          <t>Tersimpan; kartu restonya menampilkan harga, tanggal, dan tenggangnya</t>
         </is>
       </c>
       <c r="F219" s="16" t="inlineStr">
         <is>
-          <t>F-BL-02</t>
+          <t>F-BL-01, F-BL-02</t>
         </is>
       </c>
       <c r="G219" s="16" t="inlineStr"/>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="B220" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-06</t>
+          <t>TC-BL-02</t>
         </is>
       </c>
       <c r="C220" s="19" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Terbitkan tagihan sekarang dua kali beruntun</t>
+          <t>Buat resto baru, buka Billing Resto</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Tagihan tetap satu untuk periode itu</t>
+          <t>Sudah punya barisnya sendiri, berstatus Gratis</t>
         </is>
       </c>
       <c r="F220" s="13" t="inlineStr">
         <is>
-          <t>F-BL-08</t>
+          <t>F-BL-06</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr"/>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="B221" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-07</t>
+          <t>TC-BL-03</t>
         </is>
       </c>
       <c r="C221" s="18" t="inlineStr">
@@ -9471,17 +9471,17 @@
       </c>
       <c r="D221" s="16" t="inlineStr">
         <is>
-          <t>Setel jatuh tempo 3 hari lagi, buka aplikasi sebagai Kasir</t>
+          <t>Setel harga Rp 0, lewatkan tanggal jatuh tempo jauh</t>
         </is>
       </c>
       <c r="E221" s="16" t="inlineStr">
         <is>
-          <t>Pita pengingat tampil di atas layar; isi layarnya tetap bisa dipakai</t>
+          <t>Tidak pernah terbit tagihan, tidak pernah terkunci</t>
         </is>
       </c>
       <c r="F221" s="16" t="inlineStr">
         <is>
-          <t>F-BL-09</t>
+          <t>F-BL-04</t>
         </is>
       </c>
       <c r="G221" s="16" t="inlineStr"/>
@@ -9496,27 +9496,27 @@
       </c>
       <c r="B222" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-08</t>
-        </is>
-      </c>
-      <c r="C222" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-04</t>
+        </is>
+      </c>
+      <c r="C222" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>Setel jatuh tempo 4 hari lagi</t>
+          <t>Matikan saklar langganan pada resto berbayar yang menunggak</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Pita belum tampil</t>
+          <t>Tidak terkunci</t>
         </is>
       </c>
       <c r="F222" s="13" t="inlineStr">
         <is>
-          <t>F-BL-09</t>
+          <t>F-BL-05</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr"/>
@@ -9531,27 +9531,27 @@
       </c>
       <c r="B223" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-09</t>
-        </is>
-      </c>
-      <c r="C223" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-05</t>
+        </is>
+      </c>
+      <c r="C223" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D223" s="16" t="inlineStr">
         <is>
-          <t>Lewati jatuh tempo, masih dalam tenggang</t>
+          <t>Coba pilih tanggal tagihan 29, 30, atau 31</t>
         </is>
       </c>
       <c r="E223" s="16" t="inlineStr">
         <is>
-          <t>Pita berubah merah; aplikasi belum terkunci</t>
+          <t>Tidak tersedia di pilihan — hanya 1 sampai 28</t>
         </is>
       </c>
       <c r="F223" s="16" t="inlineStr">
         <is>
-          <t>F-BL-03, F-BL-10</t>
+          <t>F-BL-02</t>
         </is>
       </c>
       <c r="G223" s="16" t="inlineStr"/>
@@ -9566,27 +9566,27 @@
       </c>
       <c r="B224" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-10</t>
-        </is>
-      </c>
-      <c r="C224" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-06</t>
+        </is>
+      </c>
+      <c r="C224" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>Lewati tenggang, tagihan belum dibayar</t>
+          <t>Ketuk Terbitkan tagihan sekarang dua kali beruntun</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar diganti halaman Aplikasi Terkunci Sementara</t>
+          <t>Tagihan tetap satu untuk periode itu</t>
         </is>
       </c>
       <c r="F224" s="13" t="inlineStr">
         <is>
-          <t>F-BL-15</t>
+          <t>F-BL-08</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr"/>
@@ -9601,7 +9601,7 @@
       </c>
       <c r="B225" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-11</t>
+          <t>TC-BL-07</t>
         </is>
       </c>
       <c r="C225" s="18" t="inlineStr">
@@ -9611,17 +9611,17 @@
       </c>
       <c r="D225" s="16" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, coba buat pesanan lewat API langsung</t>
+          <t>Setel jatuh tempo 3 hari lagi, buka aplikasi sebagai Kasir</t>
         </is>
       </c>
       <c r="E225" s="16" t="inlineStr">
         <is>
-          <t>Ditolak database — bukan hanya layarnya yang menutup</t>
+          <t>Pita pengingat tampil di atas layar; isi layarnya tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F225" s="16" t="inlineStr">
         <is>
-          <t>F-BL-18, TSD §7.3</t>
+          <t>F-BL-09</t>
         </is>
       </c>
       <c r="G225" s="16" t="inlineStr"/>
@@ -9636,27 +9636,27 @@
       </c>
       <c r="B226" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-12</t>
-        </is>
-      </c>
-      <c r="C226" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-08</t>
+        </is>
+      </c>
+      <c r="C226" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, ketuk Lihat &amp; Bayar Tagihan</t>
+          <t>Setel jatuh tempo 4 hari lagi</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Layar tagihan terbuka dan bisa dipakai</t>
+          <t>Pita belum tampil</t>
         </is>
       </c>
       <c r="F226" s="13" t="inlineStr">
         <is>
-          <t>F-BL-16</t>
+          <t>F-BL-09</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr"/>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="B227" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-13</t>
+          <t>TC-BL-09</t>
         </is>
       </c>
       <c r="C227" s="18" t="inlineStr">
@@ -9681,17 +9681,17 @@
       </c>
       <c r="D227" s="16" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, ketuk Keluar</t>
+          <t>Lewati jatuh tempo, masih dalam tenggang</t>
         </is>
       </c>
       <c r="E227" s="16" t="inlineStr">
         <is>
-          <t>Berhasil keluar akun</t>
+          <t>Pita berubah merah; aplikasi belum terkunci</t>
         </is>
       </c>
       <c r="F227" s="16" t="inlineStr">
         <is>
-          <t>F-BL-16</t>
+          <t>F-BL-03, F-BL-10</t>
         </is>
       </c>
       <c r="G227" s="16" t="inlineStr"/>
@@ -9706,7 +9706,7 @@
       </c>
       <c r="B228" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14</t>
+          <t>TC-BL-10</t>
         </is>
       </c>
       <c r="C228" s="15" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Buat Virtual Account → pilih BCA</t>
+          <t>Lewati tenggang, tagihan belum dibayar</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Nomor VA tampil berikut nominal dan masa berlakunya</t>
+          <t>Seluruh layar diganti halaman Aplikasi Terkunci Sementara</t>
         </is>
       </c>
       <c r="F228" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11, F-BL-19</t>
+          <t>F-BL-15</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr"/>
@@ -9741,7 +9741,7 @@
       </c>
       <c r="B229" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14b</t>
+          <t>TC-BL-11</t>
         </is>
       </c>
       <c r="C229" s="18" t="inlineStr">
@@ -9751,17 +9751,17 @@
       </c>
       <c r="D229" s="16" t="inlineStr">
         <is>
-          <t>Tutup layar, buka lagi, ketuk lagi</t>
+          <t>Pada keadaan terkunci, coba buat pesanan lewat API langsung</t>
         </is>
       </c>
       <c r="E229" s="16" t="inlineStr">
         <is>
-          <t>Nomor VA sama, tidak diterbitkan yang baru</t>
+          <t>Ditolak database — bukan hanya layarnya yang menutup</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
         <is>
-          <t>F-BL-23</t>
+          <t>F-BL-18, TSD §7.3</t>
         </is>
       </c>
       <c r="G229" s="16" t="inlineStr"/>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="B230" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14c</t>
+          <t>TC-BL-12</t>
         </is>
       </c>
       <c r="C230" s="15" t="inlineStr">
@@ -9786,17 +9786,17 @@
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>Transfer tepat sesuai nominal ke VA itu</t>
+          <t>Pada keadaan terkunci, ketuk Lihat &amp; Bayar Tagihan</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Tagihan lunas sendiri dalam hitungan detik; kunci terbuka tanpa mengirim bukti</t>
+          <t>Layar tagihan terbuka dan bisa dipakai</t>
         </is>
       </c>
       <c r="F230" s="13" t="inlineStr">
         <is>
-          <t>F-BL-22</t>
+          <t>F-BL-16</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr"/>
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B231" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14d</t>
+          <t>TC-BL-13</t>
         </is>
       </c>
       <c r="C231" s="18" t="inlineStr">
@@ -9821,17 +9821,17 @@
       </c>
       <c r="D231" s="16" t="inlineStr">
         <is>
-          <t>Transfer kurang dari nominal</t>
+          <t>Pada keadaan terkunci, ketuk Keluar</t>
         </is>
       </c>
       <c r="E231" s="16" t="inlineStr">
         <is>
-          <t>Tidak melunasi; tagihan tetap terbuka</t>
+          <t>Berhasil keluar akun</t>
         </is>
       </c>
       <c r="F231" s="16" t="inlineStr">
         <is>
-          <t>F-BL-20</t>
+          <t>F-BL-16</t>
         </is>
       </c>
       <c r="G231" s="16" t="inlineStr"/>
@@ -9846,27 +9846,27 @@
       </c>
       <c r="B232" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14e</t>
-        </is>
-      </c>
-      <c r="C232" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-14</t>
+        </is>
+      </c>
+      <c r="C232" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Ganti Bank → pilih BNI</t>
+          <t>Ketuk Buat Virtual Account → pilih BCA</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Nomor VA baru untuk bank itu</t>
+          <t>Nomor VA tampil berikut nominal dan masa berlakunya</t>
         </is>
       </c>
       <c r="F232" s="13" t="inlineStr">
         <is>
-          <t>F-BL-19</t>
+          <t>F-BL-11, F-BL-19</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr"/>
@@ -9881,7 +9881,7 @@
       </c>
       <c r="B233" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14f</t>
+          <t>TC-BL-14b</t>
         </is>
       </c>
       <c r="C233" s="18" t="inlineStr">
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D233" s="16" t="inlineStr">
         <is>
-          <t>Periksa rekening tujuan dana VA di Dashboard Xendit</t>
+          <t>Tutup layar, buka lagi, ketuk lagi</t>
         </is>
       </c>
       <c r="E233" s="16" t="inlineStr">
         <is>
-          <t>Masuk ke akun KaataGo, bukan sub-akun resto</t>
+          <t>Nomor VA sama, tidak diterbitkan yang baru</t>
         </is>
       </c>
       <c r="F233" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11, TSD §7.3</t>
+          <t>F-BL-23</t>
         </is>
       </c>
       <c r="G233" s="16" t="inlineStr"/>
@@ -9916,7 +9916,7 @@
       </c>
       <c r="B234" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14g</t>
+          <t>TC-BL-14c</t>
         </is>
       </c>
       <c r="C234" s="15" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>Kirim callback palsu ke xendit-billing-webhook tanpa token</t>
+          <t>Transfer tepat sesuai nominal ke VA itu</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Ditolak 401; tagihan tidak berubah</t>
+          <t>Tagihan lunas sendiri dalam hitungan detik; kunci terbuka tanpa mengirim bukti</t>
         </is>
       </c>
       <c r="F234" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr"/>
@@ -9951,27 +9951,27 @@
       </c>
       <c r="B235" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14h</t>
-        </is>
-      </c>
-      <c r="C235" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-14d</t>
+        </is>
+      </c>
+      <c r="C235" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D235" s="16" t="inlineStr">
         <is>
-          <t>Xendit mengirim callback yang sama dua kali</t>
+          <t>Transfer kurang dari nominal</t>
         </is>
       </c>
       <c r="E235" s="16" t="inlineStr">
         <is>
-          <t>Tagihan tetap lunas sekali; catatan pelunasnya tidak berubah</t>
+          <t>Tidak melunasi; tagihan tetap terbuka</t>
         </is>
       </c>
       <c r="F235" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G235" s="16" t="inlineStr"/>
@@ -9986,7 +9986,7 @@
       </c>
       <c r="B236" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14i</t>
+          <t>TC-BL-14e</t>
         </is>
       </c>
       <c r="C236" s="19" t="inlineStr">
@@ -9996,17 +9996,17 @@
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>Unggah bukti transfer manual lewat jalur cadangan</t>
+          <t>Ketuk Ganti Bank → pilih BNI</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
+          <t>Nomor VA baru untuk bank itu</t>
         </is>
       </c>
       <c r="F236" s="13" t="inlineStr">
         <is>
-          <t>F-BL-24, F-BL-12</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr"/>
@@ -10021,27 +10021,27 @@
       </c>
       <c r="B237" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-26</t>
-        </is>
-      </c>
-      <c r="C237" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-14f</t>
+        </is>
+      </c>
+      <c r="C237" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D237" s="16" t="inlineStr">
         <is>
-          <t>Dengan kunci uji Xendit, buka tagihan ber-VA</t>
+          <t>Periksa rekening tujuan dana VA di Dashboard Xendit</t>
         </is>
       </c>
       <c r="E237" s="16" t="inlineStr">
         <is>
-          <t>Tombol Simulasikan Pembayaran muncul</t>
+          <t>Masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
       <c r="F237" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-11, TSD §7.3</t>
         </is>
       </c>
       <c r="G237" s="16" t="inlineStr"/>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="B238" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-27</t>
+          <t>TC-BL-14g</t>
         </is>
       </c>
       <c r="C238" s="15" t="inlineStr">
@@ -10066,17 +10066,17 @@
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Simulasikan Pembayaran</t>
+          <t>Kirim callback palsu ke xendit-billing-webhook tanpa token</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Tagihan jadi Lunas sendiri lewat webhook; kunci resto terbuka</t>
+          <t>Ditolak 401; tagihan tidak berubah</t>
         </is>
       </c>
       <c r="F238" s="13" t="inlineStr">
         <is>
-          <t>F-BL-22</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr"/>
@@ -10091,22 +10091,22 @@
       </c>
       <c r="B239" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-28</t>
-        </is>
-      </c>
-      <c r="C239" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14h</t>
+        </is>
+      </c>
+      <c r="C239" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D239" s="16" t="inlineStr">
         <is>
-          <t>Pasang kunci produksi Xendit, buka layar yang sama</t>
+          <t>Xendit mengirim callback yang sama dua kali</t>
         </is>
       </c>
       <c r="E239" s="16" t="inlineStr">
         <is>
-          <t>Tombol simulasi hilang sendiri</t>
+          <t>Tagihan tetap lunas sekali; catatan pelunasnya tidak berubah</t>
         </is>
       </c>
       <c r="F239" s="16" t="inlineStr">
@@ -10126,27 +10126,27 @@
       </c>
       <c r="B240" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-29</t>
-        </is>
-      </c>
-      <c r="C240" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14i</t>
+        </is>
+      </c>
+      <c r="C240" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>Buat diskon langganan setelah tagihan terbit → ketuk segarkan di Super Admin</t>
+          <t>Unggah bukti transfer manual lewat jalur cadangan</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Nominal tagihan turun; nomor VA lama dibuang</t>
+          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
         </is>
       </c>
       <c r="F240" s="13" t="inlineStr">
         <is>
-          <t>F-BL-05</t>
+          <t>F-BL-24, F-BL-12</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr"/>
@@ -10161,27 +10161,27 @@
       </c>
       <c r="B241" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-30</t>
-        </is>
-      </c>
-      <c r="C241" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-26</t>
+        </is>
+      </c>
+      <c r="C241" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D241" s="16" t="inlineStr">
         <is>
-          <t>Buat VA baru setelah nominalnya berubah</t>
+          <t>Dengan kunci uji Xendit, buka tagihan ber-VA</t>
         </is>
       </c>
       <c r="E241" s="16" t="inlineStr">
         <is>
-          <t>Nominalnya sesuai yang sudah dipotong</t>
+          <t>Tombol Simulasikan Pembayaran muncul</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>F-BL-20</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G241" s="16" t="inlineStr"/>
@@ -10196,7 +10196,7 @@
       </c>
       <c r="B242" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-15</t>
+          <t>TC-BL-27</t>
         </is>
       </c>
       <c r="C242" s="15" t="inlineStr">
@@ -10206,17 +10206,17 @@
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>Coba kirim bukti tanpa melampirkan foto</t>
+          <t>Ketuk Simulasikan Pembayaran</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Tombol Kirim mati</t>
+          <t>Tagihan jadi Lunas sendiri lewat webhook; kunci resto terbuka</t>
         </is>
       </c>
       <c r="F242" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr"/>
@@ -10231,7 +10231,7 @@
       </c>
       <c r="B243" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-16</t>
+          <t>TC-BL-28</t>
         </is>
       </c>
       <c r="C243" s="18" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="D243" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → tab Tagihan → Terima</t>
+          <t>Pasang kunci produksi Xendit, buka layar yang sama</t>
         </is>
       </c>
       <c r="E243" s="16" t="inlineStr">
         <is>
-          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
+          <t>Tombol simulasi hilang sendiri</t>
         </is>
       </c>
       <c r="F243" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G243" s="16" t="inlineStr"/>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="B244" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-17</t>
+          <t>TC-BL-29</t>
         </is>
       </c>
       <c r="C244" s="15" t="inlineStr">
@@ -10276,17 +10276,17 @@
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Tolak tanpa mengisi alasan</t>
+          <t>Buat diskon langganan setelah tagihan terbit → ketuk segarkan di Super Admin</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
+          <t>Nominal tagihan turun; nomor VA lama dibuang</t>
         </is>
       </c>
       <c r="F244" s="13" t="inlineStr">
         <is>
-          <t>F-BL-14</t>
+          <t>F-BL-05</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr"/>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="B245" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-18</t>
+          <t>TC-BL-30</t>
         </is>
       </c>
       <c r="C245" s="18" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="D245" s="16" t="inlineStr">
         <is>
-          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
+          <t>Buat VA baru setelah nominalnya berubah</t>
         </is>
       </c>
       <c r="E245" s="16" t="inlineStr">
         <is>
-          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
+          <t>Nominalnya sesuai yang sudah dipotong</t>
         </is>
       </c>
       <c r="F245" s="16" t="inlineStr">
         <is>
-          <t>F-BL-14, F-BL-15</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G245" s="16" t="inlineStr"/>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="B246" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-19</t>
+          <t>TC-BL-15</t>
         </is>
       </c>
       <c r="C246" s="15" t="inlineStr">
@@ -10346,17 +10346,17 @@
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Super Admin saat ada resto terkunci</t>
+          <t>Coba kirim bukti tanpa melampirkan foto</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Tidak terkunci sama sekali</t>
+          <t>Tombol Kirim mati</t>
         </is>
       </c>
       <c r="F246" s="13" t="inlineStr">
         <is>
-          <t>F-BL-17</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr"/>
@@ -10371,7 +10371,7 @@
       </c>
       <c r="B247" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-20</t>
+          <t>TC-BL-16</t>
         </is>
       </c>
       <c r="C247" s="18" t="inlineStr">
@@ -10381,17 +10381,17 @@
       </c>
       <c r="D247" s="16" t="inlineStr">
         <is>
-          <t>Sebagai resto terkunci, coba ubah harga produk</t>
+          <t>Super Admin → tab Tagihan → Terima</t>
         </is>
       </c>
       <c r="E247" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — katalog ikut dibekukan</t>
+          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
         </is>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
-          <t>F-BL-18</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G247" s="16" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="B248" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-21</t>
+          <t>TC-BL-17</t>
         </is>
       </c>
       <c r="C248" s="15" t="inlineStr">
@@ -10416,17 +10416,17 @@
       </c>
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
+          <t>Super Admin → Tolak tanpa mengisi alasan</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Resto B tidak terpengaruh</t>
+          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
         </is>
       </c>
       <c r="F248" s="13" t="inlineStr">
         <is>
-          <t>F-BL-15, A-10</t>
+          <t>F-BL-14</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr"/>
@@ -10441,7 +10441,7 @@
       </c>
       <c r="B249" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-22</t>
+          <t>TC-BL-18</t>
         </is>
       </c>
       <c r="C249" s="18" t="inlineStr">
@@ -10451,17 +10451,17 @@
       </c>
       <c r="D249" s="16" t="inlineStr">
         <is>
-          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
+          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
         </is>
       </c>
       <c r="E249" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — hanya Super Admin</t>
+          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
         </is>
       </c>
       <c r="F249" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-14, F-BL-15</t>
         </is>
       </c>
       <c r="G249" s="16" t="inlineStr"/>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="B250" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-23</t>
+          <t>TC-BL-19</t>
         </is>
       </c>
       <c r="C250" s="15" t="inlineStr">
@@ -10486,17 +10486,17 @@
       </c>
       <c r="D250" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
+          <t>Login sebagai Super Admin saat ada resto terkunci</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tidak terkunci sama sekali</t>
         </is>
       </c>
       <c r="F250" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13, TSD §7.3</t>
+          <t>F-BL-17</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr"/>
@@ -10511,27 +10511,27 @@
       </c>
       <c r="B251" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-24</t>
-        </is>
-      </c>
-      <c r="C251" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-20</t>
+        </is>
+      </c>
+      <c r="C251" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D251" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
+          <t>Sebagai resto terkunci, coba ubah harga produk</t>
         </is>
       </c>
       <c r="E251" s="16" t="inlineStr">
         <is>
-          <t>Tidak terkunci karena gagal memeriksa</t>
+          <t>Ditolak — katalog ikut dibekukan</t>
         </is>
       </c>
       <c r="F251" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-18</t>
         </is>
       </c>
       <c r="G251" s="16" t="inlineStr"/>
@@ -10546,27 +10546,27 @@
       </c>
       <c r="B252" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-25</t>
-        </is>
-      </c>
-      <c r="C252" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-21</t>
+        </is>
+      </c>
+      <c r="C252" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>Owner → Tagihan Langganan</t>
+          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Terbuka, memuat paket dan riwayat tagihan</t>
+          <t>Resto B tidak terpengaruh</t>
         </is>
       </c>
       <c r="F252" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-15, A-10</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr"/>
@@ -10576,12 +10576,12 @@
     <row r="253">
       <c r="A253" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B253" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-01</t>
+          <t>TC-BL-22</t>
         </is>
       </c>
       <c r="C253" s="18" t="inlineStr">
@@ -10591,17 +10591,17 @@
       </c>
       <c r="D253" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Riwayat Langganan</t>
+          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
         </is>
       </c>
       <c r="E253" s="16" t="inlineStr">
         <is>
-          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F253" s="16" t="inlineStr">
         <is>
-          <t>F-PF-01</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G253" s="16" t="inlineStr"/>
@@ -10611,32 +10611,32 @@
     <row r="254">
       <c r="A254" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B254" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-02</t>
-        </is>
-      </c>
-      <c r="C254" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-23</t>
+        </is>
+      </c>
+      <c r="C254" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>Periksa penanda jalur pelunasan tiap baris</t>
+          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F254" s="13" t="inlineStr">
         <is>
-          <t>F-PF-02</t>
+          <t>F-BL-13, TSD §7.3</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr"/>
@@ -10646,32 +10646,32 @@
     <row r="255">
       <c r="A255" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B255" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-03</t>
-        </is>
-      </c>
-      <c r="C255" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-24</t>
+        </is>
+      </c>
+      <c r="C255" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D255" s="16" t="inlineStr">
         <is>
-          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
+          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
         </is>
       </c>
       <c r="E255" s="16" t="inlineStr">
         <is>
-          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
+          <t>Tidak terkunci karena gagal memeriksa</t>
         </is>
       </c>
       <c r="F255" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03, F-PF-05</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G255" s="16" t="inlineStr"/>
@@ -10681,32 +10681,32 @@
     <row r="256">
       <c r="A256" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B256" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-04</t>
-        </is>
-      </c>
-      <c r="C256" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-25</t>
+        </is>
+      </c>
+      <c r="C256" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>Simpan diskon tanpa memilih resto</t>
+          <t>Owner → Tagihan Langganan</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
+          <t>Terbuka, memuat paket dan riwayat tagihan</t>
         </is>
       </c>
       <c r="F256" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr"/>
@@ -10721,27 +10721,27 @@
       </c>
       <c r="B257" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-05</t>
-        </is>
-      </c>
-      <c r="C257" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-01</t>
+        </is>
+      </c>
+      <c r="C257" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D257" s="16" t="inlineStr">
         <is>
-          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
+          <t>Super Admin → Finance → Riwayat Langganan</t>
         </is>
       </c>
       <c r="E257" s="16" t="inlineStr">
         <is>
-          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
+          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
         </is>
       </c>
       <c r="F257" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-PF-01</t>
         </is>
       </c>
       <c r="G257" s="16" t="inlineStr"/>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B258" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-06</t>
+          <t>TC-PF-02</t>
         </is>
       </c>
       <c r="C258" s="19" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
+          <t>Periksa penanda jalur pelunasan tiap baris</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
+          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
         </is>
       </c>
       <c r="F258" s="13" t="inlineStr">
         <is>
-          <t>F-PF-04</t>
+          <t>F-PF-02</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr"/>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="B259" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-07</t>
+          <t>TC-PF-03</t>
         </is>
       </c>
       <c r="C259" s="18" t="inlineStr">
@@ -10801,17 +10801,17 @@
       </c>
       <c r="D259" s="16" t="inlineStr">
         <is>
-          <t>Hapus diskon setelah tagihan terbit</t>
+          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
         </is>
       </c>
       <c r="E259" s="16" t="inlineStr">
         <is>
-          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
+          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
         </is>
       </c>
       <c r="F259" s="16" t="inlineStr">
         <is>
-          <t>F-PF-05</t>
+          <t>F-PF-03, F-PF-05</t>
         </is>
       </c>
       <c r="G259" s="16" t="inlineStr"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="B260" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-08</t>
+          <t>TC-PF-04</t>
         </is>
       </c>
       <c r="C260" s="15" t="inlineStr">
@@ -10836,17 +10836,17 @@
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
+          <t>Simpan diskon tanpa memilih resto</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Dua baris: pendapatan kredit, diskon debit</t>
+          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
         </is>
       </c>
       <c r="F260" s="13" t="inlineStr">
         <is>
-          <t>F-PF-06, F-PF-07</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr"/>
@@ -10861,27 +10861,27 @@
       </c>
       <c r="B261" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-09</t>
-        </is>
-      </c>
-      <c r="C261" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-05</t>
+        </is>
+      </c>
+      <c r="C261" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D261" s="16" t="inlineStr">
         <is>
-          <t>Tagihan ditolak lalu diterima lagi</t>
+          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
         </is>
       </c>
       <c r="E261" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
+          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
         </is>
       </c>
       <c r="F261" s="16" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G261" s="16" t="inlineStr"/>
@@ -10896,27 +10896,27 @@
       </c>
       <c r="B262" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-10</t>
-        </is>
-      </c>
-      <c r="C262" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-06</t>
+        </is>
+      </c>
+      <c r="C262" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL resto yang membayar</t>
+          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada baris pendapatan langganan di sana</t>
+          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
         </is>
       </c>
       <c r="F262" s="13" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-04</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr"/>
@@ -10931,27 +10931,27 @@
       </c>
       <c r="B263" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-11</t>
-        </is>
-      </c>
-      <c r="C263" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-07</t>
+        </is>
+      </c>
+      <c r="C263" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D263" s="16" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account KaataGo</t>
+          <t>Hapus diskon setelah tagihan terbit</t>
         </is>
       </c>
       <c r="E263" s="16" t="inlineStr">
         <is>
-          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
+          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
         </is>
       </c>
       <c r="F263" s="16" t="inlineStr">
         <is>
-          <t>F-PF-08</t>
+          <t>F-PF-05</t>
         </is>
       </c>
       <c r="G263" s="16" t="inlineStr"/>
@@ -10966,27 +10966,27 @@
       </c>
       <c r="B264" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-12</t>
-        </is>
-      </c>
-      <c r="C264" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-08</t>
+        </is>
+      </c>
+      <c r="C264" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
+          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Bekerja sama seperti di resto</t>
+          <t>Dua baris: pendapatan kredit, diskon debit</t>
         </is>
       </c>
       <c r="F264" s="13" t="inlineStr">
         <is>
-          <t>F-PF-09</t>
+          <t>F-PF-06, F-PF-07</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B265" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-13</t>
+          <t>TC-PF-09</t>
         </is>
       </c>
       <c r="C265" s="18" t="inlineStr">
@@ -11011,17 +11011,17 @@
       </c>
       <c r="D265" s="16" t="inlineStr">
         <is>
-          <t>Telusuri menu Finance KaataGo</t>
+          <t>Tagihan ditolak lalu diterima lagi</t>
         </is>
       </c>
       <c r="E265" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada Setor Saldo Cash</t>
+          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
         </is>
       </c>
       <c r="F265" s="16" t="inlineStr">
         <is>
-          <t>F-PF-10</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G265" s="16" t="inlineStr"/>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="B266" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-14</t>
+          <t>TC-PF-10</t>
         </is>
       </c>
       <c r="C266" s="15" t="inlineStr">
@@ -11046,17 +11046,17 @@
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL Semua Resto</t>
+          <t>Buka Jurnal GL resto yang membayar</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
+          <t>Tidak ada baris pendapatan langganan di sana</t>
         </is>
       </c>
       <c r="F266" s="13" t="inlineStr">
         <is>
-          <t>F-PF-11</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr"/>
@@ -11071,27 +11071,27 @@
       </c>
       <c r="B267" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-15</t>
-        </is>
-      </c>
-      <c r="C267" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-11</t>
+        </is>
+      </c>
+      <c r="C267" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D267" s="16" t="inlineStr">
         <is>
-          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E267" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun — hanya bisa dilihat</t>
+          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F267" s="16" t="inlineStr">
         <is>
-          <t>F-PF-12</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G267" s="16" t="inlineStr"/>
@@ -11106,27 +11106,27 @@
       </c>
       <c r="B268" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-16</t>
-        </is>
-      </c>
-      <c r="C268" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-12</t>
+        </is>
+      </c>
+      <c r="C268" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
+          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Bekerja sama seperti di resto</t>
         </is>
       </c>
       <c r="F268" s="13" t="inlineStr">
         <is>
-          <t>F-PF-12, TSD §7.4</t>
+          <t>F-PF-09</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr"/>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="B269" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-17</t>
+          <t>TC-PF-13</t>
         </is>
       </c>
       <c r="C269" s="18" t="inlineStr">
@@ -11151,17 +11151,17 @@
       </c>
       <c r="D269" s="16" t="inlineStr">
         <is>
-          <t>Buka Pilih Resto sebagai pelanggan</t>
+          <t>Telusuri menu Finance KaataGo</t>
         </is>
       </c>
       <c r="E269" s="16" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul di daftar mana pun</t>
+          <t>Tidak ada Setor Saldo Cash</t>
         </is>
       </c>
       <c r="F269" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-10</t>
         </is>
       </c>
       <c r="G269" s="16" t="inlineStr"/>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="B270" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-18</t>
+          <t>TC-PF-14</t>
         </is>
       </c>
       <c r="C270" s="15" t="inlineStr">
@@ -11186,17 +11186,17 @@
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
+          <t>Buka Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
+          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
         </is>
       </c>
       <c r="F270" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-11</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr"/>
@@ -11211,27 +11211,27 @@
       </c>
       <c r="B271" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-19</t>
-        </is>
-      </c>
-      <c r="C271" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-15</t>
+        </is>
+      </c>
+      <c r="C271" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D271" s="16" t="inlineStr">
         <is>
-          <t>Buka Diskon Langganan sebagai Owner resto</t>
+          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E271" s="16" t="inlineStr">
         <is>
-          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
+          <t>Tidak ada satu pun — hanya bisa dilihat</t>
         </is>
       </c>
       <c r="F271" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-PF-12</t>
         </is>
       </c>
       <c r="G271" s="16" t="inlineStr"/>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="B272" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-20</t>
+          <t>TC-PF-16</t>
         </is>
       </c>
       <c r="C272" s="15" t="inlineStr">
@@ -11256,17 +11256,17 @@
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan total debit/kredit Jurnal Semua Resto dengan Jurnal GL resto itu (saring ke resto yang sama)</t>
+          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Angkanya sama persis</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F272" s="13" t="inlineStr">
         <is>
-          <t>F-PF-14</t>
+          <t>F-PF-12, TSD §7.4</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr"/>
@@ -11281,7 +11281,7 @@
       </c>
       <c r="B273" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-21</t>
+          <t>TC-PF-17</t>
         </is>
       </c>
       <c r="C273" s="18" t="inlineStr">
@@ -11291,17 +11291,17 @@
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>Batalkan sebuah pengeluaran, lihat kedua layar jurnal</t>
+          <t>Buka Pilih Resto sebagai pelanggan</t>
         </is>
       </c>
       <c r="E273" s="16" t="inlineStr">
         <is>
-          <t>Total tidak naik; keterangan "N pembatalan tidak dihitung" muncul</t>
+          <t>KaataGo tidak muncul di daftar mana pun</t>
         </is>
       </c>
       <c r="F273" s="16" t="inlineStr">
         <is>
-          <t>F-PF-14</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G273" s="16" t="inlineStr"/>
@@ -11316,27 +11316,27 @@
       </c>
       <c r="B274" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-22</t>
-        </is>
-      </c>
-      <c r="C274" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-18</t>
+        </is>
+      </c>
+      <c r="C274" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>Cari baris pembatalan di daftar</t>
+          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Tetap tampil, bertanda PEMBATALAN</t>
+          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
         </is>
       </c>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>F-PF-15</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr"/>
@@ -11351,27 +11351,27 @@
       </c>
       <c r="B275" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-23</t>
-        </is>
-      </c>
-      <c r="C275" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-19</t>
+        </is>
+      </c>
+      <c r="C275" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D275" s="16" t="inlineStr">
         <is>
-          <t>Saring ke sebuah resto, lalu pilih Semua resto lagi</t>
+          <t>Buka Diskon Langganan sebagai Owner resto</t>
         </is>
       </c>
       <c r="E275" s="16" t="inlineStr">
         <is>
-          <t>Kembali menampilkan seluruh resto — bukan tetap tersaring</t>
+          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
         </is>
       </c>
       <c r="F275" s="16" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G275" s="16" t="inlineStr"/>
@@ -11386,7 +11386,7 @@
       </c>
       <c r="B276" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-24</t>
+          <t>TC-PF-20</t>
         </is>
       </c>
       <c r="C276" s="15" t="inlineStr">
@@ -11396,17 +11396,17 @@
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>Saring ke resto A, lalu saring lagi ke resto B yang punya jurnal</t>
+          <t>Bandingkan total debit/kredit Jurnal Semua Resto dengan Jurnal GL resto itu (saring ke resto yang sama)</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Isinya berganti ke jurnal resto B</t>
+          <t>Angkanya sama persis</t>
         </is>
       </c>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>F-PF-14</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr"/>
@@ -11421,27 +11421,27 @@
       </c>
       <c r="B277" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-25</t>
-        </is>
-      </c>
-      <c r="C277" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-21</t>
+        </is>
+      </c>
+      <c r="C277" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D277" s="16" t="inlineStr">
         <is>
-          <t>Perhatikan pita di atas layar sesudah menyaring</t>
+          <t>Batalkan sebuah pengeluaran, lihat kedua layar jurnal</t>
         </is>
       </c>
       <c r="E277" s="16" t="inlineStr">
         <is>
-          <t>Nama restonya tertulis, dengan tombol × untuk melepasnya</t>
+          <t>Total tidak naik; keterangan "N pembatalan tidak dihitung" muncul</t>
         </is>
       </c>
       <c r="F277" s="16" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>F-PF-14</t>
         </is>
       </c>
       <c r="G277" s="16" t="inlineStr"/>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="B278" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-26</t>
+          <t>TC-PF-22</t>
         </is>
       </c>
       <c r="C278" s="19" t="inlineStr">
@@ -11466,17 +11466,17 @@
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>Buka daftar saringan</t>
+          <t>Cari baris pembatalan di daftar</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Resto yang belum punya jurnal ditandai "Belum ada jurnal"</t>
+          <t>Tetap tampil, bertanda PEMBATALAN</t>
         </is>
       </c>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>F-PF-17</t>
+          <t>F-PF-15</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr"/>
@@ -11491,27 +11491,27 @@
       </c>
       <c r="B279" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-27</t>
-        </is>
-      </c>
-      <c r="C279" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-23</t>
+        </is>
+      </c>
+      <c r="C279" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>Perhatikan pengelompokan</t>
+          <t>Saring ke sebuah resto, lalu pilih Semua resto lagi</t>
         </is>
       </c>
       <c r="E279" s="16" t="inlineStr">
         <is>
-          <t>Per tanggal, bisa dilipat; tanggal terbaru terbuka, sisanya tertutup</t>
+          <t>Kembali menampilkan seluruh resto — bukan tetap tersaring</t>
         </is>
       </c>
       <c r="F279" s="16" t="inlineStr">
         <is>
-          <t>F-PF-18</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G279" s="16" t="inlineStr"/>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B280" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-28</t>
+          <t>TC-PF-24</t>
         </is>
       </c>
       <c r="C280" s="15" t="inlineStr">
@@ -11536,17 +11536,17 @@
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account resto mana pun</t>
+          <t>Saring ke resto A, lalu saring lagi ke resto B yang punya jurnal</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>GL Diskon punya bagiannya dan nomornya sudah terisi</t>
+          <t>Isinya berganti ke jurnal resto B</t>
         </is>
       </c>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>F-PF-19, F-DS-09</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr"/>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="B281" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-29</t>
+          <t>TC-PF-25</t>
         </is>
       </c>
       <c r="C281" s="20" t="inlineStr">
@@ -11571,17 +11571,17 @@
       </c>
       <c r="D281" s="16" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account KaataGo</t>
+          <t>Perhatikan pita di atas layar sesudah menyaring</t>
         </is>
       </c>
       <c r="E281" s="16" t="inlineStr">
         <is>
-          <t>Ada bagian GL Langganan; penghitung akun tidak pernah menyisakan yang mustahil terisi</t>
+          <t>Nama restonya tertulis, dengan tombol × untuk melepasnya</t>
         </is>
       </c>
       <c r="F281" s="16" t="inlineStr">
         <is>
-          <t>F-PF-19</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G281" s="16" t="inlineStr"/>
@@ -11596,27 +11596,27 @@
       </c>
       <c r="B282" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-30</t>
-        </is>
-      </c>
-      <c r="C282" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-26</t>
+        </is>
+      </c>
+      <c r="C282" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
-          <t>Pesan menu berpromo, bayar, buka Jurnal GL</t>
+          <t>Buka daftar saringan</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Baris GL Diskon menyebut nama promonya</t>
+          <t>Resto yang belum punya jurnal ditandai "Belum ada jurnal"</t>
         </is>
       </c>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>F-PF-20, F-DS-13</t>
+          <t>F-PF-17</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr"/>
@@ -11631,27 +11631,27 @@
       </c>
       <c r="B283" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-31</t>
-        </is>
-      </c>
-      <c r="C283" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-27</t>
+        </is>
+      </c>
+      <c r="C283" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D283" s="16" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL Semua Resto sesudah ada tagihan langganan lunas</t>
+          <t>Perhatikan pengelompokan</t>
         </is>
       </c>
       <c r="E283" s="16" t="inlineStr">
         <is>
-          <t>Baris pendapatan langganan tidak muncul di sana</t>
+          <t>Per tanggal, bisa dilipat; tanggal terbaru terbuka, sisanya tertutup</t>
         </is>
       </c>
       <c r="F283" s="16" t="inlineStr">
         <is>
-          <t>F-PF-21</t>
+          <t>F-PF-18</t>
         </is>
       </c>
       <c r="G283" s="16" t="inlineStr"/>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B284" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-32</t>
+          <t>TC-PF-28</t>
         </is>
       </c>
       <c r="C284" s="15" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>Buka daftar saringan resto</t>
+          <t>Buka Mapping GL Account resto mana pun</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>KaataGo tidak ada di daftarnya</t>
+          <t>GL Diskon punya bagiannya dan nomornya sudah terisi</t>
         </is>
       </c>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>F-PF-21</t>
+          <t>F-PF-19, F-DS-09</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr"/>
@@ -11701,27 +11701,27 @@
       </c>
       <c r="B285" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-33</t>
-        </is>
-      </c>
-      <c r="C285" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-29</t>
+        </is>
+      </c>
+      <c r="C285" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D285" s="16" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL KaataGo</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E285" s="16" t="inlineStr">
         <is>
-          <t>Pendapatan langganan ada di sana, dan Saldo Total tidak nol</t>
+          <t>Ada bagian GL Langganan; penghitung akun tidak pernah menyisakan yang mustahil terisi</t>
         </is>
       </c>
       <c r="F285" s="16" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-19</t>
         </is>
       </c>
       <c r="G285" s="16" t="inlineStr"/>
@@ -11736,27 +11736,27 @@
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-34</t>
-        </is>
-      </c>
-      <c r="C286" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-30</t>
+        </is>
+      </c>
+      <c r="C286" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>Periksa nomor akun di Jurnal GL KaataGo</t>
+          <t>Pesan menu berpromo, bayar, buka Jurnal GL</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Golongan 11xxxxx, berbeda dari 19xxxxx milik resto</t>
+          <t>Baris GL Diskon menyebut nama promonya</t>
         </is>
       </c>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>F-PF-08</t>
+          <t>F-PF-20, F-DS-13</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr"/>
@@ -11766,12 +11766,12 @@
     <row r="287">
       <c r="A287" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B287" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-PF-31</t>
         </is>
       </c>
       <c r="C287" s="18" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="D287" s="16" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Buka Jurnal GL Semua Resto sesudah ada tagihan langganan lunas</t>
         </is>
       </c>
       <c r="E287" s="16" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Baris pendapatan langganan tidak muncul di sana</t>
         </is>
       </c>
       <c r="F287" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-21</t>
         </is>
       </c>
       <c r="G287" s="16" t="inlineStr"/>
@@ -11801,12 +11801,12 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B288" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-PF-32</t>
         </is>
       </c>
       <c r="C288" s="15" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Buka daftar saringan resto</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>KaataGo tidak ada di daftarnya</t>
         </is>
       </c>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-21</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr"/>
@@ -11836,12 +11836,12 @@
     <row r="289">
       <c r="A289" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B289" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-PF-33</t>
         </is>
       </c>
       <c r="C289" s="18" t="inlineStr">
@@ -11851,17 +11851,17 @@
       </c>
       <c r="D289" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E289" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Pendapatan langganan ada di sana, dan Saldo Total tidak nol</t>
         </is>
       </c>
       <c r="F289" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G289" s="16" t="inlineStr"/>
@@ -11871,32 +11871,32 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B290" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
-        </is>
-      </c>
-      <c r="C290" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-34</t>
+        </is>
+      </c>
+      <c r="C290" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Periksa nomor akun di Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Golongan 11xxxxx, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr"/>
@@ -11911,7 +11911,7 @@
       </c>
       <c r="B291" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-TS-01</t>
         </is>
       </c>
       <c r="C291" s="18" t="inlineStr">
@@ -11921,17 +11921,17 @@
       </c>
       <c r="D291" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E291" s="16" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F291" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G291" s="16" t="inlineStr"/>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="B292" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-TS-02</t>
         </is>
       </c>
       <c r="C292" s="15" t="inlineStr">
@@ -11956,17 +11956,17 @@
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr"/>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="B293" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-TS-03</t>
         </is>
       </c>
       <c r="C293" s="18" t="inlineStr">
@@ -11991,17 +11991,17 @@
       </c>
       <c r="D293" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E293" s="16" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F293" s="16" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G293" s="16" t="inlineStr"/>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="B294" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
+          <t>TC-TS-04</t>
         </is>
       </c>
       <c r="C294" s="15" t="inlineStr">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr"/>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="B295" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-TS-05</t>
         </is>
       </c>
       <c r="C295" s="18" t="inlineStr">
@@ -12061,17 +12061,17 @@
       </c>
       <c r="D295" s="16" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E295" s="16" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F295" s="16" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G295" s="16" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="B296" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C296" s="15" t="inlineStr">
@@ -12096,17 +12096,17 @@
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr"/>
@@ -12121,27 +12121,27 @@
       </c>
       <c r="B297" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
-        </is>
-      </c>
-      <c r="C297" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-07</t>
+        </is>
+      </c>
+      <c r="C297" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D297" s="16" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E297" s="16" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F297" s="16" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G297" s="16" t="inlineStr"/>
@@ -12156,27 +12156,27 @@
       </c>
       <c r="B298" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C298" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C298" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E298" s="13" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr"/>
@@ -12191,27 +12191,27 @@
       </c>
       <c r="B299" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C299" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C299" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D299" s="16" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E299" s="16" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F299" s="16" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G299" s="16" t="inlineStr"/>
@@ -12226,7 +12226,7 @@
       </c>
       <c r="B300" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-TS-10</t>
         </is>
       </c>
       <c r="C300" s="15" t="inlineStr">
@@ -12236,17 +12236,17 @@
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E300" s="13" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F300" s="13" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G300" s="13" t="inlineStr"/>
@@ -12261,27 +12261,27 @@
       </c>
       <c r="B301" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
-        </is>
-      </c>
-      <c r="C301" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-11</t>
+        </is>
+      </c>
+      <c r="C301" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D301" s="16" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E301" s="16" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F301" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G301" s="16" t="inlineStr"/>
@@ -12296,27 +12296,27 @@
       </c>
       <c r="B302" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
-        </is>
-      </c>
-      <c r="C302" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C302" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D302" s="13" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E302" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F302" s="13" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr"/>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="B303" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
+          <t>TC-TS-13</t>
         </is>
       </c>
       <c r="C303" s="20" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="D303" s="16" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E303" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F303" s="16" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G303" s="16" t="inlineStr"/>
@@ -12366,27 +12366,27 @@
       </c>
       <c r="B304" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C304" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-14</t>
+        </is>
+      </c>
+      <c r="C304" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E304" s="13" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F304" s="13" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr"/>
@@ -12401,27 +12401,27 @@
       </c>
       <c r="B305" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C305" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C305" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D305" s="16" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E305" s="16" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F305" s="16" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G305" s="16" t="inlineStr"/>
@@ -12431,12 +12431,12 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B306" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
+          <t>TC-TS-16</t>
         </is>
       </c>
       <c r="C306" s="15" t="inlineStr">
@@ -12446,17 +12446,17 @@
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
         </is>
       </c>
       <c r="E306" s="13" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F306" s="13" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>F-PG-02, TSD §7.1</t>
         </is>
       </c>
       <c r="G306" s="13" t="inlineStr"/>
@@ -12466,32 +12466,32 @@
     <row r="307">
       <c r="A307" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B307" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
-        </is>
-      </c>
-      <c r="C307" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C307" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D307" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
         </is>
       </c>
       <c r="E307" s="16" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
         </is>
       </c>
       <c r="F307" s="16" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §1.2</t>
         </is>
       </c>
       <c r="G307" s="16" t="inlineStr"/>
@@ -12501,32 +12501,32 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B308" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
-        </is>
-      </c>
-      <c r="C308" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C308" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
         </is>
       </c>
       <c r="E308" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
         </is>
       </c>
       <c r="F308" s="13" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>TSD §6.5</t>
         </is>
       </c>
       <c r="G308" s="13" t="inlineStr"/>
@@ -12536,32 +12536,32 @@
     <row r="309">
       <c r="A309" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B309" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
-        </is>
-      </c>
-      <c r="C309" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C309" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D309" s="16" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Hapus resto uji</t>
         </is>
       </c>
       <c r="E309" s="16" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
         </is>
       </c>
       <c r="F309" s="16" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>TSD §4.0</t>
         </is>
       </c>
       <c r="G309" s="16" t="inlineStr"/>
@@ -12576,7 +12576,7 @@
       </c>
       <c r="B310" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-RG-01</t>
         </is>
       </c>
       <c r="C310" s="15" t="inlineStr">
@@ -12586,17 +12586,17 @@
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
         </is>
       </c>
       <c r="E310" s="13" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
         </is>
       </c>
       <c r="F310" s="13" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>F-KS-09</t>
         </is>
       </c>
       <c r="G310" s="13" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B311" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-RG-02</t>
         </is>
       </c>
       <c r="C311" s="18" t="inlineStr">
@@ -12621,17 +12621,17 @@
       </c>
       <c r="D311" s="16" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
         </is>
       </c>
       <c r="E311" s="16" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
         </is>
       </c>
       <c r="F311" s="16" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>F-PP-09, A-13</t>
         </is>
       </c>
       <c r="G311" s="16" t="inlineStr"/>
@@ -12646,27 +12646,27 @@
       </c>
       <c r="B312" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C312" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C312" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
         </is>
       </c>
       <c r="E312" s="13" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Tidak muncul sama sekali</t>
         </is>
       </c>
       <c r="F312" s="13" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="G312" s="13" t="inlineStr"/>
@@ -12681,27 +12681,27 @@
       </c>
       <c r="B313" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C313" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C313" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D313" s="16" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
         </is>
       </c>
       <c r="E313" s="16" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Nominalnya sama dengan yang diajukan</t>
         </is>
       </c>
       <c r="F313" s="16" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>F-FN-03</t>
         </is>
       </c>
       <c r="G313" s="16" t="inlineStr"/>
@@ -12716,27 +12716,27 @@
       </c>
       <c r="B314" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
-        </is>
-      </c>
-      <c r="C314" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C314" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
         </is>
       </c>
       <c r="E314" s="13" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
         </is>
       </c>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr"/>
@@ -12751,27 +12751,27 @@
       </c>
       <c r="B315" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
-        </is>
-      </c>
-      <c r="C315" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C315" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
         </is>
       </c>
       <c r="E315" s="16" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
         </is>
       </c>
       <c r="F315" s="16" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-DS-10, F-DS-12</t>
         </is>
       </c>
       <c r="G315" s="16" t="inlineStr"/>
@@ -12786,7 +12786,7 @@
       </c>
       <c r="B316" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
+          <t>TC-RG-07</t>
         </is>
       </c>
       <c r="C316" s="19" t="inlineStr">
@@ -12796,17 +12796,17 @@
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
         </is>
       </c>
       <c r="E316" s="13" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
         </is>
       </c>
       <c r="F316" s="13" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>F-IN-15</t>
         </is>
       </c>
       <c r="G316" s="13" t="inlineStr"/>
@@ -12821,7 +12821,7 @@
       </c>
       <c r="B317" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
+          <t>TC-RG-08</t>
         </is>
       </c>
       <c r="C317" s="20" t="inlineStr">
@@ -12831,17 +12831,17 @@
       </c>
       <c r="D317" s="16" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
         </is>
       </c>
       <c r="E317" s="16" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Daftar menu termuat</t>
         </is>
       </c>
       <c r="F317" s="16" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>F-DS-01</t>
         </is>
       </c>
       <c r="G317" s="16" t="inlineStr"/>
@@ -12856,27 +12856,27 @@
       </c>
       <c r="B318" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
-        </is>
-      </c>
-      <c r="C318" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C318" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
         </is>
       </c>
       <c r="E318" s="13" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Detail jurnal terbuka</t>
         </is>
       </c>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-KS-13</t>
         </is>
       </c>
       <c r="G318" s="13" t="inlineStr"/>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B319" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
+          <t>TC-RG-10</t>
         </is>
       </c>
       <c r="C319" s="20" t="inlineStr">
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D319" s="16" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
         </is>
       </c>
       <c r="E319" s="16" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Seluruh layar berganti bersih</t>
         </is>
       </c>
       <c r="F319" s="16" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>A-18</t>
         </is>
       </c>
       <c r="G319" s="16" t="inlineStr"/>
@@ -12921,25 +12921,165 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B320" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C320" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D320" s="13" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E320" s="13" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F320" s="13" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G320" s="13" t="inlineStr"/>
+      <c r="H320" s="13" t="inlineStr"/>
+      <c r="I320" s="13" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B321" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C321" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D321" s="16" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E321" s="16" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F321" s="16" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G321" s="16" t="inlineStr"/>
+      <c r="H321" s="16" t="inlineStr"/>
+      <c r="I321" s="16" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B322" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C322" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D322" s="13" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E322" s="13" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F322" s="13" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G322" s="13" t="inlineStr"/>
+      <c r="H322" s="13" t="inlineStr"/>
+      <c r="I322" s="13" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B323" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C323" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D323" s="16" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E323" s="16" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F323" s="16" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G323" s="16" t="inlineStr"/>
+      <c r="H323" s="16" t="inlineStr"/>
+      <c r="I323" s="16" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="13" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B320" s="14" t="inlineStr">
+      <c r="B324" s="14" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C320" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D320" s="13" t="inlineStr">
+      <c r="C324" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D324" s="13" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E320" s="13" t="inlineStr">
+      <c r="E324" s="13" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -12953,37 +13093,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F320" s="13" t="inlineStr">
+      <c r="F324" s="13" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G320" s="13" t="inlineStr"/>
-      <c r="H320" s="13" t="inlineStr"/>
-      <c r="I320" s="13" t="inlineStr"/>
-    </row>
-    <row r="321">
-      <c r="A321" s="16" t="inlineStr">
+      <c r="G324" s="13" t="inlineStr"/>
+      <c r="H324" s="13" t="inlineStr"/>
+      <c r="I324" s="13" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B321" s="17" t="inlineStr">
+      <c r="B325" s="17" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C321" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D321" s="16" t="inlineStr">
+      <c r="C325" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D325" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E321" s="16" t="inlineStr">
+      <c r="E325" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -12995,37 +13135,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F321" s="16" t="inlineStr">
+      <c r="F325" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G321" s="16" t="inlineStr"/>
-      <c r="H321" s="16" t="inlineStr"/>
-      <c r="I321" s="16" t="inlineStr"/>
-    </row>
-    <row r="322">
-      <c r="A322" s="13" t="inlineStr">
+      <c r="G325" s="16" t="inlineStr"/>
+      <c r="H325" s="16" t="inlineStr"/>
+      <c r="I325" s="16" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B322" s="14" t="inlineStr">
+      <c r="B326" s="14" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C322" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D322" s="13" t="inlineStr">
+      <c r="C326" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D326" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E322" s="13" t="inlineStr">
+      <c r="E326" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -13037,74 +13177,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F322" s="13" t="inlineStr">
+      <c r="F326" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G322" s="13" t="inlineStr"/>
-      <c r="H322" s="13" t="inlineStr"/>
-      <c r="I322" s="13" t="inlineStr"/>
-    </row>
-    <row r="323">
-      <c r="A323" s="16" t="inlineStr">
+      <c r="G326" s="13" t="inlineStr"/>
+      <c r="H326" s="13" t="inlineStr"/>
+      <c r="I326" s="13" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B323" s="17" t="inlineStr">
+      <c r="B327" s="17" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C323" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D323" s="16" t="inlineStr">
+      <c r="C327" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D327" s="16" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E323" s="16" t="inlineStr">
+      <c r="E327" s="16" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F323" s="16" t="inlineStr">
+      <c r="F327" s="16" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G323" s="16" t="inlineStr"/>
-      <c r="H323" s="16" t="inlineStr"/>
-      <c r="I323" s="16" t="inlineStr"/>
-    </row>
-    <row r="324">
-      <c r="A324" s="13" t="inlineStr">
+      <c r="G327" s="16" t="inlineStr"/>
+      <c r="H327" s="16" t="inlineStr"/>
+      <c r="I327" s="16" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B324" s="14" t="inlineStr">
+      <c r="B328" s="14" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C324" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D324" s="13" t="inlineStr">
+      <c r="C328" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D328" s="13" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E324" s="13" t="inlineStr">
+      <c r="E328" s="13" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -13115,73 +13255,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F324" s="13" t="inlineStr">
+      <c r="F328" s="13" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G324" s="13" t="inlineStr"/>
-      <c r="H324" s="13" t="inlineStr"/>
-      <c r="I324" s="13" t="inlineStr"/>
-    </row>
-    <row r="325">
-      <c r="A325" s="16" t="inlineStr">
+      <c r="G328" s="13" t="inlineStr"/>
+      <c r="H328" s="13" t="inlineStr"/>
+      <c r="I328" s="13" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B325" s="17" t="inlineStr">
+      <c r="B329" s="17" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C325" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D325" s="16" t="inlineStr">
+      <c r="C329" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D329" s="16" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E325" s="16" t="inlineStr">
+      <c r="E329" s="16" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F325" s="16" t="inlineStr">
+      <c r="F329" s="16" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G325" s="16" t="inlineStr"/>
-      <c r="H325" s="16" t="inlineStr"/>
-      <c r="I325" s="16" t="inlineStr"/>
-    </row>
-    <row r="326">
-      <c r="A326" s="13" t="inlineStr">
+      <c r="G329" s="16" t="inlineStr"/>
+      <c r="H329" s="16" t="inlineStr"/>
+      <c r="I329" s="16" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B326" s="14" t="inlineStr">
+      <c r="B330" s="14" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C326" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D326" s="13" t="inlineStr">
+      <c r="C330" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D330" s="13" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E326" s="13" t="inlineStr">
+      <c r="E330" s="13" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -13192,37 +13332,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F326" s="13" t="inlineStr">
+      <c r="F330" s="13" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G326" s="13" t="inlineStr"/>
-      <c r="H326" s="13" t="inlineStr"/>
-      <c r="I326" s="13" t="inlineStr"/>
-    </row>
-    <row r="327">
-      <c r="A327" s="16" t="inlineStr">
+      <c r="G330" s="13" t="inlineStr"/>
+      <c r="H330" s="13" t="inlineStr"/>
+      <c r="I330" s="13" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B327" s="17" t="inlineStr">
+      <c r="B331" s="17" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C327" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D327" s="16" t="inlineStr">
+      <c r="C331" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D331" s="16" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E327" s="16" t="inlineStr">
+      <c r="E331" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -13232,37 +13372,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F327" s="16" t="inlineStr">
+      <c r="F331" s="16" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G327" s="16" t="inlineStr"/>
-      <c r="H327" s="16" t="inlineStr"/>
-      <c r="I327" s="16" t="inlineStr"/>
-    </row>
-    <row r="328">
-      <c r="A328" s="13" t="inlineStr">
+      <c r="G331" s="16" t="inlineStr"/>
+      <c r="H331" s="16" t="inlineStr"/>
+      <c r="I331" s="16" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B328" s="14" t="inlineStr">
+      <c r="B332" s="14" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C328" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D328" s="13" t="inlineStr">
+      <c r="C332" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D332" s="13" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E328" s="13" t="inlineStr">
+      <c r="E332" s="13" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -13270,19 +13410,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F328" s="13" t="inlineStr">
+      <c r="F332" s="13" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G328" s="13" t="inlineStr"/>
-      <c r="H328" s="13" t="inlineStr"/>
-      <c r="I328" s="13" t="inlineStr"/>
+      <c r="G332" s="13" t="inlineStr"/>
+      <c r="H332" s="13" t="inlineStr"/>
+      <c r="I332" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I328"/>
+  <autoFilter ref="A1:I332"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G328" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G332" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$355</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C347,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C355,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P1",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P1",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P1",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P1",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P1",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P1",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P1",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P1",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C347,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C355,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P2",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P2",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P2",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P2",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P2",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P2",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P2",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P2",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C347,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C355,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P3",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P3",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P3",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P3",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P3",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P3",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C347,"P3",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C355,"P3",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pelanggan",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pelanggan",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pelanggan",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pelanggan",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pelanggan",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pelanggan",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pelanggan",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pelanggan",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Kasir",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kasir",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Kasir",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kasir",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Kasir",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kasir",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Kasir",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kasir",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pending Payment",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pending Payment",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pending Payment",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pending Payment",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pending Payment",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pending Payment",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pending Payment",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pending Payment",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Dapur",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Dapur",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Dapur",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Dapur",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Dapur",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Dapur",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Dapur",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Dapur",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Keuangan",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Keuangan",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Keuangan",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Keuangan",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Keuangan",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Keuangan",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Keuangan",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Keuangan",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Setor Saldo Cash",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Setor Saldo Cash",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Setor Saldo Cash",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Setor Saldo Cash",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Setor Saldo Cash",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Setor Saldo Cash",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Setor Saldo Cash",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Setor Saldo Cash",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"QR Meja",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"QR Meja",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"QR Meja",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"QR Meja",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"QR Meja",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"QR Meja",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"QR Meja",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"QR Meja",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Diskon",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Diskon",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Diskon",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Diskon",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Diskon",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Diskon",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Diskon",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Diskon",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembayaran QRIS",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembayaran QRIS",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembayaran QRIS",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembayaran QRIS",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembayaran QRIS",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembayaran QRIS",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembayaran QRIS",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembayaran QRIS",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Tampilan",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Tampilan",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Tampilan",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Tampilan",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Tampilan",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Tampilan",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Tampilan",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Tampilan",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Super Admin",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Super Admin",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Super Admin",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Super Admin",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Super Admin",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Super Admin",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Super Admin",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Super Admin",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembaruan Aplikasi",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembaruan Aplikasi",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembaruan Aplikasi",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembaruan Aplikasi",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembaruan Aplikasi",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembaruan Aplikasi",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Pembaruan Aplikasi",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembaruan Aplikasi",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A347,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G347,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G355,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G347,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G355,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G347,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G355,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A347,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G347,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G355,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1727,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I347"/>
+  <dimension ref="A1:I355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7076,32 +7076,32 @@
     <row r="153">
       <c r="A153" s="16" t="inlineStr">
         <is>
-          <t>Kotak Masuk &amp; Pengumuman</t>
+          <t>Diskon</t>
         </is>
       </c>
       <c r="B153" s="17" t="inlineStr">
         <is>
-          <t>TC-IN-01</t>
-        </is>
-      </c>
-      <c r="C153" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-DS-22</t>
+        </is>
+      </c>
+      <c r="C153" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D153" s="16" t="inlineStr">
         <is>
-          <t>Buka kotak masuk karyawan</t>
+          <t>Menu Rp 25.000, Ukuran Besar +Rp 5.000. Buat promo sasaran "Tambahan Ukuran: Besar", potongan 100%</t>
         </is>
       </c>
       <c r="E153" s="16" t="inlineStr">
         <is>
-          <t>Dua tab: Update Aplikasi dan General, masing-masing berpenghitung sendiri</t>
+          <t>Pesan Ukuran Besar → bayar Rp 25.000, bukan Rp 30.000</t>
         </is>
       </c>
       <c r="F153" s="16" t="inlineStr">
         <is>
-          <t>F-IN-01, F-IN-02</t>
+          <t>F-DS-14, F-DS-15</t>
         </is>
       </c>
       <c r="G153" s="16" t="inlineStr"/>
@@ -7111,12 +7111,12 @@
     <row r="154">
       <c r="A154" s="13" t="inlineStr">
         <is>
-          <t>Kotak Masuk &amp; Pengumuman</t>
+          <t>Diskon</t>
         </is>
       </c>
       <c r="B154" s="14" t="inlineStr">
         <is>
-          <t>TC-IN-02</t>
+          <t>TC-DS-23</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
@@ -7126,17 +7126,17 @@
       </c>
       <c r="D154" s="13" t="inlineStr">
         <is>
-          <t>Buka tab General → Tandai semua dibaca</t>
+          <t>Pesan menu yang sama dengan Ukuran Regular</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
         <is>
-          <t>Hanya tab General yang tertandai; tab Update Aplikasi tidak tersentuh</t>
+          <t>Tidak dapat potongan — pilihannya tidak dipesan</t>
         </is>
       </c>
       <c r="F154" s="13" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>F-DS-16</t>
         </is>
       </c>
       <c r="G154" s="13" t="inlineStr"/>
@@ -7146,12 +7146,12 @@
     <row r="155">
       <c r="A155" s="16" t="inlineStr">
         <is>
-          <t>Kotak Masuk &amp; Pengumuman</t>
+          <t>Diskon</t>
         </is>
       </c>
       <c r="B155" s="17" t="inlineStr">
         <is>
-          <t>TC-IN-03</t>
+          <t>TC-DS-24</t>
         </is>
       </c>
       <c r="C155" s="18" t="inlineStr">
@@ -7161,17 +7161,17 @@
       </c>
       <c r="D155" s="16" t="inlineStr">
         <is>
-          <t>Hal yang sama untuk Hapus semua</t>
+          <t>Promo sasaran topping "Keju" 100%, pesan dengan Keju</t>
         </is>
       </c>
       <c r="E155" s="16" t="inlineStr">
         <is>
-          <t>Hanya tab yang sedang dibuka</t>
+          <t>Harga toppingnya hilang, menunya tetap penuh</t>
         </is>
       </c>
       <c r="F155" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>F-DS-14, F-DS-15</t>
         </is>
       </c>
       <c r="G155" s="16" t="inlineStr"/>
@@ -7181,32 +7181,32 @@
     <row r="156">
       <c r="A156" s="13" t="inlineStr">
         <is>
-          <t>Kotak Masuk &amp; Pengumuman</t>
+          <t>Diskon</t>
         </is>
       </c>
       <c r="B156" s="14" t="inlineStr">
         <is>
-          <t>TC-IN-04</t>
-        </is>
-      </c>
-      <c r="C156" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-DS-25</t>
+        </is>
+      </c>
+      <c r="C156" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D156" s="13" t="inlineStr">
         <is>
-          <t>Hapus pesan, lalu buka dari akun lain</t>
+          <t>Promo sasaran topping "Keju", pesan tanpa Keju</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
         <is>
-          <t>Pesannya masih ada di akun lain itu</t>
+          <t>Tidak dapat potongan</t>
         </is>
       </c>
       <c r="F156" s="13" t="inlineStr">
         <is>
-          <t>F-IN-03</t>
+          <t>F-DS-16</t>
         </is>
       </c>
       <c r="G156" s="13" t="inlineStr"/>
@@ -7216,32 +7216,32 @@
     <row r="157">
       <c r="A157" s="16" t="inlineStr">
         <is>
-          <t>Kotak Masuk &amp; Pengumuman</t>
+          <t>Diskon</t>
         </is>
       </c>
       <c r="B157" s="17" t="inlineStr">
         <is>
-          <t>TC-IN-05</t>
-        </is>
-      </c>
-      <c r="C157" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-DS-26</t>
+        </is>
+      </c>
+      <c r="C157" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D157" s="16" t="inlineStr">
         <is>
-          <t>Admin resto A kirim pengumuman → buka kotak masuk karyawan resto B</t>
+          <t>Pesan 3 porsi Ukuran Besar dengan promo 100%</t>
         </is>
       </c>
       <c r="E157" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul</t>
+          <t>Ketiganya bebas biaya ukuran</t>
         </is>
       </c>
       <c r="F157" s="16" t="inlineStr">
         <is>
-          <t>F-IN-10, A-10</t>
+          <t>F-DS-15</t>
         </is>
       </c>
       <c r="G157" s="16" t="inlineStr"/>
@@ -7251,32 +7251,32 @@
     <row r="158">
       <c r="A158" s="13" t="inlineStr">
         <is>
-          <t>Kotak Masuk &amp; Pengumuman</t>
+          <t>Diskon</t>
         </is>
       </c>
       <c r="B158" s="14" t="inlineStr">
         <is>
-          <t>TC-IN-06</t>
-        </is>
-      </c>
-      <c r="C158" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-DS-27</t>
+        </is>
+      </c>
+      <c r="C158" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D158" s="13" t="inlineStr">
         <is>
-          <t>Kirim pengumuman bersasaran Karyawan → buka kotak masuk pelanggan</t>
+          <t>Pilihan yang tidak menambah harga</t>
         </is>
       </c>
       <c r="E158" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul</t>
+          <t>Tidak muncul di daftar "Yang dipotong"</t>
         </is>
       </c>
       <c r="F158" s="13" t="inlineStr">
         <is>
-          <t>F-IN-11, A-20</t>
+          <t>F-DS-14</t>
         </is>
       </c>
       <c r="G158" s="13" t="inlineStr"/>
@@ -7286,32 +7286,32 @@
     <row r="159">
       <c r="A159" s="16" t="inlineStr">
         <is>
-          <t>Kotak Masuk &amp; Pengumuman</t>
+          <t>Diskon</t>
         </is>
       </c>
       <c r="B159" s="17" t="inlineStr">
         <is>
-          <t>TC-IN-07</t>
-        </is>
-      </c>
-      <c r="C159" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-DS-28</t>
+        </is>
+      </c>
+      <c r="C159" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D159" s="16" t="inlineStr">
         <is>
-          <t>Kirim pengumuman bersasaran Customer → buka kotak masuk karyawan</t>
+          <t>Menu tanpa tambahan harga sama sekali</t>
         </is>
       </c>
       <c r="E159" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul</t>
+          <t>Kolom "Yang dipotong" tidak ditampilkan</t>
         </is>
       </c>
       <c r="F159" s="16" t="inlineStr">
         <is>
-          <t>F-IN-11</t>
+          <t>F-DS-14</t>
         </is>
       </c>
       <c r="G159" s="16" t="inlineStr"/>
@@ -7321,12 +7321,12 @@
     <row r="160">
       <c r="A160" s="13" t="inlineStr">
         <is>
-          <t>Kotak Masuk &amp; Pengumuman</t>
+          <t>Diskon</t>
         </is>
       </c>
       <c r="B160" s="14" t="inlineStr">
         <is>
-          <t>TC-IN-08</t>
+          <t>TC-DS-29</t>
         </is>
       </c>
       <c r="C160" s="19" t="inlineStr">
@@ -7336,17 +7336,17 @@
       </c>
       <c r="D160" s="13" t="inlineStr">
         <is>
-          <t>Kirim bersasaran Semua</t>
+          <t>Ganti sasaran dari level ke topping</t>
         </is>
       </c>
       <c r="E160" s="13" t="inlineStr">
         <is>
-          <t>Muncul di keduanya</t>
+          <t>Sasaran lamanya terbuang, tidak menumpuk</t>
         </is>
       </c>
       <c r="F160" s="13" t="inlineStr">
         <is>
-          <t>F-IN-11</t>
+          <t>F-DS-14</t>
         </is>
       </c>
       <c r="G160" s="13" t="inlineStr"/>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="B161" s="17" t="inlineStr">
         <is>
-          <t>TC-IN-09</t>
+          <t>TC-IN-01</t>
         </is>
       </c>
       <c r="C161" s="20" t="inlineStr">
@@ -7371,17 +7371,17 @@
       </c>
       <c r="D161" s="16" t="inlineStr">
         <is>
-          <t>Sertakan gambar promo pada pengumuman</t>
+          <t>Buka kotak masuk karyawan</t>
         </is>
       </c>
       <c r="E161" s="16" t="inlineStr">
         <is>
-          <t>Gambarnya tampil utuh saat dibuka</t>
+          <t>Dua tab: Update Aplikasi dan General, masing-masing berpenghitung sendiri</t>
         </is>
       </c>
       <c r="F161" s="16" t="inlineStr">
         <is>
-          <t>F-IN-09</t>
+          <t>F-IN-01, F-IN-02</t>
         </is>
       </c>
       <c r="G161" s="16" t="inlineStr"/>
@@ -7396,27 +7396,27 @@
       </c>
       <c r="B162" s="14" t="inlineStr">
         <is>
-          <t>TC-IN-10</t>
-        </is>
-      </c>
-      <c r="C162" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-IN-02</t>
+        </is>
+      </c>
+      <c r="C162" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D162" s="13" t="inlineStr">
         <is>
-          <t>Pelanggan yang pernah memesan di resto A membuka Kotak Masuk di menu utama</t>
+          <t>Buka tab General → Tandai semua dibaca</t>
         </is>
       </c>
       <c r="E162" s="13" t="inlineStr">
         <is>
-          <t>Promo resto A muncul berikut nama restonya</t>
+          <t>Hanya tab General yang tertandai; tab Update Aplikasi tidak tersentuh</t>
         </is>
       </c>
       <c r="F162" s="13" t="inlineStr">
         <is>
-          <t>F-IN-12, F-IN-13</t>
+          <t>F-IN-15</t>
         </is>
       </c>
       <c r="G162" s="13" t="inlineStr"/>
@@ -7431,27 +7431,27 @@
       </c>
       <c r="B163" s="17" t="inlineStr">
         <is>
-          <t>TC-IN-11</t>
-        </is>
-      </c>
-      <c r="C163" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-IN-03</t>
+        </is>
+      </c>
+      <c r="C163" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D163" s="16" t="inlineStr">
         <is>
-          <t>Hal yang sama sebagai tamu</t>
+          <t>Hal yang sama untuk Hapus semua</t>
         </is>
       </c>
       <c r="E163" s="16" t="inlineStr">
         <is>
-          <t>Tetap menerima, berdasar pesanan yang tersimpan di HP-nya</t>
+          <t>Hanya tab yang sedang dibuka</t>
         </is>
       </c>
       <c r="F163" s="16" t="inlineStr">
         <is>
-          <t>F-IN-14</t>
+          <t>F-IN-15</t>
         </is>
       </c>
       <c r="G163" s="16" t="inlineStr"/>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B164" s="14" t="inlineStr">
         <is>
-          <t>TC-IN-12</t>
+          <t>TC-IN-04</t>
         </is>
       </c>
       <c r="C164" s="19" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="D164" s="13" t="inlineStr">
         <is>
-          <t>Pelanggan tamu membuka kotak masuk</t>
+          <t>Hapus pesan, lalu buka dari akun lain</t>
         </is>
       </c>
       <c r="E164" s="13" t="inlineStr">
         <is>
-          <t>Tombol tandai/hapus tidak ditawarkan — tamu tidak punya tempat menyimpan penandanya</t>
+          <t>Pesannya masih ada di akun lain itu</t>
         </is>
       </c>
       <c r="F164" s="13" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="B165" s="17" t="inlineStr">
         <is>
-          <t>TC-IN-13</t>
+          <t>TC-IN-05</t>
         </is>
       </c>
       <c r="C165" s="18" t="inlineStr">
@@ -7511,17 +7511,17 @@
       </c>
       <c r="D165" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan pengumuman baru saat aplikasi tertutup</t>
+          <t>Admin resto A kirim pengumuman → buka kotak masuk karyawan resto B</t>
         </is>
       </c>
       <c r="E165" s="16" t="inlineStr">
         <is>
-          <t>Notifikasi sampai ke HP</t>
+          <t>Tidak muncul</t>
         </is>
       </c>
       <c r="F165" s="16" t="inlineStr">
         <is>
-          <t>F-IN-07, A-08</t>
+          <t>F-IN-10, A-10</t>
         </is>
       </c>
       <c r="G165" s="16" t="inlineStr"/>
@@ -7536,27 +7536,27 @@
       </c>
       <c r="B166" s="14" t="inlineStr">
         <is>
-          <t>TC-IN-14</t>
-        </is>
-      </c>
-      <c r="C166" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-IN-06</t>
+        </is>
+      </c>
+      <c r="C166" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D166" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan pengumuman saat aplikasi sedang dibuka</t>
+          <t>Kirim pengumuman bersasaran Karyawan → buka kotak masuk pelanggan</t>
         </is>
       </c>
       <c r="E166" s="13" t="inlineStr">
         <is>
-          <t>Notifikasi tetap muncul di bar notifikasi</t>
+          <t>Tidak muncul</t>
         </is>
       </c>
       <c r="F166" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>F-IN-11, A-20</t>
         </is>
       </c>
       <c r="G166" s="13" t="inlineStr"/>
@@ -7566,12 +7566,12 @@
     <row r="167">
       <c r="A167" s="16" t="inlineStr">
         <is>
-          <t>Pembayaran QRIS</t>
+          <t>Kotak Masuk &amp; Pengumuman</t>
         </is>
       </c>
       <c r="B167" s="17" t="inlineStr">
         <is>
-          <t>TC-PG-01</t>
+          <t>TC-IN-07</t>
         </is>
       </c>
       <c r="C167" s="18" t="inlineStr">
@@ -7581,17 +7581,17 @@
       </c>
       <c r="D167" s="16" t="inlineStr">
         <is>
-          <t>Pesan dan pilih QRIS pada resto yang sub-akunnya aktif</t>
+          <t>Kirim pengumuman bersasaran Customer → buka kotak masuk karyawan</t>
         </is>
       </c>
       <c r="E167" s="16" t="inlineStr">
         <is>
-          <t>QR-nya dari penyedia pembayaran sungguhan, bisa dipindai aplikasi bank</t>
+          <t>Tidak muncul</t>
         </is>
       </c>
       <c r="F167" s="16" t="inlineStr">
         <is>
-          <t>F-PG-01</t>
+          <t>F-IN-11</t>
         </is>
       </c>
       <c r="G167" s="16" t="inlineStr"/>
@@ -7601,32 +7601,32 @@
     <row r="168">
       <c r="A168" s="13" t="inlineStr">
         <is>
-          <t>Pembayaran QRIS</t>
+          <t>Kotak Masuk &amp; Pengumuman</t>
         </is>
       </c>
       <c r="B168" s="14" t="inlineStr">
         <is>
-          <t>TC-PG-02</t>
-        </is>
-      </c>
-      <c r="C168" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-IN-08</t>
+        </is>
+      </c>
+      <c r="C168" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D168" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan nominal di layar QRIS dengan total tagihan</t>
+          <t>Kirim bersasaran Semua</t>
         </is>
       </c>
       <c r="E168" s="13" t="inlineStr">
         <is>
-          <t>Sama persis, sudah termasuk service dan PPN, sudah dikurangi diskon</t>
+          <t>Muncul di keduanya</t>
         </is>
       </c>
       <c r="F168" s="13" t="inlineStr">
         <is>
-          <t>F-PG-01</t>
+          <t>F-IN-11</t>
         </is>
       </c>
       <c r="G168" s="13" t="inlineStr"/>
@@ -7636,32 +7636,32 @@
     <row r="169">
       <c r="A169" s="16" t="inlineStr">
         <is>
-          <t>Pembayaran QRIS</t>
+          <t>Kotak Masuk &amp; Pengumuman</t>
         </is>
       </c>
       <c r="B169" s="17" t="inlineStr">
         <is>
-          <t>TC-PG-03</t>
-        </is>
-      </c>
-      <c r="C169" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-IN-09</t>
+        </is>
+      </c>
+      <c r="C169" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D169" s="16" t="inlineStr">
         <is>
-          <t>Bayar sungguhan lewat aplikasi bank</t>
+          <t>Sertakan gambar promo pada pengumuman</t>
         </is>
       </c>
       <c r="E169" s="16" t="inlineStr">
         <is>
-          <t>Layar berpindah sendiri ke Pembayaran Berhasil, tanpa ada yang menekan apa pun</t>
+          <t>Gambarnya tampil utuh saat dibuka</t>
         </is>
       </c>
       <c r="F169" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02</t>
+          <t>F-IN-09</t>
         </is>
       </c>
       <c r="G169" s="16" t="inlineStr"/>
@@ -7671,32 +7671,32 @@
     <row r="170">
       <c r="A170" s="13" t="inlineStr">
         <is>
-          <t>Pembayaran QRIS</t>
+          <t>Kotak Masuk &amp; Pengumuman</t>
         </is>
       </c>
       <c r="B170" s="14" t="inlineStr">
         <is>
-          <t>TC-PG-04</t>
-        </is>
-      </c>
-      <c r="C170" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-IN-10</t>
+        </is>
+      </c>
+      <c r="C170" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D170" s="13" t="inlineStr">
         <is>
-          <t>Periksa layar kasir pada resto dengan penyedia aktif</t>
+          <t>Pelanggan yang pernah memesan di resto A membuka Kotak Masuk di menu utama</t>
         </is>
       </c>
       <c r="E170" s="13" t="inlineStr">
         <is>
-          <t>Tombol konfirmasi manual tidak ada</t>
+          <t>Promo resto A muncul berikut nama restonya</t>
         </is>
       </c>
       <c r="F170" s="13" t="inlineStr">
         <is>
-          <t>F-PG-07</t>
+          <t>F-IN-12, F-IN-13</t>
         </is>
       </c>
       <c r="G170" s="13" t="inlineStr"/>
@@ -7706,12 +7706,12 @@
     <row r="171">
       <c r="A171" s="16" t="inlineStr">
         <is>
-          <t>Pembayaran QRIS</t>
+          <t>Kotak Masuk &amp; Pengumuman</t>
         </is>
       </c>
       <c r="B171" s="17" t="inlineStr">
         <is>
-          <t>TC-PG-05</t>
+          <t>TC-IN-11</t>
         </is>
       </c>
       <c r="C171" s="20" t="inlineStr">
@@ -7721,17 +7721,17 @@
       </c>
       <c r="D171" s="16" t="inlineStr">
         <is>
-          <t>Resto yang belum punya sub-akun</t>
+          <t>Hal yang sama sebagai tamu</t>
         </is>
       </c>
       <c r="E171" s="16" t="inlineStr">
         <is>
-          <t>QR simulasi tampil berikut tombol konfirmasi manual</t>
+          <t>Tetap menerima, berdasar pesanan yang tersimpan di HP-nya</t>
         </is>
       </c>
       <c r="F171" s="16" t="inlineStr">
         <is>
-          <t>F-PG-06</t>
+          <t>F-IN-14</t>
         </is>
       </c>
       <c r="G171" s="16" t="inlineStr"/>
@@ -7741,12 +7741,12 @@
     <row r="172">
       <c r="A172" s="13" t="inlineStr">
         <is>
-          <t>Pembayaran QRIS</t>
+          <t>Kotak Masuk &amp; Pengumuman</t>
         </is>
       </c>
       <c r="B172" s="14" t="inlineStr">
         <is>
-          <t>TC-PG-06</t>
+          <t>TC-IN-12</t>
         </is>
       </c>
       <c r="C172" s="19" t="inlineStr">
@@ -7756,17 +7756,17 @@
       </c>
       <c r="D172" s="13" t="inlineStr">
         <is>
-          <t>Perhatikan hitungan mundur di layar QRIS</t>
+          <t>Pelanggan tamu membuka kotak masuk</t>
         </is>
       </c>
       <c r="E172" s="13" t="inlineStr">
         <is>
-          <t>Berjalan; QR kedaluwarsa saat habis</t>
+          <t>Tombol tandai/hapus tidak ditawarkan — tamu tidak punya tempat menyimpan penandanya</t>
         </is>
       </c>
       <c r="F172" s="13" t="inlineStr">
         <is>
-          <t>F-PG-05</t>
+          <t>F-IN-03</t>
         </is>
       </c>
       <c r="G172" s="13" t="inlineStr"/>
@@ -7776,12 +7776,12 @@
     <row r="173">
       <c r="A173" s="16" t="inlineStr">
         <is>
-          <t>Pembayaran QRIS</t>
+          <t>Kotak Masuk &amp; Pengumuman</t>
         </is>
       </c>
       <c r="B173" s="17" t="inlineStr">
         <is>
-          <t>TC-PG-07</t>
+          <t>TC-IN-13</t>
         </is>
       </c>
       <c r="C173" s="18" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="D173" s="16" t="inlineStr">
         <is>
-          <t>Dua resto berbeda menerima pembayaran QRIS</t>
+          <t>Terbitkan pengumuman baru saat aplikasi tertutup</t>
         </is>
       </c>
       <c r="E173" s="16" t="inlineStr">
         <is>
-          <t>Dananya masuk ke rekening masing-masing</t>
+          <t>Notifikasi sampai ke HP</t>
         </is>
       </c>
       <c r="F173" s="16" t="inlineStr">
         <is>
-          <t>F-PG-03</t>
+          <t>F-IN-07, A-08</t>
         </is>
       </c>
       <c r="G173" s="16" t="inlineStr"/>
@@ -7811,32 +7811,32 @@
     <row r="174">
       <c r="A174" s="13" t="inlineStr">
         <is>
-          <t>Pembayaran QRIS</t>
+          <t>Kotak Masuk &amp; Pengumuman</t>
         </is>
       </c>
       <c r="B174" s="14" t="inlineStr">
         <is>
-          <t>TC-PG-08</t>
-        </is>
-      </c>
-      <c r="C174" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-IN-14</t>
+        </is>
+      </c>
+      <c r="C174" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D174" s="13" t="inlineStr">
         <is>
-          <t>Buka Info Pembayaran sebagai Finance dan Owner</t>
+          <t>Terbitkan pengumuman saat aplikasi sedang dibuka</t>
         </is>
       </c>
       <c r="E174" s="13" t="inlineStr">
         <is>
-          <t>Pengenal sub-akun tidak terlihat</t>
+          <t>Notifikasi tetap muncul di bar notifikasi</t>
         </is>
       </c>
       <c r="F174" s="13" t="inlineStr">
         <is>
-          <t>F-PG-04</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G174" s="13" t="inlineStr"/>
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B175" s="17" t="inlineStr">
         <is>
-          <t>TC-PG-09</t>
+          <t>TC-PG-01</t>
         </is>
       </c>
       <c r="C175" s="18" t="inlineStr">
@@ -7861,17 +7861,17 @@
       </c>
       <c r="D175" s="16" t="inlineStr">
         <is>
-          <t>Buka layar resto sebagai Super Admin</t>
+          <t>Pesan dan pilih QRIS pada resto yang sub-akunnya aktif</t>
         </is>
       </c>
       <c r="E175" s="16" t="inlineStr">
         <is>
-          <t>Pengenal sub-akun terlihat dan bisa diubah</t>
+          <t>QR-nya dari penyedia pembayaran sungguhan, bisa dipindai aplikasi bank</t>
         </is>
       </c>
       <c r="F175" s="16" t="inlineStr">
         <is>
-          <t>F-PG-04, F-SA-05</t>
+          <t>F-PG-01</t>
         </is>
       </c>
       <c r="G175" s="16" t="inlineStr"/>
@@ -7886,27 +7886,27 @@
       </c>
       <c r="B176" s="14" t="inlineStr">
         <is>
-          <t>TC-PG-10</t>
-        </is>
-      </c>
-      <c r="C176" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PG-02</t>
+        </is>
+      </c>
+      <c r="C176" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D176" s="13" t="inlineStr">
         <is>
-          <t>Simpan QR ke galeri dari layar pelanggan</t>
+          <t>Bandingkan nominal di layar QRIS dengan total tagihan</t>
         </is>
       </c>
       <c r="E176" s="13" t="inlineStr">
         <is>
-          <t>Tersimpan dan masih bisa dipindai dari galeri</t>
+          <t>Sama persis, sudah termasuk service dan PPN, sudah dikurangi diskon</t>
         </is>
       </c>
       <c r="F176" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-PG-01</t>
         </is>
       </c>
       <c r="G176" s="13" t="inlineStr"/>
@@ -7916,12 +7916,12 @@
     <row r="177">
       <c r="A177" s="16" t="inlineStr">
         <is>
-          <t>Pembatalan &amp; Kedaluwarsa</t>
+          <t>Pembayaran QRIS</t>
         </is>
       </c>
       <c r="B177" s="17" t="inlineStr">
         <is>
-          <t>TC-CN-01</t>
+          <t>TC-PG-03</t>
         </is>
       </c>
       <c r="C177" s="18" t="inlineStr">
@@ -7931,17 +7931,17 @@
       </c>
       <c r="D177" s="16" t="inlineStr">
         <is>
-          <t>Pesanan belum dibayar → Pesanan Saya → Batalkan</t>
+          <t>Bayar sungguhan lewat aplikasi bank</t>
         </is>
       </c>
       <c r="E177" s="16" t="inlineStr">
         <is>
-          <t>Berhasil; statusnya jadi Dibatalkan</t>
+          <t>Layar berpindah sendiri ke Pembayaran Berhasil, tanpa ada yang menekan apa pun</t>
         </is>
       </c>
       <c r="F177" s="16" t="inlineStr">
         <is>
-          <t>F-CN-01, F-CN-02</t>
+          <t>F-PG-02</t>
         </is>
       </c>
       <c r="G177" s="16" t="inlineStr"/>
@@ -7951,12 +7951,12 @@
     <row r="178">
       <c r="A178" s="13" t="inlineStr">
         <is>
-          <t>Pembatalan &amp; Kedaluwarsa</t>
+          <t>Pembayaran QRIS</t>
         </is>
       </c>
       <c r="B178" s="14" t="inlineStr">
         <is>
-          <t>TC-CN-02</t>
+          <t>TC-PG-04</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr">
@@ -7966,17 +7966,17 @@
       </c>
       <c r="D178" s="13" t="inlineStr">
         <is>
-          <t>Hal yang sama dari layar Riwayat</t>
+          <t>Periksa layar kasir pada resto dengan penyedia aktif</t>
         </is>
       </c>
       <c r="E178" s="13" t="inlineStr">
         <is>
-          <t>Tombolnya ada dan bekerja sama persis</t>
+          <t>Tombol konfirmasi manual tidak ada</t>
         </is>
       </c>
       <c r="F178" s="13" t="inlineStr">
         <is>
-          <t>F-CN-02</t>
+          <t>F-PG-07</t>
         </is>
       </c>
       <c r="G178" s="13" t="inlineStr"/>
@@ -7986,32 +7986,32 @@
     <row r="179">
       <c r="A179" s="16" t="inlineStr">
         <is>
-          <t>Pembatalan &amp; Kedaluwarsa</t>
+          <t>Pembayaran QRIS</t>
         </is>
       </c>
       <c r="B179" s="17" t="inlineStr">
         <is>
-          <t>TC-CN-03</t>
-        </is>
-      </c>
-      <c r="C179" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PG-05</t>
+        </is>
+      </c>
+      <c r="C179" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D179" s="16" t="inlineStr">
         <is>
-          <t>Dapur menekan Mulai Masak → pelanggan mencoba membatalkan</t>
+          <t>Resto yang belum punya sub-akun</t>
         </is>
       </c>
       <c r="E179" s="16" t="inlineStr">
         <is>
-          <t>Ditolak; pesannya mengarahkan ke kasir</t>
+          <t>QR simulasi tampil berikut tombol konfirmasi manual</t>
         </is>
       </c>
       <c r="F179" s="16" t="inlineStr">
         <is>
-          <t>F-CN-03</t>
+          <t>F-PG-06</t>
         </is>
       </c>
       <c r="G179" s="16" t="inlineStr"/>
@@ -8021,32 +8021,32 @@
     <row r="180">
       <c r="A180" s="13" t="inlineStr">
         <is>
-          <t>Pembatalan &amp; Kedaluwarsa</t>
+          <t>Pembayaran QRIS</t>
         </is>
       </c>
       <c r="B180" s="14" t="inlineStr">
         <is>
-          <t>TC-CN-04</t>
-        </is>
-      </c>
-      <c r="C180" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PG-06</t>
+        </is>
+      </c>
+      <c r="C180" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D180" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang sudah dibayar</t>
+          <t>Perhatikan hitungan mundur di layar QRIS</t>
         </is>
       </c>
       <c r="E180" s="13" t="inlineStr">
         <is>
-          <t>Tombol batal tidak ada</t>
+          <t>Berjalan; QR kedaluwarsa saat habis</t>
         </is>
       </c>
       <c r="F180" s="13" t="inlineStr">
         <is>
-          <t>F-CN-01</t>
+          <t>F-PG-05</t>
         </is>
       </c>
       <c r="G180" s="13" t="inlineStr"/>
@@ -8056,12 +8056,12 @@
     <row r="181">
       <c r="A181" s="16" t="inlineStr">
         <is>
-          <t>Pembatalan &amp; Kedaluwarsa</t>
+          <t>Pembayaran QRIS</t>
         </is>
       </c>
       <c r="B181" s="17" t="inlineStr">
         <is>
-          <t>TC-CN-05</t>
+          <t>TC-PG-07</t>
         </is>
       </c>
       <c r="C181" s="18" t="inlineStr">
@@ -8071,17 +8071,17 @@
       </c>
       <c r="D181" s="16" t="inlineStr">
         <is>
-          <t>Coba batalkan pesanan orang lain (dari perangkat berbeda)</t>
+          <t>Dua resto berbeda menerima pembayaran QRIS</t>
         </is>
       </c>
       <c r="E181" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Dananya masuk ke rekening masing-masing</t>
         </is>
       </c>
       <c r="F181" s="16" t="inlineStr">
         <is>
-          <t>F-CN-04, TSD §5.2</t>
+          <t>F-PG-03</t>
         </is>
       </c>
       <c r="G181" s="16" t="inlineStr"/>
@@ -8091,12 +8091,12 @@
     <row r="182">
       <c r="A182" s="13" t="inlineStr">
         <is>
-          <t>Pembatalan &amp; Kedaluwarsa</t>
+          <t>Pembayaran QRIS</t>
         </is>
       </c>
       <c r="B182" s="14" t="inlineStr">
         <is>
-          <t>TC-CN-06</t>
+          <t>TC-PG-08</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr">
@@ -8106,17 +8106,17 @@
       </c>
       <c r="D182" s="13" t="inlineStr">
         <is>
-          <t>Pesanan tunai dibiarkan 31 menit</t>
+          <t>Buka Info Pembayaran sebagai Finance dan Owner</t>
         </is>
       </c>
       <c r="E182" s="13" t="inlineStr">
         <is>
-          <t>Statusnya jadi Hangus sendiri</t>
+          <t>Pengenal sub-akun tidak terlihat</t>
         </is>
       </c>
       <c r="F182" s="13" t="inlineStr">
         <is>
-          <t>F-CN-05</t>
+          <t>F-PG-04</t>
         </is>
       </c>
       <c r="G182" s="13" t="inlineStr"/>
@@ -8126,12 +8126,12 @@
     <row r="183">
       <c r="A183" s="16" t="inlineStr">
         <is>
-          <t>Pembatalan &amp; Kedaluwarsa</t>
+          <t>Pembayaran QRIS</t>
         </is>
       </c>
       <c r="B183" s="17" t="inlineStr">
         <is>
-          <t>TC-CN-07</t>
+          <t>TC-PG-09</t>
         </is>
       </c>
       <c r="C183" s="18" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="D183" s="16" t="inlineStr">
         <is>
-          <t>Bandingkan tampilan pesanan Dibatalkan dan Hangus</t>
+          <t>Buka layar resto sebagai Super Admin</t>
         </is>
       </c>
       <c r="E183" s="16" t="inlineStr">
         <is>
-          <t>Dua label berbeda, tidak tertukar</t>
+          <t>Pengenal sub-akun terlihat dan bisa diubah</t>
         </is>
       </c>
       <c r="F183" s="16" t="inlineStr">
         <is>
-          <t>F-CN-06</t>
+          <t>F-PG-04, F-SA-05</t>
         </is>
       </c>
       <c r="G183" s="16" t="inlineStr"/>
@@ -8161,32 +8161,32 @@
     <row r="184">
       <c r="A184" s="13" t="inlineStr">
         <is>
-          <t>Pembatalan &amp; Kedaluwarsa</t>
+          <t>Pembayaran QRIS</t>
         </is>
       </c>
       <c r="B184" s="14" t="inlineStr">
         <is>
-          <t>TC-CN-08</t>
-        </is>
-      </c>
-      <c r="C184" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PG-10</t>
+        </is>
+      </c>
+      <c r="C184" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D184" s="13" t="inlineStr">
         <is>
-          <t>Buka Pesanan Masuk sesudah ada pesanan dibatalkan</t>
+          <t>Simpan QR ke galeri dari layar pelanggan</t>
         </is>
       </c>
       <c r="E184" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul, dan tidak berlabel "Menunggu Pembayaran"</t>
+          <t>Tersimpan dan masih bisa dipindai dari galeri</t>
         </is>
       </c>
       <c r="F184" s="13" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G184" s="13" t="inlineStr"/>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="B185" s="17" t="inlineStr">
         <is>
-          <t>TC-CN-09</t>
+          <t>TC-CN-01</t>
         </is>
       </c>
       <c r="C185" s="18" t="inlineStr">
@@ -8211,17 +8211,17 @@
       </c>
       <c r="D185" s="16" t="inlineStr">
         <is>
-          <t>Pesanan QRIS yang belum dibayar dibiarkan 31 menit</t>
+          <t>Pesanan belum dibayar → Pesanan Saya → Batalkan</t>
         </is>
       </c>
       <c r="E185" s="16" t="inlineStr">
         <is>
-          <t>Tidak ikut hangus — tenggangnya di sisi penyedia</t>
+          <t>Berhasil; statusnya jadi Dibatalkan</t>
         </is>
       </c>
       <c r="F185" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.2</t>
+          <t>F-CN-01, F-CN-02</t>
         </is>
       </c>
       <c r="G185" s="16" t="inlineStr"/>
@@ -8231,32 +8231,32 @@
     <row r="186">
       <c r="A186" s="13" t="inlineStr">
         <is>
-          <t>Sesi Meja &amp; Identitas</t>
+          <t>Pembatalan &amp; Kedaluwarsa</t>
         </is>
       </c>
       <c r="B186" s="14" t="inlineStr">
         <is>
-          <t>TC-SS-01</t>
-        </is>
-      </c>
-      <c r="C186" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-CN-02</t>
+        </is>
+      </c>
+      <c r="C186" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D186" s="13" t="inlineStr">
         <is>
-          <t>Pindai QR meja</t>
+          <t>Hal yang sama dari layar Riwayat</t>
         </is>
       </c>
       <c r="E186" s="13" t="inlineStr">
         <is>
-          <t>Sesi terbuka: resto dan nomor meja terisi sendiri</t>
+          <t>Tombolnya ada dan bekerja sama persis</t>
         </is>
       </c>
       <c r="F186" s="13" t="inlineStr">
         <is>
-          <t>F-SS-01</t>
+          <t>F-CN-02</t>
         </is>
       </c>
       <c r="G186" s="13" t="inlineStr"/>
@@ -8266,32 +8266,32 @@
     <row r="187">
       <c r="A187" s="16" t="inlineStr">
         <is>
-          <t>Sesi Meja &amp; Identitas</t>
+          <t>Pembatalan &amp; Kedaluwarsa</t>
         </is>
       </c>
       <c r="B187" s="17" t="inlineStr">
         <is>
-          <t>TC-SS-02</t>
-        </is>
-      </c>
-      <c r="C187" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-CN-03</t>
+        </is>
+      </c>
+      <c r="C187" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D187" s="16" t="inlineStr">
         <is>
-          <t>Pesan sebagai tamu, tutup aplikasi, buka lagi</t>
+          <t>Dapur menekan Mulai Masak → pelanggan mencoba membatalkan</t>
         </is>
       </c>
       <c r="E187" s="16" t="inlineStr">
         <is>
-          <t>Riwayatnya masih ada</t>
+          <t>Ditolak; pesannya mengarahkan ke kasir</t>
         </is>
       </c>
       <c r="F187" s="16" t="inlineStr">
         <is>
-          <t>F-SS-02</t>
+          <t>F-CN-03</t>
         </is>
       </c>
       <c r="G187" s="16" t="inlineStr"/>
@@ -8301,12 +8301,12 @@
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>Sesi Meja &amp; Identitas</t>
+          <t>Pembatalan &amp; Kedaluwarsa</t>
         </is>
       </c>
       <c r="B188" s="14" t="inlineStr">
         <is>
-          <t>TC-SS-03</t>
+          <t>TC-CN-04</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr">
@@ -8316,17 +8316,17 @@
       </c>
       <c r="D188" s="13" t="inlineStr">
         <is>
-          <t>Pesan sebagai tamu → login dengan email yang belum pernah dipakai</t>
+          <t>Pesanan yang sudah dibayar</t>
         </is>
       </c>
       <c r="E188" s="13" t="inlineStr">
         <is>
-          <t>Riwayat tamunya berpindah ke akun itu</t>
+          <t>Tombol batal tidak ada</t>
         </is>
       </c>
       <c r="F188" s="13" t="inlineStr">
         <is>
-          <t>F-SS-03, F-CU-13</t>
+          <t>F-CN-01</t>
         </is>
       </c>
       <c r="G188" s="13" t="inlineStr"/>
@@ -8336,12 +8336,12 @@
     <row r="189">
       <c r="A189" s="16" t="inlineStr">
         <is>
-          <t>Sesi Meja &amp; Identitas</t>
+          <t>Pembatalan &amp; Kedaluwarsa</t>
         </is>
       </c>
       <c r="B189" s="17" t="inlineStr">
         <is>
-          <t>TC-SS-04</t>
+          <t>TC-CN-05</t>
         </is>
       </c>
       <c r="C189" s="18" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="D189" s="16" t="inlineStr">
         <is>
-          <t>Pesan sebagai tamu → login dengan email yang sudah punya riwayat</t>
+          <t>Coba batalkan pesanan orang lain (dari perangkat berbeda)</t>
         </is>
       </c>
       <c r="E189" s="16" t="inlineStr">
         <is>
-          <t>Keduanya tetap terpisah; riwayat akun tidak tercampur</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F189" s="16" t="inlineStr">
         <is>
-          <t>F-SS-04, F-SS-05</t>
+          <t>F-CN-04, TSD §5.2</t>
         </is>
       </c>
       <c r="G189" s="16" t="inlineStr"/>
@@ -8371,32 +8371,32 @@
     <row r="190">
       <c r="A190" s="13" t="inlineStr">
         <is>
-          <t>Sesi Meja &amp; Identitas</t>
+          <t>Pembatalan &amp; Kedaluwarsa</t>
         </is>
       </c>
       <c r="B190" s="14" t="inlineStr">
         <is>
-          <t>TC-SS-05</t>
-        </is>
-      </c>
-      <c r="C190" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-CN-06</t>
+        </is>
+      </c>
+      <c r="C190" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D190" s="13" t="inlineStr">
         <is>
-          <t>Kasus di atas → logout lagi</t>
+          <t>Pesanan tunai dibiarkan 31 menit</t>
         </is>
       </c>
       <c r="E190" s="13" t="inlineStr">
         <is>
-          <t>Riwayat tamu masih ada di perangkat</t>
+          <t>Statusnya jadi Hangus sendiri</t>
         </is>
       </c>
       <c r="F190" s="13" t="inlineStr">
         <is>
-          <t>F-SS-05</t>
+          <t>F-CN-05</t>
         </is>
       </c>
       <c r="G190" s="13" t="inlineStr"/>
@@ -8406,32 +8406,32 @@
     <row r="191">
       <c r="A191" s="16" t="inlineStr">
         <is>
-          <t>Sesi Meja &amp; Identitas</t>
+          <t>Pembatalan &amp; Kedaluwarsa</t>
         </is>
       </c>
       <c r="B191" s="17" t="inlineStr">
         <is>
-          <t>TC-SS-06</t>
-        </is>
-      </c>
-      <c r="C191" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-CN-07</t>
+        </is>
+      </c>
+      <c r="C191" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D191" s="16" t="inlineStr">
         <is>
-          <t>Selesaikan seluruh pesanan dalam sesi, tunggu 6 menit</t>
+          <t>Bandingkan tampilan pesanan Dibatalkan dan Hangus</t>
         </is>
       </c>
       <c r="E191" s="16" t="inlineStr">
         <is>
-          <t>Sesinya tertutup sendiri</t>
+          <t>Dua label berbeda, tidak tertukar</t>
         </is>
       </c>
       <c r="F191" s="16" t="inlineStr">
         <is>
-          <t>F-SS-06</t>
+          <t>F-CN-06</t>
         </is>
       </c>
       <c r="G191" s="16" t="inlineStr"/>
@@ -8441,32 +8441,32 @@
     <row r="192">
       <c r="A192" s="13" t="inlineStr">
         <is>
-          <t>Sesi Meja &amp; Identitas</t>
+          <t>Pembatalan &amp; Kedaluwarsa</t>
         </is>
       </c>
       <c r="B192" s="14" t="inlineStr">
         <is>
-          <t>TC-SS-07</t>
-        </is>
-      </c>
-      <c r="C192" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-CN-08</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D192" s="13" t="inlineStr">
         <is>
-          <t>Sisakan satu pesanan belum selesai, tunggu 10 menit</t>
+          <t>Buka Pesanan Masuk sesudah ada pesanan dibatalkan</t>
         </is>
       </c>
       <c r="E192" s="13" t="inlineStr">
         <is>
-          <t>Sesinya tetap terbuka</t>
+          <t>Tidak muncul, dan tidak berlabel "Menunggu Pembayaran"</t>
         </is>
       </c>
       <c r="F192" s="13" t="inlineStr">
         <is>
-          <t>F-SS-07</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="G192" s="13" t="inlineStr"/>
@@ -8476,32 +8476,32 @@
     <row r="193">
       <c r="A193" s="16" t="inlineStr">
         <is>
-          <t>Tampilan</t>
+          <t>Pembatalan &amp; Kedaluwarsa</t>
         </is>
       </c>
       <c r="B193" s="17" t="inlineStr">
         <is>
-          <t>TC-TM-01</t>
-        </is>
-      </c>
-      <c r="C193" s="22" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-CN-09</t>
+        </is>
+      </c>
+      <c r="C193" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D193" s="16" t="inlineStr">
         <is>
-          <t>Ganti tema dari halaman awal, sebelum masuk</t>
+          <t>Pesanan QRIS yang belum dibayar dibiarkan 31 menit</t>
         </is>
       </c>
       <c r="E193" s="16" t="inlineStr">
         <is>
-          <t>Berlaku seketika</t>
+          <t>Tidak ikut hangus — tenggangnya di sisi penyedia</t>
         </is>
       </c>
       <c r="F193" s="16" t="inlineStr">
         <is>
-          <t>F-TM-01, F-TM-02</t>
+          <t>TSD §7.2</t>
         </is>
       </c>
       <c r="G193" s="16" t="inlineStr"/>
@@ -8511,32 +8511,32 @@
     <row r="194">
       <c r="A194" s="13" t="inlineStr">
         <is>
-          <t>Tampilan</t>
+          <t>Sesi Meja &amp; Identitas</t>
         </is>
       </c>
       <c r="B194" s="14" t="inlineStr">
         <is>
-          <t>TC-TM-02</t>
-        </is>
-      </c>
-      <c r="C194" s="21" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-SS-01</t>
+        </is>
+      </c>
+      <c r="C194" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D194" s="13" t="inlineStr">
         <is>
-          <t>Ganti tema dari tiap peran: Kasir, Chef, Admin, Finance, Owner, Pelanggan</t>
+          <t>Pindai QR meja</t>
         </is>
       </c>
       <c r="E194" s="13" t="inlineStr">
         <is>
-          <t>Tersedia dan bekerja di semuanya</t>
+          <t>Sesi terbuka: resto dan nomor meja terisi sendiri</t>
         </is>
       </c>
       <c r="F194" s="13" t="inlineStr">
         <is>
-          <t>F-TM-02</t>
+          <t>F-SS-01</t>
         </is>
       </c>
       <c r="G194" s="13" t="inlineStr"/>
@@ -8546,32 +8546,32 @@
     <row r="195">
       <c r="A195" s="16" t="inlineStr">
         <is>
-          <t>Tampilan</t>
+          <t>Sesi Meja &amp; Identitas</t>
         </is>
       </c>
       <c r="B195" s="17" t="inlineStr">
         <is>
-          <t>TC-TM-03</t>
-        </is>
-      </c>
-      <c r="C195" s="22" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-SS-02</t>
+        </is>
+      </c>
+      <c r="C195" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D195" s="16" t="inlineStr">
         <is>
-          <t>Pilih Ikuti HP, ubah tema sistem Android</t>
+          <t>Pesan sebagai tamu, tutup aplikasi, buka lagi</t>
         </is>
       </c>
       <c r="E195" s="16" t="inlineStr">
         <is>
-          <t>Aplikasi mengikuti tanpa dibuka ulang</t>
+          <t>Riwayatnya masih ada</t>
         </is>
       </c>
       <c r="F195" s="16" t="inlineStr">
         <is>
-          <t>F-TM-01</t>
+          <t>F-SS-02</t>
         </is>
       </c>
       <c r="G195" s="16" t="inlineStr"/>
@@ -8581,32 +8581,32 @@
     <row r="196">
       <c r="A196" s="13" t="inlineStr">
         <is>
-          <t>Tampilan</t>
+          <t>Sesi Meja &amp; Identitas</t>
         </is>
       </c>
       <c r="B196" s="14" t="inlineStr">
         <is>
-          <t>TC-TM-04</t>
-        </is>
-      </c>
-      <c r="C196" s="21" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-SS-03</t>
+        </is>
+      </c>
+      <c r="C196" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D196" s="13" t="inlineStr">
         <is>
-          <t>Pilih Gelap, tutup aplikasi, buka lagi</t>
+          <t>Pesan sebagai tamu → login dengan email yang belum pernah dipakai</t>
         </is>
       </c>
       <c r="E196" s="13" t="inlineStr">
         <is>
-          <t>Tetap gelap</t>
+          <t>Riwayat tamunya berpindah ke akun itu</t>
         </is>
       </c>
       <c r="F196" s="13" t="inlineStr">
         <is>
-          <t>F-TM-03</t>
+          <t>F-SS-03, F-CU-13</t>
         </is>
       </c>
       <c r="G196" s="13" t="inlineStr"/>
@@ -8616,32 +8616,32 @@
     <row r="197">
       <c r="A197" s="16" t="inlineStr">
         <is>
-          <t>Tampilan</t>
+          <t>Sesi Meja &amp; Identitas</t>
         </is>
       </c>
       <c r="B197" s="17" t="inlineStr">
         <is>
-          <t>TC-TM-05</t>
-        </is>
-      </c>
-      <c r="C197" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SS-04</t>
+        </is>
+      </c>
+      <c r="C197" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D197" s="16" t="inlineStr">
         <is>
-          <t>Telusuri seluruh layar dalam mode gelap</t>
+          <t>Pesan sebagai tamu → login dengan email yang sudah punya riwayat</t>
         </is>
       </c>
       <c r="E197" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada tulisan yang hilang di latarnya; kartu selalu lebih terang daripada latar</t>
+          <t>Keduanya tetap terpisah; riwayat akun tidak tercampur</t>
         </is>
       </c>
       <c r="F197" s="16" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-SS-04, F-SS-05</t>
         </is>
       </c>
       <c r="G197" s="16" t="inlineStr"/>
@@ -8651,12 +8651,12 @@
     <row r="198">
       <c r="A198" s="13" t="inlineStr">
         <is>
-          <t>Tampilan</t>
+          <t>Sesi Meja &amp; Identitas</t>
         </is>
       </c>
       <c r="B198" s="14" t="inlineStr">
         <is>
-          <t>TC-TM-06</t>
+          <t>TC-SS-05</t>
         </is>
       </c>
       <c r="C198" s="19" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="D198" s="13" t="inlineStr">
         <is>
-          <t>Hal yang sama dalam mode terang</t>
+          <t>Kasus di atas → logout lagi</t>
         </is>
       </c>
       <c r="E198" s="13" t="inlineStr">
         <is>
-          <t>Sama</t>
+          <t>Riwayat tamu masih ada di perangkat</t>
         </is>
       </c>
       <c r="F198" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-SS-05</t>
         </is>
       </c>
       <c r="G198" s="13" t="inlineStr"/>
@@ -8686,32 +8686,32 @@
     <row r="199">
       <c r="A199" s="16" t="inlineStr">
         <is>
-          <t>Tampilan</t>
+          <t>Sesi Meja &amp; Identitas</t>
         </is>
       </c>
       <c r="B199" s="17" t="inlineStr">
         <is>
-          <t>TC-TM-07</t>
-        </is>
-      </c>
-      <c r="C199" s="22" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-SS-06</t>
+        </is>
+      </c>
+      <c r="C199" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D199" s="16" t="inlineStr">
         <is>
-          <t>Perkecil lebar layar / perangkat sempit</t>
+          <t>Selesaikan seluruh pesanan dalam sesi, tunggu 6 menit</t>
         </is>
       </c>
       <c r="E199" s="16" t="inlineStr">
         <is>
-          <t>Pilihan tema menyusut jadi ikon saja</t>
+          <t>Sesinya tertutup sendiri</t>
         </is>
       </c>
       <c r="F199" s="16" t="inlineStr">
         <is>
-          <t>F-TM-04</t>
+          <t>F-SS-06</t>
         </is>
       </c>
       <c r="G199" s="16" t="inlineStr"/>
@@ -8721,32 +8721,32 @@
     <row r="200">
       <c r="A200" s="13" t="inlineStr">
         <is>
-          <t>Tampilan</t>
+          <t>Sesi Meja &amp; Identitas</t>
         </is>
       </c>
       <c r="B200" s="14" t="inlineStr">
         <is>
-          <t>TC-TM-08</t>
-        </is>
-      </c>
-      <c r="C200" s="21" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-SS-07</t>
+        </is>
+      </c>
+      <c r="C200" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D200" s="13" t="inlineStr">
         <is>
-          <t>Buka daftar panjang mana pun sampai ujung bawah</t>
+          <t>Sisakan satu pesanan belum selesai, tunggu 10 menit</t>
         </is>
       </c>
       <c r="E200" s="13" t="inlineStr">
         <is>
-          <t>Tombol aksi tidak menutupi baris terakhir</t>
+          <t>Sesinya tetap terbuka</t>
         </is>
       </c>
       <c r="F200" s="13" t="inlineStr">
         <is>
-          <t>A-11</t>
+          <t>F-SS-07</t>
         </is>
       </c>
       <c r="G200" s="13" t="inlineStr"/>
@@ -8761,27 +8761,27 @@
       </c>
       <c r="B201" s="17" t="inlineStr">
         <is>
-          <t>TC-TM-09</t>
-        </is>
-      </c>
-      <c r="C201" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TM-01</t>
+        </is>
+      </c>
+      <c r="C201" s="22" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D201" s="16" t="inlineStr">
         <is>
-          <t>Buka menu utama Kasir, Admin, Finance, Super Admin, Owner</t>
+          <t>Ganti tema dari halaman awal, sebelum masuk</t>
         </is>
       </c>
       <c r="E201" s="16" t="inlineStr">
         <is>
-          <t>Halaman awal berisi kartu kelompok, bukan belasan menu</t>
+          <t>Berlaku seketika</t>
         </is>
       </c>
       <c r="F201" s="16" t="inlineStr">
         <is>
-          <t>F-TM-05</t>
+          <t>F-TM-01, F-TM-02</t>
         </is>
       </c>
       <c r="G201" s="16" t="inlineStr"/>
@@ -8796,27 +8796,27 @@
       </c>
       <c r="B202" s="14" t="inlineStr">
         <is>
-          <t>TC-TM-10</t>
-        </is>
-      </c>
-      <c r="C202" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TM-02</t>
+        </is>
+      </c>
+      <c r="C202" s="21" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D202" s="13" t="inlineStr">
         <is>
-          <t>Buka tiap kelompok, hitung seluruh menunya</t>
+          <t>Ganti tema dari tiap peran: Kasir, Chef, Admin, Finance, Owner, Pelanggan</t>
         </is>
       </c>
       <c r="E202" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun menu yang hilang</t>
+          <t>Tersedia dan bekerja di semuanya</t>
         </is>
       </c>
       <c r="F202" s="13" t="inlineStr">
         <is>
-          <t>F-TM-05</t>
+          <t>F-TM-02</t>
         </is>
       </c>
       <c r="G202" s="13" t="inlineStr"/>
@@ -8831,27 +8831,27 @@
       </c>
       <c r="B203" s="17" t="inlineStr">
         <is>
-          <t>TC-TM-11</t>
-        </is>
-      </c>
-      <c r="C203" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TM-03</t>
+        </is>
+      </c>
+      <c r="C203" s="22" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D203" s="16" t="inlineStr">
         <is>
-          <t>Baca kartu kelompok tanpa membukanya</t>
+          <t>Pilih Ikuti HP, ubah tema sistem Android</t>
         </is>
       </c>
       <c r="E203" s="16" t="inlineStr">
         <is>
-          <t>Isinya tersebut di keterangannya</t>
+          <t>Aplikasi mengikuti tanpa dibuka ulang</t>
         </is>
       </c>
       <c r="F203" s="16" t="inlineStr">
         <is>
-          <t>F-TM-06</t>
+          <t>F-TM-01</t>
         </is>
       </c>
       <c r="G203" s="16" t="inlineStr"/>
@@ -8866,27 +8866,27 @@
       </c>
       <c r="B204" s="14" t="inlineStr">
         <is>
-          <t>TC-TM-12</t>
-        </is>
-      </c>
-      <c r="C204" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TM-04</t>
+        </is>
+      </c>
+      <c r="C204" s="21" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D204" s="13" t="inlineStr">
         <is>
-          <t>Periksa Kotak Masuk, Pengaturan, dan Keluar</t>
+          <t>Pilih Gelap, tutup aplikasi, buka lagi</t>
         </is>
       </c>
       <c r="E204" s="13" t="inlineStr">
         <is>
-          <t>Ketiganya di halaman awal, tidak di dalam kelompok</t>
+          <t>Tetap gelap</t>
         </is>
       </c>
       <c r="F204" s="13" t="inlineStr">
         <is>
-          <t>F-TM-07</t>
+          <t>F-TM-03</t>
         </is>
       </c>
       <c r="G204" s="13" t="inlineStr"/>
@@ -8901,27 +8901,27 @@
       </c>
       <c r="B205" s="17" t="inlineStr">
         <is>
-          <t>TC-TM-13</t>
-        </is>
-      </c>
-      <c r="C205" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TM-05</t>
+        </is>
+      </c>
+      <c r="C205" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D205" s="16" t="inlineStr">
         <is>
-          <t>Ajukan top up petty cash, buka halaman awal peran mana pun</t>
+          <t>Telusuri seluruh layar dalam mode gelap</t>
         </is>
       </c>
       <c r="E205" s="16" t="inlineStr">
         <is>
-          <t>Kartu Keuangan membawa penanda merah tanpa perlu dibuka</t>
+          <t>Tidak ada tulisan yang hilang di latarnya; kartu selalu lebih terang daripada latar</t>
         </is>
       </c>
       <c r="F205" s="16" t="inlineStr">
         <is>
-          <t>F-TM-08, A-07</t>
+          <t>A-18</t>
         </is>
       </c>
       <c r="G205" s="16" t="inlineStr"/>
@@ -8936,27 +8936,27 @@
       </c>
       <c r="B206" s="14" t="inlineStr">
         <is>
-          <t>TC-TM-14</t>
-        </is>
-      </c>
-      <c r="C206" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TM-06</t>
+        </is>
+      </c>
+      <c r="C206" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D206" s="13" t="inlineStr">
         <is>
-          <t>Pesanan tunai pelanggan masuk antrean</t>
+          <t>Hal yang sama dalam mode terang</t>
         </is>
       </c>
       <c r="E206" s="13" t="inlineStr">
         <is>
-          <t>Kartu Penjualan membawa penandanya</t>
+          <t>Sama</t>
         </is>
       </c>
       <c r="F206" s="13" t="inlineStr">
         <is>
-          <t>F-TM-08</t>
+          <t>A-18</t>
         </is>
       </c>
       <c r="G206" s="13" t="inlineStr"/>
@@ -8971,27 +8971,27 @@
       </c>
       <c r="B207" s="17" t="inlineStr">
         <is>
-          <t>TC-TM-15</t>
-        </is>
-      </c>
-      <c r="C207" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TM-07</t>
+        </is>
+      </c>
+      <c r="C207" s="22" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D207" s="16" t="inlineStr">
         <is>
-          <t>Setujui seluruh pengajuan, buka lagi halaman awal</t>
+          <t>Perkecil lebar layar / perangkat sempit</t>
         </is>
       </c>
       <c r="E207" s="16" t="inlineStr">
         <is>
-          <t>Penanda di kartu kelompok hilang</t>
+          <t>Pilihan tema menyusut jadi ikon saja</t>
         </is>
       </c>
       <c r="F207" s="16" t="inlineStr">
         <is>
-          <t>F-TM-08</t>
+          <t>F-TM-04</t>
         </is>
       </c>
       <c r="G207" s="16" t="inlineStr"/>
@@ -9001,32 +9001,32 @@
     <row r="208">
       <c r="A208" s="13" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B208" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-01</t>
-        </is>
-      </c>
-      <c r="C208" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TM-08</t>
+        </is>
+      </c>
+      <c r="C208" s="21" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D208" s="13" t="inlineStr">
         <is>
-          <t>Buka List Resto</t>
+          <t>Buka daftar panjang mana pun sampai ujung bawah</t>
         </is>
       </c>
       <c r="E208" s="13" t="inlineStr">
         <is>
-          <t>Seluruh resto terdaftar tampil</t>
+          <t>Tombol aksi tidak menutupi baris terakhir</t>
         </is>
       </c>
       <c r="F208" s="13" t="inlineStr">
         <is>
-          <t>F-SA-01</t>
+          <t>A-11</t>
         </is>
       </c>
       <c r="G208" s="13" t="inlineStr"/>
@@ -9036,12 +9036,12 @@
     <row r="209">
       <c r="A209" s="16" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B209" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-02</t>
+          <t>TC-TM-09</t>
         </is>
       </c>
       <c r="C209" s="20" t="inlineStr">
@@ -9051,17 +9051,17 @@
       </c>
       <c r="D209" s="16" t="inlineStr">
         <is>
-          <t>Kelola karyawan lintas resto, ubah perannya</t>
+          <t>Buka menu utama Kasir, Admin, Finance, Super Admin, Owner</t>
         </is>
       </c>
       <c r="E209" s="16" t="inlineStr">
         <is>
-          <t>Perubahan berlaku; karyawan itu melihat menu sesuai peran barunya</t>
+          <t>Halaman awal berisi kartu kelompok, bukan belasan menu</t>
         </is>
       </c>
       <c r="F209" s="16" t="inlineStr">
         <is>
-          <t>F-SA-02</t>
+          <t>F-TM-05</t>
         </is>
       </c>
       <c r="G209" s="16" t="inlineStr"/>
@@ -9071,12 +9071,12 @@
     <row r="210">
       <c r="A210" s="13" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B210" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-03</t>
+          <t>TC-TM-10</t>
         </is>
       </c>
       <c r="C210" s="15" t="inlineStr">
@@ -9086,17 +9086,17 @@
       </c>
       <c r="D210" s="13" t="inlineStr">
         <is>
-          <t>Kirim pengumuman versi aplikasi</t>
+          <t>Buka tiap kelompok, hitung seluruh menunya</t>
         </is>
       </c>
       <c r="E210" s="13" t="inlineStr">
         <is>
-          <t>Sampai ke seluruh pengguna, di semua resto</t>
+          <t>Tidak ada satu pun menu yang hilang</t>
         </is>
       </c>
       <c r="F210" s="13" t="inlineStr">
         <is>
-          <t>F-SA-03, F-IN-07</t>
+          <t>F-TM-05</t>
         </is>
       </c>
       <c r="G210" s="13" t="inlineStr"/>
@@ -9106,32 +9106,32 @@
     <row r="211">
       <c r="A211" s="16" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B211" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-04</t>
-        </is>
-      </c>
-      <c r="C211" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TM-11</t>
+        </is>
+      </c>
+      <c r="C211" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D211" s="16" t="inlineStr">
         <is>
-          <t>Buka layar Kirim Pengumuman sebagai Admin resto</t>
+          <t>Baca kartu kelompok tanpa membukanya</t>
         </is>
       </c>
       <c r="E211" s="16" t="inlineStr">
         <is>
-          <t>Pilihan kategori Update Aplikasi tidak tersedia</t>
+          <t>Isinya tersebut di keterangannya</t>
         </is>
       </c>
       <c r="F211" s="16" t="inlineStr">
         <is>
-          <t>F-SA-03, F-IN-08</t>
+          <t>F-TM-06</t>
         </is>
       </c>
       <c r="G211" s="16" t="inlineStr"/>
@@ -9141,32 +9141,32 @@
     <row r="212">
       <c r="A212" s="13" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B212" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-05</t>
-        </is>
-      </c>
-      <c r="C212" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TM-12</t>
+        </is>
+      </c>
+      <c r="C212" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D212" s="13" t="inlineStr">
         <is>
-          <t>Kirim pengumuman umum ke seluruh resto</t>
+          <t>Periksa Kotak Masuk, Pengaturan, dan Keluar</t>
         </is>
       </c>
       <c r="E212" s="13" t="inlineStr">
         <is>
-          <t>Muncul di kotak masuk semua resto</t>
+          <t>Ketiganya di halaman awal, tidak di dalam kelompok</t>
         </is>
       </c>
       <c r="F212" s="13" t="inlineStr">
         <is>
-          <t>F-SA-04</t>
+          <t>F-TM-07</t>
         </is>
       </c>
       <c r="G212" s="13" t="inlineStr"/>
@@ -9176,32 +9176,32 @@
     <row r="213">
       <c r="A213" s="16" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B213" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-06</t>
-        </is>
-      </c>
-      <c r="C213" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TM-13</t>
+        </is>
+      </c>
+      <c r="C213" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D213" s="16" t="inlineStr">
         <is>
-          <t>Telusuri menu Super Admin</t>
+          <t>Ajukan top up petty cash, buka halaman awal peran mana pun</t>
         </is>
       </c>
       <c r="E213" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada layar kasir, dapur, maupun keuangan resto</t>
+          <t>Kartu Keuangan membawa penanda merah tanpa perlu dibuka</t>
         </is>
       </c>
       <c r="F213" s="16" t="inlineStr">
         <is>
-          <t>F-SA-06</t>
+          <t>F-TM-08, A-07</t>
         </is>
       </c>
       <c r="G213" s="16" t="inlineStr"/>
@@ -9211,12 +9211,12 @@
     <row r="214">
       <c r="A214" s="13" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B214" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-07</t>
+          <t>TC-TM-14</t>
         </is>
       </c>
       <c r="C214" s="15" t="inlineStr">
@@ -9226,17 +9226,17 @@
       </c>
       <c r="D214" s="13" t="inlineStr">
         <is>
-          <t>List Resto → hapus sebuah resto</t>
+          <t>Pesanan tunai pelanggan masuk antrean</t>
         </is>
       </c>
       <c r="E214" s="13" t="inlineStr">
         <is>
-          <t>Hilang dari daftar; datanya tidak dibuang</t>
+          <t>Kartu Penjualan membawa penandanya</t>
         </is>
       </c>
       <c r="F214" s="13" t="inlineStr">
         <is>
-          <t>F-SA-07</t>
+          <t>F-TM-08</t>
         </is>
       </c>
       <c r="G214" s="13" t="inlineStr"/>
@@ -9246,32 +9246,32 @@
     <row r="215">
       <c r="A215" s="16" t="inlineStr">
         <is>
-          <t>Super Admin</t>
+          <t>Tampilan</t>
         </is>
       </c>
       <c r="B215" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-08</t>
-        </is>
-      </c>
-      <c r="C215" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TM-15</t>
+        </is>
+      </c>
+      <c r="C215" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D215" s="16" t="inlineStr">
         <is>
-          <t>Buka Pilih Resto sebagai pelanggan</t>
+          <t>Setujui seluruh pengajuan, buka lagi halaman awal</t>
         </is>
       </c>
       <c r="E215" s="16" t="inlineStr">
         <is>
-          <t>Resto terhapus tidak muncul</t>
+          <t>Penanda di kartu kelompok hilang</t>
         </is>
       </c>
       <c r="F215" s="16" t="inlineStr">
         <is>
-          <t>F-SA-10</t>
+          <t>F-TM-08</t>
         </is>
       </c>
       <c r="G215" s="16" t="inlineStr"/>
@@ -9286,27 +9286,27 @@
       </c>
       <c r="B216" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-09</t>
-        </is>
-      </c>
-      <c r="C216" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-SA-01</t>
+        </is>
+      </c>
+      <c r="C216" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D216" s="13" t="inlineStr">
         <is>
-          <t>Pindai QR meja resto yang sudah dihapus, coba pesan</t>
+          <t>Buka List Resto</t>
         </is>
       </c>
       <c r="E216" s="13" t="inlineStr">
         <is>
-          <t>Ditolak database, bukan hanya disembunyikan layarnya</t>
+          <t>Seluruh resto terdaftar tampil</t>
         </is>
       </c>
       <c r="F216" s="13" t="inlineStr">
         <is>
-          <t>F-SA-10</t>
+          <t>F-SA-01</t>
         </is>
       </c>
       <c r="G216" s="13" t="inlineStr"/>
@@ -9321,27 +9321,27 @@
       </c>
       <c r="B217" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-10</t>
-        </is>
-      </c>
-      <c r="C217" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-SA-02</t>
+        </is>
+      </c>
+      <c r="C217" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D217" s="16" t="inlineStr">
         <is>
-          <t>Coba ubah harga produk resto terhapus</t>
+          <t>Kelola karyawan lintas resto, ubah perannya</t>
         </is>
       </c>
       <c r="E217" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Perubahan berlaku; karyawan itu melihat menu sesuai peran barunya</t>
         </is>
       </c>
       <c r="F217" s="16" t="inlineStr">
         <is>
-          <t>F-SA-10</t>
+          <t>F-SA-02</t>
         </is>
       </c>
       <c r="G217" s="16" t="inlineStr"/>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="B218" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-11</t>
+          <t>TC-SA-03</t>
         </is>
       </c>
       <c r="C218" s="15" t="inlineStr">
@@ -9366,17 +9366,17 @@
       </c>
       <c r="D218" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan tagihan setelah resto dihapus</t>
+          <t>Kirim pengumuman versi aplikasi</t>
         </is>
       </c>
       <c r="E218" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada tagihan baru untuk resto itu</t>
+          <t>Sampai ke seluruh pengguna, di semua resto</t>
         </is>
       </c>
       <c r="F218" s="13" t="inlineStr">
         <is>
-          <t>F-SA-11</t>
+          <t>F-SA-03, F-IN-07</t>
         </is>
       </c>
       <c r="G218" s="13" t="inlineStr"/>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="B219" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-12</t>
+          <t>TC-SA-04</t>
         </is>
       </c>
       <c r="C219" s="18" t="inlineStr">
@@ -9401,17 +9401,17 @@
       </c>
       <c r="D219" s="16" t="inlineStr">
         <is>
-          <t>Periksa tagihan lama resto terhapus</t>
+          <t>Buka layar Kirim Pengumuman sebagai Admin resto</t>
         </is>
       </c>
       <c r="E219" s="16" t="inlineStr">
         <is>
-          <t>Masih ada dan bisa ditelusuri</t>
+          <t>Pilihan kategori Update Aplikasi tidak tersedia</t>
         </is>
       </c>
       <c r="F219" s="16" t="inlineStr">
         <is>
-          <t>F-SA-11</t>
+          <t>F-SA-03, F-IN-08</t>
         </is>
       </c>
       <c r="G219" s="16" t="inlineStr"/>
@@ -9426,7 +9426,7 @@
       </c>
       <c r="B220" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-13</t>
+          <t>TC-SA-05</t>
         </is>
       </c>
       <c r="C220" s="19" t="inlineStr">
@@ -9436,17 +9436,17 @@
       </c>
       <c r="D220" s="13" t="inlineStr">
         <is>
-          <t>Nyalakan saklar Tampilkan yang dihapus</t>
+          <t>Kirim pengumuman umum ke seluruh resto</t>
         </is>
       </c>
       <c r="E220" s="13" t="inlineStr">
         <is>
-          <t>Resto terhapus muncul, hanya dengan tombol Kembalikan</t>
+          <t>Muncul di kotak masuk semua resto</t>
         </is>
       </c>
       <c r="F220" s="13" t="inlineStr">
         <is>
-          <t>F-SA-09</t>
+          <t>F-SA-04</t>
         </is>
       </c>
       <c r="G220" s="13" t="inlineStr"/>
@@ -9461,27 +9461,27 @@
       </c>
       <c r="B221" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-14</t>
-        </is>
-      </c>
-      <c r="C221" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-SA-06</t>
+        </is>
+      </c>
+      <c r="C221" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D221" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Kembalikan</t>
+          <t>Telusuri menu Super Admin</t>
         </is>
       </c>
       <c r="E221" s="16" t="inlineStr">
         <is>
-          <t>Kembali ke daftar, tapi belum aktif — harus dinyalakan sendiri</t>
+          <t>Tidak ada layar kasir, dapur, maupun keuangan resto</t>
         </is>
       </c>
       <c r="F221" s="16" t="inlineStr">
         <is>
-          <t>F-SA-08</t>
+          <t>F-SA-06</t>
         </is>
       </c>
       <c r="G221" s="16" t="inlineStr"/>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="B222" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-15</t>
+          <t>TC-SA-07</t>
         </is>
       </c>
       <c r="C222" s="15" t="inlineStr">
@@ -9506,17 +9506,17 @@
       </c>
       <c r="D222" s="13" t="inlineStr">
         <is>
-          <t>Coba hapus penyewa platform (KaataGo)</t>
+          <t>List Resto → hapus sebuah resto</t>
         </is>
       </c>
       <c r="E222" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Hilang dari daftar; datanya tidak dibuang</t>
         </is>
       </c>
       <c r="F222" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-SA-07</t>
         </is>
       </c>
       <c r="G222" s="13" t="inlineStr"/>
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B223" s="17" t="inlineStr">
         <is>
-          <t>TC-SA-16</t>
+          <t>TC-SA-08</t>
         </is>
       </c>
       <c r="C223" s="18" t="inlineStr">
@@ -9541,17 +9541,17 @@
       </c>
       <c r="D223" s="16" t="inlineStr">
         <is>
-          <t>Coba set_resto_deleted sebagai Owner resto</t>
+          <t>Buka Pilih Resto sebagai pelanggan</t>
         </is>
       </c>
       <c r="E223" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — hanya Super Admin</t>
+          <t>Resto terhapus tidak muncul</t>
         </is>
       </c>
       <c r="F223" s="16" t="inlineStr">
         <is>
-          <t>F-SA-07</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G223" s="16" t="inlineStr"/>
@@ -9566,27 +9566,27 @@
       </c>
       <c r="B224" s="14" t="inlineStr">
         <is>
-          <t>TC-SA-17</t>
-        </is>
-      </c>
-      <c r="C224" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-09</t>
+        </is>
+      </c>
+      <c r="C224" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D224" s="13" t="inlineStr">
         <is>
-          <t>Periksa baris resto terhapus di database</t>
+          <t>Pindai QR meja resto yang sudah dihapus, coba pesan</t>
         </is>
       </c>
       <c r="E224" s="13" t="inlineStr">
         <is>
-          <t>deleted_by dan deleted_at terisi</t>
+          <t>Ditolak database, bukan hanya disembunyikan layarnya</t>
         </is>
       </c>
       <c r="F224" s="13" t="inlineStr">
         <is>
-          <t>F-SA-12</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G224" s="13" t="inlineStr"/>
@@ -9596,32 +9596,32 @@
     <row r="225">
       <c r="A225" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B225" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-01</t>
-        </is>
-      </c>
-      <c r="C225" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-10</t>
+        </is>
+      </c>
+      <c r="C225" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D225" s="16" t="inlineStr">
         <is>
-          <t>Buka pengumuman versi → Unduh Versi Terbaru</t>
+          <t>Coba ubah harga produk resto terhapus</t>
         </is>
       </c>
       <c r="E225" s="16" t="inlineStr">
         <is>
-          <t>Unduhan mulai di dalam aplikasi, tidak membuka peramban</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F225" s="16" t="inlineStr">
         <is>
-          <t>F-UP-01, F-UP-02</t>
+          <t>F-SA-10</t>
         </is>
       </c>
       <c r="G225" s="16" t="inlineStr"/>
@@ -9631,32 +9631,32 @@
     <row r="226">
       <c r="A226" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B226" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-02</t>
-        </is>
-      </c>
-      <c r="C226" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-11</t>
+        </is>
+      </c>
+      <c r="C226" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D226" s="13" t="inlineStr">
         <is>
-          <t>Perhatikan bar notifikasi HP</t>
+          <t>Terbitkan tagihan setelah resto dihapus</t>
         </is>
       </c>
       <c r="E226" s="13" t="inlineStr">
         <is>
-          <t>Kemajuannya tampil berikut persennya</t>
+          <t>Tidak ada tagihan baru untuk resto itu</t>
         </is>
       </c>
       <c r="F226" s="13" t="inlineStr">
         <is>
-          <t>F-UP-03</t>
+          <t>F-SA-11</t>
         </is>
       </c>
       <c r="G226" s="13" t="inlineStr"/>
@@ -9666,32 +9666,32 @@
     <row r="227">
       <c r="A227" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B227" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-03</t>
-        </is>
-      </c>
-      <c r="C227" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-12</t>
+        </is>
+      </c>
+      <c r="C227" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D227" s="16" t="inlineStr">
         <is>
-          <t>Kunci HP saat unduhan berjalan, tunggu, buka lagi</t>
+          <t>Periksa tagihan lama resto terhapus</t>
         </is>
       </c>
       <c r="E227" s="16" t="inlineStr">
         <is>
-          <t>Unduhannya lanjut, tidak mengulang dari nol</t>
+          <t>Masih ada dan bisa ditelusuri</t>
         </is>
       </c>
       <c r="F227" s="16" t="inlineStr">
         <is>
-          <t>F-UP-04</t>
+          <t>F-SA-11</t>
         </is>
       </c>
       <c r="G227" s="16" t="inlineStr"/>
@@ -9701,12 +9701,12 @@
     <row r="228">
       <c r="A228" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B228" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-04</t>
+          <t>TC-SA-13</t>
         </is>
       </c>
       <c r="C228" s="19" t="inlineStr">
@@ -9716,17 +9716,17 @@
       </c>
       <c r="D228" s="13" t="inlineStr">
         <is>
-          <t>Tekan tombol unduh lagi saat unduhan berjalan</t>
+          <t>Nyalakan saklar Tampilkan yang dihapus</t>
         </is>
       </c>
       <c r="E228" s="13" t="inlineStr">
         <is>
-          <t>Muncul pilihan Batalkan atau Lanjutkan</t>
+          <t>Resto terhapus muncul, hanya dengan tombol Kembalikan</t>
         </is>
       </c>
       <c r="F228" s="13" t="inlineStr">
         <is>
-          <t>F-UP-05, F-IN-18</t>
+          <t>F-SA-09</t>
         </is>
       </c>
       <c r="G228" s="13" t="inlineStr"/>
@@ -9736,32 +9736,32 @@
     <row r="229">
       <c r="A229" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B229" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-05</t>
-        </is>
-      </c>
-      <c r="C229" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-14</t>
+        </is>
+      </c>
+      <c r="C229" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D229" s="16" t="inlineStr">
         <is>
-          <t>Pilih Batalkan</t>
+          <t>Ketuk Kembalikan</t>
         </is>
       </c>
       <c r="E229" s="16" t="inlineStr">
         <is>
-          <t>Unduhan berhenti; tidak ditampilkan sebagai galat</t>
+          <t>Kembali ke daftar, tapi belum aktif — harus dinyalakan sendiri</t>
         </is>
       </c>
       <c r="F229" s="16" t="inlineStr">
         <is>
-          <t>F-IN-19</t>
+          <t>F-SA-08</t>
         </is>
       </c>
       <c r="G229" s="16" t="inlineStr"/>
@@ -9771,32 +9771,32 @@
     <row r="230">
       <c r="A230" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B230" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-06</t>
-        </is>
-      </c>
-      <c r="C230" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-15</t>
+        </is>
+      </c>
+      <c r="C230" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D230" s="13" t="inlineStr">
         <is>
-          <t>Biarkan unduhan selesai</t>
+          <t>Coba hapus penyewa platform (KaataGo)</t>
         </is>
       </c>
       <c r="E230" s="13" t="inlineStr">
         <is>
-          <t>Notifikasi "ketuk untuk memasang"; pemasang Android terbuka</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F230" s="13" t="inlineStr">
         <is>
-          <t>F-UP-06, F-IN-17</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G230" s="13" t="inlineStr"/>
@@ -9806,32 +9806,32 @@
     <row r="231">
       <c r="A231" s="16" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B231" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-07</t>
-        </is>
-      </c>
-      <c r="C231" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-SA-16</t>
+        </is>
+      </c>
+      <c r="C231" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D231" s="16" t="inlineStr">
         <is>
-          <t>Matikan data seluler di tengah unduhan</t>
+          <t>Coba set_resto_deleted sebagai Owner resto</t>
         </is>
       </c>
       <c r="E231" s="16" t="inlineStr">
         <is>
-          <t>Pesannya menyebut masalah koneksi, satu kalimat, tanpa isi galat mentah</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F231" s="16" t="inlineStr">
         <is>
-          <t>F-UP-07, F-IN-19</t>
+          <t>F-SA-07</t>
         </is>
       </c>
       <c r="G231" s="16" t="inlineStr"/>
@@ -9841,32 +9841,32 @@
     <row r="232">
       <c r="A232" s="13" t="inlineStr">
         <is>
-          <t>Pembaruan Aplikasi</t>
+          <t>Super Admin</t>
         </is>
       </c>
       <c r="B232" s="14" t="inlineStr">
         <is>
-          <t>TC-UP-08</t>
-        </is>
-      </c>
-      <c r="C232" s="21" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-SA-17</t>
+        </is>
+      </c>
+      <c r="C232" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D232" s="13" t="inlineStr">
         <is>
-          <t>Penuhi penyimpanan HP, lalu unduh</t>
+          <t>Periksa baris resto terhapus di database</t>
         </is>
       </c>
       <c r="E232" s="13" t="inlineStr">
         <is>
-          <t>Pesannya menyebut penyimpanan penuh — dibedakan dari masalah koneksi</t>
+          <t>deleted_by dan deleted_at terisi</t>
         </is>
       </c>
       <c r="F232" s="13" t="inlineStr">
         <is>
-          <t>F-UP-07</t>
+          <t>F-SA-12</t>
         </is>
       </c>
       <c r="G232" s="13" t="inlineStr"/>
@@ -9881,27 +9881,27 @@
       </c>
       <c r="B233" s="17" t="inlineStr">
         <is>
-          <t>TC-UP-09</t>
-        </is>
-      </c>
-      <c r="C233" s="22" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TC-UP-01</t>
+        </is>
+      </c>
+      <c r="C233" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D233" s="16" t="inlineStr">
         <is>
-          <t>Pakai jalur cadangan lewat peramban</t>
+          <t>Buka pengumuman versi → Unduh Versi Terbaru</t>
         </is>
       </c>
       <c r="E233" s="16" t="inlineStr">
         <is>
-          <t>Berkasnya terunduh</t>
+          <t>Unduhan mulai di dalam aplikasi, tidak membuka peramban</t>
         </is>
       </c>
       <c r="F233" s="16" t="inlineStr">
         <is>
-          <t>F-IN-06</t>
+          <t>F-UP-01, F-UP-02</t>
         </is>
       </c>
       <c r="G233" s="16" t="inlineStr"/>
@@ -9911,12 +9911,12 @@
     <row r="234">
       <c r="A234" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B234" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-01</t>
+          <t>TC-UP-02</t>
         </is>
       </c>
       <c r="C234" s="19" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="D234" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Billing Resto → atur harga dan tanggal untuk sebuah resto</t>
+          <t>Perhatikan bar notifikasi HP</t>
         </is>
       </c>
       <c r="E234" s="13" t="inlineStr">
         <is>
-          <t>Tersimpan; kartu restonya menampilkan harga, tanggal, dan tenggangnya</t>
+          <t>Kemajuannya tampil berikut persennya</t>
         </is>
       </c>
       <c r="F234" s="13" t="inlineStr">
         <is>
-          <t>F-BL-01, F-BL-02</t>
+          <t>F-UP-03</t>
         </is>
       </c>
       <c r="G234" s="13" t="inlineStr"/>
@@ -9946,12 +9946,12 @@
     <row r="235">
       <c r="A235" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B235" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-02</t>
+          <t>TC-UP-03</t>
         </is>
       </c>
       <c r="C235" s="20" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="D235" s="16" t="inlineStr">
         <is>
-          <t>Buat resto baru, buka Billing Resto</t>
+          <t>Kunci HP saat unduhan berjalan, tunggu, buka lagi</t>
         </is>
       </c>
       <c r="E235" s="16" t="inlineStr">
         <is>
-          <t>Sudah punya barisnya sendiri, berstatus Gratis</t>
+          <t>Unduhannya lanjut, tidak mengulang dari nol</t>
         </is>
       </c>
       <c r="F235" s="16" t="inlineStr">
         <is>
-          <t>F-BL-06</t>
+          <t>F-UP-04</t>
         </is>
       </c>
       <c r="G235" s="16" t="inlineStr"/>
@@ -9981,32 +9981,32 @@
     <row r="236">
       <c r="A236" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B236" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-03</t>
-        </is>
-      </c>
-      <c r="C236" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-04</t>
+        </is>
+      </c>
+      <c r="C236" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D236" s="13" t="inlineStr">
         <is>
-          <t>Setel harga Rp 0, lewatkan tanggal jatuh tempo jauh</t>
+          <t>Tekan tombol unduh lagi saat unduhan berjalan</t>
         </is>
       </c>
       <c r="E236" s="13" t="inlineStr">
         <is>
-          <t>Tidak pernah terbit tagihan, tidak pernah terkunci</t>
+          <t>Muncul pilihan Batalkan atau Lanjutkan</t>
         </is>
       </c>
       <c r="F236" s="13" t="inlineStr">
         <is>
-          <t>F-BL-04</t>
+          <t>F-UP-05, F-IN-18</t>
         </is>
       </c>
       <c r="G236" s="13" t="inlineStr"/>
@@ -10016,32 +10016,32 @@
     <row r="237">
       <c r="A237" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B237" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-04</t>
-        </is>
-      </c>
-      <c r="C237" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-05</t>
+        </is>
+      </c>
+      <c r="C237" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D237" s="16" t="inlineStr">
         <is>
-          <t>Matikan saklar langganan pada resto berbayar yang menunggak</t>
+          <t>Pilih Batalkan</t>
         </is>
       </c>
       <c r="E237" s="16" t="inlineStr">
         <is>
-          <t>Tidak terkunci</t>
+          <t>Unduhan berhenti; tidak ditampilkan sebagai galat</t>
         </is>
       </c>
       <c r="F237" s="16" t="inlineStr">
         <is>
-          <t>F-BL-05</t>
+          <t>F-IN-19</t>
         </is>
       </c>
       <c r="G237" s="16" t="inlineStr"/>
@@ -10051,12 +10051,12 @@
     <row r="238">
       <c r="A238" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B238" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-05</t>
+          <t>TC-UP-06</t>
         </is>
       </c>
       <c r="C238" s="19" t="inlineStr">
@@ -10066,17 +10066,17 @@
       </c>
       <c r="D238" s="13" t="inlineStr">
         <is>
-          <t>Coba pilih tanggal tagihan 29, 30, atau 31</t>
+          <t>Biarkan unduhan selesai</t>
         </is>
       </c>
       <c r="E238" s="13" t="inlineStr">
         <is>
-          <t>Tidak tersedia di pilihan — hanya 1 sampai 28</t>
+          <t>Notifikasi "ketuk untuk memasang"; pemasang Android terbuka</t>
         </is>
       </c>
       <c r="F238" s="13" t="inlineStr">
         <is>
-          <t>F-BL-02</t>
+          <t>F-UP-06, F-IN-17</t>
         </is>
       </c>
       <c r="G238" s="13" t="inlineStr"/>
@@ -10086,12 +10086,12 @@
     <row r="239">
       <c r="A239" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B239" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-06</t>
+          <t>TC-UP-07</t>
         </is>
       </c>
       <c r="C239" s="20" t="inlineStr">
@@ -10101,17 +10101,17 @@
       </c>
       <c r="D239" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Terbitkan tagihan sekarang dua kali beruntun</t>
+          <t>Matikan data seluler di tengah unduhan</t>
         </is>
       </c>
       <c r="E239" s="16" t="inlineStr">
         <is>
-          <t>Tagihan tetap satu untuk periode itu</t>
+          <t>Pesannya menyebut masalah koneksi, satu kalimat, tanpa isi galat mentah</t>
         </is>
       </c>
       <c r="F239" s="16" t="inlineStr">
         <is>
-          <t>F-BL-08</t>
+          <t>F-UP-07, F-IN-19</t>
         </is>
       </c>
       <c r="G239" s="16" t="inlineStr"/>
@@ -10121,32 +10121,32 @@
     <row r="240">
       <c r="A240" s="13" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B240" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-07</t>
-        </is>
-      </c>
-      <c r="C240" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-UP-08</t>
+        </is>
+      </c>
+      <c r="C240" s="21" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D240" s="13" t="inlineStr">
         <is>
-          <t>Setel jatuh tempo 3 hari lagi, buka aplikasi sebagai Kasir</t>
+          <t>Penuhi penyimpanan HP, lalu unduh</t>
         </is>
       </c>
       <c r="E240" s="13" t="inlineStr">
         <is>
-          <t>Pita pengingat tampil di atas layar; isi layarnya tetap bisa dipakai</t>
+          <t>Pesannya menyebut penyimpanan penuh — dibedakan dari masalah koneksi</t>
         </is>
       </c>
       <c r="F240" s="13" t="inlineStr">
         <is>
-          <t>F-BL-09</t>
+          <t>F-UP-07</t>
         </is>
       </c>
       <c r="G240" s="13" t="inlineStr"/>
@@ -10156,32 +10156,32 @@
     <row r="241">
       <c r="A241" s="16" t="inlineStr">
         <is>
-          <t>## 19b. Langganan &amp; Tagihan Resto</t>
+          <t>Pembaruan Aplikasi</t>
         </is>
       </c>
       <c r="B241" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-08</t>
-        </is>
-      </c>
-      <c r="C241" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-UP-09</t>
+        </is>
+      </c>
+      <c r="C241" s="22" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D241" s="16" t="inlineStr">
         <is>
-          <t>Setel jatuh tempo 4 hari lagi</t>
+          <t>Pakai jalur cadangan lewat peramban</t>
         </is>
       </c>
       <c r="E241" s="16" t="inlineStr">
         <is>
-          <t>Pita belum tampil</t>
+          <t>Berkasnya terunduh</t>
         </is>
       </c>
       <c r="F241" s="16" t="inlineStr">
         <is>
-          <t>F-BL-09</t>
+          <t>F-IN-06</t>
         </is>
       </c>
       <c r="G241" s="16" t="inlineStr"/>
@@ -10196,27 +10196,27 @@
       </c>
       <c r="B242" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-09</t>
-        </is>
-      </c>
-      <c r="C242" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-01</t>
+        </is>
+      </c>
+      <c r="C242" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D242" s="13" t="inlineStr">
         <is>
-          <t>Lewati jatuh tempo, masih dalam tenggang</t>
+          <t>Super Admin → Billing Resto → atur harga dan tanggal untuk sebuah resto</t>
         </is>
       </c>
       <c r="E242" s="13" t="inlineStr">
         <is>
-          <t>Pita berubah merah; aplikasi belum terkunci</t>
+          <t>Tersimpan; kartu restonya menampilkan harga, tanggal, dan tenggangnya</t>
         </is>
       </c>
       <c r="F242" s="13" t="inlineStr">
         <is>
-          <t>F-BL-03, F-BL-10</t>
+          <t>F-BL-01, F-BL-02</t>
         </is>
       </c>
       <c r="G242" s="13" t="inlineStr"/>
@@ -10231,27 +10231,27 @@
       </c>
       <c r="B243" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-10</t>
-        </is>
-      </c>
-      <c r="C243" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-02</t>
+        </is>
+      </c>
+      <c r="C243" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D243" s="16" t="inlineStr">
         <is>
-          <t>Lewati tenggang, tagihan belum dibayar</t>
+          <t>Buat resto baru, buka Billing Resto</t>
         </is>
       </c>
       <c r="E243" s="16" t="inlineStr">
         <is>
-          <t>Seluruh layar diganti halaman Aplikasi Terkunci Sementara</t>
+          <t>Sudah punya barisnya sendiri, berstatus Gratis</t>
         </is>
       </c>
       <c r="F243" s="16" t="inlineStr">
         <is>
-          <t>F-BL-15</t>
+          <t>F-BL-06</t>
         </is>
       </c>
       <c r="G243" s="16" t="inlineStr"/>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="B244" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-11</t>
+          <t>TC-BL-03</t>
         </is>
       </c>
       <c r="C244" s="15" t="inlineStr">
@@ -10276,17 +10276,17 @@
       </c>
       <c r="D244" s="13" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, coba buat pesanan lewat API langsung</t>
+          <t>Setel harga Rp 0, lewatkan tanggal jatuh tempo jauh</t>
         </is>
       </c>
       <c r="E244" s="13" t="inlineStr">
         <is>
-          <t>Ditolak database — bukan hanya layarnya yang menutup</t>
+          <t>Tidak pernah terbit tagihan, tidak pernah terkunci</t>
         </is>
       </c>
       <c r="F244" s="13" t="inlineStr">
         <is>
-          <t>F-BL-18, TSD §7.3</t>
+          <t>F-BL-04</t>
         </is>
       </c>
       <c r="G244" s="13" t="inlineStr"/>
@@ -10301,7 +10301,7 @@
       </c>
       <c r="B245" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-12</t>
+          <t>TC-BL-04</t>
         </is>
       </c>
       <c r="C245" s="18" t="inlineStr">
@@ -10311,17 +10311,17 @@
       </c>
       <c r="D245" s="16" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, ketuk Lihat &amp; Bayar Tagihan</t>
+          <t>Matikan saklar langganan pada resto berbayar yang menunggak</t>
         </is>
       </c>
       <c r="E245" s="16" t="inlineStr">
         <is>
-          <t>Layar tagihan terbuka dan bisa dipakai</t>
+          <t>Tidak terkunci</t>
         </is>
       </c>
       <c r="F245" s="16" t="inlineStr">
         <is>
-          <t>F-BL-16</t>
+          <t>F-BL-05</t>
         </is>
       </c>
       <c r="G245" s="16" t="inlineStr"/>
@@ -10336,27 +10336,27 @@
       </c>
       <c r="B246" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-13</t>
-        </is>
-      </c>
-      <c r="C246" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-05</t>
+        </is>
+      </c>
+      <c r="C246" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D246" s="13" t="inlineStr">
         <is>
-          <t>Pada keadaan terkunci, ketuk Keluar</t>
+          <t>Coba pilih tanggal tagihan 29, 30, atau 31</t>
         </is>
       </c>
       <c r="E246" s="13" t="inlineStr">
         <is>
-          <t>Berhasil keluar akun</t>
+          <t>Tidak tersedia di pilihan — hanya 1 sampai 28</t>
         </is>
       </c>
       <c r="F246" s="13" t="inlineStr">
         <is>
-          <t>F-BL-16</t>
+          <t>F-BL-02</t>
         </is>
       </c>
       <c r="G246" s="13" t="inlineStr"/>
@@ -10371,27 +10371,27 @@
       </c>
       <c r="B247" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14</t>
-        </is>
-      </c>
-      <c r="C247" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-06</t>
+        </is>
+      </c>
+      <c r="C247" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D247" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Buat Virtual Account → pilih BCA</t>
+          <t>Ketuk Terbitkan tagihan sekarang dua kali beruntun</t>
         </is>
       </c>
       <c r="E247" s="16" t="inlineStr">
         <is>
-          <t>Nomor VA tampil berikut nominal dan masa berlakunya</t>
+          <t>Tagihan tetap satu untuk periode itu</t>
         </is>
       </c>
       <c r="F247" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11, F-BL-19</t>
+          <t>F-BL-08</t>
         </is>
       </c>
       <c r="G247" s="16" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="B248" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14b</t>
+          <t>TC-BL-07</t>
         </is>
       </c>
       <c r="C248" s="15" t="inlineStr">
@@ -10416,17 +10416,17 @@
       </c>
       <c r="D248" s="13" t="inlineStr">
         <is>
-          <t>Tutup layar, buka lagi, ketuk lagi</t>
+          <t>Setel jatuh tempo 3 hari lagi, buka aplikasi sebagai Kasir</t>
         </is>
       </c>
       <c r="E248" s="13" t="inlineStr">
         <is>
-          <t>Nomor VA sama, tidak diterbitkan yang baru</t>
+          <t>Pita pengingat tampil di atas layar; isi layarnya tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F248" s="13" t="inlineStr">
         <is>
-          <t>F-BL-23</t>
+          <t>F-BL-09</t>
         </is>
       </c>
       <c r="G248" s="13" t="inlineStr"/>
@@ -10441,27 +10441,27 @@
       </c>
       <c r="B249" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14c</t>
-        </is>
-      </c>
-      <c r="C249" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-08</t>
+        </is>
+      </c>
+      <c r="C249" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D249" s="16" t="inlineStr">
         <is>
-          <t>Transfer tepat sesuai nominal ke VA itu</t>
+          <t>Setel jatuh tempo 4 hari lagi</t>
         </is>
       </c>
       <c r="E249" s="16" t="inlineStr">
         <is>
-          <t>Tagihan lunas sendiri dalam hitungan detik; kunci terbuka tanpa mengirim bukti</t>
+          <t>Pita belum tampil</t>
         </is>
       </c>
       <c r="F249" s="16" t="inlineStr">
         <is>
-          <t>F-BL-22</t>
+          <t>F-BL-09</t>
         </is>
       </c>
       <c r="G249" s="16" t="inlineStr"/>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="B250" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14d</t>
+          <t>TC-BL-09</t>
         </is>
       </c>
       <c r="C250" s="15" t="inlineStr">
@@ -10486,17 +10486,17 @@
       </c>
       <c r="D250" s="13" t="inlineStr">
         <is>
-          <t>Transfer kurang dari nominal</t>
+          <t>Lewati jatuh tempo, masih dalam tenggang</t>
         </is>
       </c>
       <c r="E250" s="13" t="inlineStr">
         <is>
-          <t>Tidak melunasi; tagihan tetap terbuka</t>
+          <t>Pita berubah merah; aplikasi belum terkunci</t>
         </is>
       </c>
       <c r="F250" s="13" t="inlineStr">
         <is>
-          <t>F-BL-20</t>
+          <t>F-BL-03, F-BL-10</t>
         </is>
       </c>
       <c r="G250" s="13" t="inlineStr"/>
@@ -10511,27 +10511,27 @@
       </c>
       <c r="B251" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14e</t>
-        </is>
-      </c>
-      <c r="C251" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-10</t>
+        </is>
+      </c>
+      <c r="C251" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D251" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Ganti Bank → pilih BNI</t>
+          <t>Lewati tenggang, tagihan belum dibayar</t>
         </is>
       </c>
       <c r="E251" s="16" t="inlineStr">
         <is>
-          <t>Nomor VA baru untuk bank itu</t>
+          <t>Seluruh layar diganti halaman Aplikasi Terkunci Sementara</t>
         </is>
       </c>
       <c r="F251" s="16" t="inlineStr">
         <is>
-          <t>F-BL-19</t>
+          <t>F-BL-15</t>
         </is>
       </c>
       <c r="G251" s="16" t="inlineStr"/>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="B252" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14f</t>
+          <t>TC-BL-11</t>
         </is>
       </c>
       <c r="C252" s="15" t="inlineStr">
@@ -10556,17 +10556,17 @@
       </c>
       <c r="D252" s="13" t="inlineStr">
         <is>
-          <t>Periksa rekening tujuan dana VA di Dashboard Xendit</t>
+          <t>Pada keadaan terkunci, coba buat pesanan lewat API langsung</t>
         </is>
       </c>
       <c r="E252" s="13" t="inlineStr">
         <is>
-          <t>Masuk ke akun KaataGo, bukan sub-akun resto</t>
+          <t>Ditolak database — bukan hanya layarnya yang menutup</t>
         </is>
       </c>
       <c r="F252" s="13" t="inlineStr">
         <is>
-          <t>F-BL-11, TSD §7.3</t>
+          <t>F-BL-18, TSD §7.3</t>
         </is>
       </c>
       <c r="G252" s="13" t="inlineStr"/>
@@ -10581,7 +10581,7 @@
       </c>
       <c r="B253" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14g</t>
+          <t>TC-BL-12</t>
         </is>
       </c>
       <c r="C253" s="18" t="inlineStr">
@@ -10591,17 +10591,17 @@
       </c>
       <c r="D253" s="16" t="inlineStr">
         <is>
-          <t>Kirim callback palsu ke xendit-billing-webhook tanpa token</t>
+          <t>Pada keadaan terkunci, ketuk Lihat &amp; Bayar Tagihan</t>
         </is>
       </c>
       <c r="E253" s="16" t="inlineStr">
         <is>
-          <t>Ditolak 401; tagihan tidak berubah</t>
+          <t>Layar tagihan terbuka dan bisa dipakai</t>
         </is>
       </c>
       <c r="F253" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-16</t>
         </is>
       </c>
       <c r="G253" s="16" t="inlineStr"/>
@@ -10616,27 +10616,27 @@
       </c>
       <c r="B254" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-14h</t>
-        </is>
-      </c>
-      <c r="C254" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-13</t>
+        </is>
+      </c>
+      <c r="C254" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D254" s="13" t="inlineStr">
         <is>
-          <t>Xendit mengirim callback yang sama dua kali</t>
+          <t>Pada keadaan terkunci, ketuk Keluar</t>
         </is>
       </c>
       <c r="E254" s="13" t="inlineStr">
         <is>
-          <t>Tagihan tetap lunas sekali; catatan pelunasnya tidak berubah</t>
+          <t>Berhasil keluar akun</t>
         </is>
       </c>
       <c r="F254" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-16</t>
         </is>
       </c>
       <c r="G254" s="13" t="inlineStr"/>
@@ -10651,27 +10651,27 @@
       </c>
       <c r="B255" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-14i</t>
-        </is>
-      </c>
-      <c r="C255" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-14</t>
+        </is>
+      </c>
+      <c r="C255" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D255" s="16" t="inlineStr">
         <is>
-          <t>Unggah bukti transfer manual lewat jalur cadangan</t>
+          <t>Ketuk Buat Virtual Account → pilih BCA</t>
         </is>
       </c>
       <c r="E255" s="16" t="inlineStr">
         <is>
-          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
+          <t>Nomor VA tampil berikut nominal dan masa berlakunya</t>
         </is>
       </c>
       <c r="F255" s="16" t="inlineStr">
         <is>
-          <t>F-BL-24, F-BL-12</t>
+          <t>F-BL-11, F-BL-19</t>
         </is>
       </c>
       <c r="G255" s="16" t="inlineStr"/>
@@ -10686,27 +10686,27 @@
       </c>
       <c r="B256" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-26</t>
-        </is>
-      </c>
-      <c r="C256" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-14b</t>
+        </is>
+      </c>
+      <c r="C256" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D256" s="13" t="inlineStr">
         <is>
-          <t>Dengan kunci uji Xendit, buka tagihan ber-VA</t>
+          <t>Tutup layar, buka lagi, ketuk lagi</t>
         </is>
       </c>
       <c r="E256" s="13" t="inlineStr">
         <is>
-          <t>Tombol Simulasikan Pembayaran muncul</t>
+          <t>Nomor VA sama, tidak diterbitkan yang baru</t>
         </is>
       </c>
       <c r="F256" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-23</t>
         </is>
       </c>
       <c r="G256" s="13" t="inlineStr"/>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="B257" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-27</t>
+          <t>TC-BL-14c</t>
         </is>
       </c>
       <c r="C257" s="18" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="D257" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Simulasikan Pembayaran</t>
+          <t>Transfer tepat sesuai nominal ke VA itu</t>
         </is>
       </c>
       <c r="E257" s="16" t="inlineStr">
         <is>
-          <t>Tagihan jadi Lunas sendiri lewat webhook; kunci resto terbuka</t>
+          <t>Tagihan lunas sendiri dalam hitungan detik; kunci terbuka tanpa mengirim bukti</t>
         </is>
       </c>
       <c r="F257" s="16" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="B258" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-28</t>
+          <t>TC-BL-14d</t>
         </is>
       </c>
       <c r="C258" s="15" t="inlineStr">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="D258" s="13" t="inlineStr">
         <is>
-          <t>Pasang kunci produksi Xendit, buka layar yang sama</t>
+          <t>Transfer kurang dari nominal</t>
         </is>
       </c>
       <c r="E258" s="13" t="inlineStr">
         <is>
-          <t>Tombol simulasi hilang sendiri</t>
+          <t>Tidak melunasi; tagihan tetap terbuka</t>
         </is>
       </c>
       <c r="F258" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G258" s="13" t="inlineStr"/>
@@ -10791,27 +10791,27 @@
       </c>
       <c r="B259" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-29</t>
-        </is>
-      </c>
-      <c r="C259" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14e</t>
+        </is>
+      </c>
+      <c r="C259" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D259" s="16" t="inlineStr">
         <is>
-          <t>Buat diskon langganan setelah tagihan terbit → ketuk segarkan di Super Admin</t>
+          <t>Ketuk Ganti Bank → pilih BNI</t>
         </is>
       </c>
       <c r="E259" s="16" t="inlineStr">
         <is>
-          <t>Nominal tagihan turun; nomor VA lama dibuang</t>
+          <t>Nomor VA baru untuk bank itu</t>
         </is>
       </c>
       <c r="F259" s="16" t="inlineStr">
         <is>
-          <t>F-BL-05</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G259" s="16" t="inlineStr"/>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="B260" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-30</t>
+          <t>TC-BL-14f</t>
         </is>
       </c>
       <c r="C260" s="15" t="inlineStr">
@@ -10836,17 +10836,17 @@
       </c>
       <c r="D260" s="13" t="inlineStr">
         <is>
-          <t>Buat VA baru setelah nominalnya berubah</t>
+          <t>Periksa rekening tujuan dana VA di Dashboard Xendit</t>
         </is>
       </c>
       <c r="E260" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sesuai yang sudah dipotong</t>
+          <t>Masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
       <c r="F260" s="13" t="inlineStr">
         <is>
-          <t>F-BL-20</t>
+          <t>F-BL-11, TSD §7.3</t>
         </is>
       </c>
       <c r="G260" s="13" t="inlineStr"/>
@@ -10861,7 +10861,7 @@
       </c>
       <c r="B261" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-15</t>
+          <t>TC-BL-14g</t>
         </is>
       </c>
       <c r="C261" s="18" t="inlineStr">
@@ -10871,17 +10871,17 @@
       </c>
       <c r="D261" s="16" t="inlineStr">
         <is>
-          <t>Coba kirim bukti tanpa melampirkan foto</t>
+          <t>Kirim callback palsu ke xendit-billing-webhook tanpa token</t>
         </is>
       </c>
       <c r="E261" s="16" t="inlineStr">
         <is>
-          <t>Tombol Kirim mati</t>
+          <t>Ditolak 401; tagihan tidak berubah</t>
         </is>
       </c>
       <c r="F261" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G261" s="16" t="inlineStr"/>
@@ -10896,27 +10896,27 @@
       </c>
       <c r="B262" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-16</t>
-        </is>
-      </c>
-      <c r="C262" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14h</t>
+        </is>
+      </c>
+      <c r="C262" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D262" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → tab Tagihan → Terima</t>
+          <t>Xendit mengirim callback yang sama dua kali</t>
         </is>
       </c>
       <c r="E262" s="13" t="inlineStr">
         <is>
-          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
+          <t>Tagihan tetap lunas sekali; catatan pelunasnya tidak berubah</t>
         </is>
       </c>
       <c r="F262" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G262" s="13" t="inlineStr"/>
@@ -10931,27 +10931,27 @@
       </c>
       <c r="B263" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-17</t>
-        </is>
-      </c>
-      <c r="C263" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-14i</t>
+        </is>
+      </c>
+      <c r="C263" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D263" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Tolak tanpa mengisi alasan</t>
+          <t>Unggah bukti transfer manual lewat jalur cadangan</t>
         </is>
       </c>
       <c r="E263" s="16" t="inlineStr">
         <is>
-          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
+          <t>Status jadi Menunggu Verifikasi; aplikasi terbuka lagi</t>
         </is>
       </c>
       <c r="F263" s="16" t="inlineStr">
         <is>
-          <t>F-BL-14</t>
+          <t>F-BL-24, F-BL-12</t>
         </is>
       </c>
       <c r="G263" s="16" t="inlineStr"/>
@@ -10966,27 +10966,27 @@
       </c>
       <c r="B264" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-18</t>
-        </is>
-      </c>
-      <c r="C264" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-26</t>
+        </is>
+      </c>
+      <c r="C264" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D264" s="13" t="inlineStr">
         <is>
-          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
+          <t>Dengan kunci uji Xendit, buka tagihan ber-VA</t>
         </is>
       </c>
       <c r="E264" s="13" t="inlineStr">
         <is>
-          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
+          <t>Tombol Simulasikan Pembayaran muncul</t>
         </is>
       </c>
       <c r="F264" s="13" t="inlineStr">
         <is>
-          <t>F-BL-14, F-BL-15</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G264" s="13" t="inlineStr"/>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B265" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-19</t>
+          <t>TC-BL-27</t>
         </is>
       </c>
       <c r="C265" s="18" t="inlineStr">
@@ -11011,17 +11011,17 @@
       </c>
       <c r="D265" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Super Admin saat ada resto terkunci</t>
+          <t>Ketuk Simulasikan Pembayaran</t>
         </is>
       </c>
       <c r="E265" s="16" t="inlineStr">
         <is>
-          <t>Tidak terkunci sama sekali</t>
+          <t>Tagihan jadi Lunas sendiri lewat webhook; kunci resto terbuka</t>
         </is>
       </c>
       <c r="F265" s="16" t="inlineStr">
         <is>
-          <t>F-BL-17</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G265" s="16" t="inlineStr"/>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="B266" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-20</t>
+          <t>TC-BL-28</t>
         </is>
       </c>
       <c r="C266" s="15" t="inlineStr">
@@ -11046,17 +11046,17 @@
       </c>
       <c r="D266" s="13" t="inlineStr">
         <is>
-          <t>Sebagai resto terkunci, coba ubah harga produk</t>
+          <t>Pasang kunci produksi Xendit, buka layar yang sama</t>
         </is>
       </c>
       <c r="E266" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — katalog ikut dibekukan</t>
+          <t>Tombol simulasi hilang sendiri</t>
         </is>
       </c>
       <c r="F266" s="13" t="inlineStr">
         <is>
-          <t>F-BL-18</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G266" s="13" t="inlineStr"/>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="B267" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-21</t>
+          <t>TC-BL-29</t>
         </is>
       </c>
       <c r="C267" s="18" t="inlineStr">
@@ -11081,17 +11081,17 @@
       </c>
       <c r="D267" s="16" t="inlineStr">
         <is>
-          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
+          <t>Buat diskon langganan setelah tagihan terbit → ketuk segarkan di Super Admin</t>
         </is>
       </c>
       <c r="E267" s="16" t="inlineStr">
         <is>
-          <t>Resto B tidak terpengaruh</t>
+          <t>Nominal tagihan turun; nomor VA lama dibuang</t>
         </is>
       </c>
       <c r="F267" s="16" t="inlineStr">
         <is>
-          <t>F-BL-15, A-10</t>
+          <t>F-BL-05</t>
         </is>
       </c>
       <c r="G267" s="16" t="inlineStr"/>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="B268" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-22</t>
+          <t>TC-BL-30</t>
         </is>
       </c>
       <c r="C268" s="15" t="inlineStr">
@@ -11116,17 +11116,17 @@
       </c>
       <c r="D268" s="13" t="inlineStr">
         <is>
-          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
+          <t>Buat VA baru setelah nominalnya berubah</t>
         </is>
       </c>
       <c r="E268" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — hanya Super Admin</t>
+          <t>Nominalnya sesuai yang sudah dipotong</t>
         </is>
       </c>
       <c r="F268" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G268" s="13" t="inlineStr"/>
@@ -11141,7 +11141,7 @@
       </c>
       <c r="B269" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-23</t>
+          <t>TC-BL-15</t>
         </is>
       </c>
       <c r="C269" s="18" t="inlineStr">
@@ -11151,17 +11151,17 @@
       </c>
       <c r="D269" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
+          <t>Coba kirim bukti tanpa melampirkan foto</t>
         </is>
       </c>
       <c r="E269" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tombol Kirim mati</t>
         </is>
       </c>
       <c r="F269" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13, TSD §7.3</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G269" s="16" t="inlineStr"/>
@@ -11176,27 +11176,27 @@
       </c>
       <c r="B270" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-24</t>
-        </is>
-      </c>
-      <c r="C270" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-16</t>
+        </is>
+      </c>
+      <c r="C270" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
+          <t>Super Admin → tab Tagihan → Terima</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>Tidak terkunci karena gagal memeriksa</t>
+          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
         </is>
       </c>
       <c r="F270" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr"/>
@@ -11211,27 +11211,27 @@
       </c>
       <c r="B271" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-25</t>
-        </is>
-      </c>
-      <c r="C271" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-17</t>
+        </is>
+      </c>
+      <c r="C271" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D271" s="16" t="inlineStr">
         <is>
-          <t>Owner → Tagihan Langganan</t>
+          <t>Super Admin → Tolak tanpa mengisi alasan</t>
         </is>
       </c>
       <c r="E271" s="16" t="inlineStr">
         <is>
-          <t>Terbuka, memuat paket dan riwayat tagihan</t>
+          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
         </is>
       </c>
       <c r="F271" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-14</t>
         </is>
       </c>
       <c r="G271" s="16" t="inlineStr"/>
@@ -11241,12 +11241,12 @@
     <row r="272">
       <c r="A272" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B272" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-01</t>
+          <t>TC-BL-18</t>
         </is>
       </c>
       <c r="C272" s="15" t="inlineStr">
@@ -11256,17 +11256,17 @@
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Riwayat Langganan</t>
+          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
+          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
         </is>
       </c>
       <c r="F272" s="13" t="inlineStr">
         <is>
-          <t>F-PF-01</t>
+          <t>F-BL-14, F-BL-15</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr"/>
@@ -11276,32 +11276,32 @@
     <row r="273">
       <c r="A273" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B273" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-02</t>
-        </is>
-      </c>
-      <c r="C273" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-19</t>
+        </is>
+      </c>
+      <c r="C273" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>Periksa penanda jalur pelunasan tiap baris</t>
+          <t>Login sebagai Super Admin saat ada resto terkunci</t>
         </is>
       </c>
       <c r="E273" s="16" t="inlineStr">
         <is>
-          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
+          <t>Tidak terkunci sama sekali</t>
         </is>
       </c>
       <c r="F273" s="16" t="inlineStr">
         <is>
-          <t>F-PF-02</t>
+          <t>F-BL-17</t>
         </is>
       </c>
       <c r="G273" s="16" t="inlineStr"/>
@@ -11311,12 +11311,12 @@
     <row r="274">
       <c r="A274" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B274" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-03</t>
+          <t>TC-BL-20</t>
         </is>
       </c>
       <c r="C274" s="15" t="inlineStr">
@@ -11326,17 +11326,17 @@
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
+          <t>Sebagai resto terkunci, coba ubah harga produk</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
+          <t>Ditolak — katalog ikut dibekukan</t>
         </is>
       </c>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03, F-PF-05</t>
+          <t>F-BL-18</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr"/>
@@ -11346,12 +11346,12 @@
     <row r="275">
       <c r="A275" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B275" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-04</t>
+          <t>TC-BL-21</t>
         </is>
       </c>
       <c r="C275" s="18" t="inlineStr">
@@ -11361,17 +11361,17 @@
       </c>
       <c r="D275" s="16" t="inlineStr">
         <is>
-          <t>Simpan diskon tanpa memilih resto</t>
+          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
         </is>
       </c>
       <c r="E275" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
+          <t>Resto B tidak terpengaruh</t>
         </is>
       </c>
       <c r="F275" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-BL-15, A-10</t>
         </is>
       </c>
       <c r="G275" s="16" t="inlineStr"/>
@@ -11381,32 +11381,32 @@
     <row r="276">
       <c r="A276" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B276" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-05</t>
-        </is>
-      </c>
-      <c r="C276" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-22</t>
+        </is>
+      </c>
+      <c r="C276" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
+          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr"/>
@@ -11416,32 +11416,32 @@
     <row r="277">
       <c r="A277" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B277" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-06</t>
-        </is>
-      </c>
-      <c r="C277" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-23</t>
+        </is>
+      </c>
+      <c r="C277" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D277" s="16" t="inlineStr">
         <is>
-          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
+          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
         </is>
       </c>
       <c r="E277" s="16" t="inlineStr">
         <is>
-          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F277" s="16" t="inlineStr">
         <is>
-          <t>F-PF-04</t>
+          <t>F-BL-13, TSD §7.3</t>
         </is>
       </c>
       <c r="G277" s="16" t="inlineStr"/>
@@ -11451,32 +11451,32 @@
     <row r="278">
       <c r="A278" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B278" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-07</t>
-        </is>
-      </c>
-      <c r="C278" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-24</t>
+        </is>
+      </c>
+      <c r="C278" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>Hapus diskon setelah tagihan terbit</t>
+          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
+          <t>Tidak terkunci karena gagal memeriksa</t>
         </is>
       </c>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>F-PF-05</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr"/>
@@ -11486,32 +11486,32 @@
     <row r="279">
       <c r="A279" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B279" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-08</t>
-        </is>
-      </c>
-      <c r="C279" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-25</t>
+        </is>
+      </c>
+      <c r="C279" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
+          <t>Owner → Tagihan Langganan</t>
         </is>
       </c>
       <c r="E279" s="16" t="inlineStr">
         <is>
-          <t>Dua baris: pendapatan kredit, diskon debit</t>
+          <t>Terbuka, memuat paket dan riwayat tagihan</t>
         </is>
       </c>
       <c r="F279" s="16" t="inlineStr">
         <is>
-          <t>F-PF-06, F-PF-07</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G279" s="16" t="inlineStr"/>
@@ -11526,7 +11526,7 @@
       </c>
       <c r="B280" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-09</t>
+          <t>TC-PF-01</t>
         </is>
       </c>
       <c r="C280" s="15" t="inlineStr">
@@ -11536,17 +11536,17 @@
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>Tagihan ditolak lalu diterima lagi</t>
+          <t>Super Admin → Finance → Riwayat Langganan</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
+          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
         </is>
       </c>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-01</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr"/>
@@ -11561,27 +11561,27 @@
       </c>
       <c r="B281" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-10</t>
-        </is>
-      </c>
-      <c r="C281" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-02</t>
+        </is>
+      </c>
+      <c r="C281" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D281" s="16" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL resto yang membayar</t>
+          <t>Periksa penanda jalur pelunasan tiap baris</t>
         </is>
       </c>
       <c r="E281" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada baris pendapatan langganan di sana</t>
+          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
         </is>
       </c>
       <c r="F281" s="16" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-02</t>
         </is>
       </c>
       <c r="G281" s="16" t="inlineStr"/>
@@ -11596,27 +11596,27 @@
       </c>
       <c r="B282" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-11</t>
-        </is>
-      </c>
-      <c r="C282" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-03</t>
+        </is>
+      </c>
+      <c r="C282" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account KaataGo</t>
+          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
+          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
         </is>
       </c>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>F-PF-08</t>
+          <t>F-PF-03, F-PF-05</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr"/>
@@ -11631,27 +11631,27 @@
       </c>
       <c r="B283" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-12</t>
-        </is>
-      </c>
-      <c r="C283" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-04</t>
+        </is>
+      </c>
+      <c r="C283" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D283" s="16" t="inlineStr">
         <is>
-          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
+          <t>Simpan diskon tanpa memilih resto</t>
         </is>
       </c>
       <c r="E283" s="16" t="inlineStr">
         <is>
-          <t>Bekerja sama seperti di resto</t>
+          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
         </is>
       </c>
       <c r="F283" s="16" t="inlineStr">
         <is>
-          <t>F-PF-09</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G283" s="16" t="inlineStr"/>
@@ -11666,27 +11666,27 @@
       </c>
       <c r="B284" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-13</t>
-        </is>
-      </c>
-      <c r="C284" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-05</t>
+        </is>
+      </c>
+      <c r="C284" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>Telusuri menu Finance KaataGo</t>
+          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada Setor Saldo Cash</t>
+          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
         </is>
       </c>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>F-PF-10</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr"/>
@@ -11701,27 +11701,27 @@
       </c>
       <c r="B285" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-14</t>
-        </is>
-      </c>
-      <c r="C285" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-06</t>
+        </is>
+      </c>
+      <c r="C285" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D285" s="16" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL Semua Resto</t>
+          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
         </is>
       </c>
       <c r="E285" s="16" t="inlineStr">
         <is>
-          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
+          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
         </is>
       </c>
       <c r="F285" s="16" t="inlineStr">
         <is>
-          <t>F-PF-11</t>
+          <t>F-PF-04</t>
         </is>
       </c>
       <c r="G285" s="16" t="inlineStr"/>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-15</t>
+          <t>TC-PF-07</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
@@ -11746,17 +11746,17 @@
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
+          <t>Hapus diskon setelah tagihan terbit</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun — hanya bisa dilihat</t>
+          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
         </is>
       </c>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>F-PF-12</t>
+          <t>F-PF-05</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr"/>
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B287" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-16</t>
+          <t>TC-PF-08</t>
         </is>
       </c>
       <c r="C287" s="18" t="inlineStr">
@@ -11781,17 +11781,17 @@
       </c>
       <c r="D287" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
+          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E287" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Dua baris: pendapatan kredit, diskon debit</t>
         </is>
       </c>
       <c r="F287" s="16" t="inlineStr">
         <is>
-          <t>F-PF-12, TSD §7.4</t>
+          <t>F-PF-06, F-PF-07</t>
         </is>
       </c>
       <c r="G287" s="16" t="inlineStr"/>
@@ -11806,7 +11806,7 @@
       </c>
       <c r="B288" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-17</t>
+          <t>TC-PF-09</t>
         </is>
       </c>
       <c r="C288" s="15" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>Buka Pilih Resto sebagai pelanggan</t>
+          <t>Tagihan ditolak lalu diterima lagi</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul di daftar mana pun</t>
+          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
         </is>
       </c>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr"/>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="B289" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-18</t>
+          <t>TC-PF-10</t>
         </is>
       </c>
       <c r="C289" s="18" t="inlineStr">
@@ -11851,17 +11851,17 @@
       </c>
       <c r="D289" s="16" t="inlineStr">
         <is>
-          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
+          <t>Buka Jurnal GL resto yang membayar</t>
         </is>
       </c>
       <c r="E289" s="16" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
+          <t>Tidak ada baris pendapatan langganan di sana</t>
         </is>
       </c>
       <c r="F289" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G289" s="16" t="inlineStr"/>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="B290" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-19</t>
+          <t>TC-PF-11</t>
         </is>
       </c>
       <c r="C290" s="19" t="inlineStr">
@@ -11886,17 +11886,17 @@
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>Buka Diskon Langganan sebagai Owner resto</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
+          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr"/>
@@ -11911,27 +11911,27 @@
       </c>
       <c r="B291" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-20</t>
-        </is>
-      </c>
-      <c r="C291" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-12</t>
+        </is>
+      </c>
+      <c r="C291" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D291" s="16" t="inlineStr">
         <is>
-          <t>Bandingkan total debit/kredit Jurnal Semua Resto dengan Jurnal GL resto itu (saring ke resto yang sama)</t>
+          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
         </is>
       </c>
       <c r="E291" s="16" t="inlineStr">
         <is>
-          <t>Angkanya sama persis</t>
+          <t>Bekerja sama seperti di resto</t>
         </is>
       </c>
       <c r="F291" s="16" t="inlineStr">
         <is>
-          <t>F-PF-14</t>
+          <t>F-PF-09</t>
         </is>
       </c>
       <c r="G291" s="16" t="inlineStr"/>
@@ -11946,7 +11946,7 @@
       </c>
       <c r="B292" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-21</t>
+          <t>TC-PF-13</t>
         </is>
       </c>
       <c r="C292" s="15" t="inlineStr">
@@ -11956,17 +11956,17 @@
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
-          <t>Batalkan sebuah pengeluaran, lihat kedua layar jurnal</t>
+          <t>Telusuri menu Finance KaataGo</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Total tidak naik; keterangan "N pembatalan tidak dihitung" muncul</t>
+          <t>Tidak ada Setor Saldo Cash</t>
         </is>
       </c>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>F-PF-14</t>
+          <t>F-PF-10</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr"/>
@@ -11981,27 +11981,27 @@
       </c>
       <c r="B293" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-22</t>
-        </is>
-      </c>
-      <c r="C293" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-14</t>
+        </is>
+      </c>
+      <c r="C293" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D293" s="16" t="inlineStr">
         <is>
-          <t>Cari baris pembatalan di daftar</t>
+          <t>Buka Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E293" s="16" t="inlineStr">
         <is>
-          <t>Tetap tampil, bertanda PEMBATALAN</t>
+          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
         </is>
       </c>
       <c r="F293" s="16" t="inlineStr">
         <is>
-          <t>F-PF-15</t>
+          <t>F-PF-11</t>
         </is>
       </c>
       <c r="G293" s="16" t="inlineStr"/>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="B294" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-23</t>
+          <t>TC-PF-15</t>
         </is>
       </c>
       <c r="C294" s="15" t="inlineStr">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>Saring ke sebuah resto, lalu pilih Semua resto lagi</t>
+          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Kembali menampilkan seluruh resto — bukan tetap tersaring</t>
+          <t>Tidak ada satu pun — hanya bisa dilihat</t>
         </is>
       </c>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>F-PF-12</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr"/>
@@ -12051,7 +12051,7 @@
       </c>
       <c r="B295" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-24</t>
+          <t>TC-PF-16</t>
         </is>
       </c>
       <c r="C295" s="18" t="inlineStr">
@@ -12061,17 +12061,17 @@
       </c>
       <c r="D295" s="16" t="inlineStr">
         <is>
-          <t>Saring ke resto A, lalu saring lagi ke resto B yang punya jurnal</t>
+          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
         </is>
       </c>
       <c r="E295" s="16" t="inlineStr">
         <is>
-          <t>Isinya berganti ke jurnal resto B</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F295" s="16" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>F-PF-12, TSD §7.4</t>
         </is>
       </c>
       <c r="G295" s="16" t="inlineStr"/>
@@ -12086,27 +12086,27 @@
       </c>
       <c r="B296" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-25</t>
-        </is>
-      </c>
-      <c r="C296" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-17</t>
+        </is>
+      </c>
+      <c r="C296" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>Perhatikan pita di atas layar sesudah menyaring</t>
+          <t>Buka Pilih Resto sebagai pelanggan</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>Nama restonya tertulis, dengan tombol × untuk melepasnya</t>
+          <t>KaataGo tidak muncul di daftar mana pun</t>
         </is>
       </c>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr"/>
@@ -12121,27 +12121,27 @@
       </c>
       <c r="B297" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-26</t>
-        </is>
-      </c>
-      <c r="C297" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-18</t>
+        </is>
+      </c>
+      <c r="C297" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D297" s="16" t="inlineStr">
         <is>
-          <t>Buka daftar saringan</t>
+          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
         </is>
       </c>
       <c r="E297" s="16" t="inlineStr">
         <is>
-          <t>Resto yang belum punya jurnal ditandai "Belum ada jurnal"</t>
+          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
         </is>
       </c>
       <c r="F297" s="16" t="inlineStr">
         <is>
-          <t>F-PF-17</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G297" s="16" t="inlineStr"/>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="B298" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-27</t>
+          <t>TC-PF-19</t>
         </is>
       </c>
       <c r="C298" s="19" t="inlineStr">
@@ -12166,17 +12166,17 @@
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>Perhatikan pengelompokan</t>
+          <t>Buka Diskon Langganan sebagai Owner resto</t>
         </is>
       </c>
       <c r="E298" s="13" t="inlineStr">
         <is>
-          <t>Per tanggal, bisa dilipat; tanggal terbaru terbuka, sisanya tertutup</t>
+          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
         </is>
       </c>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>F-PF-18</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr"/>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="B299" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-28</t>
+          <t>TC-PF-20</t>
         </is>
       </c>
       <c r="C299" s="18" t="inlineStr">
@@ -12201,17 +12201,17 @@
       </c>
       <c r="D299" s="16" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account resto mana pun</t>
+          <t>Bandingkan total debit/kredit Jurnal Semua Resto dengan Jurnal GL resto itu (saring ke resto yang sama)</t>
         </is>
       </c>
       <c r="E299" s="16" t="inlineStr">
         <is>
-          <t>GL Diskon punya bagiannya dan nomornya sudah terisi</t>
+          <t>Angkanya sama persis</t>
         </is>
       </c>
       <c r="F299" s="16" t="inlineStr">
         <is>
-          <t>F-PF-19, F-DS-09</t>
+          <t>F-PF-14</t>
         </is>
       </c>
       <c r="G299" s="16" t="inlineStr"/>
@@ -12226,27 +12226,27 @@
       </c>
       <c r="B300" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-29</t>
-        </is>
-      </c>
-      <c r="C300" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-21</t>
+        </is>
+      </c>
+      <c r="C300" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account KaataGo</t>
+          <t>Batalkan sebuah pengeluaran, lihat kedua layar jurnal</t>
         </is>
       </c>
       <c r="E300" s="13" t="inlineStr">
         <is>
-          <t>Ada bagian GL Langganan; penghitung akun tidak pernah menyisakan yang mustahil terisi</t>
+          <t>Total tidak naik; keterangan "N pembatalan tidak dihitung" muncul</t>
         </is>
       </c>
       <c r="F300" s="13" t="inlineStr">
         <is>
-          <t>F-PF-19</t>
+          <t>F-PF-14</t>
         </is>
       </c>
       <c r="G300" s="13" t="inlineStr"/>
@@ -12261,27 +12261,27 @@
       </c>
       <c r="B301" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-30</t>
-        </is>
-      </c>
-      <c r="C301" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-22</t>
+        </is>
+      </c>
+      <c r="C301" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D301" s="16" t="inlineStr">
         <is>
-          <t>Pesan menu berpromo, bayar, buka Jurnal GL</t>
+          <t>Cari baris pembatalan di daftar</t>
         </is>
       </c>
       <c r="E301" s="16" t="inlineStr">
         <is>
-          <t>Baris GL Diskon menyebut nama promonya</t>
+          <t>Tetap tampil, bertanda PEMBATALAN</t>
         </is>
       </c>
       <c r="F301" s="16" t="inlineStr">
         <is>
-          <t>F-PF-20, F-DS-13</t>
+          <t>F-PF-15</t>
         </is>
       </c>
       <c r="G301" s="16" t="inlineStr"/>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B302" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-31</t>
+          <t>TC-PF-23</t>
         </is>
       </c>
       <c r="C302" s="15" t="inlineStr">
@@ -12306,17 +12306,17 @@
       </c>
       <c r="D302" s="13" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL Semua Resto sesudah ada tagihan langganan lunas</t>
+          <t>Saring ke sebuah resto, lalu pilih Semua resto lagi</t>
         </is>
       </c>
       <c r="E302" s="13" t="inlineStr">
         <is>
-          <t>Baris pendapatan langganan tidak muncul di sana</t>
+          <t>Kembali menampilkan seluruh resto — bukan tetap tersaring</t>
         </is>
       </c>
       <c r="F302" s="13" t="inlineStr">
         <is>
-          <t>F-PF-21</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr"/>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="B303" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-32</t>
+          <t>TC-PF-24</t>
         </is>
       </c>
       <c r="C303" s="18" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="D303" s="16" t="inlineStr">
         <is>
-          <t>Buka daftar saringan resto</t>
+          <t>Saring ke resto A, lalu saring lagi ke resto B yang punya jurnal</t>
         </is>
       </c>
       <c r="E303" s="16" t="inlineStr">
         <is>
-          <t>KaataGo tidak ada di daftarnya</t>
+          <t>Isinya berganti ke jurnal resto B</t>
         </is>
       </c>
       <c r="F303" s="16" t="inlineStr">
         <is>
-          <t>F-PF-21</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G303" s="16" t="inlineStr"/>
@@ -12366,27 +12366,27 @@
       </c>
       <c r="B304" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-33</t>
-        </is>
-      </c>
-      <c r="C304" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-25</t>
+        </is>
+      </c>
+      <c r="C304" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL KaataGo</t>
+          <t>Perhatikan pita di atas layar sesudah menyaring</t>
         </is>
       </c>
       <c r="E304" s="13" t="inlineStr">
         <is>
-          <t>Pendapatan langganan ada di sana, dan Saldo Total tidak nol</t>
+          <t>Nama restonya tertulis, dengan tombol × untuk melepasnya</t>
         </is>
       </c>
       <c r="F304" s="13" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr"/>
@@ -12401,7 +12401,7 @@
       </c>
       <c r="B305" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-34</t>
+          <t>TC-PF-26</t>
         </is>
       </c>
       <c r="C305" s="20" t="inlineStr">
@@ -12411,17 +12411,17 @@
       </c>
       <c r="D305" s="16" t="inlineStr">
         <is>
-          <t>Periksa nomor akun di Jurnal GL KaataGo</t>
+          <t>Buka daftar saringan</t>
         </is>
       </c>
       <c r="E305" s="16" t="inlineStr">
         <is>
-          <t>Golongan 11xxxxx, berbeda dari 19xxxxx milik resto</t>
+          <t>Resto yang belum punya jurnal ditandai "Belum ada jurnal"</t>
         </is>
       </c>
       <c r="F305" s="16" t="inlineStr">
         <is>
-          <t>F-PF-08</t>
+          <t>F-PF-17</t>
         </is>
       </c>
       <c r="G305" s="16" t="inlineStr"/>
@@ -12431,32 +12431,32 @@
     <row r="306">
       <c r="A306" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B306" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
-        </is>
-      </c>
-      <c r="C306" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-27</t>
+        </is>
+      </c>
+      <c r="C306" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Perhatikan pengelompokan</t>
         </is>
       </c>
       <c r="E306" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Per tanggal, bisa dilipat; tanggal terbaru terbuka, sisanya tertutup</t>
         </is>
       </c>
       <c r="F306" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-18</t>
         </is>
       </c>
       <c r="G306" s="13" t="inlineStr"/>
@@ -12466,12 +12466,12 @@
     <row r="307">
       <c r="A307" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B307" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-PF-28</t>
         </is>
       </c>
       <c r="C307" s="18" t="inlineStr">
@@ -12481,17 +12481,17 @@
       </c>
       <c r="D307" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Buka Mapping GL Account resto mana pun</t>
         </is>
       </c>
       <c r="E307" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>GL Diskon punya bagiannya dan nomornya sudah terisi</t>
         </is>
       </c>
       <c r="F307" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-19, F-DS-09</t>
         </is>
       </c>
       <c r="G307" s="16" t="inlineStr"/>
@@ -12501,32 +12501,32 @@
     <row r="308">
       <c r="A308" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B308" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
-        </is>
-      </c>
-      <c r="C308" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-29</t>
+        </is>
+      </c>
+      <c r="C308" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E308" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Ada bagian GL Langganan; penghitung akun tidak pernah menyisakan yang mustahil terisi</t>
         </is>
       </c>
       <c r="F308" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-PF-19</t>
         </is>
       </c>
       <c r="G308" s="13" t="inlineStr"/>
@@ -12536,12 +12536,12 @@
     <row r="309">
       <c r="A309" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B309" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
+          <t>TC-PF-30</t>
         </is>
       </c>
       <c r="C309" s="18" t="inlineStr">
@@ -12551,17 +12551,17 @@
       </c>
       <c r="D309" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Pesan menu berpromo, bayar, buka Jurnal GL</t>
         </is>
       </c>
       <c r="E309" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Baris GL Diskon menyebut nama promonya</t>
         </is>
       </c>
       <c r="F309" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-PF-20, F-DS-13</t>
         </is>
       </c>
       <c r="G309" s="16" t="inlineStr"/>
@@ -12571,12 +12571,12 @@
     <row r="310">
       <c r="A310" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B310" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-PF-31</t>
         </is>
       </c>
       <c r="C310" s="15" t="inlineStr">
@@ -12586,17 +12586,17 @@
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Buka Jurnal GL Semua Resto sesudah ada tagihan langganan lunas</t>
         </is>
       </c>
       <c r="E310" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Baris pendapatan langganan tidak muncul di sana</t>
         </is>
       </c>
       <c r="F310" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-PF-21</t>
         </is>
       </c>
       <c r="G310" s="13" t="inlineStr"/>
@@ -12606,12 +12606,12 @@
     <row r="311">
       <c r="A311" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B311" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-PF-32</t>
         </is>
       </c>
       <c r="C311" s="18" t="inlineStr">
@@ -12621,17 +12621,17 @@
       </c>
       <c r="D311" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Buka daftar saringan resto</t>
         </is>
       </c>
       <c r="E311" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>KaataGo tidak ada di daftarnya</t>
         </is>
       </c>
       <c r="F311" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-PF-21</t>
         </is>
       </c>
       <c r="G311" s="16" t="inlineStr"/>
@@ -12641,12 +12641,12 @@
     <row r="312">
       <c r="A312" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B312" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-PF-33</t>
         </is>
       </c>
       <c r="C312" s="15" t="inlineStr">
@@ -12656,17 +12656,17 @@
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E312" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Pendapatan langganan ada di sana, dan Saldo Total tidak nol</t>
         </is>
       </c>
       <c r="F312" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G312" s="13" t="inlineStr"/>
@@ -12676,32 +12676,32 @@
     <row r="313">
       <c r="A313" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B313" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
-        </is>
-      </c>
-      <c r="C313" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-34</t>
+        </is>
+      </c>
+      <c r="C313" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D313" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Periksa nomor akun di Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E313" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Golongan 11xxxxx, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F313" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G313" s="16" t="inlineStr"/>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="B314" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-TS-01</t>
         </is>
       </c>
       <c r="C314" s="15" t="inlineStr">
@@ -12726,17 +12726,17 @@
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E314" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr"/>
@@ -12751,7 +12751,7 @@
       </c>
       <c r="B315" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-TS-02</t>
         </is>
       </c>
       <c r="C315" s="18" t="inlineStr">
@@ -12761,17 +12761,17 @@
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E315" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F315" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G315" s="16" t="inlineStr"/>
@@ -12786,27 +12786,27 @@
       </c>
       <c r="B316" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
-        </is>
-      </c>
-      <c r="C316" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-03</t>
+        </is>
+      </c>
+      <c r="C316" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E316" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F316" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G316" s="13" t="inlineStr"/>
@@ -12821,27 +12821,27 @@
       </c>
       <c r="B317" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C317" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-04</t>
+        </is>
+      </c>
+      <c r="C317" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D317" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E317" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F317" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G317" s="16" t="inlineStr"/>
@@ -12856,27 +12856,27 @@
       </c>
       <c r="B318" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C318" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-05</t>
+        </is>
+      </c>
+      <c r="C318" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E318" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G318" s="13" t="inlineStr"/>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B319" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C319" s="18" t="inlineStr">
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D319" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E319" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F319" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G319" s="16" t="inlineStr"/>
@@ -12926,7 +12926,7 @@
       </c>
       <c r="B320" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
+          <t>TC-TS-07</t>
         </is>
       </c>
       <c r="C320" s="15" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E320" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F320" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G320" s="13" t="inlineStr"/>
@@ -12961,7 +12961,7 @@
       </c>
       <c r="B321" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-TS-08</t>
         </is>
       </c>
       <c r="C321" s="18" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="D321" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E321" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F321" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G321" s="16" t="inlineStr"/>
@@ -12996,27 +12996,27 @@
       </c>
       <c r="B322" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C322" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C322" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E322" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F322" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G322" s="13" t="inlineStr"/>
@@ -13031,27 +13031,27 @@
       </c>
       <c r="B323" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C323" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C323" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D323" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E323" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F323" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G323" s="16" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="B324" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
+          <t>TC-TS-11</t>
         </is>
       </c>
       <c r="C324" s="19" t="inlineStr">
@@ -13076,17 +13076,17 @@
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E324" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F324" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G324" s="13" t="inlineStr"/>
@@ -13096,32 +13096,32 @@
     <row r="325">
       <c r="A325" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B325" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
-        </is>
-      </c>
-      <c r="C325" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C325" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D325" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E325" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F325" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G325" s="16" t="inlineStr"/>
@@ -13131,32 +13131,32 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B326" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
-        </is>
-      </c>
-      <c r="C326" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-13</t>
+        </is>
+      </c>
+      <c r="C326" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E326" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F326" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G326" s="13" t="inlineStr"/>
@@ -13166,12 +13166,12 @@
     <row r="327">
       <c r="A327" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B327" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
+          <t>TC-TS-14</t>
         </is>
       </c>
       <c r="C327" s="18" t="inlineStr">
@@ -13181,17 +13181,17 @@
       </c>
       <c r="D327" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E327" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F327" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G327" s="16" t="inlineStr"/>
@@ -13201,12 +13201,12 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B328" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
+          <t>TC-TS-15</t>
         </is>
       </c>
       <c r="C328" s="15" t="inlineStr">
@@ -13216,17 +13216,17 @@
       </c>
       <c r="D328" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E328" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F328" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G328" s="13" t="inlineStr"/>
@@ -13236,12 +13236,12 @@
     <row r="329">
       <c r="A329" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B329" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-TS-16</t>
         </is>
       </c>
       <c r="C329" s="18" t="inlineStr">
@@ -13251,17 +13251,17 @@
       </c>
       <c r="D329" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
         </is>
       </c>
       <c r="E329" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F329" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>F-PG-02, TSD §7.1</t>
         </is>
       </c>
       <c r="G329" s="16" t="inlineStr"/>
@@ -13271,32 +13271,32 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B330" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
-        </is>
-      </c>
-      <c r="C330" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C330" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
         </is>
       </c>
       <c r="E330" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
         </is>
       </c>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>TSD §1.2</t>
         </is>
       </c>
       <c r="G330" s="13" t="inlineStr"/>
@@ -13306,12 +13306,12 @@
     <row r="331">
       <c r="A331" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B331" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
+          <t>TC-TS-18</t>
         </is>
       </c>
       <c r="C331" s="20" t="inlineStr">
@@ -13321,17 +13321,17 @@
       </c>
       <c r="D331" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
         </is>
       </c>
       <c r="E331" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
         </is>
       </c>
       <c r="F331" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>TSD §6.5</t>
         </is>
       </c>
       <c r="G331" s="16" t="inlineStr"/>
@@ -13341,12 +13341,12 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B332" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
+          <t>TC-TS-19</t>
         </is>
       </c>
       <c r="C332" s="19" t="inlineStr">
@@ -13356,17 +13356,17 @@
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Hapus resto uji</t>
         </is>
       </c>
       <c r="E332" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
         </is>
       </c>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>TSD §4.0</t>
         </is>
       </c>
       <c r="G332" s="13" t="inlineStr"/>
@@ -13381,27 +13381,27 @@
       </c>
       <c r="B333" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
-        </is>
-      </c>
-      <c r="C333" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C333" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D333" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
         </is>
       </c>
       <c r="E333" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
         </is>
       </c>
       <c r="F333" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>F-KS-09</t>
         </is>
       </c>
       <c r="G333" s="16" t="inlineStr"/>
@@ -13416,27 +13416,27 @@
       </c>
       <c r="B334" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
-        </is>
-      </c>
-      <c r="C334" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C334" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
         </is>
       </c>
       <c r="E334" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
         </is>
       </c>
       <c r="F334" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-PP-09, A-13</t>
         </is>
       </c>
       <c r="G334" s="13" t="inlineStr"/>
@@ -13451,27 +13451,27 @@
       </c>
       <c r="B335" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
-        </is>
-      </c>
-      <c r="C335" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C335" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D335" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
         </is>
       </c>
       <c r="E335" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Tidak muncul sama sekali</t>
         </is>
       </c>
       <c r="F335" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="G335" s="16" t="inlineStr"/>
@@ -13486,27 +13486,27 @@
       </c>
       <c r="B336" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
-        </is>
-      </c>
-      <c r="C336" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C336" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
         </is>
       </c>
       <c r="E336" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Nominalnya sama dengan yang diajukan</t>
         </is>
       </c>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>F-FN-03</t>
         </is>
       </c>
       <c r="G336" s="13" t="inlineStr"/>
@@ -13521,7 +13521,7 @@
       </c>
       <c r="B337" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
+          <t>TC-RG-05</t>
         </is>
       </c>
       <c r="C337" s="18" t="inlineStr">
@@ -13531,17 +13531,17 @@
       </c>
       <c r="D337" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
         </is>
       </c>
       <c r="E337" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
         </is>
       </c>
       <c r="F337" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="G337" s="16" t="inlineStr"/>
@@ -13556,27 +13556,27 @@
       </c>
       <c r="B338" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
-        </is>
-      </c>
-      <c r="C338" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C338" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D338" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
         </is>
       </c>
       <c r="E338" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
         </is>
       </c>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>F-DS-10, F-DS-12</t>
         </is>
       </c>
       <c r="G338" s="13" t="inlineStr"/>
@@ -13586,25 +13586,305 @@
     <row r="339">
       <c r="A339" s="16" t="inlineStr">
         <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B339" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C339" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D339" s="16" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E339" s="16" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F339" s="16" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G339" s="16" t="inlineStr"/>
+      <c r="H339" s="16" t="inlineStr"/>
+      <c r="I339" s="16" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B340" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C340" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D340" s="13" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E340" s="13" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F340" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G340" s="13" t="inlineStr"/>
+      <c r="H340" s="13" t="inlineStr"/>
+      <c r="I340" s="13" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B341" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C341" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D341" s="16" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E341" s="16" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F341" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G341" s="16" t="inlineStr"/>
+      <c r="H341" s="16" t="inlineStr"/>
+      <c r="I341" s="16" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B342" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C342" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D342" s="13" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E342" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F342" s="13" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G342" s="13" t="inlineStr"/>
+      <c r="H342" s="13" t="inlineStr"/>
+      <c r="I342" s="13" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B343" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C343" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D343" s="16" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E343" s="16" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F343" s="16" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G343" s="16" t="inlineStr"/>
+      <c r="H343" s="16" t="inlineStr"/>
+      <c r="I343" s="16" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B344" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C344" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D344" s="13" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E344" s="13" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F344" s="13" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G344" s="13" t="inlineStr"/>
+      <c r="H344" s="13" t="inlineStr"/>
+      <c r="I344" s="13" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B345" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C345" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D345" s="16" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E345" s="16" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F345" s="16" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G345" s="16" t="inlineStr"/>
+      <c r="H345" s="16" t="inlineStr"/>
+      <c r="I345" s="16" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B346" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C346" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D346" s="13" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E346" s="13" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F346" s="13" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G346" s="13" t="inlineStr"/>
+      <c r="H346" s="13" t="inlineStr"/>
+      <c r="I346" s="13" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="16" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B339" s="17" t="inlineStr">
+      <c r="B347" s="17" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C339" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D339" s="16" t="inlineStr">
+      <c r="C347" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D347" s="16" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E339" s="16" t="inlineStr">
+      <c r="E347" s="16" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -13618,37 +13898,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F339" s="16" t="inlineStr">
+      <c r="F347" s="16" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G339" s="16" t="inlineStr"/>
-      <c r="H339" s="16" t="inlineStr"/>
-      <c r="I339" s="16" t="inlineStr"/>
-    </row>
-    <row r="340">
-      <c r="A340" s="13" t="inlineStr">
+      <c r="G347" s="16" t="inlineStr"/>
+      <c r="H347" s="16" t="inlineStr"/>
+      <c r="I347" s="16" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B340" s="14" t="inlineStr">
+      <c r="B348" s="14" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C340" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D340" s="13" t="inlineStr">
+      <c r="C348" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D348" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E340" s="13" t="inlineStr">
+      <c r="E348" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -13660,37 +13940,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F340" s="13" t="inlineStr">
+      <c r="F348" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G340" s="13" t="inlineStr"/>
-      <c r="H340" s="13" t="inlineStr"/>
-      <c r="I340" s="13" t="inlineStr"/>
-    </row>
-    <row r="341">
-      <c r="A341" s="16" t="inlineStr">
+      <c r="G348" s="13" t="inlineStr"/>
+      <c r="H348" s="13" t="inlineStr"/>
+      <c r="I348" s="13" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B341" s="17" t="inlineStr">
+      <c r="B349" s="17" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C341" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D341" s="16" t="inlineStr">
+      <c r="C349" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D349" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E341" s="16" t="inlineStr">
+      <c r="E349" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -13702,74 +13982,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F341" s="16" t="inlineStr">
+      <c r="F349" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G341" s="16" t="inlineStr"/>
-      <c r="H341" s="16" t="inlineStr"/>
-      <c r="I341" s="16" t="inlineStr"/>
-    </row>
-    <row r="342">
-      <c r="A342" s="13" t="inlineStr">
+      <c r="G349" s="16" t="inlineStr"/>
+      <c r="H349" s="16" t="inlineStr"/>
+      <c r="I349" s="16" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B342" s="14" t="inlineStr">
+      <c r="B350" s="14" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C342" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D342" s="13" t="inlineStr">
+      <c r="C350" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D350" s="13" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E342" s="13" t="inlineStr">
+      <c r="E350" s="13" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F342" s="13" t="inlineStr">
+      <c r="F350" s="13" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G342" s="13" t="inlineStr"/>
-      <c r="H342" s="13" t="inlineStr"/>
-      <c r="I342" s="13" t="inlineStr"/>
-    </row>
-    <row r="343">
-      <c r="A343" s="16" t="inlineStr">
+      <c r="G350" s="13" t="inlineStr"/>
+      <c r="H350" s="13" t="inlineStr"/>
+      <c r="I350" s="13" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B343" s="17" t="inlineStr">
+      <c r="B351" s="17" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C343" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D343" s="16" t="inlineStr">
+      <c r="C351" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D351" s="16" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E343" s="16" t="inlineStr">
+      <c r="E351" s="16" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -13780,73 +14060,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F343" s="16" t="inlineStr">
+      <c r="F351" s="16" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G343" s="16" t="inlineStr"/>
-      <c r="H343" s="16" t="inlineStr"/>
-      <c r="I343" s="16" t="inlineStr"/>
-    </row>
-    <row r="344">
-      <c r="A344" s="13" t="inlineStr">
+      <c r="G351" s="16" t="inlineStr"/>
+      <c r="H351" s="16" t="inlineStr"/>
+      <c r="I351" s="16" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B344" s="14" t="inlineStr">
+      <c r="B352" s="14" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C344" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D344" s="13" t="inlineStr">
+      <c r="C352" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D352" s="13" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E344" s="13" t="inlineStr">
+      <c r="E352" s="13" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F344" s="13" t="inlineStr">
+      <c r="F352" s="13" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G344" s="13" t="inlineStr"/>
-      <c r="H344" s="13" t="inlineStr"/>
-      <c r="I344" s="13" t="inlineStr"/>
-    </row>
-    <row r="345">
-      <c r="A345" s="16" t="inlineStr">
+      <c r="G352" s="13" t="inlineStr"/>
+      <c r="H352" s="13" t="inlineStr"/>
+      <c r="I352" s="13" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B345" s="17" t="inlineStr">
+      <c r="B353" s="17" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C345" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D345" s="16" t="inlineStr">
+      <c r="C353" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D353" s="16" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E345" s="16" t="inlineStr">
+      <c r="E353" s="16" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -13857,37 +14137,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F345" s="16" t="inlineStr">
+      <c r="F353" s="16" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G345" s="16" t="inlineStr"/>
-      <c r="H345" s="16" t="inlineStr"/>
-      <c r="I345" s="16" t="inlineStr"/>
-    </row>
-    <row r="346">
-      <c r="A346" s="13" t="inlineStr">
+      <c r="G353" s="16" t="inlineStr"/>
+      <c r="H353" s="16" t="inlineStr"/>
+      <c r="I353" s="16" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B346" s="14" t="inlineStr">
+      <c r="B354" s="14" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C346" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D346" s="13" t="inlineStr">
+      <c r="C354" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D354" s="13" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E346" s="13" t="inlineStr">
+      <c r="E354" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -13897,37 +14177,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F346" s="13" t="inlineStr">
+      <c r="F354" s="13" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G346" s="13" t="inlineStr"/>
-      <c r="H346" s="13" t="inlineStr"/>
-      <c r="I346" s="13" t="inlineStr"/>
-    </row>
-    <row r="347">
-      <c r="A347" s="16" t="inlineStr">
+      <c r="G354" s="13" t="inlineStr"/>
+      <c r="H354" s="13" t="inlineStr"/>
+      <c r="I354" s="13" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B347" s="17" t="inlineStr">
+      <c r="B355" s="17" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C347" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D347" s="16" t="inlineStr">
+      <c r="C355" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D355" s="16" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E347" s="16" t="inlineStr">
+      <c r="E355" s="16" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -13935,19 +14215,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F347" s="16" t="inlineStr">
+      <c r="F355" s="16" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G347" s="16" t="inlineStr"/>
-      <c r="H347" s="16" t="inlineStr"/>
-      <c r="I347" s="16" t="inlineStr"/>
+      <c r="G355" s="16" t="inlineStr"/>
+      <c r="H355" s="16" t="inlineStr"/>
+      <c r="I355" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I347"/>
+  <autoFilter ref="A1:I355"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G347" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G355" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$355</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$373</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C355,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C373,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P1",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P1",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P1",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P1",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P1",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P1",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P1",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P1",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C355,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C373,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P2",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P2",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P2",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P2",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P2",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P2",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P2",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P2",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C355,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C373,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P3",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P3",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P3",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P3",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P3",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P3",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C355,"P3",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C373,"P3",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pelanggan",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pelanggan",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pelanggan",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pelanggan",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pelanggan",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pelanggan",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pelanggan",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pelanggan",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kasir",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kasir",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kasir",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kasir",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kasir",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kasir",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kasir",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kasir",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pending Payment",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pending Payment",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pending Payment",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pending Payment",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pending Payment",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pending Payment",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pending Payment",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pending Payment",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Dapur",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Dapur",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Dapur",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Dapur",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Dapur",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Dapur",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Dapur",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Dapur",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Keuangan",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Keuangan",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Keuangan",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Keuangan",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Keuangan",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Keuangan",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Keuangan",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Keuangan",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Setor Saldo Cash",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Setor Saldo Cash",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Setor Saldo Cash",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Setor Saldo Cash",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Setor Saldo Cash",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Setor Saldo Cash",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Setor Saldo Cash",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Setor Saldo Cash",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"QR Meja",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"QR Meja",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"QR Meja",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"QR Meja",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"QR Meja",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"QR Meja",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"QR Meja",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"QR Meja",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Diskon",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Diskon",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Diskon",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Diskon",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Diskon",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Diskon",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Diskon",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Diskon",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembayaran QRIS",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembayaran QRIS",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembayaran QRIS",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembayaran QRIS",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembayaran QRIS",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembayaran QRIS",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembayaran QRIS",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembayaran QRIS",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Tampilan",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Tampilan",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Tampilan",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Tampilan",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Tampilan",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Tampilan",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Tampilan",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Tampilan",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Super Admin",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Super Admin",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Super Admin",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Super Admin",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Super Admin",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Super Admin",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Super Admin",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Super Admin",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembaruan Aplikasi",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembaruan Aplikasi",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembaruan Aplikasi",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembaruan Aplikasi",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembaruan Aplikasi",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembaruan Aplikasi",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Pembaruan Aplikasi",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembaruan Aplikasi",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1413,27 +1413,27 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1444,27 +1444,27 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1475,27 +1475,27 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Uji Ujung-ke-Ujung</t>
+          <t>Regresi — bug yang pernah terjadi</t>
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G355,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G373,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G355,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G373,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G355,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G373,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A355,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G355,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G373,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1503,214 +1503,245 @@
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Uji Ujung-ke-Ujung</t>
+        </is>
+      </c>
+      <c r="B33" s="5">
+        <f>COUNTIF('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung")</f>
+        <v/>
+      </c>
+      <c r="C33" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <v/>
+      </c>
+      <c r="D33" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <v/>
+      </c>
+      <c r="E33" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <v/>
+      </c>
+      <c r="F33" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <v/>
+      </c>
+      <c r="G33" s="5">
+        <f>B33-SUM(C33:F33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Rilis ditahan selama masih ada P1 yang Gagal.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>Temuan</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Jumlah</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>Dikonfirmasi</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Sedang diperbaiki</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr">
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t>Menunggu retest</t>
         </is>
       </c>
-      <c r="G37" s="3" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>Ditutup</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>Blocker</t>
-        </is>
-      </c>
-      <c r="B38" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Blocker")</f>
-        <v/>
-      </c>
-      <c r="C38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Baru")</f>
-        <v/>
-      </c>
-      <c r="D38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Dikonfirmasi")</f>
-        <v/>
-      </c>
-      <c r="E38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Sedang diperbaiki")</f>
-        <v/>
-      </c>
-      <c r="F38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Menunggu retest")</f>
-        <v/>
-      </c>
-      <c r="G38" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Ditutup")</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="B39" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Major")</f>
+        <f>COUNTIF(Defect!M5:M64,"Blocker")</f>
         <v/>
       </c>
       <c r="C39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Baru")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
       <c r="D39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Dikonfirmasi")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
       <c r="E39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
       <c r="F39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Menunggu retest")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
       <c r="G39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Ditutup")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="B40" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Minor")</f>
+        <f>COUNTIF(Defect!M5:M64,"Major")</f>
         <v/>
       </c>
       <c r="C40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Baru")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
       <c r="D40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Dikonfirmasi")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
       <c r="F40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Menunggu retest")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
       <c r="G40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Ditutup")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="B41" s="5">
+        <f>COUNTIF(Defect!M5:M64,"Minor")</f>
+        <v/>
+      </c>
+      <c r="C41" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Baru")</f>
+        <v/>
+      </c>
+      <c r="D41" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Dikonfirmasi")</f>
+        <v/>
+      </c>
+      <c r="E41" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <v/>
+      </c>
+      <c r="F41" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Menunggu retest")</f>
+        <v/>
+      </c>
+      <c r="G41" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Ditutup")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="B41" s="5">
+      <c r="B42" s="5">
         <f>COUNTIF(Defect!M5:M64,"Trivial")</f>
         <v/>
       </c>
-      <c r="C41" s="5">
+      <c r="C42" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
-      <c r="D41" s="5">
+      <c r="D42" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
-      <c r="E41" s="5">
+      <c r="E42" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
-      <c r="F41" s="5">
+      <c r="F42" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
-      <c r="G41" s="5">
+      <c r="G42" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B42" s="7">
-        <f>SUM(B38:B41)</f>
-        <v/>
-      </c>
-      <c r="C42" s="7">
-        <f>SUM(C38:C41)</f>
-        <v/>
-      </c>
-      <c r="D42" s="7">
-        <f>SUM(D38:D41)</f>
-        <v/>
-      </c>
-      <c r="E42" s="7">
-        <f>SUM(E38:E41)</f>
-        <v/>
-      </c>
-      <c r="F42" s="7">
-        <f>SUM(F38:F41)</f>
-        <v/>
-      </c>
-      <c r="G42" s="7">
-        <f>SUM(G38:G41)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="B43" s="7">
+        <f>SUM(B39:B42)</f>
+        <v/>
+      </c>
+      <c r="C43" s="7">
+        <f>SUM(C39:C42)</f>
+        <v/>
+      </c>
+      <c r="D43" s="7">
+        <f>SUM(D39:D42)</f>
+        <v/>
+      </c>
+      <c r="E43" s="7">
+        <f>SUM(E39:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="7">
+        <f>SUM(F39:F42)</f>
+        <v/>
+      </c>
+      <c r="G43" s="7">
+        <f>SUM(G39:G42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
         <is>
           <t>Blocker yang belum Ditutup menahan rilis.</t>
         </is>
@@ -1727,7 +1758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I355"/>
+  <dimension ref="A1:I373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12711,32 +12742,32 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B314" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
-        </is>
-      </c>
-      <c r="C314" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-01</t>
+        </is>
+      </c>
+      <c r="C314" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Super Admin → Finance → Voucher Pelanggan → buat voucher 10%</t>
         </is>
       </c>
       <c r="E314" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Tersimpan berikut kodenya</t>
         </is>
       </c>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr"/>
@@ -12746,32 +12777,32 @@
     <row r="315">
       <c r="A315" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B315" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
-        </is>
-      </c>
-      <c r="C315" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-02</t>
+        </is>
+      </c>
+      <c r="C315" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Buat voucher berkode sama dengan yang sudah ada</t>
         </is>
       </c>
       <c r="E315" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Ditolak — kodenya sudah dipakai</t>
         </is>
       </c>
       <c r="F315" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G315" s="16" t="inlineStr"/>
@@ -12781,12 +12812,12 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B316" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-VC-03</t>
         </is>
       </c>
       <c r="C316" s="15" t="inlineStr">
@@ -12796,17 +12827,17 @@
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Voucher 20% tanpa batas, tagihan Rp 1.000.000</t>
         </is>
       </c>
       <c r="E316" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Potongan Rp 200.000</t>
         </is>
       </c>
       <c r="F316" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G316" s="13" t="inlineStr"/>
@@ -12816,12 +12847,12 @@
     <row r="317">
       <c r="A317" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B317" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
+          <t>TC-VC-04</t>
         </is>
       </c>
       <c r="C317" s="18" t="inlineStr">
@@ -12831,17 +12862,17 @@
       </c>
       <c r="D317" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Voucher yang sama dengan maks. Rp 20.000</t>
         </is>
       </c>
       <c r="E317" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Potongan berhenti di Rp 20.000</t>
         </is>
       </c>
       <c r="F317" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-VC-02</t>
         </is>
       </c>
       <c r="G317" s="16" t="inlineStr"/>
@@ -12851,12 +12882,12 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B318" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-VC-05</t>
         </is>
       </c>
       <c r="C318" s="15" t="inlineStr">
@@ -12866,17 +12897,17 @@
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
         </is>
       </c>
       <c r="E318" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Ditolak dengan sebutan minimalnya</t>
         </is>
       </c>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-VC-03, F-VC-10</t>
         </is>
       </c>
       <c r="G318" s="13" t="inlineStr"/>
@@ -12886,12 +12917,12 @@
     <row r="319">
       <c r="A319" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B319" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-VC-06</t>
         </is>
       </c>
       <c r="C319" s="18" t="inlineStr">
@@ -12901,17 +12932,17 @@
       </c>
       <c r="D319" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Voucher khusus resto A, dipakai di resto B</t>
         </is>
       </c>
       <c r="E319" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Ditolak — "tidak berlaku di resto ini"</t>
         </is>
       </c>
       <c r="F319" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G319" s="16" t="inlineStr"/>
@@ -12921,12 +12952,12 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B320" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-VC-07</t>
         </is>
       </c>
       <c r="C320" s="15" t="inlineStr">
@@ -12936,17 +12967,17 @@
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Voucher kuota 1, pakai dua kali oleh orang berbeda</t>
         </is>
       </c>
       <c r="E320" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Yang kedua ditolak — kuota habis</t>
         </is>
       </c>
       <c r="F320" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-VC-05</t>
         </is>
       </c>
       <c r="G320" s="13" t="inlineStr"/>
@@ -12956,12 +12987,12 @@
     <row r="321">
       <c r="A321" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B321" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
+          <t>TC-VC-08</t>
         </is>
       </c>
       <c r="C321" s="18" t="inlineStr">
@@ -12971,17 +13002,17 @@
       </c>
       <c r="D321" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Voucher kuota per pelanggan 1, pakai dua kali oleh orang sama</t>
         </is>
       </c>
       <c r="E321" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Yang kedua ditolak — "sudah kamu pakai"</t>
         </is>
       </c>
       <c r="F321" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-VC-05</t>
         </is>
       </c>
       <c r="G321" s="16" t="inlineStr"/>
@@ -12991,32 +13022,32 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B322" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
-        </is>
-      </c>
-      <c r="C322" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-09</t>
+        </is>
+      </c>
+      <c r="C322" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Ketik kode dengan huruf kecil</t>
         </is>
       </c>
       <c r="E322" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Tetap diterima</t>
         </is>
       </c>
       <c r="F322" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G322" s="13" t="inlineStr"/>
@@ -13026,32 +13057,32 @@
     <row r="323">
       <c r="A323" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B323" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
-        </is>
-      </c>
-      <c r="C323" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-10</t>
+        </is>
+      </c>
+      <c r="C323" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D323" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Ketik kode yang tidak ada</t>
         </is>
       </c>
       <c r="E323" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Ditolak dengan sebutan tidak ditemukan</t>
         </is>
       </c>
       <c r="F323" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>F-VC-10</t>
         </is>
       </c>
       <c r="G323" s="16" t="inlineStr"/>
@@ -13061,12 +13092,12 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B324" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
+          <t>TC-VC-11</t>
         </is>
       </c>
       <c r="C324" s="19" t="inlineStr">
@@ -13076,17 +13107,17 @@
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Voucher nonaktif / lewat masa berlaku</t>
         </is>
       </c>
       <c r="E324" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Ditolak, masing-masing dengan alasannya</t>
         </is>
       </c>
       <c r="F324" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>F-VC-06, F-VC-10</t>
         </is>
       </c>
       <c r="G324" s="13" t="inlineStr"/>
@@ -13096,32 +13127,32 @@
     <row r="325">
       <c r="A325" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B325" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C325" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-12</t>
+        </is>
+      </c>
+      <c r="C325" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D325" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Pasang voucher lalu selesaikan pesanan</t>
         </is>
       </c>
       <c r="E325" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
         </is>
       </c>
       <c r="F325" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>F-VC-08</t>
         </is>
       </c>
       <c r="G325" s="16" t="inlineStr"/>
@@ -13131,32 +13162,32 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B326" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C326" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-13</t>
+        </is>
+      </c>
+      <c r="C326" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Ketuk Lepas setelah voucher terpasang</t>
         </is>
       </c>
       <c r="E326" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Tagihan kembali ke nominal semula</t>
         </is>
       </c>
       <c r="F326" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>F-VC-08</t>
         </is>
       </c>
       <c r="G326" s="13" t="inlineStr"/>
@@ -13166,12 +13197,12 @@
     <row r="327">
       <c r="A327" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B327" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-VC-14</t>
         </is>
       </c>
       <c r="C327" s="18" t="inlineStr">
@@ -13181,17 +13212,17 @@
       </c>
       <c r="D327" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Periksa Jurnal GL KaataGo sesudah voucher dipakai</t>
         </is>
       </c>
       <c r="E327" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Dua baris: GL Biaya Voucher debit, kantongnya kredit</t>
         </is>
       </c>
       <c r="F327" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>F-VC-12</t>
         </is>
       </c>
       <c r="G327" s="16" t="inlineStr"/>
@@ -13201,12 +13232,12 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B328" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
+          <t>TC-VC-15</t>
         </is>
       </c>
       <c r="C328" s="15" t="inlineStr">
@@ -13216,17 +13247,17 @@
       </c>
       <c r="D328" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Periksa Jurnal GL resto yang bersangkutan</t>
         </is>
       </c>
       <c r="E328" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Tidak ada baris voucher di sana</t>
         </is>
       </c>
       <c r="F328" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>F-VC-12</t>
         </is>
       </c>
       <c r="G328" s="13" t="inlineStr"/>
@@ -13236,12 +13267,12 @@
     <row r="329">
       <c r="A329" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B329" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-VC-16</t>
         </is>
       </c>
       <c r="C329" s="18" t="inlineStr">
@@ -13251,17 +13282,17 @@
       </c>
       <c r="D329" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Panggil voucher_quote lewat API dengan nominal dipalsukan</t>
         </is>
       </c>
       <c r="E329" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Nominal yang dipakai tetap dari perhitungan server</t>
         </is>
       </c>
       <c r="F329" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>F-VC-09</t>
         </is>
       </c>
       <c r="G329" s="16" t="inlineStr"/>
@@ -13271,12 +13302,12 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B330" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
+          <t>TC-VC-17</t>
         </is>
       </c>
       <c r="C330" s="19" t="inlineStr">
@@ -13286,17 +13317,17 @@
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Buka daftar voucher sebagai Owner resto</t>
         </is>
       </c>
       <c r="E330" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Terbaca, tapi tidak bisa diubah</t>
         </is>
       </c>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G330" s="13" t="inlineStr"/>
@@ -13306,12 +13337,12 @@
     <row r="331">
       <c r="A331" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B331" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
+          <t>TC-VC-18</t>
         </is>
       </c>
       <c r="C331" s="20" t="inlineStr">
@@ -13321,17 +13352,17 @@
       </c>
       <c r="D331" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Periksa jumlah "dipakai" di kartu voucher</t>
         </is>
       </c>
       <c r="E331" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Cocok dengan jumlah pemakaian sebenarnya</t>
         </is>
       </c>
       <c r="F331" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G331" s="16" t="inlineStr"/>
@@ -13346,27 +13377,27 @@
       </c>
       <c r="B332" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C332" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-01</t>
+        </is>
+      </c>
+      <c r="C332" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E332" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G332" s="13" t="inlineStr"/>
@@ -13376,12 +13407,12 @@
     <row r="333">
       <c r="A333" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B333" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
+          <t>TC-TS-02</t>
         </is>
       </c>
       <c r="C333" s="18" t="inlineStr">
@@ -13391,17 +13422,17 @@
       </c>
       <c r="D333" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E333" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F333" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G333" s="16" t="inlineStr"/>
@@ -13411,12 +13442,12 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B334" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
+          <t>TC-TS-03</t>
         </is>
       </c>
       <c r="C334" s="15" t="inlineStr">
@@ -13426,17 +13457,17 @@
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E334" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F334" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G334" s="13" t="inlineStr"/>
@@ -13446,12 +13477,12 @@
     <row r="335">
       <c r="A335" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B335" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
+          <t>TC-TS-04</t>
         </is>
       </c>
       <c r="C335" s="18" t="inlineStr">
@@ -13461,17 +13492,17 @@
       </c>
       <c r="D335" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E335" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F335" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G335" s="16" t="inlineStr"/>
@@ -13481,12 +13512,12 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B336" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
+          <t>TC-TS-05</t>
         </is>
       </c>
       <c r="C336" s="15" t="inlineStr">
@@ -13496,17 +13527,17 @@
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E336" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G336" s="13" t="inlineStr"/>
@@ -13516,12 +13547,12 @@
     <row r="337">
       <c r="A337" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B337" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C337" s="18" t="inlineStr">
@@ -13531,17 +13562,17 @@
       </c>
       <c r="D337" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E337" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F337" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G337" s="16" t="inlineStr"/>
@@ -13551,12 +13582,12 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B338" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-TS-07</t>
         </is>
       </c>
       <c r="C338" s="15" t="inlineStr">
@@ -13566,17 +13597,17 @@
       </c>
       <c r="D338" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E338" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G338" s="13" t="inlineStr"/>
@@ -13586,32 +13617,32 @@
     <row r="339">
       <c r="A339" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B339" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C339" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C339" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D339" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E339" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F339" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G339" s="16" t="inlineStr"/>
@@ -13621,32 +13652,32 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B340" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C340" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C340" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E340" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr"/>
@@ -13656,32 +13687,32 @@
     <row r="341">
       <c r="A341" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B341" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
-        </is>
-      </c>
-      <c r="C341" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C341" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D341" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E341" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F341" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G341" s="16" t="inlineStr"/>
@@ -13691,12 +13722,12 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B342" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
+          <t>TC-TS-11</t>
         </is>
       </c>
       <c r="C342" s="19" t="inlineStr">
@@ -13706,17 +13737,17 @@
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E342" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G342" s="13" t="inlineStr"/>
@@ -13726,12 +13757,12 @@
     <row r="343">
       <c r="A343" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B343" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
+          <t>TC-TS-12</t>
         </is>
       </c>
       <c r="C343" s="20" t="inlineStr">
@@ -13741,17 +13772,17 @@
       </c>
       <c r="D343" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E343" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F343" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G343" s="16" t="inlineStr"/>
@@ -13761,12 +13792,12 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B344" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
+          <t>TC-TS-13</t>
         </is>
       </c>
       <c r="C344" s="19" t="inlineStr">
@@ -13776,17 +13807,17 @@
       </c>
       <c r="D344" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E344" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G344" s="13" t="inlineStr"/>
@@ -13796,12 +13827,12 @@
     <row r="345">
       <c r="A345" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B345" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
+          <t>TC-TS-14</t>
         </is>
       </c>
       <c r="C345" s="18" t="inlineStr">
@@ -13811,17 +13842,17 @@
       </c>
       <c r="D345" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E345" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F345" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G345" s="16" t="inlineStr"/>
@@ -13831,32 +13862,32 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B346" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
-        </is>
-      </c>
-      <c r="C346" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C346" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D346" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E346" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G346" s="13" t="inlineStr"/>
@@ -13866,25 +13897,655 @@
     <row r="347">
       <c r="A347" s="16" t="inlineStr">
         <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B347" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-16</t>
+        </is>
+      </c>
+      <c r="C347" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D347" s="16" t="inlineStr">
+        <is>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+        </is>
+      </c>
+      <c r="E347" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak</t>
+        </is>
+      </c>
+      <c r="F347" s="16" t="inlineStr">
+        <is>
+          <t>F-PG-02, TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G347" s="16" t="inlineStr"/>
+      <c r="H347" s="16" t="inlineStr"/>
+      <c r="I347" s="16" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B348" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C348" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D348" s="13" t="inlineStr">
+        <is>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+        </is>
+      </c>
+      <c r="E348" s="13" t="inlineStr">
+        <is>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+        </is>
+      </c>
+      <c r="F348" s="13" t="inlineStr">
+        <is>
+          <t>TSD §1.2</t>
+        </is>
+      </c>
+      <c r="G348" s="13" t="inlineStr"/>
+      <c r="H348" s="13" t="inlineStr"/>
+      <c r="I348" s="13" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B349" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C349" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D349" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+        </is>
+      </c>
+      <c r="E349" s="16" t="inlineStr">
+        <is>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+        </is>
+      </c>
+      <c r="F349" s="16" t="inlineStr">
+        <is>
+          <t>TSD §6.5</t>
+        </is>
+      </c>
+      <c r="G349" s="16" t="inlineStr"/>
+      <c r="H349" s="16" t="inlineStr"/>
+      <c r="I349" s="16" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B350" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C350" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D350" s="13" t="inlineStr">
+        <is>
+          <t>Hapus resto uji</t>
+        </is>
+      </c>
+      <c r="E350" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+        </is>
+      </c>
+      <c r="F350" s="13" t="inlineStr">
+        <is>
+          <t>TSD §4.0</t>
+        </is>
+      </c>
+      <c r="G350" s="13" t="inlineStr"/>
+      <c r="H350" s="13" t="inlineStr"/>
+      <c r="I350" s="13" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B351" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C351" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D351" s="16" t="inlineStr">
+        <is>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+        </is>
+      </c>
+      <c r="E351" s="16" t="inlineStr">
+        <is>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+        </is>
+      </c>
+      <c r="F351" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-09</t>
+        </is>
+      </c>
+      <c r="G351" s="16" t="inlineStr"/>
+      <c r="H351" s="16" t="inlineStr"/>
+      <c r="I351" s="16" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B352" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C352" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D352" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="E352" s="13" t="inlineStr">
+        <is>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="F352" s="13" t="inlineStr">
+        <is>
+          <t>F-PP-09, A-13</t>
+        </is>
+      </c>
+      <c r="G352" s="13" t="inlineStr"/>
+      <c r="H352" s="13" t="inlineStr"/>
+      <c r="I352" s="13" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B353" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C353" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D353" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+        </is>
+      </c>
+      <c r="E353" s="16" t="inlineStr">
+        <is>
+          <t>Tidak muncul sama sekali</t>
+        </is>
+      </c>
+      <c r="F353" s="16" t="inlineStr">
+        <is>
+          <t>A-17</t>
+        </is>
+      </c>
+      <c r="G353" s="16" t="inlineStr"/>
+      <c r="H353" s="16" t="inlineStr"/>
+      <c r="I353" s="16" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B354" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C354" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D354" s="13" t="inlineStr">
+        <is>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+        </is>
+      </c>
+      <c r="E354" s="13" t="inlineStr">
+        <is>
+          <t>Nominalnya sama dengan yang diajukan</t>
+        </is>
+      </c>
+      <c r="F354" s="13" t="inlineStr">
+        <is>
+          <t>F-FN-03</t>
+        </is>
+      </c>
+      <c r="G354" s="13" t="inlineStr"/>
+      <c r="H354" s="13" t="inlineStr"/>
+      <c r="I354" s="13" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B355" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C355" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D355" s="16" t="inlineStr">
+        <is>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+        </is>
+      </c>
+      <c r="E355" s="16" t="inlineStr">
+        <is>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
+        </is>
+      </c>
+      <c r="F355" s="16" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="G355" s="16" t="inlineStr"/>
+      <c r="H355" s="16" t="inlineStr"/>
+      <c r="I355" s="16" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B356" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C356" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D356" s="13" t="inlineStr">
+        <is>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+        </is>
+      </c>
+      <c r="E356" s="13" t="inlineStr">
+        <is>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+        </is>
+      </c>
+      <c r="F356" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-10, F-DS-12</t>
+        </is>
+      </c>
+      <c r="G356" s="13" t="inlineStr"/>
+      <c r="H356" s="13" t="inlineStr"/>
+      <c r="I356" s="13" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B357" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C357" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D357" s="16" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E357" s="16" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F357" s="16" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G357" s="16" t="inlineStr"/>
+      <c r="H357" s="16" t="inlineStr"/>
+      <c r="I357" s="16" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B358" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C358" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D358" s="13" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E358" s="13" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F358" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G358" s="13" t="inlineStr"/>
+      <c r="H358" s="13" t="inlineStr"/>
+      <c r="I358" s="13" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B359" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C359" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D359" s="16" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E359" s="16" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F359" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G359" s="16" t="inlineStr"/>
+      <c r="H359" s="16" t="inlineStr"/>
+      <c r="I359" s="16" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B360" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C360" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D360" s="13" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E360" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F360" s="13" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G360" s="13" t="inlineStr"/>
+      <c r="H360" s="13" t="inlineStr"/>
+      <c r="I360" s="13" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B361" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C361" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D361" s="16" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E361" s="16" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F361" s="16" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G361" s="16" t="inlineStr"/>
+      <c r="H361" s="16" t="inlineStr"/>
+      <c r="I361" s="16" t="inlineStr"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B362" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C362" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D362" s="13" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E362" s="13" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F362" s="13" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G362" s="13" t="inlineStr"/>
+      <c r="H362" s="13" t="inlineStr"/>
+      <c r="I362" s="13" t="inlineStr"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B363" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C363" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D363" s="16" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E363" s="16" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F363" s="16" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G363" s="16" t="inlineStr"/>
+      <c r="H363" s="16" t="inlineStr"/>
+      <c r="I363" s="16" t="inlineStr"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B364" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C364" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D364" s="13" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E364" s="13" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F364" s="13" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G364" s="13" t="inlineStr"/>
+      <c r="H364" s="13" t="inlineStr"/>
+      <c r="I364" s="13" t="inlineStr"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="16" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B347" s="17" t="inlineStr">
+      <c r="B365" s="17" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C347" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D347" s="16" t="inlineStr">
+      <c r="C365" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D365" s="16" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E347" s="16" t="inlineStr">
+      <c r="E365" s="16" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -13898,37 +14559,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F347" s="16" t="inlineStr">
+      <c r="F365" s="16" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G347" s="16" t="inlineStr"/>
-      <c r="H347" s="16" t="inlineStr"/>
-      <c r="I347" s="16" t="inlineStr"/>
-    </row>
-    <row r="348">
-      <c r="A348" s="13" t="inlineStr">
+      <c r="G365" s="16" t="inlineStr"/>
+      <c r="H365" s="16" t="inlineStr"/>
+      <c r="I365" s="16" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B348" s="14" t="inlineStr">
+      <c r="B366" s="14" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C348" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D348" s="13" t="inlineStr">
+      <c r="C366" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D366" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E348" s="13" t="inlineStr">
+      <c r="E366" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -13940,37 +14601,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F348" s="13" t="inlineStr">
+      <c r="F366" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G348" s="13" t="inlineStr"/>
-      <c r="H348" s="13" t="inlineStr"/>
-      <c r="I348" s="13" t="inlineStr"/>
-    </row>
-    <row r="349">
-      <c r="A349" s="16" t="inlineStr">
+      <c r="G366" s="13" t="inlineStr"/>
+      <c r="H366" s="13" t="inlineStr"/>
+      <c r="I366" s="13" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B349" s="17" t="inlineStr">
+      <c r="B367" s="17" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C349" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D349" s="16" t="inlineStr">
+      <c r="C367" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D367" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E349" s="16" t="inlineStr">
+      <c r="E367" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -13982,74 +14643,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F349" s="16" t="inlineStr">
+      <c r="F367" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G349" s="16" t="inlineStr"/>
-      <c r="H349" s="16" t="inlineStr"/>
-      <c r="I349" s="16" t="inlineStr"/>
-    </row>
-    <row r="350">
-      <c r="A350" s="13" t="inlineStr">
+      <c r="G367" s="16" t="inlineStr"/>
+      <c r="H367" s="16" t="inlineStr"/>
+      <c r="I367" s="16" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B350" s="14" t="inlineStr">
+      <c r="B368" s="14" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C350" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D350" s="13" t="inlineStr">
+      <c r="C368" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D368" s="13" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E350" s="13" t="inlineStr">
+      <c r="E368" s="13" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F350" s="13" t="inlineStr">
+      <c r="F368" s="13" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G350" s="13" t="inlineStr"/>
-      <c r="H350" s="13" t="inlineStr"/>
-      <c r="I350" s="13" t="inlineStr"/>
-    </row>
-    <row r="351">
-      <c r="A351" s="16" t="inlineStr">
+      <c r="G368" s="13" t="inlineStr"/>
+      <c r="H368" s="13" t="inlineStr"/>
+      <c r="I368" s="13" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B351" s="17" t="inlineStr">
+      <c r="B369" s="17" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C351" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D351" s="16" t="inlineStr">
+      <c r="C369" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D369" s="16" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E351" s="16" t="inlineStr">
+      <c r="E369" s="16" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -14060,73 +14721,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F351" s="16" t="inlineStr">
+      <c r="F369" s="16" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G351" s="16" t="inlineStr"/>
-      <c r="H351" s="16" t="inlineStr"/>
-      <c r="I351" s="16" t="inlineStr"/>
-    </row>
-    <row r="352">
-      <c r="A352" s="13" t="inlineStr">
+      <c r="G369" s="16" t="inlineStr"/>
+      <c r="H369" s="16" t="inlineStr"/>
+      <c r="I369" s="16" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B352" s="14" t="inlineStr">
+      <c r="B370" s="14" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C352" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D352" s="13" t="inlineStr">
+      <c r="C370" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D370" s="13" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E352" s="13" t="inlineStr">
+      <c r="E370" s="13" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F352" s="13" t="inlineStr">
+      <c r="F370" s="13" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G352" s="13" t="inlineStr"/>
-      <c r="H352" s="13" t="inlineStr"/>
-      <c r="I352" s="13" t="inlineStr"/>
-    </row>
-    <row r="353">
-      <c r="A353" s="16" t="inlineStr">
+      <c r="G370" s="13" t="inlineStr"/>
+      <c r="H370" s="13" t="inlineStr"/>
+      <c r="I370" s="13" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B353" s="17" t="inlineStr">
+      <c r="B371" s="17" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C353" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D353" s="16" t="inlineStr">
+      <c r="C371" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D371" s="16" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E353" s="16" t="inlineStr">
+      <c r="E371" s="16" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -14137,37 +14798,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F353" s="16" t="inlineStr">
+      <c r="F371" s="16" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G353" s="16" t="inlineStr"/>
-      <c r="H353" s="16" t="inlineStr"/>
-      <c r="I353" s="16" t="inlineStr"/>
-    </row>
-    <row r="354">
-      <c r="A354" s="13" t="inlineStr">
+      <c r="G371" s="16" t="inlineStr"/>
+      <c r="H371" s="16" t="inlineStr"/>
+      <c r="I371" s="16" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B354" s="14" t="inlineStr">
+      <c r="B372" s="14" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C354" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D354" s="13" t="inlineStr">
+      <c r="C372" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D372" s="13" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E354" s="13" t="inlineStr">
+      <c r="E372" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -14177,37 +14838,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F354" s="13" t="inlineStr">
+      <c r="F372" s="13" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G354" s="13" t="inlineStr"/>
-      <c r="H354" s="13" t="inlineStr"/>
-      <c r="I354" s="13" t="inlineStr"/>
-    </row>
-    <row r="355">
-      <c r="A355" s="16" t="inlineStr">
+      <c r="G372" s="13" t="inlineStr"/>
+      <c r="H372" s="13" t="inlineStr"/>
+      <c r="I372" s="13" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B355" s="17" t="inlineStr">
+      <c r="B373" s="17" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C355" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D355" s="16" t="inlineStr">
+      <c r="C373" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D373" s="16" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E355" s="16" t="inlineStr">
+      <c r="E373" s="16" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -14215,19 +14876,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F355" s="16" t="inlineStr">
+      <c r="F373" s="16" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G355" s="16" t="inlineStr"/>
-      <c r="H355" s="16" t="inlineStr"/>
-      <c r="I355" s="16" t="inlineStr"/>
+      <c r="G373" s="16" t="inlineStr"/>
+      <c r="H373" s="16" t="inlineStr"/>
+      <c r="I373" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I355"/>
+  <autoFilter ref="A1:I373"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G355" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G373" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rekap" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kasus Uji" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Defect" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prasyarat" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Rekap" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Kasus Uji" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Defect" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Prasyarat" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$399</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C373,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C399,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P1",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P1",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P1",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P1",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P1",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P1",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P1",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P1",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C373,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C399,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P2",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P2",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P2",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P2",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P2",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P2",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P2",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P2",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C373,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C399,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P3",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P3",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P3",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P3",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P3",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P3",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C373,"P3",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C399,"P3",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pelanggan",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pelanggan",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pelanggan",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pelanggan",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pelanggan",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pelanggan",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pelanggan",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pelanggan",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kasir",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kasir",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kasir",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kasir",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kasir",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kasir",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kasir",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kasir",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pending Payment",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pending Payment",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pending Payment",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pending Payment",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pending Payment",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pending Payment",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pending Payment",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pending Payment",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Dapur",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Dapur",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Dapur",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Dapur",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Dapur",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Dapur",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Dapur",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Dapur",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Keuangan",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Keuangan",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Keuangan",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Keuangan",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Keuangan",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Keuangan",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Keuangan",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Keuangan",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Setor Saldo Cash",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Setor Saldo Cash",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Setor Saldo Cash",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Setor Saldo Cash",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Setor Saldo Cash",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Setor Saldo Cash",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Setor Saldo Cash",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Setor Saldo Cash",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"QR Meja",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"QR Meja",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"QR Meja",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"QR Meja",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"QR Meja",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"QR Meja",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"QR Meja",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"QR Meja",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Diskon",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Diskon",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Diskon",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Diskon",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Diskon",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Diskon",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Diskon",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Diskon",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembayaran QRIS",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembayaran QRIS",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembayaran QRIS",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembayaran QRIS",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembayaran QRIS",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembayaran QRIS",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembayaran QRIS",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembayaran QRIS",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Tampilan",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Tampilan",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Tampilan",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Tampilan",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Tampilan",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Tampilan",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Tampilan",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Tampilan",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Super Admin",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Super Admin",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Super Admin",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Super Admin",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Super Admin",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Super Admin",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Super Admin",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Super Admin",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembaruan Aplikasi",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembaruan Aplikasi",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembaruan Aplikasi",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembaruan Aplikasi",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembaruan Aplikasi",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembaruan Aplikasi",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Pembaruan Aplikasi",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembaruan Aplikasi",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1510,23 +1510,23 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G373,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G399,"Lulus")</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G373,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G399,"Gagal")</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G373,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G399,"Terblokir")</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A373,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G373,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G399,"Dilewati")</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -1758,7 +1758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I373"/>
+  <dimension ref="A1:I399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12750,24 +12750,24 @@
           <t>TC-VC-01</t>
         </is>
       </c>
-      <c r="C314" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C314" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Voucher Pelanggan → buat voucher 10%</t>
+          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
         </is>
       </c>
       <c r="E314" s="13" t="inlineStr">
         <is>
-          <t>Tersimpan berikut kodenya</t>
+          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
         </is>
       </c>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-VC-01, F-VC-02</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr"/>
@@ -12785,24 +12785,24 @@
           <t>TC-VC-02</t>
         </is>
       </c>
-      <c r="C315" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C315" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>Buat voucher berkode sama dengan yang sudah ada</t>
+          <t>Terbitkan Rp 1.000.000 jadi 3</t>
         </is>
       </c>
       <c r="E315" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — kodenya sudah dipakai</t>
+          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
         </is>
       </c>
       <c r="F315" s="16" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-VC-02</t>
         </is>
       </c>
       <c r="G315" s="16" t="inlineStr"/>
@@ -12820,19 +12820,19 @@
           <t>TC-VC-03</t>
         </is>
       </c>
-      <c r="C316" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C316" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>Voucher 20% tanpa batas, tagihan Rp 1.000.000</t>
+          <t>Terbitkan dengan kode yang sudah dipakai</t>
         </is>
       </c>
       <c r="E316" s="13" t="inlineStr">
         <is>
-          <t>Potongan Rp 200.000</t>
+          <t>Ditolak — kodenya sudah ada</t>
         </is>
       </c>
       <c r="F316" s="13" t="inlineStr">
@@ -12862,17 +12862,17 @@
       </c>
       <c r="D317" s="16" t="inlineStr">
         <is>
-          <t>Voucher yang sama dengan maks. Rp 20.000</t>
+          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
         </is>
       </c>
       <c r="E317" s="16" t="inlineStr">
         <is>
-          <t>Potongan berhenti di Rp 20.000</t>
+          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
         </is>
       </c>
       <c r="F317" s="16" t="inlineStr">
         <is>
-          <t>F-VC-02</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G317" s="16" t="inlineStr"/>
@@ -12897,17 +12897,17 @@
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
+          <t>Pelanggan menebus kode di Voucher Saya</t>
         </is>
       </c>
       <c r="E318" s="13" t="inlineStr">
         <is>
-          <t>Ditolak dengan sebutan minimalnya</t>
+          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
         </is>
       </c>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>F-VC-03, F-VC-10</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G318" s="13" t="inlineStr"/>
@@ -12925,24 +12925,24 @@
           <t>TC-VC-06</t>
         </is>
       </c>
-      <c r="C319" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C319" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D319" s="16" t="inlineStr">
         <is>
-          <t>Voucher khusus resto A, dipakai di resto B</t>
+          <t>Ketik kodenya dengan huruf kecil</t>
         </is>
       </c>
       <c r="E319" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — "tidak berlaku di resto ini"</t>
+          <t>Tetap diterima</t>
         </is>
       </c>
       <c r="F319" s="16" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G319" s="16" t="inlineStr"/>
@@ -12960,24 +12960,24 @@
           <t>TC-VC-07</t>
         </is>
       </c>
-      <c r="C320" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C320" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>Voucher kuota 1, pakai dua kali oleh orang berbeda</t>
+          <t>Ketik kode yang tidak ada</t>
         </is>
       </c>
       <c r="E320" s="13" t="inlineStr">
         <is>
-          <t>Yang kedua ditolak — kuota habis</t>
+          <t>"Kode voucher tidak ditemukan"</t>
         </is>
       </c>
       <c r="F320" s="13" t="inlineStr">
         <is>
-          <t>F-VC-05</t>
+          <t>F-VC-10</t>
         </is>
       </c>
       <c r="G320" s="13" t="inlineStr"/>
@@ -13002,17 +13002,17 @@
       </c>
       <c r="D321" s="16" t="inlineStr">
         <is>
-          <t>Voucher kuota per pelanggan 1, pakai dua kali oleh orang sama</t>
+          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
         </is>
       </c>
       <c r="E321" s="16" t="inlineStr">
         <is>
-          <t>Yang kedua ditolak — "sudah kamu pakai"</t>
+          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
         </is>
       </c>
       <c r="F321" s="16" t="inlineStr">
         <is>
-          <t>F-VC-05</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G321" s="16" t="inlineStr"/>
@@ -13030,24 +13030,24 @@
           <t>TC-VC-09</t>
         </is>
       </c>
-      <c r="C322" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C322" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
-          <t>Ketik kode dengan huruf kecil</t>
+          <t>Orang yang sama menebus kode itu lagi</t>
         </is>
       </c>
       <c r="E322" s="13" t="inlineStr">
         <is>
-          <t>Tetap diterima</t>
+          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
         </is>
       </c>
       <c r="F322" s="13" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-VC-08, F-VC-10</t>
         </is>
       </c>
       <c r="G322" s="13" t="inlineStr"/>
@@ -13065,24 +13065,24 @@
           <t>TC-VC-10</t>
         </is>
       </c>
-      <c r="C323" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C323" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D323" s="16" t="inlineStr">
         <is>
-          <t>Ketik kode yang tidak ada</t>
+          <t>Batch berisi 10, orang ke-11 menebus</t>
         </is>
       </c>
       <c r="E323" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan sebutan tidak ditemukan</t>
+          <t>Ditolak — "Voucher ini sudah habis"</t>
         </is>
       </c>
       <c r="F323" s="16" t="inlineStr">
         <is>
-          <t>F-VC-10</t>
+          <t>F-VC-09, F-VC-10</t>
         </is>
       </c>
       <c r="G323" s="16" t="inlineStr"/>
@@ -13100,24 +13100,24 @@
           <t>TC-VC-11</t>
         </is>
       </c>
-      <c r="C324" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C324" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
-          <t>Voucher nonaktif / lewat masa berlaku</t>
+          <t>Dua orang menebus voucher terakhir bersamaan</t>
         </is>
       </c>
       <c r="E324" s="13" t="inlineStr">
         <is>
-          <t>Ditolak, masing-masing dengan alasannya</t>
+          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
         </is>
       </c>
       <c r="F324" s="13" t="inlineStr">
         <is>
-          <t>F-VC-06, F-VC-10</t>
+          <t>F-VC-09</t>
         </is>
       </c>
       <c r="G324" s="13" t="inlineStr"/>
@@ -13135,24 +13135,24 @@
           <t>TC-VC-12</t>
         </is>
       </c>
-      <c r="C325" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C325" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D325" s="16" t="inlineStr">
         <is>
-          <t>Pasang voucher lalu selesaikan pesanan</t>
+          <t>Tebus voucher dari batch yang sudah ditutup</t>
         </is>
       </c>
       <c r="E325" s="16" t="inlineStr">
         <is>
-          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
+          <t>"Voucher ini sudah ditutup"</t>
         </is>
       </c>
       <c r="F325" s="16" t="inlineStr">
         <is>
-          <t>F-VC-08</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G325" s="16" t="inlineStr"/>
@@ -13170,24 +13170,24 @@
           <t>TC-VC-13</t>
         </is>
       </c>
-      <c r="C326" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+      <c r="C326" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Lepas setelah voucher terpasang</t>
+          <t>Tebus voucher yang lewat masa berlaku</t>
         </is>
       </c>
       <c r="E326" s="13" t="inlineStr">
         <is>
-          <t>Tagihan kembali ke nominal semula</t>
+          <t>"Voucher ini sudah kedaluwarsa"</t>
         </is>
       </c>
       <c r="F326" s="13" t="inlineStr">
         <is>
-          <t>F-VC-08</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G326" s="13" t="inlineStr"/>
@@ -13212,17 +13212,17 @@
       </c>
       <c r="D327" s="16" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah voucher dipakai</t>
+          <t>Di keranjang, ketuk baris voucher</t>
         </is>
       </c>
       <c r="E327" s="16" t="inlineStr">
         <is>
-          <t>Dua baris: GL Biaya Voucher debit, kantongnya kredit</t>
+          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
         </is>
       </c>
       <c r="F327" s="16" t="inlineStr">
         <is>
-          <t>F-VC-12</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G327" s="16" t="inlineStr"/>
@@ -13247,17 +13247,17 @@
       </c>
       <c r="D328" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL resto yang bersangkutan</t>
+          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
         </is>
       </c>
       <c r="E328" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada baris voucher di sana</t>
+          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
         </is>
       </c>
       <c r="F328" s="13" t="inlineStr">
         <is>
-          <t>F-VC-12</t>
+          <t>F-VC-05, F-VC-10</t>
         </is>
       </c>
       <c r="G328" s="13" t="inlineStr"/>
@@ -13282,17 +13282,17 @@
       </c>
       <c r="D329" s="16" t="inlineStr">
         <is>
-          <t>Panggil voucher_quote lewat API dengan nominal dipalsukan</t>
+          <t>Voucher khusus resto A dibuka di resto B</t>
         </is>
       </c>
       <c r="E329" s="16" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari perhitungan server</t>
+          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
         </is>
       </c>
       <c r="F329" s="16" t="inlineStr">
         <is>
-          <t>F-VC-09</t>
+          <t>F-VC-06, F-VC-10</t>
         </is>
       </c>
       <c r="G329" s="16" t="inlineStr"/>
@@ -13310,24 +13310,24 @@
           <t>TC-VC-17</t>
         </is>
       </c>
-      <c r="C330" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C330" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
-          <t>Buka daftar voucher sebagai Owner resto</t>
+          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
         </is>
       </c>
       <c r="E330" s="13" t="inlineStr">
         <is>
-          <t>Terbaca, tapi tidak bisa diubah</t>
+          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
         </is>
       </c>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-VC-12</t>
         </is>
       </c>
       <c r="G330" s="13" t="inlineStr"/>
@@ -13345,19 +13345,19 @@
           <t>TC-VC-18</t>
         </is>
       </c>
-      <c r="C331" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+      <c r="C331" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D331" s="16" t="inlineStr">
         <is>
-          <t>Periksa jumlah "dipakai" di kartu voucher</t>
+          <t>Pasang voucher lalu selesaikan pesanan</t>
         </is>
       </c>
       <c r="E331" s="16" t="inlineStr">
         <is>
-          <t>Cocok dengan jumlah pemakaian sebenarnya</t>
+          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
         </is>
       </c>
       <c r="F331" s="16" t="inlineStr">
@@ -13372,12 +13372,12 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B332" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-VC-19</t>
         </is>
       </c>
       <c r="C332" s="15" t="inlineStr">
@@ -13387,17 +13387,17 @@
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Ketuk Lepas setelah voucher terpasang</t>
         </is>
       </c>
       <c r="E332" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Tagihan kembali ke nominal semula</t>
         </is>
       </c>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G332" s="13" t="inlineStr"/>
@@ -13407,12 +13407,12 @@
     <row r="333">
       <c r="A333" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B333" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-VC-20</t>
         </is>
       </c>
       <c r="C333" s="18" t="inlineStr">
@@ -13422,17 +13422,17 @@
       </c>
       <c r="D333" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
         </is>
       </c>
       <c r="E333" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
         </is>
       </c>
       <c r="F333" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G333" s="16" t="inlineStr"/>
@@ -13442,12 +13442,12 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B334" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-VC-21</t>
         </is>
       </c>
       <c r="C334" s="15" t="inlineStr">
@@ -13457,17 +13457,17 @@
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Periksa Jurnal GL restonya</t>
         </is>
       </c>
       <c r="E334" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Ada baris masuk sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F334" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G334" s="13" t="inlineStr"/>
@@ -13477,32 +13477,32 @@
     <row r="335">
       <c r="A335" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B335" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
-        </is>
-      </c>
-      <c r="C335" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-22</t>
+        </is>
+      </c>
+      <c r="C335" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D335" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
         </is>
       </c>
       <c r="E335" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Tidak muncul di daftar pilihan</t>
         </is>
       </c>
       <c r="F335" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G335" s="16" t="inlineStr"/>
@@ -13512,12 +13512,12 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B336" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-VC-23</t>
         </is>
       </c>
       <c r="C336" s="15" t="inlineStr">
@@ -13527,17 +13527,17 @@
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
         </is>
       </c>
       <c r="E336" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Debit Voucher Redeem, kredit Total Saldo</t>
         </is>
       </c>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G336" s="13" t="inlineStr"/>
@@ -13547,12 +13547,12 @@
     <row r="337">
       <c r="A337" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B337" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-VC-24</t>
         </is>
       </c>
       <c r="C337" s="18" t="inlineStr">
@@ -13562,17 +13562,17 @@
       </c>
       <c r="D337" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
         </is>
       </c>
       <c r="E337" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
         </is>
       </c>
       <c r="F337" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G337" s="16" t="inlineStr"/>
@@ -13582,12 +13582,12 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B338" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-VC-25</t>
         </is>
       </c>
       <c r="C338" s="15" t="inlineStr">
@@ -13597,17 +13597,17 @@
       </c>
       <c r="D338" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Jalankan expire_vouchers() dua kali</t>
         </is>
       </c>
       <c r="E338" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
         </is>
       </c>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G338" s="13" t="inlineStr"/>
@@ -13617,12 +13617,12 @@
     <row r="339">
       <c r="A339" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B339" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
+          <t>TC-VC-26</t>
         </is>
       </c>
       <c r="C339" s="18" t="inlineStr">
@@ -13632,17 +13632,17 @@
       </c>
       <c r="D339" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Jumlahkan keempat tahap untuk satu batch</t>
         </is>
       </c>
       <c r="E339" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
         </is>
       </c>
       <c r="F339" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-VC-13, F-VC-14</t>
         </is>
       </c>
       <c r="G339" s="16" t="inlineStr"/>
@@ -13652,12 +13652,12 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B340" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-VC-27</t>
         </is>
       </c>
       <c r="C340" s="15" t="inlineStr">
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Tulis langsung ke voucher_claims lewat API</t>
         </is>
       </c>
       <c r="E340" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr"/>
@@ -13687,12 +13687,12 @@
     <row r="341">
       <c r="A341" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B341" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-VC-28</t>
         </is>
       </c>
       <c r="C341" s="18" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="D341" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
         </is>
       </c>
       <c r="E341" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
         </is>
       </c>
       <c r="F341" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G341" s="16" t="inlineStr"/>
@@ -13722,12 +13722,12 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B342" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
+          <t>TC-VC-29</t>
         </is>
       </c>
       <c r="C342" s="19" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Periksa kartu batch di layar Super Admin</t>
         </is>
       </c>
       <c r="E342" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
         </is>
       </c>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>F-VC-15</t>
         </is>
       </c>
       <c r="G342" s="13" t="inlineStr"/>
@@ -13757,12 +13757,12 @@
     <row r="343">
       <c r="A343" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B343" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
+          <t>TC-VC-30</t>
         </is>
       </c>
       <c r="C343" s="20" t="inlineStr">
@@ -13772,17 +13772,17 @@
       </c>
       <c r="D343" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Tutup sebuah batch yang kuotanya masih ada</t>
         </is>
       </c>
       <c r="E343" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F343" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>F-VC-04</t>
         </is>
       </c>
       <c r="G343" s="16" t="inlineStr"/>
@@ -13792,32 +13792,32 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B344" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C344" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-31</t>
+        </is>
+      </c>
+      <c r="C344" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D344" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
         </is>
       </c>
       <c r="E344" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G344" s="13" t="inlineStr"/>
@@ -13827,12 +13827,12 @@
     <row r="345">
       <c r="A345" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B345" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-VC-32</t>
         </is>
       </c>
       <c r="C345" s="18" t="inlineStr">
@@ -13842,17 +13842,17 @@
       </c>
       <c r="D345" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Jalankan settle-voucher-payouts</t>
         </is>
       </c>
       <c r="E345" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
         </is>
       </c>
       <c r="F345" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G345" s="16" t="inlineStr"/>
@@ -13862,12 +13862,12 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B346" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
+          <t>TC-VC-33</t>
         </is>
       </c>
       <c r="C346" s="15" t="inlineStr">
@@ -13877,17 +13877,17 @@
       </c>
       <c r="D346" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Jalankan fungsinya dua kali berturut-turut</t>
         </is>
       </c>
       <c r="E346" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
         </is>
       </c>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G346" s="13" t="inlineStr"/>
@@ -13897,12 +13897,12 @@
     <row r="347">
       <c r="A347" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B347" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-VC-34</t>
         </is>
       </c>
       <c r="C347" s="18" t="inlineStr">
@@ -13912,17 +13912,17 @@
       </c>
       <c r="D347" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
         </is>
       </c>
       <c r="E347" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
         </is>
       </c>
       <c r="F347" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G347" s="16" t="inlineStr"/>
@@ -13932,32 +13932,32 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B348" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C348" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-35</t>
+        </is>
+      </c>
+      <c r="C348" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D348" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Perbaiki kuncinya lalu jalankan lagi</t>
         </is>
       </c>
       <c r="E348" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Baris yang tadi gagal terkirim</t>
         </is>
       </c>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G348" s="13" t="inlineStr"/>
@@ -13967,32 +13967,32 @@
     <row r="349">
       <c r="A349" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B349" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C349" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-36</t>
+        </is>
+      </c>
+      <c r="C349" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D349" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Pakai voucher di resto yang belum punya sub-akun</t>
         </is>
       </c>
       <c r="E349" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
         </is>
       </c>
       <c r="F349" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G349" s="16" t="inlineStr"/>
@@ -14002,32 +14002,32 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B350" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C350" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-37</t>
+        </is>
+      </c>
+      <c r="C350" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D350" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Buat pesanan bervoucher saat Xendit mati total</t>
         </is>
       </c>
       <c r="E350" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
         </is>
       </c>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G350" s="13" t="inlineStr"/>
@@ -14037,32 +14037,32 @@
     <row r="351">
       <c r="A351" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B351" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
-        </is>
-      </c>
-      <c r="C351" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-38</t>
+        </is>
+      </c>
+      <c r="C351" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D351" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
         </is>
       </c>
       <c r="E351" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Klaim used lama ikut terantre</t>
         </is>
       </c>
       <c r="F351" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G351" s="16" t="inlineStr"/>
@@ -14072,12 +14072,12 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B352" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
+          <t>TC-VC-39</t>
         </is>
       </c>
       <c r="C352" s="15" t="inlineStr">
@@ -14087,17 +14087,17 @@
       </c>
       <c r="D352" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Tulis langsung ke voucher_payouts lewat API</t>
         </is>
       </c>
       <c r="E352" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G352" s="13" t="inlineStr"/>
@@ -14107,32 +14107,32 @@
     <row r="353">
       <c r="A353" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B353" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
-        </is>
-      </c>
-      <c r="C353" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-40</t>
+        </is>
+      </c>
+      <c r="C353" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D353" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Baca voucher_payout_config sebagai Super Admin</t>
         </is>
       </c>
       <c r="E353" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
         </is>
       </c>
       <c r="F353" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G353" s="16" t="inlineStr"/>
@@ -14142,32 +14142,32 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B354" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
-        </is>
-      </c>
-      <c r="C354" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-41</t>
+        </is>
+      </c>
+      <c r="C354" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D354" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Jalankan penjadwal sebelum function_url diisi</t>
         </is>
       </c>
       <c r="E354" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
         </is>
       </c>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G354" s="13" t="inlineStr"/>
@@ -14177,12 +14177,12 @@
     <row r="355">
       <c r="A355" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B355" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-VC-42</t>
         </is>
       </c>
       <c r="C355" s="18" t="inlineStr">
@@ -14192,17 +14192,17 @@
       </c>
       <c r="D355" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
         </is>
       </c>
       <c r="E355" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Cocok baris per baris lewat transfer_id</t>
         </is>
       </c>
       <c r="F355" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G355" s="16" t="inlineStr"/>
@@ -14212,12 +14212,12 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B356" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-VC-43</t>
         </is>
       </c>
       <c r="C356" s="15" t="inlineStr">
@@ -14227,17 +14227,17 @@
       </c>
       <c r="D356" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Jalankan pencairan saat xenPlatform belum aktif</t>
         </is>
       </c>
       <c r="E356" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Seluruh antrean tetap pending, attempts nol, tidak ada galat</t>
         </is>
       </c>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G356" s="13" t="inlineStr"/>
@@ -14247,12 +14247,12 @@
     <row r="357">
       <c r="A357" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B357" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
+          <t>TC-VC-44</t>
         </is>
       </c>
       <c r="C357" s="20" t="inlineStr">
@@ -14262,17 +14262,17 @@
       </c>
       <c r="D357" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Aktifkan xenPlatform + pasang sub-akun, lalu tunggu penjadwal</t>
         </is>
       </c>
       <c r="E357" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Tunggakan lama ikut terangkut tanpa dijalankan ulang manual</t>
         </is>
       </c>
       <c r="F357" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>F-VC-16, F-VC-17</t>
         </is>
       </c>
       <c r="G357" s="16" t="inlineStr"/>
@@ -14282,32 +14282,32 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B358" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C358" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-01</t>
+        </is>
+      </c>
+      <c r="C358" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D358" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E358" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G358" s="13" t="inlineStr"/>
@@ -14317,32 +14317,32 @@
     <row r="359">
       <c r="A359" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B359" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
-        </is>
-      </c>
-      <c r="C359" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-02</t>
+        </is>
+      </c>
+      <c r="C359" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D359" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E359" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F359" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G359" s="16" t="inlineStr"/>
@@ -14352,32 +14352,32 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B360" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
-        </is>
-      </c>
-      <c r="C360" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-03</t>
+        </is>
+      </c>
+      <c r="C360" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D360" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E360" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G360" s="13" t="inlineStr"/>
@@ -14387,32 +14387,32 @@
     <row r="361">
       <c r="A361" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B361" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
-        </is>
-      </c>
-      <c r="C361" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-04</t>
+        </is>
+      </c>
+      <c r="C361" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D361" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E361" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F361" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G361" s="16" t="inlineStr"/>
@@ -14422,32 +14422,32 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B362" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
-        </is>
-      </c>
-      <c r="C362" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-05</t>
+        </is>
+      </c>
+      <c r="C362" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D362" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E362" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G362" s="13" t="inlineStr"/>
@@ -14457,12 +14457,12 @@
     <row r="363">
       <c r="A363" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B363" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C363" s="18" t="inlineStr">
@@ -14472,17 +14472,17 @@
       </c>
       <c r="D363" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E363" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F363" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G363" s="16" t="inlineStr"/>
@@ -14492,32 +14492,32 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B364" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
-        </is>
-      </c>
-      <c r="C364" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-07</t>
+        </is>
+      </c>
+      <c r="C364" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D364" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E364" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G364" s="13" t="inlineStr"/>
@@ -14527,25 +14527,935 @@
     <row r="365">
       <c r="A365" s="16" t="inlineStr">
         <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B365" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C365" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D365" s="16" t="inlineStr">
+        <is>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+        </is>
+      </c>
+      <c r="E365" s="16" t="inlineStr">
+        <is>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+        </is>
+      </c>
+      <c r="F365" s="16" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G365" s="16" t="inlineStr"/>
+      <c r="H365" s="16" t="inlineStr"/>
+      <c r="I365" s="16" t="inlineStr"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B366" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C366" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D366" s="13" t="inlineStr">
+        <is>
+          <t>Buat resto baru dari Super Admin</t>
+        </is>
+      </c>
+      <c r="E366" s="13" t="inlineStr">
+        <is>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+        </is>
+      </c>
+      <c r="F366" s="13" t="inlineStr">
+        <is>
+          <t>A-19, TSD §6.2</t>
+        </is>
+      </c>
+      <c r="G366" s="13" t="inlineStr"/>
+      <c r="H366" s="13" t="inlineStr"/>
+      <c r="I366" s="13" t="inlineStr"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B367" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C367" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D367" s="16" t="inlineStr">
+        <is>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+        </is>
+      </c>
+      <c r="E367" s="16" t="inlineStr">
+        <is>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+        </is>
+      </c>
+      <c r="F367" s="16" t="inlineStr">
+        <is>
+          <t>TSD §6.2</t>
+        </is>
+      </c>
+      <c r="G367" s="16" t="inlineStr"/>
+      <c r="H367" s="16" t="inlineStr"/>
+      <c r="I367" s="16" t="inlineStr"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B368" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-11</t>
+        </is>
+      </c>
+      <c r="C368" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D368" s="13" t="inlineStr">
+        <is>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+        </is>
+      </c>
+      <c r="E368" s="13" t="inlineStr">
+        <is>
+          <t>Baris masuk, lalu sent_at terisi</t>
+        </is>
+      </c>
+      <c r="F368" s="13" t="inlineStr">
+        <is>
+          <t>TSD §8</t>
+        </is>
+      </c>
+      <c r="G368" s="13" t="inlineStr"/>
+      <c r="H368" s="13" t="inlineStr"/>
+      <c r="I368" s="13" t="inlineStr"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B369" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C369" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D369" s="16" t="inlineStr">
+        <is>
+          <t>Matikan sambungan, pakai aplikasi</t>
+        </is>
+      </c>
+      <c r="E369" s="16" t="inlineStr">
+        <is>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+        </is>
+      </c>
+      <c r="F369" s="16" t="inlineStr">
+        <is>
+          <t>TSD §10, FSD §5.6</t>
+        </is>
+      </c>
+      <c r="G369" s="16" t="inlineStr"/>
+      <c r="H369" s="16" t="inlineStr"/>
+      <c r="I369" s="16" t="inlineStr"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B370" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-13</t>
+        </is>
+      </c>
+      <c r="C370" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D370" s="13" t="inlineStr">
+        <is>
+          <t>Sambungkan lagi</t>
+        </is>
+      </c>
+      <c r="E370" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
+        </is>
+      </c>
+      <c r="F370" s="13" t="inlineStr">
+        <is>
+          <t>TSD §10</t>
+        </is>
+      </c>
+      <c r="G370" s="13" t="inlineStr"/>
+      <c r="H370" s="13" t="inlineStr"/>
+      <c r="I370" s="13" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B371" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-14</t>
+        </is>
+      </c>
+      <c r="C371" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D371" s="16" t="inlineStr">
+        <is>
+          <t>Coba bayar QRIS saat luring</t>
+        </is>
+      </c>
+      <c r="E371" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+        </is>
+      </c>
+      <c r="F371" s="16" t="inlineStr">
+        <is>
+          <t>FSD §5.6</t>
+        </is>
+      </c>
+      <c r="G371" s="16" t="inlineStr"/>
+      <c r="H371" s="16" t="inlineStr"/>
+      <c r="I371" s="16" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B372" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C372" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D372" s="13" t="inlineStr">
+        <is>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+        </is>
+      </c>
+      <c r="E372" s="13" t="inlineStr">
+        <is>
+          <t>Nominal yang dipakai tetap dari basis data</t>
+        </is>
+      </c>
+      <c r="F372" s="13" t="inlineStr">
+        <is>
+          <t>TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G372" s="13" t="inlineStr"/>
+      <c r="H372" s="13" t="inlineStr"/>
+      <c r="I372" s="13" t="inlineStr"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B373" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-16</t>
+        </is>
+      </c>
+      <c r="C373" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D373" s="16" t="inlineStr">
+        <is>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+        </is>
+      </c>
+      <c r="E373" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak</t>
+        </is>
+      </c>
+      <c r="F373" s="16" t="inlineStr">
+        <is>
+          <t>F-PG-02, TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G373" s="16" t="inlineStr"/>
+      <c r="H373" s="16" t="inlineStr"/>
+      <c r="I373" s="16" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B374" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C374" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D374" s="13" t="inlineStr">
+        <is>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+        </is>
+      </c>
+      <c r="E374" s="13" t="inlineStr">
+        <is>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+        </is>
+      </c>
+      <c r="F374" s="13" t="inlineStr">
+        <is>
+          <t>TSD §1.2</t>
+        </is>
+      </c>
+      <c r="G374" s="13" t="inlineStr"/>
+      <c r="H374" s="13" t="inlineStr"/>
+      <c r="I374" s="13" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B375" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C375" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D375" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+        </is>
+      </c>
+      <c r="E375" s="16" t="inlineStr">
+        <is>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+        </is>
+      </c>
+      <c r="F375" s="16" t="inlineStr">
+        <is>
+          <t>TSD §6.5</t>
+        </is>
+      </c>
+      <c r="G375" s="16" t="inlineStr"/>
+      <c r="H375" s="16" t="inlineStr"/>
+      <c r="I375" s="16" t="inlineStr"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B376" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C376" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D376" s="13" t="inlineStr">
+        <is>
+          <t>Hapus resto uji</t>
+        </is>
+      </c>
+      <c r="E376" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+        </is>
+      </c>
+      <c r="F376" s="13" t="inlineStr">
+        <is>
+          <t>TSD §4.0</t>
+        </is>
+      </c>
+      <c r="G376" s="13" t="inlineStr"/>
+      <c r="H376" s="13" t="inlineStr"/>
+      <c r="I376" s="13" t="inlineStr"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B377" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C377" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D377" s="16" t="inlineStr">
+        <is>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+        </is>
+      </c>
+      <c r="E377" s="16" t="inlineStr">
+        <is>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+        </is>
+      </c>
+      <c r="F377" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-09</t>
+        </is>
+      </c>
+      <c r="G377" s="16" t="inlineStr"/>
+      <c r="H377" s="16" t="inlineStr"/>
+      <c r="I377" s="16" t="inlineStr"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B378" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C378" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D378" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="E378" s="13" t="inlineStr">
+        <is>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="F378" s="13" t="inlineStr">
+        <is>
+          <t>F-PP-09, A-13</t>
+        </is>
+      </c>
+      <c r="G378" s="13" t="inlineStr"/>
+      <c r="H378" s="13" t="inlineStr"/>
+      <c r="I378" s="13" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B379" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C379" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D379" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+        </is>
+      </c>
+      <c r="E379" s="16" t="inlineStr">
+        <is>
+          <t>Tidak muncul sama sekali</t>
+        </is>
+      </c>
+      <c r="F379" s="16" t="inlineStr">
+        <is>
+          <t>A-17</t>
+        </is>
+      </c>
+      <c r="G379" s="16" t="inlineStr"/>
+      <c r="H379" s="16" t="inlineStr"/>
+      <c r="I379" s="16" t="inlineStr"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B380" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C380" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D380" s="13" t="inlineStr">
+        <is>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+        </is>
+      </c>
+      <c r="E380" s="13" t="inlineStr">
+        <is>
+          <t>Nominalnya sama dengan yang diajukan</t>
+        </is>
+      </c>
+      <c r="F380" s="13" t="inlineStr">
+        <is>
+          <t>F-FN-03</t>
+        </is>
+      </c>
+      <c r="G380" s="13" t="inlineStr"/>
+      <c r="H380" s="13" t="inlineStr"/>
+      <c r="I380" s="13" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B381" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C381" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D381" s="16" t="inlineStr">
+        <is>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+        </is>
+      </c>
+      <c r="E381" s="16" t="inlineStr">
+        <is>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
+        </is>
+      </c>
+      <c r="F381" s="16" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="G381" s="16" t="inlineStr"/>
+      <c r="H381" s="16" t="inlineStr"/>
+      <c r="I381" s="16" t="inlineStr"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B382" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C382" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D382" s="13" t="inlineStr">
+        <is>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+        </is>
+      </c>
+      <c r="E382" s="13" t="inlineStr">
+        <is>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+        </is>
+      </c>
+      <c r="F382" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-10, F-DS-12</t>
+        </is>
+      </c>
+      <c r="G382" s="13" t="inlineStr"/>
+      <c r="H382" s="13" t="inlineStr"/>
+      <c r="I382" s="13" t="inlineStr"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B383" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C383" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D383" s="16" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E383" s="16" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F383" s="16" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G383" s="16" t="inlineStr"/>
+      <c r="H383" s="16" t="inlineStr"/>
+      <c r="I383" s="16" t="inlineStr"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B384" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C384" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D384" s="13" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E384" s="13" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F384" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G384" s="13" t="inlineStr"/>
+      <c r="H384" s="13" t="inlineStr"/>
+      <c r="I384" s="13" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B385" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C385" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D385" s="16" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E385" s="16" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F385" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G385" s="16" t="inlineStr"/>
+      <c r="H385" s="16" t="inlineStr"/>
+      <c r="I385" s="16" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B386" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C386" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D386" s="13" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E386" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F386" s="13" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G386" s="13" t="inlineStr"/>
+      <c r="H386" s="13" t="inlineStr"/>
+      <c r="I386" s="13" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B387" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C387" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D387" s="16" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E387" s="16" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F387" s="16" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G387" s="16" t="inlineStr"/>
+      <c r="H387" s="16" t="inlineStr"/>
+      <c r="I387" s="16" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B388" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C388" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D388" s="13" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E388" s="13" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F388" s="13" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G388" s="13" t="inlineStr"/>
+      <c r="H388" s="13" t="inlineStr"/>
+      <c r="I388" s="13" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B389" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C389" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D389" s="16" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E389" s="16" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F389" s="16" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G389" s="16" t="inlineStr"/>
+      <c r="H389" s="16" t="inlineStr"/>
+      <c r="I389" s="16" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B390" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C390" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D390" s="13" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E390" s="13" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F390" s="13" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G390" s="13" t="inlineStr"/>
+      <c r="H390" s="13" t="inlineStr"/>
+      <c r="I390" s="13" t="inlineStr"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="16" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B365" s="17" t="inlineStr">
+      <c r="B391" s="17" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C365" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D365" s="16" t="inlineStr">
+      <c r="C391" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D391" s="16" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E365" s="16" t="inlineStr">
+      <c r="E391" s="16" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -14559,37 +15469,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F365" s="16" t="inlineStr">
+      <c r="F391" s="16" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G365" s="16" t="inlineStr"/>
-      <c r="H365" s="16" t="inlineStr"/>
-      <c r="I365" s="16" t="inlineStr"/>
-    </row>
-    <row r="366">
-      <c r="A366" s="13" t="inlineStr">
+      <c r="G391" s="16" t="inlineStr"/>
+      <c r="H391" s="16" t="inlineStr"/>
+      <c r="I391" s="16" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B366" s="14" t="inlineStr">
+      <c r="B392" s="14" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C366" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D366" s="13" t="inlineStr">
+      <c r="C392" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D392" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E366" s="13" t="inlineStr">
+      <c r="E392" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -14601,37 +15511,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F366" s="13" t="inlineStr">
+      <c r="F392" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G366" s="13" t="inlineStr"/>
-      <c r="H366" s="13" t="inlineStr"/>
-      <c r="I366" s="13" t="inlineStr"/>
-    </row>
-    <row r="367">
-      <c r="A367" s="16" t="inlineStr">
+      <c r="G392" s="13" t="inlineStr"/>
+      <c r="H392" s="13" t="inlineStr"/>
+      <c r="I392" s="13" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B367" s="17" t="inlineStr">
+      <c r="B393" s="17" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C367" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D367" s="16" t="inlineStr">
+      <c r="C393" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D393" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E367" s="16" t="inlineStr">
+      <c r="E393" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -14643,74 +15553,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F367" s="16" t="inlineStr">
+      <c r="F393" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G367" s="16" t="inlineStr"/>
-      <c r="H367" s="16" t="inlineStr"/>
-      <c r="I367" s="16" t="inlineStr"/>
-    </row>
-    <row r="368">
-      <c r="A368" s="13" t="inlineStr">
+      <c r="G393" s="16" t="inlineStr"/>
+      <c r="H393" s="16" t="inlineStr"/>
+      <c r="I393" s="16" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B368" s="14" t="inlineStr">
+      <c r="B394" s="14" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C368" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D368" s="13" t="inlineStr">
+      <c r="C394" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D394" s="13" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E368" s="13" t="inlineStr">
+      <c r="E394" s="13" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F368" s="13" t="inlineStr">
+      <c r="F394" s="13" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G368" s="13" t="inlineStr"/>
-      <c r="H368" s="13" t="inlineStr"/>
-      <c r="I368" s="13" t="inlineStr"/>
-    </row>
-    <row r="369">
-      <c r="A369" s="16" t="inlineStr">
+      <c r="G394" s="13" t="inlineStr"/>
+      <c r="H394" s="13" t="inlineStr"/>
+      <c r="I394" s="13" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B369" s="17" t="inlineStr">
+      <c r="B395" s="17" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C369" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D369" s="16" t="inlineStr">
+      <c r="C395" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D395" s="16" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E369" s="16" t="inlineStr">
+      <c r="E395" s="16" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -14721,73 +15631,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F369" s="16" t="inlineStr">
+      <c r="F395" s="16" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G369" s="16" t="inlineStr"/>
-      <c r="H369" s="16" t="inlineStr"/>
-      <c r="I369" s="16" t="inlineStr"/>
-    </row>
-    <row r="370">
-      <c r="A370" s="13" t="inlineStr">
+      <c r="G395" s="16" t="inlineStr"/>
+      <c r="H395" s="16" t="inlineStr"/>
+      <c r="I395" s="16" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B370" s="14" t="inlineStr">
+      <c r="B396" s="14" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C370" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D370" s="13" t="inlineStr">
+      <c r="C396" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D396" s="13" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E370" s="13" t="inlineStr">
+      <c r="E396" s="13" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F370" s="13" t="inlineStr">
+      <c r="F396" s="13" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G370" s="13" t="inlineStr"/>
-      <c r="H370" s="13" t="inlineStr"/>
-      <c r="I370" s="13" t="inlineStr"/>
-    </row>
-    <row r="371">
-      <c r="A371" s="16" t="inlineStr">
+      <c r="G396" s="13" t="inlineStr"/>
+      <c r="H396" s="13" t="inlineStr"/>
+      <c r="I396" s="13" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B371" s="17" t="inlineStr">
+      <c r="B397" s="17" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C371" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D371" s="16" t="inlineStr">
+      <c r="C397" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D397" s="16" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E371" s="16" t="inlineStr">
+      <c r="E397" s="16" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -14798,37 +15708,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F371" s="16" t="inlineStr">
+      <c r="F397" s="16" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G371" s="16" t="inlineStr"/>
-      <c r="H371" s="16" t="inlineStr"/>
-      <c r="I371" s="16" t="inlineStr"/>
-    </row>
-    <row r="372">
-      <c r="A372" s="13" t="inlineStr">
+      <c r="G397" s="16" t="inlineStr"/>
+      <c r="H397" s="16" t="inlineStr"/>
+      <c r="I397" s="16" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B372" s="14" t="inlineStr">
+      <c r="B398" s="14" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C372" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D372" s="13" t="inlineStr">
+      <c r="C398" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D398" s="13" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E372" s="13" t="inlineStr">
+      <c r="E398" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -14838,37 +15748,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F372" s="13" t="inlineStr">
+      <c r="F398" s="13" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G372" s="13" t="inlineStr"/>
-      <c r="H372" s="13" t="inlineStr"/>
-      <c r="I372" s="13" t="inlineStr"/>
-    </row>
-    <row r="373">
-      <c r="A373" s="16" t="inlineStr">
+      <c r="G398" s="13" t="inlineStr"/>
+      <c r="H398" s="13" t="inlineStr"/>
+      <c r="I398" s="13" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B373" s="17" t="inlineStr">
+      <c r="B399" s="17" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C373" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D373" s="16" t="inlineStr">
+      <c r="C399" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D399" s="16" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E373" s="16" t="inlineStr">
+      <c r="E399" s="16" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -14876,19 +15786,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F373" s="16" t="inlineStr">
+      <c r="F399" s="16" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G373" s="16" t="inlineStr"/>
-      <c r="H373" s="16" t="inlineStr"/>
-      <c r="I373" s="16" t="inlineStr"/>
+      <c r="G399" s="16" t="inlineStr"/>
+      <c r="H399" s="16" t="inlineStr"/>
+      <c r="I399" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I373"/>
+  <autoFilter ref="A1:I399"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G373" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G399" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$399</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$453</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C399,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C453,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P1",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P1",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P1",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P1",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P1",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P1",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P1",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P1",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C399,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C453,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P2",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P2",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P2",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P2",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P2",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P2",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P2",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P2",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C399,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C453,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P3",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P3",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P3",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P3",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P3",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P3",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C399,"P3",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C453,"P3",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pelanggan",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pelanggan",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pelanggan",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pelanggan",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pelanggan",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pelanggan",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pelanggan",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pelanggan",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kasir",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kasir",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kasir",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kasir",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kasir",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kasir",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kasir",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kasir",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pending Payment",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pending Payment",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pending Payment",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pending Payment",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pending Payment",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pending Payment",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pending Payment",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pending Payment",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Dapur",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Dapur",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Dapur",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Dapur",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Dapur",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Dapur",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Dapur",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Dapur",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Keuangan",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Keuangan",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Keuangan",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Keuangan",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Keuangan",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Keuangan",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Keuangan",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Keuangan",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Setor Saldo Cash",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Setor Saldo Cash",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Setor Saldo Cash",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Setor Saldo Cash",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Setor Saldo Cash",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Setor Saldo Cash",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Setor Saldo Cash",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Setor Saldo Cash",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"QR Meja",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"QR Meja",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"QR Meja",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"QR Meja",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"QR Meja",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"QR Meja",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"QR Meja",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"QR Meja",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Diskon",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Diskon",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Diskon",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Diskon",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Diskon",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Diskon",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Diskon",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Diskon",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembayaran QRIS",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembayaran QRIS",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembayaran QRIS",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembayaran QRIS",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembayaran QRIS",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembayaran QRIS",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembayaran QRIS",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembayaran QRIS",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Tampilan",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Tampilan",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Tampilan",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Tampilan",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Tampilan",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Tampilan",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Tampilan",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Tampilan",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Super Admin",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Super Admin",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Super Admin",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Super Admin",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Super Admin",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Super Admin",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Super Admin",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Super Admin",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembaruan Aplikasi",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembaruan Aplikasi",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembaruan Aplikasi",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembaruan Aplikasi",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembaruan Aplikasi",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembaruan Aplikasi",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Pembaruan Aplikasi",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembaruan Aplikasi",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1444,27 +1444,27 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1475,27 +1475,27 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1506,27 +1506,27 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Uji Ujung-ke-Ujung</t>
+          <t>Regresi — bug yang pernah terjadi</t>
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G399,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G453,"Lulus")</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G399,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G453,"Gagal")</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G399,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G453,"Terblokir")</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A399,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G399,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G453,"Dilewati")</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -1534,214 +1534,245 @@
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Uji Ujung-ke-Ujung</t>
+        </is>
+      </c>
+      <c r="B34" s="5">
+        <f>COUNTIF('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung")</f>
+        <v/>
+      </c>
+      <c r="C34" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <v/>
+      </c>
+      <c r="D34" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <v/>
+      </c>
+      <c r="E34" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <v/>
+      </c>
+      <c r="F34" s="5">
+        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <v/>
+      </c>
+      <c r="G34" s="5">
+        <f>B34-SUM(C34:F34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Rilis ditahan selama masih ada P1 yang Gagal.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>Temuan</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Severity</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Jumlah</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>Baru</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Dikonfirmasi</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>Sedang diperbaiki</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Menunggu retest</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Ditutup</t>
         </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Blocker</t>
-        </is>
-      </c>
-      <c r="B39" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Blocker")</f>
-        <v/>
-      </c>
-      <c r="C39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Baru")</f>
-        <v/>
-      </c>
-      <c r="D39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Dikonfirmasi")</f>
-        <v/>
-      </c>
-      <c r="E39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Sedang diperbaiki")</f>
-        <v/>
-      </c>
-      <c r="F39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Menunggu retest")</f>
-        <v/>
-      </c>
-      <c r="G39" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Ditutup")</f>
-        <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Major</t>
+          <t>Blocker</t>
         </is>
       </c>
       <c r="B40" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Major")</f>
+        <f>COUNTIF(Defect!M5:M64,"Blocker")</f>
         <v/>
       </c>
       <c r="C40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Baru")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
       <c r="D40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Dikonfirmasi")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
       <c r="E40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
       <c r="F40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Menunggu retest")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
       <c r="G40" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Ditutup")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Blocker",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Minor</t>
+          <t>Major</t>
         </is>
       </c>
       <c r="B41" s="5">
-        <f>COUNTIF(Defect!M5:M64,"Minor")</f>
+        <f>COUNTIF(Defect!M5:M64,"Major")</f>
         <v/>
       </c>
       <c r="C41" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Baru")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
       <c r="D41" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Dikonfirmasi")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
       <c r="E41" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
       <c r="F41" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Menunggu retest")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
       <c r="G41" s="5">
-        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Ditutup")</f>
+        <f>COUNTIFS(Defect!M5:M64,"Major",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="B42" s="5">
+        <f>COUNTIF(Defect!M5:M64,"Minor")</f>
+        <v/>
+      </c>
+      <c r="C42" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Baru")</f>
+        <v/>
+      </c>
+      <c r="D42" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Dikonfirmasi")</f>
+        <v/>
+      </c>
+      <c r="E42" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Sedang diperbaiki")</f>
+        <v/>
+      </c>
+      <c r="F42" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Menunggu retest")</f>
+        <v/>
+      </c>
+      <c r="G42" s="5">
+        <f>COUNTIFS(Defect!M5:M64,"Minor",Defect!P5:P64,"Ditutup")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
           <t>Trivial</t>
         </is>
       </c>
-      <c r="B42" s="5">
+      <c r="B43" s="5">
         <f>COUNTIF(Defect!M5:M64,"Trivial")</f>
         <v/>
       </c>
-      <c r="C42" s="5">
+      <c r="C43" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Baru")</f>
         <v/>
       </c>
-      <c r="D42" s="5">
+      <c r="D43" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Dikonfirmasi")</f>
         <v/>
       </c>
-      <c r="E42" s="5">
+      <c r="E43" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Sedang diperbaiki")</f>
         <v/>
       </c>
-      <c r="F42" s="5">
+      <c r="F43" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Menunggu retest")</f>
         <v/>
       </c>
-      <c r="G42" s="5">
+      <c r="G43" s="5">
         <f>COUNTIFS(Defect!M5:M64,"Trivial",Defect!P5:P64,"Ditutup")</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B43" s="7">
-        <f>SUM(B39:B42)</f>
-        <v/>
-      </c>
-      <c r="C43" s="7">
-        <f>SUM(C39:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="7">
-        <f>SUM(D39:D42)</f>
-        <v/>
-      </c>
-      <c r="E43" s="7">
-        <f>SUM(E39:E42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="7">
-        <f>SUM(F39:F42)</f>
-        <v/>
-      </c>
-      <c r="G43" s="7">
-        <f>SUM(G39:G42)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="B44" s="7">
+        <f>SUM(B40:B43)</f>
+        <v/>
+      </c>
+      <c r="C44" s="7">
+        <f>SUM(C40:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="7">
+        <f>SUM(D40:D43)</f>
+        <v/>
+      </c>
+      <c r="E44" s="7">
+        <f>SUM(E40:E43)</f>
+        <v/>
+      </c>
+      <c r="F44" s="7">
+        <f>SUM(F40:F43)</f>
+        <v/>
+      </c>
+      <c r="G44" s="7">
+        <f>SUM(G40:G43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Blocker yang belum Ditutup menahan rilis.</t>
         </is>
@@ -1758,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I399"/>
+  <dimension ref="A1:I453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11172,7 +11203,7 @@
       </c>
       <c r="B269" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-15</t>
+          <t>TC-BL-31</t>
         </is>
       </c>
       <c r="C269" s="18" t="inlineStr">
@@ -11182,17 +11213,17 @@
       </c>
       <c r="D269" s="16" t="inlineStr">
         <is>
-          <t>Coba kirim bukti tanpa melampirkan foto</t>
+          <t>Set tanggal tagih 31, lihat jatuh tempo di April</t>
         </is>
       </c>
       <c r="E269" s="16" t="inlineStr">
         <is>
-          <t>Tombol Kirim mati</t>
+          <t>30 April</t>
         </is>
       </c>
       <c r="F269" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G269" s="16" t="inlineStr"/>
@@ -11207,7 +11238,7 @@
       </c>
       <c r="B270" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-16</t>
+          <t>TC-BL-32</t>
         </is>
       </c>
       <c r="C270" s="15" t="inlineStr">
@@ -11217,17 +11248,17 @@
       </c>
       <c r="D270" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → tab Tagihan → Terima</t>
+          <t>Set tanggal tagih 31, lihat jatuh tempo di Februari 2026</t>
         </is>
       </c>
       <c r="E270" s="13" t="inlineStr">
         <is>
-          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
+          <t>28 Februari</t>
         </is>
       </c>
       <c r="F270" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G270" s="13" t="inlineStr"/>
@@ -11242,7 +11273,7 @@
       </c>
       <c r="B271" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-17</t>
+          <t>TC-BL-33</t>
         </is>
       </c>
       <c r="C271" s="18" t="inlineStr">
@@ -11252,17 +11283,17 @@
       </c>
       <c r="D271" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Tolak tanpa mengisi alasan</t>
+          <t>Set tanggal tagih 31, lihat jatuh tempo di Februari 2028</t>
         </is>
       </c>
       <c r="E271" s="16" t="inlineStr">
         <is>
-          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
+          <t>29 Februari — tahun kabisat</t>
         </is>
       </c>
       <c r="F271" s="16" t="inlineStr">
         <is>
-          <t>F-BL-14</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G271" s="16" t="inlineStr"/>
@@ -11277,7 +11308,7 @@
       </c>
       <c r="B272" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-18</t>
+          <t>TC-BL-34</t>
         </is>
       </c>
       <c r="C272" s="15" t="inlineStr">
@@ -11287,17 +11318,17 @@
       </c>
       <c r="D272" s="13" t="inlineStr">
         <is>
-          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
+          <t>Set tanggal tagih 29, Februari 2026</t>
         </is>
       </c>
       <c r="E272" s="13" t="inlineStr">
         <is>
-          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
+          <t>28 Februari, bukan gagal terbit</t>
         </is>
       </c>
       <c r="F272" s="13" t="inlineStr">
         <is>
-          <t>F-BL-14, F-BL-15</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G272" s="13" t="inlineStr"/>
@@ -11312,27 +11343,27 @@
       </c>
       <c r="B273" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-19</t>
-        </is>
-      </c>
-      <c r="C273" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-35</t>
+        </is>
+      </c>
+      <c r="C273" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D273" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Super Admin saat ada resto terkunci</t>
+          <t>Buka dropdown Tanggal Tagihan di Super Admin</t>
         </is>
       </c>
       <c r="E273" s="16" t="inlineStr">
         <is>
-          <t>Tidak terkunci sama sekali</t>
+          <t>Tersedia sampai 31; di atas 28 diberi keterangan akhir bulan</t>
         </is>
       </c>
       <c r="F273" s="16" t="inlineStr">
         <is>
-          <t>F-BL-17</t>
+          <t>F-BL-19</t>
         </is>
       </c>
       <c r="G273" s="16" t="inlineStr"/>
@@ -11347,7 +11378,7 @@
       </c>
       <c r="B274" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-20</t>
+          <t>TC-BL-36</t>
         </is>
       </c>
       <c r="C274" s="15" t="inlineStr">
@@ -11357,17 +11388,17 @@
       </c>
       <c r="D274" s="13" t="inlineStr">
         <is>
-          <t>Sebagai resto terkunci, coba ubah harga produk</t>
+          <t>Lunasi tagihan 18 Agustus, lihat kartu paket</t>
         </is>
       </c>
       <c r="E274" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — katalog ikut dibekukan</t>
+          <t>Menyebut tagihan berikutnya 18 September</t>
         </is>
       </c>
       <c r="F274" s="13" t="inlineStr">
         <is>
-          <t>F-BL-18</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G274" s="13" t="inlineStr"/>
@@ -11382,7 +11413,7 @@
       </c>
       <c r="B275" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-21</t>
+          <t>TC-BL-37</t>
         </is>
       </c>
       <c r="C275" s="18" t="inlineStr">
@@ -11392,17 +11423,17 @@
       </c>
       <c r="D275" s="16" t="inlineStr">
         <is>
-          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
+          <t>Ada tagihan belum lunas, lihat kartu paket</t>
         </is>
       </c>
       <c r="E275" s="16" t="inlineStr">
         <is>
-          <t>Resto B tidak terpengaruh</t>
+          <t>Menyebut "setelah tagihan berjalan lunas" lebih dulu</t>
         </is>
       </c>
       <c r="F275" s="16" t="inlineStr">
         <is>
-          <t>F-BL-15, A-10</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G275" s="16" t="inlineStr"/>
@@ -11417,27 +11448,27 @@
       </c>
       <c r="B276" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-22</t>
-        </is>
-      </c>
-      <c r="C276" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-38</t>
+        </is>
+      </c>
+      <c r="C276" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D276" s="13" t="inlineStr">
         <is>
-          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
+          <t>Resto gratis (harga 0)</t>
         </is>
       </c>
       <c r="E276" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — hanya Super Admin</t>
+          <t>Tidak menampilkan tanggal berikutnya</t>
         </is>
       </c>
       <c r="F276" s="13" t="inlineStr">
         <is>
-          <t>F-BL-13</t>
+          <t>F-BL-20</t>
         </is>
       </c>
       <c r="G276" s="13" t="inlineStr"/>
@@ -11452,7 +11483,7 @@
       </c>
       <c r="B277" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-23</t>
+          <t>TC-BL-39</t>
         </is>
       </c>
       <c r="C277" s="18" t="inlineStr">
@@ -11462,17 +11493,17 @@
       </c>
       <c r="D277" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
+          <t>Lihat tagihan yang sudah lunas</t>
         </is>
       </c>
       <c r="E277" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Nomor Virtual Account tidak tampil</t>
         </is>
       </c>
       <c r="F277" s="16" t="inlineStr">
         <is>
-          <t>F-BL-13, TSD §7.3</t>
+          <t>F-BL-21</t>
         </is>
       </c>
       <c r="G277" s="16" t="inlineStr"/>
@@ -11487,27 +11518,27 @@
       </c>
       <c r="B278" s="14" t="inlineStr">
         <is>
-          <t>TC-BL-24</t>
-        </is>
-      </c>
-      <c r="C278" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-40</t>
+        </is>
+      </c>
+      <c r="C278" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D278" s="13" t="inlineStr">
         <is>
-          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
+          <t>Lihat tagihan yang menunggu verifikasi</t>
         </is>
       </c>
       <c r="E278" s="13" t="inlineStr">
         <is>
-          <t>Tidak terkunci karena gagal memeriksa</t>
+          <t>VA masih tampil</t>
         </is>
       </c>
       <c r="F278" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.3</t>
+          <t>F-BL-21</t>
         </is>
       </c>
       <c r="G278" s="13" t="inlineStr"/>
@@ -11522,27 +11553,27 @@
       </c>
       <c r="B279" s="17" t="inlineStr">
         <is>
-          <t>TC-BL-25</t>
-        </is>
-      </c>
-      <c r="C279" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-41</t>
+        </is>
+      </c>
+      <c r="C279" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D279" s="16" t="inlineStr">
         <is>
-          <t>Owner → Tagihan Langganan</t>
+          <t>Ketuk Unduh Invoice PDF pada tagihan lunas</t>
         </is>
       </c>
       <c r="E279" s="16" t="inlineStr">
         <is>
-          <t>Terbuka, memuat paket dan riwayat tagihan</t>
+          <t>PDF terbuka, bertanda LUNAS, tanpa nomor VA</t>
         </is>
       </c>
       <c r="F279" s="16" t="inlineStr">
         <is>
-          <t>F-BL-11</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G279" s="16" t="inlineStr"/>
@@ -11552,12 +11583,12 @@
     <row r="280">
       <c r="A280" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B280" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-01</t>
+          <t>TC-BL-42</t>
         </is>
       </c>
       <c r="C280" s="15" t="inlineStr">
@@ -11567,17 +11598,17 @@
       </c>
       <c r="D280" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Riwayat Langganan</t>
+          <t>Periksa PDF tagihan berdiskon</t>
         </is>
       </c>
       <c r="E280" s="13" t="inlineStr">
         <is>
-          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
+          <t>Harga daftar, nama potongan, dan total dibayar tertulis terpisah</t>
         </is>
       </c>
       <c r="F280" s="13" t="inlineStr">
         <is>
-          <t>F-PF-01</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G280" s="13" t="inlineStr"/>
@@ -11587,12 +11618,12 @@
     <row r="281">
       <c r="A281" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B281" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-02</t>
+          <t>TC-BL-43</t>
         </is>
       </c>
       <c r="C281" s="20" t="inlineStr">
@@ -11602,17 +11633,17 @@
       </c>
       <c r="D281" s="16" t="inlineStr">
         <is>
-          <t>Periksa penanda jalur pelunasan tiap baris</t>
+          <t>Cari tombol PDF pada tagihan belum lunas</t>
         </is>
       </c>
       <c r="E281" s="16" t="inlineStr">
         <is>
-          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
+          <t>Tidak ada</t>
         </is>
       </c>
       <c r="F281" s="16" t="inlineStr">
         <is>
-          <t>F-PF-02</t>
+          <t>F-BL-22</t>
         </is>
       </c>
       <c r="G281" s="16" t="inlineStr"/>
@@ -11622,12 +11653,12 @@
     <row r="282">
       <c r="A282" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B282" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-03</t>
+          <t>TC-BL-44</t>
         </is>
       </c>
       <c r="C282" s="15" t="inlineStr">
@@ -11637,17 +11668,17 @@
       </c>
       <c r="D282" s="13" t="inlineStr">
         <is>
-          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
+          <t>Masuk sebagai Finance, buka beranda</t>
         </is>
       </c>
       <c r="E282" s="13" t="inlineStr">
         <is>
-          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
+          <t>Ada menu Tagihan Langganan</t>
         </is>
       </c>
       <c r="F282" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03, F-PF-05</t>
+          <t>F-BL-23</t>
         </is>
       </c>
       <c r="G282" s="13" t="inlineStr"/>
@@ -11657,12 +11688,12 @@
     <row r="283">
       <c r="A283" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B283" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-04</t>
+          <t>TC-BL-45</t>
         </is>
       </c>
       <c r="C283" s="18" t="inlineStr">
@@ -11672,17 +11703,17 @@
       </c>
       <c r="D283" s="16" t="inlineStr">
         <is>
-          <t>Simpan diskon tanpa memilih resto</t>
+          <t>Finance mengunggah bukti bayar</t>
         </is>
       </c>
       <c r="E283" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
+          <t>Diterima — RPC mengizinkan peran finance</t>
         </is>
       </c>
       <c r="F283" s="16" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-BL-23</t>
         </is>
       </c>
       <c r="G283" s="16" t="inlineStr"/>
@@ -11692,12 +11723,12 @@
     <row r="284">
       <c r="A284" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B284" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-05</t>
+          <t>TC-BL-46</t>
         </is>
       </c>
       <c r="C284" s="19" t="inlineStr">
@@ -11707,17 +11738,17 @@
       </c>
       <c r="D284" s="13" t="inlineStr">
         <is>
-          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
+          <t>Finance membuat Virtual Account</t>
         </is>
       </c>
       <c r="E284" s="13" t="inlineStr">
         <is>
-          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
+          <t>Berhasil, sama seperti Owner</t>
         </is>
       </c>
       <c r="F284" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-BL-23</t>
         </is>
       </c>
       <c r="G284" s="13" t="inlineStr"/>
@@ -11727,12 +11758,12 @@
     <row r="285">
       <c r="A285" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B285" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-06</t>
+          <t>TC-BL-47</t>
         </is>
       </c>
       <c r="C285" s="20" t="inlineStr">
@@ -11742,17 +11773,17 @@
       </c>
       <c r="D285" s="16" t="inlineStr">
         <is>
-          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
+          <t>Kasir/Chef mencari menu itu</t>
         </is>
       </c>
       <c r="E285" s="16" t="inlineStr">
         <is>
-          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
+          <t>Tidak ada</t>
         </is>
       </c>
       <c r="F285" s="16" t="inlineStr">
         <is>
-          <t>F-PF-04</t>
+          <t>F-BL-23</t>
         </is>
       </c>
       <c r="G285" s="16" t="inlineStr"/>
@@ -11762,12 +11793,12 @@
     <row r="286">
       <c r="A286" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B286" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-07</t>
+          <t>TC-BL-15</t>
         </is>
       </c>
       <c r="C286" s="15" t="inlineStr">
@@ -11777,17 +11808,17 @@
       </c>
       <c r="D286" s="13" t="inlineStr">
         <is>
-          <t>Hapus diskon setelah tagihan terbit</t>
+          <t>Coba kirim bukti tanpa melampirkan foto</t>
         </is>
       </c>
       <c r="E286" s="13" t="inlineStr">
         <is>
-          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
+          <t>Tombol Kirim mati</t>
         </is>
       </c>
       <c r="F286" s="13" t="inlineStr">
         <is>
-          <t>F-PF-05</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G286" s="13" t="inlineStr"/>
@@ -11797,12 +11828,12 @@
     <row r="287">
       <c r="A287" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B287" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-08</t>
+          <t>TC-BL-16</t>
         </is>
       </c>
       <c r="C287" s="18" t="inlineStr">
@@ -11812,17 +11843,17 @@
       </c>
       <c r="D287" s="16" t="inlineStr">
         <is>
-          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
+          <t>Super Admin → tab Tagihan → Terima</t>
         </is>
       </c>
       <c r="E287" s="16" t="inlineStr">
         <is>
-          <t>Dua baris: pendapatan kredit, diskon debit</t>
+          <t>Status jadi Lunas; resto tetap terbuka; pita hilang</t>
         </is>
       </c>
       <c r="F287" s="16" t="inlineStr">
         <is>
-          <t>F-PF-06, F-PF-07</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G287" s="16" t="inlineStr"/>
@@ -11832,12 +11863,12 @@
     <row r="288">
       <c r="A288" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B288" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-09</t>
+          <t>TC-BL-17</t>
         </is>
       </c>
       <c r="C288" s="15" t="inlineStr">
@@ -11847,17 +11878,17 @@
       </c>
       <c r="D288" s="13" t="inlineStr">
         <is>
-          <t>Tagihan ditolak lalu diterima lagi</t>
+          <t>Super Admin → Tolak tanpa mengisi alasan</t>
         </is>
       </c>
       <c r="E288" s="13" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
+          <t>Tombol Tolak tidak menyelesaikan apa-apa — alasan wajib</t>
         </is>
       </c>
       <c r="F288" s="13" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-BL-14</t>
         </is>
       </c>
       <c r="G288" s="13" t="inlineStr"/>
@@ -11867,12 +11898,12 @@
     <row r="289">
       <c r="A289" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B289" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-10</t>
+          <t>TC-BL-18</t>
         </is>
       </c>
       <c r="C289" s="18" t="inlineStr">
@@ -11882,17 +11913,17 @@
       </c>
       <c r="D289" s="16" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL resto yang membayar</t>
+          <t>Tolak berikut alasan, lalu buka layar Tagihan dari sisi resto</t>
         </is>
       </c>
       <c r="E289" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada baris pendapatan langganan di sana</t>
+          <t>Alasannya terbaca; kalau sudah lewat tenggang, terkunci lagi</t>
         </is>
       </c>
       <c r="F289" s="16" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-BL-14, F-BL-15</t>
         </is>
       </c>
       <c r="G289" s="16" t="inlineStr"/>
@@ -11902,32 +11933,32 @@
     <row r="290">
       <c r="A290" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B290" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-11</t>
-        </is>
-      </c>
-      <c r="C290" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-19</t>
+        </is>
+      </c>
+      <c r="C290" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D290" s="13" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account KaataGo</t>
+          <t>Login sebagai Super Admin saat ada resto terkunci</t>
         </is>
       </c>
       <c r="E290" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
+          <t>Tidak terkunci sama sekali</t>
         </is>
       </c>
       <c r="F290" s="13" t="inlineStr">
         <is>
-          <t>F-PF-08</t>
+          <t>F-BL-17</t>
         </is>
       </c>
       <c r="G290" s="13" t="inlineStr"/>
@@ -11937,32 +11968,32 @@
     <row r="291">
       <c r="A291" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B291" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-12</t>
-        </is>
-      </c>
-      <c r="C291" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-BL-20</t>
+        </is>
+      </c>
+      <c r="C291" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D291" s="16" t="inlineStr">
         <is>
-          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
+          <t>Sebagai resto terkunci, coba ubah harga produk</t>
         </is>
       </c>
       <c r="E291" s="16" t="inlineStr">
         <is>
-          <t>Bekerja sama seperti di resto</t>
+          <t>Ditolak — katalog ikut dibekukan</t>
         </is>
       </c>
       <c r="F291" s="16" t="inlineStr">
         <is>
-          <t>F-PF-09</t>
+          <t>F-BL-18</t>
         </is>
       </c>
       <c r="G291" s="16" t="inlineStr"/>
@@ -11972,12 +12003,12 @@
     <row r="292">
       <c r="A292" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B292" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-13</t>
+          <t>TC-BL-21</t>
         </is>
       </c>
       <c r="C292" s="15" t="inlineStr">
@@ -11987,17 +12018,17 @@
       </c>
       <c r="D292" s="13" t="inlineStr">
         <is>
-          <t>Telusuri menu Finance KaataGo</t>
+          <t>Resto A terkunci; buka aplikasi sebagai karyawan resto B</t>
         </is>
       </c>
       <c r="E292" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada Setor Saldo Cash</t>
+          <t>Resto B tidak terpengaruh</t>
         </is>
       </c>
       <c r="F292" s="13" t="inlineStr">
         <is>
-          <t>F-PF-10</t>
+          <t>F-BL-15, A-10</t>
         </is>
       </c>
       <c r="G292" s="13" t="inlineStr"/>
@@ -12007,12 +12038,12 @@
     <row r="293">
       <c r="A293" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B293" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-14</t>
+          <t>TC-BL-22</t>
         </is>
       </c>
       <c r="C293" s="18" t="inlineStr">
@@ -12022,17 +12053,17 @@
       </c>
       <c r="D293" s="16" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL Semua Resto</t>
+          <t>Coba panggil review_billing_payment sebagai Owner resto</t>
         </is>
       </c>
       <c r="E293" s="16" t="inlineStr">
         <is>
-          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
+          <t>Ditolak — hanya Super Admin</t>
         </is>
       </c>
       <c r="F293" s="16" t="inlineStr">
         <is>
-          <t>F-PF-11</t>
+          <t>F-BL-13</t>
         </is>
       </c>
       <c r="G293" s="16" t="inlineStr"/>
@@ -12042,12 +12073,12 @@
     <row r="294">
       <c r="A294" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B294" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-15</t>
+          <t>TC-BL-23</t>
         </is>
       </c>
       <c r="C294" s="15" t="inlineStr">
@@ -12057,17 +12088,17 @@
       </c>
       <c r="D294" s="13" t="inlineStr">
         <is>
-          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
+          <t>Coba UPDATE billing_invoices SET status='paid' sebagai Owner</t>
         </is>
       </c>
       <c r="E294" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun — hanya bisa dilihat</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F294" s="13" t="inlineStr">
         <is>
-          <t>F-PF-12</t>
+          <t>F-BL-13, TSD §7.3</t>
         </is>
       </c>
       <c r="G294" s="13" t="inlineStr"/>
@@ -12077,32 +12108,32 @@
     <row r="295">
       <c r="A295" s="16" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B295" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-16</t>
-        </is>
-      </c>
-      <c r="C295" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-24</t>
+        </is>
+      </c>
+      <c r="C295" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D295" s="16" t="inlineStr">
         <is>
-          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
+          <t>Matikan sambungan, buka aplikasi resto berbayar yang lancar</t>
         </is>
       </c>
       <c r="E295" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tidak terkunci karena gagal memeriksa</t>
         </is>
       </c>
       <c r="F295" s="16" t="inlineStr">
         <is>
-          <t>F-PF-12, TSD §7.4</t>
+          <t>TSD §7.3</t>
         </is>
       </c>
       <c r="G295" s="16" t="inlineStr"/>
@@ -12112,32 +12143,32 @@
     <row r="296">
       <c r="A296" s="13" t="inlineStr">
         <is>
-          <t>## 19c. Finance KaataGo (Super Admin)</t>
+          <t>## 19b. Langganan &amp; Tagihan Resto</t>
         </is>
       </c>
       <c r="B296" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-17</t>
-        </is>
-      </c>
-      <c r="C296" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-BL-25</t>
+        </is>
+      </c>
+      <c r="C296" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D296" s="13" t="inlineStr">
         <is>
-          <t>Buka Pilih Resto sebagai pelanggan</t>
+          <t>Owner → Tagihan Langganan</t>
         </is>
       </c>
       <c r="E296" s="13" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul di daftar mana pun</t>
+          <t>Terbuka, memuat paket dan riwayat tagihan</t>
         </is>
       </c>
       <c r="F296" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-BL-11</t>
         </is>
       </c>
       <c r="G296" s="13" t="inlineStr"/>
@@ -12152,7 +12183,7 @@
       </c>
       <c r="B297" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-18</t>
+          <t>TC-PF-01</t>
         </is>
       </c>
       <c r="C297" s="18" t="inlineStr">
@@ -12162,17 +12193,17 @@
       </c>
       <c r="D297" s="16" t="inlineStr">
         <is>
-          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
+          <t>Super Admin → Finance → Riwayat Langganan</t>
         </is>
       </c>
       <c r="E297" s="16" t="inlineStr">
         <is>
-          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
+          <t>Tagihan lunas tampil, dikelompokkan per bulan, dengan total</t>
         </is>
       </c>
       <c r="F297" s="16" t="inlineStr">
         <is>
-          <t>TSD §7.4</t>
+          <t>F-PF-01</t>
         </is>
       </c>
       <c r="G297" s="16" t="inlineStr"/>
@@ -12187,7 +12218,7 @@
       </c>
       <c r="B298" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-19</t>
+          <t>TC-PF-02</t>
         </is>
       </c>
       <c r="C298" s="19" t="inlineStr">
@@ -12197,17 +12228,17 @@
       </c>
       <c r="D298" s="13" t="inlineStr">
         <is>
-          <t>Buka Diskon Langganan sebagai Owner resto</t>
+          <t>Periksa penanda jalur pelunasan tiap baris</t>
         </is>
       </c>
       <c r="E298" s="13" t="inlineStr">
         <is>
-          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
+          <t>Tertulis VA atau manual sesuai cara lunasnya</t>
         </is>
       </c>
       <c r="F298" s="13" t="inlineStr">
         <is>
-          <t>F-PF-03</t>
+          <t>F-PF-02</t>
         </is>
       </c>
       <c r="G298" s="13" t="inlineStr"/>
@@ -12222,7 +12253,7 @@
       </c>
       <c r="B299" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-20</t>
+          <t>TC-PF-03</t>
         </is>
       </c>
       <c r="C299" s="18" t="inlineStr">
@@ -12232,17 +12263,17 @@
       </c>
       <c r="D299" s="16" t="inlineStr">
         <is>
-          <t>Bandingkan total debit/kredit Jurnal Semua Resto dengan Jurnal GL resto itu (saring ke resto yang sama)</t>
+          <t>Buat diskon langganan 20% untuk satu resto → terbitkan tagihan</t>
         </is>
       </c>
       <c r="E299" s="16" t="inlineStr">
         <is>
-          <t>Angkanya sama persis</t>
+          <t>Tagihan resto itu berkurang 20%; resto lain tetap penuh</t>
         </is>
       </c>
       <c r="F299" s="16" t="inlineStr">
         <is>
-          <t>F-PF-14</t>
+          <t>F-PF-03, F-PF-05</t>
         </is>
       </c>
       <c r="G299" s="16" t="inlineStr"/>
@@ -12257,7 +12288,7 @@
       </c>
       <c r="B300" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-21</t>
+          <t>TC-PF-04</t>
         </is>
       </c>
       <c r="C300" s="15" t="inlineStr">
@@ -12267,17 +12298,17 @@
       </c>
       <c r="D300" s="13" t="inlineStr">
         <is>
-          <t>Batalkan sebuah pengeluaran, lihat kedua layar jurnal</t>
+          <t>Simpan diskon tanpa memilih resto</t>
         </is>
       </c>
       <c r="E300" s="13" t="inlineStr">
         <is>
-          <t>Total tidak naik; keterangan "N pembatalan tidak dihitung" muncul</t>
+          <t>Ditolak — diskon tanpa sasaran tidak mengenai siapa pun</t>
         </is>
       </c>
       <c r="F300" s="13" t="inlineStr">
         <is>
-          <t>F-PF-14</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G300" s="13" t="inlineStr"/>
@@ -12292,7 +12323,7 @@
       </c>
       <c r="B301" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-22</t>
+          <t>TC-PF-05</t>
         </is>
       </c>
       <c r="C301" s="20" t="inlineStr">
@@ -12302,17 +12333,17 @@
       </c>
       <c r="D301" s="16" t="inlineStr">
         <is>
-          <t>Cari baris pembatalan di daftar</t>
+          <t>Buat diskon rupiah lebih besar daripada harga langganan</t>
         </is>
       </c>
       <c r="E301" s="16" t="inlineStr">
         <is>
-          <t>Tetap tampil, bertanda PEMBATALAN</t>
+          <t>Potongannya berhenti di harga; tagihan tidak pernah negatif</t>
         </is>
       </c>
       <c r="F301" s="16" t="inlineStr">
         <is>
-          <t>F-PF-15</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G301" s="16" t="inlineStr"/>
@@ -12327,27 +12358,27 @@
       </c>
       <c r="B302" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-23</t>
-        </is>
-      </c>
-      <c r="C302" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-06</t>
+        </is>
+      </c>
+      <c r="C302" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D302" s="13" t="inlineStr">
         <is>
-          <t>Saring ke sebuah resto, lalu pilih Semua resto lagi</t>
+          <t>Nonaktifkan diskon, terbitkan tagihan berikutnya</t>
         </is>
       </c>
       <c r="E302" s="13" t="inlineStr">
         <is>
-          <t>Kembali menampilkan seluruh resto — bukan tetap tersaring</t>
+          <t>Tidak memotong; diskonnya tetap ada di daftar</t>
         </is>
       </c>
       <c r="F302" s="13" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>F-PF-04</t>
         </is>
       </c>
       <c r="G302" s="13" t="inlineStr"/>
@@ -12362,7 +12393,7 @@
       </c>
       <c r="B303" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-24</t>
+          <t>TC-PF-07</t>
         </is>
       </c>
       <c r="C303" s="18" t="inlineStr">
@@ -12372,17 +12403,17 @@
       </c>
       <c r="D303" s="16" t="inlineStr">
         <is>
-          <t>Saring ke resto A, lalu saring lagi ke resto B yang punya jurnal</t>
+          <t>Hapus diskon setelah tagihan terbit</t>
         </is>
       </c>
       <c r="E303" s="16" t="inlineStr">
         <is>
-          <t>Isinya berganti ke jurnal resto B</t>
+          <t>Tagihan yang sudah terbit tetap menyebut potongannya</t>
         </is>
       </c>
       <c r="F303" s="16" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>F-PF-05</t>
         </is>
       </c>
       <c r="G303" s="16" t="inlineStr"/>
@@ -12397,27 +12428,27 @@
       </c>
       <c r="B304" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-25</t>
-        </is>
-      </c>
-      <c r="C304" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-08</t>
+        </is>
+      </c>
+      <c r="C304" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D304" s="13" t="inlineStr">
         <is>
-          <t>Perhatikan pita di atas layar sesudah menyaring</t>
+          <t>Bayar tagihan berdiskon → buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E304" s="13" t="inlineStr">
         <is>
-          <t>Nama restonya tertulis, dengan tombol × untuk melepasnya</t>
+          <t>Dua baris: pendapatan kredit, diskon debit</t>
         </is>
       </c>
       <c r="F304" s="13" t="inlineStr">
         <is>
-          <t>F-PF-16</t>
+          <t>F-PF-06, F-PF-07</t>
         </is>
       </c>
       <c r="G304" s="13" t="inlineStr"/>
@@ -12432,27 +12463,27 @@
       </c>
       <c r="B305" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-26</t>
-        </is>
-      </c>
-      <c r="C305" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-09</t>
+        </is>
+      </c>
+      <c r="C305" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D305" s="16" t="inlineStr">
         <is>
-          <t>Buka daftar saringan</t>
+          <t>Tagihan ditolak lalu diterima lagi</t>
         </is>
       </c>
       <c r="E305" s="16" t="inlineStr">
         <is>
-          <t>Resto yang belum punya jurnal ditandai "Belum ada jurnal"</t>
+          <t>Jurnalnya tetap satu set — pendapatan tidak tercatat dua kali</t>
         </is>
       </c>
       <c r="F305" s="16" t="inlineStr">
         <is>
-          <t>F-PF-17</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G305" s="16" t="inlineStr"/>
@@ -12467,27 +12498,27 @@
       </c>
       <c r="B306" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-27</t>
-        </is>
-      </c>
-      <c r="C306" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-10</t>
+        </is>
+      </c>
+      <c r="C306" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D306" s="13" t="inlineStr">
         <is>
-          <t>Perhatikan pengelompokan</t>
+          <t>Buka Jurnal GL resto yang membayar</t>
         </is>
       </c>
       <c r="E306" s="13" t="inlineStr">
         <is>
-          <t>Per tanggal, bisa dilipat; tanggal terbaru terbuka, sisanya tertutup</t>
+          <t>Tidak ada baris pendapatan langganan di sana</t>
         </is>
       </c>
       <c r="F306" s="13" t="inlineStr">
         <is>
-          <t>F-PF-18</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G306" s="13" t="inlineStr"/>
@@ -12502,27 +12533,27 @@
       </c>
       <c r="B307" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-28</t>
-        </is>
-      </c>
-      <c r="C307" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-11</t>
+        </is>
+      </c>
+      <c r="C307" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D307" s="16" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account resto mana pun</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E307" s="16" t="inlineStr">
         <is>
-          <t>GL Diskon punya bagiannya dan nomornya sudah terisi</t>
+          <t>Bagan akun 11xxxxx lengkap, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F307" s="16" t="inlineStr">
         <is>
-          <t>F-PF-19, F-DS-09</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G307" s="16" t="inlineStr"/>
@@ -12537,7 +12568,7 @@
       </c>
       <c r="B308" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-29</t>
+          <t>TC-PF-12</t>
         </is>
       </c>
       <c r="C308" s="19" t="inlineStr">
@@ -12547,17 +12578,17 @@
       </c>
       <c r="D308" s="13" t="inlineStr">
         <is>
-          <t>Buka Mapping GL Account KaataGo</t>
+          <t>Catat pengeluaran dan top up petty cash KaataGo</t>
         </is>
       </c>
       <c r="E308" s="13" t="inlineStr">
         <is>
-          <t>Ada bagian GL Langganan; penghitung akun tidak pernah menyisakan yang mustahil terisi</t>
+          <t>Bekerja sama seperti di resto</t>
         </is>
       </c>
       <c r="F308" s="13" t="inlineStr">
         <is>
-          <t>F-PF-19</t>
+          <t>F-PF-09</t>
         </is>
       </c>
       <c r="G308" s="13" t="inlineStr"/>
@@ -12572,7 +12603,7 @@
       </c>
       <c r="B309" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-30</t>
+          <t>TC-PF-13</t>
         </is>
       </c>
       <c r="C309" s="18" t="inlineStr">
@@ -12582,17 +12613,17 @@
       </c>
       <c r="D309" s="16" t="inlineStr">
         <is>
-          <t>Pesan menu berpromo, bayar, buka Jurnal GL</t>
+          <t>Telusuri menu Finance KaataGo</t>
         </is>
       </c>
       <c r="E309" s="16" t="inlineStr">
         <is>
-          <t>Baris GL Diskon menyebut nama promonya</t>
+          <t>Tidak ada Setor Saldo Cash</t>
         </is>
       </c>
       <c r="F309" s="16" t="inlineStr">
         <is>
-          <t>F-PF-20, F-DS-13</t>
+          <t>F-PF-10</t>
         </is>
       </c>
       <c r="G309" s="16" t="inlineStr"/>
@@ -12607,7 +12638,7 @@
       </c>
       <c r="B310" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-31</t>
+          <t>TC-PF-14</t>
         </is>
       </c>
       <c r="C310" s="15" t="inlineStr">
@@ -12617,17 +12648,17 @@
       </c>
       <c r="D310" s="13" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL Semua Resto sesudah ada tagihan langganan lunas</t>
+          <t>Buka Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E310" s="13" t="inlineStr">
         <is>
-          <t>Baris pendapatan langganan tidak muncul di sana</t>
+          <t>Jurnal seluruh resto tampil, bisa disaring per resto</t>
         </is>
       </c>
       <c r="F310" s="13" t="inlineStr">
         <is>
-          <t>F-PF-21</t>
+          <t>F-PF-11</t>
         </is>
       </c>
       <c r="G310" s="13" t="inlineStr"/>
@@ -12642,7 +12673,7 @@
       </c>
       <c r="B311" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-32</t>
+          <t>TC-PF-15</t>
         </is>
       </c>
       <c r="C311" s="18" t="inlineStr">
@@ -12652,17 +12683,17 @@
       </c>
       <c r="D311" s="16" t="inlineStr">
         <is>
-          <t>Buka daftar saringan resto</t>
+          <t>Cari cara mengubah baris di Jurnal GL Semua Resto</t>
         </is>
       </c>
       <c r="E311" s="16" t="inlineStr">
         <is>
-          <t>KaataGo tidak ada di daftarnya</t>
+          <t>Tidak ada satu pun — hanya bisa dilihat</t>
         </is>
       </c>
       <c r="F311" s="16" t="inlineStr">
         <is>
-          <t>F-PF-21</t>
+          <t>F-PF-12</t>
         </is>
       </c>
       <c r="G311" s="16" t="inlineStr"/>
@@ -12677,7 +12708,7 @@
       </c>
       <c r="B312" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-33</t>
+          <t>TC-PF-16</t>
         </is>
       </c>
       <c r="C312" s="15" t="inlineStr">
@@ -12687,17 +12718,17 @@
       </c>
       <c r="D312" s="13" t="inlineStr">
         <is>
-          <t>Buka Jurnal GL KaataGo</t>
+          <t>Coba UPDATE gl_journal_entries sebagai Super Admin lewat API</t>
         </is>
       </c>
       <c r="E312" s="13" t="inlineStr">
         <is>
-          <t>Pendapatan langganan ada di sana, dan Saldo Total tidak nol</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F312" s="13" t="inlineStr">
         <is>
-          <t>F-PF-07</t>
+          <t>F-PF-12, TSD §7.4</t>
         </is>
       </c>
       <c r="G312" s="13" t="inlineStr"/>
@@ -12712,27 +12743,27 @@
       </c>
       <c r="B313" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-34</t>
-        </is>
-      </c>
-      <c r="C313" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-17</t>
+        </is>
+      </c>
+      <c r="C313" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D313" s="16" t="inlineStr">
         <is>
-          <t>Periksa nomor akun di Jurnal GL KaataGo</t>
+          <t>Buka Pilih Resto sebagai pelanggan</t>
         </is>
       </c>
       <c r="E313" s="16" t="inlineStr">
         <is>
-          <t>Golongan 11xxxxx, berbeda dari 19xxxxx milik resto</t>
+          <t>KaataGo tidak muncul di daftar mana pun</t>
         </is>
       </c>
       <c r="F313" s="16" t="inlineStr">
         <is>
-          <t>F-PF-08</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G313" s="16" t="inlineStr"/>
@@ -12742,12 +12773,12 @@
     <row r="314">
       <c r="A314" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B314" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-01</t>
+          <t>TC-PF-18</t>
         </is>
       </c>
       <c r="C314" s="15" t="inlineStr">
@@ -12757,17 +12788,17 @@
       </c>
       <c r="D314" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
+          <t>Buka List Resto dan Billing Resto sebagai Super Admin</t>
         </is>
       </c>
       <c r="E314" s="13" t="inlineStr">
         <is>
-          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
+          <t>KaataGo tidak muncul sebagai resto yang bisa ditagih</t>
         </is>
       </c>
       <c r="F314" s="13" t="inlineStr">
         <is>
-          <t>F-VC-01, F-VC-02</t>
+          <t>TSD §7.4</t>
         </is>
       </c>
       <c r="G314" s="13" t="inlineStr"/>
@@ -12777,32 +12808,32 @@
     <row r="315">
       <c r="A315" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B315" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-02</t>
-        </is>
-      </c>
-      <c r="C315" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-19</t>
+        </is>
+      </c>
+      <c r="C315" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D315" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan Rp 1.000.000 jadi 3</t>
+          <t>Buka Diskon Langganan sebagai Owner resto</t>
         </is>
       </c>
       <c r="E315" s="16" t="inlineStr">
         <is>
-          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
+          <t>Hanya diskon yang mengenai restonya yang terbaca</t>
         </is>
       </c>
       <c r="F315" s="16" t="inlineStr">
         <is>
-          <t>F-VC-02</t>
+          <t>F-PF-03</t>
         </is>
       </c>
       <c r="G315" s="16" t="inlineStr"/>
@@ -12812,32 +12843,32 @@
     <row r="316">
       <c r="A316" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B316" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-03</t>
-        </is>
-      </c>
-      <c r="C316" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-20</t>
+        </is>
+      </c>
+      <c r="C316" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D316" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan dengan kode yang sudah dipakai</t>
+          <t>Bandingkan total debit/kredit Jurnal Semua Resto dengan Jurnal GL resto itu (saring ke resto yang sama)</t>
         </is>
       </c>
       <c r="E316" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — kodenya sudah ada</t>
+          <t>Angkanya sama persis</t>
         </is>
       </c>
       <c r="F316" s="13" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-PF-14</t>
         </is>
       </c>
       <c r="G316" s="13" t="inlineStr"/>
@@ -12847,12 +12878,12 @@
     <row r="317">
       <c r="A317" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B317" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-04</t>
+          <t>TC-PF-21</t>
         </is>
       </c>
       <c r="C317" s="18" t="inlineStr">
@@ -12862,17 +12893,17 @@
       </c>
       <c r="D317" s="16" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
+          <t>Batalkan sebuah pengeluaran, lihat kedua layar jurnal</t>
         </is>
       </c>
       <c r="E317" s="16" t="inlineStr">
         <is>
-          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
+          <t>Total tidak naik; keterangan "N pembatalan tidak dihitung" muncul</t>
         </is>
       </c>
       <c r="F317" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-PF-14</t>
         </is>
       </c>
       <c r="G317" s="16" t="inlineStr"/>
@@ -12882,32 +12913,32 @@
     <row r="318">
       <c r="A318" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B318" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-05</t>
-        </is>
-      </c>
-      <c r="C318" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-22</t>
+        </is>
+      </c>
+      <c r="C318" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D318" s="13" t="inlineStr">
         <is>
-          <t>Pelanggan menebus kode di Voucher Saya</t>
+          <t>Cari baris pembatalan di daftar</t>
         </is>
       </c>
       <c r="E318" s="13" t="inlineStr">
         <is>
-          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
+          <t>Tetap tampil, bertanda PEMBATALAN</t>
         </is>
       </c>
       <c r="F318" s="13" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-PF-15</t>
         </is>
       </c>
       <c r="G318" s="13" t="inlineStr"/>
@@ -12917,32 +12948,32 @@
     <row r="319">
       <c r="A319" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B319" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-06</t>
-        </is>
-      </c>
-      <c r="C319" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-23</t>
+        </is>
+      </c>
+      <c r="C319" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D319" s="16" t="inlineStr">
         <is>
-          <t>Ketik kodenya dengan huruf kecil</t>
+          <t>Saring ke sebuah resto, lalu pilih Semua resto lagi</t>
         </is>
       </c>
       <c r="E319" s="16" t="inlineStr">
         <is>
-          <t>Tetap diterima</t>
+          <t>Kembali menampilkan seluruh resto — bukan tetap tersaring</t>
         </is>
       </c>
       <c r="F319" s="16" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G319" s="16" t="inlineStr"/>
@@ -12952,32 +12983,32 @@
     <row r="320">
       <c r="A320" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B320" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-07</t>
-        </is>
-      </c>
-      <c r="C320" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-24</t>
+        </is>
+      </c>
+      <c r="C320" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D320" s="13" t="inlineStr">
         <is>
-          <t>Ketik kode yang tidak ada</t>
+          <t>Saring ke resto A, lalu saring lagi ke resto B yang punya jurnal</t>
         </is>
       </c>
       <c r="E320" s="13" t="inlineStr">
         <is>
-          <t>"Kode voucher tidak ditemukan"</t>
+          <t>Isinya berganti ke jurnal resto B</t>
         </is>
       </c>
       <c r="F320" s="13" t="inlineStr">
         <is>
-          <t>F-VC-10</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G320" s="13" t="inlineStr"/>
@@ -12987,32 +13018,32 @@
     <row r="321">
       <c r="A321" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B321" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-08</t>
-        </is>
-      </c>
-      <c r="C321" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-25</t>
+        </is>
+      </c>
+      <c r="C321" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D321" s="16" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
+          <t>Perhatikan pita di atas layar sesudah menyaring</t>
         </is>
       </c>
       <c r="E321" s="16" t="inlineStr">
         <is>
-          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
+          <t>Nama restonya tertulis, dengan tombol × untuk melepasnya</t>
         </is>
       </c>
       <c r="F321" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-PF-16</t>
         </is>
       </c>
       <c r="G321" s="16" t="inlineStr"/>
@@ -13022,32 +13053,32 @@
     <row r="322">
       <c r="A322" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B322" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-09</t>
-        </is>
-      </c>
-      <c r="C322" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-26</t>
+        </is>
+      </c>
+      <c r="C322" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D322" s="13" t="inlineStr">
         <is>
-          <t>Orang yang sama menebus kode itu lagi</t>
+          <t>Buka daftar saringan</t>
         </is>
       </c>
       <c r="E322" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
+          <t>Resto yang belum punya jurnal ditandai "Belum ada jurnal"</t>
         </is>
       </c>
       <c r="F322" s="13" t="inlineStr">
         <is>
-          <t>F-VC-08, F-VC-10</t>
+          <t>F-PF-17</t>
         </is>
       </c>
       <c r="G322" s="13" t="inlineStr"/>
@@ -13057,32 +13088,32 @@
     <row r="323">
       <c r="A323" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B323" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-10</t>
-        </is>
-      </c>
-      <c r="C323" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-27</t>
+        </is>
+      </c>
+      <c r="C323" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D323" s="16" t="inlineStr">
         <is>
-          <t>Batch berisi 10, orang ke-11 menebus</t>
+          <t>Perhatikan pengelompokan</t>
         </is>
       </c>
       <c r="E323" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — "Voucher ini sudah habis"</t>
+          <t>Per tanggal, bisa dilipat; tanggal terbaru terbuka, sisanya tertutup</t>
         </is>
       </c>
       <c r="F323" s="16" t="inlineStr">
         <is>
-          <t>F-VC-09, F-VC-10</t>
+          <t>F-PF-18</t>
         </is>
       </c>
       <c r="G323" s="16" t="inlineStr"/>
@@ -13092,12 +13123,12 @@
     <row r="324">
       <c r="A324" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B324" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-11</t>
+          <t>TC-PF-28</t>
         </is>
       </c>
       <c r="C324" s="15" t="inlineStr">
@@ -13107,17 +13138,17 @@
       </c>
       <c r="D324" s="13" t="inlineStr">
         <is>
-          <t>Dua orang menebus voucher terakhir bersamaan</t>
+          <t>Buka Mapping GL Account resto mana pun</t>
         </is>
       </c>
       <c r="E324" s="13" t="inlineStr">
         <is>
-          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
+          <t>GL Diskon punya bagiannya dan nomornya sudah terisi</t>
         </is>
       </c>
       <c r="F324" s="13" t="inlineStr">
         <is>
-          <t>F-VC-09</t>
+          <t>F-PF-19, F-DS-09</t>
         </is>
       </c>
       <c r="G324" s="13" t="inlineStr"/>
@@ -13127,12 +13158,12 @@
     <row r="325">
       <c r="A325" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B325" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-12</t>
+          <t>TC-PF-29</t>
         </is>
       </c>
       <c r="C325" s="20" t="inlineStr">
@@ -13142,17 +13173,17 @@
       </c>
       <c r="D325" s="16" t="inlineStr">
         <is>
-          <t>Tebus voucher dari batch yang sudah ditutup</t>
+          <t>Buka Mapping GL Account KaataGo</t>
         </is>
       </c>
       <c r="E325" s="16" t="inlineStr">
         <is>
-          <t>"Voucher ini sudah ditutup"</t>
+          <t>Ada bagian GL Langganan; penghitung akun tidak pernah menyisakan yang mustahil terisi</t>
         </is>
       </c>
       <c r="F325" s="16" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-PF-19</t>
         </is>
       </c>
       <c r="G325" s="16" t="inlineStr"/>
@@ -13162,32 +13193,32 @@
     <row r="326">
       <c r="A326" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B326" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-13</t>
-        </is>
-      </c>
-      <c r="C326" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-30</t>
+        </is>
+      </c>
+      <c r="C326" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D326" s="13" t="inlineStr">
         <is>
-          <t>Tebus voucher yang lewat masa berlaku</t>
+          <t>Pesan menu berpromo, bayar, buka Jurnal GL</t>
         </is>
       </c>
       <c r="E326" s="13" t="inlineStr">
         <is>
-          <t>"Voucher ini sudah kedaluwarsa"</t>
+          <t>Baris GL Diskon menyebut nama promonya</t>
         </is>
       </c>
       <c r="F326" s="13" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-PF-20, F-DS-13</t>
         </is>
       </c>
       <c r="G326" s="13" t="inlineStr"/>
@@ -13197,12 +13228,12 @@
     <row r="327">
       <c r="A327" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B327" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-14</t>
+          <t>TC-PF-31</t>
         </is>
       </c>
       <c r="C327" s="18" t="inlineStr">
@@ -13212,17 +13243,17 @@
       </c>
       <c r="D327" s="16" t="inlineStr">
         <is>
-          <t>Di keranjang, ketuk baris voucher</t>
+          <t>Buka Jurnal GL Semua Resto sesudah ada tagihan langganan lunas</t>
         </is>
       </c>
       <c r="E327" s="16" t="inlineStr">
         <is>
-          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
+          <t>Baris pendapatan langganan tidak muncul di sana</t>
         </is>
       </c>
       <c r="F327" s="16" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-PF-21</t>
         </is>
       </c>
       <c r="G327" s="16" t="inlineStr"/>
@@ -13232,12 +13263,12 @@
     <row r="328">
       <c r="A328" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B328" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-15</t>
+          <t>TC-PF-32</t>
         </is>
       </c>
       <c r="C328" s="15" t="inlineStr">
@@ -13247,17 +13278,17 @@
       </c>
       <c r="D328" s="13" t="inlineStr">
         <is>
-          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
+          <t>Buka daftar saringan resto</t>
         </is>
       </c>
       <c r="E328" s="13" t="inlineStr">
         <is>
-          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
+          <t>KaataGo tidak ada di daftarnya</t>
         </is>
       </c>
       <c r="F328" s="13" t="inlineStr">
         <is>
-          <t>F-VC-05, F-VC-10</t>
+          <t>F-PF-21</t>
         </is>
       </c>
       <c r="G328" s="13" t="inlineStr"/>
@@ -13267,12 +13298,12 @@
     <row r="329">
       <c r="A329" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B329" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-16</t>
+          <t>TC-PF-33</t>
         </is>
       </c>
       <c r="C329" s="18" t="inlineStr">
@@ -13282,17 +13313,17 @@
       </c>
       <c r="D329" s="16" t="inlineStr">
         <is>
-          <t>Voucher khusus resto A dibuka di resto B</t>
+          <t>Buka Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E329" s="16" t="inlineStr">
         <is>
-          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
+          <t>Pendapatan langganan ada di sana, dan Saldo Total tidak nol</t>
         </is>
       </c>
       <c r="F329" s="16" t="inlineStr">
         <is>
-          <t>F-VC-06, F-VC-10</t>
+          <t>F-PF-07</t>
         </is>
       </c>
       <c r="G329" s="16" t="inlineStr"/>
@@ -13302,32 +13333,32 @@
     <row r="330">
       <c r="A330" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B330" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-17</t>
-        </is>
-      </c>
-      <c r="C330" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-34</t>
+        </is>
+      </c>
+      <c r="C330" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D330" s="13" t="inlineStr">
         <is>
-          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
+          <t>Periksa nomor akun di Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E330" s="13" t="inlineStr">
         <is>
-          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
+          <t>Golongan 11xxxxx, berbeda dari 19xxxxx milik resto</t>
         </is>
       </c>
       <c r="F330" s="13" t="inlineStr">
         <is>
-          <t>F-VC-12</t>
+          <t>F-PF-08</t>
         </is>
       </c>
       <c r="G330" s="13" t="inlineStr"/>
@@ -13342,7 +13373,7 @@
       </c>
       <c r="B331" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-18</t>
+          <t>TC-VC-01</t>
         </is>
       </c>
       <c r="C331" s="18" t="inlineStr">
@@ -13352,17 +13383,17 @@
       </c>
       <c r="D331" s="16" t="inlineStr">
         <is>
-          <t>Pasang voucher lalu selesaikan pesanan</t>
+          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
         </is>
       </c>
       <c r="E331" s="16" t="inlineStr">
         <is>
-          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
+          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
         </is>
       </c>
       <c r="F331" s="16" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-01, F-VC-02</t>
         </is>
       </c>
       <c r="G331" s="16" t="inlineStr"/>
@@ -13377,7 +13408,7 @@
       </c>
       <c r="B332" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-19</t>
+          <t>TC-VC-02</t>
         </is>
       </c>
       <c r="C332" s="15" t="inlineStr">
@@ -13387,17 +13418,17 @@
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Lepas setelah voucher terpasang</t>
+          <t>Terbitkan Rp 1.000.000 jadi 3</t>
         </is>
       </c>
       <c r="E332" s="13" t="inlineStr">
         <is>
-          <t>Tagihan kembali ke nominal semula</t>
+          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
         </is>
       </c>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-02</t>
         </is>
       </c>
       <c r="G332" s="13" t="inlineStr"/>
@@ -13412,27 +13443,27 @@
       </c>
       <c r="B333" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-20</t>
-        </is>
-      </c>
-      <c r="C333" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-03</t>
+        </is>
+      </c>
+      <c r="C333" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D333" s="16" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
+          <t>Terbitkan dengan kode yang sudah dipakai</t>
         </is>
       </c>
       <c r="E333" s="16" t="inlineStr">
         <is>
-          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
+          <t>Ditolak — kodenya sudah ada</t>
         </is>
       </c>
       <c r="F333" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G333" s="16" t="inlineStr"/>
@@ -13447,7 +13478,7 @@
       </c>
       <c r="B334" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-21</t>
+          <t>TC-VC-04</t>
         </is>
       </c>
       <c r="C334" s="15" t="inlineStr">
@@ -13457,12 +13488,12 @@
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL restonya</t>
+          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
         </is>
       </c>
       <c r="E334" s="13" t="inlineStr">
         <is>
-          <t>Ada baris masuk sebesar nilai vouchernya</t>
+          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
         </is>
       </c>
       <c r="F334" s="13" t="inlineStr">
@@ -13482,27 +13513,27 @@
       </c>
       <c r="B335" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-22</t>
-        </is>
-      </c>
-      <c r="C335" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-05</t>
+        </is>
+      </c>
+      <c r="C335" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D335" s="16" t="inlineStr">
         <is>
-          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
+          <t>Pelanggan menebus kode di Voucher Saya</t>
         </is>
       </c>
       <c r="E335" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul di daftar pilihan</t>
+          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
         </is>
       </c>
       <c r="F335" s="16" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G335" s="16" t="inlineStr"/>
@@ -13517,27 +13548,27 @@
       </c>
       <c r="B336" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-23</t>
-        </is>
-      </c>
-      <c r="C336" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-06</t>
+        </is>
+      </c>
+      <c r="C336" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
+          <t>Ketik kodenya dengan huruf kecil</t>
         </is>
       </c>
       <c r="E336" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher Redeem, kredit Total Saldo</t>
+          <t>Tetap diterima</t>
         </is>
       </c>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G336" s="13" t="inlineStr"/>
@@ -13552,27 +13583,27 @@
       </c>
       <c r="B337" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-24</t>
-        </is>
-      </c>
-      <c r="C337" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-07</t>
+        </is>
+      </c>
+      <c r="C337" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D337" s="16" t="inlineStr">
         <is>
-          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
+          <t>Ketik kode yang tidak ada</t>
         </is>
       </c>
       <c r="E337" s="16" t="inlineStr">
         <is>
-          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
+          <t>"Kode voucher tidak ditemukan"</t>
         </is>
       </c>
       <c r="F337" s="16" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-10</t>
         </is>
       </c>
       <c r="G337" s="16" t="inlineStr"/>
@@ -13587,7 +13618,7 @@
       </c>
       <c r="B338" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-25</t>
+          <t>TC-VC-08</t>
         </is>
       </c>
       <c r="C338" s="15" t="inlineStr">
@@ -13597,17 +13628,17 @@
       </c>
       <c r="D338" s="13" t="inlineStr">
         <is>
-          <t>Jalankan expire_vouchers() dua kali</t>
+          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
         </is>
       </c>
       <c r="E338" s="13" t="inlineStr">
         <is>
-          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
+          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
         </is>
       </c>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G338" s="13" t="inlineStr"/>
@@ -13622,7 +13653,7 @@
       </c>
       <c r="B339" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-26</t>
+          <t>TC-VC-09</t>
         </is>
       </c>
       <c r="C339" s="18" t="inlineStr">
@@ -13632,17 +13663,17 @@
       </c>
       <c r="D339" s="16" t="inlineStr">
         <is>
-          <t>Jumlahkan keempat tahap untuk satu batch</t>
+          <t>Orang yang sama menebus kode itu lagi</t>
         </is>
       </c>
       <c r="E339" s="16" t="inlineStr">
         <is>
-          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
+          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
         </is>
       </c>
       <c r="F339" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13, F-VC-14</t>
+          <t>F-VC-08, F-VC-10</t>
         </is>
       </c>
       <c r="G339" s="16" t="inlineStr"/>
@@ -13657,7 +13688,7 @@
       </c>
       <c r="B340" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-27</t>
+          <t>TC-VC-10</t>
         </is>
       </c>
       <c r="C340" s="15" t="inlineStr">
@@ -13667,17 +13698,17 @@
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
-          <t>Tulis langsung ke voucher_claims lewat API</t>
+          <t>Batch berisi 10, orang ke-11 menebus</t>
         </is>
       </c>
       <c r="E340" s="13" t="inlineStr">
         <is>
-          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
+          <t>Ditolak — "Voucher ini sudah habis"</t>
         </is>
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-09, F-VC-10</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr"/>
@@ -13692,7 +13723,7 @@
       </c>
       <c r="B341" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-28</t>
+          <t>TC-VC-11</t>
         </is>
       </c>
       <c r="C341" s="18" t="inlineStr">
@@ -13702,17 +13733,17 @@
       </c>
       <c r="D341" s="16" t="inlineStr">
         <is>
-          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
+          <t>Dua orang menebus voucher terakhir bersamaan</t>
         </is>
       </c>
       <c r="E341" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
+          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
         </is>
       </c>
       <c r="F341" s="16" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-VC-09</t>
         </is>
       </c>
       <c r="G341" s="16" t="inlineStr"/>
@@ -13727,7 +13758,7 @@
       </c>
       <c r="B342" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-29</t>
+          <t>TC-VC-12</t>
         </is>
       </c>
       <c r="C342" s="19" t="inlineStr">
@@ -13737,17 +13768,17 @@
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
-          <t>Periksa kartu batch di layar Super Admin</t>
+          <t>Tebus voucher dari batch yang sudah ditutup</t>
         </is>
       </c>
       <c r="E342" s="13" t="inlineStr">
         <is>
-          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
+          <t>"Voucher ini sudah ditutup"</t>
         </is>
       </c>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>F-VC-15</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G342" s="13" t="inlineStr"/>
@@ -13762,7 +13793,7 @@
       </c>
       <c r="B343" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-30</t>
+          <t>TC-VC-13</t>
         </is>
       </c>
       <c r="C343" s="20" t="inlineStr">
@@ -13772,17 +13803,17 @@
       </c>
       <c r="D343" s="16" t="inlineStr">
         <is>
-          <t>Tutup sebuah batch yang kuotanya masih ada</t>
+          <t>Tebus voucher yang lewat masa berlaku</t>
         </is>
       </c>
       <c r="E343" s="16" t="inlineStr">
         <is>
-          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
+          <t>"Voucher ini sudah kedaluwarsa"</t>
         </is>
       </c>
       <c r="F343" s="16" t="inlineStr">
         <is>
-          <t>F-VC-04</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G343" s="16" t="inlineStr"/>
@@ -13797,7 +13828,7 @@
       </c>
       <c r="B344" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-31</t>
+          <t>TC-VC-14</t>
         </is>
       </c>
       <c r="C344" s="15" t="inlineStr">
@@ -13807,17 +13838,17 @@
       </c>
       <c r="D344" s="13" t="inlineStr">
         <is>
-          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
+          <t>Di keranjang, ketuk baris voucher</t>
         </is>
       </c>
       <c r="E344" s="13" t="inlineStr">
         <is>
-          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
+          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
         </is>
       </c>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G344" s="13" t="inlineStr"/>
@@ -13832,7 +13863,7 @@
       </c>
       <c r="B345" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-32</t>
+          <t>TC-VC-15</t>
         </is>
       </c>
       <c r="C345" s="18" t="inlineStr">
@@ -13842,17 +13873,17 @@
       </c>
       <c r="D345" s="16" t="inlineStr">
         <is>
-          <t>Jalankan settle-voucher-payouts</t>
+          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
         </is>
       </c>
       <c r="E345" s="16" t="inlineStr">
         <is>
-          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
+          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
         </is>
       </c>
       <c r="F345" s="16" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-05, F-VC-10</t>
         </is>
       </c>
       <c r="G345" s="16" t="inlineStr"/>
@@ -13867,7 +13898,7 @@
       </c>
       <c r="B346" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-33</t>
+          <t>TC-VC-16</t>
         </is>
       </c>
       <c r="C346" s="15" t="inlineStr">
@@ -13877,17 +13908,17 @@
       </c>
       <c r="D346" s="13" t="inlineStr">
         <is>
-          <t>Jalankan fungsinya dua kali berturut-turut</t>
+          <t>Voucher khusus resto A dibuka di resto B</t>
         </is>
       </c>
       <c r="E346" s="13" t="inlineStr">
         <is>
-          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
+          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
         </is>
       </c>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>F-VC-18</t>
+          <t>F-VC-06, F-VC-10</t>
         </is>
       </c>
       <c r="G346" s="13" t="inlineStr"/>
@@ -13902,7 +13933,7 @@
       </c>
       <c r="B347" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-34</t>
+          <t>TC-VC-17</t>
         </is>
       </c>
       <c r="C347" s="18" t="inlineStr">
@@ -13912,17 +13943,17 @@
       </c>
       <c r="D347" s="16" t="inlineStr">
         <is>
-          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
+          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
         </is>
       </c>
       <c r="E347" s="16" t="inlineStr">
         <is>
-          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
+          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
         </is>
       </c>
       <c r="F347" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-12</t>
         </is>
       </c>
       <c r="G347" s="16" t="inlineStr"/>
@@ -13937,7 +13968,7 @@
       </c>
       <c r="B348" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-35</t>
+          <t>TC-VC-18</t>
         </is>
       </c>
       <c r="C348" s="15" t="inlineStr">
@@ -13947,17 +13978,17 @@
       </c>
       <c r="D348" s="13" t="inlineStr">
         <is>
-          <t>Perbaiki kuncinya lalu jalankan lagi</t>
+          <t>Pasang voucher lalu selesaikan pesanan</t>
         </is>
       </c>
       <c r="E348" s="13" t="inlineStr">
         <is>
-          <t>Baris yang tadi gagal terkirim</t>
+          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
         </is>
       </c>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G348" s="13" t="inlineStr"/>
@@ -13972,7 +14003,7 @@
       </c>
       <c r="B349" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-36</t>
+          <t>TC-VC-19</t>
         </is>
       </c>
       <c r="C349" s="18" t="inlineStr">
@@ -13982,17 +14013,17 @@
       </c>
       <c r="D349" s="16" t="inlineStr">
         <is>
-          <t>Pakai voucher di resto yang belum punya sub-akun</t>
+          <t>Ketuk Lepas setelah voucher terpasang</t>
         </is>
       </c>
       <c r="E349" s="16" t="inlineStr">
         <is>
-          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
+          <t>Tagihan kembali ke nominal semula</t>
         </is>
       </c>
       <c r="F349" s="16" t="inlineStr">
         <is>
-          <t>F-VC-19</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G349" s="16" t="inlineStr"/>
@@ -14007,7 +14038,7 @@
       </c>
       <c r="B350" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-37</t>
+          <t>TC-VC-20</t>
         </is>
       </c>
       <c r="C350" s="15" t="inlineStr">
@@ -14017,17 +14048,17 @@
       </c>
       <c r="D350" s="13" t="inlineStr">
         <is>
-          <t>Buat pesanan bervoucher saat Xendit mati total</t>
+          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
         </is>
       </c>
       <c r="E350" s="13" t="inlineStr">
         <is>
-          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
+          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
         </is>
       </c>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G350" s="13" t="inlineStr"/>
@@ -14042,27 +14073,27 @@
       </c>
       <c r="B351" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-38</t>
-        </is>
-      </c>
-      <c r="C351" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-21</t>
+        </is>
+      </c>
+      <c r="C351" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D351" s="16" t="inlineStr">
         <is>
-          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
+          <t>Periksa Jurnal GL restonya</t>
         </is>
       </c>
       <c r="E351" s="16" t="inlineStr">
         <is>
-          <t>Klaim used lama ikut terantre</t>
+          <t>Ada baris masuk sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F351" s="16" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G351" s="16" t="inlineStr"/>
@@ -14077,27 +14108,27 @@
       </c>
       <c r="B352" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-39</t>
-        </is>
-      </c>
-      <c r="C352" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-22</t>
+        </is>
+      </c>
+      <c r="C352" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D352" s="13" t="inlineStr">
         <is>
-          <t>Tulis langsung ke voucher_payouts lewat API</t>
+          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
         </is>
       </c>
       <c r="E352" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
+          <t>Tidak muncul di daftar pilihan</t>
         </is>
       </c>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>F-VC-18</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G352" s="13" t="inlineStr"/>
@@ -14112,27 +14143,27 @@
       </c>
       <c r="B353" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-40</t>
-        </is>
-      </c>
-      <c r="C353" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-23</t>
+        </is>
+      </c>
+      <c r="C353" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D353" s="16" t="inlineStr">
         <is>
-          <t>Baca voucher_payout_config sebagai Super Admin</t>
+          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
         </is>
       </c>
       <c r="E353" s="16" t="inlineStr">
         <is>
-          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
+          <t>Debit Voucher Redeem, kredit Total Saldo</t>
         </is>
       </c>
       <c r="F353" s="16" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G353" s="16" t="inlineStr"/>
@@ -14147,27 +14178,27 @@
       </c>
       <c r="B354" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-41</t>
-        </is>
-      </c>
-      <c r="C354" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-24</t>
+        </is>
+      </c>
+      <c r="C354" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D354" s="13" t="inlineStr">
         <is>
-          <t>Jalankan penjadwal sebelum function_url diisi</t>
+          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
         </is>
       </c>
       <c r="E354" s="13" t="inlineStr">
         <is>
-          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
+          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
         </is>
       </c>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G354" s="13" t="inlineStr"/>
@@ -14182,7 +14213,7 @@
       </c>
       <c r="B355" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-42</t>
+          <t>TC-VC-25</t>
         </is>
       </c>
       <c r="C355" s="18" t="inlineStr">
@@ -14192,17 +14223,17 @@
       </c>
       <c r="D355" s="16" t="inlineStr">
         <is>
-          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
+          <t>Jalankan expire_vouchers() dua kali</t>
         </is>
       </c>
       <c r="E355" s="16" t="inlineStr">
         <is>
-          <t>Cocok baris per baris lewat transfer_id</t>
+          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
         </is>
       </c>
       <c r="F355" s="16" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G355" s="16" t="inlineStr"/>
@@ -14217,7 +14248,7 @@
       </c>
       <c r="B356" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-43</t>
+          <t>TC-VC-26</t>
         </is>
       </c>
       <c r="C356" s="15" t="inlineStr">
@@ -14227,17 +14258,17 @@
       </c>
       <c r="D356" s="13" t="inlineStr">
         <is>
-          <t>Jalankan pencairan saat xenPlatform belum aktif</t>
+          <t>Jumlahkan keempat tahap untuk satu batch</t>
         </is>
       </c>
       <c r="E356" s="13" t="inlineStr">
         <is>
-          <t>Seluruh antrean tetap pending, attempts nol, tidak ada galat</t>
+          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
         </is>
       </c>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>F-VC-19</t>
+          <t>F-VC-13, F-VC-14</t>
         </is>
       </c>
       <c r="G356" s="13" t="inlineStr"/>
@@ -14252,27 +14283,27 @@
       </c>
       <c r="B357" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-44</t>
-        </is>
-      </c>
-      <c r="C357" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-27</t>
+        </is>
+      </c>
+      <c r="C357" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D357" s="16" t="inlineStr">
         <is>
-          <t>Aktifkan xenPlatform + pasang sub-akun, lalu tunggu penjadwal</t>
+          <t>Tulis langsung ke voucher_claims lewat API</t>
         </is>
       </c>
       <c r="E357" s="16" t="inlineStr">
         <is>
-          <t>Tunggakan lama ikut terangkut tanpa dijalankan ulang manual</t>
+          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F357" s="16" t="inlineStr">
         <is>
-          <t>F-VC-16, F-VC-17</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G357" s="16" t="inlineStr"/>
@@ -14282,12 +14313,12 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B358" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-VC-28</t>
         </is>
       </c>
       <c r="C358" s="15" t="inlineStr">
@@ -14297,17 +14328,17 @@
       </c>
       <c r="D358" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
         </is>
       </c>
       <c r="E358" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
         </is>
       </c>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G358" s="13" t="inlineStr"/>
@@ -14317,32 +14348,32 @@
     <row r="359">
       <c r="A359" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B359" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
-        </is>
-      </c>
-      <c r="C359" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-29</t>
+        </is>
+      </c>
+      <c r="C359" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D359" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Periksa kartu batch di layar Super Admin</t>
         </is>
       </c>
       <c r="E359" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
         </is>
       </c>
       <c r="F359" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-15</t>
         </is>
       </c>
       <c r="G359" s="16" t="inlineStr"/>
@@ -14352,32 +14383,32 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B360" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
-        </is>
-      </c>
-      <c r="C360" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-30</t>
+        </is>
+      </c>
+      <c r="C360" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D360" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Tutup sebuah batch yang kuotanya masih ada</t>
         </is>
       </c>
       <c r="E360" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-04</t>
         </is>
       </c>
       <c r="G360" s="13" t="inlineStr"/>
@@ -14387,12 +14418,12 @@
     <row r="361">
       <c r="A361" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B361" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
+          <t>TC-VC-31</t>
         </is>
       </c>
       <c r="C361" s="18" t="inlineStr">
@@ -14402,17 +14433,17 @@
       </c>
       <c r="D361" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
         </is>
       </c>
       <c r="E361" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F361" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G361" s="16" t="inlineStr"/>
@@ -14422,12 +14453,12 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B362" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-VC-32</t>
         </is>
       </c>
       <c r="C362" s="15" t="inlineStr">
@@ -14437,17 +14468,17 @@
       </c>
       <c r="D362" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Jalankan settle-voucher-payouts</t>
         </is>
       </c>
       <c r="E362" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
         </is>
       </c>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G362" s="13" t="inlineStr"/>
@@ -14457,12 +14488,12 @@
     <row r="363">
       <c r="A363" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B363" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-VC-33</t>
         </is>
       </c>
       <c r="C363" s="18" t="inlineStr">
@@ -14472,17 +14503,17 @@
       </c>
       <c r="D363" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Jalankan fungsinya dua kali berturut-turut</t>
         </is>
       </c>
       <c r="E363" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
         </is>
       </c>
       <c r="F363" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G363" s="16" t="inlineStr"/>
@@ -14492,12 +14523,12 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B364" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-VC-34</t>
         </is>
       </c>
       <c r="C364" s="15" t="inlineStr">
@@ -14507,17 +14538,17 @@
       </c>
       <c r="D364" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
         </is>
       </c>
       <c r="E364" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
         </is>
       </c>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G364" s="13" t="inlineStr"/>
@@ -14527,12 +14558,12 @@
     <row r="365">
       <c r="A365" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B365" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
+          <t>TC-VC-35</t>
         </is>
       </c>
       <c r="C365" s="18" t="inlineStr">
@@ -14542,17 +14573,17 @@
       </c>
       <c r="D365" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Perbaiki kuncinya lalu jalankan lagi</t>
         </is>
       </c>
       <c r="E365" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Baris yang tadi gagal terkirim</t>
         </is>
       </c>
       <c r="F365" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G365" s="16" t="inlineStr"/>
@@ -14562,12 +14593,12 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B366" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-VC-36</t>
         </is>
       </c>
       <c r="C366" s="15" t="inlineStr">
@@ -14577,17 +14608,17 @@
       </c>
       <c r="D366" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Pakai voucher di resto yang belum punya sub-akun</t>
         </is>
       </c>
       <c r="E366" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
         </is>
       </c>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G366" s="13" t="inlineStr"/>
@@ -14597,12 +14628,12 @@
     <row r="367">
       <c r="A367" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B367" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-VC-37</t>
         </is>
       </c>
       <c r="C367" s="18" t="inlineStr">
@@ -14612,17 +14643,17 @@
       </c>
       <c r="D367" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Buat pesanan bervoucher saat Xendit mati total</t>
         </is>
       </c>
       <c r="E367" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
         </is>
       </c>
       <c r="F367" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G367" s="16" t="inlineStr"/>
@@ -14632,12 +14663,12 @@
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B368" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
+          <t>TC-VC-38</t>
         </is>
       </c>
       <c r="C368" s="19" t="inlineStr">
@@ -14647,17 +14678,17 @@
       </c>
       <c r="D368" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
         </is>
       </c>
       <c r="E368" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Klaim used lama ikut terantre</t>
         </is>
       </c>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G368" s="13" t="inlineStr"/>
@@ -14667,32 +14698,32 @@
     <row r="369">
       <c r="A369" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B369" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C369" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-39</t>
+        </is>
+      </c>
+      <c r="C369" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D369" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Tulis langsung ke voucher_payouts lewat API</t>
         </is>
       </c>
       <c r="E369" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F369" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G369" s="16" t="inlineStr"/>
@@ -14702,12 +14733,12 @@
     <row r="370">
       <c r="A370" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B370" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
+          <t>TC-VC-40</t>
         </is>
       </c>
       <c r="C370" s="19" t="inlineStr">
@@ -14717,17 +14748,17 @@
       </c>
       <c r="D370" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Baca voucher_payout_config sebagai Super Admin</t>
         </is>
       </c>
       <c r="E370" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
         </is>
       </c>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G370" s="13" t="inlineStr"/>
@@ -14737,32 +14768,32 @@
     <row r="371">
       <c r="A371" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B371" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
-        </is>
-      </c>
-      <c r="C371" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-41</t>
+        </is>
+      </c>
+      <c r="C371" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D371" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Jalankan penjadwal sebelum function_url diisi</t>
         </is>
       </c>
       <c r="E371" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
         </is>
       </c>
       <c r="F371" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G371" s="16" t="inlineStr"/>
@@ -14772,12 +14803,12 @@
     <row r="372">
       <c r="A372" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B372" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
+          <t>TC-VC-42</t>
         </is>
       </c>
       <c r="C372" s="15" t="inlineStr">
@@ -14787,17 +14818,17 @@
       </c>
       <c r="D372" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
         </is>
       </c>
       <c r="E372" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Cocok baris per baris lewat transfer_id</t>
         </is>
       </c>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G372" s="13" t="inlineStr"/>
@@ -14807,12 +14838,12 @@
     <row r="373">
       <c r="A373" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B373" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-VC-43</t>
         </is>
       </c>
       <c r="C373" s="18" t="inlineStr">
@@ -14822,17 +14853,17 @@
       </c>
       <c r="D373" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Jalankan pencairan saat xenPlatform belum aktif</t>
         </is>
       </c>
       <c r="E373" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Seluruh antrean tetap pending, attempts nol, tidak ada galat</t>
         </is>
       </c>
       <c r="F373" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G373" s="16" t="inlineStr"/>
@@ -14842,12 +14873,12 @@
     <row r="374">
       <c r="A374" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B374" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
+          <t>TC-VC-44</t>
         </is>
       </c>
       <c r="C374" s="19" t="inlineStr">
@@ -14857,17 +14888,17 @@
       </c>
       <c r="D374" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Aktifkan xenPlatform + pasang sub-akun, lalu tunggu penjadwal</t>
         </is>
       </c>
       <c r="E374" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Tunggakan lama ikut terangkut tanpa dijalankan ulang manual</t>
         </is>
       </c>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>F-VC-16, F-VC-17</t>
         </is>
       </c>
       <c r="G374" s="13" t="inlineStr"/>
@@ -14877,32 +14908,32 @@
     <row r="375">
       <c r="A375" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B375" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C375" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-45</t>
+        </is>
+      </c>
+      <c r="C375" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D375" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Super Admin → Finance → Pemetaan GL</t>
         </is>
       </c>
       <c r="E375" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Ada bagian GL Voucher berisi GL Voucher dan GL Voucher Redeem</t>
         </is>
       </c>
       <c r="F375" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G375" s="16" t="inlineStr"/>
@@ -14912,32 +14943,32 @@
     <row r="376">
       <c r="A376" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B376" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C376" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-46</t>
+        </is>
+      </c>
+      <c r="C376" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D376" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Buka Pemetaan GL sebagai Finance resto biasa</t>
         </is>
       </c>
       <c r="E376" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Bagian GL Voucher tidak muncul, penanda "belum dipetakan" tidak berbunyi</t>
         </is>
       </c>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G376" s="13" t="inlineStr"/>
@@ -14947,32 +14978,32 @@
     <row r="377">
       <c r="A377" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B377" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
-        </is>
-      </c>
-      <c r="C377" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-47</t>
+        </is>
+      </c>
+      <c r="C377" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D377" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Ubah nomor GL Voucher lalu simpan</t>
         </is>
       </c>
       <c r="E377" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Tersimpan, dan jurnal voucher berikutnya memakai nomor baru</t>
         </is>
       </c>
       <c r="F377" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G377" s="16" t="inlineStr"/>
@@ -14982,12 +15013,12 @@
     <row r="378">
       <c r="A378" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B378" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
+          <t>TC-VC-48</t>
         </is>
       </c>
       <c r="C378" s="15" t="inlineStr">
@@ -14997,17 +15028,17 @@
       </c>
       <c r="D378" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Terbitkan batch, lalu buka Kotak Masuk pelanggan</t>
         </is>
       </c>
       <c r="E378" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Ada kabar di tab Umum berisi kode, nilai, kuota, dan tenggat</t>
         </is>
       </c>
       <c r="F378" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>F-VC-20, F-VC-21</t>
         </is>
       </c>
       <c r="G378" s="13" t="inlineStr"/>
@@ -15017,12 +15048,12 @@
     <row r="379">
       <c r="A379" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B379" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
+          <t>TC-VC-49</t>
         </is>
       </c>
       <c r="C379" s="18" t="inlineStr">
@@ -15032,17 +15063,17 @@
       </c>
       <c r="D379" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Terbitkan batch dengan HP pelanggan terkunci</t>
         </is>
       </c>
       <c r="E379" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Push muncul di layar kunci</t>
         </is>
       </c>
       <c r="F379" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>F-VC-20</t>
         </is>
       </c>
       <c r="G379" s="16" t="inlineStr"/>
@@ -15052,32 +15083,32 @@
     <row r="380">
       <c r="A380" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B380" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
-        </is>
-      </c>
-      <c r="C380" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-50</t>
+        </is>
+      </c>
+      <c r="C380" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D380" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Terbitkan batch tanpa minimal belanja</t>
         </is>
       </c>
       <c r="E380" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Kalimat minimal belanja tidak muncul di pengumuman</t>
         </is>
       </c>
       <c r="F380" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>F-VC-21</t>
         </is>
       </c>
       <c r="G380" s="13" t="inlineStr"/>
@@ -15087,32 +15118,32 @@
     <row r="381">
       <c r="A381" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B381" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
-        </is>
-      </c>
-      <c r="C381" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-51</t>
+        </is>
+      </c>
+      <c r="C381" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D381" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Buka Kotak Masuk sebagai pegawai resto</t>
         </is>
       </c>
       <c r="E381" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Kabar voucher tidak muncul — audiensnya pelanggan</t>
         </is>
       </c>
       <c r="F381" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>F-VC-20</t>
         </is>
       </c>
       <c r="G381" s="16" t="inlineStr"/>
@@ -15122,32 +15153,32 @@
     <row r="382">
       <c r="A382" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B382" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
-        </is>
-      </c>
-      <c r="C382" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-52</t>
+        </is>
+      </c>
+      <c r="C382" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D382" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Ketik nama resto di kolom cari pada form terbit</t>
         </is>
       </c>
       <c r="E382" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Daftarnya menyusut sesuai kata kuncinya</t>
         </is>
       </c>
       <c r="F382" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G382" s="13" t="inlineStr"/>
@@ -15157,32 +15188,32 @@
     <row r="383">
       <c r="A383" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B383" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C383" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-53</t>
+        </is>
+      </c>
+      <c r="C383" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D383" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Centang 3 resto, lalu cari kata yang menyaringnya keluar</t>
         </is>
       </c>
       <c r="E383" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Ketiganya tetap terpilih; hitungannya tidak berubah</t>
         </is>
       </c>
       <c r="F383" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G383" s="16" t="inlineStr"/>
@@ -15192,32 +15223,32 @@
     <row r="384">
       <c r="A384" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B384" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C384" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-54</t>
+        </is>
+      </c>
+      <c r="C384" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D384" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Saring daftarnya, lalu ketuk Pilih semua</t>
         </is>
       </c>
       <c r="E384" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Hanya yang tampil tercentang, bukan seluruh resto</t>
         </is>
       </c>
       <c r="F384" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G384" s="13" t="inlineStr"/>
@@ -15227,12 +15258,12 @@
     <row r="385">
       <c r="A385" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B385" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
+          <t>TC-VC-55</t>
         </is>
       </c>
       <c r="C385" s="20" t="inlineStr">
@@ -15242,17 +15273,17 @@
       </c>
       <c r="D385" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Ketuk Lepas semua saat semua yang tampil tercentang</t>
         </is>
       </c>
       <c r="E385" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Yang tampil terlepas; pilihan di luar saringan tetap</t>
         </is>
       </c>
       <c r="F385" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G385" s="16" t="inlineStr"/>
@@ -15262,12 +15293,12 @@
     <row r="386">
       <c r="A386" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B386" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
+          <t>TC-VC-56</t>
         </is>
       </c>
       <c r="C386" s="19" t="inlineStr">
@@ -15277,17 +15308,17 @@
       </c>
       <c r="D386" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Cari nama resto yang tidak ada</t>
         </is>
       </c>
       <c r="E386" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Muncul "Tidak ada resto bernama itu"</t>
         </is>
       </c>
       <c r="F386" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G386" s="13" t="inlineStr"/>
@@ -15297,32 +15328,32 @@
     <row r="387">
       <c r="A387" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B387" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
-        </is>
-      </c>
-      <c r="C387" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-57</t>
+        </is>
+      </c>
+      <c r="C387" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D387" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Terbitkan batch berbanner, lalu buka Kotak Masuk pelanggan</t>
         </is>
       </c>
       <c r="E387" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Gambarnya tampil bersama kabarnya</t>
         </is>
       </c>
       <c r="F387" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>F-VC-23</t>
         </is>
       </c>
       <c r="G387" s="16" t="inlineStr"/>
@@ -15332,12 +15363,12 @@
     <row r="388">
       <c r="A388" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B388" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
+          <t>TC-VC-58</t>
         </is>
       </c>
       <c r="C388" s="19" t="inlineStr">
@@ -15347,17 +15378,17 @@
       </c>
       <c r="D388" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Pilih gambar potret, lihat pratinjaunya</t>
         </is>
       </c>
       <c r="E388" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Dipotong 16:9, sama dengan yang nanti muncul di kotak masuk</t>
         </is>
       </c>
       <c r="F388" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>F-VC-23</t>
         </is>
       </c>
       <c r="G388" s="13" t="inlineStr"/>
@@ -15367,32 +15398,32 @@
     <row r="389">
       <c r="A389" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B389" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
-        </is>
-      </c>
-      <c r="C389" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-59</t>
+        </is>
+      </c>
+      <c r="C389" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D389" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Terbitkan batch tanpa banner</t>
         </is>
       </c>
       <c r="E389" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Kabarnya tetap terkirim, tanpa gambar</t>
         </is>
       </c>
       <c r="F389" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-VC-23</t>
         </is>
       </c>
       <c r="G389" s="16" t="inlineStr"/>
@@ -15402,32 +15433,32 @@
     <row r="390">
       <c r="A390" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B390" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
-        </is>
-      </c>
-      <c r="C390" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-60</t>
+        </is>
+      </c>
+      <c r="C390" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D390" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Cari tombol Hapus pada batch yang masih berjalan</t>
         </is>
       </c>
       <c r="E390" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Tidak ada — harus ditutup dulu</t>
         </is>
       </c>
       <c r="F390" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G390" s="13" t="inlineStr"/>
@@ -15437,25 +15468,1915 @@
     <row r="391">
       <c r="A391" s="16" t="inlineStr">
         <is>
+          <t>## 19d. Voucher Pelanggan</t>
+        </is>
+      </c>
+      <c r="B391" s="17" t="inlineStr">
+        <is>
+          <t>TC-VC-61</t>
+        </is>
+      </c>
+      <c r="C391" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D391" s="16" t="inlineStr">
+        <is>
+          <t>Tutup batch yang belum ada penebusnya, lalu hapus</t>
+        </is>
+      </c>
+      <c r="E391" s="16" t="inlineStr">
+        <is>
+          <t>Terhapus; dananya kembali ke GL Total Saldo</t>
+        </is>
+      </c>
+      <c r="F391" s="16" t="inlineStr">
+        <is>
+          <t>F-VC-24</t>
+        </is>
+      </c>
+      <c r="G391" s="16" t="inlineStr"/>
+      <c r="H391" s="16" t="inlineStr"/>
+      <c r="I391" s="16" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="13" t="inlineStr">
+        <is>
+          <t>## 19d. Voucher Pelanggan</t>
+        </is>
+      </c>
+      <c r="B392" s="14" t="inlineStr">
+        <is>
+          <t>TC-VC-62</t>
+        </is>
+      </c>
+      <c r="C392" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D392" s="13" t="inlineStr">
+        <is>
+          <t>Periksa Kotak Masuk pelanggan sesudah batch dihapus</t>
+        </is>
+      </c>
+      <c r="E392" s="13" t="inlineStr">
+        <is>
+          <t>Kabar vouchernya ikut hilang</t>
+        </is>
+      </c>
+      <c r="F392" s="13" t="inlineStr">
+        <is>
+          <t>F-VC-24</t>
+        </is>
+      </c>
+      <c r="G392" s="13" t="inlineStr"/>
+      <c r="H392" s="13" t="inlineStr"/>
+      <c r="I392" s="13" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="16" t="inlineStr">
+        <is>
+          <t>## 19d. Voucher Pelanggan</t>
+        </is>
+      </c>
+      <c r="B393" s="17" t="inlineStr">
+        <is>
+          <t>TC-VC-63</t>
+        </is>
+      </c>
+      <c r="C393" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D393" s="16" t="inlineStr">
+        <is>
+          <t>Panggil delete_voucher_batch untuk batch yang sudah ada penebusnya</t>
+        </is>
+      </c>
+      <c r="E393" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak, dengan jumlah penebusnya disebut</t>
+        </is>
+      </c>
+      <c r="F393" s="16" t="inlineStr">
+        <is>
+          <t>F-VC-24</t>
+        </is>
+      </c>
+      <c r="G393" s="16" t="inlineStr"/>
+      <c r="H393" s="16" t="inlineStr"/>
+      <c r="I393" s="16" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="13" t="inlineStr">
+        <is>
+          <t>## 19d. Voucher Pelanggan</t>
+        </is>
+      </c>
+      <c r="B394" s="14" t="inlineStr">
+        <is>
+          <t>TC-VC-64</t>
+        </is>
+      </c>
+      <c r="C394" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D394" s="13" t="inlineStr">
+        <is>
+          <t>Panggil delete_voucher_batch sebagai bukan Super Admin</t>
+        </is>
+      </c>
+      <c r="E394" s="13" t="inlineStr">
+        <is>
+          <t>Ditolak</t>
+        </is>
+      </c>
+      <c r="F394" s="13" t="inlineStr">
+        <is>
+          <t>F-VC-24</t>
+        </is>
+      </c>
+      <c r="G394" s="13" t="inlineStr"/>
+      <c r="H394" s="13" t="inlineStr"/>
+      <c r="I394" s="13" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="16" t="inlineStr">
+        <is>
+          <t>## 19d. Voucher Pelanggan</t>
+        </is>
+      </c>
+      <c r="B395" s="17" t="inlineStr">
+        <is>
+          <t>TC-VC-65</t>
+        </is>
+      </c>
+      <c r="C395" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D395" s="16" t="inlineStr">
+        <is>
+          <t>Hapus batch yang sudah pernah disettle penjadwal</t>
+        </is>
+      </c>
+      <c r="E395" s="16" t="inlineStr">
+        <is>
+          <t>Dananya tidak dikembalikan dua kali</t>
+        </is>
+      </c>
+      <c r="F395" s="16" t="inlineStr">
+        <is>
+          <t>F-VC-24</t>
+        </is>
+      </c>
+      <c r="G395" s="16" t="inlineStr"/>
+      <c r="H395" s="16" t="inlineStr"/>
+      <c r="I395" s="16" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="13" t="inlineStr">
+        <is>
+          <t>## 19d. Voucher Pelanggan</t>
+        </is>
+      </c>
+      <c r="B396" s="14" t="inlineStr">
+        <is>
+          <t>TC-VC-66</t>
+        </is>
+      </c>
+      <c r="C396" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D396" s="13" t="inlineStr">
+        <is>
+          <t>Ketuk Penebus pada sebuah batch</t>
+        </is>
+      </c>
+      <c r="E396" s="13" t="inlineStr">
+        <is>
+          <t>Daftar email penebut berikut tanggal tebus dan statusnya</t>
+        </is>
+      </c>
+      <c r="F396" s="13" t="inlineStr">
+        <is>
+          <t>F-VC-25</t>
+        </is>
+      </c>
+      <c r="G396" s="13" t="inlineStr"/>
+      <c r="H396" s="13" t="inlineStr"/>
+      <c r="I396" s="13" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="16" t="inlineStr">
+        <is>
+          <t>## 19d. Voucher Pelanggan</t>
+        </is>
+      </c>
+      <c r="B397" s="17" t="inlineStr">
+        <is>
+          <t>TC-VC-67</t>
+        </is>
+      </c>
+      <c r="C397" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D397" s="16" t="inlineStr">
+        <is>
+          <t>Periksa ringkasan di atas daftar penebus</t>
+        </is>
+      </c>
+      <c r="E397" s="16" t="inlineStr">
+        <is>
+          <t>Dipakai / Menggantung / Hangus berjumlah sama dengan barisnya</t>
+        </is>
+      </c>
+      <c r="F397" s="16" t="inlineStr">
+        <is>
+          <t>F-VC-25</t>
+        </is>
+      </c>
+      <c r="G397" s="16" t="inlineStr"/>
+      <c r="H397" s="16" t="inlineStr"/>
+      <c r="I397" s="16" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="13" t="inlineStr">
+        <is>
+          <t>## 19d. Voucher Pelanggan</t>
+        </is>
+      </c>
+      <c r="B398" s="14" t="inlineStr">
+        <is>
+          <t>TC-VC-68</t>
+        </is>
+      </c>
+      <c r="C398" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D398" s="13" t="inlineStr">
+        <is>
+          <t>Lewati tanggal kedaluwarsa sebelum penjadwal berjalan</t>
+        </is>
+      </c>
+      <c r="E398" s="13" t="inlineStr">
+        <is>
+          <t>Statusnya sudah Hangus, bukan Belum Dipakai</t>
+        </is>
+      </c>
+      <c r="F398" s="13" t="inlineStr">
+        <is>
+          <t>F-VC-25</t>
+        </is>
+      </c>
+      <c r="G398" s="13" t="inlineStr"/>
+      <c r="H398" s="13" t="inlineStr"/>
+      <c r="I398" s="13" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="16" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B399" s="17" t="inlineStr">
+        <is>
+          <t>TC-MR-01</t>
+        </is>
+      </c>
+      <c r="C399" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D399" s="16" t="inlineStr">
+        <is>
+          <t>Super Admin → Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="E399" s="16" t="inlineStr">
+        <is>
+          <t>Empat bagian termuat tanpa galat</t>
+        </is>
+      </c>
+      <c r="F399" s="16" t="inlineStr">
+        <is>
+          <t>F-MR-01…04</t>
+        </is>
+      </c>
+      <c r="G399" s="16" t="inlineStr"/>
+      <c r="H399" s="16" t="inlineStr"/>
+      <c r="I399" s="16" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="13" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B400" s="14" t="inlineStr">
+        <is>
+          <t>TC-MR-02</t>
+        </is>
+      </c>
+      <c r="C400" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D400" s="13" t="inlineStr">
+        <is>
+          <t>Bandingkan Top 5 Pelanggan dengan jumlah manual dari orders</t>
+        </is>
+      </c>
+      <c r="E400" s="13" t="inlineStr">
+        <is>
+          <t>Cocok nominal dan jumlah pesanannya</t>
+        </is>
+      </c>
+      <c r="F400" s="13" t="inlineStr">
+        <is>
+          <t>F-MR-01</t>
+        </is>
+      </c>
+      <c r="G400" s="13" t="inlineStr"/>
+      <c r="H400" s="13" t="inlineStr"/>
+      <c r="I400" s="13" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="16" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B401" s="17" t="inlineStr">
+        <is>
+          <t>TC-MR-03</t>
+        </is>
+      </c>
+      <c r="C401" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D401" s="16" t="inlineStr">
+        <is>
+          <t>Batalkan sebuah pesanan besar, muat ulang</t>
+        </is>
+      </c>
+      <c r="E401" s="16" t="inlineStr">
+        <is>
+          <t>Nominalnya berkurang — yang batal tidak dihitung</t>
+        </is>
+      </c>
+      <c r="F401" s="16" t="inlineStr">
+        <is>
+          <t>F-MR-05</t>
+        </is>
+      </c>
+      <c r="G401" s="16" t="inlineStr"/>
+      <c r="H401" s="16" t="inlineStr"/>
+      <c r="I401" s="16" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="13" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B402" s="14" t="inlineStr">
+        <is>
+          <t>TC-MR-04</t>
+        </is>
+      </c>
+      <c r="C402" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D402" s="13" t="inlineStr">
+        <is>
+          <t>Buat akun pelanggan baru tanpa memesan</t>
+        </is>
+      </c>
+      <c r="E402" s="13" t="inlineStr">
+        <is>
+          <t>Muncul di daftar Belum Pernah Memesan</t>
+        </is>
+      </c>
+      <c r="F402" s="13" t="inlineStr">
+        <is>
+          <t>F-MR-02</t>
+        </is>
+      </c>
+      <c r="G402" s="13" t="inlineStr"/>
+      <c r="H402" s="13" t="inlineStr"/>
+      <c r="I402" s="13" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="16" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B403" s="17" t="inlineStr">
+        <is>
+          <t>TC-MR-05</t>
+        </is>
+      </c>
+      <c r="C403" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D403" s="16" t="inlineStr">
+        <is>
+          <t>Pelanggan itu menyelesaikan satu pesanan, muat ulang</t>
+        </is>
+      </c>
+      <c r="E403" s="16" t="inlineStr">
+        <is>
+          <t>Hilang dari daftar tersebut</t>
+        </is>
+      </c>
+      <c r="F403" s="16" t="inlineStr">
+        <is>
+          <t>F-MR-02</t>
+        </is>
+      </c>
+      <c r="G403" s="16" t="inlineStr"/>
+      <c r="H403" s="16" t="inlineStr"/>
+      <c r="I403" s="16" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="13" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B404" s="14" t="inlineStr">
+        <is>
+          <t>TC-MR-06</t>
+        </is>
+      </c>
+      <c r="C404" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D404" s="13" t="inlineStr">
+        <is>
+          <t>Bandingkan Top 5 Resto dengan Jurnal GL resto bersangkutan</t>
+        </is>
+      </c>
+      <c r="E404" s="13" t="inlineStr">
+        <is>
+          <t>Nominalnya sejalan</t>
+        </is>
+      </c>
+      <c r="F404" s="13" t="inlineStr">
+        <is>
+          <t>F-MR-03</t>
+        </is>
+      </c>
+      <c r="G404" s="13" t="inlineStr"/>
+      <c r="H404" s="13" t="inlineStr"/>
+      <c r="I404" s="13" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="16" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B405" s="17" t="inlineStr">
+        <is>
+          <t>TC-MR-07</t>
+        </is>
+      </c>
+      <c r="C405" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D405" s="16" t="inlineStr">
+        <is>
+          <t>Resto yang seluruh pesanannya batal</t>
+        </is>
+      </c>
+      <c r="E405" s="16" t="inlineStr">
+        <is>
+          <t>Muncul di Belum Ada Penghasilan, jumlah pesanan 0</t>
+        </is>
+      </c>
+      <c r="F405" s="16" t="inlineStr">
+        <is>
+          <t>F-MR-04</t>
+        </is>
+      </c>
+      <c r="G405" s="16" t="inlineStr"/>
+      <c r="H405" s="16" t="inlineStr"/>
+      <c r="I405" s="16" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="13" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B406" s="14" t="inlineStr">
+        <is>
+          <t>TC-MR-08</t>
+        </is>
+      </c>
+      <c r="C406" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D406" s="13" t="inlineStr">
+        <is>
+          <t>Resto baru tanpa pesanan sama sekali</t>
+        </is>
+      </c>
+      <c r="E406" s="13" t="inlineStr">
+        <is>
+          <t>Muncul dengan "Belum ada pesanan"</t>
+        </is>
+      </c>
+      <c r="F406" s="13" t="inlineStr">
+        <is>
+          <t>F-MR-04</t>
+        </is>
+      </c>
+      <c r="G406" s="13" t="inlineStr"/>
+      <c r="H406" s="13" t="inlineStr"/>
+      <c r="I406" s="13" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="16" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B407" s="17" t="inlineStr">
+        <is>
+          <t>TC-MR-09</t>
+        </is>
+      </c>
+      <c r="C407" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D407" s="16" t="inlineStr">
+        <is>
+          <t>Periksa apakah resto KaataGo ikut terhitung</t>
+        </is>
+      </c>
+      <c r="E407" s="16" t="inlineStr">
+        <is>
+          <t>Tidak — resto platform dikecualikan</t>
+        </is>
+      </c>
+      <c r="F407" s="16" t="inlineStr">
+        <is>
+          <t>F-MR-06</t>
+        </is>
+      </c>
+      <c r="G407" s="16" t="inlineStr"/>
+      <c r="H407" s="16" t="inlineStr"/>
+      <c r="I407" s="16" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="13" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B408" s="14" t="inlineStr">
+        <is>
+          <t>TC-MR-10</t>
+        </is>
+      </c>
+      <c r="C408" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D408" s="13" t="inlineStr">
+        <is>
+          <t>Hapus lunak sebuah resto, muat ulang</t>
+        </is>
+      </c>
+      <c r="E408" s="13" t="inlineStr">
+        <is>
+          <t>Hilang dari keempat daftar</t>
+        </is>
+      </c>
+      <c r="F408" s="13" t="inlineStr">
+        <is>
+          <t>F-MR-06</t>
+        </is>
+      </c>
+      <c r="G408" s="13" t="inlineStr"/>
+      <c r="H408" s="13" t="inlineStr"/>
+      <c r="I408" s="13" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="16" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B409" s="17" t="inlineStr">
+        <is>
+          <t>TC-MR-11</t>
+        </is>
+      </c>
+      <c r="C409" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D409" s="16" t="inlineStr">
+        <is>
+          <t>Panggil report_top_customers sebagai Owner resto</t>
+        </is>
+      </c>
+      <c r="E409" s="16" t="inlineStr">
+        <is>
+          <t>Daftar kosong, bukan pesan galat</t>
+        </is>
+      </c>
+      <c r="F409" s="16" t="inlineStr">
+        <is>
+          <t>F-MR-07</t>
+        </is>
+      </c>
+      <c r="G409" s="16" t="inlineStr"/>
+      <c r="H409" s="16" t="inlineStr"/>
+      <c r="I409" s="16" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="13" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B410" s="14" t="inlineStr">
+        <is>
+          <t>TC-MR-12</t>
+        </is>
+      </c>
+      <c r="C410" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D410" s="13" t="inlineStr">
+        <is>
+          <t>Panggil salah satu RPC dengan p_limit 99999</t>
+        </is>
+      </c>
+      <c r="E410" s="13" t="inlineStr">
+        <is>
+          <t>Dijepit ke batas atasnya</t>
+        </is>
+      </c>
+      <c r="F410" s="13" t="inlineStr">
+        <is>
+          <t>F-MR-07</t>
+        </is>
+      </c>
+      <c r="G410" s="13" t="inlineStr"/>
+      <c r="H410" s="13" t="inlineStr"/>
+      <c r="I410" s="13" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="16" t="inlineStr">
+        <is>
+          <t>## 19e. Analisa Pasar</t>
+        </is>
+      </c>
+      <c r="B411" s="17" t="inlineStr">
+        <is>
+          <t>TC-MR-13</t>
+        </is>
+      </c>
+      <c r="C411" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D411" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan kasir atas nama tamu</t>
+        </is>
+      </c>
+      <c r="E411" s="16" t="inlineStr">
+        <is>
+          <t>Tidak ikut peringkat pelanggan — bukan akun terdaftar</t>
+        </is>
+      </c>
+      <c r="F411" s="16" t="inlineStr">
+        <is>
+          <t>F-MR-01</t>
+        </is>
+      </c>
+      <c r="G411" s="16" t="inlineStr"/>
+      <c r="H411" s="16" t="inlineStr"/>
+      <c r="I411" s="16" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B412" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-01</t>
+        </is>
+      </c>
+      <c r="C412" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D412" s="13" t="inlineStr">
+        <is>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+        </is>
+      </c>
+      <c r="E412" s="13" t="inlineStr">
+        <is>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
+        </is>
+      </c>
+      <c r="F412" s="13" t="inlineStr">
+        <is>
+          <t>TSD §5</t>
+        </is>
+      </c>
+      <c r="G412" s="13" t="inlineStr"/>
+      <c r="H412" s="13" t="inlineStr"/>
+      <c r="I412" s="13" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B413" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-02</t>
+        </is>
+      </c>
+      <c r="C413" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D413" s="16" t="inlineStr">
+        <is>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+        </is>
+      </c>
+      <c r="E413" s="16" t="inlineStr">
+        <is>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
+        </is>
+      </c>
+      <c r="F413" s="16" t="inlineStr">
+        <is>
+          <t>TSD §5</t>
+        </is>
+      </c>
+      <c r="G413" s="16" t="inlineStr"/>
+      <c r="H413" s="16" t="inlineStr"/>
+      <c r="I413" s="16" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B414" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-03</t>
+        </is>
+      </c>
+      <c r="C414" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D414" s="13" t="inlineStr">
+        <is>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+        </is>
+      </c>
+      <c r="E414" s="13" t="inlineStr">
+        <is>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+        </is>
+      </c>
+      <c r="F414" s="13" t="inlineStr">
+        <is>
+          <t>TSD §5</t>
+        </is>
+      </c>
+      <c r="G414" s="13" t="inlineStr"/>
+      <c r="H414" s="13" t="inlineStr"/>
+      <c r="I414" s="13" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B415" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-04</t>
+        </is>
+      </c>
+      <c r="C415" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D415" s="16" t="inlineStr">
+        <is>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+        </is>
+      </c>
+      <c r="E415" s="16" t="inlineStr">
+        <is>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+        </is>
+      </c>
+      <c r="F415" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-13, TSD §5.1</t>
+        </is>
+      </c>
+      <c r="G415" s="16" t="inlineStr"/>
+      <c r="H415" s="16" t="inlineStr"/>
+      <c r="I415" s="16" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B416" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-05</t>
+        </is>
+      </c>
+      <c r="C416" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D416" s="13" t="inlineStr">
+        <is>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+        </is>
+      </c>
+      <c r="E416" s="13" t="inlineStr">
+        <is>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+        </is>
+      </c>
+      <c r="F416" s="13" t="inlineStr">
+        <is>
+          <t>TSD §5.2</t>
+        </is>
+      </c>
+      <c r="G416" s="13" t="inlineStr"/>
+      <c r="H416" s="13" t="inlineStr"/>
+      <c r="I416" s="13" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B417" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-06</t>
+        </is>
+      </c>
+      <c r="C417" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D417" s="16" t="inlineStr">
+        <is>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+        </is>
+      </c>
+      <c r="E417" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak</t>
+        </is>
+      </c>
+      <c r="F417" s="16" t="inlineStr">
+        <is>
+          <t>TSD §5.2</t>
+        </is>
+      </c>
+      <c r="G417" s="16" t="inlineStr"/>
+      <c r="H417" s="16" t="inlineStr"/>
+      <c r="I417" s="16" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B418" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-07</t>
+        </is>
+      </c>
+      <c r="C418" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D418" s="13" t="inlineStr">
+        <is>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+        </is>
+      </c>
+      <c r="E418" s="13" t="inlineStr">
+        <is>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+        </is>
+      </c>
+      <c r="F418" s="13" t="inlineStr">
+        <is>
+          <t>TSD §11</t>
+        </is>
+      </c>
+      <c r="G418" s="13" t="inlineStr"/>
+      <c r="H418" s="13" t="inlineStr"/>
+      <c r="I418" s="13" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B419" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C419" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D419" s="16" t="inlineStr">
+        <is>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+        </is>
+      </c>
+      <c r="E419" s="16" t="inlineStr">
+        <is>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+        </is>
+      </c>
+      <c r="F419" s="16" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G419" s="16" t="inlineStr"/>
+      <c r="H419" s="16" t="inlineStr"/>
+      <c r="I419" s="16" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B420" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C420" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D420" s="13" t="inlineStr">
+        <is>
+          <t>Buat resto baru dari Super Admin</t>
+        </is>
+      </c>
+      <c r="E420" s="13" t="inlineStr">
+        <is>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+        </is>
+      </c>
+      <c r="F420" s="13" t="inlineStr">
+        <is>
+          <t>A-19, TSD §6.2</t>
+        </is>
+      </c>
+      <c r="G420" s="13" t="inlineStr"/>
+      <c r="H420" s="13" t="inlineStr"/>
+      <c r="I420" s="13" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B421" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C421" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D421" s="16" t="inlineStr">
+        <is>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+        </is>
+      </c>
+      <c r="E421" s="16" t="inlineStr">
+        <is>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+        </is>
+      </c>
+      <c r="F421" s="16" t="inlineStr">
+        <is>
+          <t>TSD §6.2</t>
+        </is>
+      </c>
+      <c r="G421" s="16" t="inlineStr"/>
+      <c r="H421" s="16" t="inlineStr"/>
+      <c r="I421" s="16" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B422" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-11</t>
+        </is>
+      </c>
+      <c r="C422" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D422" s="13" t="inlineStr">
+        <is>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+        </is>
+      </c>
+      <c r="E422" s="13" t="inlineStr">
+        <is>
+          <t>Baris masuk, lalu sent_at terisi</t>
+        </is>
+      </c>
+      <c r="F422" s="13" t="inlineStr">
+        <is>
+          <t>TSD §8</t>
+        </is>
+      </c>
+      <c r="G422" s="13" t="inlineStr"/>
+      <c r="H422" s="13" t="inlineStr"/>
+      <c r="I422" s="13" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B423" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C423" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D423" s="16" t="inlineStr">
+        <is>
+          <t>Matikan sambungan, pakai aplikasi</t>
+        </is>
+      </c>
+      <c r="E423" s="16" t="inlineStr">
+        <is>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+        </is>
+      </c>
+      <c r="F423" s="16" t="inlineStr">
+        <is>
+          <t>TSD §10, FSD §5.6</t>
+        </is>
+      </c>
+      <c r="G423" s="16" t="inlineStr"/>
+      <c r="H423" s="16" t="inlineStr"/>
+      <c r="I423" s="16" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B424" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-13</t>
+        </is>
+      </c>
+      <c r="C424" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D424" s="13" t="inlineStr">
+        <is>
+          <t>Sambungkan lagi</t>
+        </is>
+      </c>
+      <c r="E424" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
+        </is>
+      </c>
+      <c r="F424" s="13" t="inlineStr">
+        <is>
+          <t>TSD §10</t>
+        </is>
+      </c>
+      <c r="G424" s="13" t="inlineStr"/>
+      <c r="H424" s="13" t="inlineStr"/>
+      <c r="I424" s="13" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B425" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-14</t>
+        </is>
+      </c>
+      <c r="C425" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D425" s="16" t="inlineStr">
+        <is>
+          <t>Coba bayar QRIS saat luring</t>
+        </is>
+      </c>
+      <c r="E425" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+        </is>
+      </c>
+      <c r="F425" s="16" t="inlineStr">
+        <is>
+          <t>FSD §5.6</t>
+        </is>
+      </c>
+      <c r="G425" s="16" t="inlineStr"/>
+      <c r="H425" s="16" t="inlineStr"/>
+      <c r="I425" s="16" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B426" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C426" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D426" s="13" t="inlineStr">
+        <is>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+        </is>
+      </c>
+      <c r="E426" s="13" t="inlineStr">
+        <is>
+          <t>Nominal yang dipakai tetap dari basis data</t>
+        </is>
+      </c>
+      <c r="F426" s="13" t="inlineStr">
+        <is>
+          <t>TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G426" s="13" t="inlineStr"/>
+      <c r="H426" s="13" t="inlineStr"/>
+      <c r="I426" s="13" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B427" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-16</t>
+        </is>
+      </c>
+      <c r="C427" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D427" s="16" t="inlineStr">
+        <is>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+        </is>
+      </c>
+      <c r="E427" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak</t>
+        </is>
+      </c>
+      <c r="F427" s="16" t="inlineStr">
+        <is>
+          <t>F-PG-02, TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G427" s="16" t="inlineStr"/>
+      <c r="H427" s="16" t="inlineStr"/>
+      <c r="I427" s="16" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B428" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C428" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D428" s="13" t="inlineStr">
+        <is>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+        </is>
+      </c>
+      <c r="E428" s="13" t="inlineStr">
+        <is>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+        </is>
+      </c>
+      <c r="F428" s="13" t="inlineStr">
+        <is>
+          <t>TSD §1.2</t>
+        </is>
+      </c>
+      <c r="G428" s="13" t="inlineStr"/>
+      <c r="H428" s="13" t="inlineStr"/>
+      <c r="I428" s="13" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B429" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C429" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D429" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+        </is>
+      </c>
+      <c r="E429" s="16" t="inlineStr">
+        <is>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+        </is>
+      </c>
+      <c r="F429" s="16" t="inlineStr">
+        <is>
+          <t>TSD §6.5</t>
+        </is>
+      </c>
+      <c r="G429" s="16" t="inlineStr"/>
+      <c r="H429" s="16" t="inlineStr"/>
+      <c r="I429" s="16" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B430" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C430" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D430" s="13" t="inlineStr">
+        <is>
+          <t>Hapus resto uji</t>
+        </is>
+      </c>
+      <c r="E430" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+        </is>
+      </c>
+      <c r="F430" s="13" t="inlineStr">
+        <is>
+          <t>TSD §4.0</t>
+        </is>
+      </c>
+      <c r="G430" s="13" t="inlineStr"/>
+      <c r="H430" s="13" t="inlineStr"/>
+      <c r="I430" s="13" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B431" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C431" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D431" s="16" t="inlineStr">
+        <is>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+        </is>
+      </c>
+      <c r="E431" s="16" t="inlineStr">
+        <is>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+        </is>
+      </c>
+      <c r="F431" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-09</t>
+        </is>
+      </c>
+      <c r="G431" s="16" t="inlineStr"/>
+      <c r="H431" s="16" t="inlineStr"/>
+      <c r="I431" s="16" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B432" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C432" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D432" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="E432" s="13" t="inlineStr">
+        <is>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="F432" s="13" t="inlineStr">
+        <is>
+          <t>F-PP-09, A-13</t>
+        </is>
+      </c>
+      <c r="G432" s="13" t="inlineStr"/>
+      <c r="H432" s="13" t="inlineStr"/>
+      <c r="I432" s="13" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B433" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C433" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D433" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+        </is>
+      </c>
+      <c r="E433" s="16" t="inlineStr">
+        <is>
+          <t>Tidak muncul sama sekali</t>
+        </is>
+      </c>
+      <c r="F433" s="16" t="inlineStr">
+        <is>
+          <t>A-17</t>
+        </is>
+      </c>
+      <c r="G433" s="16" t="inlineStr"/>
+      <c r="H433" s="16" t="inlineStr"/>
+      <c r="I433" s="16" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B434" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C434" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D434" s="13" t="inlineStr">
+        <is>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+        </is>
+      </c>
+      <c r="E434" s="13" t="inlineStr">
+        <is>
+          <t>Nominalnya sama dengan yang diajukan</t>
+        </is>
+      </c>
+      <c r="F434" s="13" t="inlineStr">
+        <is>
+          <t>F-FN-03</t>
+        </is>
+      </c>
+      <c r="G434" s="13" t="inlineStr"/>
+      <c r="H434" s="13" t="inlineStr"/>
+      <c r="I434" s="13" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B435" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C435" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D435" s="16" t="inlineStr">
+        <is>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+        </is>
+      </c>
+      <c r="E435" s="16" t="inlineStr">
+        <is>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
+        </is>
+      </c>
+      <c r="F435" s="16" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="G435" s="16" t="inlineStr"/>
+      <c r="H435" s="16" t="inlineStr"/>
+      <c r="I435" s="16" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B436" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C436" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D436" s="13" t="inlineStr">
+        <is>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+        </is>
+      </c>
+      <c r="E436" s="13" t="inlineStr">
+        <is>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+        </is>
+      </c>
+      <c r="F436" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-10, F-DS-12</t>
+        </is>
+      </c>
+      <c r="G436" s="13" t="inlineStr"/>
+      <c r="H436" s="13" t="inlineStr"/>
+      <c r="I436" s="13" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B437" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C437" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D437" s="16" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E437" s="16" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F437" s="16" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G437" s="16" t="inlineStr"/>
+      <c r="H437" s="16" t="inlineStr"/>
+      <c r="I437" s="16" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B438" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C438" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D438" s="13" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E438" s="13" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F438" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G438" s="13" t="inlineStr"/>
+      <c r="H438" s="13" t="inlineStr"/>
+      <c r="I438" s="13" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B439" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C439" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D439" s="16" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E439" s="16" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F439" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G439" s="16" t="inlineStr"/>
+      <c r="H439" s="16" t="inlineStr"/>
+      <c r="I439" s="16" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B440" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C440" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D440" s="13" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E440" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F440" s="13" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G440" s="13" t="inlineStr"/>
+      <c r="H440" s="13" t="inlineStr"/>
+      <c r="I440" s="13" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B441" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C441" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D441" s="16" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E441" s="16" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F441" s="16" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G441" s="16" t="inlineStr"/>
+      <c r="H441" s="16" t="inlineStr"/>
+      <c r="I441" s="16" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B442" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C442" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D442" s="13" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E442" s="13" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F442" s="13" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G442" s="13" t="inlineStr"/>
+      <c r="H442" s="13" t="inlineStr"/>
+      <c r="I442" s="13" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B443" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C443" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D443" s="16" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E443" s="16" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F443" s="16" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G443" s="16" t="inlineStr"/>
+      <c r="H443" s="16" t="inlineStr"/>
+      <c r="I443" s="16" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B444" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C444" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D444" s="13" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E444" s="13" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F444" s="13" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G444" s="13" t="inlineStr"/>
+      <c r="H444" s="13" t="inlineStr"/>
+      <c r="I444" s="13" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="16" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B391" s="17" t="inlineStr">
+      <c r="B445" s="17" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C391" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D391" s="16" t="inlineStr">
+      <c r="C445" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D445" s="16" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E391" s="16" t="inlineStr">
+      <c r="E445" s="16" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -15469,37 +17390,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F391" s="16" t="inlineStr">
+      <c r="F445" s="16" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G391" s="16" t="inlineStr"/>
-      <c r="H391" s="16" t="inlineStr"/>
-      <c r="I391" s="16" t="inlineStr"/>
-    </row>
-    <row r="392">
-      <c r="A392" s="13" t="inlineStr">
+      <c r="G445" s="16" t="inlineStr"/>
+      <c r="H445" s="16" t="inlineStr"/>
+      <c r="I445" s="16" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B392" s="14" t="inlineStr">
+      <c r="B446" s="14" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C392" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D392" s="13" t="inlineStr">
+      <c r="C446" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D446" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E392" s="13" t="inlineStr">
+      <c r="E446" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -15511,37 +17432,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F392" s="13" t="inlineStr">
+      <c r="F446" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G392" s="13" t="inlineStr"/>
-      <c r="H392" s="13" t="inlineStr"/>
-      <c r="I392" s="13" t="inlineStr"/>
-    </row>
-    <row r="393">
-      <c r="A393" s="16" t="inlineStr">
+      <c r="G446" s="13" t="inlineStr"/>
+      <c r="H446" s="13" t="inlineStr"/>
+      <c r="I446" s="13" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B393" s="17" t="inlineStr">
+      <c r="B447" s="17" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C393" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D393" s="16" t="inlineStr">
+      <c r="C447" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D447" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E393" s="16" t="inlineStr">
+      <c r="E447" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -15553,74 +17474,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F393" s="16" t="inlineStr">
+      <c r="F447" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G393" s="16" t="inlineStr"/>
-      <c r="H393" s="16" t="inlineStr"/>
-      <c r="I393" s="16" t="inlineStr"/>
-    </row>
-    <row r="394">
-      <c r="A394" s="13" t="inlineStr">
+      <c r="G447" s="16" t="inlineStr"/>
+      <c r="H447" s="16" t="inlineStr"/>
+      <c r="I447" s="16" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B394" s="14" t="inlineStr">
+      <c r="B448" s="14" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C394" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D394" s="13" t="inlineStr">
+      <c r="C448" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D448" s="13" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E394" s="13" t="inlineStr">
+      <c r="E448" s="13" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F394" s="13" t="inlineStr">
+      <c r="F448" s="13" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G394" s="13" t="inlineStr"/>
-      <c r="H394" s="13" t="inlineStr"/>
-      <c r="I394" s="13" t="inlineStr"/>
-    </row>
-    <row r="395">
-      <c r="A395" s="16" t="inlineStr">
+      <c r="G448" s="13" t="inlineStr"/>
+      <c r="H448" s="13" t="inlineStr"/>
+      <c r="I448" s="13" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B395" s="17" t="inlineStr">
+      <c r="B449" s="17" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C395" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D395" s="16" t="inlineStr">
+      <c r="C449" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D449" s="16" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E395" s="16" t="inlineStr">
+      <c r="E449" s="16" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -15631,73 +17552,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F395" s="16" t="inlineStr">
+      <c r="F449" s="16" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G395" s="16" t="inlineStr"/>
-      <c r="H395" s="16" t="inlineStr"/>
-      <c r="I395" s="16" t="inlineStr"/>
-    </row>
-    <row r="396">
-      <c r="A396" s="13" t="inlineStr">
+      <c r="G449" s="16" t="inlineStr"/>
+      <c r="H449" s="16" t="inlineStr"/>
+      <c r="I449" s="16" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B396" s="14" t="inlineStr">
+      <c r="B450" s="14" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C396" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D396" s="13" t="inlineStr">
+      <c r="C450" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D450" s="13" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E396" s="13" t="inlineStr">
+      <c r="E450" s="13" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F396" s="13" t="inlineStr">
+      <c r="F450" s="13" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G396" s="13" t="inlineStr"/>
-      <c r="H396" s="13" t="inlineStr"/>
-      <c r="I396" s="13" t="inlineStr"/>
-    </row>
-    <row r="397">
-      <c r="A397" s="16" t="inlineStr">
+      <c r="G450" s="13" t="inlineStr"/>
+      <c r="H450" s="13" t="inlineStr"/>
+      <c r="I450" s="13" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B397" s="17" t="inlineStr">
+      <c r="B451" s="17" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C397" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D397" s="16" t="inlineStr">
+      <c r="C451" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D451" s="16" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E397" s="16" t="inlineStr">
+      <c r="E451" s="16" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -15708,37 +17629,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F397" s="16" t="inlineStr">
+      <c r="F451" s="16" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G397" s="16" t="inlineStr"/>
-      <c r="H397" s="16" t="inlineStr"/>
-      <c r="I397" s="16" t="inlineStr"/>
-    </row>
-    <row r="398">
-      <c r="A398" s="13" t="inlineStr">
+      <c r="G451" s="16" t="inlineStr"/>
+      <c r="H451" s="16" t="inlineStr"/>
+      <c r="I451" s="16" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B398" s="14" t="inlineStr">
+      <c r="B452" s="14" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C398" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D398" s="13" t="inlineStr">
+      <c r="C452" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D452" s="13" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E398" s="13" t="inlineStr">
+      <c r="E452" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -15748,37 +17669,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F398" s="13" t="inlineStr">
+      <c r="F452" s="13" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G398" s="13" t="inlineStr"/>
-      <c r="H398" s="13" t="inlineStr"/>
-      <c r="I398" s="13" t="inlineStr"/>
-    </row>
-    <row r="399">
-      <c r="A399" s="16" t="inlineStr">
+      <c r="G452" s="13" t="inlineStr"/>
+      <c r="H452" s="13" t="inlineStr"/>
+      <c r="I452" s="13" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B399" s="17" t="inlineStr">
+      <c r="B453" s="17" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C399" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D399" s="16" t="inlineStr">
+      <c r="C453" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D453" s="16" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E399" s="16" t="inlineStr">
+      <c r="E453" s="16" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -15786,19 +17707,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F399" s="16" t="inlineStr">
+      <c r="F453" s="16" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G399" s="16" t="inlineStr"/>
-      <c r="H399" s="16" t="inlineStr"/>
-      <c r="I399" s="16" t="inlineStr"/>
+      <c r="G453" s="16" t="inlineStr"/>
+      <c r="H453" s="16" t="inlineStr"/>
+      <c r="I453" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I399"/>
+  <autoFilter ref="A1:I453"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G399" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G453" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$453</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$473</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C453,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C473,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P1",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P1",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P1",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P1",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P1",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P1",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P1",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P1",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C453,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C473,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P2",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P2",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P2",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P2",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P2",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P2",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P2",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P2",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C453,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C473,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P3",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P3",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P3",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P3",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P3",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P3",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C453,"P3",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C473,"P3",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pelanggan",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pelanggan",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pelanggan",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pelanggan",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pelanggan",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pelanggan",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pelanggan",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pelanggan",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kasir",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kasir",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kasir",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kasir",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kasir",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kasir",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kasir",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kasir",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pending Payment",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pending Payment",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pending Payment",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pending Payment",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pending Payment",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pending Payment",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pending Payment",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pending Payment",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Dapur",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Dapur",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Dapur",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Dapur",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Dapur",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Dapur",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Dapur",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Dapur",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Keuangan",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Keuangan",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Keuangan",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Keuangan",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Keuangan",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Keuangan",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Keuangan",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Keuangan",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Setor Saldo Cash",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Setor Saldo Cash",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Setor Saldo Cash",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Setor Saldo Cash",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Setor Saldo Cash",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Setor Saldo Cash",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Setor Saldo Cash",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Setor Saldo Cash",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"QR Meja",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"QR Meja",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"QR Meja",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"QR Meja",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"QR Meja",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"QR Meja",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"QR Meja",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"QR Meja",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Diskon",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Diskon",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Diskon",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Diskon",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Diskon",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Diskon",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Diskon",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Diskon",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembayaran QRIS",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembayaran QRIS",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembayaran QRIS",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembayaran QRIS",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembayaran QRIS",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembayaran QRIS",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembayaran QRIS",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembayaran QRIS",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Tampilan",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Tampilan",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Tampilan",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Tampilan",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Tampilan",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Tampilan",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Tampilan",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Tampilan",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Super Admin",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Super Admin",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Super Admin",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Super Admin",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Super Admin",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Super Admin",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Super Admin",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Super Admin",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembaruan Aplikasi",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembaruan Aplikasi",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembaruan Aplikasi",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembaruan Aplikasi",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembaruan Aplikasi",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembaruan Aplikasi",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Pembaruan Aplikasi",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembaruan Aplikasi",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1510,23 +1510,23 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -1541,23 +1541,23 @@
         </is>
       </c>
       <c r="B34" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G453,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G473,"Lulus")</f>
         <v/>
       </c>
       <c r="D34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G453,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G473,"Gagal")</f>
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G453,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G473,"Terblokir")</f>
         <v/>
       </c>
       <c r="F34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A453,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G453,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G473,"Dilewati")</f>
         <v/>
       </c>
       <c r="G34" s="5">
@@ -1789,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I453"/>
+  <dimension ref="A1:I473"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13368,12 +13368,12 @@
     <row r="331">
       <c r="A331" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B331" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-01</t>
+          <t>TC-PF-35</t>
         </is>
       </c>
       <c r="C331" s="18" t="inlineStr">
@@ -13383,17 +13383,17 @@
       </c>
       <c r="D331" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
+          <t>Bandingkan Saldo Total di Saldo &amp; Pengeluaran dengan Jurnal GL KaataGo</t>
         </is>
       </c>
       <c r="E331" s="16" t="inlineStr">
         <is>
-          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
+          <t>Angkanya sama persis</t>
         </is>
       </c>
       <c r="F331" s="16" t="inlineStr">
         <is>
-          <t>F-VC-01, F-VC-02</t>
+          <t>F-PF-09</t>
         </is>
       </c>
       <c r="G331" s="16" t="inlineStr"/>
@@ -13403,12 +13403,12 @@
     <row r="332">
       <c r="A332" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B332" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-02</t>
+          <t>TC-PF-36</t>
         </is>
       </c>
       <c r="C332" s="15" t="inlineStr">
@@ -13418,17 +13418,17 @@
       </c>
       <c r="D332" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan Rp 1.000.000 jadi 3</t>
+          <t>Terbitkan voucher, muat ulang kedua layar</t>
         </is>
       </c>
       <c r="E332" s="13" t="inlineStr">
         <is>
-          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
+          <t>Keduanya berkurang sebesar alokasinya</t>
         </is>
       </c>
       <c r="F332" s="13" t="inlineStr">
         <is>
-          <t>F-VC-02</t>
+          <t>F-PF-09</t>
         </is>
       </c>
       <c r="G332" s="13" t="inlineStr"/>
@@ -13438,12 +13438,12 @@
     <row r="333">
       <c r="A333" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B333" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-03</t>
+          <t>TC-PF-37</t>
         </is>
       </c>
       <c r="C333" s="20" t="inlineStr">
@@ -13453,17 +13453,17 @@
       </c>
       <c r="D333" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan dengan kode yang sudah dipakai</t>
+          <t>Buka Saldo &amp; Pengeluaran untuk KaataGo</t>
         </is>
       </c>
       <c r="E333" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — kodenya sudah ada</t>
+          <t>Tidak ada kartu Saldo Cash / Non Cash</t>
         </is>
       </c>
       <c r="F333" s="16" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-PF-10</t>
         </is>
       </c>
       <c r="G333" s="16" t="inlineStr"/>
@@ -13473,32 +13473,32 @@
     <row r="334">
       <c r="A334" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B334" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-04</t>
-        </is>
-      </c>
-      <c r="C334" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-38</t>
+        </is>
+      </c>
+      <c r="C334" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
+          <t>Buka layar yang sama untuk resto biasa</t>
         </is>
       </c>
       <c r="E334" s="13" t="inlineStr">
         <is>
-          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
+          <t>Kartu Cash/Non Cash tetap ada</t>
         </is>
       </c>
       <c r="F334" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-PF-10</t>
         </is>
       </c>
       <c r="G334" s="13" t="inlineStr"/>
@@ -13508,12 +13508,12 @@
     <row r="335">
       <c r="A335" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B335" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-05</t>
+          <t>TC-CB-01</t>
         </is>
       </c>
       <c r="C335" s="18" t="inlineStr">
@@ -13523,17 +13523,17 @@
       </c>
       <c r="D335" s="16" t="inlineStr">
         <is>
-          <t>Pelanggan menebus kode di Voucher Saya</t>
+          <t>Izinkan lokasi, lihat daftar Terdekat</t>
         </is>
       </c>
       <c r="E335" s="16" t="inlineStr">
         <is>
-          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
+          <t>Hanya resto ≤ 5 km yang muncul</t>
         </is>
       </c>
       <c r="F335" s="16" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-CB-01</t>
         </is>
       </c>
       <c r="G335" s="16" t="inlineStr"/>
@@ -13543,32 +13543,32 @@
     <row r="336">
       <c r="A336" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B336" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-06</t>
-        </is>
-      </c>
-      <c r="C336" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-CB-02</t>
+        </is>
+      </c>
+      <c r="C336" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>Ketik kodenya dengan huruf kecil</t>
+          <t>Resto berjarak 7 km</t>
         </is>
       </c>
       <c r="E336" s="13" t="inlineStr">
         <is>
-          <t>Tetap diterima</t>
+          <t>Tidak di Terdekat, tapi ada di Semua Resto</t>
         </is>
       </c>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-CB-01, F-CB-02</t>
         </is>
       </c>
       <c r="G336" s="13" t="inlineStr"/>
@@ -13578,12 +13578,12 @@
     <row r="337">
       <c r="A337" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B337" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-07</t>
+          <t>TC-CB-03</t>
         </is>
       </c>
       <c r="C337" s="20" t="inlineStr">
@@ -13593,17 +13593,17 @@
       </c>
       <c r="D337" s="16" t="inlineStr">
         <is>
-          <t>Ketik kode yang tidak ada</t>
+          <t>Periksa keterangan di judul bagian Terdekat</t>
         </is>
       </c>
       <c r="E337" s="16" t="inlineStr">
         <is>
-          <t>"Kode voucher tidak ditemukan"</t>
+          <t>Tertulis "Dalam 5 km dari kamu"</t>
         </is>
       </c>
       <c r="F337" s="16" t="inlineStr">
         <is>
-          <t>F-VC-10</t>
+          <t>F-CB-01</t>
         </is>
       </c>
       <c r="G337" s="16" t="inlineStr"/>
@@ -13613,32 +13613,32 @@
     <row r="338">
       <c r="A338" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B338" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-08</t>
-        </is>
-      </c>
-      <c r="C338" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-CB-04</t>
+        </is>
+      </c>
+      <c r="C338" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D338" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
+          <t>Tolak izin lokasi</t>
         </is>
       </c>
       <c r="E338" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
+          <t>Bagian Terdekat tidak tampil; Semua Resto tetap ada</t>
         </is>
       </c>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-CB-02</t>
         </is>
       </c>
       <c r="G338" s="13" t="inlineStr"/>
@@ -13648,12 +13648,12 @@
     <row r="339">
       <c r="A339" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B339" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-09</t>
+          <t>TC-TU-01</t>
         </is>
       </c>
       <c r="C339" s="18" t="inlineStr">
@@ -13663,17 +13663,17 @@
       </c>
       <c r="D339" s="16" t="inlineStr">
         <is>
-          <t>Orang yang sama menebus kode itu lagi</t>
+          <t>Owner → Saldo &amp; Pengeluaran → Top Up Saldo</t>
         </is>
       </c>
       <c r="E339" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
+          <t>Tersimpan; Saldo Total naik sebesar nominalnya</t>
         </is>
       </c>
       <c r="F339" s="16" t="inlineStr">
         <is>
-          <t>F-VC-08, F-VC-10</t>
+          <t>F-TU-01, F-TU-02</t>
         </is>
       </c>
       <c r="G339" s="16" t="inlineStr"/>
@@ -13683,12 +13683,12 @@
     <row r="340">
       <c r="A340" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B340" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-10</t>
+          <t>TC-TU-02</t>
         </is>
       </c>
       <c r="C340" s="15" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
-          <t>Batch berisi 10, orang ke-11 menebus</t>
+          <t>Periksa Jurnal GL sesudahnya</t>
         </is>
       </c>
       <c r="E340" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Voucher ini sudah habis"</t>
+          <t>Kredit GL Total Saldo, debit GL Setoran Modal</t>
         </is>
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>F-VC-09, F-VC-10</t>
+          <t>F-TU-05</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr"/>
@@ -13718,12 +13718,12 @@
     <row r="341">
       <c r="A341" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B341" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-11</t>
+          <t>TC-TU-03</t>
         </is>
       </c>
       <c r="C341" s="18" t="inlineStr">
@@ -13733,17 +13733,17 @@
       </c>
       <c r="D341" s="16" t="inlineStr">
         <is>
-          <t>Dua orang menebus voucher terakhir bersamaan</t>
+          <t>Periksa Laporan Transaksi / Pemasukan</t>
         </is>
       </c>
       <c r="E341" s="16" t="inlineStr">
         <is>
-          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
+          <t>Setoran tidak muncul sebagai penjualan</t>
         </is>
       </c>
       <c r="F341" s="16" t="inlineStr">
         <is>
-          <t>F-VC-09</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G341" s="16" t="inlineStr"/>
@@ -13753,32 +13753,32 @@
     <row r="342">
       <c r="A342" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B342" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-12</t>
-        </is>
-      </c>
-      <c r="C342" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TU-04</t>
+        </is>
+      </c>
+      <c r="C342" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
-          <t>Tebus voucher dari batch yang sudah ditutup</t>
+          <t>Simpan tanpa mengisi Dari</t>
         </is>
       </c>
       <c r="E342" s="13" t="inlineStr">
         <is>
-          <t>"Voucher ini sudah ditutup"</t>
+          <t>Ditolak — "Sebutkan penyetornya"</t>
         </is>
       </c>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-TU-03</t>
         </is>
       </c>
       <c r="G342" s="13" t="inlineStr"/>
@@ -13788,12 +13788,12 @@
     <row r="343">
       <c r="A343" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B343" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-13</t>
+          <t>TC-TU-05</t>
         </is>
       </c>
       <c r="C343" s="20" t="inlineStr">
@@ -13803,17 +13803,17 @@
       </c>
       <c r="D343" s="16" t="inlineStr">
         <is>
-          <t>Tebus voucher yang lewat masa berlaku</t>
+          <t>Simpan tanpa bukti</t>
         </is>
       </c>
       <c r="E343" s="16" t="inlineStr">
         <is>
-          <t>"Voucher ini sudah kedaluwarsa"</t>
+          <t>Tetap tersimpan — buktinya opsional</t>
         </is>
       </c>
       <c r="F343" s="16" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-TU-03</t>
         </is>
       </c>
       <c r="G343" s="16" t="inlineStr"/>
@@ -13823,12 +13823,12 @@
     <row r="344">
       <c r="A344" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B344" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-14</t>
+          <t>TC-TU-06</t>
         </is>
       </c>
       <c r="C344" s="15" t="inlineStr">
@@ -13838,17 +13838,17 @@
       </c>
       <c r="D344" s="13" t="inlineStr">
         <is>
-          <t>Di keranjang, ketuk baris voucher</t>
+          <t>Masuk sebagai Kasir, buka layar yang sama</t>
         </is>
       </c>
       <c r="E344" s="13" t="inlineStr">
         <is>
-          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
+          <t>Riwayat terlihat, tombol Top Up Saldo tidak ada</t>
         </is>
       </c>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-TU-04</t>
         </is>
       </c>
       <c r="G344" s="13" t="inlineStr"/>
@@ -13858,12 +13858,12 @@
     <row r="345">
       <c r="A345" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B345" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-15</t>
+          <t>TC-TU-07</t>
         </is>
       </c>
       <c r="C345" s="18" t="inlineStr">
@@ -13873,17 +13873,17 @@
       </c>
       <c r="D345" s="16" t="inlineStr">
         <is>
-          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
+          <t>Kasir memanggil insert balance_topups lewat API</t>
         </is>
       </c>
       <c r="E345" s="16" t="inlineStr">
         <is>
-          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
+          <t>Ditolak RLS</t>
         </is>
       </c>
       <c r="F345" s="16" t="inlineStr">
         <is>
-          <t>F-VC-05, F-VC-10</t>
+          <t>F-TU-04</t>
         </is>
       </c>
       <c r="G345" s="16" t="inlineStr"/>
@@ -13893,12 +13893,12 @@
     <row r="346">
       <c r="A346" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B346" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-16</t>
+          <t>TC-TU-08</t>
         </is>
       </c>
       <c r="C346" s="15" t="inlineStr">
@@ -13908,17 +13908,17 @@
       </c>
       <c r="D346" s="13" t="inlineStr">
         <is>
-          <t>Voucher khusus resto A dibuka di resto B</t>
+          <t>Super Admin → Finance → Saldo &amp; Pengeluaran → Top Up</t>
         </is>
       </c>
       <c r="E346" s="13" t="inlineStr">
         <is>
-          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
+          <t>Saldo KaataGo naik; Jurnal GL KaataGo mencatatnya</t>
         </is>
       </c>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>F-VC-06, F-VC-10</t>
+          <t>F-TU-01, F-TU-05</t>
         </is>
       </c>
       <c r="G346" s="13" t="inlineStr"/>
@@ -13928,12 +13928,12 @@
     <row r="347">
       <c r="A347" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B347" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-17</t>
+          <t>TC-TU-09</t>
         </is>
       </c>
       <c r="C347" s="18" t="inlineStr">
@@ -13943,17 +13943,17 @@
       </c>
       <c r="D347" s="16" t="inlineStr">
         <is>
-          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
+          <t>Coba ubah atau hapus baris balance_topups</t>
         </is>
       </c>
       <c r="E347" s="16" t="inlineStr">
         <is>
-          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
+          <t>Ditolak — tidak ada kebijakannya</t>
         </is>
       </c>
       <c r="F347" s="16" t="inlineStr">
         <is>
-          <t>F-VC-12</t>
+          <t>F-TU-06</t>
         </is>
       </c>
       <c r="G347" s="16" t="inlineStr"/>
@@ -13963,32 +13963,32 @@
     <row r="348">
       <c r="A348" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B348" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-18</t>
-        </is>
-      </c>
-      <c r="C348" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-10</t>
+        </is>
+      </c>
+      <c r="C348" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D348" s="13" t="inlineStr">
         <is>
-          <t>Pasang voucher lalu selesaikan pesanan</t>
+          <t>Periksa kartu Cash / Non Cash sesudah top up</t>
         </is>
       </c>
       <c r="E348" s="13" t="inlineStr">
         <is>
-          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
+          <t>Non Cash naik; keduanya tetap berjumlah sama dengan Penghasilan</t>
         </is>
       </c>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G348" s="13" t="inlineStr"/>
@@ -13998,32 +13998,32 @@
     <row r="349">
       <c r="A349" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B349" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-19</t>
-        </is>
-      </c>
-      <c r="C349" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-11</t>
+        </is>
+      </c>
+      <c r="C349" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D349" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Lepas setelah voucher terpasang</t>
+          <t>Buka Pemetaan GL sebagai Finance resto</t>
         </is>
       </c>
       <c r="E349" s="16" t="inlineStr">
         <is>
-          <t>Tagihan kembali ke nominal semula</t>
+          <t>Ada bagian GL Modal</t>
         </is>
       </c>
       <c r="F349" s="16" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G349" s="16" t="inlineStr"/>
@@ -14033,32 +14033,32 @@
     <row r="350">
       <c r="A350" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B350" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-20</t>
-        </is>
-      </c>
-      <c r="C350" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-12</t>
+        </is>
+      </c>
+      <c r="C350" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D350" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
+          <t>Buka halaman awal aplikasi</t>
         </is>
       </c>
       <c r="E350" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
+          <t>Tombolnya bertuliskan KaataGo Merchant</t>
         </is>
       </c>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G350" s="13" t="inlineStr"/>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="B351" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-21</t>
+          <t>TC-VC-01</t>
         </is>
       </c>
       <c r="C351" s="18" t="inlineStr">
@@ -14083,17 +14083,17 @@
       </c>
       <c r="D351" s="16" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL restonya</t>
+          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
         </is>
       </c>
       <c r="E351" s="16" t="inlineStr">
         <is>
-          <t>Ada baris masuk sebesar nilai vouchernya</t>
+          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
         </is>
       </c>
       <c r="F351" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-01, F-VC-02</t>
         </is>
       </c>
       <c r="G351" s="16" t="inlineStr"/>
@@ -14108,27 +14108,27 @@
       </c>
       <c r="B352" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-22</t>
-        </is>
-      </c>
-      <c r="C352" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-02</t>
+        </is>
+      </c>
+      <c r="C352" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D352" s="13" t="inlineStr">
         <is>
-          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
+          <t>Terbitkan Rp 1.000.000 jadi 3</t>
         </is>
       </c>
       <c r="E352" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul di daftar pilihan</t>
+          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
         </is>
       </c>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-02</t>
         </is>
       </c>
       <c r="G352" s="13" t="inlineStr"/>
@@ -14143,27 +14143,27 @@
       </c>
       <c r="B353" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-23</t>
-        </is>
-      </c>
-      <c r="C353" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-03</t>
+        </is>
+      </c>
+      <c r="C353" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D353" s="16" t="inlineStr">
         <is>
-          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
+          <t>Terbitkan dengan kode yang sudah dipakai</t>
         </is>
       </c>
       <c r="E353" s="16" t="inlineStr">
         <is>
-          <t>Debit Voucher Redeem, kredit Total Saldo</t>
+          <t>Ditolak — kodenya sudah ada</t>
         </is>
       </c>
       <c r="F353" s="16" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G353" s="16" t="inlineStr"/>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="B354" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-24</t>
+          <t>TC-VC-04</t>
         </is>
       </c>
       <c r="C354" s="15" t="inlineStr">
@@ -14188,17 +14188,17 @@
       </c>
       <c r="D354" s="13" t="inlineStr">
         <is>
-          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
+          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
         </is>
       </c>
       <c r="E354" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
+          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
         </is>
       </c>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G354" s="13" t="inlineStr"/>
@@ -14213,7 +14213,7 @@
       </c>
       <c r="B355" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-25</t>
+          <t>TC-VC-05</t>
         </is>
       </c>
       <c r="C355" s="18" t="inlineStr">
@@ -14223,17 +14223,17 @@
       </c>
       <c r="D355" s="16" t="inlineStr">
         <is>
-          <t>Jalankan expire_vouchers() dua kali</t>
+          <t>Pelanggan menebus kode di Voucher Saya</t>
         </is>
       </c>
       <c r="E355" s="16" t="inlineStr">
         <is>
-          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
+          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
         </is>
       </c>
       <c r="F355" s="16" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G355" s="16" t="inlineStr"/>
@@ -14248,27 +14248,27 @@
       </c>
       <c r="B356" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-26</t>
-        </is>
-      </c>
-      <c r="C356" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-06</t>
+        </is>
+      </c>
+      <c r="C356" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D356" s="13" t="inlineStr">
         <is>
-          <t>Jumlahkan keempat tahap untuk satu batch</t>
+          <t>Ketik kodenya dengan huruf kecil</t>
         </is>
       </c>
       <c r="E356" s="13" t="inlineStr">
         <is>
-          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
+          <t>Tetap diterima</t>
         </is>
       </c>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13, F-VC-14</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G356" s="13" t="inlineStr"/>
@@ -14283,27 +14283,27 @@
       </c>
       <c r="B357" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-27</t>
-        </is>
-      </c>
-      <c r="C357" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-07</t>
+        </is>
+      </c>
+      <c r="C357" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D357" s="16" t="inlineStr">
         <is>
-          <t>Tulis langsung ke voucher_claims lewat API</t>
+          <t>Ketik kode yang tidak ada</t>
         </is>
       </c>
       <c r="E357" s="16" t="inlineStr">
         <is>
-          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
+          <t>"Kode voucher tidak ditemukan"</t>
         </is>
       </c>
       <c r="F357" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-10</t>
         </is>
       </c>
       <c r="G357" s="16" t="inlineStr"/>
@@ -14318,7 +14318,7 @@
       </c>
       <c r="B358" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-28</t>
+          <t>TC-VC-08</t>
         </is>
       </c>
       <c r="C358" s="15" t="inlineStr">
@@ -14328,17 +14328,17 @@
       </c>
       <c r="D358" s="13" t="inlineStr">
         <is>
-          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
+          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
         </is>
       </c>
       <c r="E358" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
+          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
         </is>
       </c>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G358" s="13" t="inlineStr"/>
@@ -14353,27 +14353,27 @@
       </c>
       <c r="B359" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-29</t>
-        </is>
-      </c>
-      <c r="C359" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-09</t>
+        </is>
+      </c>
+      <c r="C359" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D359" s="16" t="inlineStr">
         <is>
-          <t>Periksa kartu batch di layar Super Admin</t>
+          <t>Orang yang sama menebus kode itu lagi</t>
         </is>
       </c>
       <c r="E359" s="16" t="inlineStr">
         <is>
-          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
+          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
         </is>
       </c>
       <c r="F359" s="16" t="inlineStr">
         <is>
-          <t>F-VC-15</t>
+          <t>F-VC-08, F-VC-10</t>
         </is>
       </c>
       <c r="G359" s="16" t="inlineStr"/>
@@ -14388,27 +14388,27 @@
       </c>
       <c r="B360" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-30</t>
-        </is>
-      </c>
-      <c r="C360" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-10</t>
+        </is>
+      </c>
+      <c r="C360" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D360" s="13" t="inlineStr">
         <is>
-          <t>Tutup sebuah batch yang kuotanya masih ada</t>
+          <t>Batch berisi 10, orang ke-11 menebus</t>
         </is>
       </c>
       <c r="E360" s="13" t="inlineStr">
         <is>
-          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
+          <t>Ditolak — "Voucher ini sudah habis"</t>
         </is>
       </c>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>F-VC-04</t>
+          <t>F-VC-09, F-VC-10</t>
         </is>
       </c>
       <c r="G360" s="13" t="inlineStr"/>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="B361" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-31</t>
+          <t>TC-VC-11</t>
         </is>
       </c>
       <c r="C361" s="18" t="inlineStr">
@@ -14433,17 +14433,17 @@
       </c>
       <c r="D361" s="16" t="inlineStr">
         <is>
-          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
+          <t>Dua orang menebus voucher terakhir bersamaan</t>
         </is>
       </c>
       <c r="E361" s="16" t="inlineStr">
         <is>
-          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
+          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
         </is>
       </c>
       <c r="F361" s="16" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-09</t>
         </is>
       </c>
       <c r="G361" s="16" t="inlineStr"/>
@@ -14458,27 +14458,27 @@
       </c>
       <c r="B362" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-32</t>
-        </is>
-      </c>
-      <c r="C362" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-12</t>
+        </is>
+      </c>
+      <c r="C362" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D362" s="13" t="inlineStr">
         <is>
-          <t>Jalankan settle-voucher-payouts</t>
+          <t>Tebus voucher dari batch yang sudah ditutup</t>
         </is>
       </c>
       <c r="E362" s="13" t="inlineStr">
         <is>
-          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
+          <t>"Voucher ini sudah ditutup"</t>
         </is>
       </c>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G362" s="13" t="inlineStr"/>
@@ -14493,27 +14493,27 @@
       </c>
       <c r="B363" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-33</t>
-        </is>
-      </c>
-      <c r="C363" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-13</t>
+        </is>
+      </c>
+      <c r="C363" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D363" s="16" t="inlineStr">
         <is>
-          <t>Jalankan fungsinya dua kali berturut-turut</t>
+          <t>Tebus voucher yang lewat masa berlaku</t>
         </is>
       </c>
       <c r="E363" s="16" t="inlineStr">
         <is>
-          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
+          <t>"Voucher ini sudah kedaluwarsa"</t>
         </is>
       </c>
       <c r="F363" s="16" t="inlineStr">
         <is>
-          <t>F-VC-18</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G363" s="16" t="inlineStr"/>
@@ -14528,7 +14528,7 @@
       </c>
       <c r="B364" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-34</t>
+          <t>TC-VC-14</t>
         </is>
       </c>
       <c r="C364" s="15" t="inlineStr">
@@ -14538,17 +14538,17 @@
       </c>
       <c r="D364" s="13" t="inlineStr">
         <is>
-          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
+          <t>Di keranjang, ketuk baris voucher</t>
         </is>
       </c>
       <c r="E364" s="13" t="inlineStr">
         <is>
-          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
+          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
         </is>
       </c>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G364" s="13" t="inlineStr"/>
@@ -14563,7 +14563,7 @@
       </c>
       <c r="B365" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-35</t>
+          <t>TC-VC-15</t>
         </is>
       </c>
       <c r="C365" s="18" t="inlineStr">
@@ -14573,17 +14573,17 @@
       </c>
       <c r="D365" s="16" t="inlineStr">
         <is>
-          <t>Perbaiki kuncinya lalu jalankan lagi</t>
+          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
         </is>
       </c>
       <c r="E365" s="16" t="inlineStr">
         <is>
-          <t>Baris yang tadi gagal terkirim</t>
+          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
         </is>
       </c>
       <c r="F365" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-05, F-VC-10</t>
         </is>
       </c>
       <c r="G365" s="16" t="inlineStr"/>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="B366" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-36</t>
+          <t>TC-VC-16</t>
         </is>
       </c>
       <c r="C366" s="15" t="inlineStr">
@@ -14608,17 +14608,17 @@
       </c>
       <c r="D366" s="13" t="inlineStr">
         <is>
-          <t>Pakai voucher di resto yang belum punya sub-akun</t>
+          <t>Voucher khusus resto A dibuka di resto B</t>
         </is>
       </c>
       <c r="E366" s="13" t="inlineStr">
         <is>
-          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
+          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
         </is>
       </c>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>F-VC-19</t>
+          <t>F-VC-06, F-VC-10</t>
         </is>
       </c>
       <c r="G366" s="13" t="inlineStr"/>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B367" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-37</t>
+          <t>TC-VC-17</t>
         </is>
       </c>
       <c r="C367" s="18" t="inlineStr">
@@ -14643,17 +14643,17 @@
       </c>
       <c r="D367" s="16" t="inlineStr">
         <is>
-          <t>Buat pesanan bervoucher saat Xendit mati total</t>
+          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
         </is>
       </c>
       <c r="E367" s="16" t="inlineStr">
         <is>
-          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
+          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
         </is>
       </c>
       <c r="F367" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-12</t>
         </is>
       </c>
       <c r="G367" s="16" t="inlineStr"/>
@@ -14668,27 +14668,27 @@
       </c>
       <c r="B368" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-38</t>
-        </is>
-      </c>
-      <c r="C368" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-18</t>
+        </is>
+      </c>
+      <c r="C368" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D368" s="13" t="inlineStr">
         <is>
-          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
+          <t>Pasang voucher lalu selesaikan pesanan</t>
         </is>
       </c>
       <c r="E368" s="13" t="inlineStr">
         <is>
-          <t>Klaim used lama ikut terantre</t>
+          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
         </is>
       </c>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G368" s="13" t="inlineStr"/>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="B369" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-39</t>
+          <t>TC-VC-19</t>
         </is>
       </c>
       <c r="C369" s="18" t="inlineStr">
@@ -14713,17 +14713,17 @@
       </c>
       <c r="D369" s="16" t="inlineStr">
         <is>
-          <t>Tulis langsung ke voucher_payouts lewat API</t>
+          <t>Ketuk Lepas setelah voucher terpasang</t>
         </is>
       </c>
       <c r="E369" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
+          <t>Tagihan kembali ke nominal semula</t>
         </is>
       </c>
       <c r="F369" s="16" t="inlineStr">
         <is>
-          <t>F-VC-18</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G369" s="16" t="inlineStr"/>
@@ -14738,27 +14738,27 @@
       </c>
       <c r="B370" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-40</t>
-        </is>
-      </c>
-      <c r="C370" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-20</t>
+        </is>
+      </c>
+      <c r="C370" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D370" s="13" t="inlineStr">
         <is>
-          <t>Baca voucher_payout_config sebagai Super Admin</t>
+          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
         </is>
       </c>
       <c r="E370" s="13" t="inlineStr">
         <is>
-          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
+          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
         </is>
       </c>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G370" s="13" t="inlineStr"/>
@@ -14773,27 +14773,27 @@
       </c>
       <c r="B371" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-41</t>
-        </is>
-      </c>
-      <c r="C371" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-21</t>
+        </is>
+      </c>
+      <c r="C371" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D371" s="16" t="inlineStr">
         <is>
-          <t>Jalankan penjadwal sebelum function_url diisi</t>
+          <t>Periksa Jurnal GL restonya</t>
         </is>
       </c>
       <c r="E371" s="16" t="inlineStr">
         <is>
-          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
+          <t>Ada baris masuk sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F371" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G371" s="16" t="inlineStr"/>
@@ -14808,27 +14808,27 @@
       </c>
       <c r="B372" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-42</t>
-        </is>
-      </c>
-      <c r="C372" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-22</t>
+        </is>
+      </c>
+      <c r="C372" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D372" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
+          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
         </is>
       </c>
       <c r="E372" s="13" t="inlineStr">
         <is>
-          <t>Cocok baris per baris lewat transfer_id</t>
+          <t>Tidak muncul di daftar pilihan</t>
         </is>
       </c>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G372" s="13" t="inlineStr"/>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="B373" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-43</t>
+          <t>TC-VC-23</t>
         </is>
       </c>
       <c r="C373" s="18" t="inlineStr">
@@ -14853,17 +14853,17 @@
       </c>
       <c r="D373" s="16" t="inlineStr">
         <is>
-          <t>Jalankan pencairan saat xenPlatform belum aktif</t>
+          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
         </is>
       </c>
       <c r="E373" s="16" t="inlineStr">
         <is>
-          <t>Seluruh antrean tetap pending, attempts nol, tidak ada galat</t>
+          <t>Debit Voucher Redeem, kredit Total Saldo</t>
         </is>
       </c>
       <c r="F373" s="16" t="inlineStr">
         <is>
-          <t>F-VC-19</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G373" s="16" t="inlineStr"/>
@@ -14878,27 +14878,27 @@
       </c>
       <c r="B374" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-44</t>
-        </is>
-      </c>
-      <c r="C374" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-24</t>
+        </is>
+      </c>
+      <c r="C374" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D374" s="13" t="inlineStr">
         <is>
-          <t>Aktifkan xenPlatform + pasang sub-akun, lalu tunggu penjadwal</t>
+          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
         </is>
       </c>
       <c r="E374" s="13" t="inlineStr">
         <is>
-          <t>Tunggakan lama ikut terangkut tanpa dijalankan ulang manual</t>
+          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
         </is>
       </c>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16, F-VC-17</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G374" s="13" t="inlineStr"/>
@@ -14913,7 +14913,7 @@
       </c>
       <c r="B375" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-45</t>
+          <t>TC-VC-25</t>
         </is>
       </c>
       <c r="C375" s="18" t="inlineStr">
@@ -14923,17 +14923,17 @@
       </c>
       <c r="D375" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Pemetaan GL</t>
+          <t>Jalankan expire_vouchers() dua kali</t>
         </is>
       </c>
       <c r="E375" s="16" t="inlineStr">
         <is>
-          <t>Ada bagian GL Voucher berisi GL Voucher dan GL Voucher Redeem</t>
+          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
         </is>
       </c>
       <c r="F375" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G375" s="16" t="inlineStr"/>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="B376" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-46</t>
+          <t>TC-VC-26</t>
         </is>
       </c>
       <c r="C376" s="15" t="inlineStr">
@@ -14958,17 +14958,17 @@
       </c>
       <c r="D376" s="13" t="inlineStr">
         <is>
-          <t>Buka Pemetaan GL sebagai Finance resto biasa</t>
+          <t>Jumlahkan keempat tahap untuk satu batch</t>
         </is>
       </c>
       <c r="E376" s="13" t="inlineStr">
         <is>
-          <t>Bagian GL Voucher tidak muncul, penanda "belum dipetakan" tidak berbunyi</t>
+          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
         </is>
       </c>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-13, F-VC-14</t>
         </is>
       </c>
       <c r="G376" s="13" t="inlineStr"/>
@@ -14983,22 +14983,22 @@
       </c>
       <c r="B377" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-47</t>
-        </is>
-      </c>
-      <c r="C377" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-27</t>
+        </is>
+      </c>
+      <c r="C377" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D377" s="16" t="inlineStr">
         <is>
-          <t>Ubah nomor GL Voucher lalu simpan</t>
+          <t>Tulis langsung ke voucher_claims lewat API</t>
         </is>
       </c>
       <c r="E377" s="16" t="inlineStr">
         <is>
-          <t>Tersimpan, dan jurnal voucher berikutnya memakai nomor baru</t>
+          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F377" s="16" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="B378" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-48</t>
+          <t>TC-VC-28</t>
         </is>
       </c>
       <c r="C378" s="15" t="inlineStr">
@@ -15028,17 +15028,17 @@
       </c>
       <c r="D378" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan batch, lalu buka Kotak Masuk pelanggan</t>
+          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
         </is>
       </c>
       <c r="E378" s="13" t="inlineStr">
         <is>
-          <t>Ada kabar di tab Umum berisi kode, nilai, kuota, dan tenggat</t>
+          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
         </is>
       </c>
       <c r="F378" s="13" t="inlineStr">
         <is>
-          <t>F-VC-20, F-VC-21</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G378" s="13" t="inlineStr"/>
@@ -15053,27 +15053,27 @@
       </c>
       <c r="B379" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-49</t>
-        </is>
-      </c>
-      <c r="C379" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-29</t>
+        </is>
+      </c>
+      <c r="C379" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D379" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch dengan HP pelanggan terkunci</t>
+          <t>Periksa kartu batch di layar Super Admin</t>
         </is>
       </c>
       <c r="E379" s="16" t="inlineStr">
         <is>
-          <t>Push muncul di layar kunci</t>
+          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
         </is>
       </c>
       <c r="F379" s="16" t="inlineStr">
         <is>
-          <t>F-VC-20</t>
+          <t>F-VC-15</t>
         </is>
       </c>
       <c r="G379" s="16" t="inlineStr"/>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="B380" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-50</t>
+          <t>TC-VC-30</t>
         </is>
       </c>
       <c r="C380" s="19" t="inlineStr">
@@ -15098,17 +15098,17 @@
       </c>
       <c r="D380" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan batch tanpa minimal belanja</t>
+          <t>Tutup sebuah batch yang kuotanya masih ada</t>
         </is>
       </c>
       <c r="E380" s="13" t="inlineStr">
         <is>
-          <t>Kalimat minimal belanja tidak muncul di pengumuman</t>
+          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F380" s="13" t="inlineStr">
         <is>
-          <t>F-VC-21</t>
+          <t>F-VC-04</t>
         </is>
       </c>
       <c r="G380" s="13" t="inlineStr"/>
@@ -15123,27 +15123,27 @@
       </c>
       <c r="B381" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-51</t>
-        </is>
-      </c>
-      <c r="C381" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-31</t>
+        </is>
+      </c>
+      <c r="C381" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D381" s="16" t="inlineStr">
         <is>
-          <t>Buka Kotak Masuk sebagai pegawai resto</t>
+          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
         </is>
       </c>
       <c r="E381" s="16" t="inlineStr">
         <is>
-          <t>Kabar voucher tidak muncul — audiensnya pelanggan</t>
+          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F381" s="16" t="inlineStr">
         <is>
-          <t>F-VC-20</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G381" s="16" t="inlineStr"/>
@@ -15158,27 +15158,27 @@
       </c>
       <c r="B382" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-52</t>
-        </is>
-      </c>
-      <c r="C382" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-32</t>
+        </is>
+      </c>
+      <c r="C382" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D382" s="13" t="inlineStr">
         <is>
-          <t>Ketik nama resto di kolom cari pada form terbit</t>
+          <t>Jalankan settle-voucher-payouts</t>
         </is>
       </c>
       <c r="E382" s="13" t="inlineStr">
         <is>
-          <t>Daftarnya menyusut sesuai kata kuncinya</t>
+          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
         </is>
       </c>
       <c r="F382" s="13" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G382" s="13" t="inlineStr"/>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="B383" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-53</t>
+          <t>TC-VC-33</t>
         </is>
       </c>
       <c r="C383" s="18" t="inlineStr">
@@ -15203,17 +15203,17 @@
       </c>
       <c r="D383" s="16" t="inlineStr">
         <is>
-          <t>Centang 3 resto, lalu cari kata yang menyaringnya keluar</t>
+          <t>Jalankan fungsinya dua kali berturut-turut</t>
         </is>
       </c>
       <c r="E383" s="16" t="inlineStr">
         <is>
-          <t>Ketiganya tetap terpilih; hitungannya tidak berubah</t>
+          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
         </is>
       </c>
       <c r="F383" s="16" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G383" s="16" t="inlineStr"/>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="B384" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-54</t>
+          <t>TC-VC-34</t>
         </is>
       </c>
       <c r="C384" s="15" t="inlineStr">
@@ -15238,17 +15238,17 @@
       </c>
       <c r="D384" s="13" t="inlineStr">
         <is>
-          <t>Saring daftarnya, lalu ketuk Pilih semua</t>
+          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
         </is>
       </c>
       <c r="E384" s="13" t="inlineStr">
         <is>
-          <t>Hanya yang tampil tercentang, bukan seluruh resto</t>
+          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
         </is>
       </c>
       <c r="F384" s="13" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G384" s="13" t="inlineStr"/>
@@ -15263,27 +15263,27 @@
       </c>
       <c r="B385" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-55</t>
-        </is>
-      </c>
-      <c r="C385" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-35</t>
+        </is>
+      </c>
+      <c r="C385" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D385" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Lepas semua saat semua yang tampil tercentang</t>
+          <t>Perbaiki kuncinya lalu jalankan lagi</t>
         </is>
       </c>
       <c r="E385" s="16" t="inlineStr">
         <is>
-          <t>Yang tampil terlepas; pilihan di luar saringan tetap</t>
+          <t>Baris yang tadi gagal terkirim</t>
         </is>
       </c>
       <c r="F385" s="16" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G385" s="16" t="inlineStr"/>
@@ -15298,27 +15298,27 @@
       </c>
       <c r="B386" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-56</t>
-        </is>
-      </c>
-      <c r="C386" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-36</t>
+        </is>
+      </c>
+      <c r="C386" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D386" s="13" t="inlineStr">
         <is>
-          <t>Cari nama resto yang tidak ada</t>
+          <t>Pakai voucher di resto yang belum punya sub-akun</t>
         </is>
       </c>
       <c r="E386" s="13" t="inlineStr">
         <is>
-          <t>Muncul "Tidak ada resto bernama itu"</t>
+          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
         </is>
       </c>
       <c r="F386" s="13" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G386" s="13" t="inlineStr"/>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="B387" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-57</t>
+          <t>TC-VC-37</t>
         </is>
       </c>
       <c r="C387" s="18" t="inlineStr">
@@ -15343,17 +15343,17 @@
       </c>
       <c r="D387" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch berbanner, lalu buka Kotak Masuk pelanggan</t>
+          <t>Buat pesanan bervoucher saat Xendit mati total</t>
         </is>
       </c>
       <c r="E387" s="16" t="inlineStr">
         <is>
-          <t>Gambarnya tampil bersama kabarnya</t>
+          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
         </is>
       </c>
       <c r="F387" s="16" t="inlineStr">
         <is>
-          <t>F-VC-23</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G387" s="16" t="inlineStr"/>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="B388" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-58</t>
+          <t>TC-VC-38</t>
         </is>
       </c>
       <c r="C388" s="19" t="inlineStr">
@@ -15378,17 +15378,17 @@
       </c>
       <c r="D388" s="13" t="inlineStr">
         <is>
-          <t>Pilih gambar potret, lihat pratinjaunya</t>
+          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
         </is>
       </c>
       <c r="E388" s="13" t="inlineStr">
         <is>
-          <t>Dipotong 16:9, sama dengan yang nanti muncul di kotak masuk</t>
+          <t>Klaim used lama ikut terantre</t>
         </is>
       </c>
       <c r="F388" s="13" t="inlineStr">
         <is>
-          <t>F-VC-23</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G388" s="13" t="inlineStr"/>
@@ -15403,27 +15403,27 @@
       </c>
       <c r="B389" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-59</t>
-        </is>
-      </c>
-      <c r="C389" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-39</t>
+        </is>
+      </c>
+      <c r="C389" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D389" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch tanpa banner</t>
+          <t>Tulis langsung ke voucher_payouts lewat API</t>
         </is>
       </c>
       <c r="E389" s="16" t="inlineStr">
         <is>
-          <t>Kabarnya tetap terkirim, tanpa gambar</t>
+          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F389" s="16" t="inlineStr">
         <is>
-          <t>F-VC-23</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G389" s="16" t="inlineStr"/>
@@ -15438,27 +15438,27 @@
       </c>
       <c r="B390" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-60</t>
-        </is>
-      </c>
-      <c r="C390" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-40</t>
+        </is>
+      </c>
+      <c r="C390" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D390" s="13" t="inlineStr">
         <is>
-          <t>Cari tombol Hapus pada batch yang masih berjalan</t>
+          <t>Baca voucher_payout_config sebagai Super Admin</t>
         </is>
       </c>
       <c r="E390" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada — harus ditutup dulu</t>
+          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
         </is>
       </c>
       <c r="F390" s="13" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G390" s="13" t="inlineStr"/>
@@ -15473,27 +15473,27 @@
       </c>
       <c r="B391" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-61</t>
-        </is>
-      </c>
-      <c r="C391" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-41</t>
+        </is>
+      </c>
+      <c r="C391" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D391" s="16" t="inlineStr">
         <is>
-          <t>Tutup batch yang belum ada penebusnya, lalu hapus</t>
+          <t>Jalankan penjadwal sebelum function_url diisi</t>
         </is>
       </c>
       <c r="E391" s="16" t="inlineStr">
         <is>
-          <t>Terhapus; dananya kembali ke GL Total Saldo</t>
+          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
         </is>
       </c>
       <c r="F391" s="16" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G391" s="16" t="inlineStr"/>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="B392" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-62</t>
+          <t>TC-VC-42</t>
         </is>
       </c>
       <c r="C392" s="15" t="inlineStr">
@@ -15518,17 +15518,17 @@
       </c>
       <c r="D392" s="13" t="inlineStr">
         <is>
-          <t>Periksa Kotak Masuk pelanggan sesudah batch dihapus</t>
+          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
         </is>
       </c>
       <c r="E392" s="13" t="inlineStr">
         <is>
-          <t>Kabar vouchernya ikut hilang</t>
+          <t>Cocok baris per baris lewat transfer_id</t>
         </is>
       </c>
       <c r="F392" s="13" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G392" s="13" t="inlineStr"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="B393" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-63</t>
+          <t>TC-VC-43</t>
         </is>
       </c>
       <c r="C393" s="18" t="inlineStr">
@@ -15553,17 +15553,17 @@
       </c>
       <c r="D393" s="16" t="inlineStr">
         <is>
-          <t>Panggil delete_voucher_batch untuk batch yang sudah ada penebusnya</t>
+          <t>Jalankan pencairan saat xenPlatform belum aktif</t>
         </is>
       </c>
       <c r="E393" s="16" t="inlineStr">
         <is>
-          <t>Ditolak, dengan jumlah penebusnya disebut</t>
+          <t>Seluruh antrean tetap pending, attempts nol, tidak ada galat</t>
         </is>
       </c>
       <c r="F393" s="16" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G393" s="16" t="inlineStr"/>
@@ -15578,27 +15578,27 @@
       </c>
       <c r="B394" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-64</t>
-        </is>
-      </c>
-      <c r="C394" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-44</t>
+        </is>
+      </c>
+      <c r="C394" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D394" s="13" t="inlineStr">
         <is>
-          <t>Panggil delete_voucher_batch sebagai bukan Super Admin</t>
+          <t>Aktifkan xenPlatform + pasang sub-akun, lalu tunggu penjadwal</t>
         </is>
       </c>
       <c r="E394" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tunggakan lama ikut terangkut tanpa dijalankan ulang manual</t>
         </is>
       </c>
       <c r="F394" s="13" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-16, F-VC-17</t>
         </is>
       </c>
       <c r="G394" s="13" t="inlineStr"/>
@@ -15613,27 +15613,27 @@
       </c>
       <c r="B395" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-65</t>
-        </is>
-      </c>
-      <c r="C395" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-45</t>
+        </is>
+      </c>
+      <c r="C395" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D395" s="16" t="inlineStr">
         <is>
-          <t>Hapus batch yang sudah pernah disettle penjadwal</t>
+          <t>Super Admin → Finance → Pemetaan GL</t>
         </is>
       </c>
       <c r="E395" s="16" t="inlineStr">
         <is>
-          <t>Dananya tidak dikembalikan dua kali</t>
+          <t>Ada bagian GL Voucher berisi GL Voucher dan GL Voucher Redeem</t>
         </is>
       </c>
       <c r="F395" s="16" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G395" s="16" t="inlineStr"/>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="B396" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-66</t>
+          <t>TC-VC-46</t>
         </is>
       </c>
       <c r="C396" s="15" t="inlineStr">
@@ -15658,17 +15658,17 @@
       </c>
       <c r="D396" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Penebus pada sebuah batch</t>
+          <t>Buka Pemetaan GL sebagai Finance resto biasa</t>
         </is>
       </c>
       <c r="E396" s="13" t="inlineStr">
         <is>
-          <t>Daftar email penebut berikut tanggal tebus dan statusnya</t>
+          <t>Bagian GL Voucher tidak muncul, penanda "belum dipetakan" tidak berbunyi</t>
         </is>
       </c>
       <c r="F396" s="13" t="inlineStr">
         <is>
-          <t>F-VC-25</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G396" s="13" t="inlineStr"/>
@@ -15683,27 +15683,27 @@
       </c>
       <c r="B397" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-67</t>
-        </is>
-      </c>
-      <c r="C397" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-47</t>
+        </is>
+      </c>
+      <c r="C397" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D397" s="16" t="inlineStr">
         <is>
-          <t>Periksa ringkasan di atas daftar penebus</t>
+          <t>Ubah nomor GL Voucher lalu simpan</t>
         </is>
       </c>
       <c r="E397" s="16" t="inlineStr">
         <is>
-          <t>Dipakai / Menggantung / Hangus berjumlah sama dengan barisnya</t>
+          <t>Tersimpan, dan jurnal voucher berikutnya memakai nomor baru</t>
         </is>
       </c>
       <c r="F397" s="16" t="inlineStr">
         <is>
-          <t>F-VC-25</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G397" s="16" t="inlineStr"/>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="B398" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-68</t>
+          <t>TC-VC-48</t>
         </is>
       </c>
       <c r="C398" s="15" t="inlineStr">
@@ -15728,17 +15728,17 @@
       </c>
       <c r="D398" s="13" t="inlineStr">
         <is>
-          <t>Lewati tanggal kedaluwarsa sebelum penjadwal berjalan</t>
+          <t>Terbitkan batch, lalu buka Kotak Masuk pelanggan</t>
         </is>
       </c>
       <c r="E398" s="13" t="inlineStr">
         <is>
-          <t>Statusnya sudah Hangus, bukan Belum Dipakai</t>
+          <t>Ada kabar di tab Umum berisi kode, nilai, kuota, dan tenggat</t>
         </is>
       </c>
       <c r="F398" s="13" t="inlineStr">
         <is>
-          <t>F-VC-25</t>
+          <t>F-VC-20, F-VC-21</t>
         </is>
       </c>
       <c r="G398" s="13" t="inlineStr"/>
@@ -15748,12 +15748,12 @@
     <row r="399">
       <c r="A399" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B399" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-01</t>
+          <t>TC-VC-49</t>
         </is>
       </c>
       <c r="C399" s="18" t="inlineStr">
@@ -15763,17 +15763,17 @@
       </c>
       <c r="D399" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Analisa Pasar</t>
+          <t>Terbitkan batch dengan HP pelanggan terkunci</t>
         </is>
       </c>
       <c r="E399" s="16" t="inlineStr">
         <is>
-          <t>Empat bagian termuat tanpa galat</t>
+          <t>Push muncul di layar kunci</t>
         </is>
       </c>
       <c r="F399" s="16" t="inlineStr">
         <is>
-          <t>F-MR-01…04</t>
+          <t>F-VC-20</t>
         </is>
       </c>
       <c r="G399" s="16" t="inlineStr"/>
@@ -15783,32 +15783,32 @@
     <row r="400">
       <c r="A400" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B400" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-02</t>
-        </is>
-      </c>
-      <c r="C400" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-50</t>
+        </is>
+      </c>
+      <c r="C400" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D400" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan Top 5 Pelanggan dengan jumlah manual dari orders</t>
+          <t>Terbitkan batch tanpa minimal belanja</t>
         </is>
       </c>
       <c r="E400" s="13" t="inlineStr">
         <is>
-          <t>Cocok nominal dan jumlah pesanannya</t>
+          <t>Kalimat minimal belanja tidak muncul di pengumuman</t>
         </is>
       </c>
       <c r="F400" s="13" t="inlineStr">
         <is>
-          <t>F-MR-01</t>
+          <t>F-VC-21</t>
         </is>
       </c>
       <c r="G400" s="13" t="inlineStr"/>
@@ -15818,32 +15818,32 @@
     <row r="401">
       <c r="A401" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B401" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-03</t>
-        </is>
-      </c>
-      <c r="C401" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-51</t>
+        </is>
+      </c>
+      <c r="C401" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D401" s="16" t="inlineStr">
         <is>
-          <t>Batalkan sebuah pesanan besar, muat ulang</t>
+          <t>Buka Kotak Masuk sebagai pegawai resto</t>
         </is>
       </c>
       <c r="E401" s="16" t="inlineStr">
         <is>
-          <t>Nominalnya berkurang — yang batal tidak dihitung</t>
+          <t>Kabar voucher tidak muncul — audiensnya pelanggan</t>
         </is>
       </c>
       <c r="F401" s="16" t="inlineStr">
         <is>
-          <t>F-MR-05</t>
+          <t>F-VC-20</t>
         </is>
       </c>
       <c r="G401" s="16" t="inlineStr"/>
@@ -15853,32 +15853,32 @@
     <row r="402">
       <c r="A402" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B402" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-04</t>
-        </is>
-      </c>
-      <c r="C402" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-52</t>
+        </is>
+      </c>
+      <c r="C402" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D402" s="13" t="inlineStr">
         <is>
-          <t>Buat akun pelanggan baru tanpa memesan</t>
+          <t>Ketik nama resto di kolom cari pada form terbit</t>
         </is>
       </c>
       <c r="E402" s="13" t="inlineStr">
         <is>
-          <t>Muncul di daftar Belum Pernah Memesan</t>
+          <t>Daftarnya menyusut sesuai kata kuncinya</t>
         </is>
       </c>
       <c r="F402" s="13" t="inlineStr">
         <is>
-          <t>F-MR-02</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G402" s="13" t="inlineStr"/>
@@ -15888,12 +15888,12 @@
     <row r="403">
       <c r="A403" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B403" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-05</t>
+          <t>TC-VC-53</t>
         </is>
       </c>
       <c r="C403" s="18" t="inlineStr">
@@ -15903,17 +15903,17 @@
       </c>
       <c r="D403" s="16" t="inlineStr">
         <is>
-          <t>Pelanggan itu menyelesaikan satu pesanan, muat ulang</t>
+          <t>Centang 3 resto, lalu cari kata yang menyaringnya keluar</t>
         </is>
       </c>
       <c r="E403" s="16" t="inlineStr">
         <is>
-          <t>Hilang dari daftar tersebut</t>
+          <t>Ketiganya tetap terpilih; hitungannya tidak berubah</t>
         </is>
       </c>
       <c r="F403" s="16" t="inlineStr">
         <is>
-          <t>F-MR-02</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G403" s="16" t="inlineStr"/>
@@ -15923,12 +15923,12 @@
     <row r="404">
       <c r="A404" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B404" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-06</t>
+          <t>TC-VC-54</t>
         </is>
       </c>
       <c r="C404" s="15" t="inlineStr">
@@ -15938,17 +15938,17 @@
       </c>
       <c r="D404" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan Top 5 Resto dengan Jurnal GL resto bersangkutan</t>
+          <t>Saring daftarnya, lalu ketuk Pilih semua</t>
         </is>
       </c>
       <c r="E404" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sejalan</t>
+          <t>Hanya yang tampil tercentang, bukan seluruh resto</t>
         </is>
       </c>
       <c r="F404" s="13" t="inlineStr">
         <is>
-          <t>F-MR-03</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G404" s="13" t="inlineStr"/>
@@ -15958,32 +15958,32 @@
     <row r="405">
       <c r="A405" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B405" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-07</t>
-        </is>
-      </c>
-      <c r="C405" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-55</t>
+        </is>
+      </c>
+      <c r="C405" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D405" s="16" t="inlineStr">
         <is>
-          <t>Resto yang seluruh pesanannya batal</t>
+          <t>Ketuk Lepas semua saat semua yang tampil tercentang</t>
         </is>
       </c>
       <c r="E405" s="16" t="inlineStr">
         <is>
-          <t>Muncul di Belum Ada Penghasilan, jumlah pesanan 0</t>
+          <t>Yang tampil terlepas; pilihan di luar saringan tetap</t>
         </is>
       </c>
       <c r="F405" s="16" t="inlineStr">
         <is>
-          <t>F-MR-04</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G405" s="16" t="inlineStr"/>
@@ -15993,12 +15993,12 @@
     <row r="406">
       <c r="A406" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B406" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-08</t>
+          <t>TC-VC-56</t>
         </is>
       </c>
       <c r="C406" s="19" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="D406" s="13" t="inlineStr">
         <is>
-          <t>Resto baru tanpa pesanan sama sekali</t>
+          <t>Cari nama resto yang tidak ada</t>
         </is>
       </c>
       <c r="E406" s="13" t="inlineStr">
         <is>
-          <t>Muncul dengan "Belum ada pesanan"</t>
+          <t>Muncul "Tidak ada resto bernama itu"</t>
         </is>
       </c>
       <c r="F406" s="13" t="inlineStr">
         <is>
-          <t>F-MR-04</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G406" s="13" t="inlineStr"/>
@@ -16028,12 +16028,12 @@
     <row r="407">
       <c r="A407" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B407" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-09</t>
+          <t>TC-VC-57</t>
         </is>
       </c>
       <c r="C407" s="18" t="inlineStr">
@@ -16043,17 +16043,17 @@
       </c>
       <c r="D407" s="16" t="inlineStr">
         <is>
-          <t>Periksa apakah resto KaataGo ikut terhitung</t>
+          <t>Terbitkan batch berbanner, lalu buka Kotak Masuk pelanggan</t>
         </is>
       </c>
       <c r="E407" s="16" t="inlineStr">
         <is>
-          <t>Tidak — resto platform dikecualikan</t>
+          <t>Gambarnya tampil bersama kabarnya</t>
         </is>
       </c>
       <c r="F407" s="16" t="inlineStr">
         <is>
-          <t>F-MR-06</t>
+          <t>F-VC-23</t>
         </is>
       </c>
       <c r="G407" s="16" t="inlineStr"/>
@@ -16063,32 +16063,32 @@
     <row r="408">
       <c r="A408" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B408" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-10</t>
-        </is>
-      </c>
-      <c r="C408" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-58</t>
+        </is>
+      </c>
+      <c r="C408" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D408" s="13" t="inlineStr">
         <is>
-          <t>Hapus lunak sebuah resto, muat ulang</t>
+          <t>Pilih gambar potret, lihat pratinjaunya</t>
         </is>
       </c>
       <c r="E408" s="13" t="inlineStr">
         <is>
-          <t>Hilang dari keempat daftar</t>
+          <t>Dipotong 16:9, sama dengan yang nanti muncul di kotak masuk</t>
         </is>
       </c>
       <c r="F408" s="13" t="inlineStr">
         <is>
-          <t>F-MR-06</t>
+          <t>F-VC-23</t>
         </is>
       </c>
       <c r="G408" s="13" t="inlineStr"/>
@@ -16098,32 +16098,32 @@
     <row r="409">
       <c r="A409" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B409" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-11</t>
-        </is>
-      </c>
-      <c r="C409" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-59</t>
+        </is>
+      </c>
+      <c r="C409" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D409" s="16" t="inlineStr">
         <is>
-          <t>Panggil report_top_customers sebagai Owner resto</t>
+          <t>Terbitkan batch tanpa banner</t>
         </is>
       </c>
       <c r="E409" s="16" t="inlineStr">
         <is>
-          <t>Daftar kosong, bukan pesan galat</t>
+          <t>Kabarnya tetap terkirim, tanpa gambar</t>
         </is>
       </c>
       <c r="F409" s="16" t="inlineStr">
         <is>
-          <t>F-MR-07</t>
+          <t>F-VC-23</t>
         </is>
       </c>
       <c r="G409" s="16" t="inlineStr"/>
@@ -16133,32 +16133,32 @@
     <row r="410">
       <c r="A410" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B410" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-12</t>
-        </is>
-      </c>
-      <c r="C410" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-60</t>
+        </is>
+      </c>
+      <c r="C410" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D410" s="13" t="inlineStr">
         <is>
-          <t>Panggil salah satu RPC dengan p_limit 99999</t>
+          <t>Cari tombol Hapus pada batch yang masih berjalan</t>
         </is>
       </c>
       <c r="E410" s="13" t="inlineStr">
         <is>
-          <t>Dijepit ke batas atasnya</t>
+          <t>Tidak ada — harus ditutup dulu</t>
         </is>
       </c>
       <c r="F410" s="13" t="inlineStr">
         <is>
-          <t>F-MR-07</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G410" s="13" t="inlineStr"/>
@@ -16168,32 +16168,32 @@
     <row r="411">
       <c r="A411" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B411" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-13</t>
-        </is>
-      </c>
-      <c r="C411" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-61</t>
+        </is>
+      </c>
+      <c r="C411" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D411" s="16" t="inlineStr">
         <is>
-          <t>Pesanan kasir atas nama tamu</t>
+          <t>Tutup batch yang belum ada penebusnya, lalu hapus</t>
         </is>
       </c>
       <c r="E411" s="16" t="inlineStr">
         <is>
-          <t>Tidak ikut peringkat pelanggan — bukan akun terdaftar</t>
+          <t>Terhapus; dananya kembali ke GL Total Saldo</t>
         </is>
       </c>
       <c r="F411" s="16" t="inlineStr">
         <is>
-          <t>F-MR-01</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G411" s="16" t="inlineStr"/>
@@ -16203,12 +16203,12 @@
     <row r="412">
       <c r="A412" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B412" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-VC-62</t>
         </is>
       </c>
       <c r="C412" s="15" t="inlineStr">
@@ -16218,17 +16218,17 @@
       </c>
       <c r="D412" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Periksa Kotak Masuk pelanggan sesudah batch dihapus</t>
         </is>
       </c>
       <c r="E412" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Kabar vouchernya ikut hilang</t>
         </is>
       </c>
       <c r="F412" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G412" s="13" t="inlineStr"/>
@@ -16238,12 +16238,12 @@
     <row r="413">
       <c r="A413" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B413" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-VC-63</t>
         </is>
       </c>
       <c r="C413" s="18" t="inlineStr">
@@ -16253,17 +16253,17 @@
       </c>
       <c r="D413" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Panggil delete_voucher_batch untuk batch yang sudah ada penebusnya</t>
         </is>
       </c>
       <c r="E413" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Ditolak, dengan jumlah penebusnya disebut</t>
         </is>
       </c>
       <c r="F413" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G413" s="16" t="inlineStr"/>
@@ -16273,12 +16273,12 @@
     <row r="414">
       <c r="A414" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B414" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-VC-64</t>
         </is>
       </c>
       <c r="C414" s="15" t="inlineStr">
@@ -16288,17 +16288,17 @@
       </c>
       <c r="D414" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Panggil delete_voucher_batch sebagai bukan Super Admin</t>
         </is>
       </c>
       <c r="E414" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F414" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G414" s="13" t="inlineStr"/>
@@ -16308,32 +16308,32 @@
     <row r="415">
       <c r="A415" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B415" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
-        </is>
-      </c>
-      <c r="C415" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-65</t>
+        </is>
+      </c>
+      <c r="C415" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D415" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Hapus batch yang sudah pernah disettle penjadwal</t>
         </is>
       </c>
       <c r="E415" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Dananya tidak dikembalikan dua kali</t>
         </is>
       </c>
       <c r="F415" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G415" s="16" t="inlineStr"/>
@@ -16343,12 +16343,12 @@
     <row r="416">
       <c r="A416" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B416" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-VC-66</t>
         </is>
       </c>
       <c r="C416" s="15" t="inlineStr">
@@ -16358,17 +16358,17 @@
       </c>
       <c r="D416" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Ketuk Penebus pada sebuah batch</t>
         </is>
       </c>
       <c r="E416" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Daftar email penebut berikut tanggal tebus dan statusnya</t>
         </is>
       </c>
       <c r="F416" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-VC-25</t>
         </is>
       </c>
       <c r="G416" s="13" t="inlineStr"/>
@@ -16378,12 +16378,12 @@
     <row r="417">
       <c r="A417" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B417" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-VC-67</t>
         </is>
       </c>
       <c r="C417" s="18" t="inlineStr">
@@ -16393,17 +16393,17 @@
       </c>
       <c r="D417" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Periksa ringkasan di atas daftar penebus</t>
         </is>
       </c>
       <c r="E417" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Dipakai / Menggantung / Hangus berjumlah sama dengan barisnya</t>
         </is>
       </c>
       <c r="F417" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-VC-25</t>
         </is>
       </c>
       <c r="G417" s="16" t="inlineStr"/>
@@ -16413,12 +16413,12 @@
     <row r="418">
       <c r="A418" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B418" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-VC-68</t>
         </is>
       </c>
       <c r="C418" s="15" t="inlineStr">
@@ -16428,17 +16428,17 @@
       </c>
       <c r="D418" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Lewati tanggal kedaluwarsa sebelum penjadwal berjalan</t>
         </is>
       </c>
       <c r="E418" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Statusnya sudah Hangus, bukan Belum Dipakai</t>
         </is>
       </c>
       <c r="F418" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-VC-25</t>
         </is>
       </c>
       <c r="G418" s="13" t="inlineStr"/>
@@ -16448,12 +16448,12 @@
     <row r="419">
       <c r="A419" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B419" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
+          <t>TC-MR-01</t>
         </is>
       </c>
       <c r="C419" s="18" t="inlineStr">
@@ -16463,17 +16463,17 @@
       </c>
       <c r="D419" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Super Admin → Analisa Pasar</t>
         </is>
       </c>
       <c r="E419" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Empat bagian termuat tanpa galat</t>
         </is>
       </c>
       <c r="F419" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-MR-01…04</t>
         </is>
       </c>
       <c r="G419" s="16" t="inlineStr"/>
@@ -16483,12 +16483,12 @@
     <row r="420">
       <c r="A420" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B420" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-MR-02</t>
         </is>
       </c>
       <c r="C420" s="15" t="inlineStr">
@@ -16498,17 +16498,17 @@
       </c>
       <c r="D420" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Bandingkan Top 5 Pelanggan dengan jumlah manual dari orders</t>
         </is>
       </c>
       <c r="E420" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Cocok nominal dan jumlah pesanannya</t>
         </is>
       </c>
       <c r="F420" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>F-MR-01</t>
         </is>
       </c>
       <c r="G420" s="13" t="inlineStr"/>
@@ -16518,12 +16518,12 @@
     <row r="421">
       <c r="A421" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B421" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-MR-03</t>
         </is>
       </c>
       <c r="C421" s="18" t="inlineStr">
@@ -16533,17 +16533,17 @@
       </c>
       <c r="D421" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Batalkan sebuah pesanan besar, muat ulang</t>
         </is>
       </c>
       <c r="E421" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Nominalnya berkurang — yang batal tidak dihitung</t>
         </is>
       </c>
       <c r="F421" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>F-MR-05</t>
         </is>
       </c>
       <c r="G421" s="16" t="inlineStr"/>
@@ -16553,32 +16553,32 @@
     <row r="422">
       <c r="A422" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B422" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
-        </is>
-      </c>
-      <c r="C422" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-04</t>
+        </is>
+      </c>
+      <c r="C422" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D422" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Buat akun pelanggan baru tanpa memesan</t>
         </is>
       </c>
       <c r="E422" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Muncul di daftar Belum Pernah Memesan</t>
         </is>
       </c>
       <c r="F422" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>F-MR-02</t>
         </is>
       </c>
       <c r="G422" s="13" t="inlineStr"/>
@@ -16588,32 +16588,32 @@
     <row r="423">
       <c r="A423" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B423" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C423" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-05</t>
+        </is>
+      </c>
+      <c r="C423" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D423" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Pelanggan itu menyelesaikan satu pesanan, muat ulang</t>
         </is>
       </c>
       <c r="E423" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Hilang dari daftar tersebut</t>
         </is>
       </c>
       <c r="F423" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>F-MR-02</t>
         </is>
       </c>
       <c r="G423" s="16" t="inlineStr"/>
@@ -16623,32 +16623,32 @@
     <row r="424">
       <c r="A424" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B424" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C424" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-06</t>
+        </is>
+      </c>
+      <c r="C424" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D424" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Bandingkan Top 5 Resto dengan Jurnal GL resto bersangkutan</t>
         </is>
       </c>
       <c r="E424" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Nominalnya sejalan</t>
         </is>
       </c>
       <c r="F424" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>F-MR-03</t>
         </is>
       </c>
       <c r="G424" s="13" t="inlineStr"/>
@@ -16658,12 +16658,12 @@
     <row r="425">
       <c r="A425" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B425" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-MR-07</t>
         </is>
       </c>
       <c r="C425" s="18" t="inlineStr">
@@ -16673,17 +16673,17 @@
       </c>
       <c r="D425" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Resto yang seluruh pesanannya batal</t>
         </is>
       </c>
       <c r="E425" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Muncul di Belum Ada Penghasilan, jumlah pesanan 0</t>
         </is>
       </c>
       <c r="F425" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>F-MR-04</t>
         </is>
       </c>
       <c r="G425" s="16" t="inlineStr"/>
@@ -16693,32 +16693,32 @@
     <row r="426">
       <c r="A426" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B426" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
-        </is>
-      </c>
-      <c r="C426" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-MR-08</t>
+        </is>
+      </c>
+      <c r="C426" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D426" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Resto baru tanpa pesanan sama sekali</t>
         </is>
       </c>
       <c r="E426" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Muncul dengan "Belum ada pesanan"</t>
         </is>
       </c>
       <c r="F426" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>F-MR-04</t>
         </is>
       </c>
       <c r="G426" s="13" t="inlineStr"/>
@@ -16728,12 +16728,12 @@
     <row r="427">
       <c r="A427" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B427" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-MR-09</t>
         </is>
       </c>
       <c r="C427" s="18" t="inlineStr">
@@ -16743,17 +16743,17 @@
       </c>
       <c r="D427" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Periksa apakah resto KaataGo ikut terhitung</t>
         </is>
       </c>
       <c r="E427" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Tidak — resto platform dikecualikan</t>
         </is>
       </c>
       <c r="F427" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>F-MR-06</t>
         </is>
       </c>
       <c r="G427" s="16" t="inlineStr"/>
@@ -16763,32 +16763,32 @@
     <row r="428">
       <c r="A428" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B428" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C428" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-10</t>
+        </is>
+      </c>
+      <c r="C428" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D428" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Hapus lunak sebuah resto, muat ulang</t>
         </is>
       </c>
       <c r="E428" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Hilang dari keempat daftar</t>
         </is>
       </c>
       <c r="F428" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>F-MR-06</t>
         </is>
       </c>
       <c r="G428" s="13" t="inlineStr"/>
@@ -16798,32 +16798,32 @@
     <row r="429">
       <c r="A429" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B429" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C429" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-11</t>
+        </is>
+      </c>
+      <c r="C429" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D429" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Panggil report_top_customers sebagai Owner resto</t>
         </is>
       </c>
       <c r="E429" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Daftar kosong, bukan pesan galat</t>
         </is>
       </c>
       <c r="F429" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>F-MR-07</t>
         </is>
       </c>
       <c r="G429" s="16" t="inlineStr"/>
@@ -16833,12 +16833,12 @@
     <row r="430">
       <c r="A430" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B430" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
+          <t>TC-MR-12</t>
         </is>
       </c>
       <c r="C430" s="19" t="inlineStr">
@@ -16848,17 +16848,17 @@
       </c>
       <c r="D430" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Panggil salah satu RPC dengan p_limit 99999</t>
         </is>
       </c>
       <c r="E430" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Dijepit ke batas atasnya</t>
         </is>
       </c>
       <c r="F430" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>F-MR-07</t>
         </is>
       </c>
       <c r="G430" s="13" t="inlineStr"/>
@@ -16868,32 +16868,32 @@
     <row r="431">
       <c r="A431" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B431" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
-        </is>
-      </c>
-      <c r="C431" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-MR-13</t>
+        </is>
+      </c>
+      <c r="C431" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D431" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Pesanan kasir atas nama tamu</t>
         </is>
       </c>
       <c r="E431" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Tidak ikut peringkat pelanggan — bukan akun terdaftar</t>
         </is>
       </c>
       <c r="F431" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>F-MR-01</t>
         </is>
       </c>
       <c r="G431" s="16" t="inlineStr"/>
@@ -16903,12 +16903,12 @@
     <row r="432">
       <c r="A432" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B432" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
+          <t>TC-TS-01</t>
         </is>
       </c>
       <c r="C432" s="15" t="inlineStr">
@@ -16918,17 +16918,17 @@
       </c>
       <c r="D432" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E432" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F432" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G432" s="13" t="inlineStr"/>
@@ -16938,12 +16938,12 @@
     <row r="433">
       <c r="A433" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B433" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
+          <t>TC-TS-02</t>
         </is>
       </c>
       <c r="C433" s="18" t="inlineStr">
@@ -16953,17 +16953,17 @@
       </c>
       <c r="D433" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E433" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F433" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G433" s="16" t="inlineStr"/>
@@ -16973,12 +16973,12 @@
     <row r="434">
       <c r="A434" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B434" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
+          <t>TC-TS-03</t>
         </is>
       </c>
       <c r="C434" s="15" t="inlineStr">
@@ -16988,17 +16988,17 @@
       </c>
       <c r="D434" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E434" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F434" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G434" s="13" t="inlineStr"/>
@@ -17008,12 +17008,12 @@
     <row r="435">
       <c r="A435" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B435" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-TS-04</t>
         </is>
       </c>
       <c r="C435" s="18" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="D435" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E435" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F435" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G435" s="16" t="inlineStr"/>
@@ -17043,12 +17043,12 @@
     <row r="436">
       <c r="A436" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B436" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-TS-05</t>
         </is>
       </c>
       <c r="C436" s="15" t="inlineStr">
@@ -17058,17 +17058,17 @@
       </c>
       <c r="D436" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E436" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F436" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G436" s="13" t="inlineStr"/>
@@ -17078,32 +17078,32 @@
     <row r="437">
       <c r="A437" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B437" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C437" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-06</t>
+        </is>
+      </c>
+      <c r="C437" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D437" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E437" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F437" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G437" s="16" t="inlineStr"/>
@@ -17113,32 +17113,32 @@
     <row r="438">
       <c r="A438" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B438" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C438" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-07</t>
+        </is>
+      </c>
+      <c r="C438" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D438" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E438" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F438" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G438" s="13" t="inlineStr"/>
@@ -17148,32 +17148,32 @@
     <row r="439">
       <c r="A439" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B439" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
-        </is>
-      </c>
-      <c r="C439" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C439" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D439" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E439" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F439" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G439" s="16" t="inlineStr"/>
@@ -17183,32 +17183,32 @@
     <row r="440">
       <c r="A440" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B440" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
-        </is>
-      </c>
-      <c r="C440" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C440" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D440" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E440" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F440" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G440" s="13" t="inlineStr"/>
@@ -17218,32 +17218,32 @@
     <row r="441">
       <c r="A441" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B441" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
-        </is>
-      </c>
-      <c r="C441" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C441" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D441" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E441" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F441" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G441" s="16" t="inlineStr"/>
@@ -17253,12 +17253,12 @@
     <row r="442">
       <c r="A442" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B442" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
+          <t>TC-TS-11</t>
         </is>
       </c>
       <c r="C442" s="19" t="inlineStr">
@@ -17268,17 +17268,17 @@
       </c>
       <c r="D442" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E442" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F442" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G442" s="13" t="inlineStr"/>
@@ -17288,32 +17288,32 @@
     <row r="443">
       <c r="A443" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B443" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
-        </is>
-      </c>
-      <c r="C443" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C443" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D443" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E443" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F443" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G443" s="16" t="inlineStr"/>
@@ -17323,12 +17323,12 @@
     <row r="444">
       <c r="A444" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B444" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
+          <t>TC-TS-13</t>
         </is>
       </c>
       <c r="C444" s="19" t="inlineStr">
@@ -17338,17 +17338,17 @@
       </c>
       <c r="D444" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E444" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F444" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G444" s="13" t="inlineStr"/>
@@ -17358,25 +17358,725 @@
     <row r="445">
       <c r="A445" s="16" t="inlineStr">
         <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B445" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-14</t>
+        </is>
+      </c>
+      <c r="C445" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D445" s="16" t="inlineStr">
+        <is>
+          <t>Coba bayar QRIS saat luring</t>
+        </is>
+      </c>
+      <c r="E445" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+        </is>
+      </c>
+      <c r="F445" s="16" t="inlineStr">
+        <is>
+          <t>FSD §5.6</t>
+        </is>
+      </c>
+      <c r="G445" s="16" t="inlineStr"/>
+      <c r="H445" s="16" t="inlineStr"/>
+      <c r="I445" s="16" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B446" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C446" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D446" s="13" t="inlineStr">
+        <is>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+        </is>
+      </c>
+      <c r="E446" s="13" t="inlineStr">
+        <is>
+          <t>Nominal yang dipakai tetap dari basis data</t>
+        </is>
+      </c>
+      <c r="F446" s="13" t="inlineStr">
+        <is>
+          <t>TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G446" s="13" t="inlineStr"/>
+      <c r="H446" s="13" t="inlineStr"/>
+      <c r="I446" s="13" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B447" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-16</t>
+        </is>
+      </c>
+      <c r="C447" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D447" s="16" t="inlineStr">
+        <is>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+        </is>
+      </c>
+      <c r="E447" s="16" t="inlineStr">
+        <is>
+          <t>Ditolak</t>
+        </is>
+      </c>
+      <c r="F447" s="16" t="inlineStr">
+        <is>
+          <t>F-PG-02, TSD §7.1</t>
+        </is>
+      </c>
+      <c r="G447" s="16" t="inlineStr"/>
+      <c r="H447" s="16" t="inlineStr"/>
+      <c r="I447" s="16" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B448" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-17</t>
+        </is>
+      </c>
+      <c r="C448" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D448" s="13" t="inlineStr">
+        <is>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+        </is>
+      </c>
+      <c r="E448" s="13" t="inlineStr">
+        <is>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+        </is>
+      </c>
+      <c r="F448" s="13" t="inlineStr">
+        <is>
+          <t>TSD §1.2</t>
+        </is>
+      </c>
+      <c r="G448" s="13" t="inlineStr"/>
+      <c r="H448" s="13" t="inlineStr"/>
+      <c r="I448" s="13" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="16" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B449" s="17" t="inlineStr">
+        <is>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C449" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D449" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+        </is>
+      </c>
+      <c r="E449" s="16" t="inlineStr">
+        <is>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+        </is>
+      </c>
+      <c r="F449" s="16" t="inlineStr">
+        <is>
+          <t>TSD §6.5</t>
+        </is>
+      </c>
+      <c r="G449" s="16" t="inlineStr"/>
+      <c r="H449" s="16" t="inlineStr"/>
+      <c r="I449" s="16" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="13" t="inlineStr">
+        <is>
+          <t>Uji Teknis (lingkup TSD)</t>
+        </is>
+      </c>
+      <c r="B450" s="14" t="inlineStr">
+        <is>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C450" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D450" s="13" t="inlineStr">
+        <is>
+          <t>Hapus resto uji</t>
+        </is>
+      </c>
+      <c r="E450" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+        </is>
+      </c>
+      <c r="F450" s="13" t="inlineStr">
+        <is>
+          <t>TSD §4.0</t>
+        </is>
+      </c>
+      <c r="G450" s="13" t="inlineStr"/>
+      <c r="H450" s="13" t="inlineStr"/>
+      <c r="I450" s="13" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B451" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C451" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D451" s="16" t="inlineStr">
+        <is>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+        </is>
+      </c>
+      <c r="E451" s="16" t="inlineStr">
+        <is>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+        </is>
+      </c>
+      <c r="F451" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-09</t>
+        </is>
+      </c>
+      <c r="G451" s="16" t="inlineStr"/>
+      <c r="H451" s="16" t="inlineStr"/>
+      <c r="I451" s="16" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B452" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C452" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D452" s="13" t="inlineStr">
+        <is>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="E452" s="13" t="inlineStr">
+        <is>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
+        </is>
+      </c>
+      <c r="F452" s="13" t="inlineStr">
+        <is>
+          <t>F-PP-09, A-13</t>
+        </is>
+      </c>
+      <c r="G452" s="13" t="inlineStr"/>
+      <c r="H452" s="13" t="inlineStr"/>
+      <c r="I452" s="13" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B453" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C453" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D453" s="16" t="inlineStr">
+        <is>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+        </is>
+      </c>
+      <c r="E453" s="16" t="inlineStr">
+        <is>
+          <t>Tidak muncul sama sekali</t>
+        </is>
+      </c>
+      <c r="F453" s="16" t="inlineStr">
+        <is>
+          <t>A-17</t>
+        </is>
+      </c>
+      <c r="G453" s="16" t="inlineStr"/>
+      <c r="H453" s="16" t="inlineStr"/>
+      <c r="I453" s="16" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B454" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-04</t>
+        </is>
+      </c>
+      <c r="C454" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D454" s="13" t="inlineStr">
+        <is>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+        </is>
+      </c>
+      <c r="E454" s="13" t="inlineStr">
+        <is>
+          <t>Nominalnya sama dengan yang diajukan</t>
+        </is>
+      </c>
+      <c r="F454" s="13" t="inlineStr">
+        <is>
+          <t>F-FN-03</t>
+        </is>
+      </c>
+      <c r="G454" s="13" t="inlineStr"/>
+      <c r="H454" s="13" t="inlineStr"/>
+      <c r="I454" s="13" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B455" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C455" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D455" s="16" t="inlineStr">
+        <is>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+        </is>
+      </c>
+      <c r="E455" s="16" t="inlineStr">
+        <is>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
+        </is>
+      </c>
+      <c r="F455" s="16" t="inlineStr">
+        <is>
+          <t>A-14</t>
+        </is>
+      </c>
+      <c r="G455" s="16" t="inlineStr"/>
+      <c r="H455" s="16" t="inlineStr"/>
+      <c r="I455" s="16" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B456" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C456" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D456" s="13" t="inlineStr">
+        <is>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+        </is>
+      </c>
+      <c r="E456" s="13" t="inlineStr">
+        <is>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+        </is>
+      </c>
+      <c r="F456" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-10, F-DS-12</t>
+        </is>
+      </c>
+      <c r="G456" s="13" t="inlineStr"/>
+      <c r="H456" s="13" t="inlineStr"/>
+      <c r="I456" s="13" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B457" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C457" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D457" s="16" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E457" s="16" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F457" s="16" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G457" s="16" t="inlineStr"/>
+      <c r="H457" s="16" t="inlineStr"/>
+      <c r="I457" s="16" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B458" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C458" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D458" s="13" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E458" s="13" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F458" s="13" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G458" s="13" t="inlineStr"/>
+      <c r="H458" s="13" t="inlineStr"/>
+      <c r="I458" s="13" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B459" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C459" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D459" s="16" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E459" s="16" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F459" s="16" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G459" s="16" t="inlineStr"/>
+      <c r="H459" s="16" t="inlineStr"/>
+      <c r="I459" s="16" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B460" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C460" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D460" s="13" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E460" s="13" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F460" s="13" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G460" s="13" t="inlineStr"/>
+      <c r="H460" s="13" t="inlineStr"/>
+      <c r="I460" s="13" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B461" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C461" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D461" s="16" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E461" s="16" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F461" s="16" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G461" s="16" t="inlineStr"/>
+      <c r="H461" s="16" t="inlineStr"/>
+      <c r="I461" s="16" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B462" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C462" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D462" s="13" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E462" s="13" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F462" s="13" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G462" s="13" t="inlineStr"/>
+      <c r="H462" s="13" t="inlineStr"/>
+      <c r="I462" s="13" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B463" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C463" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D463" s="16" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E463" s="16" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F463" s="16" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G463" s="16" t="inlineStr"/>
+      <c r="H463" s="16" t="inlineStr"/>
+      <c r="I463" s="16" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B464" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C464" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D464" s="13" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E464" s="13" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F464" s="13" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G464" s="13" t="inlineStr"/>
+      <c r="H464" s="13" t="inlineStr"/>
+      <c r="I464" s="13" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="16" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B445" s="17" t="inlineStr">
+      <c r="B465" s="17" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C445" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D445" s="16" t="inlineStr">
+      <c r="C465" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D465" s="16" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E445" s="16" t="inlineStr">
+      <c r="E465" s="16" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -17390,37 +18090,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F445" s="16" t="inlineStr">
+      <c r="F465" s="16" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G445" s="16" t="inlineStr"/>
-      <c r="H445" s="16" t="inlineStr"/>
-      <c r="I445" s="16" t="inlineStr"/>
-    </row>
-    <row r="446">
-      <c r="A446" s="13" t="inlineStr">
+      <c r="G465" s="16" t="inlineStr"/>
+      <c r="H465" s="16" t="inlineStr"/>
+      <c r="I465" s="16" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B446" s="14" t="inlineStr">
+      <c r="B466" s="14" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C446" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D446" s="13" t="inlineStr">
+      <c r="C466" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D466" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E446" s="13" t="inlineStr">
+      <c r="E466" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -17432,37 +18132,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F446" s="13" t="inlineStr">
+      <c r="F466" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G446" s="13" t="inlineStr"/>
-      <c r="H446" s="13" t="inlineStr"/>
-      <c r="I446" s="13" t="inlineStr"/>
-    </row>
-    <row r="447">
-      <c r="A447" s="16" t="inlineStr">
+      <c r="G466" s="13" t="inlineStr"/>
+      <c r="H466" s="13" t="inlineStr"/>
+      <c r="I466" s="13" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B447" s="17" t="inlineStr">
+      <c r="B467" s="17" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C447" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D447" s="16" t="inlineStr">
+      <c r="C467" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D467" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E447" s="16" t="inlineStr">
+      <c r="E467" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -17474,74 +18174,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F447" s="16" t="inlineStr">
+      <c r="F467" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G447" s="16" t="inlineStr"/>
-      <c r="H447" s="16" t="inlineStr"/>
-      <c r="I447" s="16" t="inlineStr"/>
-    </row>
-    <row r="448">
-      <c r="A448" s="13" t="inlineStr">
+      <c r="G467" s="16" t="inlineStr"/>
+      <c r="H467" s="16" t="inlineStr"/>
+      <c r="I467" s="16" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B448" s="14" t="inlineStr">
+      <c r="B468" s="14" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C448" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D448" s="13" t="inlineStr">
+      <c r="C468" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D468" s="13" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E448" s="13" t="inlineStr">
+      <c r="E468" s="13" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F448" s="13" t="inlineStr">
+      <c r="F468" s="13" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G448" s="13" t="inlineStr"/>
-      <c r="H448" s="13" t="inlineStr"/>
-      <c r="I448" s="13" t="inlineStr"/>
-    </row>
-    <row r="449">
-      <c r="A449" s="16" t="inlineStr">
+      <c r="G468" s="13" t="inlineStr"/>
+      <c r="H468" s="13" t="inlineStr"/>
+      <c r="I468" s="13" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B449" s="17" t="inlineStr">
+      <c r="B469" s="17" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C449" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D449" s="16" t="inlineStr">
+      <c r="C469" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D469" s="16" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E449" s="16" t="inlineStr">
+      <c r="E469" s="16" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -17552,73 +18252,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F449" s="16" t="inlineStr">
+      <c r="F469" s="16" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G449" s="16" t="inlineStr"/>
-      <c r="H449" s="16" t="inlineStr"/>
-      <c r="I449" s="16" t="inlineStr"/>
-    </row>
-    <row r="450">
-      <c r="A450" s="13" t="inlineStr">
+      <c r="G469" s="16" t="inlineStr"/>
+      <c r="H469" s="16" t="inlineStr"/>
+      <c r="I469" s="16" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B450" s="14" t="inlineStr">
+      <c r="B470" s="14" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C450" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D450" s="13" t="inlineStr">
+      <c r="C470" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D470" s="13" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E450" s="13" t="inlineStr">
+      <c r="E470" s="13" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F450" s="13" t="inlineStr">
+      <c r="F470" s="13" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G450" s="13" t="inlineStr"/>
-      <c r="H450" s="13" t="inlineStr"/>
-      <c r="I450" s="13" t="inlineStr"/>
-    </row>
-    <row r="451">
-      <c r="A451" s="16" t="inlineStr">
+      <c r="G470" s="13" t="inlineStr"/>
+      <c r="H470" s="13" t="inlineStr"/>
+      <c r="I470" s="13" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B451" s="17" t="inlineStr">
+      <c r="B471" s="17" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C451" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D451" s="16" t="inlineStr">
+      <c r="C471" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D471" s="16" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E451" s="16" t="inlineStr">
+      <c r="E471" s="16" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -17629,37 +18329,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F451" s="16" t="inlineStr">
+      <c r="F471" s="16" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G451" s="16" t="inlineStr"/>
-      <c r="H451" s="16" t="inlineStr"/>
-      <c r="I451" s="16" t="inlineStr"/>
-    </row>
-    <row r="452">
-      <c r="A452" s="13" t="inlineStr">
+      <c r="G471" s="16" t="inlineStr"/>
+      <c r="H471" s="16" t="inlineStr"/>
+      <c r="I471" s="16" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B452" s="14" t="inlineStr">
+      <c r="B472" s="14" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C452" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D452" s="13" t="inlineStr">
+      <c r="C472" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D472" s="13" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E452" s="13" t="inlineStr">
+      <c r="E472" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -17669,37 +18369,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F452" s="13" t="inlineStr">
+      <c r="F472" s="13" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G452" s="13" t="inlineStr"/>
-      <c r="H452" s="13" t="inlineStr"/>
-      <c r="I452" s="13" t="inlineStr"/>
-    </row>
-    <row r="453">
-      <c r="A453" s="16" t="inlineStr">
+      <c r="G472" s="13" t="inlineStr"/>
+      <c r="H472" s="13" t="inlineStr"/>
+      <c r="I472" s="13" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B453" s="17" t="inlineStr">
+      <c r="B473" s="17" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C453" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D453" s="16" t="inlineStr">
+      <c r="C473" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D473" s="16" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E453" s="16" t="inlineStr">
+      <c r="E473" s="16" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -17707,19 +18407,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F453" s="16" t="inlineStr">
+      <c r="F473" s="16" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G453" s="16" t="inlineStr"/>
-      <c r="H453" s="16" t="inlineStr"/>
-      <c r="I453" s="16" t="inlineStr"/>
+      <c r="G473" s="16" t="inlineStr"/>
+      <c r="H473" s="16" t="inlineStr"/>
+      <c r="I473" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I453"/>
+  <autoFilter ref="A1:I473"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G453" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G473" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$473</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$475</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C473,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C475,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P1",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P1",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P1",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P1",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P1",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P1",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P1",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P1",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C473,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C475,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P2",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P2",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P2",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P2",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P2",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P2",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P2",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P2",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C473,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C475,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P3",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P3",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P3",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P3",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P3",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P3",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C473,"P3",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C475,"P3",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pelanggan",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pelanggan",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pelanggan",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pelanggan",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pelanggan",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pelanggan",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pelanggan",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pelanggan",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kasir",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kasir",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kasir",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kasir",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kasir",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kasir",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kasir",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kasir",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pending Payment",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pending Payment",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pending Payment",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pending Payment",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pending Payment",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pending Payment",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pending Payment",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pending Payment",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Dapur",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Dapur",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Dapur",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Dapur",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Dapur",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Dapur",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Dapur",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Dapur",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Keuangan",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Keuangan",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Keuangan",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Keuangan",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Keuangan",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Keuangan",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Keuangan",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Keuangan",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Setor Saldo Cash",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Setor Saldo Cash",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Setor Saldo Cash",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Setor Saldo Cash",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Setor Saldo Cash",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Setor Saldo Cash",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Setor Saldo Cash",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Setor Saldo Cash",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"QR Meja",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"QR Meja",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"QR Meja",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"QR Meja",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"QR Meja",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"QR Meja",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"QR Meja",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"QR Meja",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Diskon",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Diskon",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Diskon",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Diskon",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Diskon",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Diskon",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Diskon",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Diskon",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembayaran QRIS",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembayaran QRIS",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembayaran QRIS",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembayaran QRIS",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembayaran QRIS",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembayaran QRIS",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembayaran QRIS",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembayaran QRIS",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Tampilan",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Tampilan",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Tampilan",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Tampilan",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Tampilan",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Tampilan",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Tampilan",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Tampilan",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Super Admin",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Super Admin",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Super Admin",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Super Admin",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Super Admin",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Super Admin",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Super Admin",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Super Admin",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembaruan Aplikasi",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembaruan Aplikasi",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembaruan Aplikasi",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembaruan Aplikasi",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembaruan Aplikasi",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembaruan Aplikasi",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Pembaruan Aplikasi",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembaruan Aplikasi",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1510,23 +1510,23 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -1541,23 +1541,23 @@
         </is>
       </c>
       <c r="B34" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G473,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G475,"Lulus")</f>
         <v/>
       </c>
       <c r="D34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G473,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G475,"Gagal")</f>
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G473,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G475,"Terblokir")</f>
         <v/>
       </c>
       <c r="F34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A473,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G473,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G475,"Dilewati")</f>
         <v/>
       </c>
       <c r="G34" s="5">
@@ -1789,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I473"/>
+  <dimension ref="A1:I475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13423,7 +13423,7 @@
       </c>
       <c r="E332" s="13" t="inlineStr">
         <is>
-          <t>Keduanya berkurang sebesar alokasinya</t>
+          <t>Saldo Total tidak berubah — uangnya pindah kantong, bukan hilang</t>
         </is>
       </c>
       <c r="F332" s="13" t="inlineStr">
@@ -13443,27 +13443,27 @@
       </c>
       <c r="B333" s="17" t="inlineStr">
         <is>
-          <t>TC-PF-37</t>
-        </is>
-      </c>
-      <c r="C333" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-PF-36b</t>
+        </is>
+      </c>
+      <c r="C333" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D333" s="16" t="inlineStr">
         <is>
-          <t>Buka Saldo &amp; Pengeluaran untuk KaataGo</t>
+          <t>Voucher dipakai pelanggan di resto</t>
         </is>
       </c>
       <c r="E333" s="16" t="inlineStr">
         <is>
-          <t>Tidak ada kartu Saldo Cash / Non Cash</t>
+          <t>Saldo KaataGo berkurang sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F333" s="16" t="inlineStr">
         <is>
-          <t>F-PF-10</t>
+          <t>F-PF-09</t>
         </is>
       </c>
       <c r="G333" s="16" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="B334" s="14" t="inlineStr">
         <is>
-          <t>TC-PF-38</t>
+          <t>TC-PF-37</t>
         </is>
       </c>
       <c r="C334" s="19" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="D334" s="13" t="inlineStr">
         <is>
-          <t>Buka layar yang sama untuk resto biasa</t>
+          <t>Buka Saldo &amp; Pengeluaran untuk KaataGo</t>
         </is>
       </c>
       <c r="E334" s="13" t="inlineStr">
         <is>
-          <t>Kartu Cash/Non Cash tetap ada</t>
+          <t>Tidak ada kartu Saldo Cash / Non Cash</t>
         </is>
       </c>
       <c r="F334" s="13" t="inlineStr">
@@ -13513,27 +13513,27 @@
       </c>
       <c r="B335" s="17" t="inlineStr">
         <is>
-          <t>TC-CB-01</t>
-        </is>
-      </c>
-      <c r="C335" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-PF-38</t>
+        </is>
+      </c>
+      <c r="C335" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D335" s="16" t="inlineStr">
         <is>
-          <t>Izinkan lokasi, lihat daftar Terdekat</t>
+          <t>Buka layar yang sama untuk resto biasa</t>
         </is>
       </c>
       <c r="E335" s="16" t="inlineStr">
         <is>
-          <t>Hanya resto ≤ 5 km yang muncul</t>
+          <t>Kartu Cash/Non Cash tetap ada</t>
         </is>
       </c>
       <c r="F335" s="16" t="inlineStr">
         <is>
-          <t>F-CB-01</t>
+          <t>F-PF-10</t>
         </is>
       </c>
       <c r="G335" s="16" t="inlineStr"/>
@@ -13548,7 +13548,7 @@
       </c>
       <c r="B336" s="14" t="inlineStr">
         <is>
-          <t>TC-CB-02</t>
+          <t>TC-CB-01</t>
         </is>
       </c>
       <c r="C336" s="15" t="inlineStr">
@@ -13558,17 +13558,17 @@
       </c>
       <c r="D336" s="13" t="inlineStr">
         <is>
-          <t>Resto berjarak 7 km</t>
+          <t>Izinkan lokasi, lihat daftar Terdekat</t>
         </is>
       </c>
       <c r="E336" s="13" t="inlineStr">
         <is>
-          <t>Tidak di Terdekat, tapi ada di Semua Resto</t>
+          <t>Hanya resto ≤ 5 km yang muncul</t>
         </is>
       </c>
       <c r="F336" s="13" t="inlineStr">
         <is>
-          <t>F-CB-01, F-CB-02</t>
+          <t>F-CB-01</t>
         </is>
       </c>
       <c r="G336" s="13" t="inlineStr"/>
@@ -13583,27 +13583,27 @@
       </c>
       <c r="B337" s="17" t="inlineStr">
         <is>
-          <t>TC-CB-03</t>
-        </is>
-      </c>
-      <c r="C337" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-CB-02</t>
+        </is>
+      </c>
+      <c r="C337" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D337" s="16" t="inlineStr">
         <is>
-          <t>Periksa keterangan di judul bagian Terdekat</t>
+          <t>Resto berjarak 7 km</t>
         </is>
       </c>
       <c r="E337" s="16" t="inlineStr">
         <is>
-          <t>Tertulis "Dalam 5 km dari kamu"</t>
+          <t>Tidak di Terdekat, tapi ada di Semua Resto</t>
         </is>
       </c>
       <c r="F337" s="16" t="inlineStr">
         <is>
-          <t>F-CB-01</t>
+          <t>F-CB-01, F-CB-02</t>
         </is>
       </c>
       <c r="G337" s="16" t="inlineStr"/>
@@ -13618,7 +13618,7 @@
       </c>
       <c r="B338" s="14" t="inlineStr">
         <is>
-          <t>TC-CB-04</t>
+          <t>TC-CB-03</t>
         </is>
       </c>
       <c r="C338" s="19" t="inlineStr">
@@ -13628,17 +13628,17 @@
       </c>
       <c r="D338" s="13" t="inlineStr">
         <is>
-          <t>Tolak izin lokasi</t>
+          <t>Periksa keterangan di judul bagian Terdekat</t>
         </is>
       </c>
       <c r="E338" s="13" t="inlineStr">
         <is>
-          <t>Bagian Terdekat tidak tampil; Semua Resto tetap ada</t>
+          <t>Tertulis "Dalam 5 km dari kamu"</t>
         </is>
       </c>
       <c r="F338" s="13" t="inlineStr">
         <is>
-          <t>F-CB-02</t>
+          <t>F-CB-01</t>
         </is>
       </c>
       <c r="G338" s="13" t="inlineStr"/>
@@ -13653,27 +13653,27 @@
       </c>
       <c r="B339" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-01</t>
-        </is>
-      </c>
-      <c r="C339" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-CB-04</t>
+        </is>
+      </c>
+      <c r="C339" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D339" s="16" t="inlineStr">
         <is>
-          <t>Owner → Saldo &amp; Pengeluaran → Top Up Saldo</t>
+          <t>Tolak izin lokasi</t>
         </is>
       </c>
       <c r="E339" s="16" t="inlineStr">
         <is>
-          <t>Tersimpan; Saldo Total naik sebesar nominalnya</t>
+          <t>Bagian Terdekat tidak tampil; Semua Resto tetap ada</t>
         </is>
       </c>
       <c r="F339" s="16" t="inlineStr">
         <is>
-          <t>F-TU-01, F-TU-02</t>
+          <t>F-CB-02</t>
         </is>
       </c>
       <c r="G339" s="16" t="inlineStr"/>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="B340" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-02</t>
+          <t>TC-TU-01</t>
         </is>
       </c>
       <c r="C340" s="15" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL sesudahnya</t>
+          <t>Owner → Saldo &amp; Pengeluaran → Top Up Saldo</t>
         </is>
       </c>
       <c r="E340" s="13" t="inlineStr">
         <is>
-          <t>Kredit GL Total Saldo, debit GL Setoran Modal</t>
+          <t>Tersimpan; Saldo Total naik sebesar nominalnya</t>
         </is>
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>F-TU-05</t>
+          <t>F-TU-01, F-TU-02</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr"/>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="B341" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-03</t>
+          <t>TC-TU-01b</t>
         </is>
       </c>
       <c r="C341" s="18" t="inlineStr">
@@ -13733,17 +13733,17 @@
       </c>
       <c r="D341" s="16" t="inlineStr">
         <is>
-          <t>Periksa Laporan Transaksi / Pemasukan</t>
+          <t>Super Admin top up, periksa Saldo Total KaataGo</t>
         </is>
       </c>
       <c r="E341" s="16" t="inlineStr">
         <is>
-          <t>Setoran tidak muncul sebagai penjualan</t>
+          <t>Naik sebesar nominalnya — bukan tetap</t>
         </is>
       </c>
       <c r="F341" s="16" t="inlineStr">
         <is>
-          <t>F-TU-02</t>
+          <t>F-TU-02, F-TU-05</t>
         </is>
       </c>
       <c r="G341" s="16" t="inlineStr"/>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B342" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-04</t>
+          <t>TC-TU-02</t>
         </is>
       </c>
       <c r="C342" s="15" t="inlineStr">
@@ -13768,17 +13768,17 @@
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
-          <t>Simpan tanpa mengisi Dari</t>
+          <t>Periksa Jurnal GL sesudahnya</t>
         </is>
       </c>
       <c r="E342" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Sebutkan penyetornya"</t>
+          <t>Satu baris kredit ke GL Setoran Modal</t>
         </is>
       </c>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>F-TU-03</t>
+          <t>F-TU-05</t>
         </is>
       </c>
       <c r="G342" s="13" t="inlineStr"/>
@@ -13793,27 +13793,27 @@
       </c>
       <c r="B343" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-05</t>
-        </is>
-      </c>
-      <c r="C343" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TU-03</t>
+        </is>
+      </c>
+      <c r="C343" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D343" s="16" t="inlineStr">
         <is>
-          <t>Simpan tanpa bukti</t>
+          <t>Periksa Laporan Transaksi / Pemasukan</t>
         </is>
       </c>
       <c r="E343" s="16" t="inlineStr">
         <is>
-          <t>Tetap tersimpan — buktinya opsional</t>
+          <t>Setoran tidak muncul sebagai penjualan</t>
         </is>
       </c>
       <c r="F343" s="16" t="inlineStr">
         <is>
-          <t>F-TU-03</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G343" s="16" t="inlineStr"/>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="B344" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-06</t>
+          <t>TC-TU-04</t>
         </is>
       </c>
       <c r="C344" s="15" t="inlineStr">
@@ -13838,17 +13838,17 @@
       </c>
       <c r="D344" s="13" t="inlineStr">
         <is>
-          <t>Masuk sebagai Kasir, buka layar yang sama</t>
+          <t>Simpan tanpa mengisi Dari</t>
         </is>
       </c>
       <c r="E344" s="13" t="inlineStr">
         <is>
-          <t>Riwayat terlihat, tombol Top Up Saldo tidak ada</t>
+          <t>Ditolak — "Sebutkan penyetornya"</t>
         </is>
       </c>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>F-TU-04</t>
+          <t>F-TU-03</t>
         </is>
       </c>
       <c r="G344" s="13" t="inlineStr"/>
@@ -13863,27 +13863,27 @@
       </c>
       <c r="B345" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-07</t>
-        </is>
-      </c>
-      <c r="C345" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-05</t>
+        </is>
+      </c>
+      <c r="C345" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D345" s="16" t="inlineStr">
         <is>
-          <t>Kasir memanggil insert balance_topups lewat API</t>
+          <t>Simpan tanpa bukti</t>
         </is>
       </c>
       <c r="E345" s="16" t="inlineStr">
         <is>
-          <t>Ditolak RLS</t>
+          <t>Tetap tersimpan — buktinya opsional</t>
         </is>
       </c>
       <c r="F345" s="16" t="inlineStr">
         <is>
-          <t>F-TU-04</t>
+          <t>F-TU-03</t>
         </is>
       </c>
       <c r="G345" s="16" t="inlineStr"/>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="B346" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-08</t>
+          <t>TC-TU-06</t>
         </is>
       </c>
       <c r="C346" s="15" t="inlineStr">
@@ -13908,17 +13908,17 @@
       </c>
       <c r="D346" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Saldo &amp; Pengeluaran → Top Up</t>
+          <t>Masuk sebagai Kasir, buka layar yang sama</t>
         </is>
       </c>
       <c r="E346" s="13" t="inlineStr">
         <is>
-          <t>Saldo KaataGo naik; Jurnal GL KaataGo mencatatnya</t>
+          <t>Riwayat terlihat, tombol Top Up Saldo tidak ada</t>
         </is>
       </c>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>F-TU-01, F-TU-05</t>
+          <t>F-TU-04</t>
         </is>
       </c>
       <c r="G346" s="13" t="inlineStr"/>
@@ -13933,7 +13933,7 @@
       </c>
       <c r="B347" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-09</t>
+          <t>TC-TU-07</t>
         </is>
       </c>
       <c r="C347" s="18" t="inlineStr">
@@ -13943,17 +13943,17 @@
       </c>
       <c r="D347" s="16" t="inlineStr">
         <is>
-          <t>Coba ubah atau hapus baris balance_topups</t>
+          <t>Kasir memanggil insert balance_topups lewat API</t>
         </is>
       </c>
       <c r="E347" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — tidak ada kebijakannya</t>
+          <t>Ditolak RLS</t>
         </is>
       </c>
       <c r="F347" s="16" t="inlineStr">
         <is>
-          <t>F-TU-06</t>
+          <t>F-TU-04</t>
         </is>
       </c>
       <c r="G347" s="16" t="inlineStr"/>
@@ -13968,27 +13968,27 @@
       </c>
       <c r="B348" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-10</t>
-        </is>
-      </c>
-      <c r="C348" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TU-08</t>
+        </is>
+      </c>
+      <c r="C348" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D348" s="13" t="inlineStr">
         <is>
-          <t>Periksa kartu Cash / Non Cash sesudah top up</t>
+          <t>Super Admin → Finance → Saldo &amp; Pengeluaran → Top Up</t>
         </is>
       </c>
       <c r="E348" s="13" t="inlineStr">
         <is>
-          <t>Non Cash naik; keduanya tetap berjumlah sama dengan Penghasilan</t>
+          <t>Saldo KaataGo naik; Jurnal GL KaataGo mencatatnya</t>
         </is>
       </c>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>F-TU-02</t>
+          <t>F-TU-01, F-TU-05</t>
         </is>
       </c>
       <c r="G348" s="13" t="inlineStr"/>
@@ -14003,27 +14003,27 @@
       </c>
       <c r="B349" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-11</t>
-        </is>
-      </c>
-      <c r="C349" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TU-09</t>
+        </is>
+      </c>
+      <c r="C349" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D349" s="16" t="inlineStr">
         <is>
-          <t>Buka Pemetaan GL sebagai Finance resto</t>
+          <t>Coba ubah atau hapus baris balance_topups</t>
         </is>
       </c>
       <c r="E349" s="16" t="inlineStr">
         <is>
-          <t>Ada bagian GL Modal</t>
+          <t>Ditolak — tidak ada kebijakannya</t>
         </is>
       </c>
       <c r="F349" s="16" t="inlineStr">
         <is>
-          <t>F-TU-02</t>
+          <t>F-TU-06</t>
         </is>
       </c>
       <c r="G349" s="16" t="inlineStr"/>
@@ -14038,7 +14038,7 @@
       </c>
       <c r="B350" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-12</t>
+          <t>TC-TU-10</t>
         </is>
       </c>
       <c r="C350" s="19" t="inlineStr">
@@ -14048,17 +14048,17 @@
       </c>
       <c r="D350" s="13" t="inlineStr">
         <is>
-          <t>Buka halaman awal aplikasi</t>
+          <t>Periksa kartu Cash / Non Cash sesudah top up</t>
         </is>
       </c>
       <c r="E350" s="13" t="inlineStr">
         <is>
-          <t>Tombolnya bertuliskan KaataGo Merchant</t>
+          <t>Non Cash naik; keduanya tetap berjumlah sama dengan Penghasilan</t>
         </is>
       </c>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G350" s="13" t="inlineStr"/>
@@ -14068,32 +14068,32 @@
     <row r="351">
       <c r="A351" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B351" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-01</t>
-        </is>
-      </c>
-      <c r="C351" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-11</t>
+        </is>
+      </c>
+      <c r="C351" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D351" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
+          <t>Buka Pemetaan GL sebagai Finance resto</t>
         </is>
       </c>
       <c r="E351" s="16" t="inlineStr">
         <is>
-          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
+          <t>Ada bagian GL Modal</t>
         </is>
       </c>
       <c r="F351" s="16" t="inlineStr">
         <is>
-          <t>F-VC-01, F-VC-02</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G351" s="16" t="inlineStr"/>
@@ -14103,32 +14103,32 @@
     <row r="352">
       <c r="A352" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B352" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-02</t>
-        </is>
-      </c>
-      <c r="C352" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-12</t>
+        </is>
+      </c>
+      <c r="C352" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D352" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan Rp 1.000.000 jadi 3</t>
+          <t>Buka halaman awal aplikasi</t>
         </is>
       </c>
       <c r="E352" s="13" t="inlineStr">
         <is>
-          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
+          <t>Tombolnya bertuliskan KaataGo Merchant</t>
         </is>
       </c>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>F-VC-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G352" s="13" t="inlineStr"/>
@@ -14143,27 +14143,27 @@
       </c>
       <c r="B353" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-03</t>
-        </is>
-      </c>
-      <c r="C353" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-01</t>
+        </is>
+      </c>
+      <c r="C353" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D353" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan dengan kode yang sudah dipakai</t>
+          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
         </is>
       </c>
       <c r="E353" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — kodenya sudah ada</t>
+          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
         </is>
       </c>
       <c r="F353" s="16" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-VC-01, F-VC-02</t>
         </is>
       </c>
       <c r="G353" s="16" t="inlineStr"/>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="B354" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-04</t>
+          <t>TC-VC-02</t>
         </is>
       </c>
       <c r="C354" s="15" t="inlineStr">
@@ -14188,17 +14188,17 @@
       </c>
       <c r="D354" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
+          <t>Terbitkan Rp 1.000.000 jadi 3</t>
         </is>
       </c>
       <c r="E354" s="13" t="inlineStr">
         <is>
-          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
+          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
         </is>
       </c>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-02</t>
         </is>
       </c>
       <c r="G354" s="13" t="inlineStr"/>
@@ -14213,27 +14213,27 @@
       </c>
       <c r="B355" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-05</t>
-        </is>
-      </c>
-      <c r="C355" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-03</t>
+        </is>
+      </c>
+      <c r="C355" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D355" s="16" t="inlineStr">
         <is>
-          <t>Pelanggan menebus kode di Voucher Saya</t>
+          <t>Terbitkan dengan kode yang sudah dipakai</t>
         </is>
       </c>
       <c r="E355" s="16" t="inlineStr">
         <is>
-          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
+          <t>Ditolak — kodenya sudah ada</t>
         </is>
       </c>
       <c r="F355" s="16" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G355" s="16" t="inlineStr"/>
@@ -14248,27 +14248,27 @@
       </c>
       <c r="B356" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-06</t>
-        </is>
-      </c>
-      <c r="C356" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-04</t>
+        </is>
+      </c>
+      <c r="C356" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D356" s="13" t="inlineStr">
         <is>
-          <t>Ketik kodenya dengan huruf kecil</t>
+          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
         </is>
       </c>
       <c r="E356" s="13" t="inlineStr">
         <is>
-          <t>Tetap diterima</t>
+          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
         </is>
       </c>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G356" s="13" t="inlineStr"/>
@@ -14283,27 +14283,27 @@
       </c>
       <c r="B357" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-07</t>
-        </is>
-      </c>
-      <c r="C357" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-05</t>
+        </is>
+      </c>
+      <c r="C357" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D357" s="16" t="inlineStr">
         <is>
-          <t>Ketik kode yang tidak ada</t>
+          <t>Pelanggan menebus kode di Voucher Saya</t>
         </is>
       </c>
       <c r="E357" s="16" t="inlineStr">
         <is>
-          <t>"Kode voucher tidak ditemukan"</t>
+          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
         </is>
       </c>
       <c r="F357" s="16" t="inlineStr">
         <is>
-          <t>F-VC-10</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G357" s="16" t="inlineStr"/>
@@ -14318,27 +14318,27 @@
       </c>
       <c r="B358" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-08</t>
-        </is>
-      </c>
-      <c r="C358" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-06</t>
+        </is>
+      </c>
+      <c r="C358" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D358" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
+          <t>Ketik kodenya dengan huruf kecil</t>
         </is>
       </c>
       <c r="E358" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
+          <t>Tetap diterima</t>
         </is>
       </c>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G358" s="13" t="inlineStr"/>
@@ -14353,27 +14353,27 @@
       </c>
       <c r="B359" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-09</t>
-        </is>
-      </c>
-      <c r="C359" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-07</t>
+        </is>
+      </c>
+      <c r="C359" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D359" s="16" t="inlineStr">
         <is>
-          <t>Orang yang sama menebus kode itu lagi</t>
+          <t>Ketik kode yang tidak ada</t>
         </is>
       </c>
       <c r="E359" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
+          <t>"Kode voucher tidak ditemukan"</t>
         </is>
       </c>
       <c r="F359" s="16" t="inlineStr">
         <is>
-          <t>F-VC-08, F-VC-10</t>
+          <t>F-VC-10</t>
         </is>
       </c>
       <c r="G359" s="16" t="inlineStr"/>
@@ -14388,7 +14388,7 @@
       </c>
       <c r="B360" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-10</t>
+          <t>TC-VC-08</t>
         </is>
       </c>
       <c r="C360" s="15" t="inlineStr">
@@ -14398,17 +14398,17 @@
       </c>
       <c r="D360" s="13" t="inlineStr">
         <is>
-          <t>Batch berisi 10, orang ke-11 menebus</t>
+          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
         </is>
       </c>
       <c r="E360" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Voucher ini sudah habis"</t>
+          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
         </is>
       </c>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>F-VC-09, F-VC-10</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G360" s="13" t="inlineStr"/>
@@ -14423,7 +14423,7 @@
       </c>
       <c r="B361" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-11</t>
+          <t>TC-VC-09</t>
         </is>
       </c>
       <c r="C361" s="18" t="inlineStr">
@@ -14433,17 +14433,17 @@
       </c>
       <c r="D361" s="16" t="inlineStr">
         <is>
-          <t>Dua orang menebus voucher terakhir bersamaan</t>
+          <t>Orang yang sama menebus kode itu lagi</t>
         </is>
       </c>
       <c r="E361" s="16" t="inlineStr">
         <is>
-          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
+          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
         </is>
       </c>
       <c r="F361" s="16" t="inlineStr">
         <is>
-          <t>F-VC-09</t>
+          <t>F-VC-08, F-VC-10</t>
         </is>
       </c>
       <c r="G361" s="16" t="inlineStr"/>
@@ -14458,27 +14458,27 @@
       </c>
       <c r="B362" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-12</t>
-        </is>
-      </c>
-      <c r="C362" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-10</t>
+        </is>
+      </c>
+      <c r="C362" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D362" s="13" t="inlineStr">
         <is>
-          <t>Tebus voucher dari batch yang sudah ditutup</t>
+          <t>Batch berisi 10, orang ke-11 menebus</t>
         </is>
       </c>
       <c r="E362" s="13" t="inlineStr">
         <is>
-          <t>"Voucher ini sudah ditutup"</t>
+          <t>Ditolak — "Voucher ini sudah habis"</t>
         </is>
       </c>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-VC-09, F-VC-10</t>
         </is>
       </c>
       <c r="G362" s="13" t="inlineStr"/>
@@ -14493,27 +14493,27 @@
       </c>
       <c r="B363" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-13</t>
-        </is>
-      </c>
-      <c r="C363" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-11</t>
+        </is>
+      </c>
+      <c r="C363" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D363" s="16" t="inlineStr">
         <is>
-          <t>Tebus voucher yang lewat masa berlaku</t>
+          <t>Dua orang menebus voucher terakhir bersamaan</t>
         </is>
       </c>
       <c r="E363" s="16" t="inlineStr">
         <is>
-          <t>"Voucher ini sudah kedaluwarsa"</t>
+          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
         </is>
       </c>
       <c r="F363" s="16" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-VC-09</t>
         </is>
       </c>
       <c r="G363" s="16" t="inlineStr"/>
@@ -14528,27 +14528,27 @@
       </c>
       <c r="B364" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-14</t>
-        </is>
-      </c>
-      <c r="C364" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-12</t>
+        </is>
+      </c>
+      <c r="C364" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D364" s="13" t="inlineStr">
         <is>
-          <t>Di keranjang, ketuk baris voucher</t>
+          <t>Tebus voucher dari batch yang sudah ditutup</t>
         </is>
       </c>
       <c r="E364" s="13" t="inlineStr">
         <is>
-          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
+          <t>"Voucher ini sudah ditutup"</t>
         </is>
       </c>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G364" s="13" t="inlineStr"/>
@@ -14563,27 +14563,27 @@
       </c>
       <c r="B365" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-15</t>
-        </is>
-      </c>
-      <c r="C365" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-13</t>
+        </is>
+      </c>
+      <c r="C365" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D365" s="16" t="inlineStr">
         <is>
-          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
+          <t>Tebus voucher yang lewat masa berlaku</t>
         </is>
       </c>
       <c r="E365" s="16" t="inlineStr">
         <is>
-          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
+          <t>"Voucher ini sudah kedaluwarsa"</t>
         </is>
       </c>
       <c r="F365" s="16" t="inlineStr">
         <is>
-          <t>F-VC-05, F-VC-10</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G365" s="16" t="inlineStr"/>
@@ -14598,7 +14598,7 @@
       </c>
       <c r="B366" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-16</t>
+          <t>TC-VC-14</t>
         </is>
       </c>
       <c r="C366" s="15" t="inlineStr">
@@ -14608,17 +14608,17 @@
       </c>
       <c r="D366" s="13" t="inlineStr">
         <is>
-          <t>Voucher khusus resto A dibuka di resto B</t>
+          <t>Di keranjang, ketuk baris voucher</t>
         </is>
       </c>
       <c r="E366" s="13" t="inlineStr">
         <is>
-          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
+          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
         </is>
       </c>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>F-VC-06, F-VC-10</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G366" s="13" t="inlineStr"/>
@@ -14633,7 +14633,7 @@
       </c>
       <c r="B367" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-17</t>
+          <t>TC-VC-15</t>
         </is>
       </c>
       <c r="C367" s="18" t="inlineStr">
@@ -14643,17 +14643,17 @@
       </c>
       <c r="D367" s="16" t="inlineStr">
         <is>
-          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
+          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
         </is>
       </c>
       <c r="E367" s="16" t="inlineStr">
         <is>
-          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
+          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
         </is>
       </c>
       <c r="F367" s="16" t="inlineStr">
         <is>
-          <t>F-VC-12</t>
+          <t>F-VC-05, F-VC-10</t>
         </is>
       </c>
       <c r="G367" s="16" t="inlineStr"/>
@@ -14668,7 +14668,7 @@
       </c>
       <c r="B368" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-18</t>
+          <t>TC-VC-16</t>
         </is>
       </c>
       <c r="C368" s="15" t="inlineStr">
@@ -14678,17 +14678,17 @@
       </c>
       <c r="D368" s="13" t="inlineStr">
         <is>
-          <t>Pasang voucher lalu selesaikan pesanan</t>
+          <t>Voucher khusus resto A dibuka di resto B</t>
         </is>
       </c>
       <c r="E368" s="13" t="inlineStr">
         <is>
-          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
+          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
         </is>
       </c>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-06, F-VC-10</t>
         </is>
       </c>
       <c r="G368" s="13" t="inlineStr"/>
@@ -14703,7 +14703,7 @@
       </c>
       <c r="B369" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-19</t>
+          <t>TC-VC-17</t>
         </is>
       </c>
       <c r="C369" s="18" t="inlineStr">
@@ -14713,17 +14713,17 @@
       </c>
       <c r="D369" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Lepas setelah voucher terpasang</t>
+          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
         </is>
       </c>
       <c r="E369" s="16" t="inlineStr">
         <is>
-          <t>Tagihan kembali ke nominal semula</t>
+          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
         </is>
       </c>
       <c r="F369" s="16" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-12</t>
         </is>
       </c>
       <c r="G369" s="16" t="inlineStr"/>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="B370" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-20</t>
+          <t>TC-VC-18</t>
         </is>
       </c>
       <c r="C370" s="15" t="inlineStr">
@@ -14748,17 +14748,17 @@
       </c>
       <c r="D370" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
+          <t>Pasang voucher lalu selesaikan pesanan</t>
         </is>
       </c>
       <c r="E370" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
+          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
         </is>
       </c>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G370" s="13" t="inlineStr"/>
@@ -14773,7 +14773,7 @@
       </c>
       <c r="B371" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-21</t>
+          <t>TC-VC-19</t>
         </is>
       </c>
       <c r="C371" s="18" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="D371" s="16" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL restonya</t>
+          <t>Ketuk Lepas setelah voucher terpasang</t>
         </is>
       </c>
       <c r="E371" s="16" t="inlineStr">
         <is>
-          <t>Ada baris masuk sebesar nilai vouchernya</t>
+          <t>Tagihan kembali ke nominal semula</t>
         </is>
       </c>
       <c r="F371" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G371" s="16" t="inlineStr"/>
@@ -14808,27 +14808,27 @@
       </c>
       <c r="B372" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-22</t>
-        </is>
-      </c>
-      <c r="C372" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-20</t>
+        </is>
+      </c>
+      <c r="C372" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D372" s="13" t="inlineStr">
         <is>
-          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
+          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
         </is>
       </c>
       <c r="E372" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul di daftar pilihan</t>
+          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
         </is>
       </c>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G372" s="13" t="inlineStr"/>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="B373" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-23</t>
+          <t>TC-VC-21</t>
         </is>
       </c>
       <c r="C373" s="18" t="inlineStr">
@@ -14853,17 +14853,17 @@
       </c>
       <c r="D373" s="16" t="inlineStr">
         <is>
-          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
+          <t>Periksa Jurnal GL restonya</t>
         </is>
       </c>
       <c r="E373" s="16" t="inlineStr">
         <is>
-          <t>Debit Voucher Redeem, kredit Total Saldo</t>
+          <t>Ada baris masuk sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F373" s="16" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G373" s="16" t="inlineStr"/>
@@ -14878,27 +14878,27 @@
       </c>
       <c r="B374" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-24</t>
-        </is>
-      </c>
-      <c r="C374" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-22</t>
+        </is>
+      </c>
+      <c r="C374" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D374" s="13" t="inlineStr">
         <is>
-          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
+          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
         </is>
       </c>
       <c r="E374" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
+          <t>Tidak muncul di daftar pilihan</t>
         </is>
       </c>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G374" s="13" t="inlineStr"/>
@@ -14913,7 +14913,7 @@
       </c>
       <c r="B375" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-25</t>
+          <t>TC-VC-23</t>
         </is>
       </c>
       <c r="C375" s="18" t="inlineStr">
@@ -14923,12 +14923,12 @@
       </c>
       <c r="D375" s="16" t="inlineStr">
         <is>
-          <t>Jalankan expire_vouchers() dua kali</t>
+          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
         </is>
       </c>
       <c r="E375" s="16" t="inlineStr">
         <is>
-          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
+          <t>Debit Voucher Redeem, kredit Total Saldo</t>
         </is>
       </c>
       <c r="F375" s="16" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="B376" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-26</t>
+          <t>TC-VC-24</t>
         </is>
       </c>
       <c r="C376" s="15" t="inlineStr">
@@ -14958,17 +14958,17 @@
       </c>
       <c r="D376" s="13" t="inlineStr">
         <is>
-          <t>Jumlahkan keempat tahap untuk satu batch</t>
+          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
         </is>
       </c>
       <c r="E376" s="13" t="inlineStr">
         <is>
-          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
+          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
         </is>
       </c>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13, F-VC-14</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G376" s="13" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="B377" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-27</t>
+          <t>TC-VC-25</t>
         </is>
       </c>
       <c r="C377" s="18" t="inlineStr">
@@ -14993,17 +14993,17 @@
       </c>
       <c r="D377" s="16" t="inlineStr">
         <is>
-          <t>Tulis langsung ke voucher_claims lewat API</t>
+          <t>Jalankan expire_vouchers() dua kali</t>
         </is>
       </c>
       <c r="E377" s="16" t="inlineStr">
         <is>
-          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
+          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
         </is>
       </c>
       <c r="F377" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G377" s="16" t="inlineStr"/>
@@ -15018,7 +15018,7 @@
       </c>
       <c r="B378" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-28</t>
+          <t>TC-VC-26</t>
         </is>
       </c>
       <c r="C378" s="15" t="inlineStr">
@@ -15028,17 +15028,17 @@
       </c>
       <c r="D378" s="13" t="inlineStr">
         <is>
-          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
+          <t>Jumlahkan keempat tahap untuk satu batch</t>
         </is>
       </c>
       <c r="E378" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
+          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
         </is>
       </c>
       <c r="F378" s="13" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-VC-13, F-VC-14</t>
         </is>
       </c>
       <c r="G378" s="13" t="inlineStr"/>
@@ -15053,27 +15053,27 @@
       </c>
       <c r="B379" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-29</t>
-        </is>
-      </c>
-      <c r="C379" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-27</t>
+        </is>
+      </c>
+      <c r="C379" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D379" s="16" t="inlineStr">
         <is>
-          <t>Periksa kartu batch di layar Super Admin</t>
+          <t>Tulis langsung ke voucher_claims lewat API</t>
         </is>
       </c>
       <c r="E379" s="16" t="inlineStr">
         <is>
-          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
+          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F379" s="16" t="inlineStr">
         <is>
-          <t>F-VC-15</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G379" s="16" t="inlineStr"/>
@@ -15088,27 +15088,27 @@
       </c>
       <c r="B380" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-30</t>
-        </is>
-      </c>
-      <c r="C380" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-28</t>
+        </is>
+      </c>
+      <c r="C380" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D380" s="13" t="inlineStr">
         <is>
-          <t>Tutup sebuah batch yang kuotanya masih ada</t>
+          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
         </is>
       </c>
       <c r="E380" s="13" t="inlineStr">
         <is>
-          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
+          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
         </is>
       </c>
       <c r="F380" s="13" t="inlineStr">
         <is>
-          <t>F-VC-04</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G380" s="13" t="inlineStr"/>
@@ -15123,27 +15123,27 @@
       </c>
       <c r="B381" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-31</t>
-        </is>
-      </c>
-      <c r="C381" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-29</t>
+        </is>
+      </c>
+      <c r="C381" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D381" s="16" t="inlineStr">
         <is>
-          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
+          <t>Periksa kartu batch di layar Super Admin</t>
         </is>
       </c>
       <c r="E381" s="16" t="inlineStr">
         <is>
-          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
+          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
         </is>
       </c>
       <c r="F381" s="16" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-15</t>
         </is>
       </c>
       <c r="G381" s="16" t="inlineStr"/>
@@ -15158,27 +15158,27 @@
       </c>
       <c r="B382" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-32</t>
-        </is>
-      </c>
-      <c r="C382" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-30</t>
+        </is>
+      </c>
+      <c r="C382" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D382" s="13" t="inlineStr">
         <is>
-          <t>Jalankan settle-voucher-payouts</t>
+          <t>Tutup sebuah batch yang kuotanya masih ada</t>
         </is>
       </c>
       <c r="E382" s="13" t="inlineStr">
         <is>
-          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
+          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F382" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-04</t>
         </is>
       </c>
       <c r="G382" s="13" t="inlineStr"/>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="B383" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-33</t>
+          <t>TC-VC-31</t>
         </is>
       </c>
       <c r="C383" s="18" t="inlineStr">
@@ -15203,17 +15203,17 @@
       </c>
       <c r="D383" s="16" t="inlineStr">
         <is>
-          <t>Jalankan fungsinya dua kali berturut-turut</t>
+          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
         </is>
       </c>
       <c r="E383" s="16" t="inlineStr">
         <is>
-          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
+          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F383" s="16" t="inlineStr">
         <is>
-          <t>F-VC-18</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G383" s="16" t="inlineStr"/>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="B384" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-34</t>
+          <t>TC-VC-32</t>
         </is>
       </c>
       <c r="C384" s="15" t="inlineStr">
@@ -15238,17 +15238,17 @@
       </c>
       <c r="D384" s="13" t="inlineStr">
         <is>
-          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
+          <t>Jalankan settle-voucher-payouts</t>
         </is>
       </c>
       <c r="E384" s="13" t="inlineStr">
         <is>
-          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
+          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
         </is>
       </c>
       <c r="F384" s="13" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G384" s="13" t="inlineStr"/>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="B385" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-35</t>
+          <t>TC-VC-33</t>
         </is>
       </c>
       <c r="C385" s="18" t="inlineStr">
@@ -15273,17 +15273,17 @@
       </c>
       <c r="D385" s="16" t="inlineStr">
         <is>
-          <t>Perbaiki kuncinya lalu jalankan lagi</t>
+          <t>Jalankan fungsinya dua kali berturut-turut</t>
         </is>
       </c>
       <c r="E385" s="16" t="inlineStr">
         <is>
-          <t>Baris yang tadi gagal terkirim</t>
+          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
         </is>
       </c>
       <c r="F385" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G385" s="16" t="inlineStr"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="B386" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-36</t>
+          <t>TC-VC-34</t>
         </is>
       </c>
       <c r="C386" s="15" t="inlineStr">
@@ -15308,17 +15308,17 @@
       </c>
       <c r="D386" s="13" t="inlineStr">
         <is>
-          <t>Pakai voucher di resto yang belum punya sub-akun</t>
+          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
         </is>
       </c>
       <c r="E386" s="13" t="inlineStr">
         <is>
-          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
+          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
         </is>
       </c>
       <c r="F386" s="13" t="inlineStr">
         <is>
-          <t>F-VC-19</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G386" s="13" t="inlineStr"/>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="B387" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-37</t>
+          <t>TC-VC-35</t>
         </is>
       </c>
       <c r="C387" s="18" t="inlineStr">
@@ -15343,12 +15343,12 @@
       </c>
       <c r="D387" s="16" t="inlineStr">
         <is>
-          <t>Buat pesanan bervoucher saat Xendit mati total</t>
+          <t>Perbaiki kuncinya lalu jalankan lagi</t>
         </is>
       </c>
       <c r="E387" s="16" t="inlineStr">
         <is>
-          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
+          <t>Baris yang tadi gagal terkirim</t>
         </is>
       </c>
       <c r="F387" s="16" t="inlineStr">
@@ -15368,27 +15368,27 @@
       </c>
       <c r="B388" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-38</t>
-        </is>
-      </c>
-      <c r="C388" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-36</t>
+        </is>
+      </c>
+      <c r="C388" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D388" s="13" t="inlineStr">
         <is>
-          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
+          <t>Pakai voucher di resto yang belum punya sub-akun</t>
         </is>
       </c>
       <c r="E388" s="13" t="inlineStr">
         <is>
-          <t>Klaim used lama ikut terantre</t>
+          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
         </is>
       </c>
       <c r="F388" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G388" s="13" t="inlineStr"/>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B389" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-39</t>
+          <t>TC-VC-37</t>
         </is>
       </c>
       <c r="C389" s="18" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="D389" s="16" t="inlineStr">
         <is>
-          <t>Tulis langsung ke voucher_payouts lewat API</t>
+          <t>Buat pesanan bervoucher saat Xendit mati total</t>
         </is>
       </c>
       <c r="E389" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
+          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
         </is>
       </c>
       <c r="F389" s="16" t="inlineStr">
         <is>
-          <t>F-VC-18</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G389" s="16" t="inlineStr"/>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="B390" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-40</t>
+          <t>TC-VC-38</t>
         </is>
       </c>
       <c r="C390" s="19" t="inlineStr">
@@ -15448,12 +15448,12 @@
       </c>
       <c r="D390" s="13" t="inlineStr">
         <is>
-          <t>Baca voucher_payout_config sebagai Super Admin</t>
+          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
         </is>
       </c>
       <c r="E390" s="13" t="inlineStr">
         <is>
-          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
+          <t>Klaim used lama ikut terantre</t>
         </is>
       </c>
       <c r="F390" s="13" t="inlineStr">
@@ -15473,27 +15473,27 @@
       </c>
       <c r="B391" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-41</t>
-        </is>
-      </c>
-      <c r="C391" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-39</t>
+        </is>
+      </c>
+      <c r="C391" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D391" s="16" t="inlineStr">
         <is>
-          <t>Jalankan penjadwal sebelum function_url diisi</t>
+          <t>Tulis langsung ke voucher_payouts lewat API</t>
         </is>
       </c>
       <c r="E391" s="16" t="inlineStr">
         <is>
-          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
+          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F391" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G391" s="16" t="inlineStr"/>
@@ -15508,22 +15508,22 @@
       </c>
       <c r="B392" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-42</t>
-        </is>
-      </c>
-      <c r="C392" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-40</t>
+        </is>
+      </c>
+      <c r="C392" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D392" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
+          <t>Baca voucher_payout_config sebagai Super Admin</t>
         </is>
       </c>
       <c r="E392" s="13" t="inlineStr">
         <is>
-          <t>Cocok baris per baris lewat transfer_id</t>
+          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
         </is>
       </c>
       <c r="F392" s="13" t="inlineStr">
@@ -15543,27 +15543,27 @@
       </c>
       <c r="B393" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-43</t>
-        </is>
-      </c>
-      <c r="C393" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-41</t>
+        </is>
+      </c>
+      <c r="C393" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D393" s="16" t="inlineStr">
         <is>
-          <t>Jalankan pencairan saat xenPlatform belum aktif</t>
+          <t>Jalankan penjadwal sebelum function_url diisi</t>
         </is>
       </c>
       <c r="E393" s="16" t="inlineStr">
         <is>
-          <t>Seluruh antrean tetap pending, attempts nol, tidak ada galat</t>
+          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
         </is>
       </c>
       <c r="F393" s="16" t="inlineStr">
         <is>
-          <t>F-VC-19</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G393" s="16" t="inlineStr"/>
@@ -15578,27 +15578,27 @@
       </c>
       <c r="B394" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-44</t>
-        </is>
-      </c>
-      <c r="C394" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-42</t>
+        </is>
+      </c>
+      <c r="C394" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D394" s="13" t="inlineStr">
         <is>
-          <t>Aktifkan xenPlatform + pasang sub-akun, lalu tunggu penjadwal</t>
+          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
         </is>
       </c>
       <c r="E394" s="13" t="inlineStr">
         <is>
-          <t>Tunggakan lama ikut terangkut tanpa dijalankan ulang manual</t>
+          <t>Cocok baris per baris lewat transfer_id</t>
         </is>
       </c>
       <c r="F394" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16, F-VC-17</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G394" s="13" t="inlineStr"/>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="B395" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-45</t>
+          <t>TC-VC-43</t>
         </is>
       </c>
       <c r="C395" s="18" t="inlineStr">
@@ -15623,17 +15623,17 @@
       </c>
       <c r="D395" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Pemetaan GL</t>
+          <t>Jalankan pencairan saat xenPlatform belum aktif</t>
         </is>
       </c>
       <c r="E395" s="16" t="inlineStr">
         <is>
-          <t>Ada bagian GL Voucher berisi GL Voucher dan GL Voucher Redeem</t>
+          <t>Seluruh antrean tetap pending, attempts nol, tidak ada galat</t>
         </is>
       </c>
       <c r="F395" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G395" s="16" t="inlineStr"/>
@@ -15648,27 +15648,27 @@
       </c>
       <c r="B396" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-46</t>
-        </is>
-      </c>
-      <c r="C396" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-44</t>
+        </is>
+      </c>
+      <c r="C396" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D396" s="13" t="inlineStr">
         <is>
-          <t>Buka Pemetaan GL sebagai Finance resto biasa</t>
+          <t>Aktifkan xenPlatform + pasang sub-akun, lalu tunggu penjadwal</t>
         </is>
       </c>
       <c r="E396" s="13" t="inlineStr">
         <is>
-          <t>Bagian GL Voucher tidak muncul, penanda "belum dipetakan" tidak berbunyi</t>
+          <t>Tunggakan lama ikut terangkut tanpa dijalankan ulang manual</t>
         </is>
       </c>
       <c r="F396" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-16, F-VC-17</t>
         </is>
       </c>
       <c r="G396" s="13" t="inlineStr"/>
@@ -15683,22 +15683,22 @@
       </c>
       <c r="B397" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-47</t>
-        </is>
-      </c>
-      <c r="C397" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-45</t>
+        </is>
+      </c>
+      <c r="C397" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D397" s="16" t="inlineStr">
         <is>
-          <t>Ubah nomor GL Voucher lalu simpan</t>
+          <t>Super Admin → Finance → Pemetaan GL</t>
         </is>
       </c>
       <c r="E397" s="16" t="inlineStr">
         <is>
-          <t>Tersimpan, dan jurnal voucher berikutnya memakai nomor baru</t>
+          <t>Ada bagian GL Voucher berisi GL Voucher dan GL Voucher Redeem</t>
         </is>
       </c>
       <c r="F397" s="16" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="B398" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-48</t>
+          <t>TC-VC-46</t>
         </is>
       </c>
       <c r="C398" s="15" t="inlineStr">
@@ -15728,17 +15728,17 @@
       </c>
       <c r="D398" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan batch, lalu buka Kotak Masuk pelanggan</t>
+          <t>Buka Pemetaan GL sebagai Finance resto biasa</t>
         </is>
       </c>
       <c r="E398" s="13" t="inlineStr">
         <is>
-          <t>Ada kabar di tab Umum berisi kode, nilai, kuota, dan tenggat</t>
+          <t>Bagian GL Voucher tidak muncul, penanda "belum dipetakan" tidak berbunyi</t>
         </is>
       </c>
       <c r="F398" s="13" t="inlineStr">
         <is>
-          <t>F-VC-20, F-VC-21</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G398" s="13" t="inlineStr"/>
@@ -15753,27 +15753,27 @@
       </c>
       <c r="B399" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-49</t>
-        </is>
-      </c>
-      <c r="C399" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-47</t>
+        </is>
+      </c>
+      <c r="C399" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D399" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch dengan HP pelanggan terkunci</t>
+          <t>Ubah nomor GL Voucher lalu simpan</t>
         </is>
       </c>
       <c r="E399" s="16" t="inlineStr">
         <is>
-          <t>Push muncul di layar kunci</t>
+          <t>Tersimpan, dan jurnal voucher berikutnya memakai nomor baru</t>
         </is>
       </c>
       <c r="F399" s="16" t="inlineStr">
         <is>
-          <t>F-VC-20</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G399" s="16" t="inlineStr"/>
@@ -15788,27 +15788,27 @@
       </c>
       <c r="B400" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-50</t>
-        </is>
-      </c>
-      <c r="C400" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-48</t>
+        </is>
+      </c>
+      <c r="C400" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D400" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan batch tanpa minimal belanja</t>
+          <t>Terbitkan batch, lalu buka Kotak Masuk pelanggan</t>
         </is>
       </c>
       <c r="E400" s="13" t="inlineStr">
         <is>
-          <t>Kalimat minimal belanja tidak muncul di pengumuman</t>
+          <t>Ada kabar di tab Umum berisi kode, nilai, kuota, dan tenggat</t>
         </is>
       </c>
       <c r="F400" s="13" t="inlineStr">
         <is>
-          <t>F-VC-21</t>
+          <t>F-VC-20, F-VC-21</t>
         </is>
       </c>
       <c r="G400" s="13" t="inlineStr"/>
@@ -15823,22 +15823,22 @@
       </c>
       <c r="B401" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-51</t>
-        </is>
-      </c>
-      <c r="C401" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-49</t>
+        </is>
+      </c>
+      <c r="C401" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D401" s="16" t="inlineStr">
         <is>
-          <t>Buka Kotak Masuk sebagai pegawai resto</t>
+          <t>Terbitkan batch dengan HP pelanggan terkunci</t>
         </is>
       </c>
       <c r="E401" s="16" t="inlineStr">
         <is>
-          <t>Kabar voucher tidak muncul — audiensnya pelanggan</t>
+          <t>Push muncul di layar kunci</t>
         </is>
       </c>
       <c r="F401" s="16" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="B402" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-52</t>
+          <t>TC-VC-50</t>
         </is>
       </c>
       <c r="C402" s="19" t="inlineStr">
@@ -15868,17 +15868,17 @@
       </c>
       <c r="D402" s="13" t="inlineStr">
         <is>
-          <t>Ketik nama resto di kolom cari pada form terbit</t>
+          <t>Terbitkan batch tanpa minimal belanja</t>
         </is>
       </c>
       <c r="E402" s="13" t="inlineStr">
         <is>
-          <t>Daftarnya menyusut sesuai kata kuncinya</t>
+          <t>Kalimat minimal belanja tidak muncul di pengumuman</t>
         </is>
       </c>
       <c r="F402" s="13" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-21</t>
         </is>
       </c>
       <c r="G402" s="13" t="inlineStr"/>
@@ -15893,27 +15893,27 @@
       </c>
       <c r="B403" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-53</t>
-        </is>
-      </c>
-      <c r="C403" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-51</t>
+        </is>
+      </c>
+      <c r="C403" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D403" s="16" t="inlineStr">
         <is>
-          <t>Centang 3 resto, lalu cari kata yang menyaringnya keluar</t>
+          <t>Buka Kotak Masuk sebagai pegawai resto</t>
         </is>
       </c>
       <c r="E403" s="16" t="inlineStr">
         <is>
-          <t>Ketiganya tetap terpilih; hitungannya tidak berubah</t>
+          <t>Kabar voucher tidak muncul — audiensnya pelanggan</t>
         </is>
       </c>
       <c r="F403" s="16" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-20</t>
         </is>
       </c>
       <c r="G403" s="16" t="inlineStr"/>
@@ -15928,22 +15928,22 @@
       </c>
       <c r="B404" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-54</t>
-        </is>
-      </c>
-      <c r="C404" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-52</t>
+        </is>
+      </c>
+      <c r="C404" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D404" s="13" t="inlineStr">
         <is>
-          <t>Saring daftarnya, lalu ketuk Pilih semua</t>
+          <t>Ketik nama resto di kolom cari pada form terbit</t>
         </is>
       </c>
       <c r="E404" s="13" t="inlineStr">
         <is>
-          <t>Hanya yang tampil tercentang, bukan seluruh resto</t>
+          <t>Daftarnya menyusut sesuai kata kuncinya</t>
         </is>
       </c>
       <c r="F404" s="13" t="inlineStr">
@@ -15963,22 +15963,22 @@
       </c>
       <c r="B405" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-55</t>
-        </is>
-      </c>
-      <c r="C405" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-53</t>
+        </is>
+      </c>
+      <c r="C405" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D405" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Lepas semua saat semua yang tampil tercentang</t>
+          <t>Centang 3 resto, lalu cari kata yang menyaringnya keluar</t>
         </is>
       </c>
       <c r="E405" s="16" t="inlineStr">
         <is>
-          <t>Yang tampil terlepas; pilihan di luar saringan tetap</t>
+          <t>Ketiganya tetap terpilih; hitungannya tidak berubah</t>
         </is>
       </c>
       <c r="F405" s="16" t="inlineStr">
@@ -15998,22 +15998,22 @@
       </c>
       <c r="B406" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-56</t>
-        </is>
-      </c>
-      <c r="C406" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-54</t>
+        </is>
+      </c>
+      <c r="C406" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D406" s="13" t="inlineStr">
         <is>
-          <t>Cari nama resto yang tidak ada</t>
+          <t>Saring daftarnya, lalu ketuk Pilih semua</t>
         </is>
       </c>
       <c r="E406" s="13" t="inlineStr">
         <is>
-          <t>Muncul "Tidak ada resto bernama itu"</t>
+          <t>Hanya yang tampil tercentang, bukan seluruh resto</t>
         </is>
       </c>
       <c r="F406" s="13" t="inlineStr">
@@ -16033,27 +16033,27 @@
       </c>
       <c r="B407" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-57</t>
-        </is>
-      </c>
-      <c r="C407" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-55</t>
+        </is>
+      </c>
+      <c r="C407" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D407" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch berbanner, lalu buka Kotak Masuk pelanggan</t>
+          <t>Ketuk Lepas semua saat semua yang tampil tercentang</t>
         </is>
       </c>
       <c r="E407" s="16" t="inlineStr">
         <is>
-          <t>Gambarnya tampil bersama kabarnya</t>
+          <t>Yang tampil terlepas; pilihan di luar saringan tetap</t>
         </is>
       </c>
       <c r="F407" s="16" t="inlineStr">
         <is>
-          <t>F-VC-23</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G407" s="16" t="inlineStr"/>
@@ -16068,7 +16068,7 @@
       </c>
       <c r="B408" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-58</t>
+          <t>TC-VC-56</t>
         </is>
       </c>
       <c r="C408" s="19" t="inlineStr">
@@ -16078,17 +16078,17 @@
       </c>
       <c r="D408" s="13" t="inlineStr">
         <is>
-          <t>Pilih gambar potret, lihat pratinjaunya</t>
+          <t>Cari nama resto yang tidak ada</t>
         </is>
       </c>
       <c r="E408" s="13" t="inlineStr">
         <is>
-          <t>Dipotong 16:9, sama dengan yang nanti muncul di kotak masuk</t>
+          <t>Muncul "Tidak ada resto bernama itu"</t>
         </is>
       </c>
       <c r="F408" s="13" t="inlineStr">
         <is>
-          <t>F-VC-23</t>
+          <t>F-VC-22</t>
         </is>
       </c>
       <c r="G408" s="13" t="inlineStr"/>
@@ -16103,22 +16103,22 @@
       </c>
       <c r="B409" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-59</t>
-        </is>
-      </c>
-      <c r="C409" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-57</t>
+        </is>
+      </c>
+      <c r="C409" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D409" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch tanpa banner</t>
+          <t>Terbitkan batch berbanner, lalu buka Kotak Masuk pelanggan</t>
         </is>
       </c>
       <c r="E409" s="16" t="inlineStr">
         <is>
-          <t>Kabarnya tetap terkirim, tanpa gambar</t>
+          <t>Gambarnya tampil bersama kabarnya</t>
         </is>
       </c>
       <c r="F409" s="16" t="inlineStr">
@@ -16138,27 +16138,27 @@
       </c>
       <c r="B410" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-60</t>
-        </is>
-      </c>
-      <c r="C410" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-58</t>
+        </is>
+      </c>
+      <c r="C410" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D410" s="13" t="inlineStr">
         <is>
-          <t>Cari tombol Hapus pada batch yang masih berjalan</t>
+          <t>Pilih gambar potret, lihat pratinjaunya</t>
         </is>
       </c>
       <c r="E410" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada — harus ditutup dulu</t>
+          <t>Dipotong 16:9, sama dengan yang nanti muncul di kotak masuk</t>
         </is>
       </c>
       <c r="F410" s="13" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-23</t>
         </is>
       </c>
       <c r="G410" s="13" t="inlineStr"/>
@@ -16173,27 +16173,27 @@
       </c>
       <c r="B411" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-61</t>
-        </is>
-      </c>
-      <c r="C411" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-59</t>
+        </is>
+      </c>
+      <c r="C411" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D411" s="16" t="inlineStr">
         <is>
-          <t>Tutup batch yang belum ada penebusnya, lalu hapus</t>
+          <t>Terbitkan batch tanpa banner</t>
         </is>
       </c>
       <c r="E411" s="16" t="inlineStr">
         <is>
-          <t>Terhapus; dananya kembali ke GL Total Saldo</t>
+          <t>Kabarnya tetap terkirim, tanpa gambar</t>
         </is>
       </c>
       <c r="F411" s="16" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-23</t>
         </is>
       </c>
       <c r="G411" s="16" t="inlineStr"/>
@@ -16208,7 +16208,7 @@
       </c>
       <c r="B412" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-62</t>
+          <t>TC-VC-60</t>
         </is>
       </c>
       <c r="C412" s="15" t="inlineStr">
@@ -16218,12 +16218,12 @@
       </c>
       <c r="D412" s="13" t="inlineStr">
         <is>
-          <t>Periksa Kotak Masuk pelanggan sesudah batch dihapus</t>
+          <t>Cari tombol Hapus pada batch yang masih berjalan</t>
         </is>
       </c>
       <c r="E412" s="13" t="inlineStr">
         <is>
-          <t>Kabar vouchernya ikut hilang</t>
+          <t>Tidak ada — harus ditutup dulu</t>
         </is>
       </c>
       <c r="F412" s="13" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="B413" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-63</t>
+          <t>TC-VC-61</t>
         </is>
       </c>
       <c r="C413" s="18" t="inlineStr">
@@ -16253,12 +16253,12 @@
       </c>
       <c r="D413" s="16" t="inlineStr">
         <is>
-          <t>Panggil delete_voucher_batch untuk batch yang sudah ada penebusnya</t>
+          <t>Tutup batch yang belum ada penebusnya, lalu hapus</t>
         </is>
       </c>
       <c r="E413" s="16" t="inlineStr">
         <is>
-          <t>Ditolak, dengan jumlah penebusnya disebut</t>
+          <t>Terhapus; dananya kembali ke GL Total Saldo</t>
         </is>
       </c>
       <c r="F413" s="16" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="B414" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-64</t>
+          <t>TC-VC-62</t>
         </is>
       </c>
       <c r="C414" s="15" t="inlineStr">
@@ -16288,12 +16288,12 @@
       </c>
       <c r="D414" s="13" t="inlineStr">
         <is>
-          <t>Panggil delete_voucher_batch sebagai bukan Super Admin</t>
+          <t>Periksa Kotak Masuk pelanggan sesudah batch dihapus</t>
         </is>
       </c>
       <c r="E414" s="13" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Kabar vouchernya ikut hilang</t>
         </is>
       </c>
       <c r="F414" s="13" t="inlineStr">
@@ -16313,22 +16313,22 @@
       </c>
       <c r="B415" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-65</t>
-        </is>
-      </c>
-      <c r="C415" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-63</t>
+        </is>
+      </c>
+      <c r="C415" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D415" s="16" t="inlineStr">
         <is>
-          <t>Hapus batch yang sudah pernah disettle penjadwal</t>
+          <t>Panggil delete_voucher_batch untuk batch yang sudah ada penebusnya</t>
         </is>
       </c>
       <c r="E415" s="16" t="inlineStr">
         <is>
-          <t>Dananya tidak dikembalikan dua kali</t>
+          <t>Ditolak, dengan jumlah penebusnya disebut</t>
         </is>
       </c>
       <c r="F415" s="16" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="B416" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-66</t>
+          <t>TC-VC-64</t>
         </is>
       </c>
       <c r="C416" s="15" t="inlineStr">
@@ -16358,17 +16358,17 @@
       </c>
       <c r="D416" s="13" t="inlineStr">
         <is>
-          <t>Ketuk Penebus pada sebuah batch</t>
+          <t>Panggil delete_voucher_batch sebagai bukan Super Admin</t>
         </is>
       </c>
       <c r="E416" s="13" t="inlineStr">
         <is>
-          <t>Daftar email penebut berikut tanggal tebus dan statusnya</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F416" s="13" t="inlineStr">
         <is>
-          <t>F-VC-25</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G416" s="13" t="inlineStr"/>
@@ -16383,27 +16383,27 @@
       </c>
       <c r="B417" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-67</t>
-        </is>
-      </c>
-      <c r="C417" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-65</t>
+        </is>
+      </c>
+      <c r="C417" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D417" s="16" t="inlineStr">
         <is>
-          <t>Periksa ringkasan di atas daftar penebus</t>
+          <t>Hapus batch yang sudah pernah disettle penjadwal</t>
         </is>
       </c>
       <c r="E417" s="16" t="inlineStr">
         <is>
-          <t>Dipakai / Menggantung / Hangus berjumlah sama dengan barisnya</t>
+          <t>Dananya tidak dikembalikan dua kali</t>
         </is>
       </c>
       <c r="F417" s="16" t="inlineStr">
         <is>
-          <t>F-VC-25</t>
+          <t>F-VC-24</t>
         </is>
       </c>
       <c r="G417" s="16" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="B418" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-68</t>
+          <t>TC-VC-66</t>
         </is>
       </c>
       <c r="C418" s="15" t="inlineStr">
@@ -16428,12 +16428,12 @@
       </c>
       <c r="D418" s="13" t="inlineStr">
         <is>
-          <t>Lewati tanggal kedaluwarsa sebelum penjadwal berjalan</t>
+          <t>Ketuk Penebus pada sebuah batch</t>
         </is>
       </c>
       <c r="E418" s="13" t="inlineStr">
         <is>
-          <t>Statusnya sudah Hangus, bukan Belum Dipakai</t>
+          <t>Daftar email penebut berikut tanggal tebus dan statusnya</t>
         </is>
       </c>
       <c r="F418" s="13" t="inlineStr">
@@ -16448,12 +16448,12 @@
     <row r="419">
       <c r="A419" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B419" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-01</t>
+          <t>TC-VC-67</t>
         </is>
       </c>
       <c r="C419" s="18" t="inlineStr">
@@ -16463,17 +16463,17 @@
       </c>
       <c r="D419" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Analisa Pasar</t>
+          <t>Periksa ringkasan di atas daftar penebus</t>
         </is>
       </c>
       <c r="E419" s="16" t="inlineStr">
         <is>
-          <t>Empat bagian termuat tanpa galat</t>
+          <t>Dipakai / Menggantung / Hangus berjumlah sama dengan barisnya</t>
         </is>
       </c>
       <c r="F419" s="16" t="inlineStr">
         <is>
-          <t>F-MR-01…04</t>
+          <t>F-VC-25</t>
         </is>
       </c>
       <c r="G419" s="16" t="inlineStr"/>
@@ -16483,12 +16483,12 @@
     <row r="420">
       <c r="A420" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B420" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-02</t>
+          <t>TC-VC-68</t>
         </is>
       </c>
       <c r="C420" s="15" t="inlineStr">
@@ -16498,17 +16498,17 @@
       </c>
       <c r="D420" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan Top 5 Pelanggan dengan jumlah manual dari orders</t>
+          <t>Lewati tanggal kedaluwarsa sebelum penjadwal berjalan</t>
         </is>
       </c>
       <c r="E420" s="13" t="inlineStr">
         <is>
-          <t>Cocok nominal dan jumlah pesanannya</t>
+          <t>Statusnya sudah Hangus, bukan Belum Dipakai</t>
         </is>
       </c>
       <c r="F420" s="13" t="inlineStr">
         <is>
-          <t>F-MR-01</t>
+          <t>F-VC-25</t>
         </is>
       </c>
       <c r="G420" s="13" t="inlineStr"/>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="B421" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-03</t>
+          <t>TC-MR-01</t>
         </is>
       </c>
       <c r="C421" s="18" t="inlineStr">
@@ -16533,17 +16533,17 @@
       </c>
       <c r="D421" s="16" t="inlineStr">
         <is>
-          <t>Batalkan sebuah pesanan besar, muat ulang</t>
+          <t>Super Admin → Analisa Pasar</t>
         </is>
       </c>
       <c r="E421" s="16" t="inlineStr">
         <is>
-          <t>Nominalnya berkurang — yang batal tidak dihitung</t>
+          <t>Empat bagian termuat tanpa galat</t>
         </is>
       </c>
       <c r="F421" s="16" t="inlineStr">
         <is>
-          <t>F-MR-05</t>
+          <t>F-MR-01…04</t>
         </is>
       </c>
       <c r="G421" s="16" t="inlineStr"/>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="B422" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-04</t>
+          <t>TC-MR-02</t>
         </is>
       </c>
       <c r="C422" s="15" t="inlineStr">
@@ -16568,17 +16568,17 @@
       </c>
       <c r="D422" s="13" t="inlineStr">
         <is>
-          <t>Buat akun pelanggan baru tanpa memesan</t>
+          <t>Bandingkan Top 5 Pelanggan dengan jumlah manual dari orders</t>
         </is>
       </c>
       <c r="E422" s="13" t="inlineStr">
         <is>
-          <t>Muncul di daftar Belum Pernah Memesan</t>
+          <t>Cocok nominal dan jumlah pesanannya</t>
         </is>
       </c>
       <c r="F422" s="13" t="inlineStr">
         <is>
-          <t>F-MR-02</t>
+          <t>F-MR-01</t>
         </is>
       </c>
       <c r="G422" s="13" t="inlineStr"/>
@@ -16593,7 +16593,7 @@
       </c>
       <c r="B423" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-05</t>
+          <t>TC-MR-03</t>
         </is>
       </c>
       <c r="C423" s="18" t="inlineStr">
@@ -16603,17 +16603,17 @@
       </c>
       <c r="D423" s="16" t="inlineStr">
         <is>
-          <t>Pelanggan itu menyelesaikan satu pesanan, muat ulang</t>
+          <t>Batalkan sebuah pesanan besar, muat ulang</t>
         </is>
       </c>
       <c r="E423" s="16" t="inlineStr">
         <is>
-          <t>Hilang dari daftar tersebut</t>
+          <t>Nominalnya berkurang — yang batal tidak dihitung</t>
         </is>
       </c>
       <c r="F423" s="16" t="inlineStr">
         <is>
-          <t>F-MR-02</t>
+          <t>F-MR-05</t>
         </is>
       </c>
       <c r="G423" s="16" t="inlineStr"/>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="B424" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-06</t>
+          <t>TC-MR-04</t>
         </is>
       </c>
       <c r="C424" s="15" t="inlineStr">
@@ -16638,17 +16638,17 @@
       </c>
       <c r="D424" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan Top 5 Resto dengan Jurnal GL resto bersangkutan</t>
+          <t>Buat akun pelanggan baru tanpa memesan</t>
         </is>
       </c>
       <c r="E424" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sejalan</t>
+          <t>Muncul di daftar Belum Pernah Memesan</t>
         </is>
       </c>
       <c r="F424" s="13" t="inlineStr">
         <is>
-          <t>F-MR-03</t>
+          <t>F-MR-02</t>
         </is>
       </c>
       <c r="G424" s="13" t="inlineStr"/>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="B425" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-07</t>
+          <t>TC-MR-05</t>
         </is>
       </c>
       <c r="C425" s="18" t="inlineStr">
@@ -16673,17 +16673,17 @@
       </c>
       <c r="D425" s="16" t="inlineStr">
         <is>
-          <t>Resto yang seluruh pesanannya batal</t>
+          <t>Pelanggan itu menyelesaikan satu pesanan, muat ulang</t>
         </is>
       </c>
       <c r="E425" s="16" t="inlineStr">
         <is>
-          <t>Muncul di Belum Ada Penghasilan, jumlah pesanan 0</t>
+          <t>Hilang dari daftar tersebut</t>
         </is>
       </c>
       <c r="F425" s="16" t="inlineStr">
         <is>
-          <t>F-MR-04</t>
+          <t>F-MR-02</t>
         </is>
       </c>
       <c r="G425" s="16" t="inlineStr"/>
@@ -16698,27 +16698,27 @@
       </c>
       <c r="B426" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-08</t>
-        </is>
-      </c>
-      <c r="C426" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-06</t>
+        </is>
+      </c>
+      <c r="C426" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D426" s="13" t="inlineStr">
         <is>
-          <t>Resto baru tanpa pesanan sama sekali</t>
+          <t>Bandingkan Top 5 Resto dengan Jurnal GL resto bersangkutan</t>
         </is>
       </c>
       <c r="E426" s="13" t="inlineStr">
         <is>
-          <t>Muncul dengan "Belum ada pesanan"</t>
+          <t>Nominalnya sejalan</t>
         </is>
       </c>
       <c r="F426" s="13" t="inlineStr">
         <is>
-          <t>F-MR-04</t>
+          <t>F-MR-03</t>
         </is>
       </c>
       <c r="G426" s="13" t="inlineStr"/>
@@ -16733,7 +16733,7 @@
       </c>
       <c r="B427" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-09</t>
+          <t>TC-MR-07</t>
         </is>
       </c>
       <c r="C427" s="18" t="inlineStr">
@@ -16743,17 +16743,17 @@
       </c>
       <c r="D427" s="16" t="inlineStr">
         <is>
-          <t>Periksa apakah resto KaataGo ikut terhitung</t>
+          <t>Resto yang seluruh pesanannya batal</t>
         </is>
       </c>
       <c r="E427" s="16" t="inlineStr">
         <is>
-          <t>Tidak — resto platform dikecualikan</t>
+          <t>Muncul di Belum Ada Penghasilan, jumlah pesanan 0</t>
         </is>
       </c>
       <c r="F427" s="16" t="inlineStr">
         <is>
-          <t>F-MR-06</t>
+          <t>F-MR-04</t>
         </is>
       </c>
       <c r="G427" s="16" t="inlineStr"/>
@@ -16768,27 +16768,27 @@
       </c>
       <c r="B428" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-10</t>
-        </is>
-      </c>
-      <c r="C428" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-MR-08</t>
+        </is>
+      </c>
+      <c r="C428" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D428" s="13" t="inlineStr">
         <is>
-          <t>Hapus lunak sebuah resto, muat ulang</t>
+          <t>Resto baru tanpa pesanan sama sekali</t>
         </is>
       </c>
       <c r="E428" s="13" t="inlineStr">
         <is>
-          <t>Hilang dari keempat daftar</t>
+          <t>Muncul dengan "Belum ada pesanan"</t>
         </is>
       </c>
       <c r="F428" s="13" t="inlineStr">
         <is>
-          <t>F-MR-06</t>
+          <t>F-MR-04</t>
         </is>
       </c>
       <c r="G428" s="13" t="inlineStr"/>
@@ -16803,7 +16803,7 @@
       </c>
       <c r="B429" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-11</t>
+          <t>TC-MR-09</t>
         </is>
       </c>
       <c r="C429" s="18" t="inlineStr">
@@ -16813,17 +16813,17 @@
       </c>
       <c r="D429" s="16" t="inlineStr">
         <is>
-          <t>Panggil report_top_customers sebagai Owner resto</t>
+          <t>Periksa apakah resto KaataGo ikut terhitung</t>
         </is>
       </c>
       <c r="E429" s="16" t="inlineStr">
         <is>
-          <t>Daftar kosong, bukan pesan galat</t>
+          <t>Tidak — resto platform dikecualikan</t>
         </is>
       </c>
       <c r="F429" s="16" t="inlineStr">
         <is>
-          <t>F-MR-07</t>
+          <t>F-MR-06</t>
         </is>
       </c>
       <c r="G429" s="16" t="inlineStr"/>
@@ -16838,27 +16838,27 @@
       </c>
       <c r="B430" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-12</t>
-        </is>
-      </c>
-      <c r="C430" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-10</t>
+        </is>
+      </c>
+      <c r="C430" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D430" s="13" t="inlineStr">
         <is>
-          <t>Panggil salah satu RPC dengan p_limit 99999</t>
+          <t>Hapus lunak sebuah resto, muat ulang</t>
         </is>
       </c>
       <c r="E430" s="13" t="inlineStr">
         <is>
-          <t>Dijepit ke batas atasnya</t>
+          <t>Hilang dari keempat daftar</t>
         </is>
       </c>
       <c r="F430" s="13" t="inlineStr">
         <is>
-          <t>F-MR-07</t>
+          <t>F-MR-06</t>
         </is>
       </c>
       <c r="G430" s="13" t="inlineStr"/>
@@ -16873,27 +16873,27 @@
       </c>
       <c r="B431" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-13</t>
-        </is>
-      </c>
-      <c r="C431" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-11</t>
+        </is>
+      </c>
+      <c r="C431" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D431" s="16" t="inlineStr">
         <is>
-          <t>Pesanan kasir atas nama tamu</t>
+          <t>Panggil report_top_customers sebagai Owner resto</t>
         </is>
       </c>
       <c r="E431" s="16" t="inlineStr">
         <is>
-          <t>Tidak ikut peringkat pelanggan — bukan akun terdaftar</t>
+          <t>Daftar kosong, bukan pesan galat</t>
         </is>
       </c>
       <c r="F431" s="16" t="inlineStr">
         <is>
-          <t>F-MR-01</t>
+          <t>F-MR-07</t>
         </is>
       </c>
       <c r="G431" s="16" t="inlineStr"/>
@@ -16903,32 +16903,32 @@
     <row r="432">
       <c r="A432" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B432" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
-        </is>
-      </c>
-      <c r="C432" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-MR-12</t>
+        </is>
+      </c>
+      <c r="C432" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D432" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Panggil salah satu RPC dengan p_limit 99999</t>
         </is>
       </c>
       <c r="E432" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Dijepit ke batas atasnya</t>
         </is>
       </c>
       <c r="F432" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-MR-07</t>
         </is>
       </c>
       <c r="G432" s="13" t="inlineStr"/>
@@ -16938,32 +16938,32 @@
     <row r="433">
       <c r="A433" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B433" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
-        </is>
-      </c>
-      <c r="C433" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-MR-13</t>
+        </is>
+      </c>
+      <c r="C433" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D433" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Pesanan kasir atas nama tamu</t>
         </is>
       </c>
       <c r="E433" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Tidak ikut peringkat pelanggan — bukan akun terdaftar</t>
         </is>
       </c>
       <c r="F433" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-MR-01</t>
         </is>
       </c>
       <c r="G433" s="16" t="inlineStr"/>
@@ -16978,7 +16978,7 @@
       </c>
       <c r="B434" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-TS-01</t>
         </is>
       </c>
       <c r="C434" s="15" t="inlineStr">
@@ -16988,12 +16988,12 @@
       </c>
       <c r="D434" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E434" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F434" s="13" t="inlineStr">
@@ -17013,7 +17013,7 @@
       </c>
       <c r="B435" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
+          <t>TC-TS-02</t>
         </is>
       </c>
       <c r="C435" s="18" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="D435" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E435" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F435" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G435" s="16" t="inlineStr"/>
@@ -17048,7 +17048,7 @@
       </c>
       <c r="B436" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-TS-03</t>
         </is>
       </c>
       <c r="C436" s="15" t="inlineStr">
@@ -17058,17 +17058,17 @@
       </c>
       <c r="D436" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E436" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F436" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G436" s="13" t="inlineStr"/>
@@ -17083,7 +17083,7 @@
       </c>
       <c r="B437" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-TS-04</t>
         </is>
       </c>
       <c r="C437" s="18" t="inlineStr">
@@ -17093,17 +17093,17 @@
       </c>
       <c r="D437" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E437" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F437" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G437" s="16" t="inlineStr"/>
@@ -17118,7 +17118,7 @@
       </c>
       <c r="B438" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-TS-05</t>
         </is>
       </c>
       <c r="C438" s="15" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="D438" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E438" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F438" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G438" s="13" t="inlineStr"/>
@@ -17153,7 +17153,7 @@
       </c>
       <c r="B439" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C439" s="18" t="inlineStr">
@@ -17163,17 +17163,17 @@
       </c>
       <c r="D439" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E439" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F439" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G439" s="16" t="inlineStr"/>
@@ -17188,7 +17188,7 @@
       </c>
       <c r="B440" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
+          <t>TC-TS-07</t>
         </is>
       </c>
       <c r="C440" s="15" t="inlineStr">
@@ -17198,17 +17198,17 @@
       </c>
       <c r="D440" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E440" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F440" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G440" s="13" t="inlineStr"/>
@@ -17223,7 +17223,7 @@
       </c>
       <c r="B441" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-TS-08</t>
         </is>
       </c>
       <c r="C441" s="18" t="inlineStr">
@@ -17233,17 +17233,17 @@
       </c>
       <c r="D441" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E441" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F441" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G441" s="16" t="inlineStr"/>
@@ -17258,27 +17258,27 @@
       </c>
       <c r="B442" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
-        </is>
-      </c>
-      <c r="C442" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C442" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D442" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E442" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F442" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G442" s="13" t="inlineStr"/>
@@ -17293,27 +17293,27 @@
       </c>
       <c r="B443" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C443" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C443" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D443" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E443" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F443" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G443" s="16" t="inlineStr"/>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B444" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
+          <t>TC-TS-11</t>
         </is>
       </c>
       <c r="C444" s="19" t="inlineStr">
@@ -17338,17 +17338,17 @@
       </c>
       <c r="D444" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E444" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F444" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G444" s="13" t="inlineStr"/>
@@ -17363,27 +17363,27 @@
       </c>
       <c r="B445" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
-        </is>
-      </c>
-      <c r="C445" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C445" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D445" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E445" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F445" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G445" s="16" t="inlineStr"/>
@@ -17398,27 +17398,27 @@
       </c>
       <c r="B446" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
-        </is>
-      </c>
-      <c r="C446" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-13</t>
+        </is>
+      </c>
+      <c r="C446" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D446" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E446" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F446" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G446" s="13" t="inlineStr"/>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="B447" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-TS-14</t>
         </is>
       </c>
       <c r="C447" s="18" t="inlineStr">
@@ -17443,17 +17443,17 @@
       </c>
       <c r="D447" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E447" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F447" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G447" s="16" t="inlineStr"/>
@@ -17468,27 +17468,27 @@
       </c>
       <c r="B448" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C448" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-15</t>
+        </is>
+      </c>
+      <c r="C448" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D448" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E448" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F448" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G448" s="13" t="inlineStr"/>
@@ -17503,27 +17503,27 @@
       </c>
       <c r="B449" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C449" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-16</t>
+        </is>
+      </c>
+      <c r="C449" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D449" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
         </is>
       </c>
       <c r="E449" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F449" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>F-PG-02, TSD §7.1</t>
         </is>
       </c>
       <c r="G449" s="16" t="inlineStr"/>
@@ -17538,7 +17538,7 @@
       </c>
       <c r="B450" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
+          <t>TC-TS-17</t>
         </is>
       </c>
       <c r="C450" s="19" t="inlineStr">
@@ -17548,17 +17548,17 @@
       </c>
       <c r="D450" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
         </is>
       </c>
       <c r="E450" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
         </is>
       </c>
       <c r="F450" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §1.2</t>
         </is>
       </c>
       <c r="G450" s="13" t="inlineStr"/>
@@ -17568,32 +17568,32 @@
     <row r="451">
       <c r="A451" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B451" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
-        </is>
-      </c>
-      <c r="C451" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-18</t>
+        </is>
+      </c>
+      <c r="C451" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D451" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
         </is>
       </c>
       <c r="E451" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
         </is>
       </c>
       <c r="F451" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>TSD §6.5</t>
         </is>
       </c>
       <c r="G451" s="16" t="inlineStr"/>
@@ -17603,32 +17603,32 @@
     <row r="452">
       <c r="A452" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B452" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
-        </is>
-      </c>
-      <c r="C452" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-19</t>
+        </is>
+      </c>
+      <c r="C452" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D452" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Hapus resto uji</t>
         </is>
       </c>
       <c r="E452" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
         </is>
       </c>
       <c r="F452" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §4.0</t>
         </is>
       </c>
       <c r="G452" s="13" t="inlineStr"/>
@@ -17643,7 +17643,7 @@
       </c>
       <c r="B453" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
+          <t>TC-RG-01</t>
         </is>
       </c>
       <c r="C453" s="18" t="inlineStr">
@@ -17653,17 +17653,17 @@
       </c>
       <c r="D453" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
         </is>
       </c>
       <c r="E453" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
         </is>
       </c>
       <c r="F453" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>F-KS-09</t>
         </is>
       </c>
       <c r="G453" s="16" t="inlineStr"/>
@@ -17678,7 +17678,7 @@
       </c>
       <c r="B454" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
+          <t>TC-RG-02</t>
         </is>
       </c>
       <c r="C454" s="15" t="inlineStr">
@@ -17688,17 +17688,17 @@
       </c>
       <c r="D454" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
         </is>
       </c>
       <c r="E454" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
         </is>
       </c>
       <c r="F454" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>F-PP-09, A-13</t>
         </is>
       </c>
       <c r="G454" s="13" t="inlineStr"/>
@@ -17713,7 +17713,7 @@
       </c>
       <c r="B455" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-RG-03</t>
         </is>
       </c>
       <c r="C455" s="18" t="inlineStr">
@@ -17723,17 +17723,17 @@
       </c>
       <c r="D455" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
         </is>
       </c>
       <c r="E455" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Tidak muncul sama sekali</t>
         </is>
       </c>
       <c r="F455" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="G455" s="16" t="inlineStr"/>
@@ -17748,7 +17748,7 @@
       </c>
       <c r="B456" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-RG-04</t>
         </is>
       </c>
       <c r="C456" s="15" t="inlineStr">
@@ -17758,17 +17758,17 @@
       </c>
       <c r="D456" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
         </is>
       </c>
       <c r="E456" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Nominalnya sama dengan yang diajukan</t>
         </is>
       </c>
       <c r="F456" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>F-FN-03</t>
         </is>
       </c>
       <c r="G456" s="13" t="inlineStr"/>
@@ -17783,27 +17783,27 @@
       </c>
       <c r="B457" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
-        </is>
-      </c>
-      <c r="C457" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C457" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D457" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
         </is>
       </c>
       <c r="E457" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
         </is>
       </c>
       <c r="F457" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="G457" s="16" t="inlineStr"/>
@@ -17818,27 +17818,27 @@
       </c>
       <c r="B458" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
-        </is>
-      </c>
-      <c r="C458" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C458" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D458" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
         </is>
       </c>
       <c r="E458" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
         </is>
       </c>
       <c r="F458" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>F-DS-10, F-DS-12</t>
         </is>
       </c>
       <c r="G458" s="13" t="inlineStr"/>
@@ -17853,7 +17853,7 @@
       </c>
       <c r="B459" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
+          <t>TC-RG-07</t>
         </is>
       </c>
       <c r="C459" s="20" t="inlineStr">
@@ -17863,17 +17863,17 @@
       </c>
       <c r="D459" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
         </is>
       </c>
       <c r="E459" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
         </is>
       </c>
       <c r="F459" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>F-IN-15</t>
         </is>
       </c>
       <c r="G459" s="16" t="inlineStr"/>
@@ -17888,7 +17888,7 @@
       </c>
       <c r="B460" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
+          <t>TC-RG-08</t>
         </is>
       </c>
       <c r="C460" s="19" t="inlineStr">
@@ -17898,17 +17898,17 @@
       </c>
       <c r="D460" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
         </is>
       </c>
       <c r="E460" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Daftar menu termuat</t>
         </is>
       </c>
       <c r="F460" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-DS-01</t>
         </is>
       </c>
       <c r="G460" s="13" t="inlineStr"/>
@@ -17923,7 +17923,7 @@
       </c>
       <c r="B461" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
+          <t>TC-RG-09</t>
         </is>
       </c>
       <c r="C461" s="20" t="inlineStr">
@@ -17933,17 +17933,17 @@
       </c>
       <c r="D461" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
         </is>
       </c>
       <c r="E461" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Detail jurnal terbuka</t>
         </is>
       </c>
       <c r="F461" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>F-KS-13</t>
         </is>
       </c>
       <c r="G461" s="16" t="inlineStr"/>
@@ -17958,7 +17958,7 @@
       </c>
       <c r="B462" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
+          <t>TC-RG-10</t>
         </is>
       </c>
       <c r="C462" s="19" t="inlineStr">
@@ -17968,17 +17968,17 @@
       </c>
       <c r="D462" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
         </is>
       </c>
       <c r="E462" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Seluruh layar berganti bersih</t>
         </is>
       </c>
       <c r="F462" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>A-18</t>
         </is>
       </c>
       <c r="G462" s="13" t="inlineStr"/>
@@ -17993,27 +17993,27 @@
       </c>
       <c r="B463" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
-        </is>
-      </c>
-      <c r="C463" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C463" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D463" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
         </is>
       </c>
       <c r="E463" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Ikut tergulir bersama menunya</t>
         </is>
       </c>
       <c r="F463" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-CU-16, A-12</t>
         </is>
       </c>
       <c r="G463" s="16" t="inlineStr"/>
@@ -18028,7 +18028,7 @@
       </c>
       <c r="B464" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
+          <t>TC-RG-12</t>
         </is>
       </c>
       <c r="C464" s="19" t="inlineStr">
@@ -18038,17 +18038,17 @@
       </c>
       <c r="D464" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
         </is>
       </c>
       <c r="E464" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Owner bisa mengubahnya</t>
         </is>
       </c>
       <c r="F464" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>F-SD-02</t>
         </is>
       </c>
       <c r="G464" s="13" t="inlineStr"/>
@@ -18058,25 +18058,95 @@
     <row r="465">
       <c r="A465" s="16" t="inlineStr">
         <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B465" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C465" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D465" s="16" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E465" s="16" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F465" s="16" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G465" s="16" t="inlineStr"/>
+      <c r="H465" s="16" t="inlineStr"/>
+      <c r="I465" s="16" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B466" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C466" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D466" s="13" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E466" s="13" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F466" s="13" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G466" s="13" t="inlineStr"/>
+      <c r="H466" s="13" t="inlineStr"/>
+      <c r="I466" s="13" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="16" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B465" s="17" t="inlineStr">
+      <c r="B467" s="17" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C465" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D465" s="16" t="inlineStr">
+      <c r="C467" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D467" s="16" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E465" s="16" t="inlineStr">
+      <c r="E467" s="16" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -18090,37 +18160,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F465" s="16" t="inlineStr">
+      <c r="F467" s="16" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G465" s="16" t="inlineStr"/>
-      <c r="H465" s="16" t="inlineStr"/>
-      <c r="I465" s="16" t="inlineStr"/>
-    </row>
-    <row r="466">
-      <c r="A466" s="13" t="inlineStr">
+      <c r="G467" s="16" t="inlineStr"/>
+      <c r="H467" s="16" t="inlineStr"/>
+      <c r="I467" s="16" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B466" s="14" t="inlineStr">
+      <c r="B468" s="14" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C466" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D466" s="13" t="inlineStr">
+      <c r="C468" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D468" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E466" s="13" t="inlineStr">
+      <c r="E468" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -18132,37 +18202,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F466" s="13" t="inlineStr">
+      <c r="F468" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G466" s="13" t="inlineStr"/>
-      <c r="H466" s="13" t="inlineStr"/>
-      <c r="I466" s="13" t="inlineStr"/>
-    </row>
-    <row r="467">
-      <c r="A467" s="16" t="inlineStr">
+      <c r="G468" s="13" t="inlineStr"/>
+      <c r="H468" s="13" t="inlineStr"/>
+      <c r="I468" s="13" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B467" s="17" t="inlineStr">
+      <c r="B469" s="17" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C467" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D467" s="16" t="inlineStr">
+      <c r="C469" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D469" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E467" s="16" t="inlineStr">
+      <c r="E469" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -18174,74 +18244,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F467" s="16" t="inlineStr">
+      <c r="F469" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G467" s="16" t="inlineStr"/>
-      <c r="H467" s="16" t="inlineStr"/>
-      <c r="I467" s="16" t="inlineStr"/>
-    </row>
-    <row r="468">
-      <c r="A468" s="13" t="inlineStr">
+      <c r="G469" s="16" t="inlineStr"/>
+      <c r="H469" s="16" t="inlineStr"/>
+      <c r="I469" s="16" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B468" s="14" t="inlineStr">
+      <c r="B470" s="14" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C468" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D468" s="13" t="inlineStr">
+      <c r="C470" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D470" s="13" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E468" s="13" t="inlineStr">
+      <c r="E470" s="13" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F468" s="13" t="inlineStr">
+      <c r="F470" s="13" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G468" s="13" t="inlineStr"/>
-      <c r="H468" s="13" t="inlineStr"/>
-      <c r="I468" s="13" t="inlineStr"/>
-    </row>
-    <row r="469">
-      <c r="A469" s="16" t="inlineStr">
+      <c r="G470" s="13" t="inlineStr"/>
+      <c r="H470" s="13" t="inlineStr"/>
+      <c r="I470" s="13" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B469" s="17" t="inlineStr">
+      <c r="B471" s="17" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C469" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D469" s="16" t="inlineStr">
+      <c r="C471" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D471" s="16" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E469" s="16" t="inlineStr">
+      <c r="E471" s="16" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -18252,73 +18322,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F469" s="16" t="inlineStr">
+      <c r="F471" s="16" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G469" s="16" t="inlineStr"/>
-      <c r="H469" s="16" t="inlineStr"/>
-      <c r="I469" s="16" t="inlineStr"/>
-    </row>
-    <row r="470">
-      <c r="A470" s="13" t="inlineStr">
+      <c r="G471" s="16" t="inlineStr"/>
+      <c r="H471" s="16" t="inlineStr"/>
+      <c r="I471" s="16" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B470" s="14" t="inlineStr">
+      <c r="B472" s="14" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C470" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D470" s="13" t="inlineStr">
+      <c r="C472" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D472" s="13" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E470" s="13" t="inlineStr">
+      <c r="E472" s="13" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F470" s="13" t="inlineStr">
+      <c r="F472" s="13" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G470" s="13" t="inlineStr"/>
-      <c r="H470" s="13" t="inlineStr"/>
-      <c r="I470" s="13" t="inlineStr"/>
-    </row>
-    <row r="471">
-      <c r="A471" s="16" t="inlineStr">
+      <c r="G472" s="13" t="inlineStr"/>
+      <c r="H472" s="13" t="inlineStr"/>
+      <c r="I472" s="13" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B471" s="17" t="inlineStr">
+      <c r="B473" s="17" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C471" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D471" s="16" t="inlineStr">
+      <c r="C473" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D473" s="16" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E471" s="16" t="inlineStr">
+      <c r="E473" s="16" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -18329,37 +18399,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F471" s="16" t="inlineStr">
+      <c r="F473" s="16" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G471" s="16" t="inlineStr"/>
-      <c r="H471" s="16" t="inlineStr"/>
-      <c r="I471" s="16" t="inlineStr"/>
-    </row>
-    <row r="472">
-      <c r="A472" s="13" t="inlineStr">
+      <c r="G473" s="16" t="inlineStr"/>
+      <c r="H473" s="16" t="inlineStr"/>
+      <c r="I473" s="16" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B472" s="14" t="inlineStr">
+      <c r="B474" s="14" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C472" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D472" s="13" t="inlineStr">
+      <c r="C474" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D474" s="13" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E472" s="13" t="inlineStr">
+      <c r="E474" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -18369,37 +18439,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F472" s="13" t="inlineStr">
+      <c r="F474" s="13" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G472" s="13" t="inlineStr"/>
-      <c r="H472" s="13" t="inlineStr"/>
-      <c r="I472" s="13" t="inlineStr"/>
-    </row>
-    <row r="473">
-      <c r="A473" s="16" t="inlineStr">
+      <c r="G474" s="13" t="inlineStr"/>
+      <c r="H474" s="13" t="inlineStr"/>
+      <c r="I474" s="13" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B473" s="17" t="inlineStr">
+      <c r="B475" s="17" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C473" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D473" s="16" t="inlineStr">
+      <c r="C475" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D475" s="16" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E473" s="16" t="inlineStr">
+      <c r="E475" s="16" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -18407,19 +18477,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F473" s="16" t="inlineStr">
+      <c r="F475" s="16" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G473" s="16" t="inlineStr"/>
-      <c r="H473" s="16" t="inlineStr"/>
-      <c r="I473" s="16" t="inlineStr"/>
+      <c r="G475" s="16" t="inlineStr"/>
+      <c r="H475" s="16" t="inlineStr"/>
+      <c r="I475" s="16" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I473"/>
+  <autoFilter ref="A1:I475"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G473" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G475" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$475</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$484</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C475,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C484,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P1",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P1",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P1",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P1",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P1",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P1",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P1",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P1",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C475,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C484,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P2",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P2",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P2",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P2",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P2",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P2",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P2",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P2",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C475,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C484,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P3",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P3",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P3",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P3",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P3",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P3",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C475,"P3",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C484,"P3",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pelanggan",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pelanggan",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pelanggan",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pelanggan",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pelanggan",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pelanggan",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pelanggan",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pelanggan",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kasir",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kasir",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kasir",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kasir",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kasir",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kasir",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kasir",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kasir",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pending Payment",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pending Payment",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pending Payment",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pending Payment",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pending Payment",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pending Payment",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pending Payment",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pending Payment",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Dapur",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Dapur",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Dapur",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Dapur",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Dapur",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Dapur",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Dapur",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Dapur",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Keuangan",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Keuangan",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Keuangan",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Keuangan",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Keuangan",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Keuangan",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Keuangan",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Keuangan",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Setor Saldo Cash",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Setor Saldo Cash",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Setor Saldo Cash",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Setor Saldo Cash",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Setor Saldo Cash",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Setor Saldo Cash",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Setor Saldo Cash",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Setor Saldo Cash",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"QR Meja",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"QR Meja",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"QR Meja",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"QR Meja",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"QR Meja",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"QR Meja",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"QR Meja",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"QR Meja",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Diskon",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Diskon",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Diskon",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Diskon",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Diskon",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Diskon",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Diskon",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Diskon",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembayaran QRIS",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembayaran QRIS",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembayaran QRIS",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembayaran QRIS",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembayaran QRIS",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembayaran QRIS",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembayaran QRIS",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembayaran QRIS",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Tampilan",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Tampilan",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Tampilan",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Tampilan",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Tampilan",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Tampilan",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Tampilan",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Tampilan",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Super Admin",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Super Admin",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Super Admin",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Super Admin",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Super Admin",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Super Admin",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Super Admin",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Super Admin",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembaruan Aplikasi",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembaruan Aplikasi",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembaruan Aplikasi",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembaruan Aplikasi",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembaruan Aplikasi",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembaruan Aplikasi",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Pembaruan Aplikasi",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembaruan Aplikasi",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1510,23 +1510,23 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -1541,23 +1541,23 @@
         </is>
       </c>
       <c r="B34" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G475,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G484,"Lulus")</f>
         <v/>
       </c>
       <c r="D34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G475,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G484,"Gagal")</f>
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G475,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G484,"Terblokir")</f>
         <v/>
       </c>
       <c r="F34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A475,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G475,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G484,"Dilewati")</f>
         <v/>
       </c>
       <c r="G34" s="5">
@@ -1789,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I475"/>
+  <dimension ref="A1:I484"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16518,12 +16518,12 @@
     <row r="421">
       <c r="A421" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B421" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-01</t>
+          <t>TC-VC-69</t>
         </is>
       </c>
       <c r="C421" s="18" t="inlineStr">
@@ -16533,17 +16533,17 @@
       </c>
       <c r="D421" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Analisa Pasar</t>
+          <t>Terbitkan batch dengan ceklis Khusus pengguna baru</t>
         </is>
       </c>
       <c r="E421" s="16" t="inlineStr">
         <is>
-          <t>Empat bagian termuat tanpa galat</t>
+          <t>Tersimpan; kartunya menyebut "khusus pengguna baru"</t>
         </is>
       </c>
       <c r="F421" s="16" t="inlineStr">
         <is>
-          <t>F-MR-01…04</t>
+          <t>F-VC-26</t>
         </is>
       </c>
       <c r="G421" s="16" t="inlineStr"/>
@@ -16553,12 +16553,12 @@
     <row r="422">
       <c r="A422" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B422" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-02</t>
+          <t>TC-VC-70</t>
         </is>
       </c>
       <c r="C422" s="15" t="inlineStr">
@@ -16568,17 +16568,17 @@
       </c>
       <c r="D422" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan Top 5 Pelanggan dengan jumlah manual dari orders</t>
+          <t>Akun yang belum pernah memesan menebusnya</t>
         </is>
       </c>
       <c r="E422" s="13" t="inlineStr">
         <is>
-          <t>Cocok nominal dan jumlah pesanannya</t>
+          <t>Berhasil</t>
         </is>
       </c>
       <c r="F422" s="13" t="inlineStr">
         <is>
-          <t>F-MR-01</t>
+          <t>F-VC-26</t>
         </is>
       </c>
       <c r="G422" s="13" t="inlineStr"/>
@@ -16588,12 +16588,12 @@
     <row r="423">
       <c r="A423" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B423" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-03</t>
+          <t>TC-VC-71</t>
         </is>
       </c>
       <c r="C423" s="18" t="inlineStr">
@@ -16603,17 +16603,17 @@
       </c>
       <c r="D423" s="16" t="inlineStr">
         <is>
-          <t>Batalkan sebuah pesanan besar, muat ulang</t>
+          <t>Akun yang pernah punya pesanan terbayar menebusnya</t>
         </is>
       </c>
       <c r="E423" s="16" t="inlineStr">
         <is>
-          <t>Nominalnya berkurang — yang batal tidak dihitung</t>
+          <t>Ditolak — "hanya untuk pengguna baru KaataGo"</t>
         </is>
       </c>
       <c r="F423" s="16" t="inlineStr">
         <is>
-          <t>F-MR-05</t>
+          <t>F-VC-26, F-VC-27</t>
         </is>
       </c>
       <c r="G423" s="16" t="inlineStr"/>
@@ -16623,12 +16623,12 @@
     <row r="424">
       <c r="A424" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B424" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-04</t>
+          <t>TC-VC-72</t>
         </is>
       </c>
       <c r="C424" s="15" t="inlineStr">
@@ -16638,17 +16638,17 @@
       </c>
       <c r="D424" s="13" t="inlineStr">
         <is>
-          <t>Buat akun pelanggan baru tanpa memesan</t>
+          <t>Akun yang pesanannya semua batal menebusnya</t>
         </is>
       </c>
       <c r="E424" s="13" t="inlineStr">
         <is>
-          <t>Muncul di daftar Belum Pernah Memesan</t>
+          <t>Berhasil — batal tidak menghilangkan status pengguna baru</t>
         </is>
       </c>
       <c r="F424" s="13" t="inlineStr">
         <is>
-          <t>F-MR-02</t>
+          <t>F-VC-26</t>
         </is>
       </c>
       <c r="G424" s="13" t="inlineStr"/>
@@ -16658,12 +16658,12 @@
     <row r="425">
       <c r="A425" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B425" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-05</t>
+          <t>TC-VC-73</t>
         </is>
       </c>
       <c r="C425" s="18" t="inlineStr">
@@ -16673,17 +16673,17 @@
       </c>
       <c r="D425" s="16" t="inlineStr">
         <is>
-          <t>Pelanggan itu menyelesaikan satu pesanan, muat ulang</t>
+          <t>Akun yang pernah memesan di resto lain saja</t>
         </is>
       </c>
       <c r="E425" s="16" t="inlineStr">
         <is>
-          <t>Hilang dari daftar tersebut</t>
+          <t>Ditolak — batasnya seluruh KaataGo</t>
         </is>
       </c>
       <c r="F425" s="16" t="inlineStr">
         <is>
-          <t>F-MR-02</t>
+          <t>F-VC-26</t>
         </is>
       </c>
       <c r="G425" s="16" t="inlineStr"/>
@@ -16693,12 +16693,12 @@
     <row r="426">
       <c r="A426" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B426" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-06</t>
+          <t>TC-VC-74</t>
         </is>
       </c>
       <c r="C426" s="15" t="inlineStr">
@@ -16708,17 +16708,17 @@
       </c>
       <c r="D426" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan Top 5 Resto dengan Jurnal GL resto bersangkutan</t>
+          <t>Batch khusus pengguna baru berkuota 1, ditebus akun lama lalu akun baru</t>
         </is>
       </c>
       <c r="E426" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sejalan</t>
+          <t>Akun lama ditolak dengan sebab yang benar; kuotanya tidak berkurang</t>
         </is>
       </c>
       <c r="F426" s="13" t="inlineStr">
         <is>
-          <t>F-MR-03</t>
+          <t>F-VC-26, F-VC-27</t>
         </is>
       </c>
       <c r="G426" s="13" t="inlineStr"/>
@@ -16728,32 +16728,32 @@
     <row r="427">
       <c r="A427" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B427" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-07</t>
-        </is>
-      </c>
-      <c r="C427" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-75</t>
+        </is>
+      </c>
+      <c r="C427" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D427" s="16" t="inlineStr">
         <is>
-          <t>Resto yang seluruh pesanannya batal</t>
+          <t>Periksa pengumuman kotak masuknya</t>
         </is>
       </c>
       <c r="E427" s="16" t="inlineStr">
         <is>
-          <t>Muncul di Belum Ada Penghasilan, jumlah pesanan 0</t>
+          <t>Menyebut "Khusus pengguna baru"</t>
         </is>
       </c>
       <c r="F427" s="16" t="inlineStr">
         <is>
-          <t>F-MR-04</t>
+          <t>F-VC-28</t>
         </is>
       </c>
       <c r="G427" s="16" t="inlineStr"/>
@@ -16763,12 +16763,12 @@
     <row r="428">
       <c r="A428" s="13" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B428" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-08</t>
+          <t>TC-VC-76</t>
         </is>
       </c>
       <c r="C428" s="19" t="inlineStr">
@@ -16778,17 +16778,17 @@
       </c>
       <c r="D428" s="13" t="inlineStr">
         <is>
-          <t>Resto baru tanpa pesanan sama sekali</t>
+          <t>Terbitkan batch tanpa ceklis itu</t>
         </is>
       </c>
       <c r="E428" s="13" t="inlineStr">
         <is>
-          <t>Muncul dengan "Belum ada pesanan"</t>
+          <t>Siapa pun bisa menebus; kalimat syaratnya tidak muncul</t>
         </is>
       </c>
       <c r="F428" s="13" t="inlineStr">
         <is>
-          <t>F-MR-04</t>
+          <t>F-VC-26, F-VC-28</t>
         </is>
       </c>
       <c r="G428" s="13" t="inlineStr"/>
@@ -16798,32 +16798,32 @@
     <row r="429">
       <c r="A429" s="16" t="inlineStr">
         <is>
-          <t>## 19e. Analisa Pasar</t>
+          <t>## 19d. Voucher Pelanggan</t>
         </is>
       </c>
       <c r="B429" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-09</t>
-        </is>
-      </c>
-      <c r="C429" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-77</t>
+        </is>
+      </c>
+      <c r="C429" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D429" s="16" t="inlineStr">
         <is>
-          <t>Periksa apakah resto KaataGo ikut terhitung</t>
+          <t>Periksa batch lama yang terbit sebelum fitur ini</t>
         </is>
       </c>
       <c r="E429" s="16" t="inlineStr">
         <is>
-          <t>Tidak — resto platform dikecualikan</t>
+          <t>Tetap terbuka untuk siapa saja</t>
         </is>
       </c>
       <c r="F429" s="16" t="inlineStr">
         <is>
-          <t>F-MR-06</t>
+          <t>F-VC-26</t>
         </is>
       </c>
       <c r="G429" s="16" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="B430" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-10</t>
+          <t>TC-MR-01</t>
         </is>
       </c>
       <c r="C430" s="15" t="inlineStr">
@@ -16848,17 +16848,17 @@
       </c>
       <c r="D430" s="13" t="inlineStr">
         <is>
-          <t>Hapus lunak sebuah resto, muat ulang</t>
+          <t>Super Admin → Analisa Pasar</t>
         </is>
       </c>
       <c r="E430" s="13" t="inlineStr">
         <is>
-          <t>Hilang dari keempat daftar</t>
+          <t>Empat bagian termuat tanpa galat</t>
         </is>
       </c>
       <c r="F430" s="13" t="inlineStr">
         <is>
-          <t>F-MR-06</t>
+          <t>F-MR-01…04</t>
         </is>
       </c>
       <c r="G430" s="13" t="inlineStr"/>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="B431" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-11</t>
+          <t>TC-MR-02</t>
         </is>
       </c>
       <c r="C431" s="18" t="inlineStr">
@@ -16883,17 +16883,17 @@
       </c>
       <c r="D431" s="16" t="inlineStr">
         <is>
-          <t>Panggil report_top_customers sebagai Owner resto</t>
+          <t>Bandingkan Top 5 Pelanggan dengan jumlah manual dari orders</t>
         </is>
       </c>
       <c r="E431" s="16" t="inlineStr">
         <is>
-          <t>Daftar kosong, bukan pesan galat</t>
+          <t>Cocok nominal dan jumlah pesanannya</t>
         </is>
       </c>
       <c r="F431" s="16" t="inlineStr">
         <is>
-          <t>F-MR-07</t>
+          <t>F-MR-01</t>
         </is>
       </c>
       <c r="G431" s="16" t="inlineStr"/>
@@ -16908,27 +16908,27 @@
       </c>
       <c r="B432" s="14" t="inlineStr">
         <is>
-          <t>TC-MR-12</t>
-        </is>
-      </c>
-      <c r="C432" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-03</t>
+        </is>
+      </c>
+      <c r="C432" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D432" s="13" t="inlineStr">
         <is>
-          <t>Panggil salah satu RPC dengan p_limit 99999</t>
+          <t>Batalkan sebuah pesanan besar, muat ulang</t>
         </is>
       </c>
       <c r="E432" s="13" t="inlineStr">
         <is>
-          <t>Dijepit ke batas atasnya</t>
+          <t>Nominalnya berkurang — yang batal tidak dihitung</t>
         </is>
       </c>
       <c r="F432" s="13" t="inlineStr">
         <is>
-          <t>F-MR-07</t>
+          <t>F-MR-05</t>
         </is>
       </c>
       <c r="G432" s="13" t="inlineStr"/>
@@ -16943,27 +16943,27 @@
       </c>
       <c r="B433" s="17" t="inlineStr">
         <is>
-          <t>TC-MR-13</t>
-        </is>
-      </c>
-      <c r="C433" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-MR-04</t>
+        </is>
+      </c>
+      <c r="C433" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D433" s="16" t="inlineStr">
         <is>
-          <t>Pesanan kasir atas nama tamu</t>
+          <t>Buat akun pelanggan baru tanpa memesan</t>
         </is>
       </c>
       <c r="E433" s="16" t="inlineStr">
         <is>
-          <t>Tidak ikut peringkat pelanggan — bukan akun terdaftar</t>
+          <t>Muncul di daftar Belum Pernah Memesan</t>
         </is>
       </c>
       <c r="F433" s="16" t="inlineStr">
         <is>
-          <t>F-MR-01</t>
+          <t>F-MR-02</t>
         </is>
       </c>
       <c r="G433" s="16" t="inlineStr"/>
@@ -16973,12 +16973,12 @@
     <row r="434">
       <c r="A434" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B434" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-01</t>
+          <t>TC-MR-05</t>
         </is>
       </c>
       <c r="C434" s="15" t="inlineStr">
@@ -16988,17 +16988,17 @@
       </c>
       <c r="D434" s="13" t="inlineStr">
         <is>
-          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
+          <t>Pelanggan itu menyelesaikan satu pesanan, muat ulang</t>
         </is>
       </c>
       <c r="E434" s="13" t="inlineStr">
         <is>
-          <t>Tidak mengembalikan pesanan resto mana pun</t>
+          <t>Hilang dari daftar tersebut</t>
         </is>
       </c>
       <c r="F434" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-MR-02</t>
         </is>
       </c>
       <c r="G434" s="13" t="inlineStr"/>
@@ -17008,12 +17008,12 @@
     <row r="435">
       <c r="A435" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B435" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-02</t>
+          <t>TC-MR-06</t>
         </is>
       </c>
       <c r="C435" s="18" t="inlineStr">
@@ -17023,17 +17023,17 @@
       </c>
       <c r="D435" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
+          <t>Bandingkan Top 5 Resto dengan Jurnal GL resto bersangkutan</t>
         </is>
       </c>
       <c r="E435" s="16" t="inlineStr">
         <is>
-          <t>Kosong — bukan galat, tapi juga bukan data</t>
+          <t>Nominalnya sejalan</t>
         </is>
       </c>
       <c r="F435" s="16" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-MR-03</t>
         </is>
       </c>
       <c r="G435" s="16" t="inlineStr"/>
@@ -17043,12 +17043,12 @@
     <row r="436">
       <c r="A436" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B436" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-03</t>
+          <t>TC-MR-07</t>
         </is>
       </c>
       <c r="C436" s="15" t="inlineStr">
@@ -17058,17 +17058,17 @@
       </c>
       <c r="D436" s="13" t="inlineStr">
         <is>
-          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
+          <t>Resto yang seluruh pesanannya batal</t>
         </is>
       </c>
       <c r="E436" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
+          <t>Muncul di Belum Ada Penghasilan, jumlah pesanan 0</t>
         </is>
       </c>
       <c r="F436" s="13" t="inlineStr">
         <is>
-          <t>TSD §5</t>
+          <t>F-MR-04</t>
         </is>
       </c>
       <c r="G436" s="13" t="inlineStr"/>
@@ -17078,32 +17078,32 @@
     <row r="437">
       <c r="A437" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B437" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-04</t>
-        </is>
-      </c>
-      <c r="C437" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-MR-08</t>
+        </is>
+      </c>
+      <c r="C437" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D437" s="16" t="inlineStr">
         <is>
-          <t>Login sebagai Kasir, baca gl_journal_entries</t>
+          <t>Resto baru tanpa pesanan sama sekali</t>
         </is>
       </c>
       <c r="E437" s="16" t="inlineStr">
         <is>
-          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
+          <t>Muncul dengan "Belum ada pesanan"</t>
         </is>
       </c>
       <c r="F437" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13, TSD §5.1</t>
+          <t>F-MR-04</t>
         </is>
       </c>
       <c r="G437" s="16" t="inlineStr"/>
@@ -17113,12 +17113,12 @@
     <row r="438">
       <c r="A438" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B438" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-05</t>
+          <t>TC-MR-09</t>
         </is>
       </c>
       <c r="C438" s="15" t="inlineStr">
@@ -17128,17 +17128,17 @@
       </c>
       <c r="D438" s="13" t="inlineStr">
         <is>
-          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
+          <t>Periksa apakah resto KaataGo ikut terhitung</t>
         </is>
       </c>
       <c r="E438" s="13" t="inlineStr">
         <is>
-          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
+          <t>Tidak — resto platform dikecualikan</t>
         </is>
       </c>
       <c r="F438" s="13" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-MR-06</t>
         </is>
       </c>
       <c r="G438" s="13" t="inlineStr"/>
@@ -17148,12 +17148,12 @@
     <row r="439">
       <c r="A439" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B439" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-06</t>
+          <t>TC-MR-10</t>
         </is>
       </c>
       <c r="C439" s="18" t="inlineStr">
@@ -17163,17 +17163,17 @@
       </c>
       <c r="D439" s="16" t="inlineStr">
         <is>
-          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
+          <t>Hapus lunak sebuah resto, muat ulang</t>
         </is>
       </c>
       <c r="E439" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Hilang dari keempat daftar</t>
         </is>
       </c>
       <c r="F439" s="16" t="inlineStr">
         <is>
-          <t>TSD §5.2</t>
+          <t>F-MR-06</t>
         </is>
       </c>
       <c r="G439" s="16" t="inlineStr"/>
@@ -17183,12 +17183,12 @@
     <row r="440">
       <c r="A440" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B440" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-07</t>
+          <t>TC-MR-11</t>
         </is>
       </c>
       <c r="C440" s="15" t="inlineStr">
@@ -17198,17 +17198,17 @@
       </c>
       <c r="D440" s="13" t="inlineStr">
         <is>
-          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
+          <t>Panggil report_top_customers sebagai Owner resto</t>
         </is>
       </c>
       <c r="E440" s="13" t="inlineStr">
         <is>
-          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
+          <t>Daftar kosong, bukan pesan galat</t>
         </is>
       </c>
       <c r="F440" s="13" t="inlineStr">
         <is>
-          <t>TSD §11</t>
+          <t>F-MR-07</t>
         </is>
       </c>
       <c r="G440" s="13" t="inlineStr"/>
@@ -17218,32 +17218,32 @@
     <row r="441">
       <c r="A441" s="16" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B441" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-08</t>
-        </is>
-      </c>
-      <c r="C441" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-MR-12</t>
+        </is>
+      </c>
+      <c r="C441" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D441" s="16" t="inlineStr">
         <is>
-          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
+          <t>Panggil salah satu RPC dengan p_limit 99999</t>
         </is>
       </c>
       <c r="E441" s="16" t="inlineStr">
         <is>
-          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
+          <t>Dijepit ke batas atasnya</t>
         </is>
       </c>
       <c r="F441" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-MR-07</t>
         </is>
       </c>
       <c r="G441" s="16" t="inlineStr"/>
@@ -17253,32 +17253,32 @@
     <row r="442">
       <c r="A442" s="13" t="inlineStr">
         <is>
-          <t>Uji Teknis (lingkup TSD)</t>
+          <t>## 19e. Analisa Pasar</t>
         </is>
       </c>
       <c r="B442" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-09</t>
-        </is>
-      </c>
-      <c r="C442" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-MR-13</t>
+        </is>
+      </c>
+      <c r="C442" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D442" s="13" t="inlineStr">
         <is>
-          <t>Buat resto baru dari Super Admin</t>
+          <t>Pesanan kasir atas nama tamu</t>
         </is>
       </c>
       <c r="E442" s="13" t="inlineStr">
         <is>
-          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
+          <t>Tidak ikut peringkat pelanggan — bukan akun terdaftar</t>
         </is>
       </c>
       <c r="F442" s="13" t="inlineStr">
         <is>
-          <t>A-19, TSD §6.2</t>
+          <t>F-MR-01</t>
         </is>
       </c>
       <c r="G442" s="13" t="inlineStr"/>
@@ -17293,7 +17293,7 @@
       </c>
       <c r="B443" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-10</t>
+          <t>TC-TS-01</t>
         </is>
       </c>
       <c r="C443" s="18" t="inlineStr">
@@ -17303,17 +17303,17 @@
       </c>
       <c r="D443" s="16" t="inlineStr">
         <is>
-          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
+          <t>Panggil GET /rest/v1/orders memakai kunci anon tanpa login</t>
         </is>
       </c>
       <c r="E443" s="16" t="inlineStr">
         <is>
-          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
+          <t>Tidak mengembalikan pesanan resto mana pun</t>
         </is>
       </c>
       <c r="F443" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.2</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G443" s="16" t="inlineStr"/>
@@ -17328,27 +17328,27 @@
       </c>
       <c r="B444" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-11</t>
-        </is>
-      </c>
-      <c r="C444" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-02</t>
+        </is>
+      </c>
+      <c r="C444" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D444" s="13" t="inlineStr">
         <is>
-          <t>Periksa push_outbox sesudah pengumuman terbit</t>
+          <t>Login sebagai karyawan resto A, baca orders resto B lewat API</t>
         </is>
       </c>
       <c r="E444" s="13" t="inlineStr">
         <is>
-          <t>Baris masuk, lalu sent_at terisi</t>
+          <t>Kosong — bukan galat, tapi juga bukan data</t>
         </is>
       </c>
       <c r="F444" s="13" t="inlineStr">
         <is>
-          <t>TSD §8</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G444" s="13" t="inlineStr"/>
@@ -17363,27 +17363,27 @@
       </c>
       <c r="B445" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-12</t>
-        </is>
-      </c>
-      <c r="C445" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-03</t>
+        </is>
+      </c>
+      <c r="C445" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D445" s="16" t="inlineStr">
         <is>
-          <t>Matikan sambungan, pakai aplikasi</t>
+          <t>Login sebagai Owner, buka tiap layar resto miliknya</t>
         </is>
       </c>
       <c r="E445" s="16" t="inlineStr">
         <is>
-          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
+          <t>Tidak ada layar yang kosong karena RLS — owner harus disebut di setiap daftar peran</t>
         </is>
       </c>
       <c r="F445" s="16" t="inlineStr">
         <is>
-          <t>TSD §10, FSD §5.6</t>
+          <t>TSD §5</t>
         </is>
       </c>
       <c r="G445" s="16" t="inlineStr"/>
@@ -17398,27 +17398,27 @@
       </c>
       <c r="B446" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-13</t>
-        </is>
-      </c>
-      <c r="C446" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-04</t>
+        </is>
+      </c>
+      <c r="C446" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D446" s="13" t="inlineStr">
         <is>
-          <t>Sambungkan lagi</t>
+          <t>Login sebagai Kasir, baca gl_journal_entries</t>
         </is>
       </c>
       <c r="E446" s="13" t="inlineStr">
         <is>
-          <t>Pesanan yang dibuat saat luring terkirim</t>
+          <t>Hanya yang terkait catatan yang memang boleh dia lihat</t>
         </is>
       </c>
       <c r="F446" s="13" t="inlineStr">
         <is>
-          <t>TSD §10</t>
+          <t>F-KS-13, TSD §5.1</t>
         </is>
       </c>
       <c r="G446" s="13" t="inlineStr"/>
@@ -17433,7 +17433,7 @@
       </c>
       <c r="B447" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-14</t>
+          <t>TC-TS-05</t>
         </is>
       </c>
       <c r="C447" s="18" t="inlineStr">
@@ -17443,17 +17443,17 @@
       </c>
       <c r="D447" s="16" t="inlineStr">
         <is>
-          <t>Coba bayar QRIS saat luring</t>
+          <t>Coba UPDATE products langsung lewat API sebagai pelanggan</t>
         </is>
       </c>
       <c r="E447" s="16" t="inlineStr">
         <is>
-          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
+          <t>Ditolak; pengurangan stok hanya lewat decrement_stock</t>
         </is>
       </c>
       <c r="F447" s="16" t="inlineStr">
         <is>
-          <t>FSD §5.6</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G447" s="16" t="inlineStr"/>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="B448" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-15</t>
+          <t>TC-TS-06</t>
         </is>
       </c>
       <c r="C448" s="15" t="inlineStr">
@@ -17478,17 +17478,17 @@
       </c>
       <c r="D448" s="13" t="inlineStr">
         <is>
-          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
+          <t>Panggil cancel_my_order untuk pesanan milik orang lain</t>
         </is>
       </c>
       <c r="E448" s="13" t="inlineStr">
         <is>
-          <t>Nominal yang dipakai tetap dari basis data</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F448" s="13" t="inlineStr">
         <is>
-          <t>TSD §7.1</t>
+          <t>TSD §5.2</t>
         </is>
       </c>
       <c r="G448" s="13" t="inlineStr"/>
@@ -17503,7 +17503,7 @@
       </c>
       <c r="B449" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-16</t>
+          <t>TC-TS-07</t>
         </is>
       </c>
       <c r="C449" s="18" t="inlineStr">
@@ -17513,17 +17513,17 @@
       </c>
       <c r="D449" s="16" t="inlineStr">
         <is>
-          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
+          <t>Jalankan ulang seluruh JALANKAN-INI.sql di database yang sudah terisi</t>
         </is>
       </c>
       <c r="E449" s="16" t="inlineStr">
         <is>
-          <t>Ditolak</t>
+          <t>Selesai tanpa galat; tidak ada data yang berubah</t>
         </is>
       </c>
       <c r="F449" s="16" t="inlineStr">
         <is>
-          <t>F-PG-02, TSD §7.1</t>
+          <t>TSD §11</t>
         </is>
       </c>
       <c r="G449" s="16" t="inlineStr"/>
@@ -17538,27 +17538,27 @@
       </c>
       <c r="B450" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-17</t>
-        </is>
-      </c>
-      <c r="C450" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-08</t>
+        </is>
+      </c>
+      <c r="C450" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D450" s="13" t="inlineStr">
         <is>
-          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
+          <t>Jalankan ulang satu berkas SQL lama saja, misal cash_payment_expiry.sql</t>
         </is>
       </c>
       <c r="E450" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
+          <t>Tidak menyempitkan daftar nilai batasan mana pun</t>
         </is>
       </c>
       <c r="F450" s="13" t="inlineStr">
         <is>
-          <t>TSD §1.2</t>
+          <t>TSD §11.1</t>
         </is>
       </c>
       <c r="G450" s="13" t="inlineStr"/>
@@ -17573,27 +17573,27 @@
       </c>
       <c r="B451" s="17" t="inlineStr">
         <is>
-          <t>TC-TS-18</t>
-        </is>
-      </c>
-      <c r="C451" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-09</t>
+        </is>
+      </c>
+      <c r="C451" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D451" s="16" t="inlineStr">
         <is>
-          <t>Pesanan berpindah status lunas lebih dari sekali</t>
+          <t>Buat resto baru dari Super Admin</t>
         </is>
       </c>
       <c r="E451" s="16" t="inlineStr">
         <is>
-          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
+          <t>Bagan akun GL 12 jenis dan tarif PPN/service langsung terisi</t>
         </is>
       </c>
       <c r="F451" s="16" t="inlineStr">
         <is>
-          <t>TSD §6.5</t>
+          <t>A-19, TSD §6.2</t>
         </is>
       </c>
       <c r="G451" s="16" t="inlineStr"/>
@@ -17608,27 +17608,27 @@
       </c>
       <c r="B452" s="14" t="inlineStr">
         <is>
-          <t>TC-TS-19</t>
-        </is>
-      </c>
-      <c r="C452" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TS-10</t>
+        </is>
+      </c>
+      <c r="C452" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D452" s="13" t="inlineStr">
         <is>
-          <t>Hapus resto uji</t>
+          <t>Kosongkan satu nomor GL, lalu buat transaksi</t>
         </is>
       </c>
       <c r="E452" s="13" t="inlineStr">
         <is>
-          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
+          <t>Jurnal untuk baris itu tidak terbentuk — pastikan gejalanya dikenali penguji</t>
         </is>
       </c>
       <c r="F452" s="13" t="inlineStr">
         <is>
-          <t>TSD §4.0</t>
+          <t>TSD §6.2</t>
         </is>
       </c>
       <c r="G452" s="13" t="inlineStr"/>
@@ -17638,32 +17638,32 @@
     <row r="453">
       <c r="A453" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B453" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-01</t>
-        </is>
-      </c>
-      <c r="C453" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-11</t>
+        </is>
+      </c>
+      <c r="C453" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D453" s="16" t="inlineStr">
         <is>
-          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
+          <t>Periksa push_outbox sesudah pengumuman terbit</t>
         </is>
       </c>
       <c r="E453" s="16" t="inlineStr">
         <is>
-          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
+          <t>Baris masuk, lalu sent_at terisi</t>
         </is>
       </c>
       <c r="F453" s="16" t="inlineStr">
         <is>
-          <t>F-KS-09</t>
+          <t>TSD §8</t>
         </is>
       </c>
       <c r="G453" s="16" t="inlineStr"/>
@@ -17673,32 +17673,32 @@
     <row r="454">
       <c r="A454" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B454" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-02</t>
-        </is>
-      </c>
-      <c r="C454" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-12</t>
+        </is>
+      </c>
+      <c r="C454" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D454" s="13" t="inlineStr">
         <is>
-          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
+          <t>Matikan sambungan, pakai aplikasi</t>
         </is>
       </c>
       <c r="E454" s="13" t="inlineStr">
         <is>
-          <t>Semua cara bayar masuk Riwayat Kasir</t>
+          <t>Katalog tetap tampil; pesanan tunai tetap bisa dibuat</t>
         </is>
       </c>
       <c r="F454" s="13" t="inlineStr">
         <is>
-          <t>F-PP-09, A-13</t>
+          <t>TSD §10, FSD §5.6</t>
         </is>
       </c>
       <c r="G454" s="13" t="inlineStr"/>
@@ -17708,32 +17708,32 @@
     <row r="455">
       <c r="A455" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B455" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-03</t>
-        </is>
-      </c>
-      <c r="C455" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TS-13</t>
+        </is>
+      </c>
+      <c r="C455" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D455" s="16" t="inlineStr">
         <is>
-          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
+          <t>Sambungkan lagi</t>
         </is>
       </c>
       <c r="E455" s="16" t="inlineStr">
         <is>
-          <t>Tidak muncul sama sekali</t>
+          <t>Pesanan yang dibuat saat luring terkirim</t>
         </is>
       </c>
       <c r="F455" s="16" t="inlineStr">
         <is>
-          <t>A-17</t>
+          <t>TSD §10</t>
         </is>
       </c>
       <c r="G455" s="16" t="inlineStr"/>
@@ -17743,12 +17743,12 @@
     <row r="456">
       <c r="A456" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B456" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-04</t>
+          <t>TC-TS-14</t>
         </is>
       </c>
       <c r="C456" s="15" t="inlineStr">
@@ -17758,17 +17758,17 @@
       </c>
       <c r="D456" s="13" t="inlineStr">
         <is>
-          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
+          <t>Coba bayar QRIS saat luring</t>
         </is>
       </c>
       <c r="E456" s="13" t="inlineStr">
         <is>
-          <t>Nominalnya sama dengan yang diajukan</t>
+          <t>Ditolak dengan jelas — bukan menggantung tanpa kabar</t>
         </is>
       </c>
       <c r="F456" s="13" t="inlineStr">
         <is>
-          <t>F-FN-03</t>
+          <t>FSD §5.6</t>
         </is>
       </c>
       <c r="G456" s="13" t="inlineStr"/>
@@ -17778,12 +17778,12 @@
     <row r="457">
       <c r="A457" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B457" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-05</t>
+          <t>TC-TS-15</t>
         </is>
       </c>
       <c r="C457" s="18" t="inlineStr">
@@ -17793,17 +17793,17 @@
       </c>
       <c r="D457" s="16" t="inlineStr">
         <is>
-          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
+          <t>Panggil create-qris dengan nominal yang dipalsukan di badan permintaan</t>
         </is>
       </c>
       <c r="E457" s="16" t="inlineStr">
         <is>
-          <t>Berlaku sama di kasir dan HP pelanggan</t>
+          <t>Nominal yang dipakai tetap dari basis data</t>
         </is>
       </c>
       <c r="F457" s="16" t="inlineStr">
         <is>
-          <t>A-14</t>
+          <t>TSD §7.1</t>
         </is>
       </c>
       <c r="G457" s="16" t="inlineStr"/>
@@ -17813,12 +17813,12 @@
     <row r="458">
       <c r="A458" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B458" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-06</t>
+          <t>TC-TS-16</t>
         </is>
       </c>
       <c r="C458" s="15" t="inlineStr">
@@ -17828,17 +17828,17 @@
       </c>
       <c r="D458" s="13" t="inlineStr">
         <is>
-          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+          <t>Tandai pesanan lunas lewat API tanpa lewat webhook</t>
         </is>
       </c>
       <c r="E458" s="13" t="inlineStr">
         <is>
-          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+          <t>Ditolak</t>
         </is>
       </c>
       <c r="F458" s="13" t="inlineStr">
         <is>
-          <t>F-DS-10, F-DS-12</t>
+          <t>F-PG-02, TSD §7.1</t>
         </is>
       </c>
       <c r="G458" s="13" t="inlineStr"/>
@@ -17848,12 +17848,12 @@
     <row r="459">
       <c r="A459" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B459" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-07</t>
+          <t>TC-TS-17</t>
         </is>
       </c>
       <c r="C459" s="20" t="inlineStr">
@@ -17863,17 +17863,17 @@
       </c>
       <c r="D459" s="16" t="inlineStr">
         <is>
-          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+          <t>Bongkar APK, cari kunci Xendit/FCM/Resend</t>
         </is>
       </c>
       <c r="E459" s="16" t="inlineStr">
         <is>
-          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+          <t>Tidak ada satu pun kunci pengirim di dalamnya</t>
         </is>
       </c>
       <c r="F459" s="16" t="inlineStr">
         <is>
-          <t>F-IN-15</t>
+          <t>TSD §1.2</t>
         </is>
       </c>
       <c r="G459" s="16" t="inlineStr"/>
@@ -17883,12 +17883,12 @@
     <row r="460">
       <c r="A460" s="13" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B460" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-08</t>
+          <t>TC-TS-18</t>
         </is>
       </c>
       <c r="C460" s="19" t="inlineStr">
@@ -17898,17 +17898,17 @@
       </c>
       <c r="D460" s="13" t="inlineStr">
         <is>
-          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+          <t>Pesanan berpindah status lunas lebih dari sekali</t>
         </is>
       </c>
       <c r="E460" s="13" t="inlineStr">
         <is>
-          <t>Daftar menu termuat</t>
+          <t>Jurnalnya tetap satu set — tidak ada baris ganda</t>
         </is>
       </c>
       <c r="F460" s="13" t="inlineStr">
         <is>
-          <t>F-DS-01</t>
+          <t>TSD §6.5</t>
         </is>
       </c>
       <c r="G460" s="13" t="inlineStr"/>
@@ -17918,12 +17918,12 @@
     <row r="461">
       <c r="A461" s="16" t="inlineStr">
         <is>
-          <t>Regresi — bug yang pernah terjadi</t>
+          <t>Uji Teknis (lingkup TSD)</t>
         </is>
       </c>
       <c r="B461" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-09</t>
+          <t>TC-TS-19</t>
         </is>
       </c>
       <c r="C461" s="20" t="inlineStr">
@@ -17933,17 +17933,17 @@
       </c>
       <c r="D461" s="16" t="inlineStr">
         <is>
-          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+          <t>Hapus resto uji</t>
         </is>
       </c>
       <c r="E461" s="16" t="inlineStr">
         <is>
-          <t>Detail jurnal terbuka</t>
+          <t>Seluruh isinya ikut terhapus, termasuk jurnalnya</t>
         </is>
       </c>
       <c r="F461" s="16" t="inlineStr">
         <is>
-          <t>F-KS-13</t>
+          <t>TSD §4.0</t>
         </is>
       </c>
       <c r="G461" s="16" t="inlineStr"/>
@@ -17958,27 +17958,27 @@
       </c>
       <c r="B462" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-10</t>
-        </is>
-      </c>
-      <c r="C462" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-01</t>
+        </is>
+      </c>
+      <c r="C462" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D462" s="13" t="inlineStr">
         <is>
-          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+          <t>Nominal QRIS kasir memakai subtotal menu, bukan total tagihan</t>
         </is>
       </c>
       <c r="E462" s="13" t="inlineStr">
         <is>
-          <t>Seluruh layar berganti bersih</t>
+          <t>Nominal di layar QRIS = total termasuk service dan PPN</t>
         </is>
       </c>
       <c r="F462" s="13" t="inlineStr">
         <is>
-          <t>A-18</t>
+          <t>F-KS-09</t>
         </is>
       </c>
       <c r="G462" s="13" t="inlineStr"/>
@@ -17993,27 +17993,27 @@
       </c>
       <c r="B463" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-11</t>
-        </is>
-      </c>
-      <c r="C463" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-02</t>
+        </is>
+      </c>
+      <c r="C463" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D463" s="16" t="inlineStr">
         <is>
-          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+          <t>Pesanan dilunasi lewat QRIS hilang dari Riwayat Kasir</t>
         </is>
       </c>
       <c r="E463" s="16" t="inlineStr">
         <is>
-          <t>Ikut tergulir bersama menunya</t>
+          <t>Semua cara bayar masuk Riwayat Kasir</t>
         </is>
       </c>
       <c r="F463" s="16" t="inlineStr">
         <is>
-          <t>F-CU-16, A-12</t>
+          <t>F-PP-09, A-13</t>
         </is>
       </c>
       <c r="G463" s="16" t="inlineStr"/>
@@ -18028,27 +18028,27 @@
       </c>
       <c r="B464" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-12</t>
-        </is>
-      </c>
-      <c r="C464" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-03</t>
+        </is>
+      </c>
+      <c r="C464" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D464" s="13" t="inlineStr">
         <is>
-          <t>Owner hanya bisa melihat Info Pembayaran</t>
+          <t>Pesanan dibatalkan tampil "Menunggu Pembayaran" di Pesanan Masuk</t>
         </is>
       </c>
       <c r="E464" s="13" t="inlineStr">
         <is>
-          <t>Owner bisa mengubahnya</t>
+          <t>Tidak muncul sama sekali</t>
         </is>
       </c>
       <c r="F464" s="13" t="inlineStr">
         <is>
-          <t>F-SD-02</t>
+          <t>A-17</t>
         </is>
       </c>
       <c r="G464" s="13" t="inlineStr"/>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="B465" s="17" t="inlineStr">
         <is>
-          <t>TC-RG-13</t>
+          <t>TC-RG-04</t>
         </is>
       </c>
       <c r="C465" s="18" t="inlineStr">
@@ -18073,17 +18073,17 @@
       </c>
       <c r="D465" s="16" t="inlineStr">
         <is>
-          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+          <t>Top up Rp 100.000 tercatat Rp 200.000 di jurnal</t>
         </is>
       </c>
       <c r="E465" s="16" t="inlineStr">
         <is>
-          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+          <t>Nominalnya sama dengan yang diajukan</t>
         </is>
       </c>
       <c r="F465" s="16" t="inlineStr">
         <is>
-          <t>TSD §11.1</t>
+          <t>F-FN-03</t>
         </is>
       </c>
       <c r="G465" s="16" t="inlineStr"/>
@@ -18098,27 +18098,27 @@
       </c>
       <c r="B466" s="14" t="inlineStr">
         <is>
-          <t>TC-RG-14</t>
-        </is>
-      </c>
-      <c r="C466" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-RG-05</t>
+        </is>
+      </c>
+      <c r="C466" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D466" s="13" t="inlineStr">
         <is>
-          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+          <t>Diskon tidak berlaku untuk pesanan mandiri pelanggan</t>
         </is>
       </c>
       <c r="E466" s="13" t="inlineStr">
         <is>
-          <t>Keduanya menulis 7</t>
+          <t>Berlaku sama di kasir dan HP pelanggan</t>
         </is>
       </c>
       <c r="F466" s="13" t="inlineStr">
         <is>
-          <t>F-QR-07</t>
+          <t>A-14</t>
         </is>
       </c>
       <c r="G466" s="13" t="inlineStr"/>
@@ -18128,25 +18128,340 @@
     <row r="467">
       <c r="A467" s="16" t="inlineStr">
         <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B467" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-06</t>
+        </is>
+      </c>
+      <c r="C467" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D467" s="16" t="inlineStr">
+        <is>
+          <t>Promo "beli 2" lolos oleh keranjang berisi dua menu berbeda</t>
+        </is>
+      </c>
+      <c r="E467" s="16" t="inlineStr">
+        <is>
+          <t>Syarat jumlah dihitung per menu, dan seluruhnya harus terpenuhi</t>
+        </is>
+      </c>
+      <c r="F467" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-10, F-DS-12</t>
+        </is>
+      </c>
+      <c r="G467" s="16" t="inlineStr"/>
+      <c r="H467" s="16" t="inlineStr"/>
+      <c r="I467" s="16" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B468" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-07</t>
+        </is>
+      </c>
+      <c r="C468" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D468" s="13" t="inlineStr">
+        <is>
+          <t>Tombol pilih/hapus di kotak masuk tidak bereaksi sama sekali</t>
+        </is>
+      </c>
+      <c r="E468" s="13" t="inlineStr">
+        <is>
+          <t>Bekerja di kotak masuk karyawan dan pelanggan</t>
+        </is>
+      </c>
+      <c r="F468" s="13" t="inlineStr">
+        <is>
+          <t>F-IN-15</t>
+        </is>
+      </c>
+      <c r="G468" s="13" t="inlineStr"/>
+      <c r="H468" s="13" t="inlineStr"/>
+      <c r="I468" s="13" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B469" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-08</t>
+        </is>
+      </c>
+      <c r="C469" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D469" s="16" t="inlineStr">
+        <is>
+          <t>Layar Diskon dari hub Kasir menyebut "Belum ada produk di resto ini"</t>
+        </is>
+      </c>
+      <c r="E469" s="16" t="inlineStr">
+        <is>
+          <t>Daftar menu termuat</t>
+        </is>
+      </c>
+      <c r="F469" s="16" t="inlineStr">
+        <is>
+          <t>F-DS-01</t>
+        </is>
+      </c>
+      <c r="G469" s="16" t="inlineStr"/>
+      <c r="H469" s="16" t="inlineStr"/>
+      <c r="I469" s="16" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B470" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-09</t>
+        </is>
+      </c>
+      <c r="C470" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D470" s="13" t="inlineStr">
+        <is>
+          <t>Kasir tidak bisa membuka detail jurnal — terlihat seperti GL belum dipetakan</t>
+        </is>
+      </c>
+      <c r="E470" s="13" t="inlineStr">
+        <is>
+          <t>Detail jurnal terbuka</t>
+        </is>
+      </c>
+      <c r="F470" s="13" t="inlineStr">
+        <is>
+          <t>F-KS-13</t>
+        </is>
+      </c>
+      <c r="G470" s="13" t="inlineStr"/>
+      <c r="H470" s="13" t="inlineStr"/>
+      <c r="I470" s="13" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B471" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-10</t>
+        </is>
+      </c>
+      <c r="C471" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D471" s="16" t="inlineStr">
+        <is>
+          <t>Layar dapur meninggalkan jejak warna lama saat tema diganti</t>
+        </is>
+      </c>
+      <c r="E471" s="16" t="inlineStr">
+        <is>
+          <t>Seluruh layar berganti bersih</t>
+        </is>
+      </c>
+      <c r="F471" s="16" t="inlineStr">
+        <is>
+          <t>A-18</t>
+        </is>
+      </c>
+      <c r="G471" s="16" t="inlineStr"/>
+      <c r="H471" s="16" t="inlineStr"/>
+      <c r="I471" s="16" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B472" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-11</t>
+        </is>
+      </c>
+      <c r="C472" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D472" s="13" t="inlineStr">
+        <is>
+          <t>Banner promo menempel di atas, tidak ikut tergulir</t>
+        </is>
+      </c>
+      <c r="E472" s="13" t="inlineStr">
+        <is>
+          <t>Ikut tergulir bersama menunya</t>
+        </is>
+      </c>
+      <c r="F472" s="13" t="inlineStr">
+        <is>
+          <t>F-CU-16, A-12</t>
+        </is>
+      </c>
+      <c r="G472" s="13" t="inlineStr"/>
+      <c r="H472" s="13" t="inlineStr"/>
+      <c r="I472" s="13" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B473" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-12</t>
+        </is>
+      </c>
+      <c r="C473" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D473" s="16" t="inlineStr">
+        <is>
+          <t>Owner hanya bisa melihat Info Pembayaran</t>
+        </is>
+      </c>
+      <c r="E473" s="16" t="inlineStr">
+        <is>
+          <t>Owner bisa mengubahnya</t>
+        </is>
+      </c>
+      <c r="F473" s="16" t="inlineStr">
+        <is>
+          <t>F-SD-02</t>
+        </is>
+      </c>
+      <c r="G473" s="16" t="inlineStr"/>
+      <c r="H473" s="16" t="inlineStr"/>
+      <c r="I473" s="16" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="13" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B474" s="14" t="inlineStr">
+        <is>
+          <t>TC-RG-13</t>
+        </is>
+      </c>
+      <c r="C474" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D474" s="13" t="inlineStr">
+        <is>
+          <t>Migrasi gagal: daftar nilai batasan menyempit saat berkas lama dijalankan ulang</t>
+        </is>
+      </c>
+      <c r="E474" s="13" t="inlineStr">
+        <is>
+          <t>Menjalankan ulang berkas mana pun tidak pernah menolak data yang sudah ada</t>
+        </is>
+      </c>
+      <c r="F474" s="13" t="inlineStr">
+        <is>
+          <t>TSD §11.1</t>
+        </is>
+      </c>
+      <c r="G474" s="13" t="inlineStr"/>
+      <c r="H474" s="13" t="inlineStr"/>
+      <c r="I474" s="13" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="16" t="inlineStr">
+        <is>
+          <t>Regresi — bug yang pernah terjadi</t>
+        </is>
+      </c>
+      <c r="B475" s="17" t="inlineStr">
+        <is>
+          <t>TC-RG-14</t>
+        </is>
+      </c>
+      <c r="C475" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D475" s="16" t="inlineStr">
+        <is>
+          <t>QR meja borongan bernomor 07, berbeda dengan mode satu meja</t>
+        </is>
+      </c>
+      <c r="E475" s="16" t="inlineStr">
+        <is>
+          <t>Keduanya menulis 7</t>
+        </is>
+      </c>
+      <c r="F475" s="16" t="inlineStr">
+        <is>
+          <t>F-QR-07</t>
+        </is>
+      </c>
+      <c r="G475" s="16" t="inlineStr"/>
+      <c r="H475" s="16" t="inlineStr"/>
+      <c r="I475" s="16" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="13" t="inlineStr">
+        <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B467" s="17" t="inlineStr">
+      <c r="B476" s="14" t="inlineStr">
         <is>
           <t>E2E-09</t>
         </is>
       </c>
-      <c r="C467" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D467" s="16" t="inlineStr">
+      <c r="C476" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D476" s="13" t="inlineStr">
         <is>
           <t>Satu siklus langganan penuh</t>
         </is>
       </c>
-      <c r="E467" s="16" t="inlineStr">
+      <c r="E476" s="13" t="inlineStr">
         <is>
           <t>1. Super Admin setel resto uji: Rp 150.000, jatuh tempo 3 hari lagi, tenggang 1 hari
 2. Terbitkan tagihan → periksa muncul di tab Tagihan berstatus Belum Dibayar
@@ -18160,37 +18475,37 @@
 10. Periksa Dashboard Xendit → dana masuk ke akun KaataGo, bukan sub-akun resto</t>
         </is>
       </c>
-      <c r="F467" s="16" t="inlineStr">
+      <c r="F476" s="13" t="inlineStr">
         <is>
           <t>F-BL-07 … F-BL-18, TSD §7.3</t>
         </is>
       </c>
-      <c r="G467" s="16" t="inlineStr"/>
-      <c r="H467" s="16" t="inlineStr"/>
-      <c r="I467" s="16" t="inlineStr"/>
-    </row>
-    <row r="468">
-      <c r="A468" s="13" t="inlineStr">
+      <c r="G476" s="13" t="inlineStr"/>
+      <c r="H476" s="13" t="inlineStr"/>
+      <c r="I476" s="13" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B468" s="14" t="inlineStr">
+      <c r="B477" s="17" t="inlineStr">
         <is>
           <t>E2E-01</t>
         </is>
       </c>
-      <c r="C468" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D468" s="13" t="inlineStr">
+      <c r="C477" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D477" s="16" t="inlineStr">
         <is>
           <t>Pelanggan bayar QRIS</t>
         </is>
       </c>
-      <c r="E468" s="13" t="inlineStr">
+      <c r="E477" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan scan QR meja → pilih 2 menu → Dine In → isi nama
 2. Pilih QRIS → bayar sungguhan dari aplikasi bank
@@ -18202,37 +18517,37 @@
 8. Periksa Saldo → masuk Non Cash, bukan Cash</t>
         </is>
       </c>
-      <c r="F468" s="13" t="inlineStr">
+      <c r="F477" s="16" t="inlineStr">
         <is>
           <t>F-CU-09, F-PG-02, F-CH-06, TSD §6, TSD §7.1</t>
         </is>
       </c>
-      <c r="G468" s="13" t="inlineStr"/>
-      <c r="H468" s="13" t="inlineStr"/>
-      <c r="I468" s="13" t="inlineStr"/>
-    </row>
-    <row r="469">
-      <c r="A469" s="16" t="inlineStr">
+      <c r="G477" s="16" t="inlineStr"/>
+      <c r="H477" s="16" t="inlineStr"/>
+      <c r="I477" s="16" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B469" s="17" t="inlineStr">
+      <c r="B478" s="14" t="inlineStr">
         <is>
           <t>E2E-02</t>
         </is>
       </c>
-      <c r="C469" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D469" s="16" t="inlineStr">
+      <c r="C478" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D478" s="13" t="inlineStr">
         <is>
           <t>Pelanggan bayar tunai di kasir</t>
         </is>
       </c>
-      <c r="E469" s="16" t="inlineStr">
+      <c r="E478" s="13" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan → pilih Tunai → catat nomor pesanannya
 2. Periksa layar pelanggan → hitungan mundur 30 menit berjalan
@@ -18244,74 +18559,74 @@
 8. Periksa Saldo Cash → bertambah sebesar totalnya</t>
         </is>
       </c>
-      <c r="F469" s="16" t="inlineStr">
+      <c r="F478" s="13" t="inlineStr">
         <is>
           <t>F-CU-09, F-PP-01, F-PP-06, F-PP-07, F-CH-06, A-02, A-13</t>
         </is>
       </c>
-      <c r="G469" s="16" t="inlineStr"/>
-      <c r="H469" s="16" t="inlineStr"/>
-      <c r="I469" s="16" t="inlineStr"/>
-    </row>
-    <row r="470">
-      <c r="A470" s="13" t="inlineStr">
+      <c r="G478" s="13" t="inlineStr"/>
+      <c r="H478" s="13" t="inlineStr"/>
+      <c r="I478" s="13" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B470" s="14" t="inlineStr">
+      <c r="B479" s="17" t="inlineStr">
         <is>
           <t>E2E-03</t>
         </is>
       </c>
-      <c r="C470" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D470" s="13" t="inlineStr">
+      <c r="C479" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D479" s="16" t="inlineStr">
         <is>
           <t>Tunai dengan cara bayar diganti</t>
         </is>
       </c>
-      <c r="E470" s="13" t="inlineStr">
+      <c r="E479" s="16" t="inlineStr">
         <is>
           <t>1. Ulangi E2E-02, tapi pada langkah 4 ganti cara bayarnya ke QRIS.
 2. Pesanannya harus tetap masuk Riwayat Kasir, dan masuk Non Cash
 3. di Saldo.</t>
         </is>
       </c>
-      <c r="F470" s="13" t="inlineStr">
+      <c r="F479" s="16" t="inlineStr">
         <is>
           <t>F-PP-09, A-13, TSD §4.2</t>
         </is>
       </c>
-      <c r="G470" s="13" t="inlineStr"/>
-      <c r="H470" s="13" t="inlineStr"/>
-      <c r="I470" s="13" t="inlineStr"/>
-    </row>
-    <row r="471">
-      <c r="A471" s="16" t="inlineStr">
+      <c r="G479" s="16" t="inlineStr"/>
+      <c r="H479" s="16" t="inlineStr"/>
+      <c r="I479" s="16" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B471" s="17" t="inlineStr">
+      <c r="B480" s="14" t="inlineStr">
         <is>
           <t>E2E-04</t>
         </is>
       </c>
-      <c r="C471" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D471" s="16" t="inlineStr">
+      <c r="C480" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D480" s="13" t="inlineStr">
         <is>
           <t>Setor tunai ke rekening</t>
         </is>
       </c>
-      <c r="E471" s="16" t="inlineStr">
+      <c r="E480" s="13" t="inlineStr">
         <is>
           <t>1. Kasir buka Setor Saldo Cash → catat tunai di laci
 2. Ajukan setoran sebesar sebagian dari itu, lampirkan bukti
@@ -18322,73 +18637,73 @@
 7. Periksa Jurnal GL → titipan suspense dilepas, dana masuk GL Total Saldo</t>
         </is>
       </c>
-      <c r="F471" s="16" t="inlineStr">
+      <c r="F480" s="13" t="inlineStr">
         <is>
           <t>F-SD-01, F-SD-05, A-05, TSD §6.4</t>
         </is>
       </c>
-      <c r="G471" s="16" t="inlineStr"/>
-      <c r="H471" s="16" t="inlineStr"/>
-      <c r="I471" s="16" t="inlineStr"/>
-    </row>
-    <row r="472">
-      <c r="A472" s="13" t="inlineStr">
+      <c r="G480" s="13" t="inlineStr"/>
+      <c r="H480" s="13" t="inlineStr"/>
+      <c r="I480" s="13" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B472" s="14" t="inlineStr">
+      <c r="B481" s="17" t="inlineStr">
         <is>
           <t>E2E-05</t>
         </is>
       </c>
-      <c r="C472" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D472" s="13" t="inlineStr">
+      <c r="C481" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D481" s="16" t="inlineStr">
         <is>
           <t>Top up petty cash</t>
         </is>
       </c>
-      <c r="E472" s="13" t="inlineStr">
+      <c r="E481" s="16" t="inlineStr">
         <is>
           <t>1. Sama polanya dengan E2E-04, lewat GL Suspense Petty Cash. Top up
 2. Rp 100.000 harus menambah Petty Cash Rp 100.000 — bukan Rp 200.000.</t>
         </is>
       </c>
-      <c r="F472" s="13" t="inlineStr">
+      <c r="F481" s="16" t="inlineStr">
         <is>
           <t>F-FN-03, TSD §6.4</t>
         </is>
       </c>
-      <c r="G472" s="13" t="inlineStr"/>
-      <c r="H472" s="13" t="inlineStr"/>
-      <c r="I472" s="13" t="inlineStr"/>
-    </row>
-    <row r="473">
-      <c r="A473" s="16" t="inlineStr">
+      <c r="G481" s="16" t="inlineStr"/>
+      <c r="H481" s="16" t="inlineStr"/>
+      <c r="I481" s="16" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B473" s="17" t="inlineStr">
+      <c r="B482" s="14" t="inlineStr">
         <is>
           <t>E2E-06</t>
         </is>
       </c>
-      <c r="C473" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D473" s="16" t="inlineStr">
+      <c r="C482" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D482" s="13" t="inlineStr">
         <is>
           <t>Promo bundling dari HP pelanggan</t>
         </is>
       </c>
-      <c r="E473" s="16" t="inlineStr">
+      <c r="E482" s="13" t="inlineStr">
         <is>
           <t>1. Admin buat promo: Nasi Goreng Minimal 2 + Es Teh Minimal 1, potongan 30%
 2. Pelanggan pesan 2 Nasi Goreng saja → tidak ada potongan
@@ -18399,37 +18714,37 @@
 7. Admin hapus promonya → cetak ulang struk tadi → potongannya tetap tertulis</t>
         </is>
       </c>
-      <c r="F473" s="16" t="inlineStr">
+      <c r="F482" s="13" t="inlineStr">
         <is>
           <t>F-DS-10, F-DS-12, F-CU-17, F-DS-08, F-DS-09, A-14</t>
         </is>
       </c>
-      <c r="G473" s="16" t="inlineStr"/>
-      <c r="H473" s="16" t="inlineStr"/>
-      <c r="I473" s="16" t="inlineStr"/>
-    </row>
-    <row r="474">
-      <c r="A474" s="13" t="inlineStr">
+      <c r="G482" s="13" t="inlineStr"/>
+      <c r="H482" s="13" t="inlineStr"/>
+      <c r="I482" s="13" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="16" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B474" s="14" t="inlineStr">
+      <c r="B483" s="17" t="inlineStr">
         <is>
           <t>E2E-07</t>
         </is>
       </c>
-      <c r="C474" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D474" s="13" t="inlineStr">
+      <c r="C483" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D483" s="16" t="inlineStr">
         <is>
           <t>Pembatalan oleh pelanggan</t>
         </is>
       </c>
-      <c r="E474" s="13" t="inlineStr">
+      <c r="E483" s="16" t="inlineStr">
         <is>
           <t>1. Pelanggan pesan, pilih Tunai
 2. Batalkan dari Pesanan Saya → berhasil
@@ -18439,37 +18754,37 @@
 6. Periksa Riwayat Kasir → tidak ikut terhitung</t>
         </is>
       </c>
-      <c r="F474" s="13" t="inlineStr">
+      <c r="F483" s="16" t="inlineStr">
         <is>
           <t>F-CN-01, A-17</t>
         </is>
       </c>
-      <c r="G474" s="13" t="inlineStr"/>
-      <c r="H474" s="13" t="inlineStr"/>
-      <c r="I474" s="13" t="inlineStr"/>
-    </row>
-    <row r="475">
-      <c r="A475" s="16" t="inlineStr">
+      <c r="G483" s="16" t="inlineStr"/>
+      <c r="H483" s="16" t="inlineStr"/>
+      <c r="I483" s="16" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="13" t="inlineStr">
         <is>
           <t>Uji Ujung-ke-Ujung</t>
         </is>
       </c>
-      <c r="B475" s="17" t="inlineStr">
+      <c r="B484" s="14" t="inlineStr">
         <is>
           <t>E2E-08</t>
         </is>
       </c>
-      <c r="C475" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="D475" s="16" t="inlineStr">
+      <c r="C484" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D484" s="13" t="inlineStr">
         <is>
           <t>Isolasi antar cabang</t>
         </is>
       </c>
-      <c r="E475" s="16" t="inlineStr">
+      <c r="E484" s="13" t="inlineStr">
         <is>
           <t>1. Dengan akun Owner yang memiliki dua resto: buat transaksi, promo, dan
 2. pengumuman di resto A, lalu berpindah ke resto B. Tidak satu pun
@@ -18477,19 +18792,19 @@
 4. dan kotak masuk.</t>
         </is>
       </c>
-      <c r="F475" s="16" t="inlineStr">
+      <c r="F484" s="13" t="inlineStr">
         <is>
           <t>F-AD-08, F-IN-10, A-10</t>
         </is>
       </c>
-      <c r="G475" s="16" t="inlineStr"/>
-      <c r="H475" s="16" t="inlineStr"/>
-      <c r="I475" s="16" t="inlineStr"/>
+      <c r="G484" s="13" t="inlineStr"/>
+      <c r="H484" s="13" t="inlineStr"/>
+      <c r="I484" s="13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I475"/>
+  <autoFilter ref="A1:I484"/>
   <dataValidations count="1">
-    <dataValidation sqref="G2:G475" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G2:G484" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Lulus,Gagal,Terblokir,Dilewati"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/TEST-CASE-KAATAGO.xlsx
+++ b/docs/TEST-CASE-KAATAGO.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Cara Lampirkan Capture" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$484</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Kasus Uji'!$A$1:$I$504</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Defect'!$A$4:$V$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -691,23 +691,23 @@
         </is>
       </c>
       <c r="B5" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C484,"P1")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C504,"P1")</f>
         <v/>
       </c>
       <c r="C5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P1",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P1",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P1",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P1",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P1",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P1",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F5" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P1",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P1",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G5" s="5">
@@ -722,23 +722,23 @@
         </is>
       </c>
       <c r="B6" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C484,"P2")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C504,"P2")</f>
         <v/>
       </c>
       <c r="C6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P2",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P2",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P2",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P2",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P2",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P2",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F6" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P2",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P2",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G6" s="5">
@@ -753,23 +753,23 @@
         </is>
       </c>
       <c r="B7" s="5">
-        <f>COUNTIF('Kasus Uji'!C2:C484,"P3")</f>
+        <f>COUNTIF('Kasus Uji'!C2:C504,"P3")</f>
         <v/>
       </c>
       <c r="C7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P3",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P3",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P3",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P3",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P3",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P3",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F7" s="5">
-        <f>COUNTIFS('Kasus Uji'!C2:C484,"P3",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!C2:C504,"P3",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G7" s="5">
@@ -859,23 +859,23 @@
         </is>
       </c>
       <c r="B12" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Pelanggan")</f>
         <v/>
       </c>
       <c r="C12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pelanggan",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pelanggan",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pelanggan",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pelanggan",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pelanggan",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pelanggan",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F12" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pelanggan",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pelanggan",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G12" s="5">
@@ -890,23 +890,23 @@
         </is>
       </c>
       <c r="B13" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Kasir")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Kasir")</f>
         <v/>
       </c>
       <c r="C13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kasir",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Kasir",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kasir",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Kasir",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kasir",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Kasir",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F13" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kasir",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Kasir",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -921,23 +921,23 @@
         </is>
       </c>
       <c r="B14" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Pending Payment")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Pending Payment")</f>
         <v/>
       </c>
       <c r="C14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pending Payment",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pending Payment",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pending Payment",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pending Payment",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pending Payment",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pending Payment",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F14" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pending Payment",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pending Payment",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G14" s="5">
@@ -952,23 +952,23 @@
         </is>
       </c>
       <c r="B15" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Dapur")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Dapur")</f>
         <v/>
       </c>
       <c r="C15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Dapur",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Dapur",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Dapur",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Dapur",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Dapur",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Dapur",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F15" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Dapur",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Dapur",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -983,23 +983,23 @@
         </is>
       </c>
       <c r="B16" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Keuangan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Keuangan")</f>
         <v/>
       </c>
       <c r="C16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Keuangan",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Keuangan",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Keuangan",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Keuangan",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Keuangan",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Keuangan",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F16" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Keuangan",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Keuangan",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G16" s="5">
@@ -1014,23 +1014,23 @@
         </is>
       </c>
       <c r="B17" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Setor Saldo Cash")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Setor Saldo Cash")</f>
         <v/>
       </c>
       <c r="C17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Setor Saldo Cash",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Setor Saldo Cash",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Setor Saldo Cash",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Setor Saldo Cash",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Setor Saldo Cash",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Setor Saldo Cash",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F17" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Setor Saldo Cash",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Setor Saldo Cash",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G17" s="5">
@@ -1045,23 +1045,23 @@
         </is>
       </c>
       <c r="B18" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Katalog &amp; Pengaturan")</f>
         <v/>
       </c>
       <c r="C18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F18" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Katalog &amp; Pengaturan",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G18" s="5">
@@ -1076,23 +1076,23 @@
         </is>
       </c>
       <c r="B19" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"QR Meja")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"QR Meja")</f>
         <v/>
       </c>
       <c r="C19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"QR Meja",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"QR Meja",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"QR Meja",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"QR Meja",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"QR Meja",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"QR Meja",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F19" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"QR Meja",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"QR Meja",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G19" s="5">
@@ -1107,23 +1107,23 @@
         </is>
       </c>
       <c r="B20" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Diskon")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Diskon")</f>
         <v/>
       </c>
       <c r="C20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Diskon",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Diskon",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Diskon",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Diskon",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Diskon",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Diskon",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F20" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Diskon",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Diskon",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G20" s="5">
@@ -1138,23 +1138,23 @@
         </is>
       </c>
       <c r="B21" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Kotak Masuk &amp; Pengumuman")</f>
         <v/>
       </c>
       <c r="C21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F21" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Kotak Masuk &amp; Pengumuman",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G21" s="5">
@@ -1169,23 +1169,23 @@
         </is>
       </c>
       <c r="B22" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Pembayaran QRIS")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Pembayaran QRIS")</f>
         <v/>
       </c>
       <c r="C22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembayaran QRIS",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembayaran QRIS",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembayaran QRIS",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembayaran QRIS",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembayaran QRIS",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembayaran QRIS",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F22" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembayaran QRIS",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembayaran QRIS",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G22" s="5">
@@ -1200,23 +1200,23 @@
         </is>
       </c>
       <c r="B23" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Pembatalan &amp; Kedaluwarsa")</f>
         <v/>
       </c>
       <c r="C23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F23" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembatalan &amp; Kedaluwarsa",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G23" s="5">
@@ -1231,23 +1231,23 @@
         </is>
       </c>
       <c r="B24" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Sesi Meja &amp; Identitas")</f>
         <v/>
       </c>
       <c r="C24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F24" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Sesi Meja &amp; Identitas",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G24" s="5">
@@ -1262,23 +1262,23 @@
         </is>
       </c>
       <c r="B25" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Tampilan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Tampilan")</f>
         <v/>
       </c>
       <c r="C25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Tampilan",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Tampilan",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Tampilan",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Tampilan",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Tampilan",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Tampilan",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F25" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Tampilan",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Tampilan",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G25" s="5">
@@ -1293,23 +1293,23 @@
         </is>
       </c>
       <c r="B26" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Super Admin")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Super Admin")</f>
         <v/>
       </c>
       <c r="C26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Super Admin",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Super Admin",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Super Admin",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Super Admin",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Super Admin",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Super Admin",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F26" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Super Admin",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Super Admin",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G26" s="5">
@@ -1324,23 +1324,23 @@
         </is>
       </c>
       <c r="B27" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Pembaruan Aplikasi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Pembaruan Aplikasi")</f>
         <v/>
       </c>
       <c r="C27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembaruan Aplikasi",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembaruan Aplikasi",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembaruan Aplikasi",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembaruan Aplikasi",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembaruan Aplikasi",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembaruan Aplikasi",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F27" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Pembaruan Aplikasi",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Pembaruan Aplikasi",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G27" s="5">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="B28" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"## 19b. Langganan &amp; Tagihan Resto")</f>
         <v/>
       </c>
       <c r="C28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F28" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19b. Langganan &amp; Tagihan Resto",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G28" s="5">
@@ -1386,23 +1386,23 @@
         </is>
       </c>
       <c r="B29" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"## 19c. Finance KaataGo (Super Admin)")</f>
         <v/>
       </c>
       <c r="C29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F29" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19c. Finance KaataGo (Super Admin)",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G29" s="5">
@@ -1417,23 +1417,23 @@
         </is>
       </c>
       <c r="B30" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"## 19d. Voucher Pelanggan")</f>
         <v/>
       </c>
       <c r="C30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F30" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19d. Voucher Pelanggan",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G30" s="5">
@@ -1448,23 +1448,23 @@
         </is>
       </c>
       <c r="B31" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"## 19e. Analisa Pasar")</f>
         <v/>
       </c>
       <c r="C31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F31" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"## 19e. Analisa Pasar",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G31" s="5">
@@ -1479,23 +1479,23 @@
         </is>
       </c>
       <c r="B32" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Uji Teknis (lingkup TSD)")</f>
         <v/>
       </c>
       <c r="C32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F32" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Uji Teknis (lingkup TSD)",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G32" s="5">
@@ -1510,23 +1510,23 @@
         </is>
       </c>
       <c r="B33" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Regresi — bug yang pernah terjadi")</f>
         <v/>
       </c>
       <c r="C33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F33" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Regresi — bug yang pernah terjadi",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G33" s="5">
@@ -1541,23 +1541,23 @@
         </is>
       </c>
       <c r="B34" s="5">
-        <f>COUNTIF('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung")</f>
+        <f>COUNTIF('Kasus Uji'!A2:A504,"Uji Ujung-ke-Ujung")</f>
         <v/>
       </c>
       <c r="C34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G484,"Lulus")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G504,"Lulus")</f>
         <v/>
       </c>
       <c r="D34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G484,"Gagal")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G504,"Gagal")</f>
         <v/>
       </c>
       <c r="E34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G484,"Terblokir")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G504,"Terblokir")</f>
         <v/>
       </c>
       <c r="F34" s="5">
-        <f>COUNTIFS('Kasus Uji'!A2:A484,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G484,"Dilewati")</f>
+        <f>COUNTIFS('Kasus Uji'!A2:A504,"Uji Ujung-ke-Ujung",'Kasus Uji'!G2:G504,"Dilewati")</f>
         <v/>
       </c>
       <c r="G34" s="5">
@@ -1789,7 +1789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I484"/>
+  <dimension ref="A1:I504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="B340" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-01</t>
+          <t>TC-TB-01</t>
         </is>
       </c>
       <c r="C340" s="15" t="inlineStr">
@@ -13698,17 +13698,17 @@
       </c>
       <c r="D340" s="13" t="inlineStr">
         <is>
-          <t>Owner → Saldo &amp; Pengeluaran → Top Up Saldo</t>
+          <t>Tablet, Kasir: ketuk sebuah menu</t>
         </is>
       </c>
       <c r="E340" s="13" t="inlineStr">
         <is>
-          <t>Tersimpan; Saldo Total naik sebesar nominalnya</t>
+          <t>Popup muncul di kiri; keranjang kanan tetap terbaca penuh</t>
         </is>
       </c>
       <c r="F340" s="13" t="inlineStr">
         <is>
-          <t>F-TU-01, F-TU-02</t>
+          <t>F-TB-02</t>
         </is>
       </c>
       <c r="G340" s="13" t="inlineStr"/>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="B341" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-01b</t>
+          <t>TC-TB-02</t>
         </is>
       </c>
       <c r="C341" s="18" t="inlineStr">
@@ -13733,17 +13733,17 @@
       </c>
       <c r="D341" s="16" t="inlineStr">
         <is>
-          <t>Super Admin top up, periksa Saldo Total KaataGo</t>
+          <t>Tablet, Kasir: ketuk ikon edit pada baris keranjang</t>
         </is>
       </c>
       <c r="E341" s="16" t="inlineStr">
         <is>
-          <t>Naik sebesar nominalnya — bukan tetap</t>
+          <t>Popup editnya juga di kiri</t>
         </is>
       </c>
       <c r="F341" s="16" t="inlineStr">
         <is>
-          <t>F-TU-02, F-TU-05</t>
+          <t>F-TB-02</t>
         </is>
       </c>
       <c r="G341" s="16" t="inlineStr"/>
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B342" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-02</t>
+          <t>TC-TB-03</t>
         </is>
       </c>
       <c r="C342" s="15" t="inlineStr">
@@ -13768,17 +13768,17 @@
       </c>
       <c r="D342" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL sesudahnya</t>
+          <t>Tablet, Pelanggan: buka menu resto</t>
         </is>
       </c>
       <c r="E342" s="13" t="inlineStr">
         <is>
-          <t>Satu baris kredit ke GL Setoran Modal</t>
+          <t>Keranjang tampil sebagai panel kanan</t>
         </is>
       </c>
       <c r="F342" s="13" t="inlineStr">
         <is>
-          <t>F-TU-05</t>
+          <t>F-TB-01</t>
         </is>
       </c>
       <c r="G342" s="13" t="inlineStr"/>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="B343" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-03</t>
+          <t>TC-TB-04</t>
         </is>
       </c>
       <c r="C343" s="18" t="inlineStr">
@@ -13803,17 +13803,17 @@
       </c>
       <c r="D343" s="16" t="inlineStr">
         <is>
-          <t>Periksa Laporan Transaksi / Pemasukan</t>
+          <t>Tablet, Pelanggan: ketuk sebuah menu</t>
         </is>
       </c>
       <c r="E343" s="16" t="inlineStr">
         <is>
-          <t>Setoran tidak muncul sebagai penjualan</t>
+          <t>Popup di kiri, panel keranjang tidak tertutup</t>
         </is>
       </c>
       <c r="F343" s="16" t="inlineStr">
         <is>
-          <t>F-TU-02</t>
+          <t>F-TB-02</t>
         </is>
       </c>
       <c r="G343" s="16" t="inlineStr"/>
@@ -13828,7 +13828,7 @@
       </c>
       <c r="B344" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-04</t>
+          <t>TC-TB-05</t>
         </is>
       </c>
       <c r="C344" s="15" t="inlineStr">
@@ -13838,17 +13838,17 @@
       </c>
       <c r="D344" s="13" t="inlineStr">
         <is>
-          <t>Simpan tanpa mengisi Dari</t>
+          <t>Tablet, Pelanggan: isi meja, pilih voucher, lalu bayar dari panel</t>
         </is>
       </c>
       <c r="E344" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Sebutkan penyetornya"</t>
+          <t>Berjalan sama persis dengan halaman keranjang</t>
         </is>
       </c>
       <c r="F344" s="13" t="inlineStr">
         <is>
-          <t>F-TU-03</t>
+          <t>F-TB-01</t>
         </is>
       </c>
       <c r="G344" s="13" t="inlineStr"/>
@@ -13863,7 +13863,7 @@
       </c>
       <c r="B345" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-05</t>
+          <t>TC-TB-06</t>
         </is>
       </c>
       <c r="C345" s="20" t="inlineStr">
@@ -13873,17 +13873,17 @@
       </c>
       <c r="D345" s="16" t="inlineStr">
         <is>
-          <t>Simpan tanpa bukti</t>
+          <t>Tablet: periksa bagian bawah layar</t>
         </is>
       </c>
       <c r="E345" s="16" t="inlineStr">
         <is>
-          <t>Tetap tersimpan — buktinya opsional</t>
+          <t>Tidak ada bar keranjang</t>
         </is>
       </c>
       <c r="F345" s="16" t="inlineStr">
         <is>
-          <t>F-TU-03</t>
+          <t>F-TB-03</t>
         </is>
       </c>
       <c r="G345" s="16" t="inlineStr"/>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="B346" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-06</t>
+          <t>TC-TB-07</t>
         </is>
       </c>
       <c r="C346" s="15" t="inlineStr">
@@ -13908,17 +13908,17 @@
       </c>
       <c r="D346" s="13" t="inlineStr">
         <is>
-          <t>Masuk sebagai Kasir, buka layar yang sama</t>
+          <t>HP: ketuk sebuah menu</t>
         </is>
       </c>
       <c r="E346" s="13" t="inlineStr">
         <is>
-          <t>Riwayat terlihat, tombol Top Up Saldo tidak ada</t>
+          <t>Popup tetap di tengah; keranjang tetap bar bawah</t>
         </is>
       </c>
       <c r="F346" s="13" t="inlineStr">
         <is>
-          <t>F-TU-04</t>
+          <t>F-TB-04</t>
         </is>
       </c>
       <c r="G346" s="13" t="inlineStr"/>
@@ -13933,27 +13933,27 @@
       </c>
       <c r="B347" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-07</t>
-        </is>
-      </c>
-      <c r="C347" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TB-08</t>
+        </is>
+      </c>
+      <c r="C347" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D347" s="16" t="inlineStr">
         <is>
-          <t>Kasir memanggil insert balance_topups lewat API</t>
+          <t>Putar tablet ke potret sampai di bawah 1000px</t>
         </is>
       </c>
       <c r="E347" s="16" t="inlineStr">
         <is>
-          <t>Ditolak RLS</t>
+          <t>Kembali ke tata letak HP tanpa kehilangan isi keranjang</t>
         </is>
       </c>
       <c r="F347" s="16" t="inlineStr">
         <is>
-          <t>F-TU-04</t>
+          <t>F-TB-04</t>
         </is>
       </c>
       <c r="G347" s="16" t="inlineStr"/>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="B348" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-08</t>
+          <t>TC-TB-09</t>
         </is>
       </c>
       <c r="C348" s="15" t="inlineStr">
@@ -13978,17 +13978,17 @@
       </c>
       <c r="D348" s="13" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Saldo &amp; Pengeluaran → Top Up</t>
+          <t>Tablet melintang: buka checkout dari Kasir dengan 3 item</t>
         </is>
       </c>
       <c r="E348" s="13" t="inlineStr">
         <is>
-          <t>Saldo KaataGo naik; Jurnal GL KaataGo mencatatnya</t>
+          <t>Daftar itemnya terlihat; tidak ada yang terpotong</t>
         </is>
       </c>
       <c r="F348" s="13" t="inlineStr">
         <is>
-          <t>F-TU-01, F-TU-05</t>
+          <t>F-TB-05</t>
         </is>
       </c>
       <c r="G348" s="13" t="inlineStr"/>
@@ -14003,7 +14003,7 @@
       </c>
       <c r="B349" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-09</t>
+          <t>TC-TB-10</t>
         </is>
       </c>
       <c r="C349" s="18" t="inlineStr">
@@ -14013,17 +14013,17 @@
       </c>
       <c r="D349" s="16" t="inlineStr">
         <is>
-          <t>Coba ubah atau hapus baris balance_topups</t>
+          <t>Gulir sampai bawah di halaman itu</t>
         </is>
       </c>
       <c r="E349" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — tidak ada kebijakannya</t>
+          <t>Tombol bayarnya tercapai penuh</t>
         </is>
       </c>
       <c r="F349" s="16" t="inlineStr">
         <is>
-          <t>F-TU-06</t>
+          <t>F-TB-05</t>
         </is>
       </c>
       <c r="G349" s="16" t="inlineStr"/>
@@ -14038,27 +14038,27 @@
       </c>
       <c r="B350" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-10</t>
-        </is>
-      </c>
-      <c r="C350" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TB-11</t>
+        </is>
+      </c>
+      <c r="C350" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D350" s="13" t="inlineStr">
         <is>
-          <t>Periksa kartu Cash / Non Cash sesudah top up</t>
+          <t>Ulangi keduanya dari sisi Pelanggan</t>
         </is>
       </c>
       <c r="E350" s="13" t="inlineStr">
         <is>
-          <t>Non Cash naik; keduanya tetap berjumlah sama dengan Penghasilan</t>
+          <t>Sama — keduanya diperbaiki, bukan salah satunya</t>
         </is>
       </c>
       <c r="F350" s="13" t="inlineStr">
         <is>
-          <t>F-TU-02</t>
+          <t>F-TB-05</t>
         </is>
       </c>
       <c r="G350" s="13" t="inlineStr"/>
@@ -14073,7 +14073,7 @@
       </c>
       <c r="B351" s="17" t="inlineStr">
         <is>
-          <t>TC-TU-11</t>
+          <t>TC-TB-12</t>
         </is>
       </c>
       <c r="C351" s="20" t="inlineStr">
@@ -14083,17 +14083,17 @@
       </c>
       <c r="D351" s="16" t="inlineStr">
         <is>
-          <t>Buka Pemetaan GL sebagai Finance resto</t>
+          <t>Buka menu sebagai Admin lalu Owner</t>
         </is>
       </c>
       <c r="E351" s="16" t="inlineStr">
         <is>
-          <t>Ada bagian GL Modal</t>
+          <t>Sama persis dengan Kasir — satu layar yang sama</t>
         </is>
       </c>
       <c r="F351" s="16" t="inlineStr">
         <is>
-          <t>F-TU-02</t>
+          <t>F-TB-05, F-TB-06</t>
         </is>
       </c>
       <c r="G351" s="16" t="inlineStr"/>
@@ -14108,27 +14108,27 @@
       </c>
       <c r="B352" s="14" t="inlineStr">
         <is>
-          <t>TC-TU-12</t>
-        </is>
-      </c>
-      <c r="C352" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TB-13</t>
+        </is>
+      </c>
+      <c r="C352" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D352" s="13" t="inlineStr">
         <is>
-          <t>Buka halaman awal aplikasi</t>
+          <t>Buka daftar menu</t>
         </is>
       </c>
       <c r="E352" s="13" t="inlineStr">
         <is>
-          <t>Tombolnya bertuliskan KaataGo Merchant</t>
+          <t>Semua kategori sudah terbuka</t>
         </is>
       </c>
       <c r="F352" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>F-TB-06</t>
         </is>
       </c>
       <c r="G352" s="13" t="inlineStr"/>
@@ -14138,32 +14138,32 @@
     <row r="353">
       <c r="A353" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B353" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-01</t>
-        </is>
-      </c>
-      <c r="C353" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TB-14</t>
+        </is>
+      </c>
+      <c r="C353" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D353" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
+          <t>Lipat satu kategori</t>
         </is>
       </c>
       <c r="E353" s="16" t="inlineStr">
         <is>
-          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
+          <t>Tetap bisa dilipat</t>
         </is>
       </c>
       <c r="F353" s="16" t="inlineStr">
         <is>
-          <t>F-VC-01, F-VC-02</t>
+          <t>F-TB-06</t>
         </is>
       </c>
       <c r="G353" s="16" t="inlineStr"/>
@@ -14173,12 +14173,12 @@
     <row r="354">
       <c r="A354" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B354" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-02</t>
+          <t>TC-TB-15</t>
         </is>
       </c>
       <c r="C354" s="15" t="inlineStr">
@@ -14188,17 +14188,17 @@
       </c>
       <c r="D354" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan Rp 1.000.000 jadi 3</t>
+          <t>Tablet: lihat banner promo</t>
         </is>
       </c>
       <c r="E354" s="13" t="inlineStr">
         <is>
-          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
+          <t>Tingginya di bawah 45% layar, tidak mendorong menu keluar</t>
         </is>
       </c>
       <c r="F354" s="13" t="inlineStr">
         <is>
-          <t>F-VC-02</t>
+          <t>F-TB-07</t>
         </is>
       </c>
       <c r="G354" s="13" t="inlineStr"/>
@@ -14208,12 +14208,12 @@
     <row r="355">
       <c r="A355" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B355" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-03</t>
+          <t>TC-TB-16</t>
         </is>
       </c>
       <c r="C355" s="20" t="inlineStr">
@@ -14223,17 +14223,17 @@
       </c>
       <c r="D355" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan dengan kode yang sudah dipakai</t>
+          <t>Pasang banner yang bukan 16:9</t>
         </is>
       </c>
       <c r="E355" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — kodenya sudah ada</t>
+          <t>Kotaknya mengikuti gambar; tidak ada pita kabur di sisinya</t>
         </is>
       </c>
       <c r="F355" s="16" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-TB-07</t>
         </is>
       </c>
       <c r="G355" s="16" t="inlineStr"/>
@@ -14243,32 +14243,32 @@
     <row r="356">
       <c r="A356" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B356" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-04</t>
-        </is>
-      </c>
-      <c r="C356" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TB-17</t>
+        </is>
+      </c>
+      <c r="C356" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D356" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
+          <t>Pasang banner potret ekstrem</t>
         </is>
       </c>
       <c r="E356" s="13" t="inlineStr">
         <is>
-          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
+          <t>Dijepit — tidak mengambil alih halaman menu</t>
         </is>
       </c>
       <c r="F356" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-TB-07</t>
         </is>
       </c>
       <c r="G356" s="13" t="inlineStr"/>
@@ -14278,12 +14278,12 @@
     <row r="357">
       <c r="A357" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B357" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-05</t>
+          <t>TC-TB-18</t>
         </is>
       </c>
       <c r="C357" s="18" t="inlineStr">
@@ -14293,17 +14293,17 @@
       </c>
       <c r="D357" s="16" t="inlineStr">
         <is>
-          <t>Pelanggan menebus kode di Voucher Saya</t>
+          <t>Buka Info Resto lalu gulir</t>
         </is>
       </c>
       <c r="E357" s="16" t="inlineStr">
         <is>
-          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
+          <t>"Nama Resto" tidak terpotong di tepi atas</t>
         </is>
       </c>
       <c r="F357" s="16" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-TB-08</t>
         </is>
       </c>
       <c r="G357" s="16" t="inlineStr"/>
@@ -14313,32 +14313,32 @@
     <row r="358">
       <c r="A358" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B358" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-06</t>
-        </is>
-      </c>
-      <c r="C358" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TB-19</t>
+        </is>
+      </c>
+      <c r="C358" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D358" s="13" t="inlineStr">
         <is>
-          <t>Ketik kodenya dengan huruf kecil</t>
+          <t>Simpan Info Resto</t>
         </is>
       </c>
       <c r="E358" s="13" t="inlineStr">
         <is>
-          <t>Tetap diterima</t>
+          <t>Nama restonya tidak berubah dan tidak kosong</t>
         </is>
       </c>
       <c r="F358" s="13" t="inlineStr">
         <is>
-          <t>F-VC-07</t>
+          <t>F-TB-08</t>
         </is>
       </c>
       <c r="G358" s="13" t="inlineStr"/>
@@ -14348,12 +14348,12 @@
     <row r="359">
       <c r="A359" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B359" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-07</t>
+          <t>TC-TB-20</t>
         </is>
       </c>
       <c r="C359" s="20" t="inlineStr">
@@ -14363,17 +14363,17 @@
       </c>
       <c r="D359" s="16" t="inlineStr">
         <is>
-          <t>Ketik kode yang tidak ada</t>
+          <t>Baca keterangan di bawah nama resto</t>
         </is>
       </c>
       <c r="E359" s="16" t="inlineStr">
         <is>
-          <t>"Kode voucher tidak ditemukan"</t>
+          <t>Menyebut KaataGo Admin dan cara menghubunginya</t>
         </is>
       </c>
       <c r="F359" s="16" t="inlineStr">
         <is>
-          <t>F-VC-10</t>
+          <t>F-TB-08</t>
         </is>
       </c>
       <c r="G359" s="16" t="inlineStr"/>
@@ -14383,12 +14383,12 @@
     <row r="360">
       <c r="A360" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B360" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-08</t>
+          <t>TC-TU-01</t>
         </is>
       </c>
       <c r="C360" s="15" t="inlineStr">
@@ -14398,17 +14398,17 @@
       </c>
       <c r="D360" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
+          <t>Owner → Saldo &amp; Pengeluaran → Top Up Saldo</t>
         </is>
       </c>
       <c r="E360" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
+          <t>Tersimpan; Saldo Total naik sebesar nominalnya</t>
         </is>
       </c>
       <c r="F360" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-TU-01, F-TU-02</t>
         </is>
       </c>
       <c r="G360" s="13" t="inlineStr"/>
@@ -14418,12 +14418,12 @@
     <row r="361">
       <c r="A361" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B361" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-09</t>
+          <t>TC-TU-01b</t>
         </is>
       </c>
       <c r="C361" s="18" t="inlineStr">
@@ -14433,17 +14433,17 @@
       </c>
       <c r="D361" s="16" t="inlineStr">
         <is>
-          <t>Orang yang sama menebus kode itu lagi</t>
+          <t>Super Admin top up, periksa Saldo Total KaataGo</t>
         </is>
       </c>
       <c r="E361" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
+          <t>Naik sebesar nominalnya — bukan tetap</t>
         </is>
       </c>
       <c r="F361" s="16" t="inlineStr">
         <is>
-          <t>F-VC-08, F-VC-10</t>
+          <t>F-TU-02, F-TU-05</t>
         </is>
       </c>
       <c r="G361" s="16" t="inlineStr"/>
@@ -14453,12 +14453,12 @@
     <row r="362">
       <c r="A362" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B362" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-10</t>
+          <t>TC-TU-02</t>
         </is>
       </c>
       <c r="C362" s="15" t="inlineStr">
@@ -14468,17 +14468,17 @@
       </c>
       <c r="D362" s="13" t="inlineStr">
         <is>
-          <t>Batch berisi 10, orang ke-11 menebus</t>
+          <t>Periksa Jurnal GL sesudahnya</t>
         </is>
       </c>
       <c r="E362" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Voucher ini sudah habis"</t>
+          <t>Satu baris kredit ke GL Setoran Modal</t>
         </is>
       </c>
       <c r="F362" s="13" t="inlineStr">
         <is>
-          <t>F-VC-09, F-VC-10</t>
+          <t>F-TU-05</t>
         </is>
       </c>
       <c r="G362" s="13" t="inlineStr"/>
@@ -14488,12 +14488,12 @@
     <row r="363">
       <c r="A363" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B363" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-11</t>
+          <t>TC-TU-03</t>
         </is>
       </c>
       <c r="C363" s="18" t="inlineStr">
@@ -14503,17 +14503,17 @@
       </c>
       <c r="D363" s="16" t="inlineStr">
         <is>
-          <t>Dua orang menebus voucher terakhir bersamaan</t>
+          <t>Periksa Laporan Transaksi / Pemasukan</t>
         </is>
       </c>
       <c r="E363" s="16" t="inlineStr">
         <is>
-          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
+          <t>Setoran tidak muncul sebagai penjualan</t>
         </is>
       </c>
       <c r="F363" s="16" t="inlineStr">
         <is>
-          <t>F-VC-09</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G363" s="16" t="inlineStr"/>
@@ -14523,32 +14523,32 @@
     <row r="364">
       <c r="A364" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B364" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-12</t>
-        </is>
-      </c>
-      <c r="C364" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-TU-04</t>
+        </is>
+      </c>
+      <c r="C364" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D364" s="13" t="inlineStr">
         <is>
-          <t>Tebus voucher dari batch yang sudah ditutup</t>
+          <t>Simpan tanpa mengisi Dari</t>
         </is>
       </c>
       <c r="E364" s="13" t="inlineStr">
         <is>
-          <t>"Voucher ini sudah ditutup"</t>
+          <t>Ditolak — "Sebutkan penyetornya"</t>
         </is>
       </c>
       <c r="F364" s="13" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-TU-03</t>
         </is>
       </c>
       <c r="G364" s="13" t="inlineStr"/>
@@ -14558,12 +14558,12 @@
     <row r="365">
       <c r="A365" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B365" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-13</t>
+          <t>TC-TU-05</t>
         </is>
       </c>
       <c r="C365" s="20" t="inlineStr">
@@ -14573,17 +14573,17 @@
       </c>
       <c r="D365" s="16" t="inlineStr">
         <is>
-          <t>Tebus voucher yang lewat masa berlaku</t>
+          <t>Simpan tanpa bukti</t>
         </is>
       </c>
       <c r="E365" s="16" t="inlineStr">
         <is>
-          <t>"Voucher ini sudah kedaluwarsa"</t>
+          <t>Tetap tersimpan — buktinya opsional</t>
         </is>
       </c>
       <c r="F365" s="16" t="inlineStr">
         <is>
-          <t>F-VC-04, F-VC-10</t>
+          <t>F-TU-03</t>
         </is>
       </c>
       <c r="G365" s="16" t="inlineStr"/>
@@ -14593,12 +14593,12 @@
     <row r="366">
       <c r="A366" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B366" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-14</t>
+          <t>TC-TU-06</t>
         </is>
       </c>
       <c r="C366" s="15" t="inlineStr">
@@ -14608,17 +14608,17 @@
       </c>
       <c r="D366" s="13" t="inlineStr">
         <is>
-          <t>Di keranjang, ketuk baris voucher</t>
+          <t>Masuk sebagai Kasir, buka layar yang sama</t>
         </is>
       </c>
       <c r="E366" s="13" t="inlineStr">
         <is>
-          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
+          <t>Riwayat terlihat, tombol Top Up Saldo tidak ada</t>
         </is>
       </c>
       <c r="F366" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-TU-04</t>
         </is>
       </c>
       <c r="G366" s="13" t="inlineStr"/>
@@ -14628,12 +14628,12 @@
     <row r="367">
       <c r="A367" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B367" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-15</t>
+          <t>TC-TU-07</t>
         </is>
       </c>
       <c r="C367" s="18" t="inlineStr">
@@ -14643,17 +14643,17 @@
       </c>
       <c r="D367" s="16" t="inlineStr">
         <is>
-          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
+          <t>Kasir memanggil insert balance_topups lewat API</t>
         </is>
       </c>
       <c r="E367" s="16" t="inlineStr">
         <is>
-          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
+          <t>Ditolak RLS</t>
         </is>
       </c>
       <c r="F367" s="16" t="inlineStr">
         <is>
-          <t>F-VC-05, F-VC-10</t>
+          <t>F-TU-04</t>
         </is>
       </c>
       <c r="G367" s="16" t="inlineStr"/>
@@ -14663,12 +14663,12 @@
     <row r="368">
       <c r="A368" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B368" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-16</t>
+          <t>TC-TU-08</t>
         </is>
       </c>
       <c r="C368" s="15" t="inlineStr">
@@ -14678,17 +14678,17 @@
       </c>
       <c r="D368" s="13" t="inlineStr">
         <is>
-          <t>Voucher khusus resto A dibuka di resto B</t>
+          <t>Super Admin → Finance → Saldo &amp; Pengeluaran → Top Up</t>
         </is>
       </c>
       <c r="E368" s="13" t="inlineStr">
         <is>
-          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
+          <t>Saldo KaataGo naik; Jurnal GL KaataGo mencatatnya</t>
         </is>
       </c>
       <c r="F368" s="13" t="inlineStr">
         <is>
-          <t>F-VC-06, F-VC-10</t>
+          <t>F-TU-01, F-TU-05</t>
         </is>
       </c>
       <c r="G368" s="13" t="inlineStr"/>
@@ -14698,12 +14698,12 @@
     <row r="369">
       <c r="A369" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B369" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-17</t>
+          <t>TC-TU-09</t>
         </is>
       </c>
       <c r="C369" s="18" t="inlineStr">
@@ -14713,17 +14713,17 @@
       </c>
       <c r="D369" s="16" t="inlineStr">
         <is>
-          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
+          <t>Coba ubah atau hapus baris balance_topups</t>
         </is>
       </c>
       <c r="E369" s="16" t="inlineStr">
         <is>
-          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
+          <t>Ditolak — tidak ada kebijakannya</t>
         </is>
       </c>
       <c r="F369" s="16" t="inlineStr">
         <is>
-          <t>F-VC-12</t>
+          <t>F-TU-06</t>
         </is>
       </c>
       <c r="G369" s="16" t="inlineStr"/>
@@ -14733,32 +14733,32 @@
     <row r="370">
       <c r="A370" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B370" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-18</t>
-        </is>
-      </c>
-      <c r="C370" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-10</t>
+        </is>
+      </c>
+      <c r="C370" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D370" s="13" t="inlineStr">
         <is>
-          <t>Pasang voucher lalu selesaikan pesanan</t>
+          <t>Periksa kartu Cash / Non Cash sesudah top up</t>
         </is>
       </c>
       <c r="E370" s="13" t="inlineStr">
         <is>
-          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
+          <t>Non Cash naik; keduanya tetap berjumlah sama dengan Penghasilan</t>
         </is>
       </c>
       <c r="F370" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G370" s="13" t="inlineStr"/>
@@ -14768,32 +14768,32 @@
     <row r="371">
       <c r="A371" s="16" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B371" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-19</t>
-        </is>
-      </c>
-      <c r="C371" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-11</t>
+        </is>
+      </c>
+      <c r="C371" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D371" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Lepas setelah voucher terpasang</t>
+          <t>Buka Pemetaan GL sebagai Finance resto</t>
         </is>
       </c>
       <c r="E371" s="16" t="inlineStr">
         <is>
-          <t>Tagihan kembali ke nominal semula</t>
+          <t>Ada bagian GL Modal</t>
         </is>
       </c>
       <c r="F371" s="16" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-TU-02</t>
         </is>
       </c>
       <c r="G371" s="16" t="inlineStr"/>
@@ -14803,32 +14803,32 @@
     <row r="372">
       <c r="A372" s="13" t="inlineStr">
         <is>
-          <t>## 19d. Voucher Pelanggan</t>
+          <t>## 19c. Finance KaataGo (Super Admin)</t>
         </is>
       </c>
       <c r="B372" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-20</t>
-        </is>
-      </c>
-      <c r="C372" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-TU-12</t>
+        </is>
+      </c>
+      <c r="C372" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D372" s="13" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
+          <t>Buka halaman awal aplikasi</t>
         </is>
       </c>
       <c r="E372" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
+          <t>Tombolnya bertuliskan KaataGo Merchant</t>
         </is>
       </c>
       <c r="F372" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G372" s="13" t="inlineStr"/>
@@ -14843,7 +14843,7 @@
       </c>
       <c r="B373" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-21</t>
+          <t>TC-VC-01</t>
         </is>
       </c>
       <c r="C373" s="18" t="inlineStr">
@@ -14853,17 +14853,17 @@
       </c>
       <c r="D373" s="16" t="inlineStr">
         <is>
-          <t>Periksa Jurnal GL restonya</t>
+          <t>Super Admin → Voucher → terbitkan Rp 1.000.000 jadi 10</t>
         </is>
       </c>
       <c r="E373" s="16" t="inlineStr">
         <is>
-          <t>Ada baris masuk sebesar nilai vouchernya</t>
+          <t>10 voucher @Rp 100.000; nominalnya tampil hidup di formulir</t>
         </is>
       </c>
       <c r="F373" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-01, F-VC-02</t>
         </is>
       </c>
       <c r="G373" s="16" t="inlineStr"/>
@@ -14878,27 +14878,27 @@
       </c>
       <c r="B374" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-22</t>
-        </is>
-      </c>
-      <c r="C374" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-02</t>
+        </is>
+      </c>
+      <c r="C374" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D374" s="13" t="inlineStr">
         <is>
-          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
+          <t>Terbitkan Rp 1.000.000 jadi 3</t>
         </is>
       </c>
       <c r="E374" s="13" t="inlineStr">
         <is>
-          <t>Tidak muncul di daftar pilihan</t>
+          <t>@Rp 333.333, sisa Rp 1 disebutkan dan tidak ikut dijurnal</t>
         </is>
       </c>
       <c r="F374" s="13" t="inlineStr">
         <is>
-          <t>F-VC-11</t>
+          <t>F-VC-02</t>
         </is>
       </c>
       <c r="G374" s="13" t="inlineStr"/>
@@ -14913,27 +14913,27 @@
       </c>
       <c r="B375" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-23</t>
-        </is>
-      </c>
-      <c r="C375" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-03</t>
+        </is>
+      </c>
+      <c r="C375" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D375" s="16" t="inlineStr">
         <is>
-          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
+          <t>Terbitkan dengan kode yang sudah dipakai</t>
         </is>
       </c>
       <c r="E375" s="16" t="inlineStr">
         <is>
-          <t>Debit Voucher Redeem, kredit Total Saldo</t>
+          <t>Ditolak — kodenya sudah ada</t>
         </is>
       </c>
       <c r="F375" s="16" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G375" s="16" t="inlineStr"/>
@@ -14948,7 +14948,7 @@
       </c>
       <c r="B376" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-24</t>
+          <t>TC-VC-04</t>
         </is>
       </c>
       <c r="C376" s="15" t="inlineStr">
@@ -14958,17 +14958,17 @@
       </c>
       <c r="D376" s="13" t="inlineStr">
         <is>
-          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
+          <t>Periksa Jurnal GL KaataGo sesudah terbit</t>
         </is>
       </c>
       <c r="E376" s="13" t="inlineStr">
         <is>
-          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
+          <t>Debit Total Saldo 1100040, kredit Voucher 1100073</t>
         </is>
       </c>
       <c r="F376" s="13" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G376" s="13" t="inlineStr"/>
@@ -14983,7 +14983,7 @@
       </c>
       <c r="B377" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-25</t>
+          <t>TC-VC-05</t>
         </is>
       </c>
       <c r="C377" s="18" t="inlineStr">
@@ -14993,17 +14993,17 @@
       </c>
       <c r="D377" s="16" t="inlineStr">
         <is>
-          <t>Jalankan expire_vouchers() dua kali</t>
+          <t>Pelanggan menebus kode di Voucher Saya</t>
         </is>
       </c>
       <c r="E377" s="16" t="inlineStr">
         <is>
-          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
+          <t>Berhasil; voucher masuk daftar "Siap Dipakai"</t>
         </is>
       </c>
       <c r="F377" s="16" t="inlineStr">
         <is>
-          <t>F-VC-14</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G377" s="16" t="inlineStr"/>
@@ -15018,27 +15018,27 @@
       </c>
       <c r="B378" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-26</t>
-        </is>
-      </c>
-      <c r="C378" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-06</t>
+        </is>
+      </c>
+      <c r="C378" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D378" s="13" t="inlineStr">
         <is>
-          <t>Jumlahkan keempat tahap untuk satu batch</t>
+          <t>Ketik kodenya dengan huruf kecil</t>
         </is>
       </c>
       <c r="E378" s="13" t="inlineStr">
         <is>
-          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
+          <t>Tetap diterima</t>
         </is>
       </c>
       <c r="F378" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13, F-VC-14</t>
+          <t>F-VC-07</t>
         </is>
       </c>
       <c r="G378" s="13" t="inlineStr"/>
@@ -15053,27 +15053,27 @@
       </c>
       <c r="B379" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-27</t>
-        </is>
-      </c>
-      <c r="C379" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-07</t>
+        </is>
+      </c>
+      <c r="C379" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D379" s="16" t="inlineStr">
         <is>
-          <t>Tulis langsung ke voucher_claims lewat API</t>
+          <t>Ketik kode yang tidak ada</t>
         </is>
       </c>
       <c r="E379" s="16" t="inlineStr">
         <is>
-          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
+          <t>"Kode voucher tidak ditemukan"</t>
         </is>
       </c>
       <c r="F379" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-10</t>
         </is>
       </c>
       <c r="G379" s="16" t="inlineStr"/>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="B380" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-28</t>
+          <t>TC-VC-08</t>
         </is>
       </c>
       <c r="C380" s="15" t="inlineStr">
@@ -15098,17 +15098,17 @@
       </c>
       <c r="D380" s="13" t="inlineStr">
         <is>
-          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
+          <t>Periksa Jurnal GL KaataGo sesudah ditebus</t>
         </is>
       </c>
       <c r="E380" s="13" t="inlineStr">
         <is>
-          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
+          <t>Debit Voucher, kredit Voucher Redeem 1100074</t>
         </is>
       </c>
       <c r="F380" s="13" t="inlineStr">
         <is>
-          <t>F-VC-01</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G380" s="13" t="inlineStr"/>
@@ -15123,27 +15123,27 @@
       </c>
       <c r="B381" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-29</t>
-        </is>
-      </c>
-      <c r="C381" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-09</t>
+        </is>
+      </c>
+      <c r="C381" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D381" s="16" t="inlineStr">
         <is>
-          <t>Periksa kartu batch di layar Super Admin</t>
+          <t>Orang yang sama menebus kode itu lagi</t>
         </is>
       </c>
       <c r="E381" s="16" t="inlineStr">
         <is>
-          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
+          <t>Ditolak — "Voucher ini sudah kamu tebus"</t>
         </is>
       </c>
       <c r="F381" s="16" t="inlineStr">
         <is>
-          <t>F-VC-15</t>
+          <t>F-VC-08, F-VC-10</t>
         </is>
       </c>
       <c r="G381" s="16" t="inlineStr"/>
@@ -15158,27 +15158,27 @@
       </c>
       <c r="B382" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-30</t>
-        </is>
-      </c>
-      <c r="C382" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-10</t>
+        </is>
+      </c>
+      <c r="C382" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D382" s="13" t="inlineStr">
         <is>
-          <t>Tutup sebuah batch yang kuotanya masih ada</t>
+          <t>Batch berisi 10, orang ke-11 menebus</t>
         </is>
       </c>
       <c r="E382" s="13" t="inlineStr">
         <is>
-          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
+          <t>Ditolak — "Voucher ini sudah habis"</t>
         </is>
       </c>
       <c r="F382" s="13" t="inlineStr">
         <is>
-          <t>F-VC-04</t>
+          <t>F-VC-09, F-VC-10</t>
         </is>
       </c>
       <c r="G382" s="13" t="inlineStr"/>
@@ -15193,7 +15193,7 @@
       </c>
       <c r="B383" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-31</t>
+          <t>TC-VC-11</t>
         </is>
       </c>
       <c r="C383" s="18" t="inlineStr">
@@ -15203,17 +15203,17 @@
       </c>
       <c r="D383" s="16" t="inlineStr">
         <is>
-          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
+          <t>Dua orang menebus voucher terakhir bersamaan</t>
         </is>
       </c>
       <c r="E383" s="16" t="inlineStr">
         <is>
-          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
+          <t>Hanya satu lolos; yang lain ditolak kuota habis</t>
         </is>
       </c>
       <c r="F383" s="16" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-09</t>
         </is>
       </c>
       <c r="G383" s="16" t="inlineStr"/>
@@ -15228,27 +15228,27 @@
       </c>
       <c r="B384" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-32</t>
-        </is>
-      </c>
-      <c r="C384" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-12</t>
+        </is>
+      </c>
+      <c r="C384" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D384" s="13" t="inlineStr">
         <is>
-          <t>Jalankan settle-voucher-payouts</t>
+          <t>Tebus voucher dari batch yang sudah ditutup</t>
         </is>
       </c>
       <c r="E384" s="13" t="inlineStr">
         <is>
-          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
+          <t>"Voucher ini sudah ditutup"</t>
         </is>
       </c>
       <c r="F384" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G384" s="13" t="inlineStr"/>
@@ -15263,27 +15263,27 @@
       </c>
       <c r="B385" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-33</t>
-        </is>
-      </c>
-      <c r="C385" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-13</t>
+        </is>
+      </c>
+      <c r="C385" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D385" s="16" t="inlineStr">
         <is>
-          <t>Jalankan fungsinya dua kali berturut-turut</t>
+          <t>Tebus voucher yang lewat masa berlaku</t>
         </is>
       </c>
       <c r="E385" s="16" t="inlineStr">
         <is>
-          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
+          <t>"Voucher ini sudah kedaluwarsa"</t>
         </is>
       </c>
       <c r="F385" s="16" t="inlineStr">
         <is>
-          <t>F-VC-18</t>
+          <t>F-VC-04, F-VC-10</t>
         </is>
       </c>
       <c r="G385" s="16" t="inlineStr"/>
@@ -15298,7 +15298,7 @@
       </c>
       <c r="B386" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-34</t>
+          <t>TC-VC-14</t>
         </is>
       </c>
       <c r="C386" s="15" t="inlineStr">
@@ -15308,17 +15308,17 @@
       </c>
       <c r="D386" s="13" t="inlineStr">
         <is>
-          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
+          <t>Di keranjang, ketuk baris voucher</t>
         </is>
       </c>
       <c r="E386" s="13" t="inlineStr">
         <is>
-          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
+          <t>Muncul pilihan voucher miliknya, bukan kolom ketik kode</t>
         </is>
       </c>
       <c r="F386" s="13" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G386" s="13" t="inlineStr"/>
@@ -15333,7 +15333,7 @@
       </c>
       <c r="B387" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-35</t>
+          <t>TC-VC-15</t>
         </is>
       </c>
       <c r="C387" s="18" t="inlineStr">
@@ -15343,17 +15343,17 @@
       </c>
       <c r="D387" s="16" t="inlineStr">
         <is>
-          <t>Perbaiki kuncinya lalu jalankan lagi</t>
+          <t>Voucher min belanja Rp 50.000, tagihan Rp 30.000</t>
         </is>
       </c>
       <c r="E387" s="16" t="inlineStr">
         <is>
-          <t>Baris yang tadi gagal terkirim</t>
+          <t>Tidak bisa dipilih, disertai "Belanja belum mencapai minimum"</t>
         </is>
       </c>
       <c r="F387" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-05, F-VC-10</t>
         </is>
       </c>
       <c r="G387" s="16" t="inlineStr"/>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="B388" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-36</t>
+          <t>TC-VC-16</t>
         </is>
       </c>
       <c r="C388" s="15" t="inlineStr">
@@ -15378,17 +15378,17 @@
       </c>
       <c r="D388" s="13" t="inlineStr">
         <is>
-          <t>Pakai voucher di resto yang belum punya sub-akun</t>
+          <t>Voucher khusus resto A dibuka di resto B</t>
         </is>
       </c>
       <c r="E388" s="13" t="inlineStr">
         <is>
-          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
+          <t>Tidak bisa dipilih — "Tidak berlaku di resto ini"</t>
         </is>
       </c>
       <c r="F388" s="13" t="inlineStr">
         <is>
-          <t>F-VC-19</t>
+          <t>F-VC-06, F-VC-10</t>
         </is>
       </c>
       <c r="G388" s="13" t="inlineStr"/>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="B389" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-37</t>
+          <t>TC-VC-17</t>
         </is>
       </c>
       <c r="C389" s="18" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="D389" s="16" t="inlineStr">
         <is>
-          <t>Buat pesanan bervoucher saat Xendit mati total</t>
+          <t>Voucher Rp 100.000 pada tagihan Rp 60.000</t>
         </is>
       </c>
       <c r="E389" s="16" t="inlineStr">
         <is>
-          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
+          <t>Yang dibayar Rp 0; sisa Rp 40.000 tidak dikembalikan</t>
         </is>
       </c>
       <c r="F389" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-12</t>
         </is>
       </c>
       <c r="G389" s="16" t="inlineStr"/>
@@ -15438,27 +15438,27 @@
       </c>
       <c r="B390" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-38</t>
-        </is>
-      </c>
-      <c r="C390" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-18</t>
+        </is>
+      </c>
+      <c r="C390" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D390" s="13" t="inlineStr">
         <is>
-          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
+          <t>Pasang voucher lalu selesaikan pesanan</t>
         </is>
       </c>
       <c r="E390" s="13" t="inlineStr">
         <is>
-          <t>Klaim used lama ikut terantre</t>
+          <t>Yang dibayar sudah dipotong; nominal QRIS-nya juga</t>
         </is>
       </c>
       <c r="F390" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G390" s="13" t="inlineStr"/>
@@ -15473,7 +15473,7 @@
       </c>
       <c r="B391" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-39</t>
+          <t>TC-VC-19</t>
         </is>
       </c>
       <c r="C391" s="18" t="inlineStr">
@@ -15483,17 +15483,17 @@
       </c>
       <c r="D391" s="16" t="inlineStr">
         <is>
-          <t>Tulis langsung ke voucher_payouts lewat API</t>
+          <t>Ketuk Lepas setelah voucher terpasang</t>
         </is>
       </c>
       <c r="E391" s="16" t="inlineStr">
         <is>
-          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
+          <t>Tagihan kembali ke nominal semula</t>
         </is>
       </c>
       <c r="F391" s="16" t="inlineStr">
         <is>
-          <t>F-VC-18</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G391" s="16" t="inlineStr"/>
@@ -15508,27 +15508,27 @@
       </c>
       <c r="B392" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-40</t>
-        </is>
-      </c>
-      <c r="C392" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-20</t>
+        </is>
+      </c>
+      <c r="C392" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D392" s="13" t="inlineStr">
         <is>
-          <t>Baca voucher_payout_config sebagai Super Admin</t>
+          <t>Periksa Jurnal GL KaataGo sesudah dipakai</t>
         </is>
       </c>
       <c r="E392" s="13" t="inlineStr">
         <is>
-          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
+          <t>Debit Voucher Redeem, kredit GL Transfer restonya</t>
         </is>
       </c>
       <c r="F392" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G392" s="13" t="inlineStr"/>
@@ -15543,27 +15543,27 @@
       </c>
       <c r="B393" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-41</t>
-        </is>
-      </c>
-      <c r="C393" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-21</t>
+        </is>
+      </c>
+      <c r="C393" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D393" s="16" t="inlineStr">
         <is>
-          <t>Jalankan penjadwal sebelum function_url diisi</t>
+          <t>Periksa Jurnal GL restonya</t>
         </is>
       </c>
       <c r="E393" s="16" t="inlineStr">
         <is>
-          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
+          <t>Ada baris masuk sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F393" s="16" t="inlineStr">
         <is>
-          <t>F-VC-17</t>
+          <t>F-VC-13</t>
         </is>
       </c>
       <c r="G393" s="16" t="inlineStr"/>
@@ -15578,27 +15578,27 @@
       </c>
       <c r="B394" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-42</t>
-        </is>
-      </c>
-      <c r="C394" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-22</t>
+        </is>
+      </c>
+      <c r="C394" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D394" s="13" t="inlineStr">
         <is>
-          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
+          <t>Voucher yang sudah dipakai dibuka lagi di keranjang</t>
         </is>
       </c>
       <c r="E394" s="13" t="inlineStr">
         <is>
-          <t>Cocok baris per baris lewat transfer_id</t>
+          <t>Tidak muncul di daftar pilihan</t>
         </is>
       </c>
       <c r="F394" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16</t>
+          <t>F-VC-11</t>
         </is>
       </c>
       <c r="G394" s="13" t="inlineStr"/>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="B395" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-43</t>
+          <t>TC-VC-23</t>
         </is>
       </c>
       <c r="C395" s="18" t="inlineStr">
@@ -15623,17 +15623,17 @@
       </c>
       <c r="D395" s="16" t="inlineStr">
         <is>
-          <t>Jalankan pencairan saat xenPlatform belum aktif</t>
+          <t>Jalankan expire_vouchers() — ada klaim tak terpakai</t>
         </is>
       </c>
       <c r="E395" s="16" t="inlineStr">
         <is>
-          <t>Seluruh antrean tetap pending, attempts nol, tidak ada galat</t>
+          <t>Debit Voucher Redeem, kredit Total Saldo</t>
         </is>
       </c>
       <c r="F395" s="16" t="inlineStr">
         <is>
-          <t>F-VC-19</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G395" s="16" t="inlineStr"/>
@@ -15648,27 +15648,27 @@
       </c>
       <c r="B396" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-44</t>
-        </is>
-      </c>
-      <c r="C396" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-24</t>
+        </is>
+      </c>
+      <c r="C396" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D396" s="13" t="inlineStr">
         <is>
-          <t>Aktifkan xenPlatform + pasang sub-akun, lalu tunggu penjadwal</t>
+          <t>Batch kedaluwarsa dengan sisa kuota tak tertebus</t>
         </is>
       </c>
       <c r="E396" s="13" t="inlineStr">
         <is>
-          <t>Tunggakan lama ikut terangkut tanpa dijalankan ulang manual</t>
+          <t>Debit Voucher, kredit Total Saldo sebesar sisanya</t>
         </is>
       </c>
       <c r="F396" s="13" t="inlineStr">
         <is>
-          <t>F-VC-16, F-VC-17</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G396" s="13" t="inlineStr"/>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="B397" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-45</t>
+          <t>TC-VC-25</t>
         </is>
       </c>
       <c r="C397" s="18" t="inlineStr">
@@ -15693,17 +15693,17 @@
       </c>
       <c r="D397" s="16" t="inlineStr">
         <is>
-          <t>Super Admin → Finance → Pemetaan GL</t>
+          <t>Jalankan expire_vouchers() dua kali</t>
         </is>
       </c>
       <c r="E397" s="16" t="inlineStr">
         <is>
-          <t>Ada bagian GL Voucher berisi GL Voucher dan GL Voucher Redeem</t>
+          <t>Pengembaliannya sekali saja — dijaga settled_at</t>
         </is>
       </c>
       <c r="F397" s="16" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-14</t>
         </is>
       </c>
       <c r="G397" s="16" t="inlineStr"/>
@@ -15718,7 +15718,7 @@
       </c>
       <c r="B398" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-46</t>
+          <t>TC-VC-26</t>
         </is>
       </c>
       <c r="C398" s="15" t="inlineStr">
@@ -15728,17 +15728,17 @@
       </c>
       <c r="D398" s="13" t="inlineStr">
         <is>
-          <t>Buka Pemetaan GL sebagai Finance resto biasa</t>
+          <t>Jumlahkan keempat tahap untuk satu batch</t>
         </is>
       </c>
       <c r="E398" s="13" t="inlineStr">
         <is>
-          <t>Bagian GL Voucher tidak muncul, penanda "belum dipetakan" tidak berbunyi</t>
+          <t>Debit dan kreditnya seimbang; tidak ada dana yang hilang</t>
         </is>
       </c>
       <c r="F398" s="13" t="inlineStr">
         <is>
-          <t>F-VC-13</t>
+          <t>F-VC-13, F-VC-14</t>
         </is>
       </c>
       <c r="G398" s="13" t="inlineStr"/>
@@ -15753,22 +15753,22 @@
       </c>
       <c r="B399" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-47</t>
-        </is>
-      </c>
-      <c r="C399" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-27</t>
+        </is>
+      </c>
+      <c r="C399" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D399" s="16" t="inlineStr">
         <is>
-          <t>Ubah nomor GL Voucher lalu simpan</t>
+          <t>Tulis langsung ke voucher_claims lewat API</t>
         </is>
       </c>
       <c r="E399" s="16" t="inlineStr">
         <is>
-          <t>Tersimpan, dan jurnal voucher berikutnya memakai nomor baru</t>
+          <t>Ditolak RLS — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F399" s="16" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="B400" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-48</t>
+          <t>TC-VC-28</t>
         </is>
       </c>
       <c r="C400" s="15" t="inlineStr">
@@ -15798,17 +15798,17 @@
       </c>
       <c r="D400" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan batch, lalu buka Kotak Masuk pelanggan</t>
+          <t>Panggil generate_voucher_batch sebagai bukan Super Admin</t>
         </is>
       </c>
       <c r="E400" s="13" t="inlineStr">
         <is>
-          <t>Ada kabar di tab Umum berisi kode, nilai, kuota, dan tenggat</t>
+          <t>Ditolak — "Hanya Super Admin yang dapat menerbitkan voucher"</t>
         </is>
       </c>
       <c r="F400" s="13" t="inlineStr">
         <is>
-          <t>F-VC-20, F-VC-21</t>
+          <t>F-VC-01</t>
         </is>
       </c>
       <c r="G400" s="13" t="inlineStr"/>
@@ -15823,27 +15823,27 @@
       </c>
       <c r="B401" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-49</t>
-        </is>
-      </c>
-      <c r="C401" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-29</t>
+        </is>
+      </c>
+      <c r="C401" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D401" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch dengan HP pelanggan terkunci</t>
+          <t>Periksa kartu batch di layar Super Admin</t>
         </is>
       </c>
       <c r="E401" s="16" t="inlineStr">
         <is>
-          <t>Push muncul di layar kunci</t>
+          <t>Sisa kuota dan nilai menggantung cocok dengan penebusnya</t>
         </is>
       </c>
       <c r="F401" s="16" t="inlineStr">
         <is>
-          <t>F-VC-20</t>
+          <t>F-VC-15</t>
         </is>
       </c>
       <c r="G401" s="16" t="inlineStr"/>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="B402" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-50</t>
+          <t>TC-VC-30</t>
         </is>
       </c>
       <c r="C402" s="19" t="inlineStr">
@@ -15868,17 +15868,17 @@
       </c>
       <c r="D402" s="13" t="inlineStr">
         <is>
-          <t>Terbitkan batch tanpa minimal belanja</t>
+          <t>Tutup sebuah batch yang kuotanya masih ada</t>
         </is>
       </c>
       <c r="E402" s="13" t="inlineStr">
         <is>
-          <t>Kalimat minimal belanja tidak muncul di pengumuman</t>
+          <t>Tidak bisa ditebus lagi; yang sudah ditebus tetap bisa dipakai</t>
         </is>
       </c>
       <c r="F402" s="13" t="inlineStr">
         <is>
-          <t>F-VC-21</t>
+          <t>F-VC-04</t>
         </is>
       </c>
       <c r="G402" s="13" t="inlineStr"/>
@@ -15893,27 +15893,27 @@
       </c>
       <c r="B403" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-51</t>
-        </is>
-      </c>
-      <c r="C403" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-31</t>
+        </is>
+      </c>
+      <c r="C403" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D403" s="16" t="inlineStr">
         <is>
-          <t>Buka Kotak Masuk sebagai pegawai resto</t>
+          <t>Pakai voucher, lalu periksa tabel voucher_payouts</t>
         </is>
       </c>
       <c r="E403" s="16" t="inlineStr">
         <is>
-          <t>Kabar voucher tidak muncul — audiensnya pelanggan</t>
+          <t>Muncul satu baris pending sebesar nilai vouchernya</t>
         </is>
       </c>
       <c r="F403" s="16" t="inlineStr">
         <is>
-          <t>F-VC-20</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G403" s="16" t="inlineStr"/>
@@ -15928,27 +15928,27 @@
       </c>
       <c r="B404" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-52</t>
-        </is>
-      </c>
-      <c r="C404" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-32</t>
+        </is>
+      </c>
+      <c r="C404" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D404" s="13" t="inlineStr">
         <is>
-          <t>Ketik nama resto di kolom cari pada form terbit</t>
+          <t>Jalankan settle-voucher-payouts</t>
         </is>
       </c>
       <c r="E404" s="13" t="inlineStr">
         <is>
-          <t>Daftarnya menyusut sesuai kata kuncinya</t>
+          <t>Status jadi sent, transfer_id terisi, saldo sub-akun resto bertambah</t>
         </is>
       </c>
       <c r="F404" s="13" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G404" s="13" t="inlineStr"/>
@@ -15963,7 +15963,7 @@
       </c>
       <c r="B405" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-53</t>
+          <t>TC-VC-33</t>
         </is>
       </c>
       <c r="C405" s="18" t="inlineStr">
@@ -15973,17 +15973,17 @@
       </c>
       <c r="D405" s="16" t="inlineStr">
         <is>
-          <t>Centang 3 resto, lalu cari kata yang menyaringnya keluar</t>
+          <t>Jalankan fungsinya dua kali berturut-turut</t>
         </is>
       </c>
       <c r="E405" s="16" t="inlineStr">
         <is>
-          <t>Ketiganya tetap terpilih; hitungannya tidak berubah</t>
+          <t>Uangnya berpindah sekali; yang kedua duplikat dan tetap sent</t>
         </is>
       </c>
       <c r="F405" s="16" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G405" s="16" t="inlineStr"/>
@@ -15998,7 +15998,7 @@
       </c>
       <c r="B406" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-54</t>
+          <t>TC-VC-34</t>
         </is>
       </c>
       <c r="C406" s="15" t="inlineStr">
@@ -16008,17 +16008,17 @@
       </c>
       <c r="D406" s="13" t="inlineStr">
         <is>
-          <t>Saring daftarnya, lalu ketuk Pilih semua</t>
+          <t>Matikan Xendit (kunci salah), lalu jalankan</t>
         </is>
       </c>
       <c r="E406" s="13" t="inlineStr">
         <is>
-          <t>Hanya yang tampil tercentang, bukan seluruh resto</t>
+          <t>Status failed, last_error menyebut sebabnya, attempts naik</t>
         </is>
       </c>
       <c r="F406" s="13" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G406" s="13" t="inlineStr"/>
@@ -16033,27 +16033,27 @@
       </c>
       <c r="B407" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-55</t>
-        </is>
-      </c>
-      <c r="C407" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-35</t>
+        </is>
+      </c>
+      <c r="C407" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D407" s="16" t="inlineStr">
         <is>
-          <t>Ketuk Lepas semua saat semua yang tampil tercentang</t>
+          <t>Perbaiki kuncinya lalu jalankan lagi</t>
         </is>
       </c>
       <c r="E407" s="16" t="inlineStr">
         <is>
-          <t>Yang tampil terlepas; pilihan di luar saringan tetap</t>
+          <t>Baris yang tadi gagal terkirim</t>
         </is>
       </c>
       <c r="F407" s="16" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G407" s="16" t="inlineStr"/>
@@ -16068,27 +16068,27 @@
       </c>
       <c r="B408" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-56</t>
-        </is>
-      </c>
-      <c r="C408" s="19" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-36</t>
+        </is>
+      </c>
+      <c r="C408" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D408" s="13" t="inlineStr">
         <is>
-          <t>Cari nama resto yang tidak ada</t>
+          <t>Pakai voucher di resto yang belum punya sub-akun</t>
         </is>
       </c>
       <c r="E408" s="13" t="inlineStr">
         <is>
-          <t>Muncul "Tidak ada resto bernama itu"</t>
+          <t>Tetap pending, attempts tidak naik, tidak hilang</t>
         </is>
       </c>
       <c r="F408" s="13" t="inlineStr">
         <is>
-          <t>F-VC-22</t>
+          <t>F-VC-19</t>
         </is>
       </c>
       <c r="G408" s="13" t="inlineStr"/>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="B409" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-57</t>
+          <t>TC-VC-37</t>
         </is>
       </c>
       <c r="C409" s="18" t="inlineStr">
@@ -16113,17 +16113,17 @@
       </c>
       <c r="D409" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch berbanner, lalu buka Kotak Masuk pelanggan</t>
+          <t>Buat pesanan bervoucher saat Xendit mati total</t>
         </is>
       </c>
       <c r="E409" s="16" t="inlineStr">
         <is>
-          <t>Gambarnya tampil bersama kabarnya</t>
+          <t>Pesanannya tetap tersimpan dan masuk dapur</t>
         </is>
       </c>
       <c r="F409" s="16" t="inlineStr">
         <is>
-          <t>F-VC-23</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G409" s="16" t="inlineStr"/>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="B410" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-58</t>
+          <t>TC-VC-38</t>
         </is>
       </c>
       <c r="C410" s="19" t="inlineStr">
@@ -16148,17 +16148,17 @@
       </c>
       <c r="D410" s="13" t="inlineStr">
         <is>
-          <t>Pilih gambar potret, lihat pratinjaunya</t>
+          <t>Jalankan voucher_payouts.sql di basis data yang sudah ada pemakaian</t>
         </is>
       </c>
       <c r="E410" s="13" t="inlineStr">
         <is>
-          <t>Dipotong 16:9, sama dengan yang nanti muncul di kotak masuk</t>
+          <t>Klaim used lama ikut terantre</t>
         </is>
       </c>
       <c r="F410" s="13" t="inlineStr">
         <is>
-          <t>F-VC-23</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G410" s="13" t="inlineStr"/>
@@ -16173,27 +16173,27 @@
       </c>
       <c r="B411" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-59</t>
-        </is>
-      </c>
-      <c r="C411" s="20" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TC-VC-39</t>
+        </is>
+      </c>
+      <c r="C411" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D411" s="16" t="inlineStr">
         <is>
-          <t>Terbitkan batch tanpa banner</t>
+          <t>Tulis langsung ke voucher_payouts lewat API</t>
         </is>
       </c>
       <c r="E411" s="16" t="inlineStr">
         <is>
-          <t>Kabarnya tetap terkirim, tanpa gambar</t>
+          <t>Ditolak — tidak ada kebijakan tulis untuk siapa pun</t>
         </is>
       </c>
       <c r="F411" s="16" t="inlineStr">
         <is>
-          <t>F-VC-23</t>
+          <t>F-VC-18</t>
         </is>
       </c>
       <c r="G411" s="16" t="inlineStr"/>
@@ -16208,27 +16208,27 @@
       </c>
       <c r="B412" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-60</t>
-        </is>
-      </c>
-      <c r="C412" s="15" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-40</t>
+        </is>
+      </c>
+      <c r="C412" s="19" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D412" s="13" t="inlineStr">
         <is>
-          <t>Cari tombol Hapus pada batch yang masih berjalan</t>
+          <t>Baca voucher_payout_config sebagai Super Admin</t>
         </is>
       </c>
       <c r="E412" s="13" t="inlineStr">
         <is>
-          <t>Tidak ada — harus ditutup dulu</t>
+          <t>Kosong — kunci layanan tidak terbaca peran mana pun</t>
         </is>
       </c>
       <c r="F412" s="13" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-16</t>
         </is>
       </c>
       <c r="G412" s="13" t="inlineStr"/>
@@ -16243,27 +16243,27 @@
       </c>
       <c r="B413" s="17" t="inlineStr">
         <is>
-          <t>TC-VC-61</t>
-        </is>
-      </c>
-      <c r="C413" s="18" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TC-VC-41</t>
+        </is>
+      </c>
+      <c r="C413" s="20" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D413" s="16" t="inlineStr">
         <is>
-          <t>Tutup batch yang belum ada penebusnya, lalu hapus</t>
+          <t>Jalankan penjadwal sebelum function_url diisi</t>
         </is>
       </c>
       <c r="E413" s="16" t="inlineStr">
         <is>
-          <t>Terhapus; dananya kembali ke GL Total Saldo</t>
+          <t>Berjalan tanpa melakukan apa-apa, tanpa galat</t>
         </is>
       </c>
       <c r="F413" s="16" t="inlineStr">
         <is>
-          <t>F-VC-24</t>
+          <t>F-VC-17</t>
         </is>
       </c>
       <c r="G413" s="16" t="inlineStr"/>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="B414" s="14" t="inlineStr">
         <is>
-          <t>TC-VC-62</t>
+          <t>TC-VC-42</t>
         </is>
       </c>
       <c r="C414" s="15" t="inlineStr">
@@ -16288,17 +16288,17 @@
       </c>
       <c r="D414" s="13" t="inlineStr">
         <is>
-          <t>Periksa Kotak Masuk pelanggan sesudah batch dihapus</t>
+          <t>Bandingkan total sent dengan mutasi transfer di dashboard Xendit</t>
         </is>
       </c>
       <c r="E414" s="13" t="inlineStr">
         <is>
-          <t>Kabar vouche